--- a/rules/NEW-RULE/positive/01/data/new-rule-positive-01.xlsx
+++ b/rules/NEW-RULE/positive/01/data/new-rule-positive-01.xlsx
@@ -1,38 +1,145 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10222"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rich/Documents/github/core-contributor/rules/NEW-RULE/positive/01/data/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71311FF1-1FAD-3D49-A658-0BBB5926D5D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Library" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Datasets" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Library" sheetId="1" r:id="rId1"/>
+    <sheet name="Datasets" sheetId="2" r:id="rId2"/>
+    <sheet name="zz.xpt" sheetId="3" r:id="rId3"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="24">
+  <si>
+    <t>Product</t>
+  </si>
+  <si>
+    <t>Version</t>
+  </si>
+  <si>
+    <t>sdtmig</t>
+  </si>
+  <si>
+    <t>3-4</t>
+  </si>
+  <si>
+    <t>Filename</t>
+  </si>
+  <si>
+    <t>Label</t>
+  </si>
+  <si>
+    <t>STUDYID</t>
+  </si>
+  <si>
+    <t>DOMAIN</t>
+  </si>
+  <si>
+    <t>USUBJID</t>
+  </si>
+  <si>
+    <t>ZZSEQ</t>
+  </si>
+  <si>
+    <t>ZZTERM</t>
+  </si>
+  <si>
+    <t>Study Identifier</t>
+  </si>
+  <si>
+    <t>Domain Abbreviation</t>
+  </si>
+  <si>
+    <t>Unique Subject Identifier</t>
+  </si>
+  <si>
+    <t>Sequence Number</t>
+  </si>
+  <si>
+    <t>Reported Term</t>
+  </si>
+  <si>
+    <t>Char</t>
+  </si>
+  <si>
+    <t>Num</t>
+  </si>
+  <si>
+    <t>CDISCPILOT01</t>
+  </si>
+  <si>
+    <t>ZZ</t>
+  </si>
+  <si>
+    <t>Mild headache</t>
+  </si>
+  <si>
+    <t>CDISC001</t>
+  </si>
+  <si>
+    <t>zz.xpt</t>
+  </si>
+  <si>
+    <t>Custom Dataset</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor rgb="FFFFFFCC"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -47,81 +154,31 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+  <cellXfs count="4">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -409,36 +466,24 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Product</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Version</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>sdtmig</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>3-4</t>
-        </is>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" t="s">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -447,31 +492,122 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Filename</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Label</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
-      <c r="B2" t="inlineStr"/>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B2" t="s">
+        <v>23</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F7A6296-0816-9348-945A-3AEB3C865347}">
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="48" x14ac:dyDescent="0.2">
+      <c r="A2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A4" s="2">
+        <v>12</v>
+      </c>
+      <c r="B4" s="2">
+        <v>2</v>
+      </c>
+      <c r="C4" s="2">
+        <v>8</v>
+      </c>
+      <c r="D4" s="2">
+        <v>8</v>
+      </c>
+      <c r="E4" s="2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="32" x14ac:dyDescent="0.2">
+      <c r="A5" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D5" s="3">
+        <v>1</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/rules/NEW-RULE/positive/01/data/new-rule-positive-01.xlsx
+++ b/rules/NEW-RULE/positive/01/data/new-rule-positive-01.xlsx
@@ -1,38 +1,285 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10322"/>
+  <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rich/Documents/github/core-contributor/rules/NEW-RULE/positive/01/data/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F10155EE-D659-1A4A-BF74-1D0D9BFE67ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Library" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Datasets" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Library" sheetId="1" r:id="rId1"/>
+    <sheet name="Datasets" sheetId="2" r:id="rId2"/>
+    <sheet name="sv.xpt" sheetId="3" r:id="rId3"/>
+    <sheet name="tv.xpt" sheetId="4" r:id="rId4"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="72">
+  <si>
+    <t>Product</t>
+  </si>
+  <si>
+    <t>Version</t>
+  </si>
+  <si>
+    <t>sdtmig</t>
+  </si>
+  <si>
+    <t>3-4</t>
+  </si>
+  <si>
+    <t>Filename</t>
+  </si>
+  <si>
+    <t>Label</t>
+  </si>
+  <si>
+    <t>sv.xpt</t>
+  </si>
+  <si>
+    <t>Subject Visits</t>
+  </si>
+  <si>
+    <t>tv.xpt</t>
+  </si>
+  <si>
+    <t>Trial Visits</t>
+  </si>
+  <si>
+    <t>STUDYID</t>
+  </si>
+  <si>
+    <t>DOMAIN</t>
+  </si>
+  <si>
+    <t>USUBJID</t>
+  </si>
+  <si>
+    <t>SUBJID</t>
+  </si>
+  <si>
+    <t>VISITNUM</t>
+  </si>
+  <si>
+    <t>VISIT</t>
+  </si>
+  <si>
+    <t>EPOCH</t>
+  </si>
+  <si>
+    <t>SVSTDTC</t>
+  </si>
+  <si>
+    <t>SVENDTC</t>
+  </si>
+  <si>
+    <t>SVSTDY</t>
+  </si>
+  <si>
+    <t>SVENDY</t>
+  </si>
+  <si>
+    <t>SVUPDES</t>
+  </si>
+  <si>
+    <t>Study Identifier</t>
+  </si>
+  <si>
+    <t>Domain Abbreviation</t>
+  </si>
+  <si>
+    <t>Unique Subject Identifier</t>
+  </si>
+  <si>
+    <t>Subject Identifier for the Study</t>
+  </si>
+  <si>
+    <t>Visit Number</t>
+  </si>
+  <si>
+    <t>Visit Name</t>
+  </si>
+  <si>
+    <t>Epoch</t>
+  </si>
+  <si>
+    <t>Start Date/Time of Visit</t>
+  </si>
+  <si>
+    <t>End Date/Time of Visit</t>
+  </si>
+  <si>
+    <t>Study Day of Start of Visit</t>
+  </si>
+  <si>
+    <t>Study Day of End of Visit</t>
+  </si>
+  <si>
+    <t>Description of Unplanned Visit</t>
+  </si>
+  <si>
+    <t>Char</t>
+  </si>
+  <si>
+    <t>Num</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>CDISCPILOT01</t>
+  </si>
+  <si>
+    <t>SV</t>
+  </si>
+  <si>
+    <t>CDISC001</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>SCREENING</t>
+  </si>
+  <si>
+    <t>2021-04-27</t>
+  </si>
+  <si>
+    <t>-28</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>DAY 1</t>
+  </si>
+  <si>
+    <t>2021-05-01</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>DAY 2</t>
+  </si>
+  <si>
+    <t>YES</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>DAY 3</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>ARMCD</t>
+  </si>
+  <si>
+    <t>TVSTRL</t>
+  </si>
+  <si>
+    <t>TVENRL</t>
+  </si>
+  <si>
+    <t>Planned Arm Code</t>
+  </si>
+  <si>
+    <t>Visit Start Rule</t>
+  </si>
+  <si>
+    <t>Visit End Rule</t>
+  </si>
+  <si>
+    <t>52</t>
+  </si>
+  <si>
+    <t>TV</t>
+  </si>
+  <si>
+    <t>test</t>
+  </si>
+  <si>
+    <t>Screening</t>
+  </si>
+  <si>
+    <t>Day 2</t>
+  </si>
+  <si>
+    <t>Day 3</t>
+  </si>
+  <si>
+    <t>Day 4</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
-      <scheme val="minor"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor rgb="FFFFFFCC"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -47,81 +294,27 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+  <cellXfs count="4">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -200,6 +393,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -234,6 +428,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -268,20 +463,16 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="80000">
-              <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
+                <a:tint val="100000"/>
+                <a:shade val="100000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
+                <a:tint val="50000"/>
+                <a:shade val="100000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -403,75 +594,617 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
+  <a:objectDefaults>
+    <a:spDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="3">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </a:style>
+    </a:spDef>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
   <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Product</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Version</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>sdtmig</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>3-4</t>
-        </is>
+    <row r="1" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <ignoredErrors>
+    <ignoredError sqref="A1:B2" numberStoredAsText="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Filename</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Label</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
-      <c r="B2" t="inlineStr"/>
+    <row r="1" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>9</v>
+      </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <ignoredErrors>
+    <ignoredError sqref="A1:B3" numberStoredAsText="1"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:L8"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+      <c r="A1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" ht="64" x14ac:dyDescent="0.2">
+      <c r="A2" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A3" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A4" s="3">
+        <v>12</v>
+      </c>
+      <c r="B4" s="3">
+        <v>2</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="H4" s="3">
+        <v>10</v>
+      </c>
+      <c r="I4" s="3">
+        <v>8</v>
+      </c>
+      <c r="J4" s="3">
+        <v>8</v>
+      </c>
+      <c r="K4" s="3">
+        <v>8</v>
+      </c>
+      <c r="L4" s="3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+      <c r="A5" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="K5" s="1">
+        <v>1</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+      <c r="A6" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="L6" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+      <c r="A7" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="L7" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+      <c r="A8" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="L8" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+  <ignoredErrors>
+    <ignoredError sqref="A1:L4 A5:C8 E5:L8" numberStoredAsText="1"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:G8"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="48" x14ac:dyDescent="0.2">
+      <c r="A2" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A3" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A4" s="3">
+        <v>12</v>
+      </c>
+      <c r="B4" s="3">
+        <v>2</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A5" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A6" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A7" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A8" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <ignoredErrors>
+    <ignoredError sqref="A1:G5 A7:G8 A6:C6 E6:G6" numberStoredAsText="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
--- a/rules/NEW-RULE/positive/01/data/new-rule-positive-01.xlsx
+++ b/rules/NEW-RULE/positive/01/data/new-rule-positive-01.xlsx
@@ -555,7 +555,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H8"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="4" t="str">
@@ -662,28 +662,28 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="str">
+      <c r="A5" s="2" t="str">
         <v>CDISCPILOT01</v>
       </c>
-      <c r="B5" s="3" t="str">
+      <c r="B5" s="2" t="str">
         <v>CE</v>
       </c>
-      <c r="C5" s="3" t="str">
+      <c r="C5" s="2" t="str">
         <v>CDISC001</v>
       </c>
-      <c r="D5" s="3">
+      <c r="D5" s="2">
         <v>1</v>
       </c>
-      <c r="E5" s="3" t="str">
-        <v>LAST CONTACT</v>
-      </c>
-      <c r="F5" s="3" t="str">
+      <c r="E5" s="2" t="str">
         <v>DEATH</v>
       </c>
-      <c r="G5" s="3" t="str">
+      <c r="F5" s="2" t="str">
+        <v>DEATH</v>
+      </c>
+      <c r="G5" s="2" t="str">
         <v>CTCAE 4.03</v>
       </c>
-      <c r="H5" s="3" t="str">
+      <c r="H5" s="2" t="str">
         <v>GRADE 1</v>
       </c>
     </row>
@@ -695,22 +695,22 @@
         <v>CE</v>
       </c>
       <c r="C6" s="3" t="str">
-        <v>CDISC002</v>
+        <v>CDISC001</v>
       </c>
       <c r="D6" s="3">
         <v>2</v>
       </c>
       <c r="E6" s="3" t="str">
+        <v>LAST CONTACT</v>
+      </c>
+      <c r="F6" s="3" t="str">
         <v>DEATH</v>
-      </c>
-      <c r="F6" s="3" t="str">
-        <v>PROGRESSIVE DISEASE</v>
       </c>
       <c r="G6" s="3" t="str">
         <v>CTCAE 4.03</v>
       </c>
       <c r="H6" s="3" t="str">
-        <v>GRADE 2</v>
+        <v>GRADE 1</v>
       </c>
     </row>
     <row r="7">
@@ -721,27 +721,53 @@
         <v>CE</v>
       </c>
       <c r="C7" s="3" t="str">
-        <v>CDISC003</v>
+        <v>CDISC002</v>
       </c>
       <c r="D7" s="3">
         <v>3</v>
       </c>
       <c r="E7" s="3" t="str">
-        <v>COMPLETED</v>
+        <v>DEATH</v>
       </c>
       <c r="F7" s="3" t="str">
-        <v>Migraine</v>
+        <v>PROGRESSIVE DISEASE</v>
       </c>
       <c r="G7" s="3" t="str">
         <v>CTCAE 4.03</v>
       </c>
       <c r="H7" s="3" t="str">
+        <v>GRADE 2</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="str">
+        <v>CDISCPILOT01</v>
+      </c>
+      <c r="B8" s="3" t="str">
+        <v>CE</v>
+      </c>
+      <c r="C8" s="3" t="str">
+        <v>CDISC003</v>
+      </c>
+      <c r="D8" s="3">
+        <v>4</v>
+      </c>
+      <c r="E8" s="3" t="str">
+        <v>COMPLETED</v>
+      </c>
+      <c r="F8" s="3" t="str">
+        <v>Migraine</v>
+      </c>
+      <c r="G8" s="3" t="str">
+        <v>CTCAE 4.03</v>
+      </c>
+      <c r="H8" s="3" t="str">
         <v>GRADE 1</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H8"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/rules/NEW-RULE/positive/01/data/new-rule-positive-01.xlsx
+++ b/rules/NEW-RULE/positive/01/data/new-rule-positive-01.xlsx
@@ -5,6 +5,7 @@
   <sheets>
     <sheet name="Library" sheetId="1" r:id="rId1"/>
     <sheet name="Datasets" sheetId="2" r:id="rId2"/>
+    <sheet name="ta.xpt" sheetId="3" r:id="rId3"/>
   </sheets>
 </workbook>
 </file>
@@ -34,7 +35,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
   <numFmts count="0"/>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -43,8 +44,22 @@
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <i/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none">
         <bgColor/>
@@ -52,6 +67,12 @@
     </fill>
     <fill>
       <patternFill patternType="gray125">
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -75,10 +96,13 @@
   <cellStyleXfs>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="1" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -413,18 +437,18 @@
   <dimension ref="A1:B2"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="str">
+      <c r="A1" s="3" t="str">
         <v>Product</v>
       </c>
-      <c r="B1" s="2" t="str">
+      <c r="B1" s="3" t="str">
         <v>Version</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="str">
+      <c r="A2" s="3" t="str">
         <v>sdtmig</v>
       </c>
-      <c r="B2" s="2" t="str">
+      <c r="B2" s="3" t="str">
         <v>3-4</v>
       </c>
     </row>
@@ -440,11 +464,19 @@
   <dimension ref="A1:B2"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="str">
+      <c r="A1" s="3" t="str">
         <v>Filename</v>
       </c>
-      <c r="B1" s="2" t="str">
+      <c r="B1" s="3" t="str">
         <v>Label</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="str">
+        <v>ta.xpt</v>
+      </c>
+      <c r="B2" s="3" t="str">
+        <v>Trial Arms</v>
       </c>
     </row>
   </sheetData>
@@ -452,4 +484,399 @@
     <ignoredError numberStoredAsText="1" sqref="A1:B2"/>
   </ignoredErrors>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:J12"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="str">
+        <v>STUDYID</v>
+      </c>
+      <c r="B1" s="4" t="str">
+        <v>DOMAIN</v>
+      </c>
+      <c r="C1" s="4" t="str">
+        <v>ARMCD</v>
+      </c>
+      <c r="D1" s="4" t="str">
+        <v>ARM</v>
+      </c>
+      <c r="E1" s="4" t="str">
+        <v>TAETORD</v>
+      </c>
+      <c r="F1" s="4" t="str">
+        <v>ETCD</v>
+      </c>
+      <c r="G1" s="4" t="str">
+        <v>ELEMENT</v>
+      </c>
+      <c r="H1" s="4" t="str">
+        <v>TABRANCH</v>
+      </c>
+      <c r="I1" s="4" t="str">
+        <v>TATRANS</v>
+      </c>
+      <c r="J1" s="4" t="str">
+        <v>EPOCH</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="str">
+        <v>Study Identifier</v>
+      </c>
+      <c r="B2" s="5" t="str">
+        <v>Domain Abbreviation</v>
+      </c>
+      <c r="C2" s="5" t="str">
+        <v>Planned Arm Code</v>
+      </c>
+      <c r="D2" s="5" t="str">
+        <v>Description of Planned Arm</v>
+      </c>
+      <c r="E2" s="5" t="str">
+        <v>Planned Order of Element within Arm</v>
+      </c>
+      <c r="F2" s="5" t="str">
+        <v>Element Code</v>
+      </c>
+      <c r="G2" s="5" t="str">
+        <v>Description of Element</v>
+      </c>
+      <c r="H2" s="5" t="str">
+        <v>Branch</v>
+      </c>
+      <c r="I2" s="5" t="str">
+        <v>Transition Rule</v>
+      </c>
+      <c r="J2" s="5" t="str">
+        <v>Epoch</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="B3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="C3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="D3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="E3" s="5" t="str">
+        <v>Num</v>
+      </c>
+      <c r="F3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="G3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="H3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="I3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="J3" s="5" t="str">
+        <v>Char</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="str">
+        <v>12</v>
+      </c>
+      <c r="B4" s="5" t="str">
+        <v>2</v>
+      </c>
+      <c r="C4" s="5" t="str">
+        <v>8</v>
+      </c>
+      <c r="D4" s="5" t="str">
+        <v>28</v>
+      </c>
+      <c r="E4" s="5" t="str">
+        <v>8</v>
+      </c>
+      <c r="F4" s="5" t="str">
+        <v>7</v>
+      </c>
+      <c r="G4" s="5" t="str">
+        <v>26</v>
+      </c>
+      <c r="H4" s="5" t="str">
+        <v>200</v>
+      </c>
+      <c r="I4" s="5" t="str">
+        <v>200</v>
+      </c>
+      <c r="J4" s="5" t="str">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="str">
+        <v>CDISCPILOT01</v>
+      </c>
+      <c r="B5" s="3" t="str">
+        <v>TA</v>
+      </c>
+      <c r="C5" s="3" t="str">
+        <v>PLACEBO</v>
+      </c>
+      <c r="D5" s="3" t="str">
+        <v>Placebo</v>
+      </c>
+      <c r="E5" s="3" t="str">
+        <v>1</v>
+      </c>
+      <c r="F5" s="3" t="str">
+        <v>SCREEN</v>
+      </c>
+      <c r="G5" s="3" t="str">
+        <v>Screening</v>
+      </c>
+      <c r="H5" s="3" t="str">
+        <v>Randomized to Placebo</v>
+      </c>
+      <c r="I5" s="3" t="str">
+        <v/>
+      </c>
+      <c r="J5" s="3" t="str">
+        <v>SCREENING</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="str">
+        <v>CDISCPILOT01</v>
+      </c>
+      <c r="B6" s="3" t="str">
+        <v>TA</v>
+      </c>
+      <c r="C6" s="3" t="str">
+        <v>PLACEBO</v>
+      </c>
+      <c r="D6" s="3" t="str">
+        <v>Placebo</v>
+      </c>
+      <c r="E6" s="3" t="str">
+        <v>2</v>
+      </c>
+      <c r="F6" s="3" t="str">
+        <v>PLACEBO</v>
+      </c>
+      <c r="G6" s="3" t="str">
+        <v>Placebo</v>
+      </c>
+      <c r="H6" s="3" t="str">
+        <v/>
+      </c>
+      <c r="I6" s="3" t="str">
+        <v/>
+      </c>
+      <c r="J6" s="3" t="str">
+        <v>TREATMENT</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="str">
+        <v>CDISCPILOT01</v>
+      </c>
+      <c r="B7" s="3" t="str">
+        <v>TA</v>
+      </c>
+      <c r="C7" s="3" t="str">
+        <v>ZAN_LOW</v>
+      </c>
+      <c r="D7" s="3" t="str">
+        <v>Zanomaline Low Dose (54 mg)</v>
+      </c>
+      <c r="E7" s="3" t="str">
+        <v>1</v>
+      </c>
+      <c r="F7" s="3" t="str">
+        <v>SCREEN</v>
+      </c>
+      <c r="G7" s="3" t="str">
+        <v>Screening</v>
+      </c>
+      <c r="H7" s="3" t="str">
+        <v>Randomized to Zanomaline Low Dose</v>
+      </c>
+      <c r="I7" s="3" t="str">
+        <v/>
+      </c>
+      <c r="J7" s="3" t="str">
+        <v>SCREENING</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="str">
+        <v>CDISCPILOT01</v>
+      </c>
+      <c r="B8" s="3" t="str">
+        <v>TA</v>
+      </c>
+      <c r="C8" s="3" t="str">
+        <v>ZAN_LOW</v>
+      </c>
+      <c r="D8" s="3" t="str">
+        <v>Zanomaline Low Dose (54 mg)</v>
+      </c>
+      <c r="E8" s="3" t="str">
+        <v>2</v>
+      </c>
+      <c r="F8" s="3" t="str">
+        <v>LOW</v>
+      </c>
+      <c r="G8" s="3" t="str">
+        <v>Zanomaline 54 mg</v>
+      </c>
+      <c r="H8" s="3" t="str">
+        <v/>
+      </c>
+      <c r="I8" s="3" t="str">
+        <v/>
+      </c>
+      <c r="J8" s="3" t="str">
+        <v>TREATMENT</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="str">
+        <v>CDISCPILOT01</v>
+      </c>
+      <c r="B9" s="3" t="str">
+        <v>TA</v>
+      </c>
+      <c r="C9" s="3" t="str">
+        <v>ZAN_HIGH</v>
+      </c>
+      <c r="D9" s="3" t="str">
+        <v>Zanomaline High Dose (81 mg)</v>
+      </c>
+      <c r="E9" s="3" t="str">
+        <v>1</v>
+      </c>
+      <c r="F9" s="3" t="str">
+        <v>SCREEN</v>
+      </c>
+      <c r="G9" s="3" t="str">
+        <v>Screening</v>
+      </c>
+      <c r="H9" s="3" t="str">
+        <v>Randomized to Zanomaline High Dose</v>
+      </c>
+      <c r="I9" s="3" t="str">
+        <v/>
+      </c>
+      <c r="J9" s="3" t="str">
+        <v>SCREENING</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="str">
+        <v>CDISCPILOT01</v>
+      </c>
+      <c r="B10" s="3" t="str">
+        <v>TA</v>
+      </c>
+      <c r="C10" s="3" t="str">
+        <v>ZAN_HIGH</v>
+      </c>
+      <c r="D10" s="3" t="str">
+        <v>Zanomaline High Dose (81 mg)</v>
+      </c>
+      <c r="E10" s="3">
+        <v>2</v>
+      </c>
+      <c r="F10" s="3" t="str">
+        <v>TITRATE</v>
+      </c>
+      <c r="G10" s="3" t="str">
+        <v>Zanomaline 54 mg Titration</v>
+      </c>
+      <c r="H10" s="3" t="str">
+        <v/>
+      </c>
+      <c r="I10" s="3" t="str">
+        <v/>
+      </c>
+      <c r="J10" s="3" t="str">
+        <v>TREATMENT</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="str">
+        <v>CDISCPILOT01</v>
+      </c>
+      <c r="B11" s="3" t="str">
+        <v>TA</v>
+      </c>
+      <c r="C11" s="3" t="str">
+        <v>ZAN_HIGH</v>
+      </c>
+      <c r="D11" s="3" t="str">
+        <v>Zanomaline High Dose (81 mg)</v>
+      </c>
+      <c r="E11" s="3">
+        <v>3</v>
+      </c>
+      <c r="F11" s="3" t="str">
+        <v>HIGH</v>
+      </c>
+      <c r="G11" s="3" t="str">
+        <v>Zanomaline 81 mg</v>
+      </c>
+      <c r="H11" s="3" t="str">
+        <v/>
+      </c>
+      <c r="I11" s="3" t="str">
+        <v/>
+      </c>
+      <c r="J11" s="3" t="str">
+        <v>TREATMENT</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="str">
+        <v>CDISCPILOT01</v>
+      </c>
+      <c r="B12" s="3" t="str">
+        <v>TA</v>
+      </c>
+      <c r="C12" s="3" t="str">
+        <v>ZAN_HIGH</v>
+      </c>
+      <c r="D12" s="3" t="str">
+        <v>Zanomaline High Dose (81 mg)</v>
+      </c>
+      <c r="E12" s="3" t="str">
+        <v>4</v>
+      </c>
+      <c r="F12" s="3" t="str">
+        <v>TITRATE</v>
+      </c>
+      <c r="G12" s="3" t="str">
+        <v>Zanomaline 54 mg Titration</v>
+      </c>
+      <c r="H12" s="3" t="str">
+        <v/>
+      </c>
+      <c r="I12" s="3" t="str">
+        <v/>
+      </c>
+      <c r="J12" s="3" t="str">
+        <v>TREATMENT</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:J12"/>
+  </ignoredErrors>
+</worksheet>
 </file>
--- a/rules/NEW-RULE/positive/01/data/new-rule-positive-01.xlsx
+++ b/rules/NEW-RULE/positive/01/data/new-rule-positive-01.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rich/Documents/github/core-contributor/rules/NEW-RULE/positive/01/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F10155EE-D659-1A4A-BF74-1D0D9BFE67ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{618545CC-A684-D04C-AD3A-5458C4E3C3B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="71">
   <si>
     <t>Product</t>
   </si>
@@ -157,6 +157,9 @@
     <t>CDISC001</t>
   </si>
   <si>
+    <t/>
+  </si>
+  <si>
     <t>1</t>
   </si>
   <si>
@@ -169,9 +172,6 @@
     <t>-28</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>2</t>
   </si>
   <si>
@@ -185,9 +185,6 @@
   </si>
   <si>
     <t>DAY 2</t>
-  </si>
-  <si>
-    <t>YES</t>
   </si>
   <si>
     <t>4</t>
@@ -278,7 +275,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
-        <bgColor rgb="FFFFFFCC"/>
       </patternFill>
     </fill>
   </fills>
@@ -298,9 +294,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -747,7 +741,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="64" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:12" ht="15" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
         <v>22</v>
       </c>
@@ -785,7 +779,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:12" ht="15" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
         <v>34</v>
       </c>
@@ -823,7 +817,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:12" ht="15" x14ac:dyDescent="0.2">
       <c r="A4" s="3">
         <v>12</v>
       </c>
@@ -871,31 +865,31 @@
       <c r="C5" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D5" s="1"/>
+      <c r="D5" s="1" t="s">
+        <v>44</v>
+      </c>
       <c r="E5" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K5" s="1">
         <v>1</v>
       </c>
-      <c r="L5" s="1" t="s">
-        <v>48</v>
-      </c>
+      <c r="L5" s="1"/>
     </row>
     <row r="6" spans="1:12" ht="15" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
@@ -907,7 +901,9 @@
       <c r="C6" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D6" s="1"/>
+      <c r="D6" s="1" t="s">
+        <v>44</v>
+      </c>
       <c r="E6" s="1" t="s">
         <v>49</v>
       </c>
@@ -915,7 +911,7 @@
         <v>50</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H6" s="1" t="s">
         <v>51</v>
@@ -924,14 +920,12 @@
         <v>51</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="L6" s="1" t="s">
-        <v>48</v>
-      </c>
+        <v>44</v>
+      </c>
+      <c r="L6" s="1"/>
     </row>
     <row r="7" spans="1:12" ht="15" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
@@ -943,7 +937,9 @@
       <c r="C7" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D7" s="1"/>
+      <c r="D7" s="1" t="s">
+        <v>44</v>
+      </c>
       <c r="E7" s="1" t="s">
         <v>52</v>
       </c>
@@ -951,23 +947,21 @@
         <v>53</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="L7" s="1" t="s">
-        <v>54</v>
-      </c>
+        <v>44</v>
+      </c>
+      <c r="L7" s="1"/>
     </row>
     <row r="8" spans="1:12" ht="15" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
@@ -979,12 +973,14 @@
       <c r="C8" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D8" s="1"/>
+      <c r="D8" s="1" t="s">
+        <v>44</v>
+      </c>
       <c r="E8" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="F8" s="1" t="s">
         <v>55</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>56</v>
       </c>
       <c r="G8" s="1" t="s">
         <v>37</v>
@@ -993,23 +989,20 @@
         <v>38</v>
       </c>
       <c r="I8" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="J8" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="J8" s="1" t="s">
-        <v>58</v>
-      </c>
       <c r="K8" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="L8" s="1" t="s">
-        <v>48</v>
-      </c>
+        <v>44</v>
+      </c>
+      <c r="L8" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:L4 A5:C8 E5:L8" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:L4 A8:K8 A7:K7 A6:K6 A5:K5" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1033,16 +1026,16 @@
         <v>15</v>
       </c>
       <c r="E1" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="G1" s="2" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="48" x14ac:dyDescent="0.2">
+    </row>
+    <row r="2" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
         <v>22</v>
       </c>
@@ -1056,16 +1049,16 @@
         <v>27</v>
       </c>
       <c r="E2" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="F2" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="G2" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="G2" s="3" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    </row>
+    <row r="3" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
         <v>34</v>
       </c>
@@ -1088,7 +1081,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A4" s="3">
         <v>12</v>
       </c>
@@ -1099,16 +1092,16 @@
         <v>38</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -1116,22 +1109,22 @@
         <v>41</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="E5" s="1" t="s">
+      <c r="F5" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="F5" s="1" t="s">
-        <v>68</v>
-      </c>
       <c r="G5" s="1" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -1139,20 +1132,22 @@
         <v>41</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="D6" s="1"/>
+      <c r="D6" s="1" t="s">
+        <v>44</v>
+      </c>
       <c r="E6" s="1" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -1160,22 +1155,22 @@
         <v>41</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -1183,28 +1178,28 @@
         <v>41</v>
       </c>
       <c r="B8" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E8" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="C8" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>67</v>
-      </c>
       <c r="F8" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:G5 A7:G8 A6:C6 E6:G6" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:G8" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/rules/NEW-RULE/positive/01/data/new-rule-positive-01.xlsx
+++ b/rules/NEW-RULE/positive/01/data/new-rule-positive-01.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rich/Documents/github/core-contributor/rules/NEW-RULE/positive/01/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02658698-611A-CC47-8146-846E44257FE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7DBC523-E00B-AD43-9CF3-C3D304F8C972}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="660" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{2322A04D-5CB7-449F-8225-CADE54871F75}"/>
   </bookViews>
@@ -609,7 +609,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -677,12 +677,36 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD9D9D9"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FFD9D9D9"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD9D9D9"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD9D9D9"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -704,6 +728,24 @@
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -775,42 +817,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{2B2B045E-C057-41A4-97C8-E2239EA30542}" name="Table1" displayName="Table1" ref="A1:AA10" totalsRowShown="0">
-  <autoFilter ref="A1:AA10" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
-  <tableColumns count="27">
-    <tableColumn id="1" xr3:uid="{A51B5D23-83F9-4966-91FB-77832346D550}" name="STUDYID"/>
-    <tableColumn id="2" xr3:uid="{282CCFD6-463F-4916-AD9B-6CCEBF1EEF0D}" name="DOMAIN"/>
-    <tableColumn id="3" xr3:uid="{2BCF845F-FD8E-4372-8298-92893C0AA6AF}" name="USUBJID"/>
-    <tableColumn id="4" xr3:uid="{54365052-A4A2-46CB-BC04-54B6DF6ECAF4}" name="AESEQ"/>
-    <tableColumn id="5" xr3:uid="{81929F9D-5824-4C61-80FA-84E5E080AD6F}" name="AESPID"/>
-    <tableColumn id="6" xr3:uid="{EE3DC8C2-84BC-4C2B-B660-5D17BA98D889}" name="AETERM"/>
-    <tableColumn id="7" xr3:uid="{04D4AAE6-3EF3-4171-B242-A2953C04EC5E}" name="AELLT"/>
-    <tableColumn id="8" xr3:uid="{3D80802C-E824-4024-B16C-63057D19B9CF}" name="AELLTCD"/>
-    <tableColumn id="9" xr3:uid="{08CDBB46-C107-468B-B51F-E29F9A9B6187}" name="AEDECOD"/>
-    <tableColumn id="10" xr3:uid="{2A3FA141-C895-4763-A690-4D354CD17430}" name="AEPTCD"/>
-    <tableColumn id="11" xr3:uid="{08F8B456-8AFB-482E-BB62-C03259B7A143}" name="AEHLT"/>
-    <tableColumn id="12" xr3:uid="{987CB0C4-36F9-40B1-AC60-397ABD32C955}" name="AEHLTCD"/>
-    <tableColumn id="13" xr3:uid="{22842CE3-82EB-43D1-8AB6-0453D30441FD}" name="AEHLGT"/>
-    <tableColumn id="14" xr3:uid="{0C9FCF86-5EE3-4882-8913-B0934170FB0A}" name="AEHLGTCD"/>
-    <tableColumn id="15" xr3:uid="{CE4EB7CE-3D7C-4E43-8AD6-0F84DE6B4875}" name="AEBODSYS"/>
-    <tableColumn id="16" xr3:uid="{4E087C6C-C752-4D2E-9D49-E550F546FCB4}" name="AEBDSYCD"/>
-    <tableColumn id="17" xr3:uid="{FB3B4742-A36B-4441-B75A-49A74B282B3E}" name="AESOC"/>
-    <tableColumn id="18" xr3:uid="{8768CC9C-5555-45BA-8C9E-1943141D8414}" name="AESOCCD"/>
-    <tableColumn id="19" xr3:uid="{27D57A53-3CE6-4C6F-9EB9-4FA6174354F4}" name="AESEV"/>
-    <tableColumn id="20" xr3:uid="{42659A46-15FF-4C6F-90C2-F3A704B1779B}" name="AESER"/>
-    <tableColumn id="21" xr3:uid="{B7C28C65-2162-4D80-B6AB-5C8E79DEA352}" name="AEACN"/>
-    <tableColumn id="22" xr3:uid="{E3206E3E-1266-4C0E-B726-48A1C75F1F7B}" name="AEREL"/>
-    <tableColumn id="23" xr3:uid="{8F431BD7-5BC3-4F11-A416-D4F26152D612}" name="AEOUT"/>
-    <tableColumn id="24" xr3:uid="{6B531839-34BA-40FB-BE84-9445412F7DC5}" name="AESHOSP"/>
-    <tableColumn id="25" xr3:uid="{DA79344C-AAF5-408B-8EB6-B3DF01264286}" name="AESTDTC"/>
-    <tableColumn id="26" xr3:uid="{D308A395-305A-4F5C-B928-35E525B536E6}" name="AEENDTC"/>
-    <tableColumn id="27" xr3:uid="{697DA2FC-F247-46CE-86F5-90373BAB8219}" name="AESTDY"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1779,334 +1785,334 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" ht="16" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="Q1" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="R1" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="S1" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="T1" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="U1" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="V1" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="W1" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="X1" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Y1" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="Z1" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AA1" s="10" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="2" spans="1:27" ht="32" x14ac:dyDescent="0.2">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="G2" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="H2" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="I2" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="J2" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="K2" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="L2" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="M2" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="N2" s="1" t="s">
+      <c r="N2" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="O2" s="1" t="s">
+      <c r="O2" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="P2" s="1" t="s">
+      <c r="P2" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="Q2" s="1" t="s">
+      <c r="Q2" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="R2" s="1" t="s">
+      <c r="R2" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="S2" s="1" t="s">
+      <c r="S2" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="T2" s="1" t="s">
+      <c r="T2" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="U2" s="1" t="s">
+      <c r="U2" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="V2" s="1" t="s">
+      <c r="V2" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="W2" s="1" t="s">
+      <c r="W2" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="X2" s="1" t="s">
+      <c r="X2" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="Y2" s="1" t="s">
+      <c r="Y2" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="Z2" s="1" t="s">
+      <c r="Z2" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="AA2" s="1" t="s">
+      <c r="AA2" s="12" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="3" spans="1:27" ht="16" x14ac:dyDescent="0.2">
-      <c r="A3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D3" s="1" t="s">
+      <c r="A3" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="E3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="H3" s="1" t="s">
+      <c r="E3" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="F3" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="G3" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="H3" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="I3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="J3" s="1" t="s">
+      <c r="I3" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="J3" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="K3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="L3" s="1" t="s">
+      <c r="K3" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="L3" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="M3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="N3" s="1" t="s">
+      <c r="M3" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="N3" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="O3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="P3" s="1" t="s">
+      <c r="O3" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="P3" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="Q3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="R3" s="1" t="s">
+      <c r="Q3" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="R3" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="S3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="T3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="U3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="V3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="W3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="X3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA3" s="1" t="s">
+      <c r="S3" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="T3" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="U3" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="V3" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="W3" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="X3" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y3" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z3" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA3" s="14" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A4" s="1">
+      <c r="A4" s="11">
         <v>10</v>
       </c>
-      <c r="B4" s="1">
+      <c r="B4" s="11">
         <v>2</v>
       </c>
-      <c r="C4" s="1">
+      <c r="C4" s="11">
         <v>14</v>
       </c>
-      <c r="D4" s="1">
+      <c r="D4" s="11">
         <v>8</v>
       </c>
-      <c r="E4" s="1">
-        <v>4</v>
-      </c>
-      <c r="F4" s="1">
+      <c r="E4" s="11">
+        <v>4</v>
+      </c>
+      <c r="F4" s="11">
         <v>38</v>
       </c>
-      <c r="G4" s="1">
+      <c r="G4" s="11">
         <v>38</v>
       </c>
-      <c r="H4" s="1">
+      <c r="H4" s="11">
         <v>8</v>
       </c>
-      <c r="I4" s="1">
+      <c r="I4" s="11">
         <v>38</v>
       </c>
-      <c r="J4" s="1">
+      <c r="J4" s="11">
         <v>8</v>
       </c>
-      <c r="K4" s="1">
+      <c r="K4" s="11">
         <v>65</v>
       </c>
-      <c r="L4" s="1">
+      <c r="L4" s="11">
         <v>8</v>
       </c>
-      <c r="M4" s="1">
+      <c r="M4" s="11">
         <v>55</v>
       </c>
-      <c r="N4" s="1">
+      <c r="N4" s="11">
         <v>8</v>
       </c>
-      <c r="O4" s="1">
+      <c r="O4" s="11">
         <v>52</v>
       </c>
-      <c r="P4" s="1">
+      <c r="P4" s="11">
         <v>8</v>
       </c>
-      <c r="Q4" s="1">
+      <c r="Q4" s="11">
         <v>52</v>
       </c>
-      <c r="R4" s="1">
+      <c r="R4" s="11">
         <v>8</v>
       </c>
-      <c r="S4" s="1">
+      <c r="S4" s="11">
         <v>8</v>
       </c>
-      <c r="T4" s="1">
+      <c r="T4" s="11">
         <v>1</v>
       </c>
-      <c r="U4" s="1">
+      <c r="U4" s="11">
         <v>1</v>
       </c>
-      <c r="V4" s="1">
+      <c r="V4" s="11">
         <v>1</v>
       </c>
-      <c r="W4" s="1">
+      <c r="W4" s="11">
         <v>26</v>
       </c>
-      <c r="X4" s="1">
+      <c r="X4" s="11">
         <v>1</v>
       </c>
-      <c r="Y4" s="1">
+      <c r="Y4" s="11">
         <v>10</v>
       </c>
-      <c r="Z4" s="1">
+      <c r="Z4" s="11">
         <v>1</v>
       </c>
-      <c r="AA4" s="1">
+      <c r="AA4" s="12">
         <v>8</v>
       </c>
     </row>
@@ -2561,27 +2567,24 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="1">
-    <tablePart r:id="rId1"/>
-  </tableParts>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <Comment xmlns="9dee18c2-6da5-44c1-913e-bf7f393fe0e8" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <Comment xmlns="9dee18c2-6da5-44c1-913e-bf7f393fe0e8" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2808,19 +2811,19 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D96E9815-3E38-457E-AC60-BC705C73AD1F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D3513D4C-5F93-4AB4-B899-280E533C715E}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="9dee18c2-6da5-44c1-913e-bf7f393fe0e8"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D96E9815-3E38-457E-AC60-BC705C73AD1F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/rules/NEW-RULE/positive/01/data/new-rule-positive-01.xlsx
+++ b/rules/NEW-RULE/positive/01/data/new-rule-positive-01.xlsx
@@ -35,7 +35,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
   <numFmts count="0"/>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -58,8 +58,13 @@
       <name val="Calibri"/>
       <i/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <i/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none">
         <bgColor/>
@@ -67,6 +72,12 @@
     </fill>
     <fill>
       <patternFill patternType="gray125">
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFCC"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -96,13 +107,14 @@
   <cellStyleXfs>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="1" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -529,104 +541,104 @@
       <c r="A2" s="5" t="str">
         <v>Study Identifier</v>
       </c>
-      <c r="B2" s="5" t="str">
+      <c r="B2" s="6" t="str">
         <v>Domain Abbreviation</v>
       </c>
-      <c r="C2" s="5" t="str">
+      <c r="C2" s="6" t="str">
         <v>Sequence Number</v>
       </c>
-      <c r="D2" s="5" t="str">
+      <c r="D2" s="6" t="str">
         <v>Group ID</v>
       </c>
-      <c r="E2" s="5" t="str">
+      <c r="E2" s="6" t="str">
         <v>Trial Summary Parameter Short Name</v>
       </c>
-      <c r="F2" s="5" t="str">
+      <c r="F2" s="6" t="str">
         <v>Trial Summary Parameter</v>
       </c>
-      <c r="G2" s="5" t="str">
+      <c r="G2" s="6" t="str">
         <v>Parameter Value</v>
       </c>
-      <c r="H2" s="5" t="str">
+      <c r="H2" s="6" t="str">
         <v>Parameter Null Flavor</v>
       </c>
-      <c r="I2" s="5" t="str">
+      <c r="I2" s="6" t="str">
         <v>Parameter Value Code</v>
       </c>
-      <c r="J2" s="5" t="str">
+      <c r="J2" s="6" t="str">
         <v>Name of the Reference Terminology</v>
       </c>
-      <c r="K2" s="5" t="str">
+      <c r="K2" s="6" t="str">
         <v>Version of the Reference Terminology</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="str">
-        <v>Char</v>
-      </c>
-      <c r="B3" s="5" t="str">
-        <v>Char</v>
-      </c>
-      <c r="C3" s="5" t="str">
+      <c r="A3" s="6" t="str">
+        <v>Char</v>
+      </c>
+      <c r="B3" s="6" t="str">
+        <v>Char</v>
+      </c>
+      <c r="C3" s="6" t="str">
         <v>Num</v>
       </c>
-      <c r="D3" s="5" t="str">
-        <v>Char</v>
-      </c>
-      <c r="E3" s="5" t="str">
-        <v>Char</v>
-      </c>
-      <c r="F3" s="5" t="str">
-        <v>Char</v>
-      </c>
-      <c r="G3" s="5" t="str">
-        <v>Char</v>
-      </c>
-      <c r="H3" s="5" t="str">
-        <v>Char</v>
-      </c>
-      <c r="I3" s="5" t="str">
-        <v>Char</v>
-      </c>
-      <c r="J3" s="5" t="str">
-        <v>Char</v>
-      </c>
-      <c r="K3" s="5" t="str">
+      <c r="D3" s="6" t="str">
+        <v>Char</v>
+      </c>
+      <c r="E3" s="6" t="str">
+        <v>Char</v>
+      </c>
+      <c r="F3" s="6" t="str">
+        <v>Char</v>
+      </c>
+      <c r="G3" s="6" t="str">
+        <v>Char</v>
+      </c>
+      <c r="H3" s="6" t="str">
+        <v>Char</v>
+      </c>
+      <c r="I3" s="6" t="str">
+        <v>Char</v>
+      </c>
+      <c r="J3" s="6" t="str">
+        <v>Char</v>
+      </c>
+      <c r="K3" s="6" t="str">
         <v>Char</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5">
+      <c r="A4" s="6">
         <v>10</v>
       </c>
-      <c r="B4" s="5">
+      <c r="B4" s="6">
         <v>2</v>
       </c>
-      <c r="C4" s="5">
+      <c r="C4" s="6">
         <v>8</v>
       </c>
-      <c r="D4" s="5">
+      <c r="D4" s="6">
         <v>5</v>
       </c>
-      <c r="E4" s="5">
+      <c r="E4" s="6">
         <v>8</v>
       </c>
-      <c r="F4" s="5">
+      <c r="F4" s="6">
         <v>40</v>
       </c>
-      <c r="G4" s="5">
+      <c r="G4" s="6">
         <v>149</v>
       </c>
-      <c r="H4" s="5">
+      <c r="H4" s="6">
         <v>2</v>
       </c>
-      <c r="I4" s="5">
+      <c r="I4" s="6">
         <v>11</v>
       </c>
-      <c r="J4" s="5">
+      <c r="J4" s="6">
         <v>18</v>
       </c>
-      <c r="K4" s="5">
+      <c r="K4" s="6">
         <v>10</v>
       </c>
     </row>
@@ -650,7 +662,10 @@
         <v>Extension Trial Indicator</v>
       </c>
       <c r="G5" s="4" t="str">
-        <v>CEROUS SALICYLATE</v>
+        <v>UNIITERM1</v>
+      </c>
+      <c r="I5" s="2" t="str">
+        <v>00000UNII1</v>
       </c>
     </row>
   </sheetData>

--- a/rules/NEW-RULE/positive/01/data/new-rule-positive-01.xlsx
+++ b/rules/NEW-RULE/positive/01/data/new-rule-positive-01.xlsx
@@ -35,7 +35,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
   <numFmts count="0"/>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -58,13 +58,8 @@
       <name val="Calibri"/>
       <i/>
     </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <i/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none">
         <bgColor/>
@@ -72,12 +67,6 @@
     </fill>
     <fill>
       <patternFill patternType="gray125">
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFCC"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -107,14 +96,13 @@
   <cellStyleXfs>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="1" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -541,104 +529,104 @@
       <c r="A2" s="5" t="str">
         <v>Study Identifier</v>
       </c>
-      <c r="B2" s="6" t="str">
+      <c r="B2" s="5" t="str">
         <v>Domain Abbreviation</v>
       </c>
-      <c r="C2" s="6" t="str">
+      <c r="C2" s="5" t="str">
         <v>Sequence Number</v>
       </c>
-      <c r="D2" s="6" t="str">
+      <c r="D2" s="5" t="str">
         <v>Group ID</v>
       </c>
-      <c r="E2" s="6" t="str">
+      <c r="E2" s="5" t="str">
         <v>Trial Summary Parameter Short Name</v>
       </c>
-      <c r="F2" s="6" t="str">
+      <c r="F2" s="5" t="str">
         <v>Trial Summary Parameter</v>
       </c>
-      <c r="G2" s="6" t="str">
+      <c r="G2" s="5" t="str">
         <v>Parameter Value</v>
       </c>
-      <c r="H2" s="6" t="str">
+      <c r="H2" s="5" t="str">
         <v>Parameter Null Flavor</v>
       </c>
-      <c r="I2" s="6" t="str">
+      <c r="I2" s="5" t="str">
         <v>Parameter Value Code</v>
       </c>
-      <c r="J2" s="6" t="str">
+      <c r="J2" s="5" t="str">
         <v>Name of the Reference Terminology</v>
       </c>
-      <c r="K2" s="6" t="str">
+      <c r="K2" s="5" t="str">
         <v>Version of the Reference Terminology</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="B3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="C3" s="6" t="str">
+      <c r="A3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="B3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="C3" s="5" t="str">
         <v>Num</v>
       </c>
-      <c r="D3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="E3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="F3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="G3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="H3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="I3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="J3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="K3" s="6" t="str">
+      <c r="D3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="E3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="F3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="G3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="H3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="I3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="J3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="K3" s="5" t="str">
         <v>Char</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6">
+      <c r="A4" s="5">
         <v>10</v>
       </c>
-      <c r="B4" s="6">
+      <c r="B4" s="5">
         <v>2</v>
       </c>
-      <c r="C4" s="6">
+      <c r="C4" s="5">
         <v>8</v>
       </c>
-      <c r="D4" s="6">
+      <c r="D4" s="5">
         <v>5</v>
       </c>
-      <c r="E4" s="6">
+      <c r="E4" s="5">
         <v>8</v>
       </c>
-      <c r="F4" s="6">
+      <c r="F4" s="5">
         <v>40</v>
       </c>
-      <c r="G4" s="6">
+      <c r="G4" s="5">
         <v>149</v>
       </c>
-      <c r="H4" s="6">
+      <c r="H4" s="5">
         <v>2</v>
       </c>
-      <c r="I4" s="6">
+      <c r="I4" s="5">
         <v>11</v>
       </c>
-      <c r="J4" s="6">
+      <c r="J4" s="5">
         <v>18</v>
       </c>
-      <c r="K4" s="6">
+      <c r="K4" s="5">
         <v>10</v>
       </c>
     </row>
@@ -656,7 +644,7 @@
         <v/>
       </c>
       <c r="E5" s="4" t="str">
-        <v>CURTRT</v>
+        <v>COMPTRT</v>
       </c>
       <c r="F5" s="4" t="str">
         <v>Extension Trial Indicator</v>
@@ -664,7 +652,10 @@
       <c r="G5" s="4" t="str">
         <v>UNIITERM1</v>
       </c>
-      <c r="I5" s="2" t="str">
+      <c r="H5" s="2" t="str">
+        <v/>
+      </c>
+      <c r="I5" s="4" t="str">
         <v>00000UNII1</v>
       </c>
     </row>

--- a/rules/NEW-RULE/positive/01/data/new-rule-positive-01.xlsx
+++ b/rules/NEW-RULE/positive/01/data/new-rule-positive-01.xlsx
@@ -656,15 +656,18 @@
         <v/>
       </c>
       <c r="E5" s="4" t="str">
-        <v>CURTRT</v>
+        <v>TRT</v>
       </c>
       <c r="F5" s="4" t="str">
         <v>Extension Trial Indicator</v>
       </c>
       <c r="G5" s="4" t="str">
-        <v>UNIITERM1</v>
-      </c>
-      <c r="I5" s="2" t="str">
+        <v>DI(DEHYDROABIETYL)AMINE ACETATE</v>
+      </c>
+      <c r="H5" s="2" t="str">
+        <v/>
+      </c>
+      <c r="I5" s="4" t="str">
         <v>00000UNII1</v>
       </c>
     </row>

--- a/rules/NEW-RULE/positive/01/data/new-rule-positive-01.xlsx
+++ b/rules/NEW-RULE/positive/01/data/new-rule-positive-01.xlsx
@@ -35,7 +35,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
   <numFmts count="0"/>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -58,13 +58,8 @@
       <name val="Calibri"/>
       <i/>
     </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <i/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none">
         <bgColor/>
@@ -72,12 +67,6 @@
     </fill>
     <fill>
       <patternFill patternType="gray125">
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFCC"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -107,14 +96,13 @@
   <cellStyleXfs>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="1" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -541,104 +529,104 @@
       <c r="A2" s="5" t="str">
         <v>Study Identifier</v>
       </c>
-      <c r="B2" s="6" t="str">
+      <c r="B2" s="5" t="str">
         <v>Domain Abbreviation</v>
       </c>
-      <c r="C2" s="6" t="str">
+      <c r="C2" s="5" t="str">
         <v>Sequence Number</v>
       </c>
-      <c r="D2" s="6" t="str">
+      <c r="D2" s="5" t="str">
         <v>Group ID</v>
       </c>
-      <c r="E2" s="6" t="str">
+      <c r="E2" s="5" t="str">
         <v>Trial Summary Parameter Short Name</v>
       </c>
-      <c r="F2" s="6" t="str">
+      <c r="F2" s="5" t="str">
         <v>Trial Summary Parameter</v>
       </c>
-      <c r="G2" s="6" t="str">
+      <c r="G2" s="5" t="str">
         <v>Parameter Value</v>
       </c>
-      <c r="H2" s="6" t="str">
+      <c r="H2" s="5" t="str">
         <v>Parameter Null Flavor</v>
       </c>
-      <c r="I2" s="6" t="str">
+      <c r="I2" s="5" t="str">
         <v>Parameter Value Code</v>
       </c>
-      <c r="J2" s="6" t="str">
+      <c r="J2" s="5" t="str">
         <v>Name of the Reference Terminology</v>
       </c>
-      <c r="K2" s="6" t="str">
+      <c r="K2" s="5" t="str">
         <v>Version of the Reference Terminology</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="B3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="C3" s="6" t="str">
+      <c r="A3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="B3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="C3" s="5" t="str">
         <v>Num</v>
       </c>
-      <c r="D3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="E3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="F3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="G3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="H3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="I3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="J3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="K3" s="6" t="str">
+      <c r="D3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="E3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="F3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="G3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="H3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="I3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="J3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="K3" s="5" t="str">
         <v>Char</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6">
+      <c r="A4" s="5">
         <v>10</v>
       </c>
-      <c r="B4" s="6">
+      <c r="B4" s="5">
         <v>2</v>
       </c>
-      <c r="C4" s="6">
+      <c r="C4" s="5">
         <v>8</v>
       </c>
-      <c r="D4" s="6">
+      <c r="D4" s="5">
         <v>5</v>
       </c>
-      <c r="E4" s="6">
+      <c r="E4" s="5">
         <v>8</v>
       </c>
-      <c r="F4" s="6">
+      <c r="F4" s="5">
         <v>40</v>
       </c>
-      <c r="G4" s="6">
+      <c r="G4" s="5">
         <v>149</v>
       </c>
-      <c r="H4" s="6">
+      <c r="H4" s="5">
         <v>2</v>
       </c>
-      <c r="I4" s="6">
+      <c r="I4" s="5">
         <v>11</v>
       </c>
-      <c r="J4" s="6">
+      <c r="J4" s="5">
         <v>18</v>
       </c>
-      <c r="K4" s="6">
+      <c r="K4" s="5">
         <v>10</v>
       </c>
     </row>
@@ -662,9 +650,12 @@
         <v>Extension Trial Indicator</v>
       </c>
       <c r="G5" s="4" t="str">
-        <v>UNIITERM1</v>
-      </c>
-      <c r="I5" s="2" t="str">
+        <v>DI(DEHYDROABIETYL)AMINE ACETATE</v>
+      </c>
+      <c r="H5" s="2" t="str">
+        <v/>
+      </c>
+      <c r="I5" s="4" t="str">
         <v>00000UNII1</v>
       </c>
     </row>

--- a/rules/NEW-RULE/positive/01/data/new-rule-positive-01.xlsx
+++ b/rules/NEW-RULE/positive/01/data/new-rule-positive-01.xlsx
@@ -650,9 +650,9 @@
         <v>Extension Trial Indicator</v>
       </c>
       <c r="G5" s="4" t="str">
-        <v>UNIITERM1</v>
-      </c>
-      <c r="H5" s="2" t="str">
+        <v>DI(DEHYDROABIETYL)AMINE ACETATE</v>
+      </c>
+      <c r="H5" s="4" t="str">
         <v/>
       </c>
       <c r="I5" s="4" t="str">

--- a/rules/NEW-RULE/positive/01/data/new-rule-positive-01.xlsx
+++ b/rules/NEW-RULE/positive/01/data/new-rule-positive-01.xlsx
@@ -872,7 +872,7 @@
         <v/>
       </c>
       <c r="Y5" s="4">
-        <v>10029205</v>
+        <v>10005329</v>
       </c>
     </row>
   </sheetData>

--- a/rules/NEW-RULE/positive/01/data/new-rule-positive-01.xlsx
+++ b/rules/NEW-RULE/positive/01/data/new-rule-positive-01.xlsx
@@ -644,7 +644,7 @@
         <v/>
       </c>
       <c r="E5" s="4" t="str">
-        <v>CURTRT</v>
+        <v>COMPTRT</v>
       </c>
       <c r="F5" s="4" t="str">
         <v>Extension Trial Indicator</v>
@@ -652,7 +652,10 @@
       <c r="G5" s="4" t="str">
         <v>UNIITERM1</v>
       </c>
-      <c r="I5" s="2" t="str">
+      <c r="H5" s="2" t="str">
+        <v/>
+      </c>
+      <c r="I5" s="4" t="str">
         <v>00000UNII1</v>
       </c>
     </row>

--- a/rules/NEW-RULE/positive/01/data/new-rule-positive-01.xlsx
+++ b/rules/NEW-RULE/positive/01/data/new-rule-positive-01.xlsx
@@ -644,7 +644,7 @@
         <v/>
       </c>
       <c r="E5" s="4" t="str">
-        <v>CURTRT</v>
+        <v>TRT</v>
       </c>
       <c r="F5" s="4" t="str">
         <v>Extension Trial Indicator</v>
@@ -652,7 +652,10 @@
       <c r="G5" s="4" t="str">
         <v>UNIITERM1</v>
       </c>
-      <c r="I5" s="2" t="str">
+      <c r="H5" s="2" t="str">
+        <v/>
+      </c>
+      <c r="I5" s="4" t="str">
         <v>00000UNII1</v>
       </c>
     </row>

--- a/rules/NEW-RULE/positive/01/data/new-rule-positive-01.xlsx
+++ b/rules/NEW-RULE/positive/01/data/new-rule-positive-01.xlsx
@@ -35,7 +35,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
   <numFmts count="0"/>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -58,8 +58,13 @@
       <name val="Calibri"/>
       <i/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <i/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none">
         <bgColor/>
@@ -67,6 +72,12 @@
     </fill>
     <fill>
       <patternFill patternType="gray125">
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFCC"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -96,13 +107,14 @@
   <cellStyleXfs>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="1" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -535,98 +547,98 @@
       <c r="C2" s="5" t="str">
         <v>Sequence Number</v>
       </c>
-      <c r="D2" s="5" t="str">
+      <c r="D2" s="6" t="str">
         <v>Group ID</v>
       </c>
-      <c r="E2" s="5" t="str">
+      <c r="E2" s="6" t="str">
         <v>Trial Summary Parameter Short Name</v>
       </c>
-      <c r="F2" s="5" t="str">
+      <c r="F2" s="6" t="str">
         <v>Trial Summary Parameter</v>
       </c>
-      <c r="G2" s="5" t="str">
+      <c r="G2" s="6" t="str">
         <v>Parameter Value</v>
       </c>
-      <c r="H2" s="5" t="str">
+      <c r="H2" s="6" t="str">
         <v>Parameter Null Flavor</v>
       </c>
-      <c r="I2" s="5" t="str">
+      <c r="I2" s="6" t="str">
         <v>Parameter Value Code</v>
       </c>
-      <c r="J2" s="5" t="str">
+      <c r="J2" s="6" t="str">
         <v>Name of the Reference Terminology</v>
       </c>
-      <c r="K2" s="5" t="str">
+      <c r="K2" s="6" t="str">
         <v>Version of the Reference Terminology</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="str">
-        <v>Char</v>
-      </c>
-      <c r="B3" s="5" t="str">
-        <v>Char</v>
-      </c>
-      <c r="C3" s="5" t="str">
+      <c r="A3" s="6" t="str">
+        <v>Char</v>
+      </c>
+      <c r="B3" s="6" t="str">
+        <v>Char</v>
+      </c>
+      <c r="C3" s="6" t="str">
         <v>Num</v>
       </c>
-      <c r="D3" s="5" t="str">
-        <v>Char</v>
-      </c>
-      <c r="E3" s="5" t="str">
-        <v>Char</v>
-      </c>
-      <c r="F3" s="5" t="str">
-        <v>Char</v>
-      </c>
-      <c r="G3" s="5" t="str">
-        <v>Char</v>
-      </c>
-      <c r="H3" s="5" t="str">
-        <v>Char</v>
-      </c>
-      <c r="I3" s="5" t="str">
-        <v>Char</v>
-      </c>
-      <c r="J3" s="5" t="str">
-        <v>Char</v>
-      </c>
-      <c r="K3" s="5" t="str">
+      <c r="D3" s="6" t="str">
+        <v>Char</v>
+      </c>
+      <c r="E3" s="6" t="str">
+        <v>Char</v>
+      </c>
+      <c r="F3" s="6" t="str">
+        <v>Char</v>
+      </c>
+      <c r="G3" s="6" t="str">
+        <v>Char</v>
+      </c>
+      <c r="H3" s="6" t="str">
+        <v>Char</v>
+      </c>
+      <c r="I3" s="6" t="str">
+        <v>Char</v>
+      </c>
+      <c r="J3" s="6" t="str">
+        <v>Char</v>
+      </c>
+      <c r="K3" s="6" t="str">
         <v>Char</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5">
+      <c r="A4" s="6">
         <v>10</v>
       </c>
-      <c r="B4" s="5">
+      <c r="B4" s="6">
         <v>2</v>
       </c>
-      <c r="C4" s="5">
+      <c r="C4" s="6">
         <v>8</v>
       </c>
-      <c r="D4" s="5">
+      <c r="D4" s="6">
         <v>5</v>
       </c>
-      <c r="E4" s="5">
+      <c r="E4" s="6">
         <v>8</v>
       </c>
-      <c r="F4" s="5">
+      <c r="F4" s="6">
         <v>40</v>
       </c>
-      <c r="G4" s="5">
+      <c r="G4" s="6">
         <v>149</v>
       </c>
-      <c r="H4" s="5">
+      <c r="H4" s="6">
         <v>2</v>
       </c>
-      <c r="I4" s="5">
+      <c r="I4" s="6">
         <v>11</v>
       </c>
-      <c r="J4" s="5">
+      <c r="J4" s="6">
         <v>18</v>
       </c>
-      <c r="K4" s="5">
+      <c r="K4" s="6">
         <v>10</v>
       </c>
     </row>
@@ -644,19 +656,19 @@
         <v/>
       </c>
       <c r="E5" s="4" t="str">
-        <v>COMPTRT</v>
+        <v>INDIC</v>
       </c>
       <c r="F5" s="4" t="str">
         <v>Extension Trial Indicator</v>
       </c>
       <c r="G5" s="4" t="str">
-        <v>DI(DEHYDROABIETYL)AMINE ACETATE</v>
+        <v>Acetylcholine Activity Alteration</v>
       </c>
       <c r="H5" s="4" t="str">
         <v/>
       </c>
       <c r="I5" s="4" t="str">
-        <v>00000UNII1</v>
+        <v>N0000008290</v>
       </c>
     </row>
   </sheetData>

--- a/rules/NEW-RULE/positive/01/data/new-rule-positive-01.xlsx
+++ b/rules/NEW-RULE/positive/01/data/new-rule-positive-01.xlsx
@@ -35,7 +35,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
   <numFmts count="0"/>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -58,13 +58,8 @@
       <name val="Calibri"/>
       <i/>
     </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <i/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none">
         <bgColor/>
@@ -72,12 +67,6 @@
     </fill>
     <fill>
       <patternFill patternType="gray125">
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFCC"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -107,14 +96,13 @@
   <cellStyleXfs>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="1" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -547,98 +535,98 @@
       <c r="C2" s="5" t="str">
         <v>Sequence Number</v>
       </c>
-      <c r="D2" s="6" t="str">
+      <c r="D2" s="5" t="str">
         <v>Group ID</v>
       </c>
-      <c r="E2" s="6" t="str">
+      <c r="E2" s="5" t="str">
         <v>Trial Summary Parameter Short Name</v>
       </c>
-      <c r="F2" s="6" t="str">
+      <c r="F2" s="5" t="str">
         <v>Trial Summary Parameter</v>
       </c>
-      <c r="G2" s="6" t="str">
+      <c r="G2" s="5" t="str">
         <v>Parameter Value</v>
       </c>
-      <c r="H2" s="6" t="str">
+      <c r="H2" s="5" t="str">
         <v>Parameter Null Flavor</v>
       </c>
-      <c r="I2" s="6" t="str">
+      <c r="I2" s="5" t="str">
         <v>Parameter Value Code</v>
       </c>
-      <c r="J2" s="6" t="str">
+      <c r="J2" s="5" t="str">
         <v>Name of the Reference Terminology</v>
       </c>
-      <c r="K2" s="6" t="str">
+      <c r="K2" s="5" t="str">
         <v>Version of the Reference Terminology</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="B3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="C3" s="6" t="str">
+      <c r="A3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="B3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="C3" s="5" t="str">
         <v>Num</v>
       </c>
-      <c r="D3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="E3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="F3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="G3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="H3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="I3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="J3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="K3" s="6" t="str">
+      <c r="D3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="E3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="F3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="G3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="H3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="I3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="J3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="K3" s="5" t="str">
         <v>Char</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6">
+      <c r="A4" s="5">
         <v>10</v>
       </c>
-      <c r="B4" s="6">
+      <c r="B4" s="5">
         <v>2</v>
       </c>
-      <c r="C4" s="6">
+      <c r="C4" s="5">
         <v>8</v>
       </c>
-      <c r="D4" s="6">
+      <c r="D4" s="5">
         <v>5</v>
       </c>
-      <c r="E4" s="6">
+      <c r="E4" s="5">
         <v>8</v>
       </c>
-      <c r="F4" s="6">
+      <c r="F4" s="5">
         <v>40</v>
       </c>
-      <c r="G4" s="6">
+      <c r="G4" s="5">
         <v>149</v>
       </c>
-      <c r="H4" s="6">
+      <c r="H4" s="5">
         <v>2</v>
       </c>
-      <c r="I4" s="6">
+      <c r="I4" s="5">
         <v>11</v>
       </c>
-      <c r="J4" s="6">
+      <c r="J4" s="5">
         <v>18</v>
       </c>
-      <c r="K4" s="6">
+      <c r="K4" s="5">
         <v>10</v>
       </c>
     </row>

--- a/rules/NEW-RULE/positive/01/data/new-rule-positive-01.xlsx
+++ b/rules/NEW-RULE/positive/01/data/new-rule-positive-01.xlsx
@@ -35,7 +35,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
   <numFmts count="0"/>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -58,13 +58,8 @@
       <name val="Calibri"/>
       <i/>
     </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <i/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none">
         <bgColor/>
@@ -72,12 +67,6 @@
     </fill>
     <fill>
       <patternFill patternType="gray125">
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFCC"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -107,14 +96,13 @@
   <cellStyleXfs>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="1" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -547,98 +535,98 @@
       <c r="C2" s="5" t="str">
         <v>Sequence Number</v>
       </c>
-      <c r="D2" s="6" t="str">
+      <c r="D2" s="5" t="str">
         <v>Group ID</v>
       </c>
-      <c r="E2" s="6" t="str">
+      <c r="E2" s="5" t="str">
         <v>Trial Summary Parameter Short Name</v>
       </c>
-      <c r="F2" s="6" t="str">
+      <c r="F2" s="5" t="str">
         <v>Trial Summary Parameter</v>
       </c>
-      <c r="G2" s="6" t="str">
+      <c r="G2" s="5" t="str">
         <v>Parameter Value</v>
       </c>
-      <c r="H2" s="6" t="str">
+      <c r="H2" s="5" t="str">
         <v>Parameter Null Flavor</v>
       </c>
-      <c r="I2" s="6" t="str">
+      <c r="I2" s="5" t="str">
         <v>Parameter Value Code</v>
       </c>
-      <c r="J2" s="6" t="str">
+      <c r="J2" s="5" t="str">
         <v>Name of the Reference Terminology</v>
       </c>
-      <c r="K2" s="6" t="str">
+      <c r="K2" s="5" t="str">
         <v>Version of the Reference Terminology</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="B3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="C3" s="6" t="str">
+      <c r="A3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="B3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="C3" s="5" t="str">
         <v>Num</v>
       </c>
-      <c r="D3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="E3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="F3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="G3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="H3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="I3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="J3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="K3" s="6" t="str">
+      <c r="D3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="E3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="F3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="G3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="H3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="I3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="J3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="K3" s="5" t="str">
         <v>Char</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6">
+      <c r="A4" s="5">
         <v>10</v>
       </c>
-      <c r="B4" s="6">
+      <c r="B4" s="5">
         <v>2</v>
       </c>
-      <c r="C4" s="6">
+      <c r="C4" s="5">
         <v>8</v>
       </c>
-      <c r="D4" s="6">
+      <c r="D4" s="5">
         <v>5</v>
       </c>
-      <c r="E4" s="6">
+      <c r="E4" s="5">
         <v>8</v>
       </c>
-      <c r="F4" s="6">
+      <c r="F4" s="5">
         <v>40</v>
       </c>
-      <c r="G4" s="6">
+      <c r="G4" s="5">
         <v>149</v>
       </c>
-      <c r="H4" s="6">
+      <c r="H4" s="5">
         <v>2</v>
       </c>
-      <c r="I4" s="6">
+      <c r="I4" s="5">
         <v>11</v>
       </c>
-      <c r="J4" s="6">
+      <c r="J4" s="5">
         <v>18</v>
       </c>
-      <c r="K4" s="6">
+      <c r="K4" s="5">
         <v>10</v>
       </c>
     </row>
@@ -656,7 +644,7 @@
         <v/>
       </c>
       <c r="E5" s="4" t="str">
-        <v>INDIC</v>
+        <v>PCLAS</v>
       </c>
       <c r="F5" s="4" t="str">
         <v>Extension Trial Indicator</v>

--- a/rules/NEW-RULE/positive/01/data/new-rule-positive-01.xlsx
+++ b/rules/NEW-RULE/positive/01/data/new-rule-positive-01.xlsx
@@ -644,7 +644,7 @@
         <v/>
       </c>
       <c r="E5" s="4" t="str">
-        <v>INDIC</v>
+        <v>PCLAS</v>
       </c>
       <c r="F5" s="4" t="str">
         <v>Extension Trial Indicator</v>

--- a/rules/NEW-RULE/positive/01/data/new-rule-positive-01.xlsx
+++ b/rules/NEW-RULE/positive/01/data/new-rule-positive-01.xlsx
@@ -6,7 +6,7 @@
     <sheet name="Library" sheetId="1" r:id="rId1"/>
     <sheet name="Datasets" sheetId="2" r:id="rId2"/>
     <sheet name="dm.xpt" sheetId="3" r:id="rId3"/>
-    <sheet name="ae.xpt" sheetId="4" r:id="rId4"/>
+    <sheet name="ds.xpt" sheetId="4" r:id="rId4"/>
   </sheets>
 </workbook>
 </file>
@@ -36,7 +36,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
   <numFmts count="0"/>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -53,23 +57,6 @@
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
       <i/>
     </font>
     <font>
@@ -78,7 +65,7 @@
       <i/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="4">
     <fill>
       <patternFill patternType="none">
         <bgColor/>
@@ -86,21 +73,6 @@
     </fill>
     <fill>
       <patternFill patternType="gray125">
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <bgColor/>
       </patternFill>
     </fill>
@@ -136,17 +108,14 @@
   <cellStyleXfs>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="1" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -481,18 +450,18 @@
   <dimension ref="A1:B2"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="str">
+      <c r="A1" s="3" t="str">
         <v>Product</v>
       </c>
-      <c r="B1" s="2" t="str">
+      <c r="B1" s="3" t="str">
         <v>Version</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="str">
+      <c r="A2" s="3" t="str">
         <v>sdtmig</v>
       </c>
-      <c r="B2" s="2" t="str">
+      <c r="B2" s="3" t="str">
         <v>3-4</v>
       </c>
     </row>
@@ -508,27 +477,27 @@
   <dimension ref="A1:B3"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="str">
+      <c r="A1" s="3" t="str">
         <v>Filename</v>
       </c>
-      <c r="B1" s="2" t="str">
+      <c r="B1" s="3" t="str">
         <v>Label</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="str">
+      <c r="A2" s="3" t="str">
         <v>dm.xpt</v>
       </c>
-      <c r="B2" s="2" t="str">
+      <c r="B2" s="3" t="str">
         <v>Demographics</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="str">
-        <v>ae.xpt</v>
-      </c>
-      <c r="B3" s="2" t="str">
-        <v>Adverse Events</v>
+      <c r="A3" s="3" t="str">
+        <v>ds.xpt</v>
+      </c>
+      <c r="B3" s="3" t="str">
+        <v>Disposition</v>
       </c>
     </row>
   </sheetData>
@@ -543,642 +512,642 @@
   <dimension ref="A1:Z8"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="str">
+      <c r="A1" s="4" t="str">
         <v>STUDYID</v>
       </c>
-      <c r="B1" s="3" t="str">
+      <c r="B1" s="4" t="str">
         <v>DOMAIN</v>
       </c>
-      <c r="C1" s="3" t="str">
+      <c r="C1" s="4" t="str">
         <v>USUBJID</v>
       </c>
-      <c r="D1" s="3" t="str">
+      <c r="D1" s="4" t="str">
         <v>SUBJID</v>
       </c>
-      <c r="E1" s="3" t="str">
+      <c r="E1" s="4" t="str">
         <v>RFSTDTC</v>
       </c>
-      <c r="F1" s="3" t="str">
+      <c r="F1" s="4" t="str">
         <v>RFENDTC</v>
       </c>
-      <c r="G1" s="3" t="str">
+      <c r="G1" s="4" t="str">
         <v>RFXSTDTC</v>
       </c>
-      <c r="H1" s="3" t="str">
+      <c r="H1" s="4" t="str">
         <v>RFXENDTC</v>
       </c>
-      <c r="I1" s="3" t="str">
+      <c r="I1" s="4" t="str">
         <v>RFICDTC</v>
       </c>
-      <c r="J1" s="3" t="str">
+      <c r="J1" s="4" t="str">
         <v>RFPENDTC</v>
       </c>
-      <c r="K1" s="3" t="str">
+      <c r="K1" s="4" t="str">
         <v>DTHDTC</v>
       </c>
       <c r="L1" s="4" t="str">
         <v>DTHFL</v>
       </c>
-      <c r="M1" s="3" t="str">
+      <c r="M1" s="4" t="str">
         <v>SITEID</v>
       </c>
-      <c r="N1" s="3" t="str">
+      <c r="N1" s="4" t="str">
         <v>BRTHDTC</v>
       </c>
-      <c r="O1" s="3" t="str">
+      <c r="O1" s="4" t="str">
         <v>AGE</v>
       </c>
-      <c r="P1" s="3" t="str">
+      <c r="P1" s="4" t="str">
         <v>AGEU</v>
       </c>
-      <c r="Q1" s="3" t="str">
+      <c r="Q1" s="4" t="str">
         <v>SEX</v>
       </c>
-      <c r="R1" s="3" t="str">
+      <c r="R1" s="4" t="str">
         <v>RACE</v>
       </c>
-      <c r="S1" s="3" t="str">
+      <c r="S1" s="4" t="str">
         <v>ETHNIC</v>
       </c>
-      <c r="T1" s="3" t="str">
+      <c r="T1" s="4" t="str">
         <v>ARMCD</v>
       </c>
-      <c r="U1" s="3" t="str">
+      <c r="U1" s="4" t="str">
         <v>ARM</v>
       </c>
-      <c r="V1" s="3" t="str">
+      <c r="V1" s="4" t="str">
         <v>ACTARMCD</v>
       </c>
-      <c r="W1" s="3" t="str">
+      <c r="W1" s="4" t="str">
         <v>ACTARM</v>
       </c>
-      <c r="X1" s="3" t="str">
+      <c r="X1" s="4" t="str">
         <v>ARMNRS</v>
       </c>
-      <c r="Y1" s="3" t="str">
+      <c r="Y1" s="4" t="str">
         <v>ACTARMUD</v>
       </c>
-      <c r="Z1" s="3" t="str">
+      <c r="Z1" s="4" t="str">
         <v>COUNTRY</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="str">
+      <c r="A2" s="3" t="str">
         <v>Study Identifier</v>
       </c>
-      <c r="B2" s="5" t="str">
+      <c r="B2" s="3" t="str">
         <v>Domain Abbreviation</v>
       </c>
-      <c r="C2" s="6" t="str">
+      <c r="C2" s="3" t="str">
         <v>Unique Subject Identifier</v>
       </c>
-      <c r="D2" s="6" t="str">
+      <c r="D2" s="3" t="str">
         <v>Subject Identifier for the Study</v>
       </c>
-      <c r="E2" s="6" t="str">
+      <c r="E2" s="3" t="str">
         <v>Subject Reference Start Date/Time</v>
       </c>
-      <c r="F2" s="6" t="str">
+      <c r="F2" s="3" t="str">
         <v>Subject Reference End Date/Time</v>
       </c>
-      <c r="G2" s="6" t="str">
+      <c r="G2" s="3" t="str">
         <v>Date/Time of First Study Treatment</v>
       </c>
-      <c r="H2" s="6" t="str">
+      <c r="H2" s="3" t="str">
         <v>Date/Time of Last Study Treatment</v>
       </c>
-      <c r="I2" s="6" t="str">
+      <c r="I2" s="3" t="str">
         <v>Date/Time of Informed Consent</v>
       </c>
-      <c r="J2" s="6" t="str">
+      <c r="J2" s="3" t="str">
         <v>Date/Time of End of Participation</v>
       </c>
-      <c r="K2" s="6" t="str">
+      <c r="K2" s="3" t="str">
         <v>Date/Time of Death</v>
       </c>
-      <c r="L2" s="6" t="str">
+      <c r="L2" s="3" t="str">
         <v>Subject Death Flag</v>
       </c>
-      <c r="M2" s="6" t="str">
+      <c r="M2" s="3" t="str">
         <v>Study Site Identifier</v>
       </c>
-      <c r="N2" s="6" t="str">
+      <c r="N2" s="3" t="str">
         <v>Date/Time of Birth</v>
       </c>
-      <c r="O2" s="6" t="str">
+      <c r="O2" s="3" t="str">
         <v>Age</v>
       </c>
-      <c r="P2" s="6" t="str">
+      <c r="P2" s="3" t="str">
         <v>Age Units</v>
       </c>
-      <c r="Q2" s="6" t="str">
+      <c r="Q2" s="3" t="str">
         <v>Sex</v>
       </c>
-      <c r="R2" s="6" t="str">
+      <c r="R2" s="3" t="str">
         <v>Race</v>
       </c>
-      <c r="S2" s="6" t="str">
+      <c r="S2" s="3" t="str">
         <v>Ethnicity</v>
       </c>
-      <c r="T2" s="6" t="str">
+      <c r="T2" s="3" t="str">
         <v>Planned Arm Code</v>
       </c>
-      <c r="U2" s="6" t="str">
+      <c r="U2" s="3" t="str">
         <v>Description of Planned Arm</v>
       </c>
-      <c r="V2" s="6" t="str">
+      <c r="V2" s="3" t="str">
         <v>Actual Arm Code</v>
       </c>
-      <c r="W2" s="6" t="str">
+      <c r="W2" s="3" t="str">
         <v>Description of Actual Arm</v>
       </c>
-      <c r="X2" s="6" t="str">
+      <c r="X2" s="3" t="str">
         <v>Reason Arm and/or Actual Arm is Null</v>
       </c>
-      <c r="Y2" s="6" t="str">
+      <c r="Y2" s="3" t="str">
         <v>Description of Unplanned Actual Arm</v>
       </c>
-      <c r="Z2" s="6" t="str">
+      <c r="Z2" s="3" t="str">
         <v>Country</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="B3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="C3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="D3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="E3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="F3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="G3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="H3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="I3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="J3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="K3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="L3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="M3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="N3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="O3" s="7" t="str">
+      <c r="A3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="B3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="C3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="D3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="E3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="F3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="G3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="H3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="I3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="J3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="K3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="L3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="M3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="N3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="O3" s="3" t="str">
         <v>Num</v>
       </c>
-      <c r="P3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="Q3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="R3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="S3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="T3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="U3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="V3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="W3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="X3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="Y3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="Z3" s="7" t="str">
+      <c r="P3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="Q3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="R3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="S3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="T3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="U3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="V3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="W3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="X3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="Y3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="Z3" s="3" t="str">
         <v>Char</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6">
+      <c r="A4" s="3">
         <v>12</v>
       </c>
-      <c r="B4" s="6">
+      <c r="B4" s="3">
         <v>2</v>
       </c>
-      <c r="C4" s="6">
+      <c r="C4" s="3">
         <v>8</v>
       </c>
-      <c r="D4" s="6">
+      <c r="D4" s="3">
         <v>4</v>
       </c>
-      <c r="E4" s="6">
+      <c r="E4" s="3">
         <v>10</v>
       </c>
-      <c r="F4" s="6">
+      <c r="F4" s="3">
         <v>10</v>
       </c>
-      <c r="G4" s="6">
+      <c r="G4" s="3">
         <v>10</v>
       </c>
-      <c r="H4" s="6">
+      <c r="H4" s="3">
         <v>10</v>
       </c>
-      <c r="I4" s="6">
+      <c r="I4" s="3">
         <v>10</v>
       </c>
-      <c r="J4" s="6">
+      <c r="J4" s="3">
         <v>10</v>
       </c>
-      <c r="K4" s="6">
+      <c r="K4" s="3">
         <v>10</v>
       </c>
-      <c r="L4" s="6">
+      <c r="L4" s="3">
         <v>1</v>
       </c>
-      <c r="M4" s="6">
+      <c r="M4" s="3">
         <v>3</v>
       </c>
-      <c r="N4" s="6">
+      <c r="N4" s="3">
         <v>10</v>
       </c>
-      <c r="O4" s="6">
+      <c r="O4" s="3">
         <v>8</v>
       </c>
-      <c r="P4" s="6">
+      <c r="P4" s="3">
         <v>5</v>
       </c>
-      <c r="Q4" s="6">
+      <c r="Q4" s="3">
         <v>1</v>
       </c>
-      <c r="R4" s="6">
+      <c r="R4" s="3">
         <v>41</v>
       </c>
-      <c r="S4" s="6">
+      <c r="S4" s="3">
         <v>22</v>
       </c>
-      <c r="T4" s="6">
+      <c r="T4" s="3">
         <v>8</v>
       </c>
-      <c r="U4" s="6">
+      <c r="U4" s="3">
         <v>28</v>
       </c>
-      <c r="V4" s="6">
+      <c r="V4" s="3">
         <v>8</v>
       </c>
-      <c r="W4" s="6">
+      <c r="W4" s="3">
         <v>28</v>
       </c>
-      <c r="X4" s="6">
+      <c r="X4" s="3">
         <v>14</v>
       </c>
-      <c r="Y4" s="6">
+      <c r="Y4" s="3">
         <v>200</v>
       </c>
-      <c r="Z4" s="6">
+      <c r="Z4" s="3">
         <v>3</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="str">
+      <c r="A5" s="3" t="str">
         <v>CDISCPILOT01</v>
       </c>
-      <c r="B5" s="7" t="str">
+      <c r="B5" s="3" t="str">
         <v>DM</v>
       </c>
-      <c r="C5" s="7" t="str">
+      <c r="C5" s="3" t="str">
         <v>CDISC001</v>
       </c>
-      <c r="D5" s="7">
+      <c r="D5" s="3">
         <v>1115</v>
       </c>
-      <c r="E5" s="7" t="str">
+      <c r="E5" s="3" t="str">
         <v>2018-05-17T09:35</v>
       </c>
-      <c r="F5" s="7" t="str">
+      <c r="F5" s="3" t="str">
         <v>2018-08-03</v>
       </c>
-      <c r="G5" s="7" t="str">
+      <c r="G5" s="3" t="str">
         <v>2018-05-17T09:35</v>
       </c>
-      <c r="H5" s="7" t="str">
+      <c r="H5" s="3" t="str">
         <v>2018-08-03</v>
       </c>
-      <c r="I5" s="7" t="str">
+      <c r="I5" s="3" t="str">
         <v>2018-04-26</v>
       </c>
-      <c r="J5" s="7" t="str">
+      <c r="J5" s="3" t="str">
         <v>2018-08-22</v>
       </c>
-      <c r="K5" s="7" t="str">
+      <c r="K5" s="3" t="str">
         <v>2018-08-22</v>
       </c>
-      <c r="L5" s="6" t="str">
+      <c r="L5" s="3" t="str">
         <v>Y</v>
       </c>
-      <c r="M5" s="7">
+      <c r="M5" s="3">
         <v>701</v>
       </c>
-      <c r="N5" s="7" t="str">
+      <c r="N5" s="3" t="str">
         <v>1947-07-24T00:00:00.000Z</v>
       </c>
-      <c r="O5" s="7" t="str">
+      <c r="O5" s="3" t="str">
         <v>70</v>
       </c>
-      <c r="P5" s="7" t="str">
+      <c r="P5" s="3" t="str">
         <v>YEARS</v>
       </c>
-      <c r="Q5" s="7" t="str">
+      <c r="Q5" s="3" t="str">
         <v>M</v>
       </c>
-      <c r="R5" s="7" t="str">
+      <c r="R5" s="3" t="str">
         <v>WHITE</v>
       </c>
-      <c r="S5" s="7" t="str">
+      <c r="S5" s="3" t="str">
         <v>NOT HISPANIC OR LATINO</v>
       </c>
-      <c r="T5" s="7" t="str">
+      <c r="T5" s="3" t="str">
         <v>A</v>
       </c>
-      <c r="U5" s="7" t="str">
+      <c r="U5" s="3" t="str">
         <v>Drug A</v>
       </c>
-      <c r="V5" s="7" t="str">
+      <c r="V5" s="3" t="str">
         <v>A</v>
       </c>
-      <c r="W5" s="7" t="str">
+      <c r="W5" s="3" t="str">
         <v>Drug A</v>
       </c>
-      <c r="X5" s="7" t="str">
+      <c r="X5" s="3" t="str">
         <v/>
       </c>
-      <c r="Y5" s="7" t="str">
+      <c r="Y5" s="3" t="str">
         <v/>
       </c>
-      <c r="Z5" s="7" t="str">
+      <c r="Z5" s="3" t="str">
         <v>AUS</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="str">
+      <c r="A6" s="3" t="str">
         <v>CDISCPILOT01</v>
       </c>
-      <c r="B6" s="6" t="str">
+      <c r="B6" s="3" t="str">
         <v>DM</v>
       </c>
-      <c r="C6" s="6" t="str">
+      <c r="C6" s="3" t="str">
         <v>CDISC002</v>
       </c>
-      <c r="D6" s="6">
+      <c r="D6" s="3">
         <v>1211</v>
       </c>
-      <c r="E6" s="6" t="str">
+      <c r="E6" s="3" t="str">
         <v>2018-05-24T12:00</v>
       </c>
-      <c r="F6" s="6" t="str">
+      <c r="F6" s="3" t="str">
         <v>2018-11-06</v>
       </c>
-      <c r="G6" s="6" t="str">
+      <c r="G6" s="3" t="str">
         <v>2018-05-24T12:00</v>
       </c>
-      <c r="H6" s="6" t="str">
+      <c r="H6" s="3" t="str">
         <v>2018-11-06</v>
       </c>
-      <c r="I6" s="6" t="str">
+      <c r="I6" s="3" t="str">
         <v>2018-05-07</v>
       </c>
-      <c r="J6" s="6" t="str">
+      <c r="J6" s="3" t="str">
         <v>2019-02-04</v>
       </c>
-      <c r="K6" s="6" t="str">
+      <c r="K6" s="3" t="str">
         <v>2019-02-04</v>
       </c>
-      <c r="L6" s="6" t="str">
+      <c r="L6" s="3" t="str">
         <v>Y</v>
       </c>
-      <c r="M6" s="6">
+      <c r="M6" s="3">
         <v>701</v>
       </c>
-      <c r="N6" s="6" t="str">
+      <c r="N6" s="3" t="str">
         <v>1905-05-08T00:00:00.000Z</v>
       </c>
-      <c r="O6" s="6" t="str">
+      <c r="O6" s="3" t="str">
         <v>78</v>
       </c>
-      <c r="P6" s="6" t="str">
+      <c r="P6" s="3" t="str">
         <v>YEARS</v>
       </c>
-      <c r="Q6" s="6" t="str">
+      <c r="Q6" s="3" t="str">
         <v>M</v>
       </c>
-      <c r="R6" s="6" t="str">
+      <c r="R6" s="3" t="str">
         <v>WHITE</v>
       </c>
-      <c r="S6" s="6" t="str">
+      <c r="S6" s="3" t="str">
         <v>NOT HISPANIC OR LATINO</v>
       </c>
-      <c r="T6" s="6" t="str">
+      <c r="T6" s="3" t="str">
         <v>P</v>
       </c>
-      <c r="U6" s="6" t="str">
+      <c r="U6" s="3" t="str">
         <v>Placebo</v>
       </c>
-      <c r="V6" s="6" t="str">
+      <c r="V6" s="3" t="str">
         <v>P</v>
       </c>
-      <c r="W6" s="6" t="str">
+      <c r="W6" s="3" t="str">
         <v>Placebo</v>
       </c>
-      <c r="X6" s="6" t="str">
+      <c r="X6" s="3" t="str">
         <v/>
       </c>
-      <c r="Y6" s="6" t="str">
+      <c r="Y6" s="3" t="str">
         <v/>
       </c>
-      <c r="Z6" s="6" t="str">
+      <c r="Z6" s="3" t="str">
         <v>AUS</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="str">
+      <c r="A7" s="3" t="str">
         <v>CDISCPILOT01</v>
       </c>
-      <c r="B7" s="7" t="str">
+      <c r="B7" s="3" t="str">
         <v>DM</v>
       </c>
-      <c r="C7" s="7" t="str">
+      <c r="C7" s="3" t="str">
         <v>CDISC003</v>
       </c>
-      <c r="D7" s="7">
+      <c r="D7" s="3">
         <v>1302</v>
       </c>
-      <c r="E7" s="7" t="str">
+      <c r="E7" s="3" t="str">
         <v>2006-01-16</v>
       </c>
-      <c r="F7" s="7" t="str">
+      <c r="F7" s="3" t="str">
         <v>2006-03-19</v>
       </c>
-      <c r="G7" s="7" t="str">
+      <c r="G7" s="3" t="str">
         <v>2006-01-16</v>
       </c>
-      <c r="H7" s="7" t="str">
+      <c r="H7" s="3" t="str">
         <v>2006-03-19</v>
       </c>
-      <c r="I7" s="7" t="str">
+      <c r="I7" s="3" t="str">
         <v>2006-01-02</v>
       </c>
-      <c r="J7" s="7" t="str">
+      <c r="J7" s="3" t="str">
         <v>2006-03-19</v>
       </c>
-      <c r="K7" s="7" t="str">
+      <c r="K7" s="3" t="str">
         <v/>
       </c>
-      <c r="L7" s="6" t="str">
+      <c r="L7" s="3" t="str">
         <v>Y</v>
       </c>
-      <c r="M7" s="7">
+      <c r="M7" s="3">
         <v>701</v>
       </c>
-      <c r="N7" s="7" t="str">
+      <c r="N7" s="3" t="str">
         <v>1944-06-16T00:00:00.000Z</v>
       </c>
-      <c r="O7" s="7" t="str">
+      <c r="O7" s="3" t="str">
         <v>74</v>
       </c>
-      <c r="P7" s="7" t="str">
+      <c r="P7" s="3" t="str">
         <v>YEARS</v>
       </c>
-      <c r="Q7" s="7" t="str">
+      <c r="Q7" s="3" t="str">
         <v>M</v>
       </c>
-      <c r="R7" s="7" t="str">
+      <c r="R7" s="3" t="str">
         <v>WHITE</v>
       </c>
-      <c r="S7" s="7" t="str">
+      <c r="S7" s="3" t="str">
         <v>NOT HISPANIC OR LATINO</v>
       </c>
-      <c r="T7" s="7" t="str">
+      <c r="T7" s="3" t="str">
         <v>B</v>
       </c>
-      <c r="U7" s="7" t="str">
+      <c r="U7" s="3" t="str">
         <v>Drug B</v>
       </c>
-      <c r="V7" s="7" t="str">
+      <c r="V7" s="3" t="str">
         <v>B</v>
       </c>
-      <c r="W7" s="7" t="str">
+      <c r="W7" s="3" t="str">
         <v>Drug B</v>
       </c>
-      <c r="X7" s="7" t="str">
+      <c r="X7" s="3" t="str">
         <v/>
       </c>
-      <c r="Y7" s="7" t="str">
+      <c r="Y7" s="3" t="str">
         <v/>
       </c>
-      <c r="Z7" s="7" t="str">
+      <c r="Z7" s="3" t="str">
         <v>CZE</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="str">
+      <c r="A8" s="3" t="str">
         <v>CDISCPILOT01</v>
       </c>
-      <c r="B8" s="7" t="str">
+      <c r="B8" s="3" t="str">
         <v>DM</v>
       </c>
-      <c r="C8" s="7" t="str">
+      <c r="C8" s="3" t="str">
         <v>CDISC004</v>
       </c>
-      <c r="D8" s="7">
+      <c r="D8" s="3">
         <v>1402</v>
       </c>
-      <c r="E8" s="7" t="str">
+      <c r="E8" s="3" t="str">
         <v>2018-07-16T09:15</v>
       </c>
-      <c r="F8" s="7" t="str">
+      <c r="F8" s="3" t="str">
         <v>2018-11-06T14:00</v>
       </c>
-      <c r="G8" s="7" t="str">
+      <c r="G8" s="3" t="str">
         <v>2018-07-16T09:15</v>
       </c>
-      <c r="H8" s="7" t="str">
+      <c r="H8" s="3" t="str">
         <v>2018-11-06T14:00</v>
       </c>
-      <c r="I8" s="7" t="str">
+      <c r="I8" s="3" t="str">
         <v>2018-06-27</v>
       </c>
-      <c r="J8" s="7" t="str">
+      <c r="J8" s="3" t="str">
         <v>2018-12-11</v>
       </c>
-      <c r="K8" s="7" t="str">
+      <c r="K8" s="3" t="str">
         <v/>
       </c>
-      <c r="L8" s="6" t="str">
+      <c r="L8" s="3" t="str">
         <v/>
       </c>
-      <c r="M8" s="7">
+      <c r="M8" s="3">
         <v>701</v>
       </c>
-      <c r="N8" s="7" t="str">
+      <c r="N8" s="3" t="str">
         <v>1905-04-16T00:00:00.000Z</v>
       </c>
-      <c r="O8" s="7" t="str">
+      <c r="O8" s="3" t="str">
         <v>68</v>
       </c>
-      <c r="P8" s="7" t="str">
+      <c r="P8" s="3" t="str">
         <v>YEARS</v>
       </c>
-      <c r="Q8" s="7" t="str">
+      <c r="Q8" s="3" t="str">
         <v>F</v>
       </c>
-      <c r="R8" s="7" t="str">
+      <c r="R8" s="3" t="str">
         <v>WHITE</v>
       </c>
-      <c r="S8" s="7" t="str">
+      <c r="S8" s="3" t="str">
         <v>HISPANIC OR LATINO</v>
       </c>
-      <c r="T8" s="7" t="str">
+      <c r="T8" s="3" t="str">
         <v>B</v>
       </c>
-      <c r="U8" s="7" t="str">
+      <c r="U8" s="3" t="str">
         <v>Drug B</v>
       </c>
-      <c r="V8" s="7" t="str">
+      <c r="V8" s="3" t="str">
         <v>B</v>
       </c>
-      <c r="W8" s="7" t="str">
+      <c r="W8" s="3" t="str">
         <v>Drug B</v>
       </c>
-      <c r="X8" s="7" t="str">
+      <c r="X8" s="3" t="str">
         <v/>
       </c>
-      <c r="Y8" s="7" t="str">
+      <c r="Y8" s="3" t="str">
         <v/>
       </c>
-      <c r="Z8" s="7" t="str">
+      <c r="Z8" s="3" t="str">
         <v>CAN</v>
       </c>
     </row>
@@ -1194,72 +1163,72 @@
   <dimension ref="A1:D5"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="str">
+      <c r="A1" s="4" t="str">
         <v>STUDYID</v>
       </c>
-      <c r="B1" s="3" t="str">
+      <c r="B1" s="4" t="str">
         <v>DOMAIN</v>
       </c>
-      <c r="C1" s="3" t="str">
+      <c r="C1" s="4" t="str">
         <v>USUBJID</v>
       </c>
-      <c r="D1" s="3" t="str">
-        <v>AESEQ</v>
+      <c r="D1" s="4" t="str">
+        <v>DSSEQ</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="8" t="str">
+      <c r="A2" s="5" t="str">
         <v>Study Identifier</v>
       </c>
-      <c r="B2" s="8" t="str">
+      <c r="B2" s="6" t="str">
         <v>Domain Abbreviation</v>
       </c>
-      <c r="C2" s="9" t="str">
+      <c r="C2" s="6" t="str">
         <v>Unique Subject Identifier</v>
       </c>
-      <c r="D2" s="9" t="str">
+      <c r="D2" s="6" t="str">
         <v>Sequence Number</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="9" t="str">
-        <v>Char</v>
-      </c>
-      <c r="B3" s="9" t="str">
-        <v>Char</v>
-      </c>
-      <c r="C3" s="9" t="str">
-        <v>Char</v>
-      </c>
-      <c r="D3" s="9" t="str">
+      <c r="A3" s="6" t="str">
+        <v>Char</v>
+      </c>
+      <c r="B3" s="6" t="str">
+        <v>Char</v>
+      </c>
+      <c r="C3" s="6" t="str">
+        <v>Char</v>
+      </c>
+      <c r="D3" s="6" t="str">
         <v>Num</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="9" t="str">
+      <c r="A4" s="6" t="str">
         <v>10</v>
       </c>
-      <c r="B4" s="9" t="str">
+      <c r="B4" s="6" t="str">
         <v>2</v>
       </c>
-      <c r="C4" s="9" t="str">
+      <c r="C4" s="6" t="str">
         <v>14</v>
       </c>
-      <c r="D4" s="9" t="str">
+      <c r="D4" s="6" t="str">
         <v>8</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="str">
+      <c r="A5" s="3" t="str">
         <v>CDISCPILOT01</v>
       </c>
-      <c r="B5" s="7" t="str">
-        <v>AE</v>
-      </c>
-      <c r="C5" s="7" t="str">
+      <c r="B5" s="3" t="str">
+        <v>DS</v>
+      </c>
+      <c r="C5" s="3" t="str">
         <v>CDISC-TEST-001</v>
       </c>
-      <c r="D5" s="7" t="str">
+      <c r="D5" s="3" t="str">
         <v>1</v>
       </c>
     </row>

--- a/rules/NEW-RULE/positive/01/data/new-rule-positive-01.xlsx
+++ b/rules/NEW-RULE/positive/01/data/new-rule-positive-01.xlsx
@@ -6,7 +6,7 @@
     <sheet name="Library" sheetId="1" r:id="rId1"/>
     <sheet name="Datasets" sheetId="2" r:id="rId2"/>
     <sheet name="dm.xpt" sheetId="3" r:id="rId3"/>
-    <sheet name="ae.xpt" sheetId="4" r:id="rId4"/>
+    <sheet name="ex.xpt" sheetId="4" r:id="rId4"/>
   </sheets>
 </workbook>
 </file>
@@ -36,7 +36,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
   <numFmts count="0"/>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -53,23 +57,6 @@
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
       <i/>
     </font>
     <font>
@@ -78,7 +65,7 @@
       <i/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="4">
     <fill>
       <patternFill patternType="none">
         <bgColor/>
@@ -86,21 +73,6 @@
     </fill>
     <fill>
       <patternFill patternType="gray125">
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <bgColor/>
       </patternFill>
     </fill>
@@ -136,17 +108,14 @@
   <cellStyleXfs>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="1" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -481,18 +450,18 @@
   <dimension ref="A1:B2"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="str">
+      <c r="A1" s="3" t="str">
         <v>Product</v>
       </c>
-      <c r="B1" s="2" t="str">
+      <c r="B1" s="3" t="str">
         <v>Version</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="str">
+      <c r="A2" s="3" t="str">
         <v>sdtmig</v>
       </c>
-      <c r="B2" s="2" t="str">
+      <c r="B2" s="3" t="str">
         <v>3-4</v>
       </c>
     </row>
@@ -508,27 +477,27 @@
   <dimension ref="A1:B3"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="str">
+      <c r="A1" s="3" t="str">
         <v>Filename</v>
       </c>
-      <c r="B1" s="2" t="str">
+      <c r="B1" s="3" t="str">
         <v>Label</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="str">
+      <c r="A2" s="3" t="str">
         <v>dm.xpt</v>
       </c>
-      <c r="B2" s="2" t="str">
+      <c r="B2" s="3" t="str">
         <v>Demographics</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="str">
-        <v>ae.xpt</v>
-      </c>
-      <c r="B3" s="2" t="str">
-        <v>Adverse Events</v>
+      <c r="A3" s="3" t="str">
+        <v>ex.xpt</v>
+      </c>
+      <c r="B3" s="3" t="str">
+        <v>Exposure</v>
       </c>
     </row>
   </sheetData>
@@ -543,642 +512,642 @@
   <dimension ref="A1:Z8"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="str">
+      <c r="A1" s="4" t="str">
         <v>STUDYID</v>
       </c>
-      <c r="B1" s="3" t="str">
+      <c r="B1" s="4" t="str">
         <v>DOMAIN</v>
       </c>
-      <c r="C1" s="3" t="str">
+      <c r="C1" s="4" t="str">
         <v>USUBJID</v>
       </c>
-      <c r="D1" s="3" t="str">
+      <c r="D1" s="4" t="str">
         <v>SUBJID</v>
       </c>
-      <c r="E1" s="3" t="str">
+      <c r="E1" s="4" t="str">
         <v>RFSTDTC</v>
       </c>
-      <c r="F1" s="3" t="str">
+      <c r="F1" s="4" t="str">
         <v>RFENDTC</v>
       </c>
-      <c r="G1" s="3" t="str">
+      <c r="G1" s="4" t="str">
         <v>RFXSTDTC</v>
       </c>
-      <c r="H1" s="3" t="str">
+      <c r="H1" s="4" t="str">
         <v>RFXENDTC</v>
       </c>
-      <c r="I1" s="3" t="str">
+      <c r="I1" s="4" t="str">
         <v>RFICDTC</v>
       </c>
-      <c r="J1" s="3" t="str">
+      <c r="J1" s="4" t="str">
         <v>RFPENDTC</v>
       </c>
-      <c r="K1" s="3" t="str">
+      <c r="K1" s="4" t="str">
         <v>DTHDTC</v>
       </c>
       <c r="L1" s="4" t="str">
         <v>DTHFL</v>
       </c>
-      <c r="M1" s="3" t="str">
+      <c r="M1" s="4" t="str">
         <v>SITEID</v>
       </c>
-      <c r="N1" s="3" t="str">
+      <c r="N1" s="4" t="str">
         <v>BRTHDTC</v>
       </c>
-      <c r="O1" s="3" t="str">
+      <c r="O1" s="4" t="str">
         <v>AGE</v>
       </c>
-      <c r="P1" s="3" t="str">
+      <c r="P1" s="4" t="str">
         <v>AGEU</v>
       </c>
-      <c r="Q1" s="3" t="str">
+      <c r="Q1" s="4" t="str">
         <v>SEX</v>
       </c>
-      <c r="R1" s="3" t="str">
+      <c r="R1" s="4" t="str">
         <v>RACE</v>
       </c>
-      <c r="S1" s="3" t="str">
+      <c r="S1" s="4" t="str">
         <v>ETHNIC</v>
       </c>
-      <c r="T1" s="3" t="str">
+      <c r="T1" s="4" t="str">
         <v>ARMCD</v>
       </c>
-      <c r="U1" s="3" t="str">
+      <c r="U1" s="4" t="str">
         <v>ARM</v>
       </c>
-      <c r="V1" s="3" t="str">
+      <c r="V1" s="4" t="str">
         <v>ACTARMCD</v>
       </c>
-      <c r="W1" s="3" t="str">
+      <c r="W1" s="4" t="str">
         <v>ACTARM</v>
       </c>
-      <c r="X1" s="3" t="str">
+      <c r="X1" s="4" t="str">
         <v>ARMNRS</v>
       </c>
-      <c r="Y1" s="3" t="str">
+      <c r="Y1" s="4" t="str">
         <v>ACTARMUD</v>
       </c>
-      <c r="Z1" s="3" t="str">
+      <c r="Z1" s="4" t="str">
         <v>COUNTRY</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="str">
+      <c r="A2" s="3" t="str">
         <v>Study Identifier</v>
       </c>
-      <c r="B2" s="5" t="str">
+      <c r="B2" s="3" t="str">
         <v>Domain Abbreviation</v>
       </c>
-      <c r="C2" s="6" t="str">
+      <c r="C2" s="3" t="str">
         <v>Unique Subject Identifier</v>
       </c>
-      <c r="D2" s="6" t="str">
+      <c r="D2" s="3" t="str">
         <v>Subject Identifier for the Study</v>
       </c>
-      <c r="E2" s="6" t="str">
+      <c r="E2" s="3" t="str">
         <v>Subject Reference Start Date/Time</v>
       </c>
-      <c r="F2" s="6" t="str">
+      <c r="F2" s="3" t="str">
         <v>Subject Reference End Date/Time</v>
       </c>
-      <c r="G2" s="6" t="str">
+      <c r="G2" s="3" t="str">
         <v>Date/Time of First Study Treatment</v>
       </c>
-      <c r="H2" s="6" t="str">
+      <c r="H2" s="3" t="str">
         <v>Date/Time of Last Study Treatment</v>
       </c>
-      <c r="I2" s="6" t="str">
+      <c r="I2" s="3" t="str">
         <v>Date/Time of Informed Consent</v>
       </c>
-      <c r="J2" s="6" t="str">
+      <c r="J2" s="3" t="str">
         <v>Date/Time of End of Participation</v>
       </c>
-      <c r="K2" s="6" t="str">
+      <c r="K2" s="3" t="str">
         <v>Date/Time of Death</v>
       </c>
-      <c r="L2" s="6" t="str">
+      <c r="L2" s="3" t="str">
         <v>Subject Death Flag</v>
       </c>
-      <c r="M2" s="6" t="str">
+      <c r="M2" s="3" t="str">
         <v>Study Site Identifier</v>
       </c>
-      <c r="N2" s="6" t="str">
+      <c r="N2" s="3" t="str">
         <v>Date/Time of Birth</v>
       </c>
-      <c r="O2" s="6" t="str">
+      <c r="O2" s="3" t="str">
         <v>Age</v>
       </c>
-      <c r="P2" s="6" t="str">
+      <c r="P2" s="3" t="str">
         <v>Age Units</v>
       </c>
-      <c r="Q2" s="6" t="str">
+      <c r="Q2" s="3" t="str">
         <v>Sex</v>
       </c>
-      <c r="R2" s="6" t="str">
+      <c r="R2" s="3" t="str">
         <v>Race</v>
       </c>
-      <c r="S2" s="6" t="str">
+      <c r="S2" s="3" t="str">
         <v>Ethnicity</v>
       </c>
-      <c r="T2" s="6" t="str">
+      <c r="T2" s="3" t="str">
         <v>Planned Arm Code</v>
       </c>
-      <c r="U2" s="6" t="str">
+      <c r="U2" s="3" t="str">
         <v>Description of Planned Arm</v>
       </c>
-      <c r="V2" s="6" t="str">
+      <c r="V2" s="3" t="str">
         <v>Actual Arm Code</v>
       </c>
-      <c r="W2" s="6" t="str">
+      <c r="W2" s="3" t="str">
         <v>Description of Actual Arm</v>
       </c>
-      <c r="X2" s="6" t="str">
+      <c r="X2" s="3" t="str">
         <v>Reason Arm and/or Actual Arm is Null</v>
       </c>
-      <c r="Y2" s="6" t="str">
+      <c r="Y2" s="3" t="str">
         <v>Description of Unplanned Actual Arm</v>
       </c>
-      <c r="Z2" s="6" t="str">
+      <c r="Z2" s="3" t="str">
         <v>Country</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="B3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="C3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="D3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="E3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="F3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="G3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="H3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="I3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="J3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="K3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="L3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="M3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="N3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="O3" s="7" t="str">
+      <c r="A3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="B3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="C3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="D3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="E3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="F3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="G3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="H3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="I3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="J3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="K3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="L3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="M3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="N3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="O3" s="3" t="str">
         <v>Num</v>
       </c>
-      <c r="P3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="Q3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="R3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="S3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="T3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="U3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="V3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="W3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="X3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="Y3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="Z3" s="7" t="str">
+      <c r="P3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="Q3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="R3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="S3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="T3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="U3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="V3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="W3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="X3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="Y3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="Z3" s="3" t="str">
         <v>Char</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6">
+      <c r="A4" s="3">
         <v>12</v>
       </c>
-      <c r="B4" s="6">
+      <c r="B4" s="3">
         <v>2</v>
       </c>
-      <c r="C4" s="6">
+      <c r="C4" s="3">
         <v>8</v>
       </c>
-      <c r="D4" s="6">
+      <c r="D4" s="3">
         <v>4</v>
       </c>
-      <c r="E4" s="6">
+      <c r="E4" s="3">
         <v>10</v>
       </c>
-      <c r="F4" s="6">
+      <c r="F4" s="3">
         <v>10</v>
       </c>
-      <c r="G4" s="6">
+      <c r="G4" s="3">
         <v>10</v>
       </c>
-      <c r="H4" s="6">
+      <c r="H4" s="3">
         <v>10</v>
       </c>
-      <c r="I4" s="6">
+      <c r="I4" s="3">
         <v>10</v>
       </c>
-      <c r="J4" s="6">
+      <c r="J4" s="3">
         <v>10</v>
       </c>
-      <c r="K4" s="6">
+      <c r="K4" s="3">
         <v>10</v>
       </c>
-      <c r="L4" s="6">
+      <c r="L4" s="3">
         <v>1</v>
       </c>
-      <c r="M4" s="6">
+      <c r="M4" s="3">
         <v>3</v>
       </c>
-      <c r="N4" s="6">
+      <c r="N4" s="3">
         <v>10</v>
       </c>
-      <c r="O4" s="6">
+      <c r="O4" s="3">
         <v>8</v>
       </c>
-      <c r="P4" s="6">
+      <c r="P4" s="3">
         <v>5</v>
       </c>
-      <c r="Q4" s="6">
+      <c r="Q4" s="3">
         <v>1</v>
       </c>
-      <c r="R4" s="6">
+      <c r="R4" s="3">
         <v>41</v>
       </c>
-      <c r="S4" s="6">
+      <c r="S4" s="3">
         <v>22</v>
       </c>
-      <c r="T4" s="6">
+      <c r="T4" s="3">
         <v>8</v>
       </c>
-      <c r="U4" s="6">
+      <c r="U4" s="3">
         <v>28</v>
       </c>
-      <c r="V4" s="6">
+      <c r="V4" s="3">
         <v>8</v>
       </c>
-      <c r="W4" s="6">
+      <c r="W4" s="3">
         <v>28</v>
       </c>
-      <c r="X4" s="6">
+      <c r="X4" s="3">
         <v>14</v>
       </c>
-      <c r="Y4" s="6">
+      <c r="Y4" s="3">
         <v>200</v>
       </c>
-      <c r="Z4" s="6">
+      <c r="Z4" s="3">
         <v>3</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="str">
+      <c r="A5" s="3" t="str">
         <v>CDISCPILOT01</v>
       </c>
-      <c r="B5" s="7" t="str">
+      <c r="B5" s="3" t="str">
         <v>DM</v>
       </c>
-      <c r="C5" s="7" t="str">
+      <c r="C5" s="3" t="str">
         <v>CDISC001</v>
       </c>
-      <c r="D5" s="7">
+      <c r="D5" s="3">
         <v>1115</v>
       </c>
-      <c r="E5" s="7" t="str">
+      <c r="E5" s="3" t="str">
         <v>2018-05-17T09:35</v>
       </c>
-      <c r="F5" s="7" t="str">
+      <c r="F5" s="3" t="str">
         <v>2018-08-03</v>
       </c>
-      <c r="G5" s="7" t="str">
+      <c r="G5" s="3" t="str">
         <v>2018-05-17T09:35</v>
       </c>
-      <c r="H5" s="7" t="str">
+      <c r="H5" s="3" t="str">
         <v>2018-08-03</v>
       </c>
-      <c r="I5" s="7" t="str">
+      <c r="I5" s="3" t="str">
         <v>2018-04-26</v>
       </c>
-      <c r="J5" s="7" t="str">
+      <c r="J5" s="3" t="str">
         <v>2018-08-22</v>
       </c>
-      <c r="K5" s="7" t="str">
+      <c r="K5" s="3" t="str">
         <v>2018-08-22</v>
       </c>
-      <c r="L5" s="6" t="str">
+      <c r="L5" s="3" t="str">
         <v>Y</v>
       </c>
-      <c r="M5" s="7">
+      <c r="M5" s="3">
         <v>701</v>
       </c>
-      <c r="N5" s="7" t="str">
+      <c r="N5" s="3" t="str">
         <v>1947-07-24T00:00:00.000Z</v>
       </c>
-      <c r="O5" s="7" t="str">
+      <c r="O5" s="3" t="str">
         <v>70</v>
       </c>
-      <c r="P5" s="7" t="str">
+      <c r="P5" s="3" t="str">
         <v>YEARS</v>
       </c>
-      <c r="Q5" s="7" t="str">
+      <c r="Q5" s="3" t="str">
         <v>M</v>
       </c>
-      <c r="R5" s="7" t="str">
+      <c r="R5" s="3" t="str">
         <v>WHITE</v>
       </c>
-      <c r="S5" s="7" t="str">
+      <c r="S5" s="3" t="str">
         <v>NOT HISPANIC OR LATINO</v>
       </c>
-      <c r="T5" s="7" t="str">
+      <c r="T5" s="3" t="str">
         <v>A</v>
       </c>
-      <c r="U5" s="7" t="str">
+      <c r="U5" s="3" t="str">
         <v>Drug A</v>
       </c>
-      <c r="V5" s="7" t="str">
+      <c r="V5" s="3" t="str">
         <v>A</v>
       </c>
-      <c r="W5" s="7" t="str">
+      <c r="W5" s="3" t="str">
         <v>Drug A</v>
       </c>
-      <c r="X5" s="7" t="str">
+      <c r="X5" s="3" t="str">
         <v/>
       </c>
-      <c r="Y5" s="7" t="str">
+      <c r="Y5" s="3" t="str">
         <v/>
       </c>
-      <c r="Z5" s="7" t="str">
+      <c r="Z5" s="3" t="str">
         <v>AUS</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="str">
+      <c r="A6" s="3" t="str">
         <v>CDISCPILOT01</v>
       </c>
-      <c r="B6" s="6" t="str">
+      <c r="B6" s="3" t="str">
         <v>DM</v>
       </c>
-      <c r="C6" s="6" t="str">
+      <c r="C6" s="3" t="str">
         <v>CDISC002</v>
       </c>
-      <c r="D6" s="6">
+      <c r="D6" s="3">
         <v>1211</v>
       </c>
-      <c r="E6" s="6" t="str">
+      <c r="E6" s="3" t="str">
         <v>2018-05-24T12:00</v>
       </c>
-      <c r="F6" s="6" t="str">
+      <c r="F6" s="3" t="str">
         <v>2018-11-06</v>
       </c>
-      <c r="G6" s="6" t="str">
+      <c r="G6" s="3" t="str">
         <v>2018-05-24T12:00</v>
       </c>
-      <c r="H6" s="6" t="str">
+      <c r="H6" s="3" t="str">
         <v>2018-11-06</v>
       </c>
-      <c r="I6" s="6" t="str">
+      <c r="I6" s="3" t="str">
         <v>2018-05-07</v>
       </c>
-      <c r="J6" s="6" t="str">
+      <c r="J6" s="3" t="str">
         <v>2019-02-04</v>
       </c>
-      <c r="K6" s="6" t="str">
+      <c r="K6" s="3" t="str">
         <v>2019-02-04</v>
       </c>
-      <c r="L6" s="6" t="str">
+      <c r="L6" s="3" t="str">
         <v>Y</v>
       </c>
-      <c r="M6" s="6">
+      <c r="M6" s="3">
         <v>701</v>
       </c>
-      <c r="N6" s="6" t="str">
+      <c r="N6" s="3" t="str">
         <v>1905-05-08T00:00:00.000Z</v>
       </c>
-      <c r="O6" s="6" t="str">
+      <c r="O6" s="3" t="str">
         <v>78</v>
       </c>
-      <c r="P6" s="6" t="str">
+      <c r="P6" s="3" t="str">
         <v>YEARS</v>
       </c>
-      <c r="Q6" s="6" t="str">
+      <c r="Q6" s="3" t="str">
         <v>M</v>
       </c>
-      <c r="R6" s="6" t="str">
+      <c r="R6" s="3" t="str">
         <v>WHITE</v>
       </c>
-      <c r="S6" s="6" t="str">
+      <c r="S6" s="3" t="str">
         <v>NOT HISPANIC OR LATINO</v>
       </c>
-      <c r="T6" s="6" t="str">
+      <c r="T6" s="3" t="str">
         <v>P</v>
       </c>
-      <c r="U6" s="6" t="str">
+      <c r="U6" s="3" t="str">
         <v>Placebo</v>
       </c>
-      <c r="V6" s="6" t="str">
+      <c r="V6" s="3" t="str">
         <v>P</v>
       </c>
-      <c r="W6" s="6" t="str">
+      <c r="W6" s="3" t="str">
         <v>Placebo</v>
       </c>
-      <c r="X6" s="6" t="str">
+      <c r="X6" s="3" t="str">
         <v/>
       </c>
-      <c r="Y6" s="6" t="str">
+      <c r="Y6" s="3" t="str">
         <v/>
       </c>
-      <c r="Z6" s="6" t="str">
+      <c r="Z6" s="3" t="str">
         <v>AUS</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="str">
+      <c r="A7" s="3" t="str">
         <v>CDISCPILOT01</v>
       </c>
-      <c r="B7" s="7" t="str">
+      <c r="B7" s="3" t="str">
         <v>DM</v>
       </c>
-      <c r="C7" s="7" t="str">
+      <c r="C7" s="3" t="str">
         <v>CDISC003</v>
       </c>
-      <c r="D7" s="7">
+      <c r="D7" s="3">
         <v>1302</v>
       </c>
-      <c r="E7" s="7" t="str">
+      <c r="E7" s="3" t="str">
         <v>2006-01-16</v>
       </c>
-      <c r="F7" s="7" t="str">
+      <c r="F7" s="3" t="str">
         <v>2006-03-19</v>
       </c>
-      <c r="G7" s="7" t="str">
+      <c r="G7" s="3" t="str">
         <v>2006-01-16</v>
       </c>
-      <c r="H7" s="7" t="str">
+      <c r="H7" s="3" t="str">
         <v>2006-03-19</v>
       </c>
-      <c r="I7" s="7" t="str">
+      <c r="I7" s="3" t="str">
         <v>2006-01-02</v>
       </c>
-      <c r="J7" s="7" t="str">
+      <c r="J7" s="3" t="str">
         <v>2006-03-19</v>
       </c>
-      <c r="K7" s="7" t="str">
+      <c r="K7" s="3" t="str">
         <v/>
       </c>
-      <c r="L7" s="6" t="str">
+      <c r="L7" s="3" t="str">
         <v>Y</v>
       </c>
-      <c r="M7" s="7">
+      <c r="M7" s="3">
         <v>701</v>
       </c>
-      <c r="N7" s="7" t="str">
+      <c r="N7" s="3" t="str">
         <v>1944-06-16T00:00:00.000Z</v>
       </c>
-      <c r="O7" s="7" t="str">
+      <c r="O7" s="3" t="str">
         <v>74</v>
       </c>
-      <c r="P7" s="7" t="str">
+      <c r="P7" s="3" t="str">
         <v>YEARS</v>
       </c>
-      <c r="Q7" s="7" t="str">
+      <c r="Q7" s="3" t="str">
         <v>M</v>
       </c>
-      <c r="R7" s="7" t="str">
+      <c r="R7" s="3" t="str">
         <v>WHITE</v>
       </c>
-      <c r="S7" s="7" t="str">
+      <c r="S7" s="3" t="str">
         <v>NOT HISPANIC OR LATINO</v>
       </c>
-      <c r="T7" s="7" t="str">
+      <c r="T7" s="3" t="str">
         <v>B</v>
       </c>
-      <c r="U7" s="7" t="str">
+      <c r="U7" s="3" t="str">
         <v>Drug B</v>
       </c>
-      <c r="V7" s="7" t="str">
+      <c r="V7" s="3" t="str">
         <v>B</v>
       </c>
-      <c r="W7" s="7" t="str">
+      <c r="W7" s="3" t="str">
         <v>Drug B</v>
       </c>
-      <c r="X7" s="7" t="str">
+      <c r="X7" s="3" t="str">
         <v/>
       </c>
-      <c r="Y7" s="7" t="str">
+      <c r="Y7" s="3" t="str">
         <v/>
       </c>
-      <c r="Z7" s="7" t="str">
+      <c r="Z7" s="3" t="str">
         <v>CZE</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="str">
+      <c r="A8" s="3" t="str">
         <v>CDISCPILOT01</v>
       </c>
-      <c r="B8" s="7" t="str">
+      <c r="B8" s="3" t="str">
         <v>DM</v>
       </c>
-      <c r="C8" s="7" t="str">
+      <c r="C8" s="3" t="str">
         <v>CDISC004</v>
       </c>
-      <c r="D8" s="7">
+      <c r="D8" s="3">
         <v>1402</v>
       </c>
-      <c r="E8" s="7" t="str">
+      <c r="E8" s="3" t="str">
         <v>2018-07-16T09:15</v>
       </c>
-      <c r="F8" s="7" t="str">
+      <c r="F8" s="3" t="str">
         <v>2018-11-06T14:00</v>
       </c>
-      <c r="G8" s="7" t="str">
+      <c r="G8" s="3" t="str">
         <v>2018-07-16T09:15</v>
       </c>
-      <c r="H8" s="7" t="str">
+      <c r="H8" s="3" t="str">
         <v>2018-11-06T14:00</v>
       </c>
-      <c r="I8" s="7" t="str">
+      <c r="I8" s="3" t="str">
         <v>2018-06-27</v>
       </c>
-      <c r="J8" s="7" t="str">
+      <c r="J8" s="3" t="str">
         <v>2018-12-11</v>
       </c>
-      <c r="K8" s="7" t="str">
+      <c r="K8" s="3" t="str">
         <v/>
       </c>
-      <c r="L8" s="6" t="str">
+      <c r="L8" s="3" t="str">
         <v/>
       </c>
-      <c r="M8" s="7">
+      <c r="M8" s="3">
         <v>701</v>
       </c>
-      <c r="N8" s="7" t="str">
+      <c r="N8" s="3" t="str">
         <v>1905-04-16T00:00:00.000Z</v>
       </c>
-      <c r="O8" s="7" t="str">
+      <c r="O8" s="3" t="str">
         <v>68</v>
       </c>
-      <c r="P8" s="7" t="str">
+      <c r="P8" s="3" t="str">
         <v>YEARS</v>
       </c>
-      <c r="Q8" s="7" t="str">
+      <c r="Q8" s="3" t="str">
         <v>F</v>
       </c>
-      <c r="R8" s="7" t="str">
+      <c r="R8" s="3" t="str">
         <v>WHITE</v>
       </c>
-      <c r="S8" s="7" t="str">
+      <c r="S8" s="3" t="str">
         <v>HISPANIC OR LATINO</v>
       </c>
-      <c r="T8" s="7" t="str">
+      <c r="T8" s="3" t="str">
         <v>B</v>
       </c>
-      <c r="U8" s="7" t="str">
+      <c r="U8" s="3" t="str">
         <v>Drug B</v>
       </c>
-      <c r="V8" s="7" t="str">
+      <c r="V8" s="3" t="str">
         <v>B</v>
       </c>
-      <c r="W8" s="7" t="str">
+      <c r="W8" s="3" t="str">
         <v>Drug B</v>
       </c>
-      <c r="X8" s="7" t="str">
+      <c r="X8" s="3" t="str">
         <v/>
       </c>
-      <c r="Y8" s="7" t="str">
+      <c r="Y8" s="3" t="str">
         <v/>
       </c>
-      <c r="Z8" s="7" t="str">
+      <c r="Z8" s="3" t="str">
         <v>CAN</v>
       </c>
     </row>
@@ -1194,72 +1163,72 @@
   <dimension ref="A1:D5"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="str">
+      <c r="A1" s="4" t="str">
         <v>STUDYID</v>
       </c>
-      <c r="B1" s="3" t="str">
+      <c r="B1" s="4" t="str">
         <v>DOMAIN</v>
       </c>
-      <c r="C1" s="3" t="str">
+      <c r="C1" s="4" t="str">
         <v>USUBJID</v>
       </c>
-      <c r="D1" s="3" t="str">
-        <v>AESEQ</v>
+      <c r="D1" s="4" t="str">
+        <v>EXSEQ</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="8" t="str">
+      <c r="A2" s="5" t="str">
         <v>Study Identifier</v>
       </c>
-      <c r="B2" s="8" t="str">
+      <c r="B2" s="5" t="str">
         <v>Domain Abbreviation</v>
       </c>
-      <c r="C2" s="9" t="str">
+      <c r="C2" s="6" t="str">
         <v>Unique Subject Identifier</v>
       </c>
-      <c r="D2" s="9" t="str">
+      <c r="D2" s="6" t="str">
         <v>Sequence Number</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="9" t="str">
-        <v>Char</v>
-      </c>
-      <c r="B3" s="9" t="str">
-        <v>Char</v>
-      </c>
-      <c r="C3" s="9" t="str">
-        <v>Char</v>
-      </c>
-      <c r="D3" s="9" t="str">
+      <c r="A3" s="6" t="str">
+        <v>Char</v>
+      </c>
+      <c r="B3" s="6" t="str">
+        <v>Char</v>
+      </c>
+      <c r="C3" s="6" t="str">
+        <v>Char</v>
+      </c>
+      <c r="D3" s="6" t="str">
         <v>Num</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="9" t="str">
+      <c r="A4" s="6" t="str">
         <v>10</v>
       </c>
-      <c r="B4" s="9" t="str">
+      <c r="B4" s="6" t="str">
         <v>2</v>
       </c>
-      <c r="C4" s="9" t="str">
+      <c r="C4" s="6" t="str">
         <v>14</v>
       </c>
-      <c r="D4" s="9" t="str">
+      <c r="D4" s="6" t="str">
         <v>8</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="str">
+      <c r="A5" s="3" t="str">
         <v>CDISCPILOT01</v>
       </c>
-      <c r="B5" s="7" t="str">
-        <v>AE</v>
-      </c>
-      <c r="C5" s="7" t="str">
+      <c r="B5" s="3" t="str">
+        <v>EX</v>
+      </c>
+      <c r="C5" s="3" t="str">
         <v>CDISC-TEST-001</v>
       </c>
-      <c r="D5" s="7" t="str">
+      <c r="D5" s="3" t="str">
         <v>1</v>
       </c>
     </row>

--- a/rules/NEW-RULE/positive/01/data/new-rule-positive-01.xlsx
+++ b/rules/NEW-RULE/positive/01/data/new-rule-positive-01.xlsx
@@ -6,7 +6,7 @@
     <sheet name="Library" sheetId="1" r:id="rId1"/>
     <sheet name="Datasets" sheetId="2" r:id="rId2"/>
     <sheet name="dm.xpt" sheetId="3" r:id="rId3"/>
-    <sheet name="ae.xpt" sheetId="4" r:id="rId4"/>
+    <sheet name="vs.xpt" sheetId="4" r:id="rId4"/>
   </sheets>
 </workbook>
 </file>
@@ -36,7 +36,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
   <numFmts count="0"/>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -53,23 +57,6 @@
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
       <i/>
     </font>
     <font>
@@ -78,7 +65,7 @@
       <i/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="4">
     <fill>
       <patternFill patternType="none">
         <bgColor/>
@@ -86,21 +73,6 @@
     </fill>
     <fill>
       <patternFill patternType="gray125">
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <bgColor/>
       </patternFill>
     </fill>
@@ -136,17 +108,14 @@
   <cellStyleXfs>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="1" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -481,18 +450,18 @@
   <dimension ref="A1:B2"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="str">
+      <c r="A1" s="3" t="str">
         <v>Product</v>
       </c>
-      <c r="B1" s="2" t="str">
+      <c r="B1" s="3" t="str">
         <v>Version</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="str">
+      <c r="A2" s="3" t="str">
         <v>sdtmig</v>
       </c>
-      <c r="B2" s="2" t="str">
+      <c r="B2" s="3" t="str">
         <v>3-4</v>
       </c>
     </row>
@@ -508,27 +477,27 @@
   <dimension ref="A1:B3"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="str">
+      <c r="A1" s="3" t="str">
         <v>Filename</v>
       </c>
-      <c r="B1" s="2" t="str">
+      <c r="B1" s="3" t="str">
         <v>Label</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="str">
+      <c r="A2" s="3" t="str">
         <v>dm.xpt</v>
       </c>
-      <c r="B2" s="2" t="str">
+      <c r="B2" s="3" t="str">
         <v>Demographics</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="str">
-        <v>ae.xpt</v>
-      </c>
-      <c r="B3" s="2" t="str">
-        <v>Adverse Events</v>
+      <c r="A3" s="3" t="str">
+        <v>vs.xpt</v>
+      </c>
+      <c r="B3" s="3" t="str">
+        <v>Vital Signs</v>
       </c>
     </row>
   </sheetData>
@@ -543,642 +512,642 @@
   <dimension ref="A1:Z8"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="str">
+      <c r="A1" s="4" t="str">
         <v>STUDYID</v>
       </c>
-      <c r="B1" s="3" t="str">
+      <c r="B1" s="4" t="str">
         <v>DOMAIN</v>
       </c>
-      <c r="C1" s="3" t="str">
+      <c r="C1" s="4" t="str">
         <v>USUBJID</v>
       </c>
-      <c r="D1" s="3" t="str">
+      <c r="D1" s="4" t="str">
         <v>SUBJID</v>
       </c>
-      <c r="E1" s="3" t="str">
+      <c r="E1" s="4" t="str">
         <v>RFSTDTC</v>
       </c>
-      <c r="F1" s="3" t="str">
+      <c r="F1" s="4" t="str">
         <v>RFENDTC</v>
       </c>
-      <c r="G1" s="3" t="str">
+      <c r="G1" s="4" t="str">
         <v>RFXSTDTC</v>
       </c>
-      <c r="H1" s="3" t="str">
+      <c r="H1" s="4" t="str">
         <v>RFXENDTC</v>
       </c>
-      <c r="I1" s="3" t="str">
+      <c r="I1" s="4" t="str">
         <v>RFICDTC</v>
       </c>
-      <c r="J1" s="3" t="str">
+      <c r="J1" s="4" t="str">
         <v>RFPENDTC</v>
       </c>
-      <c r="K1" s="3" t="str">
+      <c r="K1" s="4" t="str">
         <v>DTHDTC</v>
       </c>
       <c r="L1" s="4" t="str">
         <v>DTHFL</v>
       </c>
-      <c r="M1" s="3" t="str">
+      <c r="M1" s="4" t="str">
         <v>SITEID</v>
       </c>
-      <c r="N1" s="3" t="str">
+      <c r="N1" s="4" t="str">
         <v>BRTHDTC</v>
       </c>
-      <c r="O1" s="3" t="str">
+      <c r="O1" s="4" t="str">
         <v>AGE</v>
       </c>
-      <c r="P1" s="3" t="str">
+      <c r="P1" s="4" t="str">
         <v>AGEU</v>
       </c>
-      <c r="Q1" s="3" t="str">
+      <c r="Q1" s="4" t="str">
         <v>SEX</v>
       </c>
-      <c r="R1" s="3" t="str">
+      <c r="R1" s="4" t="str">
         <v>RACE</v>
       </c>
-      <c r="S1" s="3" t="str">
+      <c r="S1" s="4" t="str">
         <v>ETHNIC</v>
       </c>
-      <c r="T1" s="3" t="str">
+      <c r="T1" s="4" t="str">
         <v>ARMCD</v>
       </c>
-      <c r="U1" s="3" t="str">
+      <c r="U1" s="4" t="str">
         <v>ARM</v>
       </c>
-      <c r="V1" s="3" t="str">
+      <c r="V1" s="4" t="str">
         <v>ACTARMCD</v>
       </c>
-      <c r="W1" s="3" t="str">
+      <c r="W1" s="4" t="str">
         <v>ACTARM</v>
       </c>
-      <c r="X1" s="3" t="str">
+      <c r="X1" s="4" t="str">
         <v>ARMNRS</v>
       </c>
-      <c r="Y1" s="3" t="str">
+      <c r="Y1" s="4" t="str">
         <v>ACTARMUD</v>
       </c>
-      <c r="Z1" s="3" t="str">
+      <c r="Z1" s="4" t="str">
         <v>COUNTRY</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="str">
+      <c r="A2" s="3" t="str">
         <v>Study Identifier</v>
       </c>
-      <c r="B2" s="5" t="str">
+      <c r="B2" s="3" t="str">
         <v>Domain Abbreviation</v>
       </c>
-      <c r="C2" s="6" t="str">
+      <c r="C2" s="3" t="str">
         <v>Unique Subject Identifier</v>
       </c>
-      <c r="D2" s="6" t="str">
+      <c r="D2" s="3" t="str">
         <v>Subject Identifier for the Study</v>
       </c>
-      <c r="E2" s="6" t="str">
+      <c r="E2" s="3" t="str">
         <v>Subject Reference Start Date/Time</v>
       </c>
-      <c r="F2" s="6" t="str">
+      <c r="F2" s="3" t="str">
         <v>Subject Reference End Date/Time</v>
       </c>
-      <c r="G2" s="6" t="str">
+      <c r="G2" s="3" t="str">
         <v>Date/Time of First Study Treatment</v>
       </c>
-      <c r="H2" s="6" t="str">
+      <c r="H2" s="3" t="str">
         <v>Date/Time of Last Study Treatment</v>
       </c>
-      <c r="I2" s="6" t="str">
+      <c r="I2" s="3" t="str">
         <v>Date/Time of Informed Consent</v>
       </c>
-      <c r="J2" s="6" t="str">
+      <c r="J2" s="3" t="str">
         <v>Date/Time of End of Participation</v>
       </c>
-      <c r="K2" s="6" t="str">
+      <c r="K2" s="3" t="str">
         <v>Date/Time of Death</v>
       </c>
-      <c r="L2" s="6" t="str">
+      <c r="L2" s="3" t="str">
         <v>Subject Death Flag</v>
       </c>
-      <c r="M2" s="6" t="str">
+      <c r="M2" s="3" t="str">
         <v>Study Site Identifier</v>
       </c>
-      <c r="N2" s="6" t="str">
+      <c r="N2" s="3" t="str">
         <v>Date/Time of Birth</v>
       </c>
-      <c r="O2" s="6" t="str">
+      <c r="O2" s="3" t="str">
         <v>Age</v>
       </c>
-      <c r="P2" s="6" t="str">
+      <c r="P2" s="3" t="str">
         <v>Age Units</v>
       </c>
-      <c r="Q2" s="6" t="str">
+      <c r="Q2" s="3" t="str">
         <v>Sex</v>
       </c>
-      <c r="R2" s="6" t="str">
+      <c r="R2" s="3" t="str">
         <v>Race</v>
       </c>
-      <c r="S2" s="6" t="str">
+      <c r="S2" s="3" t="str">
         <v>Ethnicity</v>
       </c>
-      <c r="T2" s="6" t="str">
+      <c r="T2" s="3" t="str">
         <v>Planned Arm Code</v>
       </c>
-      <c r="U2" s="6" t="str">
+      <c r="U2" s="3" t="str">
         <v>Description of Planned Arm</v>
       </c>
-      <c r="V2" s="6" t="str">
+      <c r="V2" s="3" t="str">
         <v>Actual Arm Code</v>
       </c>
-      <c r="W2" s="6" t="str">
+      <c r="W2" s="3" t="str">
         <v>Description of Actual Arm</v>
       </c>
-      <c r="X2" s="6" t="str">
+      <c r="X2" s="3" t="str">
         <v>Reason Arm and/or Actual Arm is Null</v>
       </c>
-      <c r="Y2" s="6" t="str">
+      <c r="Y2" s="3" t="str">
         <v>Description of Unplanned Actual Arm</v>
       </c>
-      <c r="Z2" s="6" t="str">
+      <c r="Z2" s="3" t="str">
         <v>Country</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="B3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="C3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="D3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="E3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="F3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="G3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="H3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="I3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="J3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="K3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="L3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="M3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="N3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="O3" s="7" t="str">
+      <c r="A3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="B3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="C3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="D3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="E3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="F3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="G3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="H3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="I3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="J3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="K3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="L3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="M3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="N3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="O3" s="3" t="str">
         <v>Num</v>
       </c>
-      <c r="P3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="Q3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="R3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="S3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="T3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="U3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="V3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="W3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="X3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="Y3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="Z3" s="7" t="str">
+      <c r="P3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="Q3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="R3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="S3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="T3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="U3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="V3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="W3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="X3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="Y3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="Z3" s="3" t="str">
         <v>Char</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6">
+      <c r="A4" s="3">
         <v>12</v>
       </c>
-      <c r="B4" s="6">
+      <c r="B4" s="3">
         <v>2</v>
       </c>
-      <c r="C4" s="6">
+      <c r="C4" s="3">
         <v>8</v>
       </c>
-      <c r="D4" s="6">
+      <c r="D4" s="3">
         <v>4</v>
       </c>
-      <c r="E4" s="6">
+      <c r="E4" s="3">
         <v>10</v>
       </c>
-      <c r="F4" s="6">
+      <c r="F4" s="3">
         <v>10</v>
       </c>
-      <c r="G4" s="6">
+      <c r="G4" s="3">
         <v>10</v>
       </c>
-      <c r="H4" s="6">
+      <c r="H4" s="3">
         <v>10</v>
       </c>
-      <c r="I4" s="6">
+      <c r="I4" s="3">
         <v>10</v>
       </c>
-      <c r="J4" s="6">
+      <c r="J4" s="3">
         <v>10</v>
       </c>
-      <c r="K4" s="6">
+      <c r="K4" s="3">
         <v>10</v>
       </c>
-      <c r="L4" s="6">
+      <c r="L4" s="3">
         <v>1</v>
       </c>
-      <c r="M4" s="6">
+      <c r="M4" s="3">
         <v>3</v>
       </c>
-      <c r="N4" s="6">
+      <c r="N4" s="3">
         <v>10</v>
       </c>
-      <c r="O4" s="6">
+      <c r="O4" s="3">
         <v>8</v>
       </c>
-      <c r="P4" s="6">
+      <c r="P4" s="3">
         <v>5</v>
       </c>
-      <c r="Q4" s="6">
+      <c r="Q4" s="3">
         <v>1</v>
       </c>
-      <c r="R4" s="6">
+      <c r="R4" s="3">
         <v>41</v>
       </c>
-      <c r="S4" s="6">
+      <c r="S4" s="3">
         <v>22</v>
       </c>
-      <c r="T4" s="6">
+      <c r="T4" s="3">
         <v>8</v>
       </c>
-      <c r="U4" s="6">
+      <c r="U4" s="3">
         <v>28</v>
       </c>
-      <c r="V4" s="6">
+      <c r="V4" s="3">
         <v>8</v>
       </c>
-      <c r="W4" s="6">
+      <c r="W4" s="3">
         <v>28</v>
       </c>
-      <c r="X4" s="6">
+      <c r="X4" s="3">
         <v>14</v>
       </c>
-      <c r="Y4" s="6">
+      <c r="Y4" s="3">
         <v>200</v>
       </c>
-      <c r="Z4" s="6">
+      <c r="Z4" s="3">
         <v>3</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="str">
+      <c r="A5" s="3" t="str">
         <v>CDISCPILOT01</v>
       </c>
-      <c r="B5" s="7" t="str">
+      <c r="B5" s="3" t="str">
         <v>DM</v>
       </c>
-      <c r="C5" s="7" t="str">
+      <c r="C5" s="3" t="str">
         <v>CDISC001</v>
       </c>
-      <c r="D5" s="7">
+      <c r="D5" s="3">
         <v>1115</v>
       </c>
-      <c r="E5" s="7" t="str">
+      <c r="E5" s="3" t="str">
         <v>2018-05-17T09:35</v>
       </c>
-      <c r="F5" s="7" t="str">
+      <c r="F5" s="3" t="str">
         <v>2018-08-03</v>
       </c>
-      <c r="G5" s="7" t="str">
+      <c r="G5" s="3" t="str">
         <v>2018-05-17T09:35</v>
       </c>
-      <c r="H5" s="7" t="str">
+      <c r="H5" s="3" t="str">
         <v>2018-08-03</v>
       </c>
-      <c r="I5" s="7" t="str">
+      <c r="I5" s="3" t="str">
         <v>2018-04-26</v>
       </c>
-      <c r="J5" s="7" t="str">
+      <c r="J5" s="3" t="str">
         <v>2018-08-22</v>
       </c>
-      <c r="K5" s="7" t="str">
+      <c r="K5" s="3" t="str">
         <v>2018-08-22</v>
       </c>
-      <c r="L5" s="6" t="str">
+      <c r="L5" s="3" t="str">
         <v>Y</v>
       </c>
-      <c r="M5" s="7">
+      <c r="M5" s="3">
         <v>701</v>
       </c>
-      <c r="N5" s="7" t="str">
+      <c r="N5" s="3" t="str">
         <v>1947-07-24T00:00:00.000Z</v>
       </c>
-      <c r="O5" s="7" t="str">
+      <c r="O5" s="3" t="str">
         <v>70</v>
       </c>
-      <c r="P5" s="7" t="str">
+      <c r="P5" s="3" t="str">
         <v>YEARS</v>
       </c>
-      <c r="Q5" s="7" t="str">
+      <c r="Q5" s="3" t="str">
         <v>M</v>
       </c>
-      <c r="R5" s="7" t="str">
+      <c r="R5" s="3" t="str">
         <v>WHITE</v>
       </c>
-      <c r="S5" s="7" t="str">
+      <c r="S5" s="3" t="str">
         <v>NOT HISPANIC OR LATINO</v>
       </c>
-      <c r="T5" s="7" t="str">
+      <c r="T5" s="3" t="str">
         <v>A</v>
       </c>
-      <c r="U5" s="7" t="str">
+      <c r="U5" s="3" t="str">
         <v>Drug A</v>
       </c>
-      <c r="V5" s="7" t="str">
+      <c r="V5" s="3" t="str">
         <v>A</v>
       </c>
-      <c r="W5" s="7" t="str">
+      <c r="W5" s="3" t="str">
         <v>Drug A</v>
       </c>
-      <c r="X5" s="7" t="str">
+      <c r="X5" s="3" t="str">
         <v/>
       </c>
-      <c r="Y5" s="7" t="str">
+      <c r="Y5" s="3" t="str">
         <v/>
       </c>
-      <c r="Z5" s="7" t="str">
+      <c r="Z5" s="3" t="str">
         <v>AUS</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="str">
+      <c r="A6" s="3" t="str">
         <v>CDISCPILOT01</v>
       </c>
-      <c r="B6" s="6" t="str">
+      <c r="B6" s="3" t="str">
         <v>DM</v>
       </c>
-      <c r="C6" s="6" t="str">
+      <c r="C6" s="3" t="str">
         <v>CDISC002</v>
       </c>
-      <c r="D6" s="6">
+      <c r="D6" s="3">
         <v>1211</v>
       </c>
-      <c r="E6" s="6" t="str">
+      <c r="E6" s="3" t="str">
         <v>2018-05-24T12:00</v>
       </c>
-      <c r="F6" s="6" t="str">
+      <c r="F6" s="3" t="str">
         <v>2018-11-06</v>
       </c>
-      <c r="G6" s="6" t="str">
+      <c r="G6" s="3" t="str">
         <v>2018-05-24T12:00</v>
       </c>
-      <c r="H6" s="6" t="str">
+      <c r="H6" s="3" t="str">
         <v>2018-11-06</v>
       </c>
-      <c r="I6" s="6" t="str">
+      <c r="I6" s="3" t="str">
         <v>2018-05-07</v>
       </c>
-      <c r="J6" s="6" t="str">
+      <c r="J6" s="3" t="str">
         <v>2019-02-04</v>
       </c>
-      <c r="K6" s="6" t="str">
+      <c r="K6" s="3" t="str">
         <v>2019-02-04</v>
       </c>
-      <c r="L6" s="6" t="str">
+      <c r="L6" s="3" t="str">
         <v>Y</v>
       </c>
-      <c r="M6" s="6">
+      <c r="M6" s="3">
         <v>701</v>
       </c>
-      <c r="N6" s="6" t="str">
+      <c r="N6" s="3" t="str">
         <v>1905-05-08T00:00:00.000Z</v>
       </c>
-      <c r="O6" s="6" t="str">
+      <c r="O6" s="3" t="str">
         <v>78</v>
       </c>
-      <c r="P6" s="6" t="str">
+      <c r="P6" s="3" t="str">
         <v>YEARS</v>
       </c>
-      <c r="Q6" s="6" t="str">
+      <c r="Q6" s="3" t="str">
         <v>M</v>
       </c>
-      <c r="R6" s="6" t="str">
+      <c r="R6" s="3" t="str">
         <v>WHITE</v>
       </c>
-      <c r="S6" s="6" t="str">
+      <c r="S6" s="3" t="str">
         <v>NOT HISPANIC OR LATINO</v>
       </c>
-      <c r="T6" s="6" t="str">
+      <c r="T6" s="3" t="str">
         <v>P</v>
       </c>
-      <c r="U6" s="6" t="str">
+      <c r="U6" s="3" t="str">
         <v>Placebo</v>
       </c>
-      <c r="V6" s="6" t="str">
+      <c r="V6" s="3" t="str">
         <v>P</v>
       </c>
-      <c r="W6" s="6" t="str">
+      <c r="W6" s="3" t="str">
         <v>Placebo</v>
       </c>
-      <c r="X6" s="6" t="str">
+      <c r="X6" s="3" t="str">
         <v/>
       </c>
-      <c r="Y6" s="6" t="str">
+      <c r="Y6" s="3" t="str">
         <v/>
       </c>
-      <c r="Z6" s="6" t="str">
+      <c r="Z6" s="3" t="str">
         <v>AUS</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="str">
+      <c r="A7" s="3" t="str">
         <v>CDISCPILOT01</v>
       </c>
-      <c r="B7" s="7" t="str">
+      <c r="B7" s="3" t="str">
         <v>DM</v>
       </c>
-      <c r="C7" s="7" t="str">
+      <c r="C7" s="3" t="str">
         <v>CDISC003</v>
       </c>
-      <c r="D7" s="7">
+      <c r="D7" s="3">
         <v>1302</v>
       </c>
-      <c r="E7" s="7" t="str">
+      <c r="E7" s="3" t="str">
         <v>2006-01-16</v>
       </c>
-      <c r="F7" s="7" t="str">
+      <c r="F7" s="3" t="str">
         <v>2006-03-19</v>
       </c>
-      <c r="G7" s="7" t="str">
+      <c r="G7" s="3" t="str">
         <v>2006-01-16</v>
       </c>
-      <c r="H7" s="7" t="str">
+      <c r="H7" s="3" t="str">
         <v>2006-03-19</v>
       </c>
-      <c r="I7" s="7" t="str">
+      <c r="I7" s="3" t="str">
         <v>2006-01-02</v>
       </c>
-      <c r="J7" s="7" t="str">
+      <c r="J7" s="3" t="str">
         <v>2006-03-19</v>
       </c>
-      <c r="K7" s="7" t="str">
+      <c r="K7" s="3" t="str">
         <v/>
       </c>
-      <c r="L7" s="6" t="str">
+      <c r="L7" s="3" t="str">
         <v>Y</v>
       </c>
-      <c r="M7" s="7">
+      <c r="M7" s="3">
         <v>701</v>
       </c>
-      <c r="N7" s="7" t="str">
+      <c r="N7" s="3" t="str">
         <v>1944-06-16T00:00:00.000Z</v>
       </c>
-      <c r="O7" s="7" t="str">
+      <c r="O7" s="3" t="str">
         <v>74</v>
       </c>
-      <c r="P7" s="7" t="str">
+      <c r="P7" s="3" t="str">
         <v>YEARS</v>
       </c>
-      <c r="Q7" s="7" t="str">
+      <c r="Q7" s="3" t="str">
         <v>M</v>
       </c>
-      <c r="R7" s="7" t="str">
+      <c r="R7" s="3" t="str">
         <v>WHITE</v>
       </c>
-      <c r="S7" s="7" t="str">
+      <c r="S7" s="3" t="str">
         <v>NOT HISPANIC OR LATINO</v>
       </c>
-      <c r="T7" s="7" t="str">
+      <c r="T7" s="3" t="str">
         <v>B</v>
       </c>
-      <c r="U7" s="7" t="str">
+      <c r="U7" s="3" t="str">
         <v>Drug B</v>
       </c>
-      <c r="V7" s="7" t="str">
+      <c r="V7" s="3" t="str">
         <v>B</v>
       </c>
-      <c r="W7" s="7" t="str">
+      <c r="W7" s="3" t="str">
         <v>Drug B</v>
       </c>
-      <c r="X7" s="7" t="str">
+      <c r="X7" s="3" t="str">
         <v/>
       </c>
-      <c r="Y7" s="7" t="str">
+      <c r="Y7" s="3" t="str">
         <v/>
       </c>
-      <c r="Z7" s="7" t="str">
+      <c r="Z7" s="3" t="str">
         <v>CZE</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="str">
+      <c r="A8" s="3" t="str">
         <v>CDISCPILOT01</v>
       </c>
-      <c r="B8" s="7" t="str">
+      <c r="B8" s="3" t="str">
         <v>DM</v>
       </c>
-      <c r="C8" s="7" t="str">
+      <c r="C8" s="3" t="str">
         <v>CDISC004</v>
       </c>
-      <c r="D8" s="7">
+      <c r="D8" s="3">
         <v>1402</v>
       </c>
-      <c r="E8" s="7" t="str">
+      <c r="E8" s="3" t="str">
         <v>2018-07-16T09:15</v>
       </c>
-      <c r="F8" s="7" t="str">
+      <c r="F8" s="3" t="str">
         <v>2018-11-06T14:00</v>
       </c>
-      <c r="G8" s="7" t="str">
+      <c r="G8" s="3" t="str">
         <v>2018-07-16T09:15</v>
       </c>
-      <c r="H8" s="7" t="str">
+      <c r="H8" s="3" t="str">
         <v>2018-11-06T14:00</v>
       </c>
-      <c r="I8" s="7" t="str">
+      <c r="I8" s="3" t="str">
         <v>2018-06-27</v>
       </c>
-      <c r="J8" s="7" t="str">
+      <c r="J8" s="3" t="str">
         <v>2018-12-11</v>
       </c>
-      <c r="K8" s="7" t="str">
+      <c r="K8" s="3" t="str">
         <v/>
       </c>
-      <c r="L8" s="6" t="str">
+      <c r="L8" s="3" t="str">
         <v/>
       </c>
-      <c r="M8" s="7">
+      <c r="M8" s="3">
         <v>701</v>
       </c>
-      <c r="N8" s="7" t="str">
+      <c r="N8" s="3" t="str">
         <v>1905-04-16T00:00:00.000Z</v>
       </c>
-      <c r="O8" s="7" t="str">
+      <c r="O8" s="3" t="str">
         <v>68</v>
       </c>
-      <c r="P8" s="7" t="str">
+      <c r="P8" s="3" t="str">
         <v>YEARS</v>
       </c>
-      <c r="Q8" s="7" t="str">
+      <c r="Q8" s="3" t="str">
         <v>F</v>
       </c>
-      <c r="R8" s="7" t="str">
+      <c r="R8" s="3" t="str">
         <v>WHITE</v>
       </c>
-      <c r="S8" s="7" t="str">
+      <c r="S8" s="3" t="str">
         <v>HISPANIC OR LATINO</v>
       </c>
-      <c r="T8" s="7" t="str">
+      <c r="T8" s="3" t="str">
         <v>B</v>
       </c>
-      <c r="U8" s="7" t="str">
+      <c r="U8" s="3" t="str">
         <v>Drug B</v>
       </c>
-      <c r="V8" s="7" t="str">
+      <c r="V8" s="3" t="str">
         <v>B</v>
       </c>
-      <c r="W8" s="7" t="str">
+      <c r="W8" s="3" t="str">
         <v>Drug B</v>
       </c>
-      <c r="X8" s="7" t="str">
+      <c r="X8" s="3" t="str">
         <v/>
       </c>
-      <c r="Y8" s="7" t="str">
+      <c r="Y8" s="3" t="str">
         <v/>
       </c>
-      <c r="Z8" s="7" t="str">
+      <c r="Z8" s="3" t="str">
         <v>CAN</v>
       </c>
     </row>
@@ -1194,72 +1163,72 @@
   <dimension ref="A1:D5"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="str">
+      <c r="A1" s="4" t="str">
         <v>STUDYID</v>
       </c>
-      <c r="B1" s="3" t="str">
+      <c r="B1" s="4" t="str">
         <v>DOMAIN</v>
       </c>
-      <c r="C1" s="3" t="str">
+      <c r="C1" s="4" t="str">
         <v>USUBJID</v>
       </c>
-      <c r="D1" s="3" t="str">
-        <v>AESEQ</v>
+      <c r="D1" s="4" t="str">
+        <v>VSSEQ</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="8" t="str">
+      <c r="A2" s="5" t="str">
         <v>Study Identifier</v>
       </c>
-      <c r="B2" s="8" t="str">
+      <c r="B2" s="5" t="str">
         <v>Domain Abbreviation</v>
       </c>
-      <c r="C2" s="9" t="str">
+      <c r="C2" s="6" t="str">
         <v>Unique Subject Identifier</v>
       </c>
-      <c r="D2" s="9" t="str">
+      <c r="D2" s="6" t="str">
         <v>Sequence Number</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="9" t="str">
-        <v>Char</v>
-      </c>
-      <c r="B3" s="9" t="str">
-        <v>Char</v>
-      </c>
-      <c r="C3" s="9" t="str">
-        <v>Char</v>
-      </c>
-      <c r="D3" s="9" t="str">
+      <c r="A3" s="6" t="str">
+        <v>Char</v>
+      </c>
+      <c r="B3" s="6" t="str">
+        <v>Char</v>
+      </c>
+      <c r="C3" s="6" t="str">
+        <v>Char</v>
+      </c>
+      <c r="D3" s="6" t="str">
         <v>Num</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="9" t="str">
+      <c r="A4" s="6" t="str">
         <v>10</v>
       </c>
-      <c r="B4" s="9" t="str">
+      <c r="B4" s="6" t="str">
         <v>2</v>
       </c>
-      <c r="C4" s="9" t="str">
+      <c r="C4" s="6" t="str">
         <v>14</v>
       </c>
-      <c r="D4" s="9" t="str">
+      <c r="D4" s="6" t="str">
         <v>8</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="str">
+      <c r="A5" s="3" t="str">
         <v>CDISCPILOT01</v>
       </c>
-      <c r="B5" s="7" t="str">
-        <v>AE</v>
-      </c>
-      <c r="C5" s="7" t="str">
+      <c r="B5" s="3" t="str">
+        <v>VS</v>
+      </c>
+      <c r="C5" s="3" t="str">
         <v>CDISC-TEST-001</v>
       </c>
-      <c r="D5" s="7" t="str">
+      <c r="D5" s="3" t="str">
         <v>1</v>
       </c>
     </row>

--- a/rules/NEW-RULE/positive/01/data/new-rule-positive-01.xlsx
+++ b/rules/NEW-RULE/positive/01/data/new-rule-positive-01.xlsx
@@ -6,7 +6,7 @@
     <sheet name="Library" sheetId="1" r:id="rId1"/>
     <sheet name="Datasets" sheetId="2" r:id="rId2"/>
     <sheet name="dm.xpt" sheetId="3" r:id="rId3"/>
-    <sheet name="ae.xpt" sheetId="4" r:id="rId4"/>
+    <sheet name="ce.xpt" sheetId="4" r:id="rId4"/>
   </sheets>
 </workbook>
 </file>
@@ -36,7 +36,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
   <numFmts count="0"/>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -53,23 +57,6 @@
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
       <i/>
     </font>
     <font>
@@ -78,7 +65,7 @@
       <i/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="4">
     <fill>
       <patternFill patternType="none">
         <bgColor/>
@@ -86,21 +73,6 @@
     </fill>
     <fill>
       <patternFill patternType="gray125">
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <bgColor/>
       </patternFill>
     </fill>
@@ -136,17 +108,14 @@
   <cellStyleXfs>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="1" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -481,18 +450,18 @@
   <dimension ref="A1:B2"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="str">
+      <c r="A1" s="3" t="str">
         <v>Product</v>
       </c>
-      <c r="B1" s="2" t="str">
+      <c r="B1" s="3" t="str">
         <v>Version</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="str">
+      <c r="A2" s="3" t="str">
         <v>sdtmig</v>
       </c>
-      <c r="B2" s="2" t="str">
+      <c r="B2" s="3" t="str">
         <v>3-4</v>
       </c>
     </row>
@@ -508,27 +477,27 @@
   <dimension ref="A1:B3"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="str">
+      <c r="A1" s="3" t="str">
         <v>Filename</v>
       </c>
-      <c r="B1" s="2" t="str">
+      <c r="B1" s="3" t="str">
         <v>Label</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="str">
+      <c r="A2" s="3" t="str">
         <v>dm.xpt</v>
       </c>
-      <c r="B2" s="2" t="str">
+      <c r="B2" s="3" t="str">
         <v>Demographics</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="str">
-        <v>ae.xpt</v>
-      </c>
-      <c r="B3" s="2" t="str">
-        <v>Adverse Events</v>
+      <c r="A3" s="3" t="str">
+        <v>ce.xpt</v>
+      </c>
+      <c r="B3" s="3" t="str">
+        <v>Clinical Events</v>
       </c>
     </row>
   </sheetData>
@@ -543,642 +512,642 @@
   <dimension ref="A1:Z8"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="str">
+      <c r="A1" s="4" t="str">
         <v>STUDYID</v>
       </c>
-      <c r="B1" s="3" t="str">
+      <c r="B1" s="4" t="str">
         <v>DOMAIN</v>
       </c>
-      <c r="C1" s="3" t="str">
+      <c r="C1" s="4" t="str">
         <v>USUBJID</v>
       </c>
-      <c r="D1" s="3" t="str">
+      <c r="D1" s="4" t="str">
         <v>SUBJID</v>
       </c>
-      <c r="E1" s="3" t="str">
+      <c r="E1" s="4" t="str">
         <v>RFSTDTC</v>
       </c>
-      <c r="F1" s="3" t="str">
+      <c r="F1" s="4" t="str">
         <v>RFENDTC</v>
       </c>
-      <c r="G1" s="3" t="str">
+      <c r="G1" s="4" t="str">
         <v>RFXSTDTC</v>
       </c>
-      <c r="H1" s="3" t="str">
+      <c r="H1" s="4" t="str">
         <v>RFXENDTC</v>
       </c>
-      <c r="I1" s="3" t="str">
+      <c r="I1" s="4" t="str">
         <v>RFICDTC</v>
       </c>
-      <c r="J1" s="3" t="str">
+      <c r="J1" s="4" t="str">
         <v>RFPENDTC</v>
       </c>
-      <c r="K1" s="3" t="str">
+      <c r="K1" s="4" t="str">
         <v>DTHDTC</v>
       </c>
       <c r="L1" s="4" t="str">
         <v>DTHFL</v>
       </c>
-      <c r="M1" s="3" t="str">
+      <c r="M1" s="4" t="str">
         <v>SITEID</v>
       </c>
-      <c r="N1" s="3" t="str">
+      <c r="N1" s="4" t="str">
         <v>BRTHDTC</v>
       </c>
-      <c r="O1" s="3" t="str">
+      <c r="O1" s="4" t="str">
         <v>AGE</v>
       </c>
-      <c r="P1" s="3" t="str">
+      <c r="P1" s="4" t="str">
         <v>AGEU</v>
       </c>
-      <c r="Q1" s="3" t="str">
+      <c r="Q1" s="4" t="str">
         <v>SEX</v>
       </c>
-      <c r="R1" s="3" t="str">
+      <c r="R1" s="4" t="str">
         <v>RACE</v>
       </c>
-      <c r="S1" s="3" t="str">
+      <c r="S1" s="4" t="str">
         <v>ETHNIC</v>
       </c>
-      <c r="T1" s="3" t="str">
+      <c r="T1" s="4" t="str">
         <v>ARMCD</v>
       </c>
-      <c r="U1" s="3" t="str">
+      <c r="U1" s="4" t="str">
         <v>ARM</v>
       </c>
-      <c r="V1" s="3" t="str">
+      <c r="V1" s="4" t="str">
         <v>ACTARMCD</v>
       </c>
-      <c r="W1" s="3" t="str">
+      <c r="W1" s="4" t="str">
         <v>ACTARM</v>
       </c>
-      <c r="X1" s="3" t="str">
+      <c r="X1" s="4" t="str">
         <v>ARMNRS</v>
       </c>
-      <c r="Y1" s="3" t="str">
+      <c r="Y1" s="4" t="str">
         <v>ACTARMUD</v>
       </c>
-      <c r="Z1" s="3" t="str">
+      <c r="Z1" s="4" t="str">
         <v>COUNTRY</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="str">
+      <c r="A2" s="3" t="str">
         <v>Study Identifier</v>
       </c>
-      <c r="B2" s="5" t="str">
+      <c r="B2" s="3" t="str">
         <v>Domain Abbreviation</v>
       </c>
-      <c r="C2" s="6" t="str">
+      <c r="C2" s="3" t="str">
         <v>Unique Subject Identifier</v>
       </c>
-      <c r="D2" s="6" t="str">
+      <c r="D2" s="3" t="str">
         <v>Subject Identifier for the Study</v>
       </c>
-      <c r="E2" s="6" t="str">
+      <c r="E2" s="3" t="str">
         <v>Subject Reference Start Date/Time</v>
       </c>
-      <c r="F2" s="6" t="str">
+      <c r="F2" s="3" t="str">
         <v>Subject Reference End Date/Time</v>
       </c>
-      <c r="G2" s="6" t="str">
+      <c r="G2" s="3" t="str">
         <v>Date/Time of First Study Treatment</v>
       </c>
-      <c r="H2" s="6" t="str">
+      <c r="H2" s="3" t="str">
         <v>Date/Time of Last Study Treatment</v>
       </c>
-      <c r="I2" s="6" t="str">
+      <c r="I2" s="3" t="str">
         <v>Date/Time of Informed Consent</v>
       </c>
-      <c r="J2" s="6" t="str">
+      <c r="J2" s="3" t="str">
         <v>Date/Time of End of Participation</v>
       </c>
-      <c r="K2" s="6" t="str">
+      <c r="K2" s="3" t="str">
         <v>Date/Time of Death</v>
       </c>
-      <c r="L2" s="6" t="str">
+      <c r="L2" s="3" t="str">
         <v>Subject Death Flag</v>
       </c>
-      <c r="M2" s="6" t="str">
+      <c r="M2" s="3" t="str">
         <v>Study Site Identifier</v>
       </c>
-      <c r="N2" s="6" t="str">
+      <c r="N2" s="3" t="str">
         <v>Date/Time of Birth</v>
       </c>
-      <c r="O2" s="6" t="str">
+      <c r="O2" s="3" t="str">
         <v>Age</v>
       </c>
-      <c r="P2" s="6" t="str">
+      <c r="P2" s="3" t="str">
         <v>Age Units</v>
       </c>
-      <c r="Q2" s="6" t="str">
+      <c r="Q2" s="3" t="str">
         <v>Sex</v>
       </c>
-      <c r="R2" s="6" t="str">
+      <c r="R2" s="3" t="str">
         <v>Race</v>
       </c>
-      <c r="S2" s="6" t="str">
+      <c r="S2" s="3" t="str">
         <v>Ethnicity</v>
       </c>
-      <c r="T2" s="6" t="str">
+      <c r="T2" s="3" t="str">
         <v>Planned Arm Code</v>
       </c>
-      <c r="U2" s="6" t="str">
+      <c r="U2" s="3" t="str">
         <v>Description of Planned Arm</v>
       </c>
-      <c r="V2" s="6" t="str">
+      <c r="V2" s="3" t="str">
         <v>Actual Arm Code</v>
       </c>
-      <c r="W2" s="6" t="str">
+      <c r="W2" s="3" t="str">
         <v>Description of Actual Arm</v>
       </c>
-      <c r="X2" s="6" t="str">
+      <c r="X2" s="3" t="str">
         <v>Reason Arm and/or Actual Arm is Null</v>
       </c>
-      <c r="Y2" s="6" t="str">
+      <c r="Y2" s="3" t="str">
         <v>Description of Unplanned Actual Arm</v>
       </c>
-      <c r="Z2" s="6" t="str">
+      <c r="Z2" s="3" t="str">
         <v>Country</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="B3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="C3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="D3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="E3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="F3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="G3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="H3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="I3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="J3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="K3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="L3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="M3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="N3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="O3" s="7" t="str">
+      <c r="A3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="B3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="C3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="D3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="E3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="F3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="G3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="H3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="I3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="J3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="K3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="L3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="M3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="N3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="O3" s="3" t="str">
         <v>Num</v>
       </c>
-      <c r="P3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="Q3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="R3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="S3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="T3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="U3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="V3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="W3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="X3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="Y3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="Z3" s="7" t="str">
+      <c r="P3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="Q3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="R3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="S3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="T3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="U3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="V3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="W3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="X3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="Y3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="Z3" s="3" t="str">
         <v>Char</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6">
+      <c r="A4" s="3">
         <v>12</v>
       </c>
-      <c r="B4" s="6">
+      <c r="B4" s="3">
         <v>2</v>
       </c>
-      <c r="C4" s="6">
+      <c r="C4" s="3">
         <v>8</v>
       </c>
-      <c r="D4" s="6">
+      <c r="D4" s="3">
         <v>4</v>
       </c>
-      <c r="E4" s="6">
+      <c r="E4" s="3">
         <v>10</v>
       </c>
-      <c r="F4" s="6">
+      <c r="F4" s="3">
         <v>10</v>
       </c>
-      <c r="G4" s="6">
+      <c r="G4" s="3">
         <v>10</v>
       </c>
-      <c r="H4" s="6">
+      <c r="H4" s="3">
         <v>10</v>
       </c>
-      <c r="I4" s="6">
+      <c r="I4" s="3">
         <v>10</v>
       </c>
-      <c r="J4" s="6">
+      <c r="J4" s="3">
         <v>10</v>
       </c>
-      <c r="K4" s="6">
+      <c r="K4" s="3">
         <v>10</v>
       </c>
-      <c r="L4" s="6">
+      <c r="L4" s="3">
         <v>1</v>
       </c>
-      <c r="M4" s="6">
+      <c r="M4" s="3">
         <v>3</v>
       </c>
-      <c r="N4" s="6">
+      <c r="N4" s="3">
         <v>10</v>
       </c>
-      <c r="O4" s="6">
+      <c r="O4" s="3">
         <v>8</v>
       </c>
-      <c r="P4" s="6">
+      <c r="P4" s="3">
         <v>5</v>
       </c>
-      <c r="Q4" s="6">
+      <c r="Q4" s="3">
         <v>1</v>
       </c>
-      <c r="R4" s="6">
+      <c r="R4" s="3">
         <v>41</v>
       </c>
-      <c r="S4" s="6">
+      <c r="S4" s="3">
         <v>22</v>
       </c>
-      <c r="T4" s="6">
+      <c r="T4" s="3">
         <v>8</v>
       </c>
-      <c r="U4" s="6">
+      <c r="U4" s="3">
         <v>28</v>
       </c>
-      <c r="V4" s="6">
+      <c r="V4" s="3">
         <v>8</v>
       </c>
-      <c r="W4" s="6">
+      <c r="W4" s="3">
         <v>28</v>
       </c>
-      <c r="X4" s="6">
+      <c r="X4" s="3">
         <v>14</v>
       </c>
-      <c r="Y4" s="6">
+      <c r="Y4" s="3">
         <v>200</v>
       </c>
-      <c r="Z4" s="6">
+      <c r="Z4" s="3">
         <v>3</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="str">
+      <c r="A5" s="3" t="str">
         <v>CDISCPILOT01</v>
       </c>
-      <c r="B5" s="7" t="str">
+      <c r="B5" s="3" t="str">
         <v>DM</v>
       </c>
-      <c r="C5" s="7" t="str">
+      <c r="C5" s="3" t="str">
         <v>CDISC001</v>
       </c>
-      <c r="D5" s="7">
+      <c r="D5" s="3">
         <v>1115</v>
       </c>
-      <c r="E5" s="7" t="str">
+      <c r="E5" s="3" t="str">
         <v>2018-05-17T09:35</v>
       </c>
-      <c r="F5" s="7" t="str">
+      <c r="F5" s="3" t="str">
         <v>2018-08-03</v>
       </c>
-      <c r="G5" s="7" t="str">
+      <c r="G5" s="3" t="str">
         <v>2018-05-17T09:35</v>
       </c>
-      <c r="H5" s="7" t="str">
+      <c r="H5" s="3" t="str">
         <v>2018-08-03</v>
       </c>
-      <c r="I5" s="7" t="str">
+      <c r="I5" s="3" t="str">
         <v>2018-04-26</v>
       </c>
-      <c r="J5" s="7" t="str">
+      <c r="J5" s="3" t="str">
         <v>2018-08-22</v>
       </c>
-      <c r="K5" s="7" t="str">
+      <c r="K5" s="3" t="str">
         <v>2018-08-22</v>
       </c>
-      <c r="L5" s="6" t="str">
+      <c r="L5" s="3" t="str">
         <v>Y</v>
       </c>
-      <c r="M5" s="7">
+      <c r="M5" s="3">
         <v>701</v>
       </c>
-      <c r="N5" s="7" t="str">
+      <c r="N5" s="3" t="str">
         <v>1947-07-24T00:00:00.000Z</v>
       </c>
-      <c r="O5" s="7" t="str">
+      <c r="O5" s="3" t="str">
         <v>70</v>
       </c>
-      <c r="P5" s="7" t="str">
+      <c r="P5" s="3" t="str">
         <v>YEARS</v>
       </c>
-      <c r="Q5" s="7" t="str">
+      <c r="Q5" s="3" t="str">
         <v>M</v>
       </c>
-      <c r="R5" s="7" t="str">
+      <c r="R5" s="3" t="str">
         <v>WHITE</v>
       </c>
-      <c r="S5" s="7" t="str">
+      <c r="S5" s="3" t="str">
         <v>NOT HISPANIC OR LATINO</v>
       </c>
-      <c r="T5" s="7" t="str">
+      <c r="T5" s="3" t="str">
         <v>A</v>
       </c>
-      <c r="U5" s="7" t="str">
+      <c r="U5" s="3" t="str">
         <v>Drug A</v>
       </c>
-      <c r="V5" s="7" t="str">
+      <c r="V5" s="3" t="str">
         <v>A</v>
       </c>
-      <c r="W5" s="7" t="str">
+      <c r="W5" s="3" t="str">
         <v>Drug A</v>
       </c>
-      <c r="X5" s="7" t="str">
+      <c r="X5" s="3" t="str">
         <v/>
       </c>
-      <c r="Y5" s="7" t="str">
+      <c r="Y5" s="3" t="str">
         <v/>
       </c>
-      <c r="Z5" s="7" t="str">
+      <c r="Z5" s="3" t="str">
         <v>AUS</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="str">
+      <c r="A6" s="3" t="str">
         <v>CDISCPILOT01</v>
       </c>
-      <c r="B6" s="6" t="str">
+      <c r="B6" s="3" t="str">
         <v>DM</v>
       </c>
-      <c r="C6" s="6" t="str">
+      <c r="C6" s="3" t="str">
         <v>CDISC002</v>
       </c>
-      <c r="D6" s="6">
+      <c r="D6" s="3">
         <v>1211</v>
       </c>
-      <c r="E6" s="6" t="str">
+      <c r="E6" s="3" t="str">
         <v>2018-05-24T12:00</v>
       </c>
-      <c r="F6" s="6" t="str">
+      <c r="F6" s="3" t="str">
         <v>2018-11-06</v>
       </c>
-      <c r="G6" s="6" t="str">
+      <c r="G6" s="3" t="str">
         <v>2018-05-24T12:00</v>
       </c>
-      <c r="H6" s="6" t="str">
+      <c r="H6" s="3" t="str">
         <v>2018-11-06</v>
       </c>
-      <c r="I6" s="6" t="str">
+      <c r="I6" s="3" t="str">
         <v>2018-05-07</v>
       </c>
-      <c r="J6" s="6" t="str">
+      <c r="J6" s="3" t="str">
         <v>2019-02-04</v>
       </c>
-      <c r="K6" s="6" t="str">
+      <c r="K6" s="3" t="str">
         <v>2019-02-04</v>
       </c>
-      <c r="L6" s="6" t="str">
+      <c r="L6" s="3" t="str">
         <v>Y</v>
       </c>
-      <c r="M6" s="6">
+      <c r="M6" s="3">
         <v>701</v>
       </c>
-      <c r="N6" s="6" t="str">
+      <c r="N6" s="3" t="str">
         <v>1905-05-08T00:00:00.000Z</v>
       </c>
-      <c r="O6" s="6" t="str">
+      <c r="O6" s="3" t="str">
         <v>78</v>
       </c>
-      <c r="P6" s="6" t="str">
+      <c r="P6" s="3" t="str">
         <v>YEARS</v>
       </c>
-      <c r="Q6" s="6" t="str">
+      <c r="Q6" s="3" t="str">
         <v>M</v>
       </c>
-      <c r="R6" s="6" t="str">
+      <c r="R6" s="3" t="str">
         <v>WHITE</v>
       </c>
-      <c r="S6" s="6" t="str">
+      <c r="S6" s="3" t="str">
         <v>NOT HISPANIC OR LATINO</v>
       </c>
-      <c r="T6" s="6" t="str">
+      <c r="T6" s="3" t="str">
         <v>P</v>
       </c>
-      <c r="U6" s="6" t="str">
+      <c r="U6" s="3" t="str">
         <v>Placebo</v>
       </c>
-      <c r="V6" s="6" t="str">
+      <c r="V6" s="3" t="str">
         <v>P</v>
       </c>
-      <c r="W6" s="6" t="str">
+      <c r="W6" s="3" t="str">
         <v>Placebo</v>
       </c>
-      <c r="X6" s="6" t="str">
+      <c r="X6" s="3" t="str">
         <v/>
       </c>
-      <c r="Y6" s="6" t="str">
+      <c r="Y6" s="3" t="str">
         <v/>
       </c>
-      <c r="Z6" s="6" t="str">
+      <c r="Z6" s="3" t="str">
         <v>AUS</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="str">
+      <c r="A7" s="3" t="str">
         <v>CDISCPILOT01</v>
       </c>
-      <c r="B7" s="7" t="str">
+      <c r="B7" s="3" t="str">
         <v>DM</v>
       </c>
-      <c r="C7" s="7" t="str">
+      <c r="C7" s="3" t="str">
         <v>CDISC003</v>
       </c>
-      <c r="D7" s="7">
+      <c r="D7" s="3">
         <v>1302</v>
       </c>
-      <c r="E7" s="7" t="str">
+      <c r="E7" s="3" t="str">
         <v>2006-01-16</v>
       </c>
-      <c r="F7" s="7" t="str">
+      <c r="F7" s="3" t="str">
         <v>2006-03-19</v>
       </c>
-      <c r="G7" s="7" t="str">
+      <c r="G7" s="3" t="str">
         <v>2006-01-16</v>
       </c>
-      <c r="H7" s="7" t="str">
+      <c r="H7" s="3" t="str">
         <v>2006-03-19</v>
       </c>
-      <c r="I7" s="7" t="str">
+      <c r="I7" s="3" t="str">
         <v>2006-01-02</v>
       </c>
-      <c r="J7" s="7" t="str">
+      <c r="J7" s="3" t="str">
         <v>2006-03-19</v>
       </c>
-      <c r="K7" s="7" t="str">
+      <c r="K7" s="3" t="str">
         <v/>
       </c>
-      <c r="L7" s="6" t="str">
+      <c r="L7" s="3" t="str">
         <v>Y</v>
       </c>
-      <c r="M7" s="7">
+      <c r="M7" s="3">
         <v>701</v>
       </c>
-      <c r="N7" s="7" t="str">
+      <c r="N7" s="3" t="str">
         <v>1944-06-16T00:00:00.000Z</v>
       </c>
-      <c r="O7" s="7" t="str">
+      <c r="O7" s="3" t="str">
         <v>74</v>
       </c>
-      <c r="P7" s="7" t="str">
+      <c r="P7" s="3" t="str">
         <v>YEARS</v>
       </c>
-      <c r="Q7" s="7" t="str">
+      <c r="Q7" s="3" t="str">
         <v>M</v>
       </c>
-      <c r="R7" s="7" t="str">
+      <c r="R7" s="3" t="str">
         <v>WHITE</v>
       </c>
-      <c r="S7" s="7" t="str">
+      <c r="S7" s="3" t="str">
         <v>NOT HISPANIC OR LATINO</v>
       </c>
-      <c r="T7" s="7" t="str">
+      <c r="T7" s="3" t="str">
         <v>B</v>
       </c>
-      <c r="U7" s="7" t="str">
+      <c r="U7" s="3" t="str">
         <v>Drug B</v>
       </c>
-      <c r="V7" s="7" t="str">
+      <c r="V7" s="3" t="str">
         <v>B</v>
       </c>
-      <c r="W7" s="7" t="str">
+      <c r="W7" s="3" t="str">
         <v>Drug B</v>
       </c>
-      <c r="X7" s="7" t="str">
+      <c r="X7" s="3" t="str">
         <v/>
       </c>
-      <c r="Y7" s="7" t="str">
+      <c r="Y7" s="3" t="str">
         <v/>
       </c>
-      <c r="Z7" s="7" t="str">
+      <c r="Z7" s="3" t="str">
         <v>CZE</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="str">
+      <c r="A8" s="3" t="str">
         <v>CDISCPILOT01</v>
       </c>
-      <c r="B8" s="7" t="str">
+      <c r="B8" s="3" t="str">
         <v>DM</v>
       </c>
-      <c r="C8" s="7" t="str">
+      <c r="C8" s="3" t="str">
         <v>CDISC004</v>
       </c>
-      <c r="D8" s="7">
+      <c r="D8" s="3">
         <v>1402</v>
       </c>
-      <c r="E8" s="7" t="str">
+      <c r="E8" s="3" t="str">
         <v>2018-07-16T09:15</v>
       </c>
-      <c r="F8" s="7" t="str">
+      <c r="F8" s="3" t="str">
         <v>2018-11-06T14:00</v>
       </c>
-      <c r="G8" s="7" t="str">
+      <c r="G8" s="3" t="str">
         <v>2018-07-16T09:15</v>
       </c>
-      <c r="H8" s="7" t="str">
+      <c r="H8" s="3" t="str">
         <v>2018-11-06T14:00</v>
       </c>
-      <c r="I8" s="7" t="str">
+      <c r="I8" s="3" t="str">
         <v>2018-06-27</v>
       </c>
-      <c r="J8" s="7" t="str">
+      <c r="J8" s="3" t="str">
         <v>2018-12-11</v>
       </c>
-      <c r="K8" s="7" t="str">
+      <c r="K8" s="3" t="str">
         <v/>
       </c>
-      <c r="L8" s="6" t="str">
+      <c r="L8" s="3" t="str">
         <v/>
       </c>
-      <c r="M8" s="7">
+      <c r="M8" s="3">
         <v>701</v>
       </c>
-      <c r="N8" s="7" t="str">
+      <c r="N8" s="3" t="str">
         <v>1905-04-16T00:00:00.000Z</v>
       </c>
-      <c r="O8" s="7" t="str">
+      <c r="O8" s="3" t="str">
         <v>68</v>
       </c>
-      <c r="P8" s="7" t="str">
+      <c r="P8" s="3" t="str">
         <v>YEARS</v>
       </c>
-      <c r="Q8" s="7" t="str">
+      <c r="Q8" s="3" t="str">
         <v>F</v>
       </c>
-      <c r="R8" s="7" t="str">
+      <c r="R8" s="3" t="str">
         <v>WHITE</v>
       </c>
-      <c r="S8" s="7" t="str">
+      <c r="S8" s="3" t="str">
         <v>HISPANIC OR LATINO</v>
       </c>
-      <c r="T8" s="7" t="str">
+      <c r="T8" s="3" t="str">
         <v>B</v>
       </c>
-      <c r="U8" s="7" t="str">
+      <c r="U8" s="3" t="str">
         <v>Drug B</v>
       </c>
-      <c r="V8" s="7" t="str">
+      <c r="V8" s="3" t="str">
         <v>B</v>
       </c>
-      <c r="W8" s="7" t="str">
+      <c r="W8" s="3" t="str">
         <v>Drug B</v>
       </c>
-      <c r="X8" s="7" t="str">
+      <c r="X8" s="3" t="str">
         <v/>
       </c>
-      <c r="Y8" s="7" t="str">
+      <c r="Y8" s="3" t="str">
         <v/>
       </c>
-      <c r="Z8" s="7" t="str">
+      <c r="Z8" s="3" t="str">
         <v>CAN</v>
       </c>
     </row>
@@ -1194,72 +1163,72 @@
   <dimension ref="A1:D5"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="str">
+      <c r="A1" s="4" t="str">
         <v>STUDYID</v>
       </c>
-      <c r="B1" s="3" t="str">
+      <c r="B1" s="4" t="str">
         <v>DOMAIN</v>
       </c>
-      <c r="C1" s="3" t="str">
+      <c r="C1" s="4" t="str">
         <v>USUBJID</v>
       </c>
-      <c r="D1" s="3" t="str">
-        <v>AESEQ</v>
+      <c r="D1" s="4" t="str">
+        <v>CESEQ</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="8" t="str">
+      <c r="A2" s="5" t="str">
         <v>Study Identifier</v>
       </c>
-      <c r="B2" s="8" t="str">
+      <c r="B2" s="5" t="str">
         <v>Domain Abbreviation</v>
       </c>
-      <c r="C2" s="9" t="str">
+      <c r="C2" s="6" t="str">
         <v>Unique Subject Identifier</v>
       </c>
-      <c r="D2" s="9" t="str">
+      <c r="D2" s="6" t="str">
         <v>Sequence Number</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="9" t="str">
-        <v>Char</v>
-      </c>
-      <c r="B3" s="9" t="str">
-        <v>Char</v>
-      </c>
-      <c r="C3" s="9" t="str">
-        <v>Char</v>
-      </c>
-      <c r="D3" s="9" t="str">
+      <c r="A3" s="6" t="str">
+        <v>Char</v>
+      </c>
+      <c r="B3" s="6" t="str">
+        <v>Char</v>
+      </c>
+      <c r="C3" s="6" t="str">
+        <v>Char</v>
+      </c>
+      <c r="D3" s="6" t="str">
         <v>Num</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="9" t="str">
+      <c r="A4" s="6" t="str">
         <v>10</v>
       </c>
-      <c r="B4" s="9" t="str">
+      <c r="B4" s="6" t="str">
         <v>2</v>
       </c>
-      <c r="C4" s="9" t="str">
+      <c r="C4" s="6" t="str">
         <v>14</v>
       </c>
-      <c r="D4" s="9" t="str">
+      <c r="D4" s="6" t="str">
         <v>8</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="str">
+      <c r="A5" s="3" t="str">
         <v>CDISCPILOT01</v>
       </c>
-      <c r="B5" s="7" t="str">
-        <v>AE</v>
-      </c>
-      <c r="C5" s="7" t="str">
+      <c r="B5" s="3" t="str">
+        <v>CE</v>
+      </c>
+      <c r="C5" s="3" t="str">
         <v>CDISC-TEST-001</v>
       </c>
-      <c r="D5" s="7" t="str">
+      <c r="D5" s="3" t="str">
         <v>1</v>
       </c>
     </row>

--- a/rules/NEW-RULE/positive/01/data/new-rule-positive-01.xlsx
+++ b/rules/NEW-RULE/positive/01/data/new-rule-positive-01.xlsx
@@ -6,7 +6,7 @@
     <sheet name="Library" sheetId="1" r:id="rId1"/>
     <sheet name="Datasets" sheetId="2" r:id="rId2"/>
     <sheet name="dm.xpt" sheetId="3" r:id="rId3"/>
-    <sheet name="ae.xpt" sheetId="4" r:id="rId4"/>
+    <sheet name="cm.xpt" sheetId="4" r:id="rId4"/>
   </sheets>
 </workbook>
 </file>
@@ -36,7 +36,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
   <numFmts count="0"/>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -53,23 +57,6 @@
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
       <i/>
     </font>
     <font>
@@ -78,7 +65,7 @@
       <i/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="4">
     <fill>
       <patternFill patternType="none">
         <bgColor/>
@@ -86,21 +73,6 @@
     </fill>
     <fill>
       <patternFill patternType="gray125">
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <bgColor/>
       </patternFill>
     </fill>
@@ -136,17 +108,14 @@
   <cellStyleXfs>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="1" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -481,18 +450,18 @@
   <dimension ref="A1:B2"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="str">
+      <c r="A1" s="3" t="str">
         <v>Product</v>
       </c>
-      <c r="B1" s="2" t="str">
+      <c r="B1" s="3" t="str">
         <v>Version</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="str">
+      <c r="A2" s="3" t="str">
         <v>sdtmig</v>
       </c>
-      <c r="B2" s="2" t="str">
+      <c r="B2" s="3" t="str">
         <v>3-4</v>
       </c>
     </row>
@@ -508,27 +477,27 @@
   <dimension ref="A1:B3"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="str">
+      <c r="A1" s="3" t="str">
         <v>Filename</v>
       </c>
-      <c r="B1" s="2" t="str">
+      <c r="B1" s="3" t="str">
         <v>Label</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="str">
+      <c r="A2" s="3" t="str">
         <v>dm.xpt</v>
       </c>
-      <c r="B2" s="2" t="str">
+      <c r="B2" s="3" t="str">
         <v>Demographics</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="str">
-        <v>ae.xpt</v>
-      </c>
-      <c r="B3" s="2" t="str">
-        <v>Adverse Events</v>
+      <c r="A3" s="3" t="str">
+        <v>cm.xpt</v>
+      </c>
+      <c r="B3" s="3" t="str">
+        <v>Concomitant Medications</v>
       </c>
     </row>
   </sheetData>
@@ -543,642 +512,642 @@
   <dimension ref="A1:Z8"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="str">
+      <c r="A1" s="4" t="str">
         <v>STUDYID</v>
       </c>
-      <c r="B1" s="3" t="str">
+      <c r="B1" s="4" t="str">
         <v>DOMAIN</v>
       </c>
-      <c r="C1" s="3" t="str">
+      <c r="C1" s="4" t="str">
         <v>USUBJID</v>
       </c>
-      <c r="D1" s="3" t="str">
+      <c r="D1" s="4" t="str">
         <v>SUBJID</v>
       </c>
-      <c r="E1" s="3" t="str">
+      <c r="E1" s="4" t="str">
         <v>RFSTDTC</v>
       </c>
-      <c r="F1" s="3" t="str">
+      <c r="F1" s="4" t="str">
         <v>RFENDTC</v>
       </c>
-      <c r="G1" s="3" t="str">
+      <c r="G1" s="4" t="str">
         <v>RFXSTDTC</v>
       </c>
-      <c r="H1" s="3" t="str">
+      <c r="H1" s="4" t="str">
         <v>RFXENDTC</v>
       </c>
-      <c r="I1" s="3" t="str">
+      <c r="I1" s="4" t="str">
         <v>RFICDTC</v>
       </c>
-      <c r="J1" s="3" t="str">
+      <c r="J1" s="4" t="str">
         <v>RFPENDTC</v>
       </c>
-      <c r="K1" s="3" t="str">
+      <c r="K1" s="4" t="str">
         <v>DTHDTC</v>
       </c>
       <c r="L1" s="4" t="str">
         <v>DTHFL</v>
       </c>
-      <c r="M1" s="3" t="str">
+      <c r="M1" s="4" t="str">
         <v>SITEID</v>
       </c>
-      <c r="N1" s="3" t="str">
+      <c r="N1" s="4" t="str">
         <v>BRTHDTC</v>
       </c>
-      <c r="O1" s="3" t="str">
+      <c r="O1" s="4" t="str">
         <v>AGE</v>
       </c>
-      <c r="P1" s="3" t="str">
+      <c r="P1" s="4" t="str">
         <v>AGEU</v>
       </c>
-      <c r="Q1" s="3" t="str">
+      <c r="Q1" s="4" t="str">
         <v>SEX</v>
       </c>
-      <c r="R1" s="3" t="str">
+      <c r="R1" s="4" t="str">
         <v>RACE</v>
       </c>
-      <c r="S1" s="3" t="str">
+      <c r="S1" s="4" t="str">
         <v>ETHNIC</v>
       </c>
-      <c r="T1" s="3" t="str">
+      <c r="T1" s="4" t="str">
         <v>ARMCD</v>
       </c>
-      <c r="U1" s="3" t="str">
+      <c r="U1" s="4" t="str">
         <v>ARM</v>
       </c>
-      <c r="V1" s="3" t="str">
+      <c r="V1" s="4" t="str">
         <v>ACTARMCD</v>
       </c>
-      <c r="W1" s="3" t="str">
+      <c r="W1" s="4" t="str">
         <v>ACTARM</v>
       </c>
-      <c r="X1" s="3" t="str">
+      <c r="X1" s="4" t="str">
         <v>ARMNRS</v>
       </c>
-      <c r="Y1" s="3" t="str">
+      <c r="Y1" s="4" t="str">
         <v>ACTARMUD</v>
       </c>
-      <c r="Z1" s="3" t="str">
+      <c r="Z1" s="4" t="str">
         <v>COUNTRY</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="str">
+      <c r="A2" s="3" t="str">
         <v>Study Identifier</v>
       </c>
-      <c r="B2" s="5" t="str">
+      <c r="B2" s="3" t="str">
         <v>Domain Abbreviation</v>
       </c>
-      <c r="C2" s="6" t="str">
+      <c r="C2" s="3" t="str">
         <v>Unique Subject Identifier</v>
       </c>
-      <c r="D2" s="6" t="str">
+      <c r="D2" s="3" t="str">
         <v>Subject Identifier for the Study</v>
       </c>
-      <c r="E2" s="6" t="str">
+      <c r="E2" s="3" t="str">
         <v>Subject Reference Start Date/Time</v>
       </c>
-      <c r="F2" s="6" t="str">
+      <c r="F2" s="3" t="str">
         <v>Subject Reference End Date/Time</v>
       </c>
-      <c r="G2" s="6" t="str">
+      <c r="G2" s="3" t="str">
         <v>Date/Time of First Study Treatment</v>
       </c>
-      <c r="H2" s="6" t="str">
+      <c r="H2" s="3" t="str">
         <v>Date/Time of Last Study Treatment</v>
       </c>
-      <c r="I2" s="6" t="str">
+      <c r="I2" s="3" t="str">
         <v>Date/Time of Informed Consent</v>
       </c>
-      <c r="J2" s="6" t="str">
+      <c r="J2" s="3" t="str">
         <v>Date/Time of End of Participation</v>
       </c>
-      <c r="K2" s="6" t="str">
+      <c r="K2" s="3" t="str">
         <v>Date/Time of Death</v>
       </c>
-      <c r="L2" s="6" t="str">
+      <c r="L2" s="3" t="str">
         <v>Subject Death Flag</v>
       </c>
-      <c r="M2" s="6" t="str">
+      <c r="M2" s="3" t="str">
         <v>Study Site Identifier</v>
       </c>
-      <c r="N2" s="6" t="str">
+      <c r="N2" s="3" t="str">
         <v>Date/Time of Birth</v>
       </c>
-      <c r="O2" s="6" t="str">
+      <c r="O2" s="3" t="str">
         <v>Age</v>
       </c>
-      <c r="P2" s="6" t="str">
+      <c r="P2" s="3" t="str">
         <v>Age Units</v>
       </c>
-      <c r="Q2" s="6" t="str">
+      <c r="Q2" s="3" t="str">
         <v>Sex</v>
       </c>
-      <c r="R2" s="6" t="str">
+      <c r="R2" s="3" t="str">
         <v>Race</v>
       </c>
-      <c r="S2" s="6" t="str">
+      <c r="S2" s="3" t="str">
         <v>Ethnicity</v>
       </c>
-      <c r="T2" s="6" t="str">
+      <c r="T2" s="3" t="str">
         <v>Planned Arm Code</v>
       </c>
-      <c r="U2" s="6" t="str">
+      <c r="U2" s="3" t="str">
         <v>Description of Planned Arm</v>
       </c>
-      <c r="V2" s="6" t="str">
+      <c r="V2" s="3" t="str">
         <v>Actual Arm Code</v>
       </c>
-      <c r="W2" s="6" t="str">
+      <c r="W2" s="3" t="str">
         <v>Description of Actual Arm</v>
       </c>
-      <c r="X2" s="6" t="str">
+      <c r="X2" s="3" t="str">
         <v>Reason Arm and/or Actual Arm is Null</v>
       </c>
-      <c r="Y2" s="6" t="str">
+      <c r="Y2" s="3" t="str">
         <v>Description of Unplanned Actual Arm</v>
       </c>
-      <c r="Z2" s="6" t="str">
+      <c r="Z2" s="3" t="str">
         <v>Country</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="B3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="C3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="D3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="E3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="F3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="G3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="H3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="I3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="J3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="K3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="L3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="M3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="N3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="O3" s="7" t="str">
+      <c r="A3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="B3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="C3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="D3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="E3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="F3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="G3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="H3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="I3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="J3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="K3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="L3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="M3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="N3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="O3" s="3" t="str">
         <v>Num</v>
       </c>
-      <c r="P3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="Q3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="R3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="S3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="T3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="U3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="V3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="W3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="X3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="Y3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="Z3" s="7" t="str">
+      <c r="P3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="Q3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="R3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="S3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="T3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="U3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="V3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="W3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="X3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="Y3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="Z3" s="3" t="str">
         <v>Char</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6">
+      <c r="A4" s="3">
         <v>12</v>
       </c>
-      <c r="B4" s="6">
+      <c r="B4" s="3">
         <v>2</v>
       </c>
-      <c r="C4" s="6">
+      <c r="C4" s="3">
         <v>8</v>
       </c>
-      <c r="D4" s="6">
+      <c r="D4" s="3">
         <v>4</v>
       </c>
-      <c r="E4" s="6">
+      <c r="E4" s="3">
         <v>10</v>
       </c>
-      <c r="F4" s="6">
+      <c r="F4" s="3">
         <v>10</v>
       </c>
-      <c r="G4" s="6">
+      <c r="G4" s="3">
         <v>10</v>
       </c>
-      <c r="H4" s="6">
+      <c r="H4" s="3">
         <v>10</v>
       </c>
-      <c r="I4" s="6">
+      <c r="I4" s="3">
         <v>10</v>
       </c>
-      <c r="J4" s="6">
+      <c r="J4" s="3">
         <v>10</v>
       </c>
-      <c r="K4" s="6">
+      <c r="K4" s="3">
         <v>10</v>
       </c>
-      <c r="L4" s="6">
+      <c r="L4" s="3">
         <v>1</v>
       </c>
-      <c r="M4" s="6">
+      <c r="M4" s="3">
         <v>3</v>
       </c>
-      <c r="N4" s="6">
+      <c r="N4" s="3">
         <v>10</v>
       </c>
-      <c r="O4" s="6">
+      <c r="O4" s="3">
         <v>8</v>
       </c>
-      <c r="P4" s="6">
+      <c r="P4" s="3">
         <v>5</v>
       </c>
-      <c r="Q4" s="6">
+      <c r="Q4" s="3">
         <v>1</v>
       </c>
-      <c r="R4" s="6">
+      <c r="R4" s="3">
         <v>41</v>
       </c>
-      <c r="S4" s="6">
+      <c r="S4" s="3">
         <v>22</v>
       </c>
-      <c r="T4" s="6">
+      <c r="T4" s="3">
         <v>8</v>
       </c>
-      <c r="U4" s="6">
+      <c r="U4" s="3">
         <v>28</v>
       </c>
-      <c r="V4" s="6">
+      <c r="V4" s="3">
         <v>8</v>
       </c>
-      <c r="W4" s="6">
+      <c r="W4" s="3">
         <v>28</v>
       </c>
-      <c r="X4" s="6">
+      <c r="X4" s="3">
         <v>14</v>
       </c>
-      <c r="Y4" s="6">
+      <c r="Y4" s="3">
         <v>200</v>
       </c>
-      <c r="Z4" s="6">
+      <c r="Z4" s="3">
         <v>3</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="str">
+      <c r="A5" s="3" t="str">
         <v>CDISCPILOT01</v>
       </c>
-      <c r="B5" s="7" t="str">
+      <c r="B5" s="3" t="str">
         <v>DM</v>
       </c>
-      <c r="C5" s="7" t="str">
+      <c r="C5" s="3" t="str">
         <v>CDISC001</v>
       </c>
-      <c r="D5" s="7">
+      <c r="D5" s="3">
         <v>1115</v>
       </c>
-      <c r="E5" s="7" t="str">
+      <c r="E5" s="3" t="str">
         <v>2018-05-17T09:35</v>
       </c>
-      <c r="F5" s="7" t="str">
+      <c r="F5" s="3" t="str">
         <v>2018-08-03</v>
       </c>
-      <c r="G5" s="7" t="str">
+      <c r="G5" s="3" t="str">
         <v>2018-05-17T09:35</v>
       </c>
-      <c r="H5" s="7" t="str">
+      <c r="H5" s="3" t="str">
         <v>2018-08-03</v>
       </c>
-      <c r="I5" s="7" t="str">
+      <c r="I5" s="3" t="str">
         <v>2018-04-26</v>
       </c>
-      <c r="J5" s="7" t="str">
+      <c r="J5" s="3" t="str">
         <v>2018-08-22</v>
       </c>
-      <c r="K5" s="7" t="str">
+      <c r="K5" s="3" t="str">
         <v>2018-08-22</v>
       </c>
-      <c r="L5" s="6" t="str">
+      <c r="L5" s="3" t="str">
         <v>Y</v>
       </c>
-      <c r="M5" s="7">
+      <c r="M5" s="3">
         <v>701</v>
       </c>
-      <c r="N5" s="7" t="str">
+      <c r="N5" s="3" t="str">
         <v>1947-07-24T00:00:00.000Z</v>
       </c>
-      <c r="O5" s="7" t="str">
+      <c r="O5" s="3" t="str">
         <v>70</v>
       </c>
-      <c r="P5" s="7" t="str">
+      <c r="P5" s="3" t="str">
         <v>YEARS</v>
       </c>
-      <c r="Q5" s="7" t="str">
+      <c r="Q5" s="3" t="str">
         <v>M</v>
       </c>
-      <c r="R5" s="7" t="str">
+      <c r="R5" s="3" t="str">
         <v>WHITE</v>
       </c>
-      <c r="S5" s="7" t="str">
+      <c r="S5" s="3" t="str">
         <v>NOT HISPANIC OR LATINO</v>
       </c>
-      <c r="T5" s="7" t="str">
+      <c r="T5" s="3" t="str">
         <v>A</v>
       </c>
-      <c r="U5" s="7" t="str">
+      <c r="U5" s="3" t="str">
         <v>Drug A</v>
       </c>
-      <c r="V5" s="7" t="str">
+      <c r="V5" s="3" t="str">
         <v>A</v>
       </c>
-      <c r="W5" s="7" t="str">
+      <c r="W5" s="3" t="str">
         <v>Drug A</v>
       </c>
-      <c r="X5" s="7" t="str">
+      <c r="X5" s="3" t="str">
         <v/>
       </c>
-      <c r="Y5" s="7" t="str">
+      <c r="Y5" s="3" t="str">
         <v/>
       </c>
-      <c r="Z5" s="7" t="str">
+      <c r="Z5" s="3" t="str">
         <v>AUS</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="str">
+      <c r="A6" s="3" t="str">
         <v>CDISCPILOT01</v>
       </c>
-      <c r="B6" s="6" t="str">
+      <c r="B6" s="3" t="str">
         <v>DM</v>
       </c>
-      <c r="C6" s="6" t="str">
+      <c r="C6" s="3" t="str">
         <v>CDISC002</v>
       </c>
-      <c r="D6" s="6">
+      <c r="D6" s="3">
         <v>1211</v>
       </c>
-      <c r="E6" s="6" t="str">
+      <c r="E6" s="3" t="str">
         <v>2018-05-24T12:00</v>
       </c>
-      <c r="F6" s="6" t="str">
+      <c r="F6" s="3" t="str">
         <v>2018-11-06</v>
       </c>
-      <c r="G6" s="6" t="str">
+      <c r="G6" s="3" t="str">
         <v>2018-05-24T12:00</v>
       </c>
-      <c r="H6" s="6" t="str">
+      <c r="H6" s="3" t="str">
         <v>2018-11-06</v>
       </c>
-      <c r="I6" s="6" t="str">
+      <c r="I6" s="3" t="str">
         <v>2018-05-07</v>
       </c>
-      <c r="J6" s="6" t="str">
+      <c r="J6" s="3" t="str">
         <v>2019-02-04</v>
       </c>
-      <c r="K6" s="6" t="str">
+      <c r="K6" s="3" t="str">
         <v>2019-02-04</v>
       </c>
-      <c r="L6" s="6" t="str">
+      <c r="L6" s="3" t="str">
         <v>Y</v>
       </c>
-      <c r="M6" s="6">
+      <c r="M6" s="3">
         <v>701</v>
       </c>
-      <c r="N6" s="6" t="str">
+      <c r="N6" s="3" t="str">
         <v>1905-05-08T00:00:00.000Z</v>
       </c>
-      <c r="O6" s="6" t="str">
+      <c r="O6" s="3" t="str">
         <v>78</v>
       </c>
-      <c r="P6" s="6" t="str">
+      <c r="P6" s="3" t="str">
         <v>YEARS</v>
       </c>
-      <c r="Q6" s="6" t="str">
+      <c r="Q6" s="3" t="str">
         <v>M</v>
       </c>
-      <c r="R6" s="6" t="str">
+      <c r="R6" s="3" t="str">
         <v>WHITE</v>
       </c>
-      <c r="S6" s="6" t="str">
+      <c r="S6" s="3" t="str">
         <v>NOT HISPANIC OR LATINO</v>
       </c>
-      <c r="T6" s="6" t="str">
+      <c r="T6" s="3" t="str">
         <v>P</v>
       </c>
-      <c r="U6" s="6" t="str">
+      <c r="U6" s="3" t="str">
         <v>Placebo</v>
       </c>
-      <c r="V6" s="6" t="str">
+      <c r="V6" s="3" t="str">
         <v>P</v>
       </c>
-      <c r="W6" s="6" t="str">
+      <c r="W6" s="3" t="str">
         <v>Placebo</v>
       </c>
-      <c r="X6" s="6" t="str">
+      <c r="X6" s="3" t="str">
         <v/>
       </c>
-      <c r="Y6" s="6" t="str">
+      <c r="Y6" s="3" t="str">
         <v/>
       </c>
-      <c r="Z6" s="6" t="str">
+      <c r="Z6" s="3" t="str">
         <v>AUS</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="str">
+      <c r="A7" s="3" t="str">
         <v>CDISCPILOT01</v>
       </c>
-      <c r="B7" s="7" t="str">
+      <c r="B7" s="3" t="str">
         <v>DM</v>
       </c>
-      <c r="C7" s="7" t="str">
+      <c r="C7" s="3" t="str">
         <v>CDISC003</v>
       </c>
-      <c r="D7" s="7">
+      <c r="D7" s="3">
         <v>1302</v>
       </c>
-      <c r="E7" s="7" t="str">
+      <c r="E7" s="3" t="str">
         <v>2006-01-16</v>
       </c>
-      <c r="F7" s="7" t="str">
+      <c r="F7" s="3" t="str">
         <v>2006-03-19</v>
       </c>
-      <c r="G7" s="7" t="str">
+      <c r="G7" s="3" t="str">
         <v>2006-01-16</v>
       </c>
-      <c r="H7" s="7" t="str">
+      <c r="H7" s="3" t="str">
         <v>2006-03-19</v>
       </c>
-      <c r="I7" s="7" t="str">
+      <c r="I7" s="3" t="str">
         <v>2006-01-02</v>
       </c>
-      <c r="J7" s="7" t="str">
+      <c r="J7" s="3" t="str">
         <v>2006-03-19</v>
       </c>
-      <c r="K7" s="7" t="str">
+      <c r="K7" s="3" t="str">
         <v/>
       </c>
-      <c r="L7" s="6" t="str">
+      <c r="L7" s="3" t="str">
         <v>Y</v>
       </c>
-      <c r="M7" s="7">
+      <c r="M7" s="3">
         <v>701</v>
       </c>
-      <c r="N7" s="7" t="str">
+      <c r="N7" s="3" t="str">
         <v>1944-06-16T00:00:00.000Z</v>
       </c>
-      <c r="O7" s="7" t="str">
+      <c r="O7" s="3" t="str">
         <v>74</v>
       </c>
-      <c r="P7" s="7" t="str">
+      <c r="P7" s="3" t="str">
         <v>YEARS</v>
       </c>
-      <c r="Q7" s="7" t="str">
+      <c r="Q7" s="3" t="str">
         <v>M</v>
       </c>
-      <c r="R7" s="7" t="str">
+      <c r="R7" s="3" t="str">
         <v>WHITE</v>
       </c>
-      <c r="S7" s="7" t="str">
+      <c r="S7" s="3" t="str">
         <v>NOT HISPANIC OR LATINO</v>
       </c>
-      <c r="T7" s="7" t="str">
+      <c r="T7" s="3" t="str">
         <v>B</v>
       </c>
-      <c r="U7" s="7" t="str">
+      <c r="U7" s="3" t="str">
         <v>Drug B</v>
       </c>
-      <c r="V7" s="7" t="str">
+      <c r="V7" s="3" t="str">
         <v>B</v>
       </c>
-      <c r="W7" s="7" t="str">
+      <c r="W7" s="3" t="str">
         <v>Drug B</v>
       </c>
-      <c r="X7" s="7" t="str">
+      <c r="X7" s="3" t="str">
         <v/>
       </c>
-      <c r="Y7" s="7" t="str">
+      <c r="Y7" s="3" t="str">
         <v/>
       </c>
-      <c r="Z7" s="7" t="str">
+      <c r="Z7" s="3" t="str">
         <v>CZE</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="str">
+      <c r="A8" s="3" t="str">
         <v>CDISCPILOT01</v>
       </c>
-      <c r="B8" s="7" t="str">
+      <c r="B8" s="3" t="str">
         <v>DM</v>
       </c>
-      <c r="C8" s="7" t="str">
+      <c r="C8" s="3" t="str">
         <v>CDISC004</v>
       </c>
-      <c r="D8" s="7">
+      <c r="D8" s="3">
         <v>1402</v>
       </c>
-      <c r="E8" s="7" t="str">
+      <c r="E8" s="3" t="str">
         <v>2018-07-16T09:15</v>
       </c>
-      <c r="F8" s="7" t="str">
+      <c r="F8" s="3" t="str">
         <v>2018-11-06T14:00</v>
       </c>
-      <c r="G8" s="7" t="str">
+      <c r="G8" s="3" t="str">
         <v>2018-07-16T09:15</v>
       </c>
-      <c r="H8" s="7" t="str">
+      <c r="H8" s="3" t="str">
         <v>2018-11-06T14:00</v>
       </c>
-      <c r="I8" s="7" t="str">
+      <c r="I8" s="3" t="str">
         <v>2018-06-27</v>
       </c>
-      <c r="J8" s="7" t="str">
+      <c r="J8" s="3" t="str">
         <v>2018-12-11</v>
       </c>
-      <c r="K8" s="7" t="str">
+      <c r="K8" s="3" t="str">
         <v/>
       </c>
-      <c r="L8" s="6" t="str">
+      <c r="L8" s="3" t="str">
         <v/>
       </c>
-      <c r="M8" s="7">
+      <c r="M8" s="3">
         <v>701</v>
       </c>
-      <c r="N8" s="7" t="str">
+      <c r="N8" s="3" t="str">
         <v>1905-04-16T00:00:00.000Z</v>
       </c>
-      <c r="O8" s="7" t="str">
+      <c r="O8" s="3" t="str">
         <v>68</v>
       </c>
-      <c r="P8" s="7" t="str">
+      <c r="P8" s="3" t="str">
         <v>YEARS</v>
       </c>
-      <c r="Q8" s="7" t="str">
+      <c r="Q8" s="3" t="str">
         <v>F</v>
       </c>
-      <c r="R8" s="7" t="str">
+      <c r="R8" s="3" t="str">
         <v>WHITE</v>
       </c>
-      <c r="S8" s="7" t="str">
+      <c r="S8" s="3" t="str">
         <v>HISPANIC OR LATINO</v>
       </c>
-      <c r="T8" s="7" t="str">
+      <c r="T8" s="3" t="str">
         <v>B</v>
       </c>
-      <c r="U8" s="7" t="str">
+      <c r="U8" s="3" t="str">
         <v>Drug B</v>
       </c>
-      <c r="V8" s="7" t="str">
+      <c r="V8" s="3" t="str">
         <v>B</v>
       </c>
-      <c r="W8" s="7" t="str">
+      <c r="W8" s="3" t="str">
         <v>Drug B</v>
       </c>
-      <c r="X8" s="7" t="str">
+      <c r="X8" s="3" t="str">
         <v/>
       </c>
-      <c r="Y8" s="7" t="str">
+      <c r="Y8" s="3" t="str">
         <v/>
       </c>
-      <c r="Z8" s="7" t="str">
+      <c r="Z8" s="3" t="str">
         <v>CAN</v>
       </c>
     </row>
@@ -1194,72 +1163,72 @@
   <dimension ref="A1:D5"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="str">
+      <c r="A1" s="4" t="str">
         <v>STUDYID</v>
       </c>
-      <c r="B1" s="3" t="str">
+      <c r="B1" s="4" t="str">
         <v>DOMAIN</v>
       </c>
-      <c r="C1" s="3" t="str">
+      <c r="C1" s="4" t="str">
         <v>USUBJID</v>
       </c>
-      <c r="D1" s="3" t="str">
-        <v>AESEQ</v>
+      <c r="D1" s="4" t="str">
+        <v>CMSEQ</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="8" t="str">
+      <c r="A2" s="5" t="str">
         <v>Study Identifier</v>
       </c>
-      <c r="B2" s="8" t="str">
+      <c r="B2" s="5" t="str">
         <v>Domain Abbreviation</v>
       </c>
-      <c r="C2" s="9" t="str">
+      <c r="C2" s="5" t="str">
         <v>Unique Subject Identifier</v>
       </c>
-      <c r="D2" s="9" t="str">
+      <c r="D2" s="6" t="str">
         <v>Sequence Number</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="9" t="str">
-        <v>Char</v>
-      </c>
-      <c r="B3" s="9" t="str">
-        <v>Char</v>
-      </c>
-      <c r="C3" s="9" t="str">
-        <v>Char</v>
-      </c>
-      <c r="D3" s="9" t="str">
+      <c r="A3" s="6" t="str">
+        <v>Char</v>
+      </c>
+      <c r="B3" s="6" t="str">
+        <v>Char</v>
+      </c>
+      <c r="C3" s="6" t="str">
+        <v>Char</v>
+      </c>
+      <c r="D3" s="6" t="str">
         <v>Num</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="9" t="str">
+      <c r="A4" s="6" t="str">
         <v>10</v>
       </c>
-      <c r="B4" s="9" t="str">
+      <c r="B4" s="6" t="str">
         <v>2</v>
       </c>
-      <c r="C4" s="9" t="str">
+      <c r="C4" s="6" t="str">
         <v>14</v>
       </c>
-      <c r="D4" s="9" t="str">
+      <c r="D4" s="6" t="str">
         <v>8</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="str">
+      <c r="A5" s="3" t="str">
         <v>CDISCPILOT01</v>
       </c>
-      <c r="B5" s="7" t="str">
-        <v>AE</v>
-      </c>
-      <c r="C5" s="7" t="str">
+      <c r="B5" s="3" t="str">
+        <v>CM</v>
+      </c>
+      <c r="C5" s="3" t="str">
         <v>CDISC-TEST-001</v>
       </c>
-      <c r="D5" s="7" t="str">
+      <c r="D5" s="3" t="str">
         <v>1</v>
       </c>
     </row>

--- a/rules/NEW-RULE/positive/01/data/new-rule-positive-01.xlsx
+++ b/rules/NEW-RULE/positive/01/data/new-rule-positive-01.xlsx
@@ -6,7 +6,7 @@
     <sheet name="Library" sheetId="1" r:id="rId1"/>
     <sheet name="Datasets" sheetId="2" r:id="rId2"/>
     <sheet name="dm.xpt" sheetId="3" r:id="rId3"/>
-    <sheet name="ae.xpt" sheetId="4" r:id="rId4"/>
+    <sheet name="eg.xpt" sheetId="4" r:id="rId4"/>
   </sheets>
 </workbook>
 </file>
@@ -36,7 +36,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
   <numFmts count="0"/>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -53,23 +57,6 @@
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
       <i/>
     </font>
     <font>
@@ -78,7 +65,7 @@
       <i/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="4">
     <fill>
       <patternFill patternType="none">
         <bgColor/>
@@ -86,21 +73,6 @@
     </fill>
     <fill>
       <patternFill patternType="gray125">
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <bgColor/>
       </patternFill>
     </fill>
@@ -136,17 +108,14 @@
   <cellStyleXfs>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="1" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -481,18 +450,18 @@
   <dimension ref="A1:B2"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="str">
+      <c r="A1" s="3" t="str">
         <v>Product</v>
       </c>
-      <c r="B1" s="2" t="str">
+      <c r="B1" s="3" t="str">
         <v>Version</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="str">
+      <c r="A2" s="3" t="str">
         <v>sdtmig</v>
       </c>
-      <c r="B2" s="2" t="str">
+      <c r="B2" s="3" t="str">
         <v>3-4</v>
       </c>
     </row>
@@ -508,27 +477,27 @@
   <dimension ref="A1:B3"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="str">
+      <c r="A1" s="3" t="str">
         <v>Filename</v>
       </c>
-      <c r="B1" s="2" t="str">
+      <c r="B1" s="3" t="str">
         <v>Label</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="str">
+      <c r="A2" s="3" t="str">
         <v>dm.xpt</v>
       </c>
-      <c r="B2" s="2" t="str">
+      <c r="B2" s="3" t="str">
         <v>Demographics</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="str">
-        <v>ae.xpt</v>
-      </c>
-      <c r="B3" s="2" t="str">
-        <v>Adverse Events</v>
+      <c r="A3" s="3" t="str">
+        <v>eg.xpt</v>
+      </c>
+      <c r="B3" s="3" t="str">
+        <v>ECG Test Results</v>
       </c>
     </row>
   </sheetData>
@@ -543,642 +512,642 @@
   <dimension ref="A1:Z8"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="str">
+      <c r="A1" s="4" t="str">
         <v>STUDYID</v>
       </c>
-      <c r="B1" s="3" t="str">
+      <c r="B1" s="4" t="str">
         <v>DOMAIN</v>
       </c>
-      <c r="C1" s="3" t="str">
+      <c r="C1" s="4" t="str">
         <v>USUBJID</v>
       </c>
-      <c r="D1" s="3" t="str">
+      <c r="D1" s="4" t="str">
         <v>SUBJID</v>
       </c>
-      <c r="E1" s="3" t="str">
+      <c r="E1" s="4" t="str">
         <v>RFSTDTC</v>
       </c>
-      <c r="F1" s="3" t="str">
+      <c r="F1" s="4" t="str">
         <v>RFENDTC</v>
       </c>
-      <c r="G1" s="3" t="str">
+      <c r="G1" s="4" t="str">
         <v>RFXSTDTC</v>
       </c>
-      <c r="H1" s="3" t="str">
+      <c r="H1" s="4" t="str">
         <v>RFXENDTC</v>
       </c>
-      <c r="I1" s="3" t="str">
+      <c r="I1" s="4" t="str">
         <v>RFICDTC</v>
       </c>
-      <c r="J1" s="3" t="str">
+      <c r="J1" s="4" t="str">
         <v>RFPENDTC</v>
       </c>
-      <c r="K1" s="3" t="str">
+      <c r="K1" s="4" t="str">
         <v>DTHDTC</v>
       </c>
       <c r="L1" s="4" t="str">
         <v>DTHFL</v>
       </c>
-      <c r="M1" s="3" t="str">
+      <c r="M1" s="4" t="str">
         <v>SITEID</v>
       </c>
-      <c r="N1" s="3" t="str">
+      <c r="N1" s="4" t="str">
         <v>BRTHDTC</v>
       </c>
-      <c r="O1" s="3" t="str">
+      <c r="O1" s="4" t="str">
         <v>AGE</v>
       </c>
-      <c r="P1" s="3" t="str">
+      <c r="P1" s="4" t="str">
         <v>AGEU</v>
       </c>
-      <c r="Q1" s="3" t="str">
+      <c r="Q1" s="4" t="str">
         <v>SEX</v>
       </c>
-      <c r="R1" s="3" t="str">
+      <c r="R1" s="4" t="str">
         <v>RACE</v>
       </c>
-      <c r="S1" s="3" t="str">
+      <c r="S1" s="4" t="str">
         <v>ETHNIC</v>
       </c>
-      <c r="T1" s="3" t="str">
+      <c r="T1" s="4" t="str">
         <v>ARMCD</v>
       </c>
-      <c r="U1" s="3" t="str">
+      <c r="U1" s="4" t="str">
         <v>ARM</v>
       </c>
-      <c r="V1" s="3" t="str">
+      <c r="V1" s="4" t="str">
         <v>ACTARMCD</v>
       </c>
-      <c r="W1" s="3" t="str">
+      <c r="W1" s="4" t="str">
         <v>ACTARM</v>
       </c>
-      <c r="X1" s="3" t="str">
+      <c r="X1" s="4" t="str">
         <v>ARMNRS</v>
       </c>
-      <c r="Y1" s="3" t="str">
+      <c r="Y1" s="4" t="str">
         <v>ACTARMUD</v>
       </c>
-      <c r="Z1" s="3" t="str">
+      <c r="Z1" s="4" t="str">
         <v>COUNTRY</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="str">
+      <c r="A2" s="3" t="str">
         <v>Study Identifier</v>
       </c>
-      <c r="B2" s="5" t="str">
+      <c r="B2" s="3" t="str">
         <v>Domain Abbreviation</v>
       </c>
-      <c r="C2" s="6" t="str">
+      <c r="C2" s="3" t="str">
         <v>Unique Subject Identifier</v>
       </c>
-      <c r="D2" s="6" t="str">
+      <c r="D2" s="3" t="str">
         <v>Subject Identifier for the Study</v>
       </c>
-      <c r="E2" s="6" t="str">
+      <c r="E2" s="3" t="str">
         <v>Subject Reference Start Date/Time</v>
       </c>
-      <c r="F2" s="6" t="str">
+      <c r="F2" s="3" t="str">
         <v>Subject Reference End Date/Time</v>
       </c>
-      <c r="G2" s="6" t="str">
+      <c r="G2" s="3" t="str">
         <v>Date/Time of First Study Treatment</v>
       </c>
-      <c r="H2" s="6" t="str">
+      <c r="H2" s="3" t="str">
         <v>Date/Time of Last Study Treatment</v>
       </c>
-      <c r="I2" s="6" t="str">
+      <c r="I2" s="3" t="str">
         <v>Date/Time of Informed Consent</v>
       </c>
-      <c r="J2" s="6" t="str">
+      <c r="J2" s="3" t="str">
         <v>Date/Time of End of Participation</v>
       </c>
-      <c r="K2" s="6" t="str">
+      <c r="K2" s="3" t="str">
         <v>Date/Time of Death</v>
       </c>
-      <c r="L2" s="6" t="str">
+      <c r="L2" s="3" t="str">
         <v>Subject Death Flag</v>
       </c>
-      <c r="M2" s="6" t="str">
+      <c r="M2" s="3" t="str">
         <v>Study Site Identifier</v>
       </c>
-      <c r="N2" s="6" t="str">
+      <c r="N2" s="3" t="str">
         <v>Date/Time of Birth</v>
       </c>
-      <c r="O2" s="6" t="str">
+      <c r="O2" s="3" t="str">
         <v>Age</v>
       </c>
-      <c r="P2" s="6" t="str">
+      <c r="P2" s="3" t="str">
         <v>Age Units</v>
       </c>
-      <c r="Q2" s="6" t="str">
+      <c r="Q2" s="3" t="str">
         <v>Sex</v>
       </c>
-      <c r="R2" s="6" t="str">
+      <c r="R2" s="3" t="str">
         <v>Race</v>
       </c>
-      <c r="S2" s="6" t="str">
+      <c r="S2" s="3" t="str">
         <v>Ethnicity</v>
       </c>
-      <c r="T2" s="6" t="str">
+      <c r="T2" s="3" t="str">
         <v>Planned Arm Code</v>
       </c>
-      <c r="U2" s="6" t="str">
+      <c r="U2" s="3" t="str">
         <v>Description of Planned Arm</v>
       </c>
-      <c r="V2" s="6" t="str">
+      <c r="V2" s="3" t="str">
         <v>Actual Arm Code</v>
       </c>
-      <c r="W2" s="6" t="str">
+      <c r="W2" s="3" t="str">
         <v>Description of Actual Arm</v>
       </c>
-      <c r="X2" s="6" t="str">
+      <c r="X2" s="3" t="str">
         <v>Reason Arm and/or Actual Arm is Null</v>
       </c>
-      <c r="Y2" s="6" t="str">
+      <c r="Y2" s="3" t="str">
         <v>Description of Unplanned Actual Arm</v>
       </c>
-      <c r="Z2" s="6" t="str">
+      <c r="Z2" s="3" t="str">
         <v>Country</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="B3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="C3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="D3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="E3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="F3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="G3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="H3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="I3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="J3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="K3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="L3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="M3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="N3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="O3" s="7" t="str">
+      <c r="A3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="B3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="C3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="D3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="E3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="F3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="G3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="H3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="I3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="J3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="K3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="L3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="M3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="N3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="O3" s="3" t="str">
         <v>Num</v>
       </c>
-      <c r="P3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="Q3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="R3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="S3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="T3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="U3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="V3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="W3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="X3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="Y3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="Z3" s="7" t="str">
+      <c r="P3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="Q3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="R3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="S3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="T3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="U3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="V3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="W3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="X3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="Y3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="Z3" s="3" t="str">
         <v>Char</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6">
+      <c r="A4" s="3">
         <v>12</v>
       </c>
-      <c r="B4" s="6">
+      <c r="B4" s="3">
         <v>2</v>
       </c>
-      <c r="C4" s="6">
+      <c r="C4" s="3">
         <v>8</v>
       </c>
-      <c r="D4" s="6">
+      <c r="D4" s="3">
         <v>4</v>
       </c>
-      <c r="E4" s="6">
+      <c r="E4" s="3">
         <v>10</v>
       </c>
-      <c r="F4" s="6">
+      <c r="F4" s="3">
         <v>10</v>
       </c>
-      <c r="G4" s="6">
+      <c r="G4" s="3">
         <v>10</v>
       </c>
-      <c r="H4" s="6">
+      <c r="H4" s="3">
         <v>10</v>
       </c>
-      <c r="I4" s="6">
+      <c r="I4" s="3">
         <v>10</v>
       </c>
-      <c r="J4" s="6">
+      <c r="J4" s="3">
         <v>10</v>
       </c>
-      <c r="K4" s="6">
+      <c r="K4" s="3">
         <v>10</v>
       </c>
-      <c r="L4" s="6">
+      <c r="L4" s="3">
         <v>1</v>
       </c>
-      <c r="M4" s="6">
+      <c r="M4" s="3">
         <v>3</v>
       </c>
-      <c r="N4" s="6">
+      <c r="N4" s="3">
         <v>10</v>
       </c>
-      <c r="O4" s="6">
+      <c r="O4" s="3">
         <v>8</v>
       </c>
-      <c r="P4" s="6">
+      <c r="P4" s="3">
         <v>5</v>
       </c>
-      <c r="Q4" s="6">
+      <c r="Q4" s="3">
         <v>1</v>
       </c>
-      <c r="R4" s="6">
+      <c r="R4" s="3">
         <v>41</v>
       </c>
-      <c r="S4" s="6">
+      <c r="S4" s="3">
         <v>22</v>
       </c>
-      <c r="T4" s="6">
+      <c r="T4" s="3">
         <v>8</v>
       </c>
-      <c r="U4" s="6">
+      <c r="U4" s="3">
         <v>28</v>
       </c>
-      <c r="V4" s="6">
+      <c r="V4" s="3">
         <v>8</v>
       </c>
-      <c r="W4" s="6">
+      <c r="W4" s="3">
         <v>28</v>
       </c>
-      <c r="X4" s="6">
+      <c r="X4" s="3">
         <v>14</v>
       </c>
-      <c r="Y4" s="6">
+      <c r="Y4" s="3">
         <v>200</v>
       </c>
-      <c r="Z4" s="6">
+      <c r="Z4" s="3">
         <v>3</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="str">
+      <c r="A5" s="3" t="str">
         <v>CDISCPILOT01</v>
       </c>
-      <c r="B5" s="7" t="str">
+      <c r="B5" s="3" t="str">
         <v>DM</v>
       </c>
-      <c r="C5" s="7" t="str">
+      <c r="C5" s="3" t="str">
         <v>CDISC001</v>
       </c>
-      <c r="D5" s="7">
+      <c r="D5" s="3">
         <v>1115</v>
       </c>
-      <c r="E5" s="7" t="str">
+      <c r="E5" s="3" t="str">
         <v>2018-05-17T09:35</v>
       </c>
-      <c r="F5" s="7" t="str">
+      <c r="F5" s="3" t="str">
         <v>2018-08-03</v>
       </c>
-      <c r="G5" s="7" t="str">
+      <c r="G5" s="3" t="str">
         <v>2018-05-17T09:35</v>
       </c>
-      <c r="H5" s="7" t="str">
+      <c r="H5" s="3" t="str">
         <v>2018-08-03</v>
       </c>
-      <c r="I5" s="7" t="str">
+      <c r="I5" s="3" t="str">
         <v>2018-04-26</v>
       </c>
-      <c r="J5" s="7" t="str">
+      <c r="J5" s="3" t="str">
         <v>2018-08-22</v>
       </c>
-      <c r="K5" s="7" t="str">
+      <c r="K5" s="3" t="str">
         <v>2018-08-22</v>
       </c>
-      <c r="L5" s="6" t="str">
+      <c r="L5" s="3" t="str">
         <v>Y</v>
       </c>
-      <c r="M5" s="7">
+      <c r="M5" s="3">
         <v>701</v>
       </c>
-      <c r="N5" s="7" t="str">
+      <c r="N5" s="3" t="str">
         <v>1947-07-24T00:00:00.000Z</v>
       </c>
-      <c r="O5" s="7" t="str">
+      <c r="O5" s="3" t="str">
         <v>70</v>
       </c>
-      <c r="P5" s="7" t="str">
+      <c r="P5" s="3" t="str">
         <v>YEARS</v>
       </c>
-      <c r="Q5" s="7" t="str">
+      <c r="Q5" s="3" t="str">
         <v>M</v>
       </c>
-      <c r="R5" s="7" t="str">
+      <c r="R5" s="3" t="str">
         <v>WHITE</v>
       </c>
-      <c r="S5" s="7" t="str">
+      <c r="S5" s="3" t="str">
         <v>NOT HISPANIC OR LATINO</v>
       </c>
-      <c r="T5" s="7" t="str">
+      <c r="T5" s="3" t="str">
         <v>A</v>
       </c>
-      <c r="U5" s="7" t="str">
+      <c r="U5" s="3" t="str">
         <v>Drug A</v>
       </c>
-      <c r="V5" s="7" t="str">
+      <c r="V5" s="3" t="str">
         <v>A</v>
       </c>
-      <c r="W5" s="7" t="str">
+      <c r="W5" s="3" t="str">
         <v>Drug A</v>
       </c>
-      <c r="X5" s="7" t="str">
+      <c r="X5" s="3" t="str">
         <v/>
       </c>
-      <c r="Y5" s="7" t="str">
+      <c r="Y5" s="3" t="str">
         <v/>
       </c>
-      <c r="Z5" s="7" t="str">
+      <c r="Z5" s="3" t="str">
         <v>AUS</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="str">
+      <c r="A6" s="3" t="str">
         <v>CDISCPILOT01</v>
       </c>
-      <c r="B6" s="6" t="str">
+      <c r="B6" s="3" t="str">
         <v>DM</v>
       </c>
-      <c r="C6" s="6" t="str">
+      <c r="C6" s="3" t="str">
         <v>CDISC002</v>
       </c>
-      <c r="D6" s="6">
+      <c r="D6" s="3">
         <v>1211</v>
       </c>
-      <c r="E6" s="6" t="str">
+      <c r="E6" s="3" t="str">
         <v>2018-05-24T12:00</v>
       </c>
-      <c r="F6" s="6" t="str">
+      <c r="F6" s="3" t="str">
         <v>2018-11-06</v>
       </c>
-      <c r="G6" s="6" t="str">
+      <c r="G6" s="3" t="str">
         <v>2018-05-24T12:00</v>
       </c>
-      <c r="H6" s="6" t="str">
+      <c r="H6" s="3" t="str">
         <v>2018-11-06</v>
       </c>
-      <c r="I6" s="6" t="str">
+      <c r="I6" s="3" t="str">
         <v>2018-05-07</v>
       </c>
-      <c r="J6" s="6" t="str">
+      <c r="J6" s="3" t="str">
         <v>2019-02-04</v>
       </c>
-      <c r="K6" s="6" t="str">
+      <c r="K6" s="3" t="str">
         <v>2019-02-04</v>
       </c>
-      <c r="L6" s="6" t="str">
+      <c r="L6" s="3" t="str">
         <v>Y</v>
       </c>
-      <c r="M6" s="6">
+      <c r="M6" s="3">
         <v>701</v>
       </c>
-      <c r="N6" s="6" t="str">
+      <c r="N6" s="3" t="str">
         <v>1905-05-08T00:00:00.000Z</v>
       </c>
-      <c r="O6" s="6" t="str">
+      <c r="O6" s="3" t="str">
         <v>78</v>
       </c>
-      <c r="P6" s="6" t="str">
+      <c r="P6" s="3" t="str">
         <v>YEARS</v>
       </c>
-      <c r="Q6" s="6" t="str">
+      <c r="Q6" s="3" t="str">
         <v>M</v>
       </c>
-      <c r="R6" s="6" t="str">
+      <c r="R6" s="3" t="str">
         <v>WHITE</v>
       </c>
-      <c r="S6" s="6" t="str">
+      <c r="S6" s="3" t="str">
         <v>NOT HISPANIC OR LATINO</v>
       </c>
-      <c r="T6" s="6" t="str">
+      <c r="T6" s="3" t="str">
         <v>P</v>
       </c>
-      <c r="U6" s="6" t="str">
+      <c r="U6" s="3" t="str">
         <v>Placebo</v>
       </c>
-      <c r="V6" s="6" t="str">
+      <c r="V6" s="3" t="str">
         <v>P</v>
       </c>
-      <c r="W6" s="6" t="str">
+      <c r="W6" s="3" t="str">
         <v>Placebo</v>
       </c>
-      <c r="X6" s="6" t="str">
+      <c r="X6" s="3" t="str">
         <v/>
       </c>
-      <c r="Y6" s="6" t="str">
+      <c r="Y6" s="3" t="str">
         <v/>
       </c>
-      <c r="Z6" s="6" t="str">
+      <c r="Z6" s="3" t="str">
         <v>AUS</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="str">
+      <c r="A7" s="3" t="str">
         <v>CDISCPILOT01</v>
       </c>
-      <c r="B7" s="7" t="str">
+      <c r="B7" s="3" t="str">
         <v>DM</v>
       </c>
-      <c r="C7" s="7" t="str">
+      <c r="C7" s="3" t="str">
         <v>CDISC003</v>
       </c>
-      <c r="D7" s="7">
+      <c r="D7" s="3">
         <v>1302</v>
       </c>
-      <c r="E7" s="7" t="str">
+      <c r="E7" s="3" t="str">
         <v>2006-01-16</v>
       </c>
-      <c r="F7" s="7" t="str">
+      <c r="F7" s="3" t="str">
         <v>2006-03-19</v>
       </c>
-      <c r="G7" s="7" t="str">
+      <c r="G7" s="3" t="str">
         <v>2006-01-16</v>
       </c>
-      <c r="H7" s="7" t="str">
+      <c r="H7" s="3" t="str">
         <v>2006-03-19</v>
       </c>
-      <c r="I7" s="7" t="str">
+      <c r="I7" s="3" t="str">
         <v>2006-01-02</v>
       </c>
-      <c r="J7" s="7" t="str">
+      <c r="J7" s="3" t="str">
         <v>2006-03-19</v>
       </c>
-      <c r="K7" s="7" t="str">
+      <c r="K7" s="3" t="str">
         <v/>
       </c>
-      <c r="L7" s="6" t="str">
+      <c r="L7" s="3" t="str">
         <v>Y</v>
       </c>
-      <c r="M7" s="7">
+      <c r="M7" s="3">
         <v>701</v>
       </c>
-      <c r="N7" s="7" t="str">
+      <c r="N7" s="3" t="str">
         <v>1944-06-16T00:00:00.000Z</v>
       </c>
-      <c r="O7" s="7" t="str">
+      <c r="O7" s="3" t="str">
         <v>74</v>
       </c>
-      <c r="P7" s="7" t="str">
+      <c r="P7" s="3" t="str">
         <v>YEARS</v>
       </c>
-      <c r="Q7" s="7" t="str">
+      <c r="Q7" s="3" t="str">
         <v>M</v>
       </c>
-      <c r="R7" s="7" t="str">
+      <c r="R7" s="3" t="str">
         <v>WHITE</v>
       </c>
-      <c r="S7" s="7" t="str">
+      <c r="S7" s="3" t="str">
         <v>NOT HISPANIC OR LATINO</v>
       </c>
-      <c r="T7" s="7" t="str">
+      <c r="T7" s="3" t="str">
         <v>B</v>
       </c>
-      <c r="U7" s="7" t="str">
+      <c r="U7" s="3" t="str">
         <v>Drug B</v>
       </c>
-      <c r="V7" s="7" t="str">
+      <c r="V7" s="3" t="str">
         <v>B</v>
       </c>
-      <c r="W7" s="7" t="str">
+      <c r="W7" s="3" t="str">
         <v>Drug B</v>
       </c>
-      <c r="X7" s="7" t="str">
+      <c r="X7" s="3" t="str">
         <v/>
       </c>
-      <c r="Y7" s="7" t="str">
+      <c r="Y7" s="3" t="str">
         <v/>
       </c>
-      <c r="Z7" s="7" t="str">
+      <c r="Z7" s="3" t="str">
         <v>CZE</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="str">
+      <c r="A8" s="3" t="str">
         <v>CDISCPILOT01</v>
       </c>
-      <c r="B8" s="7" t="str">
+      <c r="B8" s="3" t="str">
         <v>DM</v>
       </c>
-      <c r="C8" s="7" t="str">
+      <c r="C8" s="3" t="str">
         <v>CDISC004</v>
       </c>
-      <c r="D8" s="7">
+      <c r="D8" s="3">
         <v>1402</v>
       </c>
-      <c r="E8" s="7" t="str">
+      <c r="E8" s="3" t="str">
         <v>2018-07-16T09:15</v>
       </c>
-      <c r="F8" s="7" t="str">
+      <c r="F8" s="3" t="str">
         <v>2018-11-06T14:00</v>
       </c>
-      <c r="G8" s="7" t="str">
+      <c r="G8" s="3" t="str">
         <v>2018-07-16T09:15</v>
       </c>
-      <c r="H8" s="7" t="str">
+      <c r="H8" s="3" t="str">
         <v>2018-11-06T14:00</v>
       </c>
-      <c r="I8" s="7" t="str">
+      <c r="I8" s="3" t="str">
         <v>2018-06-27</v>
       </c>
-      <c r="J8" s="7" t="str">
+      <c r="J8" s="3" t="str">
         <v>2018-12-11</v>
       </c>
-      <c r="K8" s="7" t="str">
+      <c r="K8" s="3" t="str">
         <v/>
       </c>
-      <c r="L8" s="6" t="str">
+      <c r="L8" s="3" t="str">
         <v/>
       </c>
-      <c r="M8" s="7">
+      <c r="M8" s="3">
         <v>701</v>
       </c>
-      <c r="N8" s="7" t="str">
+      <c r="N8" s="3" t="str">
         <v>1905-04-16T00:00:00.000Z</v>
       </c>
-      <c r="O8" s="7" t="str">
+      <c r="O8" s="3" t="str">
         <v>68</v>
       </c>
-      <c r="P8" s="7" t="str">
+      <c r="P8" s="3" t="str">
         <v>YEARS</v>
       </c>
-      <c r="Q8" s="7" t="str">
+      <c r="Q8" s="3" t="str">
         <v>F</v>
       </c>
-      <c r="R8" s="7" t="str">
+      <c r="R8" s="3" t="str">
         <v>WHITE</v>
       </c>
-      <c r="S8" s="7" t="str">
+      <c r="S8" s="3" t="str">
         <v>HISPANIC OR LATINO</v>
       </c>
-      <c r="T8" s="7" t="str">
+      <c r="T8" s="3" t="str">
         <v>B</v>
       </c>
-      <c r="U8" s="7" t="str">
+      <c r="U8" s="3" t="str">
         <v>Drug B</v>
       </c>
-      <c r="V8" s="7" t="str">
+      <c r="V8" s="3" t="str">
         <v>B</v>
       </c>
-      <c r="W8" s="7" t="str">
+      <c r="W8" s="3" t="str">
         <v>Drug B</v>
       </c>
-      <c r="X8" s="7" t="str">
+      <c r="X8" s="3" t="str">
         <v/>
       </c>
-      <c r="Y8" s="7" t="str">
+      <c r="Y8" s="3" t="str">
         <v/>
       </c>
-      <c r="Z8" s="7" t="str">
+      <c r="Z8" s="3" t="str">
         <v>CAN</v>
       </c>
     </row>
@@ -1194,72 +1163,72 @@
   <dimension ref="A1:D5"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="str">
+      <c r="A1" s="4" t="str">
         <v>STUDYID</v>
       </c>
-      <c r="B1" s="3" t="str">
+      <c r="B1" s="4" t="str">
         <v>DOMAIN</v>
       </c>
-      <c r="C1" s="3" t="str">
+      <c r="C1" s="4" t="str">
         <v>USUBJID</v>
       </c>
-      <c r="D1" s="3" t="str">
-        <v>AESEQ</v>
+      <c r="D1" s="4" t="str">
+        <v>EGSEQ</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="8" t="str">
+      <c r="A2" s="5" t="str">
         <v>Study Identifier</v>
       </c>
-      <c r="B2" s="8" t="str">
+      <c r="B2" s="6" t="str">
         <v>Domain Abbreviation</v>
       </c>
-      <c r="C2" s="9" t="str">
+      <c r="C2" s="6" t="str">
         <v>Unique Subject Identifier</v>
       </c>
-      <c r="D2" s="9" t="str">
+      <c r="D2" s="6" t="str">
         <v>Sequence Number</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="9" t="str">
-        <v>Char</v>
-      </c>
-      <c r="B3" s="9" t="str">
-        <v>Char</v>
-      </c>
-      <c r="C3" s="9" t="str">
-        <v>Char</v>
-      </c>
-      <c r="D3" s="9" t="str">
+      <c r="A3" s="6" t="str">
+        <v>Char</v>
+      </c>
+      <c r="B3" s="6" t="str">
+        <v>Char</v>
+      </c>
+      <c r="C3" s="6" t="str">
+        <v>Char</v>
+      </c>
+      <c r="D3" s="6" t="str">
         <v>Num</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="9" t="str">
+      <c r="A4" s="6" t="str">
         <v>10</v>
       </c>
-      <c r="B4" s="9" t="str">
+      <c r="B4" s="6" t="str">
         <v>2</v>
       </c>
-      <c r="C4" s="9" t="str">
+      <c r="C4" s="6" t="str">
         <v>14</v>
       </c>
-      <c r="D4" s="9" t="str">
+      <c r="D4" s="6" t="str">
         <v>8</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="str">
+      <c r="A5" s="3" t="str">
         <v>CDISCPILOT01</v>
       </c>
-      <c r="B5" s="7" t="str">
-        <v>AE</v>
-      </c>
-      <c r="C5" s="7" t="str">
+      <c r="B5" s="3" t="str">
+        <v>EG</v>
+      </c>
+      <c r="C5" s="3" t="str">
         <v>CDISC-TEST-001</v>
       </c>
-      <c r="D5" s="7" t="str">
+      <c r="D5" s="3" t="str">
         <v>1</v>
       </c>
     </row>

--- a/rules/NEW-RULE/positive/01/data/new-rule-positive-01.xlsx
+++ b/rules/NEW-RULE/positive/01/data/new-rule-positive-01.xlsx
@@ -6,7 +6,7 @@
     <sheet name="Library" sheetId="1" r:id="rId1"/>
     <sheet name="Datasets" sheetId="2" r:id="rId2"/>
     <sheet name="dm.xpt" sheetId="3" r:id="rId3"/>
-    <sheet name="ae.xpt" sheetId="4" r:id="rId4"/>
+    <sheet name="mh.xpt" sheetId="4" r:id="rId4"/>
   </sheets>
 </workbook>
 </file>
@@ -36,7 +36,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
   <numFmts count="0"/>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -53,23 +57,6 @@
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
       <i/>
     </font>
     <font>
@@ -78,7 +65,7 @@
       <i/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="4">
     <fill>
       <patternFill patternType="none">
         <bgColor/>
@@ -86,21 +73,6 @@
     </fill>
     <fill>
       <patternFill patternType="gray125">
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <bgColor/>
       </patternFill>
     </fill>
@@ -136,17 +108,14 @@
   <cellStyleXfs>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="1" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -481,18 +450,18 @@
   <dimension ref="A1:B2"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="str">
+      <c r="A1" s="3" t="str">
         <v>Product</v>
       </c>
-      <c r="B1" s="2" t="str">
+      <c r="B1" s="3" t="str">
         <v>Version</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="str">
+      <c r="A2" s="3" t="str">
         <v>sdtmig</v>
       </c>
-      <c r="B2" s="2" t="str">
+      <c r="B2" s="3" t="str">
         <v>3-4</v>
       </c>
     </row>
@@ -508,26 +477,26 @@
   <dimension ref="A1:B3"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="str">
+      <c r="A1" s="3" t="str">
         <v>Filename</v>
       </c>
-      <c r="B1" s="2" t="str">
+      <c r="B1" s="3" t="str">
         <v>Label</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="str">
+      <c r="A2" s="3" t="str">
         <v>dm.xpt</v>
       </c>
-      <c r="B2" s="2" t="str">
+      <c r="B2" s="3" t="str">
         <v>Demographics</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="str">
+      <c r="A3" s="3" t="str">
         <v>ae.xpt</v>
       </c>
-      <c r="B3" s="2" t="str">
+      <c r="B3" s="3" t="str">
         <v>Adverse Events</v>
       </c>
     </row>
@@ -543,642 +512,642 @@
   <dimension ref="A1:Z8"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="str">
+      <c r="A1" s="4" t="str">
         <v>STUDYID</v>
       </c>
-      <c r="B1" s="3" t="str">
+      <c r="B1" s="4" t="str">
         <v>DOMAIN</v>
       </c>
-      <c r="C1" s="3" t="str">
+      <c r="C1" s="4" t="str">
         <v>USUBJID</v>
       </c>
-      <c r="D1" s="3" t="str">
+      <c r="D1" s="4" t="str">
         <v>SUBJID</v>
       </c>
-      <c r="E1" s="3" t="str">
+      <c r="E1" s="4" t="str">
         <v>RFSTDTC</v>
       </c>
-      <c r="F1" s="3" t="str">
+      <c r="F1" s="4" t="str">
         <v>RFENDTC</v>
       </c>
-      <c r="G1" s="3" t="str">
+      <c r="G1" s="4" t="str">
         <v>RFXSTDTC</v>
       </c>
-      <c r="H1" s="3" t="str">
+      <c r="H1" s="4" t="str">
         <v>RFXENDTC</v>
       </c>
-      <c r="I1" s="3" t="str">
+      <c r="I1" s="4" t="str">
         <v>RFICDTC</v>
       </c>
-      <c r="J1" s="3" t="str">
+      <c r="J1" s="4" t="str">
         <v>RFPENDTC</v>
       </c>
-      <c r="K1" s="3" t="str">
+      <c r="K1" s="4" t="str">
         <v>DTHDTC</v>
       </c>
       <c r="L1" s="4" t="str">
         <v>DTHFL</v>
       </c>
-      <c r="M1" s="3" t="str">
+      <c r="M1" s="4" t="str">
         <v>SITEID</v>
       </c>
-      <c r="N1" s="3" t="str">
+      <c r="N1" s="4" t="str">
         <v>BRTHDTC</v>
       </c>
-      <c r="O1" s="3" t="str">
+      <c r="O1" s="4" t="str">
         <v>AGE</v>
       </c>
-      <c r="P1" s="3" t="str">
+      <c r="P1" s="4" t="str">
         <v>AGEU</v>
       </c>
-      <c r="Q1" s="3" t="str">
+      <c r="Q1" s="4" t="str">
         <v>SEX</v>
       </c>
-      <c r="R1" s="3" t="str">
+      <c r="R1" s="4" t="str">
         <v>RACE</v>
       </c>
-      <c r="S1" s="3" t="str">
+      <c r="S1" s="4" t="str">
         <v>ETHNIC</v>
       </c>
-      <c r="T1" s="3" t="str">
+      <c r="T1" s="4" t="str">
         <v>ARMCD</v>
       </c>
-      <c r="U1" s="3" t="str">
+      <c r="U1" s="4" t="str">
         <v>ARM</v>
       </c>
-      <c r="V1" s="3" t="str">
+      <c r="V1" s="4" t="str">
         <v>ACTARMCD</v>
       </c>
-      <c r="W1" s="3" t="str">
+      <c r="W1" s="4" t="str">
         <v>ACTARM</v>
       </c>
-      <c r="X1" s="3" t="str">
+      <c r="X1" s="4" t="str">
         <v>ARMNRS</v>
       </c>
-      <c r="Y1" s="3" t="str">
+      <c r="Y1" s="4" t="str">
         <v>ACTARMUD</v>
       </c>
-      <c r="Z1" s="3" t="str">
+      <c r="Z1" s="4" t="str">
         <v>COUNTRY</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="str">
+      <c r="A2" s="3" t="str">
         <v>Study Identifier</v>
       </c>
-      <c r="B2" s="5" t="str">
+      <c r="B2" s="3" t="str">
         <v>Domain Abbreviation</v>
       </c>
-      <c r="C2" s="6" t="str">
+      <c r="C2" s="3" t="str">
         <v>Unique Subject Identifier</v>
       </c>
-      <c r="D2" s="6" t="str">
+      <c r="D2" s="3" t="str">
         <v>Subject Identifier for the Study</v>
       </c>
-      <c r="E2" s="6" t="str">
+      <c r="E2" s="3" t="str">
         <v>Subject Reference Start Date/Time</v>
       </c>
-      <c r="F2" s="6" t="str">
+      <c r="F2" s="3" t="str">
         <v>Subject Reference End Date/Time</v>
       </c>
-      <c r="G2" s="6" t="str">
+      <c r="G2" s="3" t="str">
         <v>Date/Time of First Study Treatment</v>
       </c>
-      <c r="H2" s="6" t="str">
+      <c r="H2" s="3" t="str">
         <v>Date/Time of Last Study Treatment</v>
       </c>
-      <c r="I2" s="6" t="str">
+      <c r="I2" s="3" t="str">
         <v>Date/Time of Informed Consent</v>
       </c>
-      <c r="J2" s="6" t="str">
+      <c r="J2" s="3" t="str">
         <v>Date/Time of End of Participation</v>
       </c>
-      <c r="K2" s="6" t="str">
+      <c r="K2" s="3" t="str">
         <v>Date/Time of Death</v>
       </c>
-      <c r="L2" s="6" t="str">
+      <c r="L2" s="3" t="str">
         <v>Subject Death Flag</v>
       </c>
-      <c r="M2" s="6" t="str">
+      <c r="M2" s="3" t="str">
         <v>Study Site Identifier</v>
       </c>
-      <c r="N2" s="6" t="str">
+      <c r="N2" s="3" t="str">
         <v>Date/Time of Birth</v>
       </c>
-      <c r="O2" s="6" t="str">
+      <c r="O2" s="3" t="str">
         <v>Age</v>
       </c>
-      <c r="P2" s="6" t="str">
+      <c r="P2" s="3" t="str">
         <v>Age Units</v>
       </c>
-      <c r="Q2" s="6" t="str">
+      <c r="Q2" s="3" t="str">
         <v>Sex</v>
       </c>
-      <c r="R2" s="6" t="str">
+      <c r="R2" s="3" t="str">
         <v>Race</v>
       </c>
-      <c r="S2" s="6" t="str">
+      <c r="S2" s="3" t="str">
         <v>Ethnicity</v>
       </c>
-      <c r="T2" s="6" t="str">
+      <c r="T2" s="3" t="str">
         <v>Planned Arm Code</v>
       </c>
-      <c r="U2" s="6" t="str">
+      <c r="U2" s="3" t="str">
         <v>Description of Planned Arm</v>
       </c>
-      <c r="V2" s="6" t="str">
+      <c r="V2" s="3" t="str">
         <v>Actual Arm Code</v>
       </c>
-      <c r="W2" s="6" t="str">
+      <c r="W2" s="3" t="str">
         <v>Description of Actual Arm</v>
       </c>
-      <c r="X2" s="6" t="str">
+      <c r="X2" s="3" t="str">
         <v>Reason Arm and/or Actual Arm is Null</v>
       </c>
-      <c r="Y2" s="6" t="str">
+      <c r="Y2" s="3" t="str">
         <v>Description of Unplanned Actual Arm</v>
       </c>
-      <c r="Z2" s="6" t="str">
+      <c r="Z2" s="3" t="str">
         <v>Country</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="B3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="C3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="D3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="E3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="F3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="G3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="H3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="I3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="J3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="K3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="L3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="M3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="N3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="O3" s="7" t="str">
+      <c r="A3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="B3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="C3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="D3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="E3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="F3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="G3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="H3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="I3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="J3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="K3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="L3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="M3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="N3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="O3" s="3" t="str">
         <v>Num</v>
       </c>
-      <c r="P3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="Q3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="R3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="S3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="T3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="U3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="V3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="W3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="X3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="Y3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="Z3" s="7" t="str">
+      <c r="P3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="Q3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="R3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="S3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="T3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="U3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="V3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="W3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="X3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="Y3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="Z3" s="3" t="str">
         <v>Char</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6">
+      <c r="A4" s="3">
         <v>12</v>
       </c>
-      <c r="B4" s="6">
+      <c r="B4" s="3">
         <v>2</v>
       </c>
-      <c r="C4" s="6">
+      <c r="C4" s="3">
         <v>8</v>
       </c>
-      <c r="D4" s="6">
+      <c r="D4" s="3">
         <v>4</v>
       </c>
-      <c r="E4" s="6">
+      <c r="E4" s="3">
         <v>10</v>
       </c>
-      <c r="F4" s="6">
+      <c r="F4" s="3">
         <v>10</v>
       </c>
-      <c r="G4" s="6">
+      <c r="G4" s="3">
         <v>10</v>
       </c>
-      <c r="H4" s="6">
+      <c r="H4" s="3">
         <v>10</v>
       </c>
-      <c r="I4" s="6">
+      <c r="I4" s="3">
         <v>10</v>
       </c>
-      <c r="J4" s="6">
+      <c r="J4" s="3">
         <v>10</v>
       </c>
-      <c r="K4" s="6">
+      <c r="K4" s="3">
         <v>10</v>
       </c>
-      <c r="L4" s="6">
+      <c r="L4" s="3">
         <v>1</v>
       </c>
-      <c r="M4" s="6">
+      <c r="M4" s="3">
         <v>3</v>
       </c>
-      <c r="N4" s="6">
+      <c r="N4" s="3">
         <v>10</v>
       </c>
-      <c r="O4" s="6">
+      <c r="O4" s="3">
         <v>8</v>
       </c>
-      <c r="P4" s="6">
+      <c r="P4" s="3">
         <v>5</v>
       </c>
-      <c r="Q4" s="6">
+      <c r="Q4" s="3">
         <v>1</v>
       </c>
-      <c r="R4" s="6">
+      <c r="R4" s="3">
         <v>41</v>
       </c>
-      <c r="S4" s="6">
+      <c r="S4" s="3">
         <v>22</v>
       </c>
-      <c r="T4" s="6">
+      <c r="T4" s="3">
         <v>8</v>
       </c>
-      <c r="U4" s="6">
+      <c r="U4" s="3">
         <v>28</v>
       </c>
-      <c r="V4" s="6">
+      <c r="V4" s="3">
         <v>8</v>
       </c>
-      <c r="W4" s="6">
+      <c r="W4" s="3">
         <v>28</v>
       </c>
-      <c r="X4" s="6">
+      <c r="X4" s="3">
         <v>14</v>
       </c>
-      <c r="Y4" s="6">
+      <c r="Y4" s="3">
         <v>200</v>
       </c>
-      <c r="Z4" s="6">
+      <c r="Z4" s="3">
         <v>3</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="str">
+      <c r="A5" s="3" t="str">
         <v>CDISCPILOT01</v>
       </c>
-      <c r="B5" s="7" t="str">
+      <c r="B5" s="3" t="str">
         <v>DM</v>
       </c>
-      <c r="C5" s="7" t="str">
+      <c r="C5" s="3" t="str">
         <v>CDISC001</v>
       </c>
-      <c r="D5" s="7">
+      <c r="D5" s="3">
         <v>1115</v>
       </c>
-      <c r="E5" s="7" t="str">
+      <c r="E5" s="3" t="str">
         <v>2018-05-17T09:35</v>
       </c>
-      <c r="F5" s="7" t="str">
+      <c r="F5" s="3" t="str">
         <v>2018-08-03</v>
       </c>
-      <c r="G5" s="7" t="str">
+      <c r="G5" s="3" t="str">
         <v>2018-05-17T09:35</v>
       </c>
-      <c r="H5" s="7" t="str">
+      <c r="H5" s="3" t="str">
         <v>2018-08-03</v>
       </c>
-      <c r="I5" s="7" t="str">
+      <c r="I5" s="3" t="str">
         <v>2018-04-26</v>
       </c>
-      <c r="J5" s="7" t="str">
+      <c r="J5" s="3" t="str">
         <v>2018-08-22</v>
       </c>
-      <c r="K5" s="7" t="str">
+      <c r="K5" s="3" t="str">
         <v>2018-08-22</v>
       </c>
-      <c r="L5" s="6" t="str">
+      <c r="L5" s="3" t="str">
         <v>Y</v>
       </c>
-      <c r="M5" s="7">
+      <c r="M5" s="3">
         <v>701</v>
       </c>
-      <c r="N5" s="7" t="str">
+      <c r="N5" s="3" t="str">
         <v>1947-07-24T00:00:00.000Z</v>
       </c>
-      <c r="O5" s="7" t="str">
+      <c r="O5" s="3" t="str">
         <v>70</v>
       </c>
-      <c r="P5" s="7" t="str">
+      <c r="P5" s="3" t="str">
         <v>YEARS</v>
       </c>
-      <c r="Q5" s="7" t="str">
+      <c r="Q5" s="3" t="str">
         <v>M</v>
       </c>
-      <c r="R5" s="7" t="str">
+      <c r="R5" s="3" t="str">
         <v>WHITE</v>
       </c>
-      <c r="S5" s="7" t="str">
+      <c r="S5" s="3" t="str">
         <v>NOT HISPANIC OR LATINO</v>
       </c>
-      <c r="T5" s="7" t="str">
+      <c r="T5" s="3" t="str">
         <v>A</v>
       </c>
-      <c r="U5" s="7" t="str">
+      <c r="U5" s="3" t="str">
         <v>Drug A</v>
       </c>
-      <c r="V5" s="7" t="str">
+      <c r="V5" s="3" t="str">
         <v>A</v>
       </c>
-      <c r="W5" s="7" t="str">
+      <c r="W5" s="3" t="str">
         <v>Drug A</v>
       </c>
-      <c r="X5" s="7" t="str">
+      <c r="X5" s="3" t="str">
         <v/>
       </c>
-      <c r="Y5" s="7" t="str">
+      <c r="Y5" s="3" t="str">
         <v/>
       </c>
-      <c r="Z5" s="7" t="str">
+      <c r="Z5" s="3" t="str">
         <v>AUS</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="str">
+      <c r="A6" s="3" t="str">
         <v>CDISCPILOT01</v>
       </c>
-      <c r="B6" s="6" t="str">
+      <c r="B6" s="3" t="str">
         <v>DM</v>
       </c>
-      <c r="C6" s="6" t="str">
+      <c r="C6" s="3" t="str">
         <v>CDISC002</v>
       </c>
-      <c r="D6" s="6">
+      <c r="D6" s="3">
         <v>1211</v>
       </c>
-      <c r="E6" s="6" t="str">
+      <c r="E6" s="3" t="str">
         <v>2018-05-24T12:00</v>
       </c>
-      <c r="F6" s="6" t="str">
+      <c r="F6" s="3" t="str">
         <v>2018-11-06</v>
       </c>
-      <c r="G6" s="6" t="str">
+      <c r="G6" s="3" t="str">
         <v>2018-05-24T12:00</v>
       </c>
-      <c r="H6" s="6" t="str">
+      <c r="H6" s="3" t="str">
         <v>2018-11-06</v>
       </c>
-      <c r="I6" s="6" t="str">
+      <c r="I6" s="3" t="str">
         <v>2018-05-07</v>
       </c>
-      <c r="J6" s="6" t="str">
+      <c r="J6" s="3" t="str">
         <v>2019-02-04</v>
       </c>
-      <c r="K6" s="6" t="str">
+      <c r="K6" s="3" t="str">
         <v>2019-02-04</v>
       </c>
-      <c r="L6" s="6" t="str">
+      <c r="L6" s="3" t="str">
         <v>Y</v>
       </c>
-      <c r="M6" s="6">
+      <c r="M6" s="3">
         <v>701</v>
       </c>
-      <c r="N6" s="6" t="str">
+      <c r="N6" s="3" t="str">
         <v>1905-05-08T00:00:00.000Z</v>
       </c>
-      <c r="O6" s="6" t="str">
+      <c r="O6" s="3" t="str">
         <v>78</v>
       </c>
-      <c r="P6" s="6" t="str">
+      <c r="P6" s="3" t="str">
         <v>YEARS</v>
       </c>
-      <c r="Q6" s="6" t="str">
+      <c r="Q6" s="3" t="str">
         <v>M</v>
       </c>
-      <c r="R6" s="6" t="str">
+      <c r="R6" s="3" t="str">
         <v>WHITE</v>
       </c>
-      <c r="S6" s="6" t="str">
+      <c r="S6" s="3" t="str">
         <v>NOT HISPANIC OR LATINO</v>
       </c>
-      <c r="T6" s="6" t="str">
+      <c r="T6" s="3" t="str">
         <v>P</v>
       </c>
-      <c r="U6" s="6" t="str">
+      <c r="U6" s="3" t="str">
         <v>Placebo</v>
       </c>
-      <c r="V6" s="6" t="str">
+      <c r="V6" s="3" t="str">
         <v>P</v>
       </c>
-      <c r="W6" s="6" t="str">
+      <c r="W6" s="3" t="str">
         <v>Placebo</v>
       </c>
-      <c r="X6" s="6" t="str">
+      <c r="X6" s="3" t="str">
         <v/>
       </c>
-      <c r="Y6" s="6" t="str">
+      <c r="Y6" s="3" t="str">
         <v/>
       </c>
-      <c r="Z6" s="6" t="str">
+      <c r="Z6" s="3" t="str">
         <v>AUS</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="str">
+      <c r="A7" s="3" t="str">
         <v>CDISCPILOT01</v>
       </c>
-      <c r="B7" s="7" t="str">
+      <c r="B7" s="3" t="str">
         <v>DM</v>
       </c>
-      <c r="C7" s="7" t="str">
+      <c r="C7" s="3" t="str">
         <v>CDISC003</v>
       </c>
-      <c r="D7" s="7">
+      <c r="D7" s="3">
         <v>1302</v>
       </c>
-      <c r="E7" s="7" t="str">
+      <c r="E7" s="3" t="str">
         <v>2006-01-16</v>
       </c>
-      <c r="F7" s="7" t="str">
+      <c r="F7" s="3" t="str">
         <v>2006-03-19</v>
       </c>
-      <c r="G7" s="7" t="str">
+      <c r="G7" s="3" t="str">
         <v>2006-01-16</v>
       </c>
-      <c r="H7" s="7" t="str">
+      <c r="H7" s="3" t="str">
         <v>2006-03-19</v>
       </c>
-      <c r="I7" s="7" t="str">
+      <c r="I7" s="3" t="str">
         <v>2006-01-02</v>
       </c>
-      <c r="J7" s="7" t="str">
+      <c r="J7" s="3" t="str">
         <v>2006-03-19</v>
       </c>
-      <c r="K7" s="7" t="str">
+      <c r="K7" s="3" t="str">
         <v/>
       </c>
-      <c r="L7" s="6" t="str">
+      <c r="L7" s="3" t="str">
         <v>Y</v>
       </c>
-      <c r="M7" s="7">
+      <c r="M7" s="3">
         <v>701</v>
       </c>
-      <c r="N7" s="7" t="str">
+      <c r="N7" s="3" t="str">
         <v>1944-06-16T00:00:00.000Z</v>
       </c>
-      <c r="O7" s="7" t="str">
+      <c r="O7" s="3" t="str">
         <v>74</v>
       </c>
-      <c r="P7" s="7" t="str">
+      <c r="P7" s="3" t="str">
         <v>YEARS</v>
       </c>
-      <c r="Q7" s="7" t="str">
+      <c r="Q7" s="3" t="str">
         <v>M</v>
       </c>
-      <c r="R7" s="7" t="str">
+      <c r="R7" s="3" t="str">
         <v>WHITE</v>
       </c>
-      <c r="S7" s="7" t="str">
+      <c r="S7" s="3" t="str">
         <v>NOT HISPANIC OR LATINO</v>
       </c>
-      <c r="T7" s="7" t="str">
+      <c r="T7" s="3" t="str">
         <v>B</v>
       </c>
-      <c r="U7" s="7" t="str">
+      <c r="U7" s="3" t="str">
         <v>Drug B</v>
       </c>
-      <c r="V7" s="7" t="str">
+      <c r="V7" s="3" t="str">
         <v>B</v>
       </c>
-      <c r="W7" s="7" t="str">
+      <c r="W7" s="3" t="str">
         <v>Drug B</v>
       </c>
-      <c r="X7" s="7" t="str">
+      <c r="X7" s="3" t="str">
         <v/>
       </c>
-      <c r="Y7" s="7" t="str">
+      <c r="Y7" s="3" t="str">
         <v/>
       </c>
-      <c r="Z7" s="7" t="str">
+      <c r="Z7" s="3" t="str">
         <v>CZE</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="str">
+      <c r="A8" s="3" t="str">
         <v>CDISCPILOT01</v>
       </c>
-      <c r="B8" s="7" t="str">
+      <c r="B8" s="3" t="str">
         <v>DM</v>
       </c>
-      <c r="C8" s="7" t="str">
+      <c r="C8" s="3" t="str">
         <v>CDISC004</v>
       </c>
-      <c r="D8" s="7">
+      <c r="D8" s="3">
         <v>1402</v>
       </c>
-      <c r="E8" s="7" t="str">
+      <c r="E8" s="3" t="str">
         <v>2018-07-16T09:15</v>
       </c>
-      <c r="F8" s="7" t="str">
+      <c r="F8" s="3" t="str">
         <v>2018-11-06T14:00</v>
       </c>
-      <c r="G8" s="7" t="str">
+      <c r="G8" s="3" t="str">
         <v>2018-07-16T09:15</v>
       </c>
-      <c r="H8" s="7" t="str">
+      <c r="H8" s="3" t="str">
         <v>2018-11-06T14:00</v>
       </c>
-      <c r="I8" s="7" t="str">
+      <c r="I8" s="3" t="str">
         <v>2018-06-27</v>
       </c>
-      <c r="J8" s="7" t="str">
+      <c r="J8" s="3" t="str">
         <v>2018-12-11</v>
       </c>
-      <c r="K8" s="7" t="str">
+      <c r="K8" s="3" t="str">
         <v/>
       </c>
-      <c r="L8" s="6" t="str">
+      <c r="L8" s="3" t="str">
         <v/>
       </c>
-      <c r="M8" s="7">
+      <c r="M8" s="3">
         <v>701</v>
       </c>
-      <c r="N8" s="7" t="str">
+      <c r="N8" s="3" t="str">
         <v>1905-04-16T00:00:00.000Z</v>
       </c>
-      <c r="O8" s="7" t="str">
+      <c r="O8" s="3" t="str">
         <v>68</v>
       </c>
-      <c r="P8" s="7" t="str">
+      <c r="P8" s="3" t="str">
         <v>YEARS</v>
       </c>
-      <c r="Q8" s="7" t="str">
+      <c r="Q8" s="3" t="str">
         <v>F</v>
       </c>
-      <c r="R8" s="7" t="str">
+      <c r="R8" s="3" t="str">
         <v>WHITE</v>
       </c>
-      <c r="S8" s="7" t="str">
+      <c r="S8" s="3" t="str">
         <v>HISPANIC OR LATINO</v>
       </c>
-      <c r="T8" s="7" t="str">
+      <c r="T8" s="3" t="str">
         <v>B</v>
       </c>
-      <c r="U8" s="7" t="str">
+      <c r="U8" s="3" t="str">
         <v>Drug B</v>
       </c>
-      <c r="V8" s="7" t="str">
+      <c r="V8" s="3" t="str">
         <v>B</v>
       </c>
-      <c r="W8" s="7" t="str">
+      <c r="W8" s="3" t="str">
         <v>Drug B</v>
       </c>
-      <c r="X8" s="7" t="str">
+      <c r="X8" s="3" t="str">
         <v/>
       </c>
-      <c r="Y8" s="7" t="str">
+      <c r="Y8" s="3" t="str">
         <v/>
       </c>
-      <c r="Z8" s="7" t="str">
+      <c r="Z8" s="3" t="str">
         <v>CAN</v>
       </c>
     </row>
@@ -1194,72 +1163,72 @@
   <dimension ref="A1:D5"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="str">
+      <c r="A1" s="4" t="str">
         <v>STUDYID</v>
       </c>
-      <c r="B1" s="3" t="str">
+      <c r="B1" s="4" t="str">
         <v>DOMAIN</v>
       </c>
-      <c r="C1" s="3" t="str">
+      <c r="C1" s="4" t="str">
         <v>USUBJID</v>
       </c>
-      <c r="D1" s="3" t="str">
-        <v>AESEQ</v>
+      <c r="D1" s="4" t="str">
+        <v>MHSEQ</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="8" t="str">
+      <c r="A2" s="5" t="str">
         <v>Study Identifier</v>
       </c>
-      <c r="B2" s="8" t="str">
+      <c r="B2" s="6" t="str">
         <v>Domain Abbreviation</v>
       </c>
-      <c r="C2" s="9" t="str">
+      <c r="C2" s="6" t="str">
         <v>Unique Subject Identifier</v>
       </c>
-      <c r="D2" s="9" t="str">
+      <c r="D2" s="6" t="str">
         <v>Sequence Number</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="9" t="str">
-        <v>Char</v>
-      </c>
-      <c r="B3" s="9" t="str">
-        <v>Char</v>
-      </c>
-      <c r="C3" s="9" t="str">
-        <v>Char</v>
-      </c>
-      <c r="D3" s="9" t="str">
+      <c r="A3" s="6" t="str">
+        <v>Char</v>
+      </c>
+      <c r="B3" s="6" t="str">
+        <v>Char</v>
+      </c>
+      <c r="C3" s="6" t="str">
+        <v>Char</v>
+      </c>
+      <c r="D3" s="6" t="str">
         <v>Num</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="9" t="str">
+      <c r="A4" s="6" t="str">
         <v>10</v>
       </c>
-      <c r="B4" s="9" t="str">
+      <c r="B4" s="6" t="str">
         <v>2</v>
       </c>
-      <c r="C4" s="9" t="str">
+      <c r="C4" s="6" t="str">
         <v>14</v>
       </c>
-      <c r="D4" s="9" t="str">
+      <c r="D4" s="6" t="str">
         <v>8</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="str">
+      <c r="A5" s="3" t="str">
         <v>CDISCPILOT01</v>
       </c>
-      <c r="B5" s="7" t="str">
-        <v>AE</v>
-      </c>
-      <c r="C5" s="7" t="str">
+      <c r="B5" s="3" t="str">
+        <v>MH</v>
+      </c>
+      <c r="C5" s="3" t="str">
         <v>CDISC-TEST-001</v>
       </c>
-      <c r="D5" s="7" t="str">
+      <c r="D5" s="3" t="str">
         <v>1</v>
       </c>
     </row>

--- a/rules/NEW-RULE/positive/01/data/new-rule-positive-01.xlsx
+++ b/rules/NEW-RULE/positive/01/data/new-rule-positive-01.xlsx
@@ -36,7 +36,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
   <numFmts count="0"/>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -59,13 +59,8 @@
       <name val="Calibri"/>
       <i/>
     </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <i/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none">
         <bgColor/>
@@ -73,12 +68,6 @@
     </fill>
     <fill>
       <patternFill patternType="gray125">
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -108,14 +97,13 @@
   <cellStyleXfs>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="1" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -494,10 +482,10 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="str">
-        <v>ae.xpt</v>
+        <v>mh.xpt</v>
       </c>
       <c r="B3" s="3" t="str">
-        <v>Adverse Events</v>
+        <v>Medical History</v>
       </c>
     </row>
   </sheetData>
@@ -1180,41 +1168,41 @@
       <c r="A2" s="5" t="str">
         <v>Study Identifier</v>
       </c>
-      <c r="B2" s="6" t="str">
+      <c r="B2" s="5" t="str">
         <v>Domain Abbreviation</v>
       </c>
-      <c r="C2" s="6" t="str">
+      <c r="C2" s="5" t="str">
         <v>Unique Subject Identifier</v>
       </c>
-      <c r="D2" s="6" t="str">
+      <c r="D2" s="5" t="str">
         <v>Sequence Number</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="B3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="C3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="D3" s="6" t="str">
+      <c r="A3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="B3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="C3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="D3" s="5" t="str">
         <v>Num</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="str">
+      <c r="A4" s="5" t="str">
         <v>10</v>
       </c>
-      <c r="B4" s="6" t="str">
+      <c r="B4" s="5" t="str">
         <v>2</v>
       </c>
-      <c r="C4" s="6" t="str">
+      <c r="C4" s="5" t="str">
         <v>14</v>
       </c>
-      <c r="D4" s="6" t="str">
+      <c r="D4" s="5" t="str">
         <v>8</v>
       </c>
     </row>

--- a/rules/NEW-RULE/positive/01/data/new-rule-positive-01.xlsx
+++ b/rules/NEW-RULE/positive/01/data/new-rule-positive-01.xlsx
@@ -1,41 +1,101 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
-  <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
-  </bookViews>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Library" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Datasets" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Library" sheetId="1" r:id="rId1"/>
+    <sheet name="Datasets" sheetId="2" r:id="rId2"/>
+    <sheet name="ie.xpt" sheetId="3" r:id="rId3"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <color theme="1"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <scheme val="minor"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <i/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none">
+        <bgColor/>
+      </patternFill>
     </fill>
     <fill>
-      <patternFill patternType="gray125"/>
+      <patternFill patternType="gray125">
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor/>
+      </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left/>
       <right/>
@@ -44,84 +104,24 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+  <cellXfs count="8">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="1" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+  <cellStyles>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
 </styleSheet>
 </file>
 
@@ -200,6 +200,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -234,6 +235,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -268,20 +270,16 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
+                <a:tint val="100000"/>
+                <a:shade val="100000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="80000">
-              <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
+                <a:tint val="50000"/>
+                <a:shade val="100000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -403,75 +401,316 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
+  <a:objectDefaults>
+    <a:spDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="3">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </a:style>
+    </a:spDef>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
   <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Product</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Version</t>
-        </is>
+      <c r="A1" s="3" t="str">
+        <v>Product</v>
+      </c>
+      <c r="B1" s="3" t="str">
+        <v>Version</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>sdtmig</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>3-4</t>
-        </is>
+      <c r="A2" s="2" t="str">
+        <v>sdtmig</v>
+      </c>
+      <c r="B2" s="2" t="str">
+        <v>3-4</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:B2"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Filename</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Label</t>
-        </is>
+      <c r="A1" s="3" t="str">
+        <v>Filename</v>
+      </c>
+      <c r="B1" s="3" t="str">
+        <v>Label</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr"/>
-      <c r="B2" t="inlineStr"/>
+      <c r="A2" s="4" t="str">
+        <v>ie.xpt</v>
+      </c>
+      <c r="B2" s="4" t="str">
+        <v>Inclusion Exclusion</v>
+      </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:B2"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M5"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="str">
+        <v>STUDYID</v>
+      </c>
+      <c r="B1" s="3" t="str">
+        <v>DOMAIN</v>
+      </c>
+      <c r="C1" s="3" t="str">
+        <v>USUBJID</v>
+      </c>
+      <c r="D1" s="3" t="str">
+        <v>IESEQ</v>
+      </c>
+      <c r="E1" s="3" t="str">
+        <v>IETESTCD</v>
+      </c>
+      <c r="F1" s="3" t="str">
+        <v>IETEST</v>
+      </c>
+      <c r="G1" s="3" t="str">
+        <v>IECAT</v>
+      </c>
+      <c r="H1" s="3" t="str">
+        <v>IEORRES</v>
+      </c>
+      <c r="I1" s="3" t="str">
+        <v>IESTRESC</v>
+      </c>
+      <c r="J1" s="3" t="str">
+        <v>EPOCH</v>
+      </c>
+      <c r="K1" s="3" t="str">
+        <v>IEDTC</v>
+      </c>
+      <c r="L1" s="3" t="str">
+        <v>IEDY</v>
+      </c>
+      <c r="M1" s="5" t="str">
+        <v>IELOINC</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="6" t="str">
+        <v>Study Identifier</v>
+      </c>
+      <c r="B2" s="6" t="str">
+        <v>Domain Abbreviation</v>
+      </c>
+      <c r="C2" s="6" t="str">
+        <v>Unique Subject Identifier</v>
+      </c>
+      <c r="D2" s="6" t="str">
+        <v>Sequence Number</v>
+      </c>
+      <c r="E2" s="6" t="str">
+        <v>Inclusion/Exclusion Criterion Short Name</v>
+      </c>
+      <c r="F2" s="6" t="str">
+        <v>Inclusion/Exclusion Criterion</v>
+      </c>
+      <c r="G2" s="6" t="str">
+        <v>Inclusion/Exclusion Category</v>
+      </c>
+      <c r="H2" s="6" t="str">
+        <v>I/E Criterion Original Result</v>
+      </c>
+      <c r="I2" s="6" t="str">
+        <v>I/E Criterion Result in Std Format</v>
+      </c>
+      <c r="J2" s="6" t="str">
+        <v>Epoch</v>
+      </c>
+      <c r="K2" s="6" t="str">
+        <v>Date/Time of Collection</v>
+      </c>
+      <c r="L2" s="6" t="str">
+        <v>Study Day of Collection</v>
+      </c>
+      <c r="M2" s="6" t="str">
+        <v>LOINC Code</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="str">
+        <v>Char</v>
+      </c>
+      <c r="B3" s="6" t="str">
+        <v>Char</v>
+      </c>
+      <c r="C3" s="6" t="str">
+        <v>Char</v>
+      </c>
+      <c r="D3" s="6" t="str">
+        <v>Num</v>
+      </c>
+      <c r="E3" s="6" t="str">
+        <v>Char</v>
+      </c>
+      <c r="F3" s="6" t="str">
+        <v>Char</v>
+      </c>
+      <c r="G3" s="6" t="str">
+        <v>Char</v>
+      </c>
+      <c r="H3" s="6" t="str">
+        <v>Char</v>
+      </c>
+      <c r="I3" s="6" t="str">
+        <v>Char</v>
+      </c>
+      <c r="J3" s="6" t="str">
+        <v>Char</v>
+      </c>
+      <c r="K3" s="6" t="str">
+        <v>Char</v>
+      </c>
+      <c r="L3" s="6" t="str">
+        <v>Num</v>
+      </c>
+      <c r="M3" s="6" t="str">
+        <v>Char</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6">
+        <v>12</v>
+      </c>
+      <c r="B4" s="6">
+        <v>2</v>
+      </c>
+      <c r="C4" s="6">
+        <v>8</v>
+      </c>
+      <c r="D4" s="6">
+        <v>8</v>
+      </c>
+      <c r="E4" s="6">
+        <v>7</v>
+      </c>
+      <c r="F4" s="6">
+        <v>196</v>
+      </c>
+      <c r="G4" s="6">
+        <v>9</v>
+      </c>
+      <c r="H4" s="6">
+        <v>1</v>
+      </c>
+      <c r="I4" s="6">
+        <v>1</v>
+      </c>
+      <c r="J4" s="6">
+        <v>9</v>
+      </c>
+      <c r="K4" s="6">
+        <v>10</v>
+      </c>
+      <c r="L4" s="6">
+        <v>8</v>
+      </c>
+      <c r="M4" s="6" t="str">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="str">
+        <v>CDISCPILOT01</v>
+      </c>
+      <c r="B5" s="7" t="str">
+        <v>IE</v>
+      </c>
+      <c r="C5" s="7" t="str">
+        <v>CDISC01</v>
+      </c>
+      <c r="D5" s="7">
+        <v>1</v>
+      </c>
+      <c r="E5" s="7" t="str">
+        <v>INCL01</v>
+      </c>
+      <c r="F5" s="7" t="str">
+        <v>Is not pregnant or nursing.</v>
+      </c>
+      <c r="G5" s="7" t="str">
+        <v>INCLUSION</v>
+      </c>
+      <c r="H5" s="7" t="str">
+        <v>Y</v>
+      </c>
+      <c r="I5" s="7" t="str">
+        <v>Y</v>
+      </c>
+      <c r="J5" s="7" t="str">
+        <v>SCREENING</v>
+      </c>
+      <c r="K5" s="7" t="str">
+        <v>2014-03-17</v>
+      </c>
+      <c r="L5" s="2" t="str">
+        <v/>
+      </c>
+      <c r="M5" s="4" t="str">
+        <v>100000-9</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:M5"/>
+  </ignoredErrors>
 </worksheet>
 </file>
--- a/rules/NEW-RULE/positive/01/data/new-rule-positive-01.xlsx
+++ b/rules/NEW-RULE/positive/01/data/new-rule-positive-01.xlsx
@@ -6,7 +6,7 @@
     <sheet name="Library" sheetId="1" r:id="rId1"/>
     <sheet name="Datasets" sheetId="2" r:id="rId2"/>
     <sheet name="dm.xpt" sheetId="3" r:id="rId3"/>
-    <sheet name="ae.xpt" sheetId="4" r:id="rId4"/>
+    <sheet name="pc.xpt" sheetId="4" r:id="rId4"/>
   </sheets>
 </workbook>
 </file>
@@ -36,7 +36,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
   <numFmts count="0"/>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -53,23 +57,6 @@
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
       <i/>
     </font>
     <font>
@@ -78,7 +65,7 @@
       <i/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="4">
     <fill>
       <patternFill patternType="none">
         <bgColor/>
@@ -86,21 +73,6 @@
     </fill>
     <fill>
       <patternFill patternType="gray125">
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <bgColor/>
       </patternFill>
     </fill>
@@ -136,17 +108,14 @@
   <cellStyleXfs>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="1" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -481,18 +450,18 @@
   <dimension ref="A1:B2"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="str">
+      <c r="A1" s="3" t="str">
         <v>Product</v>
       </c>
-      <c r="B1" s="2" t="str">
+      <c r="B1" s="3" t="str">
         <v>Version</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="str">
+      <c r="A2" s="3" t="str">
         <v>sdtmig</v>
       </c>
-      <c r="B2" s="2" t="str">
+      <c r="B2" s="3" t="str">
         <v>3-4</v>
       </c>
     </row>
@@ -508,27 +477,27 @@
   <dimension ref="A1:B3"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="str">
+      <c r="A1" s="3" t="str">
         <v>Filename</v>
       </c>
-      <c r="B1" s="2" t="str">
+      <c r="B1" s="3" t="str">
         <v>Label</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="str">
+      <c r="A2" s="3" t="str">
         <v>dm.xpt</v>
       </c>
-      <c r="B2" s="2" t="str">
+      <c r="B2" s="3" t="str">
         <v>Demographics</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="str">
-        <v>ae.xpt</v>
-      </c>
-      <c r="B3" s="2" t="str">
-        <v>Adverse Events</v>
+      <c r="A3" s="3" t="str">
+        <v>pc.xpt</v>
+      </c>
+      <c r="B3" s="3" t="str">
+        <v>Pharmacokinetic Concentrations</v>
       </c>
     </row>
   </sheetData>
@@ -543,642 +512,642 @@
   <dimension ref="A1:Z8"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="str">
+      <c r="A1" s="4" t="str">
         <v>STUDYID</v>
       </c>
-      <c r="B1" s="3" t="str">
+      <c r="B1" s="4" t="str">
         <v>DOMAIN</v>
       </c>
-      <c r="C1" s="3" t="str">
+      <c r="C1" s="4" t="str">
         <v>USUBJID</v>
       </c>
-      <c r="D1" s="3" t="str">
+      <c r="D1" s="4" t="str">
         <v>SUBJID</v>
       </c>
-      <c r="E1" s="3" t="str">
+      <c r="E1" s="4" t="str">
         <v>RFSTDTC</v>
       </c>
-      <c r="F1" s="3" t="str">
+      <c r="F1" s="4" t="str">
         <v>RFENDTC</v>
       </c>
-      <c r="G1" s="3" t="str">
+      <c r="G1" s="4" t="str">
         <v>RFXSTDTC</v>
       </c>
-      <c r="H1" s="3" t="str">
+      <c r="H1" s="4" t="str">
         <v>RFXENDTC</v>
       </c>
-      <c r="I1" s="3" t="str">
+      <c r="I1" s="4" t="str">
         <v>RFICDTC</v>
       </c>
-      <c r="J1" s="3" t="str">
+      <c r="J1" s="4" t="str">
         <v>RFPENDTC</v>
       </c>
-      <c r="K1" s="3" t="str">
+      <c r="K1" s="4" t="str">
         <v>DTHDTC</v>
       </c>
       <c r="L1" s="4" t="str">
         <v>DTHFL</v>
       </c>
-      <c r="M1" s="3" t="str">
+      <c r="M1" s="4" t="str">
         <v>SITEID</v>
       </c>
-      <c r="N1" s="3" t="str">
+      <c r="N1" s="4" t="str">
         <v>BRTHDTC</v>
       </c>
-      <c r="O1" s="3" t="str">
+      <c r="O1" s="4" t="str">
         <v>AGE</v>
       </c>
-      <c r="P1" s="3" t="str">
+      <c r="P1" s="4" t="str">
         <v>AGEU</v>
       </c>
-      <c r="Q1" s="3" t="str">
+      <c r="Q1" s="4" t="str">
         <v>SEX</v>
       </c>
-      <c r="R1" s="3" t="str">
+      <c r="R1" s="4" t="str">
         <v>RACE</v>
       </c>
-      <c r="S1" s="3" t="str">
+      <c r="S1" s="4" t="str">
         <v>ETHNIC</v>
       </c>
-      <c r="T1" s="3" t="str">
+      <c r="T1" s="4" t="str">
         <v>ARMCD</v>
       </c>
-      <c r="U1" s="3" t="str">
+      <c r="U1" s="4" t="str">
         <v>ARM</v>
       </c>
-      <c r="V1" s="3" t="str">
+      <c r="V1" s="4" t="str">
         <v>ACTARMCD</v>
       </c>
-      <c r="W1" s="3" t="str">
+      <c r="W1" s="4" t="str">
         <v>ACTARM</v>
       </c>
-      <c r="X1" s="3" t="str">
+      <c r="X1" s="4" t="str">
         <v>ARMNRS</v>
       </c>
-      <c r="Y1" s="3" t="str">
+      <c r="Y1" s="4" t="str">
         <v>ACTARMUD</v>
       </c>
-      <c r="Z1" s="3" t="str">
+      <c r="Z1" s="4" t="str">
         <v>COUNTRY</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="str">
+      <c r="A2" s="3" t="str">
         <v>Study Identifier</v>
       </c>
-      <c r="B2" s="5" t="str">
+      <c r="B2" s="3" t="str">
         <v>Domain Abbreviation</v>
       </c>
-      <c r="C2" s="6" t="str">
+      <c r="C2" s="3" t="str">
         <v>Unique Subject Identifier</v>
       </c>
-      <c r="D2" s="6" t="str">
+      <c r="D2" s="3" t="str">
         <v>Subject Identifier for the Study</v>
       </c>
-      <c r="E2" s="6" t="str">
+      <c r="E2" s="3" t="str">
         <v>Subject Reference Start Date/Time</v>
       </c>
-      <c r="F2" s="6" t="str">
+      <c r="F2" s="3" t="str">
         <v>Subject Reference End Date/Time</v>
       </c>
-      <c r="G2" s="6" t="str">
+      <c r="G2" s="3" t="str">
         <v>Date/Time of First Study Treatment</v>
       </c>
-      <c r="H2" s="6" t="str">
+      <c r="H2" s="3" t="str">
         <v>Date/Time of Last Study Treatment</v>
       </c>
-      <c r="I2" s="6" t="str">
+      <c r="I2" s="3" t="str">
         <v>Date/Time of Informed Consent</v>
       </c>
-      <c r="J2" s="6" t="str">
+      <c r="J2" s="3" t="str">
         <v>Date/Time of End of Participation</v>
       </c>
-      <c r="K2" s="6" t="str">
+      <c r="K2" s="3" t="str">
         <v>Date/Time of Death</v>
       </c>
-      <c r="L2" s="6" t="str">
+      <c r="L2" s="3" t="str">
         <v>Subject Death Flag</v>
       </c>
-      <c r="M2" s="6" t="str">
+      <c r="M2" s="3" t="str">
         <v>Study Site Identifier</v>
       </c>
-      <c r="N2" s="6" t="str">
+      <c r="N2" s="3" t="str">
         <v>Date/Time of Birth</v>
       </c>
-      <c r="O2" s="6" t="str">
+      <c r="O2" s="3" t="str">
         <v>Age</v>
       </c>
-      <c r="P2" s="6" t="str">
+      <c r="P2" s="3" t="str">
         <v>Age Units</v>
       </c>
-      <c r="Q2" s="6" t="str">
+      <c r="Q2" s="3" t="str">
         <v>Sex</v>
       </c>
-      <c r="R2" s="6" t="str">
+      <c r="R2" s="3" t="str">
         <v>Race</v>
       </c>
-      <c r="S2" s="6" t="str">
+      <c r="S2" s="3" t="str">
         <v>Ethnicity</v>
       </c>
-      <c r="T2" s="6" t="str">
+      <c r="T2" s="3" t="str">
         <v>Planned Arm Code</v>
       </c>
-      <c r="U2" s="6" t="str">
+      <c r="U2" s="3" t="str">
         <v>Description of Planned Arm</v>
       </c>
-      <c r="V2" s="6" t="str">
+      <c r="V2" s="3" t="str">
         <v>Actual Arm Code</v>
       </c>
-      <c r="W2" s="6" t="str">
+      <c r="W2" s="3" t="str">
         <v>Description of Actual Arm</v>
       </c>
-      <c r="X2" s="6" t="str">
+      <c r="X2" s="3" t="str">
         <v>Reason Arm and/or Actual Arm is Null</v>
       </c>
-      <c r="Y2" s="6" t="str">
+      <c r="Y2" s="3" t="str">
         <v>Description of Unplanned Actual Arm</v>
       </c>
-      <c r="Z2" s="6" t="str">
+      <c r="Z2" s="3" t="str">
         <v>Country</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="B3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="C3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="D3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="E3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="F3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="G3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="H3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="I3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="J3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="K3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="L3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="M3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="N3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="O3" s="7" t="str">
+      <c r="A3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="B3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="C3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="D3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="E3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="F3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="G3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="H3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="I3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="J3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="K3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="L3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="M3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="N3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="O3" s="3" t="str">
         <v>Num</v>
       </c>
-      <c r="P3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="Q3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="R3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="S3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="T3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="U3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="V3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="W3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="X3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="Y3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="Z3" s="7" t="str">
+      <c r="P3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="Q3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="R3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="S3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="T3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="U3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="V3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="W3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="X3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="Y3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="Z3" s="3" t="str">
         <v>Char</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6">
+      <c r="A4" s="3">
         <v>12</v>
       </c>
-      <c r="B4" s="6">
+      <c r="B4" s="3">
         <v>2</v>
       </c>
-      <c r="C4" s="6">
+      <c r="C4" s="3">
         <v>8</v>
       </c>
-      <c r="D4" s="6">
+      <c r="D4" s="3">
         <v>4</v>
       </c>
-      <c r="E4" s="6">
+      <c r="E4" s="3">
         <v>10</v>
       </c>
-      <c r="F4" s="6">
+      <c r="F4" s="3">
         <v>10</v>
       </c>
-      <c r="G4" s="6">
+      <c r="G4" s="3">
         <v>10</v>
       </c>
-      <c r="H4" s="6">
+      <c r="H4" s="3">
         <v>10</v>
       </c>
-      <c r="I4" s="6">
+      <c r="I4" s="3">
         <v>10</v>
       </c>
-      <c r="J4" s="6">
+      <c r="J4" s="3">
         <v>10</v>
       </c>
-      <c r="K4" s="6">
+      <c r="K4" s="3">
         <v>10</v>
       </c>
-      <c r="L4" s="6">
+      <c r="L4" s="3">
         <v>1</v>
       </c>
-      <c r="M4" s="6">
+      <c r="M4" s="3">
         <v>3</v>
       </c>
-      <c r="N4" s="6">
+      <c r="N4" s="3">
         <v>10</v>
       </c>
-      <c r="O4" s="6">
+      <c r="O4" s="3">
         <v>8</v>
       </c>
-      <c r="P4" s="6">
+      <c r="P4" s="3">
         <v>5</v>
       </c>
-      <c r="Q4" s="6">
+      <c r="Q4" s="3">
         <v>1</v>
       </c>
-      <c r="R4" s="6">
+      <c r="R4" s="3">
         <v>41</v>
       </c>
-      <c r="S4" s="6">
+      <c r="S4" s="3">
         <v>22</v>
       </c>
-      <c r="T4" s="6">
+      <c r="T4" s="3">
         <v>8</v>
       </c>
-      <c r="U4" s="6">
+      <c r="U4" s="3">
         <v>28</v>
       </c>
-      <c r="V4" s="6">
+      <c r="V4" s="3">
         <v>8</v>
       </c>
-      <c r="W4" s="6">
+      <c r="W4" s="3">
         <v>28</v>
       </c>
-      <c r="X4" s="6">
+      <c r="X4" s="3">
         <v>14</v>
       </c>
-      <c r="Y4" s="6">
+      <c r="Y4" s="3">
         <v>200</v>
       </c>
-      <c r="Z4" s="6">
+      <c r="Z4" s="3">
         <v>3</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="str">
+      <c r="A5" s="3" t="str">
         <v>CDISCPILOT01</v>
       </c>
-      <c r="B5" s="7" t="str">
+      <c r="B5" s="3" t="str">
         <v>DM</v>
       </c>
-      <c r="C5" s="7" t="str">
+      <c r="C5" s="3" t="str">
         <v>CDISC001</v>
       </c>
-      <c r="D5" s="7">
+      <c r="D5" s="3">
         <v>1115</v>
       </c>
-      <c r="E5" s="7" t="str">
+      <c r="E5" s="3" t="str">
         <v>2018-05-17T09:35</v>
       </c>
-      <c r="F5" s="7" t="str">
+      <c r="F5" s="3" t="str">
         <v>2018-08-03</v>
       </c>
-      <c r="G5" s="7" t="str">
+      <c r="G5" s="3" t="str">
         <v>2018-05-17T09:35</v>
       </c>
-      <c r="H5" s="7" t="str">
+      <c r="H5" s="3" t="str">
         <v>2018-08-03</v>
       </c>
-      <c r="I5" s="7" t="str">
+      <c r="I5" s="3" t="str">
         <v>2018-04-26</v>
       </c>
-      <c r="J5" s="7" t="str">
+      <c r="J5" s="3" t="str">
         <v>2018-08-22</v>
       </c>
-      <c r="K5" s="7" t="str">
+      <c r="K5" s="3" t="str">
         <v>2018-08-22</v>
       </c>
-      <c r="L5" s="6" t="str">
+      <c r="L5" s="3" t="str">
         <v>Y</v>
       </c>
-      <c r="M5" s="7">
+      <c r="M5" s="3">
         <v>701</v>
       </c>
-      <c r="N5" s="7" t="str">
+      <c r="N5" s="3" t="str">
         <v>1947-07-24T00:00:00.000Z</v>
       </c>
-      <c r="O5" s="7" t="str">
+      <c r="O5" s="3" t="str">
         <v>70</v>
       </c>
-      <c r="P5" s="7" t="str">
+      <c r="P5" s="3" t="str">
         <v>YEARS</v>
       </c>
-      <c r="Q5" s="7" t="str">
+      <c r="Q5" s="3" t="str">
         <v>M</v>
       </c>
-      <c r="R5" s="7" t="str">
+      <c r="R5" s="3" t="str">
         <v>WHITE</v>
       </c>
-      <c r="S5" s="7" t="str">
+      <c r="S5" s="3" t="str">
         <v>NOT HISPANIC OR LATINO</v>
       </c>
-      <c r="T5" s="7" t="str">
+      <c r="T5" s="3" t="str">
         <v>A</v>
       </c>
-      <c r="U5" s="7" t="str">
+      <c r="U5" s="3" t="str">
         <v>Drug A</v>
       </c>
-      <c r="V5" s="7" t="str">
+      <c r="V5" s="3" t="str">
         <v>A</v>
       </c>
-      <c r="W5" s="7" t="str">
+      <c r="W5" s="3" t="str">
         <v>Drug A</v>
       </c>
-      <c r="X5" s="7" t="str">
+      <c r="X5" s="3" t="str">
         <v/>
       </c>
-      <c r="Y5" s="7" t="str">
+      <c r="Y5" s="3" t="str">
         <v/>
       </c>
-      <c r="Z5" s="7" t="str">
+      <c r="Z5" s="3" t="str">
         <v>AUS</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="str">
+      <c r="A6" s="3" t="str">
         <v>CDISCPILOT01</v>
       </c>
-      <c r="B6" s="6" t="str">
+      <c r="B6" s="3" t="str">
         <v>DM</v>
       </c>
-      <c r="C6" s="6" t="str">
+      <c r="C6" s="3" t="str">
         <v>CDISC002</v>
       </c>
-      <c r="D6" s="6">
+      <c r="D6" s="3">
         <v>1211</v>
       </c>
-      <c r="E6" s="6" t="str">
+      <c r="E6" s="3" t="str">
         <v>2018-05-24T12:00</v>
       </c>
-      <c r="F6" s="6" t="str">
+      <c r="F6" s="3" t="str">
         <v>2018-11-06</v>
       </c>
-      <c r="G6" s="6" t="str">
+      <c r="G6" s="3" t="str">
         <v>2018-05-24T12:00</v>
       </c>
-      <c r="H6" s="6" t="str">
+      <c r="H6" s="3" t="str">
         <v>2018-11-06</v>
       </c>
-      <c r="I6" s="6" t="str">
+      <c r="I6" s="3" t="str">
         <v>2018-05-07</v>
       </c>
-      <c r="J6" s="6" t="str">
+      <c r="J6" s="3" t="str">
         <v>2019-02-04</v>
       </c>
-      <c r="K6" s="6" t="str">
+      <c r="K6" s="3" t="str">
         <v>2019-02-04</v>
       </c>
-      <c r="L6" s="6" t="str">
+      <c r="L6" s="3" t="str">
         <v>Y</v>
       </c>
-      <c r="M6" s="6">
+      <c r="M6" s="3">
         <v>701</v>
       </c>
-      <c r="N6" s="6" t="str">
+      <c r="N6" s="3" t="str">
         <v>1905-05-08T00:00:00.000Z</v>
       </c>
-      <c r="O6" s="6" t="str">
+      <c r="O6" s="3" t="str">
         <v>78</v>
       </c>
-      <c r="P6" s="6" t="str">
+      <c r="P6" s="3" t="str">
         <v>YEARS</v>
       </c>
-      <c r="Q6" s="6" t="str">
+      <c r="Q6" s="3" t="str">
         <v>M</v>
       </c>
-      <c r="R6" s="6" t="str">
+      <c r="R6" s="3" t="str">
         <v>WHITE</v>
       </c>
-      <c r="S6" s="6" t="str">
+      <c r="S6" s="3" t="str">
         <v>NOT HISPANIC OR LATINO</v>
       </c>
-      <c r="T6" s="6" t="str">
+      <c r="T6" s="3" t="str">
         <v>P</v>
       </c>
-      <c r="U6" s="6" t="str">
+      <c r="U6" s="3" t="str">
         <v>Placebo</v>
       </c>
-      <c r="V6" s="6" t="str">
+      <c r="V6" s="3" t="str">
         <v>P</v>
       </c>
-      <c r="W6" s="6" t="str">
+      <c r="W6" s="3" t="str">
         <v>Placebo</v>
       </c>
-      <c r="X6" s="6" t="str">
+      <c r="X6" s="3" t="str">
         <v/>
       </c>
-      <c r="Y6" s="6" t="str">
+      <c r="Y6" s="3" t="str">
         <v/>
       </c>
-      <c r="Z6" s="6" t="str">
+      <c r="Z6" s="3" t="str">
         <v>AUS</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="str">
+      <c r="A7" s="3" t="str">
         <v>CDISCPILOT01</v>
       </c>
-      <c r="B7" s="7" t="str">
+      <c r="B7" s="3" t="str">
         <v>DM</v>
       </c>
-      <c r="C7" s="7" t="str">
+      <c r="C7" s="3" t="str">
         <v>CDISC003</v>
       </c>
-      <c r="D7" s="7">
+      <c r="D7" s="3">
         <v>1302</v>
       </c>
-      <c r="E7" s="7" t="str">
+      <c r="E7" s="3" t="str">
         <v>2006-01-16</v>
       </c>
-      <c r="F7" s="7" t="str">
+      <c r="F7" s="3" t="str">
         <v>2006-03-19</v>
       </c>
-      <c r="G7" s="7" t="str">
+      <c r="G7" s="3" t="str">
         <v>2006-01-16</v>
       </c>
-      <c r="H7" s="7" t="str">
+      <c r="H7" s="3" t="str">
         <v>2006-03-19</v>
       </c>
-      <c r="I7" s="7" t="str">
+      <c r="I7" s="3" t="str">
         <v>2006-01-02</v>
       </c>
-      <c r="J7" s="7" t="str">
+      <c r="J7" s="3" t="str">
         <v>2006-03-19</v>
       </c>
-      <c r="K7" s="7" t="str">
+      <c r="K7" s="3" t="str">
         <v/>
       </c>
-      <c r="L7" s="6" t="str">
+      <c r="L7" s="3" t="str">
         <v>Y</v>
       </c>
-      <c r="M7" s="7">
+      <c r="M7" s="3">
         <v>701</v>
       </c>
-      <c r="N7" s="7" t="str">
+      <c r="N7" s="3" t="str">
         <v>1944-06-16T00:00:00.000Z</v>
       </c>
-      <c r="O7" s="7" t="str">
+      <c r="O7" s="3" t="str">
         <v>74</v>
       </c>
-      <c r="P7" s="7" t="str">
+      <c r="P7" s="3" t="str">
         <v>YEARS</v>
       </c>
-      <c r="Q7" s="7" t="str">
+      <c r="Q7" s="3" t="str">
         <v>M</v>
       </c>
-      <c r="R7" s="7" t="str">
+      <c r="R7" s="3" t="str">
         <v>WHITE</v>
       </c>
-      <c r="S7" s="7" t="str">
+      <c r="S7" s="3" t="str">
         <v>NOT HISPANIC OR LATINO</v>
       </c>
-      <c r="T7" s="7" t="str">
+      <c r="T7" s="3" t="str">
         <v>B</v>
       </c>
-      <c r="U7" s="7" t="str">
+      <c r="U7" s="3" t="str">
         <v>Drug B</v>
       </c>
-      <c r="V7" s="7" t="str">
+      <c r="V7" s="3" t="str">
         <v>B</v>
       </c>
-      <c r="W7" s="7" t="str">
+      <c r="W7" s="3" t="str">
         <v>Drug B</v>
       </c>
-      <c r="X7" s="7" t="str">
+      <c r="X7" s="3" t="str">
         <v/>
       </c>
-      <c r="Y7" s="7" t="str">
+      <c r="Y7" s="3" t="str">
         <v/>
       </c>
-      <c r="Z7" s="7" t="str">
+      <c r="Z7" s="3" t="str">
         <v>CZE</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="str">
+      <c r="A8" s="3" t="str">
         <v>CDISCPILOT01</v>
       </c>
-      <c r="B8" s="7" t="str">
+      <c r="B8" s="3" t="str">
         <v>DM</v>
       </c>
-      <c r="C8" s="7" t="str">
+      <c r="C8" s="3" t="str">
         <v>CDISC004</v>
       </c>
-      <c r="D8" s="7">
+      <c r="D8" s="3">
         <v>1402</v>
       </c>
-      <c r="E8" s="7" t="str">
+      <c r="E8" s="3" t="str">
         <v>2018-07-16T09:15</v>
       </c>
-      <c r="F8" s="7" t="str">
+      <c r="F8" s="3" t="str">
         <v>2018-11-06T14:00</v>
       </c>
-      <c r="G8" s="7" t="str">
+      <c r="G8" s="3" t="str">
         <v>2018-07-16T09:15</v>
       </c>
-      <c r="H8" s="7" t="str">
+      <c r="H8" s="3" t="str">
         <v>2018-11-06T14:00</v>
       </c>
-      <c r="I8" s="7" t="str">
+      <c r="I8" s="3" t="str">
         <v>2018-06-27</v>
       </c>
-      <c r="J8" s="7" t="str">
+      <c r="J8" s="3" t="str">
         <v>2018-12-11</v>
       </c>
-      <c r="K8" s="7" t="str">
+      <c r="K8" s="3" t="str">
         <v/>
       </c>
-      <c r="L8" s="6" t="str">
+      <c r="L8" s="3" t="str">
         <v/>
       </c>
-      <c r="M8" s="7">
+      <c r="M8" s="3">
         <v>701</v>
       </c>
-      <c r="N8" s="7" t="str">
+      <c r="N8" s="3" t="str">
         <v>1905-04-16T00:00:00.000Z</v>
       </c>
-      <c r="O8" s="7" t="str">
+      <c r="O8" s="3" t="str">
         <v>68</v>
       </c>
-      <c r="P8" s="7" t="str">
+      <c r="P8" s="3" t="str">
         <v>YEARS</v>
       </c>
-      <c r="Q8" s="7" t="str">
+      <c r="Q8" s="3" t="str">
         <v>F</v>
       </c>
-      <c r="R8" s="7" t="str">
+      <c r="R8" s="3" t="str">
         <v>WHITE</v>
       </c>
-      <c r="S8" s="7" t="str">
+      <c r="S8" s="3" t="str">
         <v>HISPANIC OR LATINO</v>
       </c>
-      <c r="T8" s="7" t="str">
+      <c r="T8" s="3" t="str">
         <v>B</v>
       </c>
-      <c r="U8" s="7" t="str">
+      <c r="U8" s="3" t="str">
         <v>Drug B</v>
       </c>
-      <c r="V8" s="7" t="str">
+      <c r="V8" s="3" t="str">
         <v>B</v>
       </c>
-      <c r="W8" s="7" t="str">
+      <c r="W8" s="3" t="str">
         <v>Drug B</v>
       </c>
-      <c r="X8" s="7" t="str">
+      <c r="X8" s="3" t="str">
         <v/>
       </c>
-      <c r="Y8" s="7" t="str">
+      <c r="Y8" s="3" t="str">
         <v/>
       </c>
-      <c r="Z8" s="7" t="str">
+      <c r="Z8" s="3" t="str">
         <v>CAN</v>
       </c>
     </row>
@@ -1194,72 +1163,72 @@
   <dimension ref="A1:D5"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="str">
+      <c r="A1" s="4" t="str">
         <v>STUDYID</v>
       </c>
-      <c r="B1" s="3" t="str">
+      <c r="B1" s="4" t="str">
         <v>DOMAIN</v>
       </c>
-      <c r="C1" s="3" t="str">
+      <c r="C1" s="4" t="str">
         <v>USUBJID</v>
       </c>
-      <c r="D1" s="3" t="str">
-        <v>AESEQ</v>
+      <c r="D1" s="4" t="str">
+        <v>PCSEQ</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="8" t="str">
+      <c r="A2" s="5" t="str">
         <v>Study Identifier</v>
       </c>
-      <c r="B2" s="8" t="str">
+      <c r="B2" s="6" t="str">
         <v>Domain Abbreviation</v>
       </c>
-      <c r="C2" s="9" t="str">
+      <c r="C2" s="6" t="str">
         <v>Unique Subject Identifier</v>
       </c>
-      <c r="D2" s="9" t="str">
+      <c r="D2" s="6" t="str">
         <v>Sequence Number</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="9" t="str">
-        <v>Char</v>
-      </c>
-      <c r="B3" s="9" t="str">
-        <v>Char</v>
-      </c>
-      <c r="C3" s="9" t="str">
-        <v>Char</v>
-      </c>
-      <c r="D3" s="9" t="str">
+      <c r="A3" s="6" t="str">
+        <v>Char</v>
+      </c>
+      <c r="B3" s="6" t="str">
+        <v>Char</v>
+      </c>
+      <c r="C3" s="6" t="str">
+        <v>Char</v>
+      </c>
+      <c r="D3" s="6" t="str">
         <v>Num</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="9" t="str">
+      <c r="A4" s="6" t="str">
         <v>10</v>
       </c>
-      <c r="B4" s="9" t="str">
+      <c r="B4" s="6" t="str">
         <v>2</v>
       </c>
-      <c r="C4" s="9" t="str">
+      <c r="C4" s="6" t="str">
         <v>14</v>
       </c>
-      <c r="D4" s="9" t="str">
+      <c r="D4" s="6" t="str">
         <v>8</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="str">
+      <c r="A5" s="3" t="str">
         <v>CDISCPILOT01</v>
       </c>
-      <c r="B5" s="7" t="str">
-        <v>AE</v>
-      </c>
-      <c r="C5" s="7" t="str">
+      <c r="B5" s="3" t="str">
+        <v>PC</v>
+      </c>
+      <c r="C5" s="3" t="str">
         <v>CDISC-TEST-001</v>
       </c>
-      <c r="D5" s="7" t="str">
+      <c r="D5" s="3" t="str">
         <v>1</v>
       </c>
     </row>

--- a/rules/NEW-RULE/positive/01/data/new-rule-positive-01.xlsx
+++ b/rules/NEW-RULE/positive/01/data/new-rule-positive-01.xlsx
@@ -6,7 +6,7 @@
     <sheet name="Library" sheetId="1" r:id="rId1"/>
     <sheet name="Datasets" sheetId="2" r:id="rId2"/>
     <sheet name="dm.xpt" sheetId="3" r:id="rId3"/>
-    <sheet name="ae.xpt" sheetId="4" r:id="rId4"/>
+    <sheet name="pp.xpt" sheetId="4" r:id="rId4"/>
   </sheets>
 </workbook>
 </file>
@@ -36,7 +36,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
   <numFmts count="0"/>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -53,23 +57,6 @@
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
       <i/>
     </font>
     <font>
@@ -78,7 +65,7 @@
       <i/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="4">
     <fill>
       <patternFill patternType="none">
         <bgColor/>
@@ -86,21 +73,6 @@
     </fill>
     <fill>
       <patternFill patternType="gray125">
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <bgColor/>
       </patternFill>
     </fill>
@@ -136,17 +108,14 @@
   <cellStyleXfs>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="1" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -481,18 +450,18 @@
   <dimension ref="A1:B2"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="str">
+      <c r="A1" s="3" t="str">
         <v>Product</v>
       </c>
-      <c r="B1" s="2" t="str">
+      <c r="B1" s="3" t="str">
         <v>Version</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="str">
+      <c r="A2" s="3" t="str">
         <v>sdtmig</v>
       </c>
-      <c r="B2" s="2" t="str">
+      <c r="B2" s="3" t="str">
         <v>3-4</v>
       </c>
     </row>
@@ -508,27 +477,27 @@
   <dimension ref="A1:B3"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="str">
+      <c r="A1" s="3" t="str">
         <v>Filename</v>
       </c>
-      <c r="B1" s="2" t="str">
+      <c r="B1" s="3" t="str">
         <v>Label</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="str">
+      <c r="A2" s="3" t="str">
         <v>dm.xpt</v>
       </c>
-      <c r="B2" s="2" t="str">
+      <c r="B2" s="3" t="str">
         <v>Demographics</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="str">
-        <v>ae.xpt</v>
-      </c>
-      <c r="B3" s="2" t="str">
-        <v>Adverse Events</v>
+      <c r="A3" s="3" t="str">
+        <v>pp.xpt</v>
+      </c>
+      <c r="B3" s="3" t="str">
+        <v>Pharmacokinetics Parameters</v>
       </c>
     </row>
   </sheetData>
@@ -543,642 +512,642 @@
   <dimension ref="A1:Z8"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="str">
+      <c r="A1" s="4" t="str">
         <v>STUDYID</v>
       </c>
-      <c r="B1" s="3" t="str">
+      <c r="B1" s="4" t="str">
         <v>DOMAIN</v>
       </c>
-      <c r="C1" s="3" t="str">
+      <c r="C1" s="4" t="str">
         <v>USUBJID</v>
       </c>
-      <c r="D1" s="3" t="str">
+      <c r="D1" s="4" t="str">
         <v>SUBJID</v>
       </c>
-      <c r="E1" s="3" t="str">
+      <c r="E1" s="4" t="str">
         <v>RFSTDTC</v>
       </c>
-      <c r="F1" s="3" t="str">
+      <c r="F1" s="4" t="str">
         <v>RFENDTC</v>
       </c>
-      <c r="G1" s="3" t="str">
+      <c r="G1" s="4" t="str">
         <v>RFXSTDTC</v>
       </c>
-      <c r="H1" s="3" t="str">
+      <c r="H1" s="4" t="str">
         <v>RFXENDTC</v>
       </c>
-      <c r="I1" s="3" t="str">
+      <c r="I1" s="4" t="str">
         <v>RFICDTC</v>
       </c>
-      <c r="J1" s="3" t="str">
+      <c r="J1" s="4" t="str">
         <v>RFPENDTC</v>
       </c>
-      <c r="K1" s="3" t="str">
+      <c r="K1" s="4" t="str">
         <v>DTHDTC</v>
       </c>
       <c r="L1" s="4" t="str">
         <v>DTHFL</v>
       </c>
-      <c r="M1" s="3" t="str">
+      <c r="M1" s="4" t="str">
         <v>SITEID</v>
       </c>
-      <c r="N1" s="3" t="str">
+      <c r="N1" s="4" t="str">
         <v>BRTHDTC</v>
       </c>
-      <c r="O1" s="3" t="str">
+      <c r="O1" s="4" t="str">
         <v>AGE</v>
       </c>
-      <c r="P1" s="3" t="str">
+      <c r="P1" s="4" t="str">
         <v>AGEU</v>
       </c>
-      <c r="Q1" s="3" t="str">
+      <c r="Q1" s="4" t="str">
         <v>SEX</v>
       </c>
-      <c r="R1" s="3" t="str">
+      <c r="R1" s="4" t="str">
         <v>RACE</v>
       </c>
-      <c r="S1" s="3" t="str">
+      <c r="S1" s="4" t="str">
         <v>ETHNIC</v>
       </c>
-      <c r="T1" s="3" t="str">
+      <c r="T1" s="4" t="str">
         <v>ARMCD</v>
       </c>
-      <c r="U1" s="3" t="str">
+      <c r="U1" s="4" t="str">
         <v>ARM</v>
       </c>
-      <c r="V1" s="3" t="str">
+      <c r="V1" s="4" t="str">
         <v>ACTARMCD</v>
       </c>
-      <c r="W1" s="3" t="str">
+      <c r="W1" s="4" t="str">
         <v>ACTARM</v>
       </c>
-      <c r="X1" s="3" t="str">
+      <c r="X1" s="4" t="str">
         <v>ARMNRS</v>
       </c>
-      <c r="Y1" s="3" t="str">
+      <c r="Y1" s="4" t="str">
         <v>ACTARMUD</v>
       </c>
-      <c r="Z1" s="3" t="str">
+      <c r="Z1" s="4" t="str">
         <v>COUNTRY</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="str">
+      <c r="A2" s="3" t="str">
         <v>Study Identifier</v>
       </c>
-      <c r="B2" s="5" t="str">
+      <c r="B2" s="3" t="str">
         <v>Domain Abbreviation</v>
       </c>
-      <c r="C2" s="6" t="str">
+      <c r="C2" s="3" t="str">
         <v>Unique Subject Identifier</v>
       </c>
-      <c r="D2" s="6" t="str">
+      <c r="D2" s="3" t="str">
         <v>Subject Identifier for the Study</v>
       </c>
-      <c r="E2" s="6" t="str">
+      <c r="E2" s="3" t="str">
         <v>Subject Reference Start Date/Time</v>
       </c>
-      <c r="F2" s="6" t="str">
+      <c r="F2" s="3" t="str">
         <v>Subject Reference End Date/Time</v>
       </c>
-      <c r="G2" s="6" t="str">
+      <c r="G2" s="3" t="str">
         <v>Date/Time of First Study Treatment</v>
       </c>
-      <c r="H2" s="6" t="str">
+      <c r="H2" s="3" t="str">
         <v>Date/Time of Last Study Treatment</v>
       </c>
-      <c r="I2" s="6" t="str">
+      <c r="I2" s="3" t="str">
         <v>Date/Time of Informed Consent</v>
       </c>
-      <c r="J2" s="6" t="str">
+      <c r="J2" s="3" t="str">
         <v>Date/Time of End of Participation</v>
       </c>
-      <c r="K2" s="6" t="str">
+      <c r="K2" s="3" t="str">
         <v>Date/Time of Death</v>
       </c>
-      <c r="L2" s="6" t="str">
+      <c r="L2" s="3" t="str">
         <v>Subject Death Flag</v>
       </c>
-      <c r="M2" s="6" t="str">
+      <c r="M2" s="3" t="str">
         <v>Study Site Identifier</v>
       </c>
-      <c r="N2" s="6" t="str">
+      <c r="N2" s="3" t="str">
         <v>Date/Time of Birth</v>
       </c>
-      <c r="O2" s="6" t="str">
+      <c r="O2" s="3" t="str">
         <v>Age</v>
       </c>
-      <c r="P2" s="6" t="str">
+      <c r="P2" s="3" t="str">
         <v>Age Units</v>
       </c>
-      <c r="Q2" s="6" t="str">
+      <c r="Q2" s="3" t="str">
         <v>Sex</v>
       </c>
-      <c r="R2" s="6" t="str">
+      <c r="R2" s="3" t="str">
         <v>Race</v>
       </c>
-      <c r="S2" s="6" t="str">
+      <c r="S2" s="3" t="str">
         <v>Ethnicity</v>
       </c>
-      <c r="T2" s="6" t="str">
+      <c r="T2" s="3" t="str">
         <v>Planned Arm Code</v>
       </c>
-      <c r="U2" s="6" t="str">
+      <c r="U2" s="3" t="str">
         <v>Description of Planned Arm</v>
       </c>
-      <c r="V2" s="6" t="str">
+      <c r="V2" s="3" t="str">
         <v>Actual Arm Code</v>
       </c>
-      <c r="W2" s="6" t="str">
+      <c r="W2" s="3" t="str">
         <v>Description of Actual Arm</v>
       </c>
-      <c r="X2" s="6" t="str">
+      <c r="X2" s="3" t="str">
         <v>Reason Arm and/or Actual Arm is Null</v>
       </c>
-      <c r="Y2" s="6" t="str">
+      <c r="Y2" s="3" t="str">
         <v>Description of Unplanned Actual Arm</v>
       </c>
-      <c r="Z2" s="6" t="str">
+      <c r="Z2" s="3" t="str">
         <v>Country</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="B3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="C3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="D3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="E3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="F3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="G3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="H3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="I3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="J3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="K3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="L3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="M3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="N3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="O3" s="7" t="str">
+      <c r="A3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="B3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="C3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="D3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="E3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="F3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="G3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="H3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="I3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="J3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="K3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="L3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="M3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="N3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="O3" s="3" t="str">
         <v>Num</v>
       </c>
-      <c r="P3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="Q3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="R3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="S3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="T3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="U3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="V3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="W3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="X3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="Y3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="Z3" s="7" t="str">
+      <c r="P3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="Q3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="R3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="S3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="T3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="U3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="V3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="W3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="X3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="Y3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="Z3" s="3" t="str">
         <v>Char</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6">
+      <c r="A4" s="3">
         <v>12</v>
       </c>
-      <c r="B4" s="6">
+      <c r="B4" s="3">
         <v>2</v>
       </c>
-      <c r="C4" s="6">
+      <c r="C4" s="3">
         <v>8</v>
       </c>
-      <c r="D4" s="6">
+      <c r="D4" s="3">
         <v>4</v>
       </c>
-      <c r="E4" s="6">
+      <c r="E4" s="3">
         <v>10</v>
       </c>
-      <c r="F4" s="6">
+      <c r="F4" s="3">
         <v>10</v>
       </c>
-      <c r="G4" s="6">
+      <c r="G4" s="3">
         <v>10</v>
       </c>
-      <c r="H4" s="6">
+      <c r="H4" s="3">
         <v>10</v>
       </c>
-      <c r="I4" s="6">
+      <c r="I4" s="3">
         <v>10</v>
       </c>
-      <c r="J4" s="6">
+      <c r="J4" s="3">
         <v>10</v>
       </c>
-      <c r="K4" s="6">
+      <c r="K4" s="3">
         <v>10</v>
       </c>
-      <c r="L4" s="6">
+      <c r="L4" s="3">
         <v>1</v>
       </c>
-      <c r="M4" s="6">
+      <c r="M4" s="3">
         <v>3</v>
       </c>
-      <c r="N4" s="6">
+      <c r="N4" s="3">
         <v>10</v>
       </c>
-      <c r="O4" s="6">
+      <c r="O4" s="3">
         <v>8</v>
       </c>
-      <c r="P4" s="6">
+      <c r="P4" s="3">
         <v>5</v>
       </c>
-      <c r="Q4" s="6">
+      <c r="Q4" s="3">
         <v>1</v>
       </c>
-      <c r="R4" s="6">
+      <c r="R4" s="3">
         <v>41</v>
       </c>
-      <c r="S4" s="6">
+      <c r="S4" s="3">
         <v>22</v>
       </c>
-      <c r="T4" s="6">
+      <c r="T4" s="3">
         <v>8</v>
       </c>
-      <c r="U4" s="6">
+      <c r="U4" s="3">
         <v>28</v>
       </c>
-      <c r="V4" s="6">
+      <c r="V4" s="3">
         <v>8</v>
       </c>
-      <c r="W4" s="6">
+      <c r="W4" s="3">
         <v>28</v>
       </c>
-      <c r="X4" s="6">
+      <c r="X4" s="3">
         <v>14</v>
       </c>
-      <c r="Y4" s="6">
+      <c r="Y4" s="3">
         <v>200</v>
       </c>
-      <c r="Z4" s="6">
+      <c r="Z4" s="3">
         <v>3</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="str">
+      <c r="A5" s="3" t="str">
         <v>CDISCPILOT01</v>
       </c>
-      <c r="B5" s="7" t="str">
+      <c r="B5" s="3" t="str">
         <v>DM</v>
       </c>
-      <c r="C5" s="7" t="str">
+      <c r="C5" s="3" t="str">
         <v>CDISC001</v>
       </c>
-      <c r="D5" s="7">
+      <c r="D5" s="3">
         <v>1115</v>
       </c>
-      <c r="E5" s="7" t="str">
+      <c r="E5" s="3" t="str">
         <v>2018-05-17T09:35</v>
       </c>
-      <c r="F5" s="7" t="str">
+      <c r="F5" s="3" t="str">
         <v>2018-08-03</v>
       </c>
-      <c r="G5" s="7" t="str">
+      <c r="G5" s="3" t="str">
         <v>2018-05-17T09:35</v>
       </c>
-      <c r="H5" s="7" t="str">
+      <c r="H5" s="3" t="str">
         <v>2018-08-03</v>
       </c>
-      <c r="I5" s="7" t="str">
+      <c r="I5" s="3" t="str">
         <v>2018-04-26</v>
       </c>
-      <c r="J5" s="7" t="str">
+      <c r="J5" s="3" t="str">
         <v>2018-08-22</v>
       </c>
-      <c r="K5" s="7" t="str">
+      <c r="K5" s="3" t="str">
         <v>2018-08-22</v>
       </c>
-      <c r="L5" s="6" t="str">
+      <c r="L5" s="3" t="str">
         <v>Y</v>
       </c>
-      <c r="M5" s="7">
+      <c r="M5" s="3">
         <v>701</v>
       </c>
-      <c r="N5" s="7" t="str">
+      <c r="N5" s="3" t="str">
         <v>1947-07-24T00:00:00.000Z</v>
       </c>
-      <c r="O5" s="7" t="str">
+      <c r="O5" s="3" t="str">
         <v>70</v>
       </c>
-      <c r="P5" s="7" t="str">
+      <c r="P5" s="3" t="str">
         <v>YEARS</v>
       </c>
-      <c r="Q5" s="7" t="str">
+      <c r="Q5" s="3" t="str">
         <v>M</v>
       </c>
-      <c r="R5" s="7" t="str">
+      <c r="R5" s="3" t="str">
         <v>WHITE</v>
       </c>
-      <c r="S5" s="7" t="str">
+      <c r="S5" s="3" t="str">
         <v>NOT HISPANIC OR LATINO</v>
       </c>
-      <c r="T5" s="7" t="str">
+      <c r="T5" s="3" t="str">
         <v>A</v>
       </c>
-      <c r="U5" s="7" t="str">
+      <c r="U5" s="3" t="str">
         <v>Drug A</v>
       </c>
-      <c r="V5" s="7" t="str">
+      <c r="V5" s="3" t="str">
         <v>A</v>
       </c>
-      <c r="W5" s="7" t="str">
+      <c r="W5" s="3" t="str">
         <v>Drug A</v>
       </c>
-      <c r="X5" s="7" t="str">
+      <c r="X5" s="3" t="str">
         <v/>
       </c>
-      <c r="Y5" s="7" t="str">
+      <c r="Y5" s="3" t="str">
         <v/>
       </c>
-      <c r="Z5" s="7" t="str">
+      <c r="Z5" s="3" t="str">
         <v>AUS</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="str">
+      <c r="A6" s="3" t="str">
         <v>CDISCPILOT01</v>
       </c>
-      <c r="B6" s="6" t="str">
+      <c r="B6" s="3" t="str">
         <v>DM</v>
       </c>
-      <c r="C6" s="6" t="str">
+      <c r="C6" s="3" t="str">
         <v>CDISC002</v>
       </c>
-      <c r="D6" s="6">
+      <c r="D6" s="3">
         <v>1211</v>
       </c>
-      <c r="E6" s="6" t="str">
+      <c r="E6" s="3" t="str">
         <v>2018-05-24T12:00</v>
       </c>
-      <c r="F6" s="6" t="str">
+      <c r="F6" s="3" t="str">
         <v>2018-11-06</v>
       </c>
-      <c r="G6" s="6" t="str">
+      <c r="G6" s="3" t="str">
         <v>2018-05-24T12:00</v>
       </c>
-      <c r="H6" s="6" t="str">
+      <c r="H6" s="3" t="str">
         <v>2018-11-06</v>
       </c>
-      <c r="I6" s="6" t="str">
+      <c r="I6" s="3" t="str">
         <v>2018-05-07</v>
       </c>
-      <c r="J6" s="6" t="str">
+      <c r="J6" s="3" t="str">
         <v>2019-02-04</v>
       </c>
-      <c r="K6" s="6" t="str">
+      <c r="K6" s="3" t="str">
         <v>2019-02-04</v>
       </c>
-      <c r="L6" s="6" t="str">
+      <c r="L6" s="3" t="str">
         <v>Y</v>
       </c>
-      <c r="M6" s="6">
+      <c r="M6" s="3">
         <v>701</v>
       </c>
-      <c r="N6" s="6" t="str">
+      <c r="N6" s="3" t="str">
         <v>1905-05-08T00:00:00.000Z</v>
       </c>
-      <c r="O6" s="6" t="str">
+      <c r="O6" s="3" t="str">
         <v>78</v>
       </c>
-      <c r="P6" s="6" t="str">
+      <c r="P6" s="3" t="str">
         <v>YEARS</v>
       </c>
-      <c r="Q6" s="6" t="str">
+      <c r="Q6" s="3" t="str">
         <v>M</v>
       </c>
-      <c r="R6" s="6" t="str">
+      <c r="R6" s="3" t="str">
         <v>WHITE</v>
       </c>
-      <c r="S6" s="6" t="str">
+      <c r="S6" s="3" t="str">
         <v>NOT HISPANIC OR LATINO</v>
       </c>
-      <c r="T6" s="6" t="str">
+      <c r="T6" s="3" t="str">
         <v>P</v>
       </c>
-      <c r="U6" s="6" t="str">
+      <c r="U6" s="3" t="str">
         <v>Placebo</v>
       </c>
-      <c r="V6" s="6" t="str">
+      <c r="V6" s="3" t="str">
         <v>P</v>
       </c>
-      <c r="W6" s="6" t="str">
+      <c r="W6" s="3" t="str">
         <v>Placebo</v>
       </c>
-      <c r="X6" s="6" t="str">
+      <c r="X6" s="3" t="str">
         <v/>
       </c>
-      <c r="Y6" s="6" t="str">
+      <c r="Y6" s="3" t="str">
         <v/>
       </c>
-      <c r="Z6" s="6" t="str">
+      <c r="Z6" s="3" t="str">
         <v>AUS</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="str">
+      <c r="A7" s="3" t="str">
         <v>CDISCPILOT01</v>
       </c>
-      <c r="B7" s="7" t="str">
+      <c r="B7" s="3" t="str">
         <v>DM</v>
       </c>
-      <c r="C7" s="7" t="str">
+      <c r="C7" s="3" t="str">
         <v>CDISC003</v>
       </c>
-      <c r="D7" s="7">
+      <c r="D7" s="3">
         <v>1302</v>
       </c>
-      <c r="E7" s="7" t="str">
+      <c r="E7" s="3" t="str">
         <v>2006-01-16</v>
       </c>
-      <c r="F7" s="7" t="str">
+      <c r="F7" s="3" t="str">
         <v>2006-03-19</v>
       </c>
-      <c r="G7" s="7" t="str">
+      <c r="G7" s="3" t="str">
         <v>2006-01-16</v>
       </c>
-      <c r="H7" s="7" t="str">
+      <c r="H7" s="3" t="str">
         <v>2006-03-19</v>
       </c>
-      <c r="I7" s="7" t="str">
+      <c r="I7" s="3" t="str">
         <v>2006-01-02</v>
       </c>
-      <c r="J7" s="7" t="str">
+      <c r="J7" s="3" t="str">
         <v>2006-03-19</v>
       </c>
-      <c r="K7" s="7" t="str">
+      <c r="K7" s="3" t="str">
         <v/>
       </c>
-      <c r="L7" s="6" t="str">
+      <c r="L7" s="3" t="str">
         <v>Y</v>
       </c>
-      <c r="M7" s="7">
+      <c r="M7" s="3">
         <v>701</v>
       </c>
-      <c r="N7" s="7" t="str">
+      <c r="N7" s="3" t="str">
         <v>1944-06-16T00:00:00.000Z</v>
       </c>
-      <c r="O7" s="7" t="str">
+      <c r="O7" s="3" t="str">
         <v>74</v>
       </c>
-      <c r="P7" s="7" t="str">
+      <c r="P7" s="3" t="str">
         <v>YEARS</v>
       </c>
-      <c r="Q7" s="7" t="str">
+      <c r="Q7" s="3" t="str">
         <v>M</v>
       </c>
-      <c r="R7" s="7" t="str">
+      <c r="R7" s="3" t="str">
         <v>WHITE</v>
       </c>
-      <c r="S7" s="7" t="str">
+      <c r="S7" s="3" t="str">
         <v>NOT HISPANIC OR LATINO</v>
       </c>
-      <c r="T7" s="7" t="str">
+      <c r="T7" s="3" t="str">
         <v>B</v>
       </c>
-      <c r="U7" s="7" t="str">
+      <c r="U7" s="3" t="str">
         <v>Drug B</v>
       </c>
-      <c r="V7" s="7" t="str">
+      <c r="V7" s="3" t="str">
         <v>B</v>
       </c>
-      <c r="W7" s="7" t="str">
+      <c r="W7" s="3" t="str">
         <v>Drug B</v>
       </c>
-      <c r="X7" s="7" t="str">
+      <c r="X7" s="3" t="str">
         <v/>
       </c>
-      <c r="Y7" s="7" t="str">
+      <c r="Y7" s="3" t="str">
         <v/>
       </c>
-      <c r="Z7" s="7" t="str">
+      <c r="Z7" s="3" t="str">
         <v>CZE</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="str">
+      <c r="A8" s="3" t="str">
         <v>CDISCPILOT01</v>
       </c>
-      <c r="B8" s="7" t="str">
+      <c r="B8" s="3" t="str">
         <v>DM</v>
       </c>
-      <c r="C8" s="7" t="str">
+      <c r="C8" s="3" t="str">
         <v>CDISC004</v>
       </c>
-      <c r="D8" s="7">
+      <c r="D8" s="3">
         <v>1402</v>
       </c>
-      <c r="E8" s="7" t="str">
+      <c r="E8" s="3" t="str">
         <v>2018-07-16T09:15</v>
       </c>
-      <c r="F8" s="7" t="str">
+      <c r="F8" s="3" t="str">
         <v>2018-11-06T14:00</v>
       </c>
-      <c r="G8" s="7" t="str">
+      <c r="G8" s="3" t="str">
         <v>2018-07-16T09:15</v>
       </c>
-      <c r="H8" s="7" t="str">
+      <c r="H8" s="3" t="str">
         <v>2018-11-06T14:00</v>
       </c>
-      <c r="I8" s="7" t="str">
+      <c r="I8" s="3" t="str">
         <v>2018-06-27</v>
       </c>
-      <c r="J8" s="7" t="str">
+      <c r="J8" s="3" t="str">
         <v>2018-12-11</v>
       </c>
-      <c r="K8" s="7" t="str">
+      <c r="K8" s="3" t="str">
         <v/>
       </c>
-      <c r="L8" s="6" t="str">
+      <c r="L8" s="3" t="str">
         <v/>
       </c>
-      <c r="M8" s="7">
+      <c r="M8" s="3">
         <v>701</v>
       </c>
-      <c r="N8" s="7" t="str">
+      <c r="N8" s="3" t="str">
         <v>1905-04-16T00:00:00.000Z</v>
       </c>
-      <c r="O8" s="7" t="str">
+      <c r="O8" s="3" t="str">
         <v>68</v>
       </c>
-      <c r="P8" s="7" t="str">
+      <c r="P8" s="3" t="str">
         <v>YEARS</v>
       </c>
-      <c r="Q8" s="7" t="str">
+      <c r="Q8" s="3" t="str">
         <v>F</v>
       </c>
-      <c r="R8" s="7" t="str">
+      <c r="R8" s="3" t="str">
         <v>WHITE</v>
       </c>
-      <c r="S8" s="7" t="str">
+      <c r="S8" s="3" t="str">
         <v>HISPANIC OR LATINO</v>
       </c>
-      <c r="T8" s="7" t="str">
+      <c r="T8" s="3" t="str">
         <v>B</v>
       </c>
-      <c r="U8" s="7" t="str">
+      <c r="U8" s="3" t="str">
         <v>Drug B</v>
       </c>
-      <c r="V8" s="7" t="str">
+      <c r="V8" s="3" t="str">
         <v>B</v>
       </c>
-      <c r="W8" s="7" t="str">
+      <c r="W8" s="3" t="str">
         <v>Drug B</v>
       </c>
-      <c r="X8" s="7" t="str">
+      <c r="X8" s="3" t="str">
         <v/>
       </c>
-      <c r="Y8" s="7" t="str">
+      <c r="Y8" s="3" t="str">
         <v/>
       </c>
-      <c r="Z8" s="7" t="str">
+      <c r="Z8" s="3" t="str">
         <v>CAN</v>
       </c>
     </row>
@@ -1194,72 +1163,72 @@
   <dimension ref="A1:D5"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="str">
+      <c r="A1" s="4" t="str">
         <v>STUDYID</v>
       </c>
-      <c r="B1" s="3" t="str">
+      <c r="B1" s="4" t="str">
         <v>DOMAIN</v>
       </c>
-      <c r="C1" s="3" t="str">
+      <c r="C1" s="4" t="str">
         <v>USUBJID</v>
       </c>
-      <c r="D1" s="3" t="str">
-        <v>AESEQ</v>
+      <c r="D1" s="4" t="str">
+        <v>PPSEQ</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="8" t="str">
+      <c r="A2" s="5" t="str">
         <v>Study Identifier</v>
       </c>
-      <c r="B2" s="8" t="str">
+      <c r="B2" s="6" t="str">
         <v>Domain Abbreviation</v>
       </c>
-      <c r="C2" s="9" t="str">
+      <c r="C2" s="6" t="str">
         <v>Unique Subject Identifier</v>
       </c>
-      <c r="D2" s="9" t="str">
+      <c r="D2" s="6" t="str">
         <v>Sequence Number</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="9" t="str">
-        <v>Char</v>
-      </c>
-      <c r="B3" s="9" t="str">
-        <v>Char</v>
-      </c>
-      <c r="C3" s="9" t="str">
-        <v>Char</v>
-      </c>
-      <c r="D3" s="9" t="str">
+      <c r="A3" s="6" t="str">
+        <v>Char</v>
+      </c>
+      <c r="B3" s="6" t="str">
+        <v>Char</v>
+      </c>
+      <c r="C3" s="6" t="str">
+        <v>Char</v>
+      </c>
+      <c r="D3" s="6" t="str">
         <v>Num</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="9" t="str">
+      <c r="A4" s="6" t="str">
         <v>10</v>
       </c>
-      <c r="B4" s="9" t="str">
+      <c r="B4" s="6" t="str">
         <v>2</v>
       </c>
-      <c r="C4" s="9" t="str">
+      <c r="C4" s="6" t="str">
         <v>14</v>
       </c>
-      <c r="D4" s="9" t="str">
+      <c r="D4" s="6" t="str">
         <v>8</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="str">
+      <c r="A5" s="3" t="str">
         <v>CDISCPILOT01</v>
       </c>
-      <c r="B5" s="7" t="str">
-        <v>AE</v>
-      </c>
-      <c r="C5" s="7" t="str">
+      <c r="B5" s="3" t="str">
+        <v>PP</v>
+      </c>
+      <c r="C5" s="3" t="str">
         <v>CDISC-TEST-001</v>
       </c>
-      <c r="D5" s="7" t="str">
+      <c r="D5" s="3" t="str">
         <v>1</v>
       </c>
     </row>

--- a/rules/NEW-RULE/positive/01/data/new-rule-positive-01.xlsx
+++ b/rules/NEW-RULE/positive/01/data/new-rule-positive-01.xlsx
@@ -6,7 +6,7 @@
     <sheet name="Library" sheetId="1" r:id="rId1"/>
     <sheet name="Datasets" sheetId="2" r:id="rId2"/>
     <sheet name="dm.xpt" sheetId="3" r:id="rId3"/>
-    <sheet name="ae.xpt" sheetId="4" r:id="rId4"/>
+    <sheet name="sv.xpt" sheetId="4" r:id="rId4"/>
   </sheets>
 </workbook>
 </file>
@@ -36,7 +36,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
   <numFmts count="0"/>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -53,23 +57,6 @@
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
       <i/>
     </font>
     <font>
@@ -78,7 +65,7 @@
       <i/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="4">
     <fill>
       <patternFill patternType="none">
         <bgColor/>
@@ -86,21 +73,6 @@
     </fill>
     <fill>
       <patternFill patternType="gray125">
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <bgColor/>
       </patternFill>
     </fill>
@@ -136,17 +108,14 @@
   <cellStyleXfs>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="1" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -481,18 +450,18 @@
   <dimension ref="A1:B2"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="str">
+      <c r="A1" s="3" t="str">
         <v>Product</v>
       </c>
-      <c r="B1" s="2" t="str">
+      <c r="B1" s="3" t="str">
         <v>Version</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="str">
+      <c r="A2" s="3" t="str">
         <v>sdtmig</v>
       </c>
-      <c r="B2" s="2" t="str">
+      <c r="B2" s="3" t="str">
         <v>3-4</v>
       </c>
     </row>
@@ -508,27 +477,27 @@
   <dimension ref="A1:B3"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="str">
+      <c r="A1" s="3" t="str">
         <v>Filename</v>
       </c>
-      <c r="B1" s="2" t="str">
+      <c r="B1" s="3" t="str">
         <v>Label</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="str">
+      <c r="A2" s="3" t="str">
         <v>dm.xpt</v>
       </c>
-      <c r="B2" s="2" t="str">
+      <c r="B2" s="3" t="str">
         <v>Demographics</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="str">
-        <v>ae.xpt</v>
-      </c>
-      <c r="B3" s="2" t="str">
-        <v>Adverse Events</v>
+      <c r="A3" s="3" t="str">
+        <v>sv.xpt</v>
+      </c>
+      <c r="B3" s="3" t="str">
+        <v>Subject Visits</v>
       </c>
     </row>
   </sheetData>
@@ -543,642 +512,642 @@
   <dimension ref="A1:Z8"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="str">
+      <c r="A1" s="4" t="str">
         <v>STUDYID</v>
       </c>
-      <c r="B1" s="3" t="str">
+      <c r="B1" s="4" t="str">
         <v>DOMAIN</v>
       </c>
-      <c r="C1" s="3" t="str">
+      <c r="C1" s="4" t="str">
         <v>USUBJID</v>
       </c>
-      <c r="D1" s="3" t="str">
+      <c r="D1" s="4" t="str">
         <v>SUBJID</v>
       </c>
-      <c r="E1" s="3" t="str">
+      <c r="E1" s="4" t="str">
         <v>RFSTDTC</v>
       </c>
-      <c r="F1" s="3" t="str">
+      <c r="F1" s="4" t="str">
         <v>RFENDTC</v>
       </c>
-      <c r="G1" s="3" t="str">
+      <c r="G1" s="4" t="str">
         <v>RFXSTDTC</v>
       </c>
-      <c r="H1" s="3" t="str">
+      <c r="H1" s="4" t="str">
         <v>RFXENDTC</v>
       </c>
-      <c r="I1" s="3" t="str">
+      <c r="I1" s="4" t="str">
         <v>RFICDTC</v>
       </c>
-      <c r="J1" s="3" t="str">
+      <c r="J1" s="4" t="str">
         <v>RFPENDTC</v>
       </c>
-      <c r="K1" s="3" t="str">
+      <c r="K1" s="4" t="str">
         <v>DTHDTC</v>
       </c>
       <c r="L1" s="4" t="str">
         <v>DTHFL</v>
       </c>
-      <c r="M1" s="3" t="str">
+      <c r="M1" s="4" t="str">
         <v>SITEID</v>
       </c>
-      <c r="N1" s="3" t="str">
+      <c r="N1" s="4" t="str">
         <v>BRTHDTC</v>
       </c>
-      <c r="O1" s="3" t="str">
+      <c r="O1" s="4" t="str">
         <v>AGE</v>
       </c>
-      <c r="P1" s="3" t="str">
+      <c r="P1" s="4" t="str">
         <v>AGEU</v>
       </c>
-      <c r="Q1" s="3" t="str">
+      <c r="Q1" s="4" t="str">
         <v>SEX</v>
       </c>
-      <c r="R1" s="3" t="str">
+      <c r="R1" s="4" t="str">
         <v>RACE</v>
       </c>
-      <c r="S1" s="3" t="str">
+      <c r="S1" s="4" t="str">
         <v>ETHNIC</v>
       </c>
-      <c r="T1" s="3" t="str">
+      <c r="T1" s="4" t="str">
         <v>ARMCD</v>
       </c>
-      <c r="U1" s="3" t="str">
+      <c r="U1" s="4" t="str">
         <v>ARM</v>
       </c>
-      <c r="V1" s="3" t="str">
+      <c r="V1" s="4" t="str">
         <v>ACTARMCD</v>
       </c>
-      <c r="W1" s="3" t="str">
+      <c r="W1" s="4" t="str">
         <v>ACTARM</v>
       </c>
-      <c r="X1" s="3" t="str">
+      <c r="X1" s="4" t="str">
         <v>ARMNRS</v>
       </c>
-      <c r="Y1" s="3" t="str">
+      <c r="Y1" s="4" t="str">
         <v>ACTARMUD</v>
       </c>
-      <c r="Z1" s="3" t="str">
+      <c r="Z1" s="4" t="str">
         <v>COUNTRY</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="str">
+      <c r="A2" s="3" t="str">
         <v>Study Identifier</v>
       </c>
-      <c r="B2" s="5" t="str">
+      <c r="B2" s="3" t="str">
         <v>Domain Abbreviation</v>
       </c>
-      <c r="C2" s="6" t="str">
+      <c r="C2" s="3" t="str">
         <v>Unique Subject Identifier</v>
       </c>
-      <c r="D2" s="6" t="str">
+      <c r="D2" s="3" t="str">
         <v>Subject Identifier for the Study</v>
       </c>
-      <c r="E2" s="6" t="str">
+      <c r="E2" s="3" t="str">
         <v>Subject Reference Start Date/Time</v>
       </c>
-      <c r="F2" s="6" t="str">
+      <c r="F2" s="3" t="str">
         <v>Subject Reference End Date/Time</v>
       </c>
-      <c r="G2" s="6" t="str">
+      <c r="G2" s="3" t="str">
         <v>Date/Time of First Study Treatment</v>
       </c>
-      <c r="H2" s="6" t="str">
+      <c r="H2" s="3" t="str">
         <v>Date/Time of Last Study Treatment</v>
       </c>
-      <c r="I2" s="6" t="str">
+      <c r="I2" s="3" t="str">
         <v>Date/Time of Informed Consent</v>
       </c>
-      <c r="J2" s="6" t="str">
+      <c r="J2" s="3" t="str">
         <v>Date/Time of End of Participation</v>
       </c>
-      <c r="K2" s="6" t="str">
+      <c r="K2" s="3" t="str">
         <v>Date/Time of Death</v>
       </c>
-      <c r="L2" s="6" t="str">
+      <c r="L2" s="3" t="str">
         <v>Subject Death Flag</v>
       </c>
-      <c r="M2" s="6" t="str">
+      <c r="M2" s="3" t="str">
         <v>Study Site Identifier</v>
       </c>
-      <c r="N2" s="6" t="str">
+      <c r="N2" s="3" t="str">
         <v>Date/Time of Birth</v>
       </c>
-      <c r="O2" s="6" t="str">
+      <c r="O2" s="3" t="str">
         <v>Age</v>
       </c>
-      <c r="P2" s="6" t="str">
+      <c r="P2" s="3" t="str">
         <v>Age Units</v>
       </c>
-      <c r="Q2" s="6" t="str">
+      <c r="Q2" s="3" t="str">
         <v>Sex</v>
       </c>
-      <c r="R2" s="6" t="str">
+      <c r="R2" s="3" t="str">
         <v>Race</v>
       </c>
-      <c r="S2" s="6" t="str">
+      <c r="S2" s="3" t="str">
         <v>Ethnicity</v>
       </c>
-      <c r="T2" s="6" t="str">
+      <c r="T2" s="3" t="str">
         <v>Planned Arm Code</v>
       </c>
-      <c r="U2" s="6" t="str">
+      <c r="U2" s="3" t="str">
         <v>Description of Planned Arm</v>
       </c>
-      <c r="V2" s="6" t="str">
+      <c r="V2" s="3" t="str">
         <v>Actual Arm Code</v>
       </c>
-      <c r="W2" s="6" t="str">
+      <c r="W2" s="3" t="str">
         <v>Description of Actual Arm</v>
       </c>
-      <c r="X2" s="6" t="str">
+      <c r="X2" s="3" t="str">
         <v>Reason Arm and/or Actual Arm is Null</v>
       </c>
-      <c r="Y2" s="6" t="str">
+      <c r="Y2" s="3" t="str">
         <v>Description of Unplanned Actual Arm</v>
       </c>
-      <c r="Z2" s="6" t="str">
+      <c r="Z2" s="3" t="str">
         <v>Country</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="B3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="C3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="D3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="E3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="F3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="G3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="H3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="I3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="J3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="K3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="L3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="M3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="N3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="O3" s="7" t="str">
+      <c r="A3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="B3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="C3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="D3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="E3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="F3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="G3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="H3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="I3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="J3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="K3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="L3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="M3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="N3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="O3" s="3" t="str">
         <v>Num</v>
       </c>
-      <c r="P3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="Q3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="R3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="S3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="T3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="U3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="V3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="W3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="X3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="Y3" s="7" t="str">
-        <v>Char</v>
-      </c>
-      <c r="Z3" s="7" t="str">
+      <c r="P3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="Q3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="R3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="S3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="T3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="U3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="V3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="W3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="X3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="Y3" s="3" t="str">
+        <v>Char</v>
+      </c>
+      <c r="Z3" s="3" t="str">
         <v>Char</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6">
+      <c r="A4" s="3">
         <v>12</v>
       </c>
-      <c r="B4" s="6">
+      <c r="B4" s="3">
         <v>2</v>
       </c>
-      <c r="C4" s="6">
+      <c r="C4" s="3">
         <v>8</v>
       </c>
-      <c r="D4" s="6">
+      <c r="D4" s="3">
         <v>4</v>
       </c>
-      <c r="E4" s="6">
+      <c r="E4" s="3">
         <v>10</v>
       </c>
-      <c r="F4" s="6">
+      <c r="F4" s="3">
         <v>10</v>
       </c>
-      <c r="G4" s="6">
+      <c r="G4" s="3">
         <v>10</v>
       </c>
-      <c r="H4" s="6">
+      <c r="H4" s="3">
         <v>10</v>
       </c>
-      <c r="I4" s="6">
+      <c r="I4" s="3">
         <v>10</v>
       </c>
-      <c r="J4" s="6">
+      <c r="J4" s="3">
         <v>10</v>
       </c>
-      <c r="K4" s="6">
+      <c r="K4" s="3">
         <v>10</v>
       </c>
-      <c r="L4" s="6">
+      <c r="L4" s="3">
         <v>1</v>
       </c>
-      <c r="M4" s="6">
+      <c r="M4" s="3">
         <v>3</v>
       </c>
-      <c r="N4" s="6">
+      <c r="N4" s="3">
         <v>10</v>
       </c>
-      <c r="O4" s="6">
+      <c r="O4" s="3">
         <v>8</v>
       </c>
-      <c r="P4" s="6">
+      <c r="P4" s="3">
         <v>5</v>
       </c>
-      <c r="Q4" s="6">
+      <c r="Q4" s="3">
         <v>1</v>
       </c>
-      <c r="R4" s="6">
+      <c r="R4" s="3">
         <v>41</v>
       </c>
-      <c r="S4" s="6">
+      <c r="S4" s="3">
         <v>22</v>
       </c>
-      <c r="T4" s="6">
+      <c r="T4" s="3">
         <v>8</v>
       </c>
-      <c r="U4" s="6">
+      <c r="U4" s="3">
         <v>28</v>
       </c>
-      <c r="V4" s="6">
+      <c r="V4" s="3">
         <v>8</v>
       </c>
-      <c r="W4" s="6">
+      <c r="W4" s="3">
         <v>28</v>
       </c>
-      <c r="X4" s="6">
+      <c r="X4" s="3">
         <v>14</v>
       </c>
-      <c r="Y4" s="6">
+      <c r="Y4" s="3">
         <v>200</v>
       </c>
-      <c r="Z4" s="6">
+      <c r="Z4" s="3">
         <v>3</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="str">
+      <c r="A5" s="3" t="str">
         <v>CDISCPILOT01</v>
       </c>
-      <c r="B5" s="7" t="str">
+      <c r="B5" s="3" t="str">
         <v>DM</v>
       </c>
-      <c r="C5" s="7" t="str">
+      <c r="C5" s="3" t="str">
         <v>CDISC001</v>
       </c>
-      <c r="D5" s="7">
+      <c r="D5" s="3">
         <v>1115</v>
       </c>
-      <c r="E5" s="7" t="str">
+      <c r="E5" s="3" t="str">
         <v>2018-05-17T09:35</v>
       </c>
-      <c r="F5" s="7" t="str">
+      <c r="F5" s="3" t="str">
         <v>2018-08-03</v>
       </c>
-      <c r="G5" s="7" t="str">
+      <c r="G5" s="3" t="str">
         <v>2018-05-17T09:35</v>
       </c>
-      <c r="H5" s="7" t="str">
+      <c r="H5" s="3" t="str">
         <v>2018-08-03</v>
       </c>
-      <c r="I5" s="7" t="str">
+      <c r="I5" s="3" t="str">
         <v>2018-04-26</v>
       </c>
-      <c r="J5" s="7" t="str">
+      <c r="J5" s="3" t="str">
         <v>2018-08-22</v>
       </c>
-      <c r="K5" s="7" t="str">
+      <c r="K5" s="3" t="str">
         <v>2018-08-22</v>
       </c>
-      <c r="L5" s="6" t="str">
+      <c r="L5" s="3" t="str">
         <v>Y</v>
       </c>
-      <c r="M5" s="7">
+      <c r="M5" s="3">
         <v>701</v>
       </c>
-      <c r="N5" s="7" t="str">
+      <c r="N5" s="3" t="str">
         <v>1947-07-24T00:00:00.000Z</v>
       </c>
-      <c r="O5" s="7" t="str">
+      <c r="O5" s="3" t="str">
         <v>70</v>
       </c>
-      <c r="P5" s="7" t="str">
+      <c r="P5" s="3" t="str">
         <v>YEARS</v>
       </c>
-      <c r="Q5" s="7" t="str">
+      <c r="Q5" s="3" t="str">
         <v>M</v>
       </c>
-      <c r="R5" s="7" t="str">
+      <c r="R5" s="3" t="str">
         <v>WHITE</v>
       </c>
-      <c r="S5" s="7" t="str">
+      <c r="S5" s="3" t="str">
         <v>NOT HISPANIC OR LATINO</v>
       </c>
-      <c r="T5" s="7" t="str">
+      <c r="T5" s="3" t="str">
         <v>A</v>
       </c>
-      <c r="U5" s="7" t="str">
+      <c r="U5" s="3" t="str">
         <v>Drug A</v>
       </c>
-      <c r="V5" s="7" t="str">
+      <c r="V5" s="3" t="str">
         <v>A</v>
       </c>
-      <c r="W5" s="7" t="str">
+      <c r="W5" s="3" t="str">
         <v>Drug A</v>
       </c>
-      <c r="X5" s="7" t="str">
+      <c r="X5" s="3" t="str">
         <v/>
       </c>
-      <c r="Y5" s="7" t="str">
+      <c r="Y5" s="3" t="str">
         <v/>
       </c>
-      <c r="Z5" s="7" t="str">
+      <c r="Z5" s="3" t="str">
         <v>AUS</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="str">
+      <c r="A6" s="3" t="str">
         <v>CDISCPILOT01</v>
       </c>
-      <c r="B6" s="6" t="str">
+      <c r="B6" s="3" t="str">
         <v>DM</v>
       </c>
-      <c r="C6" s="6" t="str">
+      <c r="C6" s="3" t="str">
         <v>CDISC002</v>
       </c>
-      <c r="D6" s="6">
+      <c r="D6" s="3">
         <v>1211</v>
       </c>
-      <c r="E6" s="6" t="str">
+      <c r="E6" s="3" t="str">
         <v>2018-05-24T12:00</v>
       </c>
-      <c r="F6" s="6" t="str">
+      <c r="F6" s="3" t="str">
         <v>2018-11-06</v>
       </c>
-      <c r="G6" s="6" t="str">
+      <c r="G6" s="3" t="str">
         <v>2018-05-24T12:00</v>
       </c>
-      <c r="H6" s="6" t="str">
+      <c r="H6" s="3" t="str">
         <v>2018-11-06</v>
       </c>
-      <c r="I6" s="6" t="str">
+      <c r="I6" s="3" t="str">
         <v>2018-05-07</v>
       </c>
-      <c r="J6" s="6" t="str">
+      <c r="J6" s="3" t="str">
         <v>2019-02-04</v>
       </c>
-      <c r="K6" s="6" t="str">
+      <c r="K6" s="3" t="str">
         <v>2019-02-04</v>
       </c>
-      <c r="L6" s="6" t="str">
+      <c r="L6" s="3" t="str">
         <v>Y</v>
       </c>
-      <c r="M6" s="6">
+      <c r="M6" s="3">
         <v>701</v>
       </c>
-      <c r="N6" s="6" t="str">
+      <c r="N6" s="3" t="str">
         <v>1905-05-08T00:00:00.000Z</v>
       </c>
-      <c r="O6" s="6" t="str">
+      <c r="O6" s="3" t="str">
         <v>78</v>
       </c>
-      <c r="P6" s="6" t="str">
+      <c r="P6" s="3" t="str">
         <v>YEARS</v>
       </c>
-      <c r="Q6" s="6" t="str">
+      <c r="Q6" s="3" t="str">
         <v>M</v>
       </c>
-      <c r="R6" s="6" t="str">
+      <c r="R6" s="3" t="str">
         <v>WHITE</v>
       </c>
-      <c r="S6" s="6" t="str">
+      <c r="S6" s="3" t="str">
         <v>NOT HISPANIC OR LATINO</v>
       </c>
-      <c r="T6" s="6" t="str">
+      <c r="T6" s="3" t="str">
         <v>P</v>
       </c>
-      <c r="U6" s="6" t="str">
+      <c r="U6" s="3" t="str">
         <v>Placebo</v>
       </c>
-      <c r="V6" s="6" t="str">
+      <c r="V6" s="3" t="str">
         <v>P</v>
       </c>
-      <c r="W6" s="6" t="str">
+      <c r="W6" s="3" t="str">
         <v>Placebo</v>
       </c>
-      <c r="X6" s="6" t="str">
+      <c r="X6" s="3" t="str">
         <v/>
       </c>
-      <c r="Y6" s="6" t="str">
+      <c r="Y6" s="3" t="str">
         <v/>
       </c>
-      <c r="Z6" s="6" t="str">
+      <c r="Z6" s="3" t="str">
         <v>AUS</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="str">
+      <c r="A7" s="3" t="str">
         <v>CDISCPILOT01</v>
       </c>
-      <c r="B7" s="7" t="str">
+      <c r="B7" s="3" t="str">
         <v>DM</v>
       </c>
-      <c r="C7" s="7" t="str">
+      <c r="C7" s="3" t="str">
         <v>CDISC003</v>
       </c>
-      <c r="D7" s="7">
+      <c r="D7" s="3">
         <v>1302</v>
       </c>
-      <c r="E7" s="7" t="str">
+      <c r="E7" s="3" t="str">
         <v>2006-01-16</v>
       </c>
-      <c r="F7" s="7" t="str">
+      <c r="F7" s="3" t="str">
         <v>2006-03-19</v>
       </c>
-      <c r="G7" s="7" t="str">
+      <c r="G7" s="3" t="str">
         <v>2006-01-16</v>
       </c>
-      <c r="H7" s="7" t="str">
+      <c r="H7" s="3" t="str">
         <v>2006-03-19</v>
       </c>
-      <c r="I7" s="7" t="str">
+      <c r="I7" s="3" t="str">
         <v>2006-01-02</v>
       </c>
-      <c r="J7" s="7" t="str">
+      <c r="J7" s="3" t="str">
         <v>2006-03-19</v>
       </c>
-      <c r="K7" s="7" t="str">
+      <c r="K7" s="3" t="str">
         <v/>
       </c>
-      <c r="L7" s="6" t="str">
+      <c r="L7" s="3" t="str">
         <v>Y</v>
       </c>
-      <c r="M7" s="7">
+      <c r="M7" s="3">
         <v>701</v>
       </c>
-      <c r="N7" s="7" t="str">
+      <c r="N7" s="3" t="str">
         <v>1944-06-16T00:00:00.000Z</v>
       </c>
-      <c r="O7" s="7" t="str">
+      <c r="O7" s="3" t="str">
         <v>74</v>
       </c>
-      <c r="P7" s="7" t="str">
+      <c r="P7" s="3" t="str">
         <v>YEARS</v>
       </c>
-      <c r="Q7" s="7" t="str">
+      <c r="Q7" s="3" t="str">
         <v>M</v>
       </c>
-      <c r="R7" s="7" t="str">
+      <c r="R7" s="3" t="str">
         <v>WHITE</v>
       </c>
-      <c r="S7" s="7" t="str">
+      <c r="S7" s="3" t="str">
         <v>NOT HISPANIC OR LATINO</v>
       </c>
-      <c r="T7" s="7" t="str">
+      <c r="T7" s="3" t="str">
         <v>B</v>
       </c>
-      <c r="U7" s="7" t="str">
+      <c r="U7" s="3" t="str">
         <v>Drug B</v>
       </c>
-      <c r="V7" s="7" t="str">
+      <c r="V7" s="3" t="str">
         <v>B</v>
       </c>
-      <c r="W7" s="7" t="str">
+      <c r="W7" s="3" t="str">
         <v>Drug B</v>
       </c>
-      <c r="X7" s="7" t="str">
+      <c r="X7" s="3" t="str">
         <v/>
       </c>
-      <c r="Y7" s="7" t="str">
+      <c r="Y7" s="3" t="str">
         <v/>
       </c>
-      <c r="Z7" s="7" t="str">
+      <c r="Z7" s="3" t="str">
         <v>CZE</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="str">
+      <c r="A8" s="3" t="str">
         <v>CDISCPILOT01</v>
       </c>
-      <c r="B8" s="7" t="str">
+      <c r="B8" s="3" t="str">
         <v>DM</v>
       </c>
-      <c r="C8" s="7" t="str">
+      <c r="C8" s="3" t="str">
         <v>CDISC004</v>
       </c>
-      <c r="D8" s="7">
+      <c r="D8" s="3">
         <v>1402</v>
       </c>
-      <c r="E8" s="7" t="str">
+      <c r="E8" s="3" t="str">
         <v>2018-07-16T09:15</v>
       </c>
-      <c r="F8" s="7" t="str">
+      <c r="F8" s="3" t="str">
         <v>2018-11-06T14:00</v>
       </c>
-      <c r="G8" s="7" t="str">
+      <c r="G8" s="3" t="str">
         <v>2018-07-16T09:15</v>
       </c>
-      <c r="H8" s="7" t="str">
+      <c r="H8" s="3" t="str">
         <v>2018-11-06T14:00</v>
       </c>
-      <c r="I8" s="7" t="str">
+      <c r="I8" s="3" t="str">
         <v>2018-06-27</v>
       </c>
-      <c r="J8" s="7" t="str">
+      <c r="J8" s="3" t="str">
         <v>2018-12-11</v>
       </c>
-      <c r="K8" s="7" t="str">
+      <c r="K8" s="3" t="str">
         <v/>
       </c>
-      <c r="L8" s="6" t="str">
+      <c r="L8" s="3" t="str">
         <v/>
       </c>
-      <c r="M8" s="7">
+      <c r="M8" s="3">
         <v>701</v>
       </c>
-      <c r="N8" s="7" t="str">
+      <c r="N8" s="3" t="str">
         <v>1905-04-16T00:00:00.000Z</v>
       </c>
-      <c r="O8" s="7" t="str">
+      <c r="O8" s="3" t="str">
         <v>68</v>
       </c>
-      <c r="P8" s="7" t="str">
+      <c r="P8" s="3" t="str">
         <v>YEARS</v>
       </c>
-      <c r="Q8" s="7" t="str">
+      <c r="Q8" s="3" t="str">
         <v>F</v>
       </c>
-      <c r="R8" s="7" t="str">
+      <c r="R8" s="3" t="str">
         <v>WHITE</v>
       </c>
-      <c r="S8" s="7" t="str">
+      <c r="S8" s="3" t="str">
         <v>HISPANIC OR LATINO</v>
       </c>
-      <c r="T8" s="7" t="str">
+      <c r="T8" s="3" t="str">
         <v>B</v>
       </c>
-      <c r="U8" s="7" t="str">
+      <c r="U8" s="3" t="str">
         <v>Drug B</v>
       </c>
-      <c r="V8" s="7" t="str">
+      <c r="V8" s="3" t="str">
         <v>B</v>
       </c>
-      <c r="W8" s="7" t="str">
+      <c r="W8" s="3" t="str">
         <v>Drug B</v>
       </c>
-      <c r="X8" s="7" t="str">
+      <c r="X8" s="3" t="str">
         <v/>
       </c>
-      <c r="Y8" s="7" t="str">
+      <c r="Y8" s="3" t="str">
         <v/>
       </c>
-      <c r="Z8" s="7" t="str">
+      <c r="Z8" s="3" t="str">
         <v>CAN</v>
       </c>
     </row>
@@ -1194,72 +1163,72 @@
   <dimension ref="A1:D5"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="str">
+      <c r="A1" s="4" t="str">
         <v>STUDYID</v>
       </c>
-      <c r="B1" s="3" t="str">
+      <c r="B1" s="4" t="str">
         <v>DOMAIN</v>
       </c>
-      <c r="C1" s="3" t="str">
+      <c r="C1" s="4" t="str">
         <v>USUBJID</v>
       </c>
-      <c r="D1" s="3" t="str">
-        <v>AESEQ</v>
+      <c r="D1" s="4" t="str">
+        <v>SVSEQ</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="8" t="str">
+      <c r="A2" s="5" t="str">
         <v>Study Identifier</v>
       </c>
-      <c r="B2" s="8" t="str">
+      <c r="B2" s="6" t="str">
         <v>Domain Abbreviation</v>
       </c>
-      <c r="C2" s="9" t="str">
+      <c r="C2" s="6" t="str">
         <v>Unique Subject Identifier</v>
       </c>
-      <c r="D2" s="9" t="str">
+      <c r="D2" s="6" t="str">
         <v>Sequence Number</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="9" t="str">
-        <v>Char</v>
-      </c>
-      <c r="B3" s="9" t="str">
-        <v>Char</v>
-      </c>
-      <c r="C3" s="9" t="str">
-        <v>Char</v>
-      </c>
-      <c r="D3" s="9" t="str">
+      <c r="A3" s="6" t="str">
+        <v>Char</v>
+      </c>
+      <c r="B3" s="6" t="str">
+        <v>Char</v>
+      </c>
+      <c r="C3" s="6" t="str">
+        <v>Char</v>
+      </c>
+      <c r="D3" s="6" t="str">
         <v>Num</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="9" t="str">
+      <c r="A4" s="6" t="str">
         <v>10</v>
       </c>
-      <c r="B4" s="9" t="str">
+      <c r="B4" s="6" t="str">
         <v>2</v>
       </c>
-      <c r="C4" s="9" t="str">
+      <c r="C4" s="6" t="str">
         <v>14</v>
       </c>
-      <c r="D4" s="9" t="str">
+      <c r="D4" s="6" t="str">
         <v>8</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="str">
+      <c r="A5" s="3" t="str">
         <v>CDISCPILOT01</v>
       </c>
-      <c r="B5" s="7" t="str">
-        <v>AE</v>
-      </c>
-      <c r="C5" s="7" t="str">
+      <c r="B5" s="3" t="str">
+        <v>SV</v>
+      </c>
+      <c r="C5" s="3" t="str">
         <v>CDISC-TEST-001</v>
       </c>
-      <c r="D5" s="7" t="str">
+      <c r="D5" s="3" t="str">
         <v>1</v>
       </c>
     </row>

--- a/rules/NEW-RULE/positive/01/data/new-rule-positive-01.xlsx
+++ b/rules/NEW-RULE/positive/01/data/new-rule-positive-01.xlsx
@@ -1,41 +1,268 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11214"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/maxverisian/verisian/core-contributor/rules/NEW-RULE/positive/01/data/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52AC69A0-5975-4944-8E66-4062CC6EE8DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="0" yWindow="660" windowWidth="15040" windowHeight="9360" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
     <sheet name="Library" sheetId="1" r:id="rId1"/>
     <sheet name="Datasets" sheetId="2" r:id="rId2"/>
-    <sheet name="ie.xpt" sheetId="3" r:id="rId3"/>
+    <sheet name="lb.xpt" sheetId="3" r:id="rId3"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="78">
+  <si>
+    <t>Product</t>
+  </si>
+  <si>
+    <t>Version</t>
+  </si>
+  <si>
+    <t>sdtmig</t>
+  </si>
+  <si>
+    <t>3-4</t>
+  </si>
+  <si>
+    <t>Filename</t>
+  </si>
+  <si>
+    <t>Label</t>
+  </si>
+  <si>
+    <t>STUDYID</t>
+  </si>
+  <si>
+    <t>DOMAIN</t>
+  </si>
+  <si>
+    <t>USUBJID</t>
+  </si>
+  <si>
+    <t>EPOCH</t>
+  </si>
+  <si>
+    <t>Study Identifier</t>
+  </si>
+  <si>
+    <t>Domain Abbreviation</t>
+  </si>
+  <si>
+    <t>Unique Subject Identifier</t>
+  </si>
+  <si>
+    <t>Sequence Number</t>
+  </si>
+  <si>
+    <t>Epoch</t>
+  </si>
+  <si>
+    <t>LOINC Code</t>
+  </si>
+  <si>
+    <t>Char</t>
+  </si>
+  <si>
+    <t>Num</t>
+  </si>
+  <si>
+    <t>CDISCPILOT01</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>SCREENING</t>
+  </si>
+  <si>
+    <t>100000-9</t>
+  </si>
+  <si>
+    <t>lb.xpt</t>
+  </si>
+  <si>
+    <t>Laboratory</t>
+  </si>
+  <si>
+    <t>LBSEQ</t>
+  </si>
+  <si>
+    <t>LBTESTCD</t>
+  </si>
+  <si>
+    <t>LBTEST</t>
+  </si>
+  <si>
+    <t>LBCAT</t>
+  </si>
+  <si>
+    <t>LBORRES</t>
+  </si>
+  <si>
+    <t>LBORRESU</t>
+  </si>
+  <si>
+    <t>LBORNRLO</t>
+  </si>
+  <si>
+    <t>LBORNRHI</t>
+  </si>
+  <si>
+    <t>LBSTRESC</t>
+  </si>
+  <si>
+    <t>LBSTRESN</t>
+  </si>
+  <si>
+    <t>LBSTRESU</t>
+  </si>
+  <si>
+    <t>LBSTNRLO</t>
+  </si>
+  <si>
+    <t>LBSTNRHI</t>
+  </si>
+  <si>
+    <t>LBNRIND</t>
+  </si>
+  <si>
+    <t>LBLOBXFL</t>
+  </si>
+  <si>
+    <t>LBDRVFL</t>
+  </si>
+  <si>
+    <t>VISITNUM</t>
+  </si>
+  <si>
+    <t>VISIT</t>
+  </si>
+  <si>
+    <t>LBDTC</t>
+  </si>
+  <si>
+    <t>LBDY</t>
+  </si>
+  <si>
+    <t>Lab Test or Examination Short Name</t>
+  </si>
+  <si>
+    <t>Lab Test or Examination Name</t>
+  </si>
+  <si>
+    <t>Category for Lab Test</t>
+  </si>
+  <si>
+    <t>Result or Finding in Original Units</t>
+  </si>
+  <si>
+    <t>Original Units</t>
+  </si>
+  <si>
+    <t>Reference Range Lower Limit in Orig Unit</t>
+  </si>
+  <si>
+    <t>Reference Range Upper Limit in Orig Unit</t>
+  </si>
+  <si>
+    <t>Character Result/Finding in Std Format</t>
+  </si>
+  <si>
+    <t>Numeric Result/Finding in Standard Units</t>
+  </si>
+  <si>
+    <t>Standard Units</t>
+  </si>
+  <si>
+    <t>Reference Range Lower Limit-Std Units</t>
+  </si>
+  <si>
+    <t>Reference Range Upper Limit-Std Units</t>
+  </si>
+  <si>
+    <t>Reference Range Indicator</t>
+  </si>
+  <si>
+    <t>Last Observation Before Exposure Flag</t>
+  </si>
+  <si>
+    <t>Derived Flag</t>
+  </si>
+  <si>
+    <t>Visit Number</t>
+  </si>
+  <si>
+    <t>Visit Name</t>
+  </si>
+  <si>
+    <t>Date/Time of Specimen Collection</t>
+  </si>
+  <si>
+    <t>Study Day of Specimen Collection</t>
+  </si>
+  <si>
+    <t>LB</t>
+  </si>
+  <si>
+    <t>CDISC001</t>
+  </si>
+  <si>
+    <t>ALB</t>
+  </si>
+  <si>
+    <t>Albumin</t>
+  </si>
+  <si>
+    <t>CHEMISTRY</t>
+  </si>
+  <si>
+    <t>3.9</t>
+  </si>
+  <si>
+    <t>g/dL</t>
+  </si>
+  <si>
+    <t>3.5</t>
+  </si>
+  <si>
+    <t>4.6</t>
+  </si>
+  <si>
+    <t>39</t>
+  </si>
+  <si>
+    <t>g/L</t>
+  </si>
+  <si>
+    <t>NORMAL</t>
+  </si>
+  <si>
+    <t>SCREENING 1</t>
+  </si>
+  <si>
+    <t>2012-11-23T11:20</t>
+  </si>
+  <si>
+    <t>LBLOINC</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <numFmts count="0"/>
-  <fonts count="7" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -43,48 +270,37 @@
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
       <name val="Calibri"/>
-      <b/>
+      <family val="2"/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
       <name val="Calibri"/>
-      <color rgb="FF000000"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-      <color rgb="FF000000"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <i/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
-      <patternFill patternType="none">
-        <bgColor/>
-      </patternFill>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="gray125">
-        <bgColor/>
+      <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
-        <bgColor/>
+        <bgColor rgb="FFFFFFCC"/>
       </patternFill>
     </fill>
   </fills>
@@ -97,31 +313,58 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
+      <left style="thin">
+        <color rgb="FFD9D9D9"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD9D9D9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD9D9D9"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs>
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="1" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -446,187 +689,297 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="3" t="str">
-        <v>Product</v>
-      </c>
-      <c r="B1" s="3" t="str">
-        <v>Version</v>
+    <row r="1" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="str">
-        <v>sdtmig</v>
-      </c>
-      <c r="B2" s="2" t="str">
-        <v>3-4</v>
+    <row r="2" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" t="s">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B2"/>
+    <ignoredError sqref="A1:B2" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="3" t="str">
-        <v>Filename</v>
-      </c>
-      <c r="B1" s="3" t="str">
-        <v>Label</v>
+    <row r="1" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>5</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="4" t="str">
-        <v>ie.xpt</v>
-      </c>
-      <c r="B2" s="4" t="str">
-        <v>Inclusion Exclusion</v>
+    <row r="2" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A2" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B2"/>
-  </ignoredErrors>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:Y8"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="3" t="str">
-        <v>STUDYID</v>
-      </c>
-      <c r="B1" s="3" t="str">
-        <v>DOMAIN</v>
-      </c>
-      <c r="C1" s="3" t="str">
-        <v>USUBJID</v>
-      </c>
-      <c r="D1" s="3" t="str">
-        <v>IESEQ</v>
-      </c>
-      <c r="E1" s="3" t="str">
-        <v>IETESTCD</v>
-      </c>
-      <c r="F1" s="3" t="str">
-        <v>IETEST</v>
-      </c>
-      <c r="G1" s="3" t="str">
-        <v>IECAT</v>
-      </c>
-      <c r="H1" s="3" t="str">
-        <v>IEORRES</v>
-      </c>
-      <c r="I1" s="3" t="str">
-        <v>IESTRESC</v>
-      </c>
-      <c r="J1" s="3" t="str">
-        <v>EPOCH</v>
-      </c>
-      <c r="K1" s="3" t="str">
-        <v>IEDTC</v>
-      </c>
-      <c r="L1" s="3" t="str">
-        <v>IEDY</v>
-      </c>
-      <c r="M1" s="5" t="str">
-        <v>IELOINC</v>
+    <row r="1" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A1" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="L1" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="M1" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="N1" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="O1" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="P1" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q1" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="R1" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="S1" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="T1" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="U1" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="V1" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="W1" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="X1" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y1" s="4" t="s">
+        <v>77</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="6" t="str">
-        <v>Study Identifier</v>
-      </c>
-      <c r="B2" s="6" t="str">
-        <v>Domain Abbreviation</v>
-      </c>
-      <c r="C2" s="6" t="str">
-        <v>Unique Subject Identifier</v>
-      </c>
-      <c r="D2" s="6" t="str">
-        <v>Sequence Number</v>
-      </c>
-      <c r="E2" s="6" t="str">
-        <v>Inclusion/Exclusion Criterion Short Name</v>
-      </c>
-      <c r="F2" s="6" t="str">
-        <v>Inclusion/Exclusion Criterion</v>
-      </c>
-      <c r="G2" s="6" t="str">
-        <v>Inclusion/Exclusion Category</v>
-      </c>
-      <c r="H2" s="6" t="str">
-        <v>I/E Criterion Original Result</v>
-      </c>
-      <c r="I2" s="6" t="str">
-        <v>I/E Criterion Result in Std Format</v>
-      </c>
-      <c r="J2" s="6" t="str">
-        <v>Epoch</v>
-      </c>
-      <c r="K2" s="6" t="str">
-        <v>Date/Time of Collection</v>
-      </c>
-      <c r="L2" s="6" t="str">
-        <v>Study Day of Collection</v>
-      </c>
-      <c r="M2" s="6" t="str">
-        <v>LOINC Code</v>
+    <row r="2" spans="1:25" ht="80" x14ac:dyDescent="0.2">
+      <c r="A2" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="H2" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="I2" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="J2" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="K2" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="L2" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="M2" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="N2" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="O2" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="P2" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q2" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="R2" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="S2" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="T2" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="U2" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="V2" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="W2" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="X2" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="Y2" s="2" t="s">
+        <v>15</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="B3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="C3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="D3" s="6" t="str">
-        <v>Num</v>
-      </c>
-      <c r="E3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="F3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="G3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="H3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="I3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="J3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="K3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="L3" s="6" t="str">
-        <v>Num</v>
-      </c>
-      <c r="M3" s="6" t="str">
-        <v>Char</v>
+    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A3" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="I3" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="J3" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="K3" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="L3" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="M3" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="N3" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="O3" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="P3" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q3" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="R3" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="S3" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="T3" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="U3" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="V3" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="W3" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="X3" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="Y3" s="6" t="s">
+        <v>16</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:25" ht="15" x14ac:dyDescent="0.2">
       <c r="A4" s="6">
         <v>12</v>
       </c>
@@ -643,74 +996,220 @@
         <v>7</v>
       </c>
       <c r="F4" s="6">
-        <v>196</v>
+        <v>39</v>
       </c>
       <c r="G4" s="6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H4" s="6">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I4" s="6">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J4" s="6">
-        <v>9</v>
+        <v>200</v>
       </c>
       <c r="K4" s="6">
-        <v>10</v>
+        <v>200</v>
       </c>
       <c r="L4" s="6">
         <v>8</v>
       </c>
-      <c r="M4" s="6" t="str">
+      <c r="M4" s="6">
         <v>8</v>
       </c>
+      <c r="N4" s="6">
+        <v>7</v>
+      </c>
+      <c r="O4" s="6">
+        <v>8</v>
+      </c>
+      <c r="P4" s="6">
+        <v>8</v>
+      </c>
+      <c r="Q4" s="6">
+        <v>8</v>
+      </c>
+      <c r="R4" s="6">
+        <v>1</v>
+      </c>
+      <c r="S4" s="6">
+        <v>10</v>
+      </c>
+      <c r="T4" s="6">
+        <v>8</v>
+      </c>
+      <c r="U4" s="6">
+        <v>200</v>
+      </c>
+      <c r="V4" s="6">
+        <v>9</v>
+      </c>
+      <c r="W4" s="6">
+        <v>19</v>
+      </c>
+      <c r="X4" s="6">
+        <v>8</v>
+      </c>
+      <c r="Y4" s="2">
+        <v>8</v>
+      </c>
     </row>
-    <row r="5">
-      <c r="A5" s="7" t="str">
-        <v>CDISCPILOT01</v>
-      </c>
-      <c r="B5" s="7" t="str">
-        <v>IE</v>
-      </c>
-      <c r="C5" s="7" t="str">
-        <v>CDISC01</v>
+    <row r="5" spans="1:25" ht="32" x14ac:dyDescent="0.2">
+      <c r="A5" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>64</v>
       </c>
       <c r="D5" s="7">
         <v>1</v>
       </c>
-      <c r="E5" s="7" t="str">
-        <v>INCL01</v>
-      </c>
-      <c r="F5" s="7" t="str">
-        <v>Is not pregnant or nursing.</v>
-      </c>
-      <c r="G5" s="7" t="str">
-        <v>INCLUSION</v>
-      </c>
-      <c r="H5" s="7" t="str">
-        <v>Y</v>
-      </c>
-      <c r="I5" s="7" t="str">
-        <v>Y</v>
-      </c>
-      <c r="J5" s="7" t="str">
-        <v>SCREENING</v>
-      </c>
-      <c r="K5" s="7" t="str">
-        <v>2014-03-17</v>
-      </c>
-      <c r="L5" s="2" t="str">
-        <v/>
-      </c>
-      <c r="M5" s="4" t="str">
-        <v>100000-9</v>
-      </c>
+      <c r="E5" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="H5" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="I5" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="J5" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="K5" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="L5" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="M5" s="7">
+        <v>39</v>
+      </c>
+      <c r="N5" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="O5" s="7">
+        <v>35</v>
+      </c>
+      <c r="P5" s="7">
+        <v>46</v>
+      </c>
+      <c r="Q5" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="R5" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="S5" s="8"/>
+      <c r="T5" s="7">
+        <v>1</v>
+      </c>
+      <c r="U5" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="V5" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="W5" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="X5" s="7">
+        <v>-7</v>
+      </c>
+      <c r="Y5" s="10" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" spans="1:25" ht="15" x14ac:dyDescent="0.2">
+      <c r="A6" s="7"/>
+      <c r="B6" s="7"/>
+      <c r="C6" s="7"/>
+      <c r="D6" s="7"/>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
+      <c r="G6" s="7"/>
+      <c r="H6" s="7"/>
+      <c r="I6" s="7"/>
+      <c r="J6" s="7"/>
+      <c r="K6" s="7"/>
+      <c r="L6" s="7"/>
+      <c r="M6" s="7"/>
+      <c r="N6" s="7"/>
+      <c r="O6" s="7"/>
+      <c r="P6" s="7"/>
+      <c r="Q6" s="7"/>
+      <c r="R6" s="7"/>
+      <c r="S6" s="8"/>
+      <c r="T6" s="7"/>
+      <c r="U6" s="7"/>
+      <c r="V6" s="7"/>
+      <c r="W6" s="7"/>
+      <c r="X6" s="7"/>
+    </row>
+    <row r="7" spans="1:25" ht="15" x14ac:dyDescent="0.2">
+      <c r="A7" s="7"/>
+      <c r="B7" s="7"/>
+      <c r="C7" s="7"/>
+      <c r="D7" s="7"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="7"/>
+      <c r="I7" s="7"/>
+      <c r="J7" s="7"/>
+      <c r="K7" s="7"/>
+      <c r="L7" s="7"/>
+      <c r="M7" s="7"/>
+      <c r="N7" s="7"/>
+      <c r="O7" s="7"/>
+      <c r="P7" s="7"/>
+      <c r="Q7" s="7"/>
+      <c r="R7" s="7"/>
+      <c r="S7" s="9"/>
+      <c r="T7" s="7"/>
+      <c r="U7" s="7"/>
+      <c r="V7" s="7"/>
+      <c r="W7" s="7"/>
+      <c r="X7" s="7"/>
+    </row>
+    <row r="8" spans="1:25" ht="15" x14ac:dyDescent="0.2">
+      <c r="A8" s="7"/>
+      <c r="B8" s="7"/>
+      <c r="C8" s="7"/>
+      <c r="D8" s="7"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="7"/>
+      <c r="G8" s="7"/>
+      <c r="H8" s="7"/>
+      <c r="I8" s="7"/>
+      <c r="J8" s="7"/>
+      <c r="K8" s="7"/>
+      <c r="L8" s="7"/>
+      <c r="M8" s="7"/>
+      <c r="N8" s="7"/>
+      <c r="O8" s="7"/>
+      <c r="P8" s="7"/>
+      <c r="Q8" s="7"/>
+      <c r="R8" s="7"/>
+      <c r="S8" s="7"/>
+      <c r="T8" s="7"/>
+      <c r="U8" s="7"/>
+      <c r="V8" s="7"/>
+      <c r="W8" s="7"/>
+      <c r="X8" s="7"/>
     </row>
   </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M5"/>
-  </ignoredErrors>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/rules/NEW-RULE/positive/01/data/new-rule-positive-01.xlsx
+++ b/rules/NEW-RULE/positive/01/data/new-rule-positive-01.xlsx
@@ -1,40 +1,196 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10419"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rich/Documents/github/core-contributor/rules/NEW-RULE/positive/01/data/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDACDA1F-E5B0-7347-9586-1649A8E4020B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="30320" yWindow="-8560" windowWidth="51200" windowHeight="28200" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
     <sheet name="Library" sheetId="1" r:id="rId1"/>
     <sheet name="Datasets" sheetId="2" r:id="rId2"/>
     <sheet name="aplb.xpt" sheetId="3" r:id="rId3"/>
+    <sheet name="lb.xpt" sheetId="4" r:id="rId4"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="54">
+  <si>
+    <t>Product</t>
+  </si>
+  <si>
+    <t>Version</t>
+  </si>
+  <si>
+    <t>sdtmig</t>
+  </si>
+  <si>
+    <t>3-4</t>
+  </si>
+  <si>
+    <t>sdtmct</t>
+  </si>
+  <si>
+    <t>2025-03-28</t>
+  </si>
+  <si>
+    <t>Filename</t>
+  </si>
+  <si>
+    <t>Label</t>
+  </si>
+  <si>
+    <t>aplb.xpt</t>
+  </si>
+  <si>
+    <t>Associated Persons Laboratory Test Results</t>
+  </si>
+  <si>
+    <t>STUDYID</t>
+  </si>
+  <si>
+    <t>DOMAIN</t>
+  </si>
+  <si>
+    <t>APID</t>
+  </si>
+  <si>
+    <t>LBSEQ</t>
+  </si>
+  <si>
+    <t>RSUBJID</t>
+  </si>
+  <si>
+    <t>RDEVID</t>
+  </si>
+  <si>
+    <t>SREL</t>
+  </si>
+  <si>
+    <t>LBTESTCD</t>
+  </si>
+  <si>
+    <t>LBTEST</t>
+  </si>
+  <si>
+    <t>LBORRES</t>
+  </si>
+  <si>
+    <t>LBSTRESC</t>
+  </si>
+  <si>
+    <t>LBDTC</t>
+  </si>
+  <si>
+    <t>Study Identifier</t>
+  </si>
+  <si>
+    <t>Unique Subject Identifier</t>
+  </si>
+  <si>
+    <t>Associated Persons Identifier</t>
+  </si>
+  <si>
+    <t>Sequence Number</t>
+  </si>
+  <si>
+    <t>Related Subject or Pool Identifier</t>
+  </si>
+  <si>
+    <t>Related Device Identifier</t>
+  </si>
+  <si>
+    <t>Subject Relationship</t>
+  </si>
+  <si>
+    <t>Lab Test or Examination Short Name</t>
+  </si>
+  <si>
+    <t>Lab Test or Examination Name</t>
+  </si>
+  <si>
+    <t>Result or Finding in Original Units</t>
+  </si>
+  <si>
+    <t>Character Result/Finding in Std Format</t>
+  </si>
+  <si>
+    <t>Date/Time of Specimen Collection</t>
+  </si>
+  <si>
+    <t>Char</t>
+  </si>
+  <si>
+    <t>Num</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>HEM021</t>
+  </si>
+  <si>
+    <t>APLB</t>
+  </si>
+  <si>
+    <t>POOL1</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>GRNMO13</t>
+  </si>
+  <si>
+    <t>DONOR, SAMPLE</t>
+  </si>
+  <si>
+    <t>BADSTUFF</t>
+  </si>
+  <si>
+    <t>POSITIVE</t>
+  </si>
+  <si>
+    <t>2006-04-01T00:00:00.000Z</t>
+  </si>
+  <si>
+    <t>USUBJID</t>
+  </si>
+  <si>
+    <t>Domain</t>
+  </si>
+  <si>
+    <t>CDISC001</t>
+  </si>
+  <si>
+    <t>LB</t>
+  </si>
+  <si>
+    <t>APDM</t>
+  </si>
+  <si>
+    <t>ZZ</t>
+  </si>
+  <si>
+    <t>lb.xpt</t>
+  </si>
+  <si>
+    <t>Laboratory Test Results</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <numFmts count="0"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -43,48 +199,40 @@
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <i/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
     <fill>
-      <patternFill patternType="none">
-        <bgColor/>
-      </patternFill>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="gray125">
-        <bgColor/>
-      </patternFill>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
-        <bgColor/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -93,22 +241,29 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs>
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="1" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -433,264 +588,426 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="str">
-        <v>Product</v>
-      </c>
-      <c r="B1" s="2" t="str">
-        <v>Version</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="str">
-        <v>sdtmig</v>
-      </c>
-      <c r="B2" s="2" t="str">
-        <v>3-4</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="str">
-        <v>sdtmct</v>
-      </c>
-      <c r="B3" s="2" t="str">
-        <v>2025-03-28</v>
+    <row r="1" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B3"/>
+    <ignoredError sqref="A1:B3" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="str">
-        <v>Filename</v>
-      </c>
-      <c r="B1" s="2" t="str">
-        <v>Label</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="str">
-        <v>aplb.xpt</v>
-      </c>
-      <c r="B2" s="2" t="str">
-        <v>Associated Persons Laboratory Test Results</v>
+    <row r="1" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A3" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>53</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B2"/>
+    <ignoredError sqref="A1:B2" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:L6"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="3" t="str">
-        <v>STUDYID</v>
-      </c>
-      <c r="B1" s="3" t="str">
-        <v>DOMAIN</v>
-      </c>
-      <c r="C1" s="3" t="str">
-        <v>APID</v>
-      </c>
-      <c r="D1" s="3" t="str">
-        <v>LBSEQ</v>
-      </c>
-      <c r="E1" s="3" t="str">
-        <v>RSUBJID</v>
-      </c>
-      <c r="F1" s="3" t="str">
-        <v>RDEVID</v>
-      </c>
-      <c r="G1" s="3" t="str">
-        <v>SREL</v>
-      </c>
-      <c r="H1" s="3" t="str">
-        <v>LBTESTCD</v>
-      </c>
-      <c r="I1" s="3" t="str">
-        <v>LBTEST</v>
-      </c>
-      <c r="J1" s="3" t="str">
-        <v>LBORRES</v>
-      </c>
-      <c r="K1" s="3" t="str">
-        <v>LBSTRESC</v>
-      </c>
-      <c r="L1" s="3" t="str">
-        <v>LBDTC</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="str">
-        <v>Study Identifier</v>
-      </c>
-      <c r="B2" s="4" t="str">
-        <v>Unique Subject Identifier</v>
-      </c>
-      <c r="C2" s="4" t="str">
-        <v>Associated Persons Identifier</v>
-      </c>
-      <c r="D2" s="4" t="str">
-        <v>Sequence Number</v>
-      </c>
-      <c r="E2" s="4" t="str">
-        <v>Related Subject or Pool Identifier</v>
-      </c>
-      <c r="F2" s="4" t="str">
-        <v>Related Device Identifier</v>
-      </c>
-      <c r="G2" s="4" t="str">
-        <v>Subject Relationship</v>
-      </c>
-      <c r="H2" s="4" t="str">
-        <v>Lab Test or Examination Short Name</v>
-      </c>
-      <c r="I2" s="4" t="str">
-        <v>Lab Test or Examination Name</v>
-      </c>
-      <c r="J2" s="4" t="str">
-        <v>Result or Finding in Original Units</v>
-      </c>
-      <c r="K2" s="4" t="str">
-        <v>Character Result/Finding in Std Format</v>
-      </c>
-      <c r="L2" s="4" t="str">
-        <v>Date/Time of Specimen Collection</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="str">
-        <v>Char</v>
-      </c>
-      <c r="B3" s="4" t="str">
-        <v>Char</v>
-      </c>
-      <c r="C3" s="4" t="str">
-        <v>Char</v>
-      </c>
-      <c r="D3" s="4" t="str">
-        <v>Num</v>
-      </c>
-      <c r="E3" s="4" t="str">
-        <v>Char</v>
-      </c>
-      <c r="F3" s="4" t="str">
-        <v>Char</v>
-      </c>
-      <c r="G3" s="4" t="str">
-        <v>Char</v>
-      </c>
-      <c r="H3" s="4" t="str">
-        <v>Char</v>
-      </c>
-      <c r="I3" s="4" t="str">
-        <v>Char</v>
-      </c>
-      <c r="J3" s="4" t="str">
-        <v>Char</v>
-      </c>
-      <c r="K3" s="4" t="str">
-        <v>Char</v>
-      </c>
-      <c r="L3" s="4" t="str">
-        <v>Char</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="4">
-        <v>50</v>
-      </c>
-      <c r="B4" s="4">
-        <v>50</v>
-      </c>
-      <c r="C4" s="4">
-        <v>50</v>
-      </c>
-      <c r="D4" s="4" t="str">
-        <v>8</v>
-      </c>
-      <c r="E4" s="4">
-        <v>50</v>
-      </c>
-      <c r="F4" s="4">
-        <v>50</v>
-      </c>
-      <c r="G4" s="4">
-        <v>50</v>
-      </c>
-      <c r="H4" s="4">
-        <v>50</v>
-      </c>
-      <c r="I4" s="4">
-        <v>50</v>
-      </c>
-      <c r="J4" s="4">
-        <v>50</v>
-      </c>
-      <c r="K4" s="4">
-        <v>50</v>
-      </c>
-      <c r="L4" s="4">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="str">
-        <v>HEM021</v>
-      </c>
-      <c r="B5" s="2" t="str">
-        <v>APLB</v>
-      </c>
-      <c r="C5" s="2" t="str">
-        <v>POOL1</v>
-      </c>
-      <c r="D5" s="2">
+    <row r="1" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+      <c r="A2" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+      <c r="A3" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+      <c r="A4" s="2">
+        <v>50</v>
+      </c>
+      <c r="B4" s="2">
+        <v>50</v>
+      </c>
+      <c r="C4" s="2">
+        <v>50</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E4" s="2">
+        <v>50</v>
+      </c>
+      <c r="F4" s="2">
+        <v>50</v>
+      </c>
+      <c r="G4" s="2">
+        <v>50</v>
+      </c>
+      <c r="H4" s="2">
+        <v>50</v>
+      </c>
+      <c r="I4" s="2">
+        <v>50</v>
+      </c>
+      <c r="J4" s="2">
+        <v>50</v>
+      </c>
+      <c r="K4" s="2">
+        <v>50</v>
+      </c>
+      <c r="L4" s="2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+      <c r="A5" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B5" t="s">
+        <v>38</v>
+      </c>
+      <c r="C5" t="s">
+        <v>39</v>
+      </c>
+      <c r="D5">
         <v>1</v>
       </c>
-      <c r="E5" s="2" t="str">
-        <v/>
-      </c>
-      <c r="F5" s="2" t="str">
-        <v>GRNMO13</v>
-      </c>
-      <c r="G5" s="2" t="str">
-        <v>DONOR, SAMPLE</v>
-      </c>
-      <c r="H5" s="2" t="str">
-        <v>BADSTUFF</v>
-      </c>
-      <c r="I5" s="2" t="str">
-        <v>BADSTUFF</v>
-      </c>
-      <c r="J5" s="2" t="str">
-        <v>POSITIVE</v>
-      </c>
-      <c r="K5" s="2" t="str">
-        <v>POSITIVE</v>
-      </c>
-      <c r="L5" s="5" t="str">
-        <v>2006-04-01T00:00:00.000Z</v>
+      <c r="E5" t="s">
+        <v>40</v>
+      </c>
+      <c r="F5" t="s">
+        <v>41</v>
+      </c>
+      <c r="G5" t="s">
+        <v>42</v>
+      </c>
+      <c r="H5" t="s">
+        <v>43</v>
+      </c>
+      <c r="I5" t="s">
+        <v>43</v>
+      </c>
+      <c r="J5" t="s">
+        <v>44</v>
+      </c>
+      <c r="K5" t="s">
+        <v>44</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+      <c r="A6" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C6" t="s">
+        <v>39</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6" t="s">
+        <v>40</v>
+      </c>
+      <c r="F6" t="s">
+        <v>41</v>
+      </c>
+      <c r="G6" t="s">
+        <v>42</v>
+      </c>
+      <c r="H6" t="s">
+        <v>43</v>
+      </c>
+      <c r="I6" t="s">
+        <v>43</v>
+      </c>
+      <c r="J6" t="s">
+        <v>44</v>
+      </c>
+      <c r="K6" t="s">
+        <v>44</v>
+      </c>
+      <c r="L6" s="3" t="s">
+        <v>45</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L5"/>
+    <ignoredError sqref="A1:L5" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9740AA00-2BC5-9040-9646-E65285399E1F}">
+  <dimension ref="A1:D7"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A2" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A3" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A4" s="2">
+        <v>50</v>
+      </c>
+      <c r="B4" s="2">
+        <v>50</v>
+      </c>
+      <c r="C4" s="2">
+        <v>50</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A5" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A6" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A7" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+</worksheet>
 </file>
--- a/rules/NEW-RULE/positive/01/data/new-rule-positive-01.xlsx
+++ b/rules/NEW-RULE/positive/01/data/new-rule-positive-01.xlsx
@@ -652,8 +652,11 @@
       <c r="G5" s="4" t="str">
         <v>UNIITERM1</v>
       </c>
-      <c r="I5" s="2" t="str">
-        <v>00000UNII1</v>
+      <c r="H5" s="2" t="str">
+        <v/>
+      </c>
+      <c r="I5" s="4" t="str">
+        <v>0001H6R5H1</v>
       </c>
     </row>
   </sheetData>

--- a/rules/NEW-RULE/positive/01/data/new-rule-positive-01.xlsx
+++ b/rules/NEW-RULE/positive/01/data/new-rule-positive-01.xlsx
@@ -35,7 +35,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
   <numFmts count="0"/>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -58,13 +58,8 @@
       <name val="Calibri"/>
       <i/>
     </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <i/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none">
         <bgColor/>
@@ -72,12 +67,6 @@
     </fill>
     <fill>
       <patternFill patternType="gray125">
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFCC"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -107,14 +96,13 @@
   <cellStyleXfs>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="1" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -547,98 +535,98 @@
       <c r="C2" s="5" t="str">
         <v>Sequence Number</v>
       </c>
-      <c r="D2" s="6" t="str">
+      <c r="D2" s="5" t="str">
         <v>Group ID</v>
       </c>
-      <c r="E2" s="6" t="str">
+      <c r="E2" s="5" t="str">
         <v>Trial Summary Parameter Short Name</v>
       </c>
-      <c r="F2" s="6" t="str">
+      <c r="F2" s="5" t="str">
         <v>Trial Summary Parameter</v>
       </c>
-      <c r="G2" s="6" t="str">
+      <c r="G2" s="5" t="str">
         <v>Parameter Value</v>
       </c>
-      <c r="H2" s="6" t="str">
+      <c r="H2" s="5" t="str">
         <v>Parameter Null Flavor</v>
       </c>
-      <c r="I2" s="6" t="str">
+      <c r="I2" s="5" t="str">
         <v>Parameter Value Code</v>
       </c>
-      <c r="J2" s="6" t="str">
+      <c r="J2" s="5" t="str">
         <v>Name of the Reference Terminology</v>
       </c>
-      <c r="K2" s="6" t="str">
+      <c r="K2" s="5" t="str">
         <v>Version of the Reference Terminology</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="B3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="C3" s="6" t="str">
+      <c r="A3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="B3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="C3" s="5" t="str">
         <v>Num</v>
       </c>
-      <c r="D3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="E3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="F3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="G3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="H3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="I3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="J3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="K3" s="6" t="str">
+      <c r="D3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="E3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="F3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="G3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="H3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="I3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="J3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="K3" s="5" t="str">
         <v>Char</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6">
+      <c r="A4" s="5">
         <v>10</v>
       </c>
-      <c r="B4" s="6">
+      <c r="B4" s="5">
         <v>2</v>
       </c>
-      <c r="C4" s="6">
+      <c r="C4" s="5">
         <v>8</v>
       </c>
-      <c r="D4" s="6">
+      <c r="D4" s="5">
         <v>5</v>
       </c>
-      <c r="E4" s="6">
+      <c r="E4" s="5">
         <v>8</v>
       </c>
-      <c r="F4" s="6">
+      <c r="F4" s="5">
         <v>40</v>
       </c>
-      <c r="G4" s="6">
+      <c r="G4" s="5">
         <v>149</v>
       </c>
-      <c r="H4" s="6">
+      <c r="H4" s="5">
         <v>2</v>
       </c>
-      <c r="I4" s="6">
+      <c r="I4" s="5">
         <v>11</v>
       </c>
-      <c r="J4" s="6">
+      <c r="J4" s="5">
         <v>18</v>
       </c>
-      <c r="K4" s="6">
+      <c r="K4" s="5">
         <v>10</v>
       </c>
     </row>
@@ -662,13 +650,13 @@
         <v>Extension Trial Indicator</v>
       </c>
       <c r="G5" s="4" t="str">
-        <v>Acetylcholine Activity Alteration</v>
+        <v>Description term 1.</v>
       </c>
       <c r="H5" s="4" t="str">
         <v/>
       </c>
-      <c r="I5" s="4" t="str">
-        <v>N0000008290</v>
+      <c r="I5" s="4">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/rules/NEW-RULE/positive/01/data/new-rule-positive-01.xlsx
+++ b/rules/NEW-RULE/positive/01/data/new-rule-positive-01.xlsx
@@ -652,11 +652,11 @@
       <c r="G5" s="4" t="str">
         <v>UNIITERM1</v>
       </c>
-      <c r="H5" s="2" t="str">
+      <c r="H5" s="4" t="str">
         <v/>
       </c>
       <c r="I5" s="4" t="str">
-        <v>00000UNII1</v>
+        <v>000360VJE1</v>
       </c>
     </row>
   </sheetData>

--- a/rules/NEW-RULE/positive/01/data/new-rule-positive-01.xlsx
+++ b/rules/NEW-RULE/positive/01/data/new-rule-positive-01.xlsx
@@ -652,11 +652,11 @@
       <c r="G5" s="4" t="str">
         <v>UNIITERM1</v>
       </c>
-      <c r="H5" s="2" t="str">
+      <c r="H5" s="4" t="str">
         <v/>
       </c>
       <c r="I5" s="4" t="str">
-        <v>00000UNII1</v>
+        <v>0005633KTU</v>
       </c>
     </row>
   </sheetData>

--- a/rules/NEW-RULE/positive/01/data/new-rule-positive-01.xlsx
+++ b/rules/NEW-RULE/positive/01/data/new-rule-positive-01.xlsx
@@ -650,7 +650,7 @@
         <v>Extension Trial Indicator</v>
       </c>
       <c r="G5" s="4" t="str">
-        <v>Description term 1.</v>
+        <v>TextDefinition term 1.</v>
       </c>
       <c r="H5" s="4" t="str">
         <v/>

--- a/rules/NEW-RULE/positive/01/data/new-rule-positive-01.xlsx
+++ b/rules/NEW-RULE/positive/01/data/new-rule-positive-01.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10419"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rich/Documents/github/core-contributor/rules/NEW-RULE/positive/01/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8D5B569-B431-7F4F-93CD-037931AB6095}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{796F6728-8907-CA49-9795-F63DDBA249D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30240" yWindow="-8560" windowWidth="51200" windowHeight="28200" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Library" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="75">
   <si>
     <t>Product</t>
   </si>
@@ -172,9 +172,6 @@
     <t>DKA1</t>
   </si>
   <si>
-    <t>DKA10</t>
-  </si>
-  <si>
     <t>002</t>
   </si>
   <si>
@@ -187,18 +184,6 @@
     <t>2006-10-11</t>
   </si>
   <si>
-    <t>DKA00003</t>
-  </si>
-  <si>
-    <t>DKA002</t>
-  </si>
-  <si>
-    <t>DKA999</t>
-  </si>
-  <si>
-    <t>DKA1000</t>
-  </si>
-  <si>
     <t>2025-01-01</t>
   </si>
   <si>
@@ -214,12 +199,6 @@
     <t>DKA0002</t>
   </si>
   <si>
-    <t>DKA04</t>
-  </si>
-  <si>
-    <t>DKA011</t>
-  </si>
-  <si>
     <t>2026-12-31</t>
   </si>
   <si>
@@ -251,6 +230,24 @@
   </si>
   <si>
     <t>2000-01-02</t>
+  </si>
+  <si>
+    <t>DKA03</t>
+  </si>
+  <si>
+    <t>DKA4</t>
+  </si>
+  <si>
+    <t>DKA005</t>
+  </si>
+  <si>
+    <t>DKA001</t>
+  </si>
+  <si>
+    <t>DKA00002</t>
+  </si>
+  <si>
+    <t>DKA2</t>
   </si>
 </sst>
 </file>
@@ -857,7 +854,7 @@
         <v>2</v>
       </c>
       <c r="E6" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="F6" t="s">
         <v>39</v>
@@ -880,7 +877,7 @@
         <v>3</v>
       </c>
       <c r="E7" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="F7" t="s">
         <v>39</v>
@@ -903,7 +900,7 @@
         <v>4</v>
       </c>
       <c r="E8" t="s">
-        <v>49</v>
+        <v>70</v>
       </c>
       <c r="F8" t="s">
         <v>39</v>
@@ -926,7 +923,7 @@
         <v>5</v>
       </c>
       <c r="E9" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="F9" t="s">
         <v>39</v>
@@ -943,19 +940,19 @@
         <v>33</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D10">
         <v>4</v>
       </c>
       <c r="E10" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="F10" t="s">
         <v>39</v>
       </c>
       <c r="G10" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.2">
@@ -966,19 +963,19 @@
         <v>33</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D11">
         <v>9</v>
       </c>
       <c r="E11" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="F11" t="s">
         <v>39</v>
       </c>
       <c r="G11" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.2">
@@ -989,19 +986,19 @@
         <v>33</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D12">
         <v>6</v>
       </c>
       <c r="E12" t="s">
-        <v>54</v>
+        <v>73</v>
       </c>
       <c r="F12" t="s">
         <v>39</v>
       </c>
       <c r="G12" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.2">
@@ -1012,19 +1009,19 @@
         <v>33</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D13">
         <v>3</v>
       </c>
       <c r="E13" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="F13" t="s">
         <v>39</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.2">
@@ -1035,13 +1032,13 @@
         <v>33</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="D14">
         <v>1</v>
       </c>
       <c r="E14" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="F14" t="s">
         <v>39</v>
@@ -1055,13 +1052,13 @@
         <v>33</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="D15">
         <v>2</v>
       </c>
       <c r="E15" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="F15" t="s">
         <v>39</v>
@@ -1075,16 +1072,16 @@
         <v>33</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D16">
         <v>1</v>
       </c>
       <c r="E16" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="F16" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
@@ -1095,19 +1092,19 @@
         <v>33</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="D17">
         <v>1</v>
       </c>
       <c r="E17" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="F17" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.2">
@@ -1118,19 +1115,19 @@
         <v>33</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="D18">
         <v>2</v>
       </c>
       <c r="E18" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="F18" t="s">
+        <v>60</v>
+      </c>
+      <c r="G18" s="4" t="s">
         <v>67</v>
-      </c>
-      <c r="G18" s="4" t="s">
-        <v>74</v>
       </c>
     </row>
   </sheetData>
@@ -1237,13 +1234,13 @@
         <v>38</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
     </row>
   </sheetData>

--- a/rules/NEW-RULE/positive/01/data/new-rule-positive-01.xlsx
+++ b/rules/NEW-RULE/positive/01/data/new-rule-positive-01.xlsx
@@ -1,41 +1,183 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11214"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/maxverisian/verisian/core-contributor/rules/NEW-RULE/positive/01/data/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86980BAF-71AC-124D-8AE3-34C0EF08CEED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="14760" yWindow="660" windowWidth="15480" windowHeight="18980" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Library" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Datasets" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Library" sheetId="1" r:id="rId1"/>
+    <sheet name="Datasets" sheetId="2" r:id="rId2"/>
+    <sheet name="ts.xpt" sheetId="3" r:id="rId3"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="38">
+  <si>
+    <t>Product</t>
+  </si>
+  <si>
+    <t>Version</t>
+  </si>
+  <si>
+    <t>sdtmig</t>
+  </si>
+  <si>
+    <t>3-4</t>
+  </si>
+  <si>
+    <t>Filename</t>
+  </si>
+  <si>
+    <t>Label</t>
+  </si>
+  <si>
+    <t>ts.xpt</t>
+  </si>
+  <si>
+    <t>Trial Summary Parameters</t>
+  </si>
+  <si>
+    <t>STUDYID</t>
+  </si>
+  <si>
+    <t>DOMAIN</t>
+  </si>
+  <si>
+    <t>TSSEQ</t>
+  </si>
+  <si>
+    <t>TSGRPID</t>
+  </si>
+  <si>
+    <t>TSPARMCD</t>
+  </si>
+  <si>
+    <t>TSPARM</t>
+  </si>
+  <si>
+    <t>TSVAL</t>
+  </si>
+  <si>
+    <t>TSVALNF</t>
+  </si>
+  <si>
+    <t>TSVALCD</t>
+  </si>
+  <si>
+    <t>TSVCDREF</t>
+  </si>
+  <si>
+    <t>TSVCDVER</t>
+  </si>
+  <si>
+    <t>Study Identifier</t>
+  </si>
+  <si>
+    <t>Domain Abbreviation</t>
+  </si>
+  <si>
+    <t>Sequence Number</t>
+  </si>
+  <si>
+    <t>Group ID</t>
+  </si>
+  <si>
+    <t>Trial Summary Parameter Short Name</t>
+  </si>
+  <si>
+    <t>Trial Summary Parameter</t>
+  </si>
+  <si>
+    <t>Parameter Value</t>
+  </si>
+  <si>
+    <t>Parameter Null Flavor</t>
+  </si>
+  <si>
+    <t>Parameter Value Code</t>
+  </si>
+  <si>
+    <t>Name of the Reference Terminology</t>
+  </si>
+  <si>
+    <t>Version of the Reference Terminology</t>
+  </si>
+  <si>
+    <t>Char</t>
+  </si>
+  <si>
+    <t>Num</t>
+  </si>
+  <si>
+    <t>CDISCPILOT01</t>
+  </si>
+  <si>
+    <t>TS</t>
+  </si>
+  <si>
+    <t>ISO 8601</t>
+  </si>
+  <si>
+    <t>SSTDTC</t>
+  </si>
+  <si>
+    <t>Study Start Date</t>
+  </si>
+  <si>
+    <t>2026-03-01</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor rgb="FFFFFFCC"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -43,85 +185,50 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD9D9D9"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD9D9D9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+  <cellXfs count="4">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -409,36 +516,24 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Product</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Version</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>sdtmig</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>3-4</t>
-        </is>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" t="s">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -447,31 +542,319 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Filename</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Label</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
-      <c r="B2" t="inlineStr"/>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>7</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C032464-63DD-D94A-B4AF-1CB07DD85ACE}">
+  <dimension ref="A1:K17"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="80" x14ac:dyDescent="0.2">
+      <c r="A2" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+      <c r="A3" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A4" s="2">
+        <v>12</v>
+      </c>
+      <c r="B4" s="2">
+        <v>2</v>
+      </c>
+      <c r="C4" s="2">
+        <v>8</v>
+      </c>
+      <c r="D4" s="2">
+        <v>200</v>
+      </c>
+      <c r="E4" s="2">
+        <v>8</v>
+      </c>
+      <c r="F4" s="2">
+        <v>40</v>
+      </c>
+      <c r="G4" s="2">
+        <v>200</v>
+      </c>
+      <c r="H4" s="2">
+        <v>4</v>
+      </c>
+      <c r="I4" s="2">
+        <v>200</v>
+      </c>
+      <c r="J4" s="2">
+        <v>200</v>
+      </c>
+      <c r="K4" s="2">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="32" x14ac:dyDescent="0.2">
+      <c r="A5" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C5" s="3">
+        <v>1</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A6" s="3"/>
+      <c r="B6" s="3"/>
+      <c r="C6" s="3"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="3"/>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A7" s="3"/>
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="I7" s="3"/>
+      <c r="J7" s="3"/>
+      <c r="K7" s="3"/>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A8" s="3"/>
+      <c r="B8" s="3"/>
+      <c r="C8" s="3"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="3"/>
+      <c r="I8" s="3"/>
+      <c r="J8" s="3"/>
+      <c r="K8" s="3"/>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A9" s="3"/>
+      <c r="B9" s="3"/>
+      <c r="C9" s="3"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="3"/>
+      <c r="I9" s="3"/>
+      <c r="J9" s="3"/>
+      <c r="K9" s="3"/>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A10" s="3"/>
+      <c r="B10" s="3"/>
+      <c r="C10" s="3"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="3"/>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A11" s="3"/>
+      <c r="B11" s="3"/>
+      <c r="C11" s="3"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="3"/>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A12" s="3"/>
+      <c r="B12" s="3"/>
+      <c r="C12" s="3"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
+      <c r="G12" s="3"/>
+      <c r="I12" s="3"/>
+      <c r="J12" s="3"/>
+      <c r="K12" s="3"/>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A13" s="3"/>
+      <c r="B13" s="3"/>
+      <c r="C13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+      <c r="G13" s="3"/>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A14" s="3"/>
+      <c r="B14" s="3"/>
+      <c r="C14" s="3"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
+      <c r="G14" s="3"/>
+      <c r="I14" s="3"/>
+      <c r="J14" s="3"/>
+      <c r="K14" s="3"/>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A15" s="3"/>
+      <c r="B15" s="3"/>
+      <c r="C15" s="3"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3"/>
+      <c r="G15" s="3"/>
+      <c r="I15" s="3"/>
+      <c r="J15" s="3"/>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A16" s="3"/>
+      <c r="B16" s="3"/>
+      <c r="C16" s="3"/>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3"/>
+      <c r="G16" s="3"/>
+      <c r="I16" s="3"/>
+      <c r="J16" s="3"/>
+      <c r="K16" s="3"/>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A17" s="3"/>
+      <c r="B17" s="3"/>
+      <c r="C17" s="3"/>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3"/>
+      <c r="G17" s="3"/>
+      <c r="I17" s="3"/>
+      <c r="J17" s="3"/>
+      <c r="K17" s="3"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/rules/NEW-RULE/positive/01/data/new-rule-positive-01.xlsx
+++ b/rules/NEW-RULE/positive/01/data/new-rule-positive-01.xlsx
@@ -35,7 +35,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
   <numFmts count="0"/>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -102,13 +106,14 @@
   <cellStyleXfs>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="1" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -443,26 +448,26 @@
   <dimension ref="A1:B3"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="str">
+      <c r="A1" s="3" t="str">
         <v>Product</v>
       </c>
-      <c r="B1" s="2" t="str">
+      <c r="B1" s="3" t="str">
         <v>Version</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="str">
+      <c r="A2" s="3" t="str">
         <v>sdtmig</v>
       </c>
-      <c r="B2" s="2" t="str">
+      <c r="B2" s="3" t="str">
         <v>3-4</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="str">
+      <c r="A3" s="3" t="str">
         <v>sdtmct</v>
       </c>
-      <c r="B3" s="2" t="str">
+      <c r="B3" s="3" t="str">
         <v>2025-03-28</v>
       </c>
     </row>
@@ -478,18 +483,18 @@
   <dimension ref="A1:B2"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="str">
+      <c r="A1" s="3" t="str">
         <v>Filename</v>
       </c>
-      <c r="B1" s="2" t="str">
+      <c r="B1" s="3" t="str">
         <v>Label</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="str">
+      <c r="A2" s="3" t="str">
         <v>pp.xpt</v>
       </c>
-      <c r="B2" s="2" t="str">
+      <c r="B2" s="3" t="str">
         <v>Pharmacokinetics Parameters</v>
       </c>
     </row>
@@ -505,331 +510,331 @@
   <dimension ref="A1:O7"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="str">
+      <c r="A1" s="4" t="str">
         <v>STUDYID</v>
       </c>
-      <c r="B1" s="3" t="str">
+      <c r="B1" s="4" t="str">
         <v>DOMAIN</v>
       </c>
-      <c r="C1" s="3" t="str">
+      <c r="C1" s="4" t="str">
         <v>USUBJID</v>
       </c>
-      <c r="D1" s="3" t="str">
+      <c r="D1" s="4" t="str">
         <v>PPSEQ</v>
       </c>
-      <c r="E1" s="3" t="str">
+      <c r="E1" s="4" t="str">
         <v>PPGRPID</v>
       </c>
-      <c r="F1" s="3" t="str">
+      <c r="F1" s="4" t="str">
         <v>PPTESTCD</v>
       </c>
-      <c r="G1" s="3" t="str">
+      <c r="G1" s="4" t="str">
         <v>PPTEST</v>
       </c>
-      <c r="H1" s="3" t="str">
+      <c r="H1" s="4" t="str">
         <v>PPCAT</v>
       </c>
-      <c r="I1" s="3" t="str">
+      <c r="I1" s="4" t="str">
         <v>PPORRES</v>
       </c>
-      <c r="J1" s="3" t="str">
+      <c r="J1" s="4" t="str">
         <v>PPORRESU</v>
       </c>
-      <c r="K1" s="3" t="str">
+      <c r="K1" s="4" t="str">
         <v>PPSTRESC</v>
       </c>
-      <c r="L1" s="3" t="str">
+      <c r="L1" s="4" t="str">
         <v>PPSTRESN</v>
       </c>
-      <c r="M1" s="3" t="str">
+      <c r="M1" s="4" t="str">
         <v>PPSTRESU</v>
       </c>
-      <c r="N1" s="3" t="str">
+      <c r="N1" s="4" t="str">
         <v>PPSPEC</v>
       </c>
-      <c r="O1" s="3" t="str">
+      <c r="O1" s="4" t="str">
         <v>PPRFTDTC</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="str">
+      <c r="A2" s="5" t="str">
         <v>Study Identifier</v>
       </c>
-      <c r="B2" s="4" t="str">
+      <c r="B2" s="5" t="str">
         <v>Domain Abbreviation</v>
       </c>
-      <c r="C2" s="4" t="str">
+      <c r="C2" s="5" t="str">
         <v>Unique Subject Identifier</v>
       </c>
-      <c r="D2" s="4" t="str">
+      <c r="D2" s="5" t="str">
         <v>Sequence Number</v>
       </c>
-      <c r="E2" s="4" t="str">
+      <c r="E2" s="5" t="str">
         <v>Group ID</v>
       </c>
-      <c r="F2" s="4" t="str">
+      <c r="F2" s="5" t="str">
         <v>Parameter Short Name</v>
       </c>
-      <c r="G2" s="4" t="str">
+      <c r="G2" s="5" t="str">
         <v>Parameter Name</v>
       </c>
-      <c r="H2" s="4" t="str">
+      <c r="H2" s="5" t="str">
         <v>Parameter Category</v>
       </c>
-      <c r="I2" s="4" t="str">
+      <c r="I2" s="5" t="str">
         <v>Result or Finding in Original Units</v>
       </c>
-      <c r="J2" s="4" t="str">
+      <c r="J2" s="5" t="str">
         <v>Original Units</v>
       </c>
-      <c r="K2" s="4" t="str">
+      <c r="K2" s="5" t="str">
         <v>Character Result/Finding in Std Format</v>
       </c>
-      <c r="L2" s="4" t="str">
+      <c r="L2" s="5" t="str">
         <v>Numeric Result/Finding in Standard Units</v>
       </c>
-      <c r="M2" s="4" t="str">
+      <c r="M2" s="5" t="str">
         <v>Standard Units</v>
       </c>
-      <c r="N2" s="4" t="str">
+      <c r="N2" s="5" t="str">
         <v>Specimen Material Type</v>
       </c>
-      <c r="O2" s="4" t="str">
+      <c r="O2" s="5" t="str">
         <v>Date/Time of Reference Point</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="str">
-        <v>Char</v>
-      </c>
-      <c r="B3" s="4" t="str">
-        <v>Char</v>
-      </c>
-      <c r="C3" s="4" t="str">
-        <v>Char</v>
-      </c>
-      <c r="D3" s="4" t="str">
+      <c r="A3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="B3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="C3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="D3" s="5" t="str">
         <v>Num</v>
       </c>
-      <c r="E3" s="4" t="str">
-        <v>Char</v>
-      </c>
-      <c r="F3" s="4" t="str">
-        <v>Char</v>
-      </c>
-      <c r="G3" s="4" t="str">
-        <v>Char</v>
-      </c>
-      <c r="H3" s="4" t="str">
-        <v>Char</v>
-      </c>
-      <c r="I3" s="4" t="str">
-        <v>Char</v>
-      </c>
-      <c r="J3" s="4" t="str">
-        <v>Char</v>
-      </c>
-      <c r="K3" s="4" t="str">
-        <v>Char</v>
-      </c>
-      <c r="L3" s="4" t="str">
+      <c r="E3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="F3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="G3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="H3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="I3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="J3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="K3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="L3" s="5" t="str">
         <v>Num</v>
       </c>
-      <c r="M3" s="4" t="str">
-        <v>Char</v>
-      </c>
-      <c r="N3" s="4" t="str">
-        <v>Char</v>
-      </c>
-      <c r="O3" s="4" t="str">
+      <c r="M3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="N3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="O3" s="5" t="str">
         <v>Char</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="str">
-        <v>50</v>
-      </c>
-      <c r="B4" s="4" t="str">
-        <v>50</v>
-      </c>
-      <c r="C4" s="4" t="str">
-        <v>50</v>
-      </c>
-      <c r="D4" s="4" t="str">
+      <c r="A4" s="5" t="str">
+        <v>50</v>
+      </c>
+      <c r="B4" s="5" t="str">
+        <v>50</v>
+      </c>
+      <c r="C4" s="5" t="str">
+        <v>50</v>
+      </c>
+      <c r="D4" s="5" t="str">
         <v>8</v>
       </c>
-      <c r="E4" s="4" t="str">
-        <v>50</v>
-      </c>
-      <c r="F4" s="4" t="str">
-        <v>50</v>
-      </c>
-      <c r="G4" s="4" t="str">
-        <v>50</v>
-      </c>
-      <c r="H4" s="4" t="str">
-        <v>50</v>
-      </c>
-      <c r="I4" s="4" t="str">
-        <v>50</v>
-      </c>
-      <c r="J4" s="4" t="str">
-        <v>50</v>
-      </c>
-      <c r="K4" s="4" t="str">
-        <v>50</v>
-      </c>
-      <c r="L4" s="4" t="str">
+      <c r="E4" s="5" t="str">
+        <v>50</v>
+      </c>
+      <c r="F4" s="5" t="str">
+        <v>50</v>
+      </c>
+      <c r="G4" s="5" t="str">
+        <v>50</v>
+      </c>
+      <c r="H4" s="5" t="str">
+        <v>50</v>
+      </c>
+      <c r="I4" s="5" t="str">
+        <v>50</v>
+      </c>
+      <c r="J4" s="5" t="str">
+        <v>50</v>
+      </c>
+      <c r="K4" s="5" t="str">
+        <v>50</v>
+      </c>
+      <c r="L4" s="5" t="str">
         <v>8</v>
       </c>
-      <c r="M4" s="4" t="str">
-        <v>50</v>
-      </c>
-      <c r="N4" s="4" t="str">
-        <v>50</v>
-      </c>
-      <c r="O4" s="4" t="str">
+      <c r="M4" s="5" t="str">
+        <v>50</v>
+      </c>
+      <c r="N4" s="5" t="str">
+        <v>50</v>
+      </c>
+      <c r="O4" s="5" t="str">
         <v>50</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="str">
+      <c r="A5" s="6" t="str">
         <v>Sample001</v>
       </c>
-      <c r="B5" s="5" t="str">
+      <c r="B5" s="6" t="str">
         <v>PP</v>
       </c>
-      <c r="C5" s="5" t="str">
+      <c r="C5" s="6" t="str">
         <v>01-004</v>
       </c>
-      <c r="D5" s="5">
+      <c r="D5" s="6">
         <v>1</v>
       </c>
-      <c r="E5" s="5" t="str">
+      <c r="E5" s="6" t="str">
         <v>Part A Period 1</v>
       </c>
-      <c r="F5" s="5" t="str">
+      <c r="F5" s="6" t="str">
         <v>AUCIFP</v>
       </c>
-      <c r="G5" s="5" t="str">
+      <c r="G5" s="6" t="str">
         <v>AUC Infinity Pred</v>
       </c>
-      <c r="H5" s="5" t="str">
+      <c r="H5" s="6" t="str">
         <v>PPCAT01</v>
       </c>
-      <c r="I5" s="5">
+      <c r="I5" s="6">
         <v>1194.546</v>
       </c>
-      <c r="J5" s="5" t="str">
+      <c r="J5" s="6" t="str">
         <v>h*ng/mL</v>
       </c>
-      <c r="K5" s="5">
+      <c r="K5" s="6">
         <v>1195</v>
       </c>
-      <c r="L5" s="5">
+      <c r="L5" s="6">
         <v>1195</v>
       </c>
-      <c r="M5" s="5" t="str">
+      <c r="M5" s="6" t="str">
         <v>h*ng/mL</v>
       </c>
-      <c r="N5" s="5" t="str">
+      <c r="N5" s="6" t="str">
         <v>PLASMA</v>
       </c>
-      <c r="O5" s="5" t="str">
+      <c r="O5" s="6" t="str">
         <v>2018-04-09T09:05</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="str">
+      <c r="A6" s="6" t="str">
         <v>Sample001</v>
       </c>
-      <c r="B6" s="5" t="str">
+      <c r="B6" s="6" t="str">
         <v>PP</v>
       </c>
-      <c r="C6" s="5" t="str">
+      <c r="C6" s="6" t="str">
         <v>01-005</v>
       </c>
-      <c r="D6" s="5">
+      <c r="D6" s="6">
         <v>1</v>
       </c>
-      <c r="E6" s="5" t="str">
+      <c r="E6" s="6" t="str">
         <v>Part A Period 1</v>
       </c>
-      <c r="F6" s="5" t="str">
-        <v>AUCIFP</v>
-      </c>
-      <c r="G6" s="5" t="str">
+      <c r="F6" s="6" t="str">
+        <v>AUCIFPW</v>
+      </c>
+      <c r="G6" s="6" t="str">
         <v>AURC Infinity Obs Norm by WT</v>
       </c>
-      <c r="H6" s="5" t="str">
+      <c r="H6" s="6" t="str">
         <v>PPCAT01</v>
       </c>
-      <c r="I6" s="5">
+      <c r="I6" s="6">
         <v>1194.546</v>
       </c>
-      <c r="J6" s="5" t="str">
+      <c r="J6" s="6" t="str">
         <v>day*mg/mL/g</v>
       </c>
-      <c r="K6" s="5">
+      <c r="K6" s="6">
         <v>1195</v>
       </c>
-      <c r="L6" s="5">
+      <c r="L6" s="6">
         <v>1195</v>
       </c>
-      <c r="M6" s="5" t="str">
+      <c r="M6" s="6" t="str">
         <v>day*mg/mL/g</v>
       </c>
-      <c r="N6" s="5" t="str">
+      <c r="N6" s="6" t="str">
         <v>PLASMA</v>
       </c>
-      <c r="O6" s="5" t="str">
+      <c r="O6" s="6" t="str">
         <v>2018-04-09T09:05</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="str">
+      <c r="A7" s="6" t="str">
         <v>Sample001</v>
       </c>
-      <c r="B7" s="5" t="str">
+      <c r="B7" s="6" t="str">
         <v>PP</v>
       </c>
-      <c r="C7" s="5" t="str">
+      <c r="C7" s="6" t="str">
         <v>01-006</v>
       </c>
-      <c r="D7" s="5">
+      <c r="D7" s="6">
         <v>1</v>
       </c>
-      <c r="E7" s="5" t="str">
+      <c r="E7" s="6" t="str">
         <v>Part A Period 1</v>
       </c>
-      <c r="F7" s="5" t="str">
-        <v>AUCIFP</v>
-      </c>
-      <c r="G7" s="5" t="str">
+      <c r="F7" s="6" t="str">
+        <v>AUCIFPW</v>
+      </c>
+      <c r="G7" s="6" t="str">
         <v>AURC Infinity Obs Norm by WT</v>
       </c>
-      <c r="H7" s="5" t="str">
+      <c r="H7" s="6" t="str">
         <v>PPCAT01</v>
       </c>
-      <c r="I7" s="5">
+      <c r="I7" s="6">
         <v>1194.546</v>
       </c>
-      <c r="J7" s="5" t="str">
+      <c r="J7" s="6" t="str">
         <v>h*ng/mL/kg</v>
       </c>
-      <c r="K7" s="5">
+      <c r="K7" s="6">
         <v>1195</v>
       </c>
-      <c r="L7" s="5">
+      <c r="L7" s="6">
         <v>1195</v>
       </c>
-      <c r="M7" s="5" t="str">
+      <c r="M7" s="6" t="str">
         <v>h*ng/mL/kg</v>
       </c>
-      <c r="N7" s="5" t="str">
+      <c r="N7" s="6" t="str">
         <v>PLASMA</v>
       </c>
-      <c r="O7" s="5" t="str">
+      <c r="O7" s="6" t="str">
         <v>2018-04-09T09:05</v>
       </c>
     </row>

--- a/rules/NEW-RULE/positive/01/data/new-rule-positive-01.xlsx
+++ b/rules/NEW-RULE/positive/01/data/new-rule-positive-01.xlsx
@@ -1,40 +1,132 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rich/Documents/github/core-contributor/rules/NEW-RULE/positive/01/data/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D46CB74-AE58-9C41-8770-9F83AF085134}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
     <sheet name="Library" sheetId="1" r:id="rId1"/>
     <sheet name="Datasets" sheetId="2" r:id="rId2"/>
     <sheet name="cm.xpt" sheetId="3" r:id="rId3"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="33">
+  <si>
+    <t>Product</t>
+  </si>
+  <si>
+    <t>Version</t>
+  </si>
+  <si>
+    <t>sdtmig</t>
+  </si>
+  <si>
+    <t>3-4</t>
+  </si>
+  <si>
+    <t>Filename</t>
+  </si>
+  <si>
+    <t>Label</t>
+  </si>
+  <si>
+    <t>cm.xpt</t>
+  </si>
+  <si>
+    <t>Concomitant Medications</t>
+  </si>
+  <si>
+    <t>STUDYID</t>
+  </si>
+  <si>
+    <t>DOMAIN</t>
+  </si>
+  <si>
+    <t>USUBJID</t>
+  </si>
+  <si>
+    <t>CMSEQ</t>
+  </si>
+  <si>
+    <t>CMCLAS</t>
+  </si>
+  <si>
+    <t>CMCLASCD</t>
+  </si>
+  <si>
+    <t>Study Identifier</t>
+  </si>
+  <si>
+    <t>Domain Abbreviation</t>
+  </si>
+  <si>
+    <t>Unique Subject Identifier</t>
+  </si>
+  <si>
+    <t>Sequence Number</t>
+  </si>
+  <si>
+    <t>Medication Class</t>
+  </si>
+  <si>
+    <t>Medication Class Code</t>
+  </si>
+  <si>
+    <t>Char</t>
+  </si>
+  <si>
+    <t>Num</t>
+  </si>
+  <si>
+    <t>STUDY001</t>
+  </si>
+  <si>
+    <t>CM</t>
+  </si>
+  <si>
+    <t>STUDY001-SUBJ0001</t>
+  </si>
+  <si>
+    <t>Platelet aggregation inhibitors excl. heparin</t>
+  </si>
+  <si>
+    <t>B01AC</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Aspirin</t>
+  </si>
+  <si>
+    <t>CMTRT</t>
+  </si>
+  <si>
+    <t>CMDECOD</t>
+  </si>
+  <si>
+    <t>Reported Name of Drug, Med, or Therapy</t>
+  </si>
+  <si>
+    <t>Standardized Medication Name</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <numFmts count="0"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -43,48 +135,40 @@
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
       <name val="Calibri"/>
-      <b/>
+      <family val="2"/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
       <name val="Calibri"/>
-      <i/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
     <fill>
-      <patternFill patternType="none">
-        <bgColor/>
-      </patternFill>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="gray125">
-        <bgColor/>
-      </patternFill>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
-        <bgColor/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -93,22 +177,29 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs>
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="1" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -433,237 +524,286 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="3" t="str">
-        <v>Product</v>
-      </c>
-      <c r="B1" s="3" t="str">
-        <v>Version</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="3" t="str">
-        <v>sdtmig</v>
-      </c>
-      <c r="B2" s="3" t="str">
-        <v>3-4</v>
+    <row r="1" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B2"/>
+    <ignoredError sqref="A1:B2" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="3" t="str">
-        <v>Filename</v>
-      </c>
-      <c r="B1" s="3" t="str">
-        <v>Label</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="3" t="str">
-        <v>cm.xpt</v>
-      </c>
-      <c r="B2" s="3" t="str">
-        <v>Concomitant Medications</v>
+    <row r="1" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B2"/>
+    <ignoredError sqref="A1:B2" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F9"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:H9"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="4" t="str">
-        <v>STUDYID</v>
-      </c>
-      <c r="B1" s="4" t="str">
-        <v>DOMAIN</v>
-      </c>
-      <c r="C1" s="4" t="str">
-        <v>USUBJID</v>
-      </c>
-      <c r="D1" s="4" t="str">
-        <v>CMSEQ</v>
-      </c>
-      <c r="E1" s="4" t="str">
-        <v>CMCLAS</v>
-      </c>
-      <c r="F1" s="4" t="str">
-        <v>CMCLASCD</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="5" t="str">
-        <v>Study Identifier</v>
-      </c>
-      <c r="B2" s="5" t="str">
-        <v>Domain Abbreviation</v>
-      </c>
-      <c r="C2" s="5" t="str">
-        <v>Unique Subject Identifier</v>
-      </c>
-      <c r="D2" s="5" t="str">
-        <v>Sequence Number</v>
-      </c>
-      <c r="E2" s="5" t="str">
-        <v>Medication Class</v>
-      </c>
-      <c r="F2" s="5" t="str">
-        <v>Medication Class Code</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="5" t="str">
-        <v>Char</v>
-      </c>
-      <c r="B3" s="5" t="str">
-        <v>Char</v>
-      </c>
-      <c r="C3" s="5" t="str">
-        <v>Char</v>
-      </c>
-      <c r="D3" s="5" t="str">
-        <v>Num</v>
-      </c>
-      <c r="E3" s="5" t="str">
-        <v>Char</v>
-      </c>
-      <c r="F3" s="5" t="str">
-        <v>Char</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="5">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A2" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A3" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A4" s="3">
         <v>50</v>
       </c>
-      <c r="B4" s="5">
+      <c r="B4" s="3">
         <v>50</v>
       </c>
-      <c r="C4" s="5">
+      <c r="C4" s="3">
         <v>50</v>
       </c>
-      <c r="D4" s="5">
+      <c r="D4" s="3">
         <v>8</v>
       </c>
-      <c r="E4" s="5">
+      <c r="E4" s="3">
         <v>50</v>
       </c>
-      <c r="F4" s="5">
+      <c r="F4" s="3">
         <v>50</v>
       </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="str">
-        <v>STUDY001</v>
-      </c>
-      <c r="B5" s="3" t="str">
-        <v>CM</v>
-      </c>
-      <c r="C5" s="3" t="str">
-        <v>STUDY001-SUBJ0001</v>
-      </c>
-      <c r="D5" s="3">
+      <c r="G4" s="3">
+        <v>50</v>
+      </c>
+      <c r="H4" s="3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A5" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D5" s="1">
         <v>1</v>
       </c>
-      <c r="E5" s="3" t="str">
-        <v>Platelet aggregation inhibitors excl. heparin</v>
-      </c>
-      <c r="F5" s="3" t="str">
-        <v>B01AC</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="str">
-        <v>STUDY001</v>
-      </c>
-      <c r="B6" s="3" t="str">
-        <v>CM</v>
-      </c>
-      <c r="C6" s="3" t="str">
-        <v>STUDY001-SUBJ0001</v>
-      </c>
-      <c r="D6" s="3">
+      <c r="E5" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A6" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D6" s="1">
         <v>1</v>
       </c>
-      <c r="E6" s="3" t="str">
-        <v>Platelet aggregation inhibitors excl. heparin</v>
-      </c>
-      <c r="F6" s="2" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="str">
-        <v/>
-      </c>
-      <c r="B7" s="3" t="str">
-        <v/>
-      </c>
-      <c r="C7" s="3" t="str">
-        <v/>
-      </c>
-      <c r="D7" s="3" t="str">
-        <v/>
-      </c>
-      <c r="E7" s="3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="str">
-        <v/>
-      </c>
-      <c r="B8" s="3" t="str">
-        <v/>
-      </c>
-      <c r="C8" s="3" t="str">
-        <v/>
-      </c>
-      <c r="D8" s="3" t="str">
-        <v/>
-      </c>
-      <c r="E8" s="3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="str">
-        <v/>
-      </c>
-      <c r="B9" s="3" t="str">
-        <v/>
-      </c>
-      <c r="C9" s="3" t="str">
-        <v/>
-      </c>
-      <c r="D9" s="3" t="str">
-        <v/>
-      </c>
-      <c r="E9" s="3" t="str">
-        <v/>
+      <c r="E6" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H6" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A7" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1"/>
+      <c r="G7" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A8" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A9" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F9"/>
+    <ignoredError sqref="G1:H9 A1:D9" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/rules/NEW-RULE/positive/01/data/new-rule-positive-01.xlsx
+++ b/rules/NEW-RULE/positive/01/data/new-rule-positive-01.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/enrico/Work/core-contributor/rules/NEW-RULE/positive/01/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{241BD48C-2FAC-ED46-AD83-5B3DD0C3686D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C0E1BDC-70E9-4E48-BED1-0CF59552A6CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30240" yWindow="-4560" windowWidth="51200" windowHeight="28800" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30240" yWindow="-4560" windowWidth="51200" windowHeight="28800" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Library" sheetId="1" r:id="rId1"/>
@@ -711,7 +711,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -720,8 +720,7 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1428,10 +1427,10 @@
       <c r="F5" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="G5" s="9" t="s">
+      <c r="G5" s="8" t="s">
         <v>138</v>
       </c>
-      <c r="H5" s="9" t="s">
+      <c r="H5" s="8" t="s">
         <v>159</v>
       </c>
       <c r="I5" s="3" t="s">
@@ -1502,10 +1501,10 @@
       <c r="F6" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="G6" s="9" t="s">
+      <c r="G6" s="8" t="s">
         <v>162</v>
       </c>
-      <c r="H6" s="9" t="s">
+      <c r="H6" s="8" t="s">
         <v>164</v>
       </c>
       <c r="I6" s="3" t="s">
@@ -1578,10 +1577,10 @@
       <c r="F7" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="G7" s="9" t="s">
+      <c r="G7" s="8" t="s">
         <v>167</v>
       </c>
-      <c r="H7" s="9" t="s">
+      <c r="H7" s="8" t="s">
         <v>166</v>
       </c>
       <c r="I7" s="3" t="s">
@@ -1652,10 +1651,10 @@
       <c r="F8" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="G8" s="9" t="s">
+      <c r="G8" s="8" t="s">
         <v>170</v>
       </c>
-      <c r="H8" s="9" t="s">
+      <c r="H8" s="8" t="s">
         <v>171</v>
       </c>
       <c r="I8" s="3" t="s">
@@ -1720,10 +1719,10 @@
       <c r="F9" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="G9" s="9" t="s">
+      <c r="G9" s="8" t="s">
         <v>174</v>
       </c>
-      <c r="H9" s="9" t="s">
+      <c r="H9" s="8" t="s">
         <v>173</v>
       </c>
       <c r="I9" s="3" t="s">
@@ -1792,10 +1791,10 @@
       <c r="F10" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="G10" s="9" t="s">
+      <c r="G10" s="8" t="s">
         <v>176</v>
       </c>
-      <c r="H10" s="9" t="s">
+      <c r="H10" s="8" t="s">
         <v>157</v>
       </c>
       <c r="I10" s="3" t="s">
@@ -1860,10 +1859,10 @@
       <c r="F11" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="G11" s="9" t="s">
+      <c r="G11" s="8" t="s">
         <v>177</v>
       </c>
-      <c r="H11" s="9" t="s">
+      <c r="H11" s="8" t="s">
         <v>179</v>
       </c>
       <c r="I11" s="3" t="s">
@@ -1934,10 +1933,10 @@
       <c r="F12" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="G12" s="9" t="s">
+      <c r="G12" s="8" t="s">
         <v>182</v>
       </c>
-      <c r="H12" s="9" t="s">
+      <c r="H12" s="8" t="s">
         <v>183</v>
       </c>
       <c r="I12" s="3" t="s">
@@ -2010,10 +2009,10 @@
       <c r="F13" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="G13" s="9" t="s">
+      <c r="G13" s="8" t="s">
         <v>185</v>
       </c>
-      <c r="H13" s="9" t="s">
+      <c r="H13" s="8" t="s">
         <v>153</v>
       </c>
       <c r="I13" s="3" t="s">
@@ -2084,10 +2083,10 @@
       <c r="F14" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="G14" s="9" t="s">
+      <c r="G14" s="8" t="s">
         <v>187</v>
       </c>
-      <c r="H14" s="9" t="s">
+      <c r="H14" s="8" t="s">
         <v>187</v>
       </c>
       <c r="I14" s="3" t="s">
@@ -2449,7 +2448,7 @@
       <c r="Q5" s="8" t="s">
         <v>139</v>
       </c>
-      <c r="R5" s="3" t="s">
+      <c r="R5" s="8" t="s">
         <v>138</v>
       </c>
       <c r="S5" s="3">
@@ -2511,7 +2510,7 @@
       <c r="Q6" s="8" t="s">
         <v>140</v>
       </c>
-      <c r="R6" s="3" t="s">
+      <c r="R6" s="8" t="s">
         <v>139</v>
       </c>
       <c r="S6" s="3">
@@ -2573,7 +2572,7 @@
       <c r="Q7" s="8" t="s">
         <v>141</v>
       </c>
-      <c r="R7" s="3" t="s">
+      <c r="R7" s="8" t="s">
         <v>140</v>
       </c>
       <c r="S7" s="3">
@@ -2635,7 +2634,7 @@
       <c r="Q8" s="8" t="s">
         <v>142</v>
       </c>
-      <c r="R8" s="3" t="s">
+      <c r="R8" s="8" t="s">
         <v>141</v>
       </c>
       <c r="S8" s="3">
@@ -2697,7 +2696,7 @@
       <c r="Q9" s="8" t="s">
         <v>143</v>
       </c>
-      <c r="R9" s="3" t="s">
+      <c r="R9" s="8" t="s">
         <v>142</v>
       </c>
       <c r="S9" s="3">
@@ -2759,7 +2758,7 @@
       <c r="Q10" s="8" t="s">
         <v>144</v>
       </c>
-      <c r="R10" s="3" t="s">
+      <c r="R10" s="8" t="s">
         <v>143</v>
       </c>
       <c r="S10" s="3">
@@ -2821,7 +2820,7 @@
       <c r="Q11" s="8" t="s">
         <v>145</v>
       </c>
-      <c r="R11" s="3" t="s">
+      <c r="R11" s="8" t="s">
         <v>144</v>
       </c>
       <c r="S11" s="3">
@@ -2883,7 +2882,7 @@
       <c r="Q12" s="8" t="s">
         <v>146</v>
       </c>
-      <c r="R12" s="3" t="s">
+      <c r="R12" s="8" t="s">
         <v>145</v>
       </c>
       <c r="S12" s="3">
@@ -2945,7 +2944,7 @@
       <c r="Q13" s="8" t="s">
         <v>147</v>
       </c>
-      <c r="R13" s="3" t="s">
+      <c r="R13" s="8" t="s">
         <v>146</v>
       </c>
       <c r="S13" s="3">
@@ -3007,7 +3006,7 @@
       <c r="Q14" s="8" t="s">
         <v>190</v>
       </c>
-      <c r="R14" s="3" t="s">
+      <c r="R14" s="8" t="s">
         <v>147</v>
       </c>
       <c r="S14" s="3">
@@ -3069,7 +3068,7 @@
       <c r="Q15" s="8" t="s">
         <v>191</v>
       </c>
-      <c r="R15" s="3" t="s">
+      <c r="R15" s="8" t="s">
         <v>150</v>
       </c>
       <c r="S15" s="3">
@@ -3131,7 +3130,7 @@
       <c r="Q16" s="8" t="s">
         <v>192</v>
       </c>
-      <c r="R16" s="3" t="s">
+      <c r="R16" s="8" t="s">
         <v>151</v>
       </c>
       <c r="S16" s="3">
@@ -3193,7 +3192,7 @@
       <c r="Q17" s="8" t="s">
         <v>193</v>
       </c>
-      <c r="R17" s="3" t="s">
+      <c r="R17" s="8" t="s">
         <v>152</v>
       </c>
       <c r="S17" s="3">
@@ -3255,7 +3254,7 @@
       <c r="Q18" s="8" t="s">
         <v>194</v>
       </c>
-      <c r="R18" s="3" t="s">
+      <c r="R18" s="8" t="s">
         <v>154</v>
       </c>
       <c r="S18" s="3">
@@ -3317,7 +3316,7 @@
       <c r="Q19" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="R19" s="3" t="s">
+      <c r="R19" s="8" t="s">
         <v>155</v>
       </c>
       <c r="S19" s="3">
@@ -3379,7 +3378,7 @@
       <c r="Q20" s="8" t="s">
         <v>196</v>
       </c>
-      <c r="R20" s="3" t="s">
+      <c r="R20" s="8" t="s">
         <v>158</v>
       </c>
       <c r="S20" s="3">

--- a/rules/NEW-RULE/positive/01/data/new-rule-positive-01.xlsx
+++ b/rules/NEW-RULE/positive/01/data/new-rule-positive-01.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rich/Documents/github/core-contributor/rules/NEW-RULE/positive/01/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E8881B5-FE43-F44B-88AE-203ABD5D84BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D639977E-2DD7-334A-8240-BA648A729613}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="41960" yWindow="-3520" windowWidth="30240" windowHeight="18980" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Library" sheetId="1" r:id="rId1"/>
@@ -832,11 +832,11 @@
       <c r="D5" t="s">
         <v>24</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E5" t="s">
+        <v>25</v>
+      </c>
+      <c r="F5" s="5" t="s">
         <v>42</v>
-      </c>
-      <c r="F5" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="16" x14ac:dyDescent="0.2">
@@ -849,11 +849,11 @@
       <c r="D6" t="s">
         <v>24</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F6" s="5" t="s">
         <v>42</v>
-      </c>
-      <c r="F6" t="s">
-        <v>25</v>
       </c>
       <c r="G6" t="s">
         <v>28</v>
@@ -869,11 +869,11 @@
       <c r="D7" t="s">
         <v>24</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="E7" t="s">
+        <v>28</v>
+      </c>
+      <c r="F7" s="5" t="s">
         <v>42</v>
-      </c>
-      <c r="F7" t="s">
-        <v>28</v>
       </c>
       <c r="G7" t="s">
         <v>30</v>
@@ -889,11 +889,11 @@
       <c r="D8" t="s">
         <v>24</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="E8" t="s">
+        <v>30</v>
+      </c>
+      <c r="F8" s="5" t="s">
         <v>42</v>
-      </c>
-      <c r="F8" t="s">
-        <v>30</v>
       </c>
       <c r="G8" t="s">
         <v>32</v>
@@ -909,11 +909,11 @@
       <c r="D9" t="s">
         <v>35</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="E9" t="s">
+        <v>36</v>
+      </c>
+      <c r="F9" s="5" t="s">
         <v>42</v>
-      </c>
-      <c r="F9" t="s">
-        <v>36</v>
       </c>
       <c r="G9" t="s">
         <v>37</v>
@@ -932,11 +932,11 @@
       <c r="D10" t="s">
         <v>24</v>
       </c>
-      <c r="E10" s="5" t="s">
+      <c r="E10" t="s">
+        <v>39</v>
+      </c>
+      <c r="F10" s="5" t="s">
         <v>73</v>
-      </c>
-      <c r="F10" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
@@ -950,10 +950,10 @@
         <v>24</v>
       </c>
       <c r="E11" t="s">
+        <v>40</v>
+      </c>
+      <c r="F11" t="s">
         <v>74</v>
-      </c>
-      <c r="F11" t="s">
-        <v>40</v>
       </c>
       <c r="G11" t="s">
         <v>41</v>

--- a/rules/NEW-RULE/positive/01/data/new-rule-positive-01.xlsx
+++ b/rules/NEW-RULE/positive/01/data/new-rule-positive-01.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rich/Documents/github/core-contributor/rules/NEW-RULE/positive/01/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A88199F2-B4CE-4C4C-B3B6-8B3E53301F6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52D7A594-AC92-6F40-AB3D-C9475E67DD23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2320" yWindow="1320" windowWidth="30240" windowHeight="18980" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="39080" yWindow="-1720" windowWidth="30240" windowHeight="18980" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Library" sheetId="1" r:id="rId1"/>
@@ -795,10 +795,10 @@
         <v>29</v>
       </c>
       <c r="H6">
+        <v>3</v>
+      </c>
+      <c r="I6">
         <v>4</v>
-      </c>
-      <c r="I6">
-        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="16" x14ac:dyDescent="0.2">
@@ -821,10 +821,10 @@
         <v>31</v>
       </c>
       <c r="H7">
+        <v>5</v>
+      </c>
+      <c r="I7">
         <v>66</v>
-      </c>
-      <c r="I7">
-        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="16" x14ac:dyDescent="0.2">
@@ -847,10 +847,10 @@
         <v>33</v>
       </c>
       <c r="H8">
+        <v>20</v>
+      </c>
+      <c r="I8">
         <v>2000</v>
-      </c>
-      <c r="I8">
-        <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="16" x14ac:dyDescent="0.2">
@@ -873,10 +873,10 @@
         <v>38</v>
       </c>
       <c r="H9">
+        <v>1</v>
+      </c>
+      <c r="I9">
         <v>51</v>
-      </c>
-      <c r="I9">
-        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="16" x14ac:dyDescent="0.2">
@@ -898,7 +898,7 @@
       <c r="F10" t="s">
         <v>41</v>
       </c>
-      <c r="H10">
+      <c r="I10">
         <v>5</v>
       </c>
     </row>
@@ -921,7 +921,7 @@
       <c r="G11" t="s">
         <v>43</v>
       </c>
-      <c r="I11">
+      <c r="H11">
         <v>4</v>
       </c>
     </row>

--- a/rules/NEW-RULE/positive/01/data/new-rule-positive-01.xlsx
+++ b/rules/NEW-RULE/positive/01/data/new-rule-positive-01.xlsx
@@ -1,40 +1,346 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11214"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/maxverisian/verisian/core-contributor/rules/NEW-RULE/positive/01/data/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2EB0E31-73E5-1142-B07F-494A66FA84DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
     <sheet name="Library" sheetId="1" r:id="rId1"/>
     <sheet name="Datasets" sheetId="2" r:id="rId2"/>
-    <sheet name="ts.xpt" sheetId="3" r:id="rId3"/>
+    <sheet name="ae.xpt" sheetId="3" r:id="rId3"/>
+    <sheet name="ts.xpt" sheetId="4" r:id="rId4"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="104">
+  <si>
+    <t>Product</t>
+  </si>
+  <si>
+    <t>Version</t>
+  </si>
+  <si>
+    <t>sdtmig</t>
+  </si>
+  <si>
+    <t>3-4</t>
+  </si>
+  <si>
+    <t>Filename</t>
+  </si>
+  <si>
+    <t>Label</t>
+  </si>
+  <si>
+    <t>ae.xpt</t>
+  </si>
+  <si>
+    <t>Adverse Events</t>
+  </si>
+  <si>
+    <t>ts.xpt</t>
+  </si>
+  <si>
+    <t>Trial Summary Parameters</t>
+  </si>
+  <si>
+    <t>STUDYID</t>
+  </si>
+  <si>
+    <t>DOMAIN</t>
+  </si>
+  <si>
+    <t>USUBJID</t>
+  </si>
+  <si>
+    <t>AESEQ</t>
+  </si>
+  <si>
+    <t>AETERM</t>
+  </si>
+  <si>
+    <t>AESEV</t>
+  </si>
+  <si>
+    <t>AESER</t>
+  </si>
+  <si>
+    <t>AEACN</t>
+  </si>
+  <si>
+    <t>AEREL</t>
+  </si>
+  <si>
+    <t>AEOUT</t>
+  </si>
+  <si>
+    <t>AESCAN</t>
+  </si>
+  <si>
+    <t>AESCONG</t>
+  </si>
+  <si>
+    <t>AESDISAB</t>
+  </si>
+  <si>
+    <t>AESDTH</t>
+  </si>
+  <si>
+    <t>AESHOSP</t>
+  </si>
+  <si>
+    <t>AESLIFE</t>
+  </si>
+  <si>
+    <t>AESOD</t>
+  </si>
+  <si>
+    <t>AESMIE</t>
+  </si>
+  <si>
+    <t>AECONTRT</t>
+  </si>
+  <si>
+    <t>EPOCH</t>
+  </si>
+  <si>
+    <t>AESTDTC</t>
+  </si>
+  <si>
+    <t>AEENDTC</t>
+  </si>
+  <si>
+    <t>AESTDY</t>
+  </si>
+  <si>
+    <t>AEENDY</t>
+  </si>
+  <si>
+    <t>AEENRTPT</t>
+  </si>
+  <si>
+    <t>AEENTPT</t>
+  </si>
+  <si>
+    <t>Study Identifier</t>
+  </si>
+  <si>
+    <t>Domain Abbreviation</t>
+  </si>
+  <si>
+    <t>Unique Subject Identifier</t>
+  </si>
+  <si>
+    <t>Sequence Number</t>
+  </si>
+  <si>
+    <t>Reported Term for the Adverse Event</t>
+  </si>
+  <si>
+    <t>Severity/Intensity</t>
+  </si>
+  <si>
+    <t>Serious Event</t>
+  </si>
+  <si>
+    <t>Action Taken with Study Treatment</t>
+  </si>
+  <si>
+    <t>Causality</t>
+  </si>
+  <si>
+    <t>Outcome of Adverse Event</t>
+  </si>
+  <si>
+    <t>Involves Cancer</t>
+  </si>
+  <si>
+    <t>Congenital Anomaly or Birth Defect</t>
+  </si>
+  <si>
+    <t>Persist or Signif Disability/Incapacity</t>
+  </si>
+  <si>
+    <t>Results in Death</t>
+  </si>
+  <si>
+    <t>Requires or Prolongs Hospitalization</t>
+  </si>
+  <si>
+    <t>Is Life Threatening</t>
+  </si>
+  <si>
+    <t>Occurred with Overdose</t>
+  </si>
+  <si>
+    <t>Other Medically Important Serious Event</t>
+  </si>
+  <si>
+    <t>Concomitant or Additional Trtmnt Given</t>
+  </si>
+  <si>
+    <t>Epoch</t>
+  </si>
+  <si>
+    <t>Start Date/Time of Adverse Event</t>
+  </si>
+  <si>
+    <t>End Date/Time of Adverse Event</t>
+  </si>
+  <si>
+    <t>Study Day of Start of Adverse Event</t>
+  </si>
+  <si>
+    <t>Study Day of End of Adverse Event</t>
+  </si>
+  <si>
+    <t>End Relative to Reference Time Point</t>
+  </si>
+  <si>
+    <t>End Reference Time Point</t>
+  </si>
+  <si>
+    <t>Char</t>
+  </si>
+  <si>
+    <t>Num</t>
+  </si>
+  <si>
+    <t>50</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>CDISCPILOT01</t>
+  </si>
+  <si>
+    <t>AE</t>
+  </si>
+  <si>
+    <t>CDISC001</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>INJECTION SITE REACTION</t>
+  </si>
+  <si>
+    <t>MODERATE</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>DRUG WITHDRAWN</t>
+  </si>
+  <si>
+    <t>RELATED</t>
+  </si>
+  <si>
+    <t>NOT RECOVERED/NOT RESOLVED</t>
+  </si>
+  <si>
+    <t>TREATMENT</t>
+  </si>
+  <si>
+    <t>2012-12-02</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>ONGOING</t>
+  </si>
+  <si>
+    <t>2013-05-20</t>
+  </si>
+  <si>
+    <t>TSSEQ</t>
+  </si>
+  <si>
+    <t>TSGRPID</t>
+  </si>
+  <si>
+    <t>TSPARMCD</t>
+  </si>
+  <si>
+    <t>TSPARM</t>
+  </si>
+  <si>
+    <t>TSVAL</t>
+  </si>
+  <si>
+    <t>TSVALNF</t>
+  </si>
+  <si>
+    <t>TSVALCD</t>
+  </si>
+  <si>
+    <t>TSVCDREF</t>
+  </si>
+  <si>
+    <t>TSVCDVER</t>
+  </si>
+  <si>
+    <t>Group ID</t>
+  </si>
+  <si>
+    <t>Trial Summary Parameter Short Name</t>
+  </si>
+  <si>
+    <t>Trial Summary Parameter</t>
+  </si>
+  <si>
+    <t>Parameter Value</t>
+  </si>
+  <si>
+    <t>Parameter Null Flavor</t>
+  </si>
+  <si>
+    <t>Parameter Value Code</t>
+  </si>
+  <si>
+    <t>Name of the Reference Terminology</t>
+  </si>
+  <si>
+    <t>Version of the Reference Terminology</t>
+  </si>
+  <si>
+    <t>TS</t>
+  </si>
+  <si>
+    <t>SSTDTC</t>
+  </si>
+  <si>
+    <t>Study Start Date</t>
+  </si>
+  <si>
+    <t>2026-03-02</t>
+  </si>
+  <si>
+    <t>ISO 8601</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <numFmts count="0"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -43,59 +349,52 @@
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <i/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <i/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
     <fill>
-      <patternFill patternType="none">
-        <bgColor/>
-      </patternFill>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="gray125">
-        <bgColor/>
+      <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -104,23 +403,30 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs>
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="1" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -445,238 +751,665 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="str">
-        <v>Product</v>
-      </c>
-      <c r="B1" s="2" t="str">
-        <v>Version</v>
+    <row r="1" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="str">
-        <v>sdtmig</v>
-      </c>
-      <c r="B2" s="2" t="str">
-        <v>3-4</v>
+    <row r="2" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" t="s">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B2"/>
+    <ignoredError sqref="A1:B2" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="str">
-        <v>Filename</v>
-      </c>
-      <c r="B1" s="2" t="str">
-        <v>Label</v>
+    <row r="1" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" t="s">
+        <v>5</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="str">
-        <v>ts.xpt</v>
-      </c>
-      <c r="B2" s="2" t="str">
-        <v>Trial Summary Parameters</v>
+    <row r="2" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B2"/>
+    <ignoredError sqref="A1:B3" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:Z5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="3" t="str">
-        <v>STUDYID</v>
-      </c>
-      <c r="B1" s="3" t="str">
-        <v>DOMAIN</v>
-      </c>
-      <c r="C1" s="3" t="str">
-        <v>TSSEQ</v>
-      </c>
-      <c r="D1" s="3" t="str">
-        <v>TSGRPID</v>
-      </c>
-      <c r="E1" s="3" t="str">
-        <v>TSPARMCD</v>
-      </c>
-      <c r="F1" s="3" t="str">
-        <v>TSPARM</v>
-      </c>
-      <c r="G1" s="3" t="str">
-        <v>TSVAL</v>
-      </c>
-      <c r="H1" s="3" t="str">
-        <v>TSVALNF</v>
-      </c>
-      <c r="I1" s="3" t="str">
-        <v>TSVALCD</v>
-      </c>
-      <c r="J1" s="3" t="str">
-        <v>TSVCDREF</v>
-      </c>
-      <c r="K1" s="3" t="str">
-        <v>TSVCDVER</v>
+    <row r="1" spans="1:26" ht="15" x14ac:dyDescent="0.2">
+      <c r="A1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="R1" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="T1" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="U1" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="V1" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="W1" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="X1" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="Y1" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="Z1" s="2" t="s">
+        <v>35</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="4" t="str">
-        <v>Study Identifier</v>
-      </c>
-      <c r="B2" s="5" t="str">
-        <v>Domain Abbreviation</v>
-      </c>
-      <c r="C2" s="5" t="str">
-        <v>Sequence Number</v>
-      </c>
-      <c r="D2" s="5" t="str">
-        <v>Group ID</v>
-      </c>
-      <c r="E2" s="5" t="str">
-        <v>Trial Summary Parameter Short Name</v>
-      </c>
-      <c r="F2" s="5" t="str">
-        <v>Trial Summary Parameter</v>
-      </c>
-      <c r="G2" s="5" t="str">
-        <v>Parameter Value</v>
-      </c>
-      <c r="H2" s="5" t="str">
-        <v>Parameter Null Flavor</v>
-      </c>
-      <c r="I2" s="5" t="str">
-        <v>Parameter Value Code</v>
-      </c>
-      <c r="J2" s="5" t="str">
-        <v>Name of the Reference Terminology</v>
-      </c>
-      <c r="K2" s="5" t="str">
-        <v>Version of the Reference Terminology</v>
+    <row r="2" spans="1:26" ht="15" x14ac:dyDescent="0.2">
+      <c r="A2" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="L2" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="M2" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="N2" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="O2" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="P2" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q2" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="R2" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="S2" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="T2" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="U2" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="V2" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="W2" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="X2" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="Y2" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="Z2" s="4" t="s">
+        <v>61</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="5" t="str">
-        <v>Char</v>
-      </c>
-      <c r="B3" s="5" t="str">
-        <v>Char</v>
-      </c>
-      <c r="C3" s="5" t="str">
-        <v>Num</v>
-      </c>
-      <c r="D3" s="5" t="str">
-        <v>Char</v>
-      </c>
-      <c r="E3" s="5" t="str">
-        <v>Char</v>
-      </c>
-      <c r="F3" s="5" t="str">
-        <v>Char</v>
-      </c>
-      <c r="G3" s="5" t="str">
-        <v>Char</v>
-      </c>
-      <c r="H3" s="5" t="str">
-        <v>Char</v>
-      </c>
-      <c r="I3" s="5" t="str">
-        <v>Char</v>
-      </c>
-      <c r="J3" s="5" t="str">
-        <v>Char</v>
-      </c>
-      <c r="K3" s="5" t="str">
-        <v>Char</v>
+    <row r="3" spans="1:26" ht="15" x14ac:dyDescent="0.2">
+      <c r="A3" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="K3" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="L3" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="M3" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="N3" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="O3" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="P3" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q3" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="R3" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="S3" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="T3" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="U3" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="V3" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="W3" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="X3" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="Y3" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="Z3" s="4" t="s">
+        <v>62</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="5">
-        <v>12</v>
-      </c>
-      <c r="B4" s="5">
-        <v>2</v>
-      </c>
-      <c r="C4" s="5">
-        <v>8</v>
-      </c>
-      <c r="D4" s="5">
-        <v>200</v>
-      </c>
-      <c r="E4" s="5">
-        <v>8</v>
-      </c>
-      <c r="F4" s="5">
-        <v>40</v>
-      </c>
-      <c r="G4" s="5">
-        <v>200</v>
-      </c>
-      <c r="H4" s="5">
-        <v>4</v>
-      </c>
-      <c r="I4" s="5">
-        <v>200</v>
-      </c>
-      <c r="J4" s="5">
-        <v>200</v>
-      </c>
-      <c r="K4" s="5">
-        <v>200</v>
+    <row r="4" spans="1:26" ht="15" x14ac:dyDescent="0.2">
+      <c r="A4" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="K4" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="L4" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="M4" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="N4" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="O4" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="P4" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q4" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="R4" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="S4" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="T4" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="U4" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="V4" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="W4" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="X4" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="Y4" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="Z4" s="4" t="s">
+        <v>64</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="6" t="str">
-        <v>CDISCPILOT01</v>
-      </c>
-      <c r="B5" s="6" t="str">
-        <v>TS</v>
-      </c>
-      <c r="C5" s="6">
-        <v>1</v>
-      </c>
-      <c r="D5" s="2" t="str">
-        <v/>
-      </c>
-      <c r="E5" s="6" t="str">
-        <v>SSTDTC</v>
-      </c>
-      <c r="F5" s="6" t="str">
-        <v>Study Start Date</v>
-      </c>
-      <c r="G5" s="6" t="str">
-        <v>2026-03-02</v>
-      </c>
-      <c r="H5" s="2" t="str">
-        <v/>
-      </c>
-      <c r="I5" s="2" t="str">
-        <v/>
-      </c>
-      <c r="J5" s="6" t="str">
-        <v>ISO 8601</v>
+    <row r="5" spans="1:26" ht="15" x14ac:dyDescent="0.2">
+      <c r="A5" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="J5" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="K5" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="L5" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="M5" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="N5" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="O5" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="P5" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q5" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="R5" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="S5" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="T5" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="U5" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="V5" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="W5" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="X5" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="Y5" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="Z5" s="5" t="s">
+        <v>81</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K5"/>
+    <ignoredError sqref="A1:Z5" numberStoredAsText="1"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:K5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:11" ht="15" x14ac:dyDescent="0.2">
+      <c r="A1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="15" x14ac:dyDescent="0.2">
+      <c r="A2" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="15" x14ac:dyDescent="0.2">
+      <c r="A3" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="K3" s="4" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="15" x14ac:dyDescent="0.2">
+      <c r="A4" s="4">
+        <v>12</v>
+      </c>
+      <c r="B4" s="4">
+        <v>2</v>
+      </c>
+      <c r="C4" s="4">
+        <v>8</v>
+      </c>
+      <c r="D4" s="4">
+        <v>200</v>
+      </c>
+      <c r="E4" s="4">
+        <v>8</v>
+      </c>
+      <c r="F4" s="4">
+        <v>40</v>
+      </c>
+      <c r="G4" s="4">
+        <v>200</v>
+      </c>
+      <c r="H4" s="4">
+        <v>4</v>
+      </c>
+      <c r="I4" s="4">
+        <v>200</v>
+      </c>
+      <c r="J4" s="4">
+        <v>200</v>
+      </c>
+      <c r="K4" s="4">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="15" x14ac:dyDescent="0.2">
+      <c r="A5" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="C5" s="1">
+        <v>1</v>
+      </c>
+      <c r="D5" t="s">
+        <v>78</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="H5" t="s">
+        <v>78</v>
+      </c>
+      <c r="I5" t="s">
+        <v>78</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>103</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <ignoredErrors>
+    <ignoredError sqref="A1:K5" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/rules/NEW-RULE/positive/01/data/new-rule-positive-01.xlsx
+++ b/rules/NEW-RULE/positive/01/data/new-rule-positive-01.xlsx
@@ -36,7 +36,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
   <numFmts count="0"/>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -59,13 +59,8 @@
       <name val="Calibri"/>
       <i/>
     </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <i/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none">
         <bgColor/>
@@ -73,12 +68,6 @@
     </fill>
     <fill>
       <patternFill patternType="gray125">
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -108,14 +97,13 @@
   <cellStyleXfs>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="1" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -538,69 +526,69 @@
       <c r="A2" s="5" t="str">
         <v>Study Identifier</v>
       </c>
-      <c r="B2" s="6" t="str">
+      <c r="B2" s="5" t="str">
         <v>Related Domain Abbreviation</v>
       </c>
-      <c r="C2" s="6" t="str">
+      <c r="C2" s="5" t="str">
         <v>Unique Subject Identifier</v>
       </c>
-      <c r="D2" s="6" t="str">
+      <c r="D2" s="5" t="str">
         <v>Identifying Variable</v>
       </c>
-      <c r="E2" s="6" t="str">
+      <c r="E2" s="5" t="str">
         <v>Identifying Variable Value</v>
       </c>
-      <c r="F2" s="6" t="str">
+      <c r="F2" s="5" t="str">
         <v>Relationship Type</v>
       </c>
-      <c r="G2" s="6" t="str">
+      <c r="G2" s="5" t="str">
         <v>Relationship Identifier</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="B3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="C3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="D3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="E3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="F3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="G3" s="6" t="str">
+      <c r="A3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="B3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="C3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="D3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="E3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="F3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="G3" s="5" t="str">
         <v>Char</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6">
+      <c r="A4" s="5">
         <v>12</v>
       </c>
-      <c r="B4" s="6">
-        <v>6</v>
-      </c>
-      <c r="C4" s="6">
+      <c r="B4" s="5">
+        <v>2</v>
+      </c>
+      <c r="C4" s="5">
         <v>8</v>
       </c>
-      <c r="D4" s="6">
-        <v>200</v>
-      </c>
-      <c r="E4" s="6">
-        <v>200</v>
-      </c>
-      <c r="F4" s="6">
+      <c r="D4" s="5">
+        <v>5</v>
+      </c>
+      <c r="E4" s="5">
+        <v>1</v>
+      </c>
+      <c r="F4" s="5">
+        <v>3</v>
+      </c>
+      <c r="G4" s="5">
         <v>4</v>
-      </c>
-      <c r="G4" s="6">
-        <v>200</v>
       </c>
     </row>
     <row r="5">
@@ -670,98 +658,98 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="str">
+      <c r="A2" s="5" t="str">
         <v>Study Identifier</v>
       </c>
-      <c r="B2" s="6" t="str">
+      <c r="B2" s="5" t="str">
         <v>Related Domain Abbreviation</v>
       </c>
-      <c r="C2" s="6" t="str">
+      <c r="C2" s="5" t="str">
         <v>Unique Subject Identifier</v>
       </c>
-      <c r="D2" s="6" t="str">
+      <c r="D2" s="5" t="str">
         <v>Identifying Variable</v>
       </c>
-      <c r="E2" s="6" t="str">
+      <c r="E2" s="5" t="str">
         <v>Identifying Variable Value</v>
       </c>
-      <c r="F2" s="6" t="str">
+      <c r="F2" s="5" t="str">
         <v>Qualifier Variable Name</v>
       </c>
-      <c r="G2" s="6" t="str">
+      <c r="G2" s="5" t="str">
         <v>Qualifier Variable Label</v>
       </c>
-      <c r="H2" s="6" t="str">
+      <c r="H2" s="5" t="str">
         <v>Data Value</v>
       </c>
-      <c r="I2" s="6" t="str">
+      <c r="I2" s="5" t="str">
         <v>Origin</v>
       </c>
-      <c r="J2" s="6" t="str">
+      <c r="J2" s="5" t="str">
         <v>Evaluator</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="B3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="C3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="D3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="E3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="F3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="G3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="H3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="I3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="J3" s="6" t="str">
+      <c r="A3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="B3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="C3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="D3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="E3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="F3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="G3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="H3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="I3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="J3" s="5" t="str">
         <v>Char</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6">
+      <c r="A4" s="5">
         <v>12</v>
       </c>
-      <c r="B4" s="6">
+      <c r="B4" s="5">
         <v>2</v>
       </c>
-      <c r="C4" s="6">
-        <v>14</v>
-      </c>
-      <c r="D4" s="6">
+      <c r="C4" s="5">
+        <v>8</v>
+      </c>
+      <c r="D4" s="5">
         <v>6</v>
       </c>
-      <c r="E4" s="6">
-        <v>4</v>
-      </c>
-      <c r="F4" s="6">
+      <c r="E4" s="5">
+        <v>1</v>
+      </c>
+      <c r="F4" s="5">
         <v>7</v>
       </c>
-      <c r="G4" s="6">
-        <v>40</v>
-      </c>
-      <c r="H4" s="6">
-        <v>19</v>
-      </c>
-      <c r="I4" s="6">
+      <c r="G4" s="5">
+        <v>18</v>
+      </c>
+      <c r="H4" s="5">
+        <v>9</v>
+      </c>
+      <c r="I4" s="5">
         <v>8</v>
       </c>
-      <c r="J4" s="6">
+      <c r="J4" s="5">
         <v>22</v>
       </c>
     </row>

--- a/rules/NEW-RULE/positive/01/data/new-rule-positive-01.xlsx
+++ b/rules/NEW-RULE/positive/01/data/new-rule-positive-01.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rich/Documents/github/core-contributor/rules/NEW-RULE/positive/01/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D46CB74-AE58-9C41-8770-9F83AF085134}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A30C8741-84D1-9746-A493-C1A2F2D744C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="33">
   <si>
     <t>Product</t>
   </si>
@@ -526,9 +526,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -536,7 +536,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -555,9 +555,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
@@ -565,7 +565,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
@@ -712,7 +712,7 @@
       <c r="G5" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="H5" s="1" t="s">
+      <c r="H5" s="4" t="s">
         <v>26</v>
       </c>
     </row>
@@ -747,18 +747,23 @@
         <v>27</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E7" s="1"/>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
+      </c>
+      <c r="D7" s="1">
+        <v>1</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G7" s="1"/>
+      <c r="H7" s="1" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
@@ -803,7 +808,7 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
   <ignoredErrors>
-    <ignoredError sqref="G1:H9 A1:D9" numberStoredAsText="1"/>
+    <ignoredError sqref="G1:H4 A1:D6 G8:H9 A8:D9 A7 G6:H6 G5" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/rules/NEW-RULE/positive/01/data/new-rule-positive-01.xlsx
+++ b/rules/NEW-RULE/positive/01/data/new-rule-positive-01.xlsx
@@ -1,41 +1,92 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
-  <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
-  </bookViews>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Library" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Datasets" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Library" sheetId="1" r:id="rId1"/>
+    <sheet name="Datasets" sheetId="2" r:id="rId2"/>
+    <sheet name="dm.xpt" sheetId="3" r:id="rId3"/>
+    <sheet name="ec.xpt" sheetId="4" r:id="rId4"/>
+    <sheet name="ex.xpt" sheetId="5" r:id="rId5"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <color theme="1"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <scheme val="minor"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <i/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none">
+        <bgColor/>
+      </patternFill>
     </fill>
     <fill>
-      <patternFill patternType="gray125"/>
+      <patternFill patternType="gray125">
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor/>
+      </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left/>
       <right/>
@@ -44,84 +95,22 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+  <cellXfs count="6">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="1" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+  <cellStyles>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
 </styleSheet>
 </file>
 
@@ -200,6 +189,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -234,6 +224,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -268,20 +259,16 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="80000">
-              <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
+                <a:tint val="100000"/>
+                <a:shade val="100000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
+                <a:tint val="50000"/>
+                <a:shade val="100000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -403,75 +390,2901 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
+  <a:objectDefaults>
+    <a:spDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="3">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </a:style>
+    </a:spDef>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
   <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Product</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Version</t>
-        </is>
+      <c r="A1" s="3" t="str">
+        <v>Product</v>
+      </c>
+      <c r="B1" s="3" t="str">
+        <v>Version</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>sdtmig</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>3-4</t>
-        </is>
+      <c r="A2" s="2" t="str">
+        <v>sdtmig</v>
+      </c>
+      <c r="B2" s="2" t="str">
+        <v>3-4</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:B2"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B4"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Filename</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Label</t>
-        </is>
+      <c r="A1" s="3" t="str">
+        <v>Filename</v>
+      </c>
+      <c r="B1" s="3" t="str">
+        <v>Label</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr"/>
-      <c r="B2" t="inlineStr"/>
+      <c r="A2" s="4" t="str">
+        <v>dm.xpt</v>
+      </c>
+      <c r="B2" s="4" t="str">
+        <v>Demographics</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="str">
+        <v>ec.xpt</v>
+      </c>
+      <c r="B3" s="4" t="str">
+        <v>Exposure as Collected</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="str">
+        <v>ex.xpt</v>
+      </c>
+      <c r="B4" s="2" t="str">
+        <v>Exposure</v>
+      </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:B4"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z14"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="str">
+        <v>STUDYID</v>
+      </c>
+      <c r="B1" s="3" t="str">
+        <v>DOMAIN</v>
+      </c>
+      <c r="C1" s="3" t="str">
+        <v>USUBJID</v>
+      </c>
+      <c r="D1" s="3" t="str">
+        <v>SUBJID</v>
+      </c>
+      <c r="E1" s="3" t="str">
+        <v>RFSTDTC</v>
+      </c>
+      <c r="F1" s="3" t="str">
+        <v>RFENDTC</v>
+      </c>
+      <c r="G1" s="3" t="str">
+        <v>RFXSTDTC</v>
+      </c>
+      <c r="H1" s="3" t="str">
+        <v>RFXENDTC</v>
+      </c>
+      <c r="I1" s="3" t="str">
+        <v>RFICDTC</v>
+      </c>
+      <c r="J1" s="3" t="str">
+        <v>RFPENDTC</v>
+      </c>
+      <c r="K1" s="3" t="str">
+        <v>DTHDTC</v>
+      </c>
+      <c r="L1" s="3" t="str">
+        <v>DTHFL</v>
+      </c>
+      <c r="M1" s="3" t="str">
+        <v>SITEID</v>
+      </c>
+      <c r="N1" s="3" t="str">
+        <v>BRTHDTC</v>
+      </c>
+      <c r="O1" s="3" t="str">
+        <v>AGE</v>
+      </c>
+      <c r="P1" s="3" t="str">
+        <v>AGEU</v>
+      </c>
+      <c r="Q1" s="3" t="str">
+        <v>SEX</v>
+      </c>
+      <c r="R1" s="3" t="str">
+        <v>RACE</v>
+      </c>
+      <c r="S1" s="3" t="str">
+        <v>ETHNIC</v>
+      </c>
+      <c r="T1" s="3" t="str">
+        <v>ARMCD</v>
+      </c>
+      <c r="U1" s="3" t="str">
+        <v>ARM</v>
+      </c>
+      <c r="V1" s="3" t="str">
+        <v>ACTARMCD</v>
+      </c>
+      <c r="W1" s="3" t="str">
+        <v>ACTARM</v>
+      </c>
+      <c r="X1" s="3" t="str">
+        <v>ARMNRS</v>
+      </c>
+      <c r="Y1" s="3" t="str">
+        <v>ACTARMUD</v>
+      </c>
+      <c r="Z1" s="3" t="str">
+        <v>COUNTRY</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="str">
+        <v>Study Identifier</v>
+      </c>
+      <c r="B2" s="5" t="str">
+        <v>Domain Abbreviation</v>
+      </c>
+      <c r="C2" s="5" t="str">
+        <v>Unique Subject Identifier</v>
+      </c>
+      <c r="D2" s="5" t="str">
+        <v>Subject Identifier for the Study</v>
+      </c>
+      <c r="E2" s="5" t="str">
+        <v>Subject Reference Start Date/Time</v>
+      </c>
+      <c r="F2" s="5" t="str">
+        <v>Subject Reference End Date/Time</v>
+      </c>
+      <c r="G2" s="5" t="str">
+        <v>Date/Time of First Study Treatment</v>
+      </c>
+      <c r="H2" s="5" t="str">
+        <v>Date/Time of Last Study Treatment</v>
+      </c>
+      <c r="I2" s="5" t="str">
+        <v>Date/Time of Informed Consent</v>
+      </c>
+      <c r="J2" s="5" t="str">
+        <v>Date/Time of End of Participation</v>
+      </c>
+      <c r="K2" s="5" t="str">
+        <v>Date/Time of Death</v>
+      </c>
+      <c r="L2" s="5" t="str">
+        <v>Subject Death Flag</v>
+      </c>
+      <c r="M2" s="5" t="str">
+        <v>Study Site Identifier</v>
+      </c>
+      <c r="N2" s="5" t="str">
+        <v>Date/Time of Birth</v>
+      </c>
+      <c r="O2" s="5" t="str">
+        <v>Age</v>
+      </c>
+      <c r="P2" s="5" t="str">
+        <v>Age Units</v>
+      </c>
+      <c r="Q2" s="5" t="str">
+        <v>Sex</v>
+      </c>
+      <c r="R2" s="5" t="str">
+        <v>Race</v>
+      </c>
+      <c r="S2" s="5" t="str">
+        <v>Ethnicity</v>
+      </c>
+      <c r="T2" s="5" t="str">
+        <v>Planned Arm Code</v>
+      </c>
+      <c r="U2" s="5" t="str">
+        <v>Description of Planned Arm</v>
+      </c>
+      <c r="V2" s="5" t="str">
+        <v>Actual Arm Code</v>
+      </c>
+      <c r="W2" s="5" t="str">
+        <v>Description of Actual Arm</v>
+      </c>
+      <c r="X2" s="5" t="str">
+        <v>Reason Arm and/or Actual Arm is Null</v>
+      </c>
+      <c r="Y2" s="5" t="str">
+        <v>Description of Unplanned Actual Arm</v>
+      </c>
+      <c r="Z2" s="5" t="str">
+        <v>Country</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="B3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="C3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="D3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="E3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="F3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="G3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="H3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="I3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="J3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="K3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="L3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="M3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="N3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="O3" s="5" t="str">
+        <v>Num</v>
+      </c>
+      <c r="P3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="Q3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="R3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="S3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="T3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="U3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="V3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="W3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="X3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="Y3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="Z3" s="5" t="str">
+        <v>Char</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5">
+        <v>12</v>
+      </c>
+      <c r="B4" s="5">
+        <v>2</v>
+      </c>
+      <c r="C4" s="5">
+        <v>8</v>
+      </c>
+      <c r="D4" s="5">
+        <v>4</v>
+      </c>
+      <c r="E4" s="5">
+        <v>10</v>
+      </c>
+      <c r="F4" s="5">
+        <v>10</v>
+      </c>
+      <c r="G4" s="5">
+        <v>19</v>
+      </c>
+      <c r="H4" s="5">
+        <v>19</v>
+      </c>
+      <c r="I4" s="5">
+        <v>10</v>
+      </c>
+      <c r="J4" s="5">
+        <v>10</v>
+      </c>
+      <c r="K4" s="5">
+        <v>10</v>
+      </c>
+      <c r="L4" s="5">
+        <v>1</v>
+      </c>
+      <c r="M4" s="5">
+        <v>3</v>
+      </c>
+      <c r="N4" s="5">
+        <v>10</v>
+      </c>
+      <c r="O4" s="5">
+        <v>8</v>
+      </c>
+      <c r="P4" s="5">
+        <v>5</v>
+      </c>
+      <c r="Q4" s="5">
+        <v>1</v>
+      </c>
+      <c r="R4" s="5">
+        <v>41</v>
+      </c>
+      <c r="S4" s="5">
+        <v>22</v>
+      </c>
+      <c r="T4" s="5">
+        <v>8</v>
+      </c>
+      <c r="U4" s="5">
+        <v>28</v>
+      </c>
+      <c r="V4" s="5">
+        <v>8</v>
+      </c>
+      <c r="W4" s="5">
+        <v>28</v>
+      </c>
+      <c r="X4" s="5">
+        <v>14</v>
+      </c>
+      <c r="Y4" s="5">
+        <v>200</v>
+      </c>
+      <c r="Z4" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="str">
+        <v>CDISCPILOT01</v>
+      </c>
+      <c r="B5" s="4" t="str">
+        <v>DM</v>
+      </c>
+      <c r="C5" s="4" t="str">
+        <v>CDISC001</v>
+      </c>
+      <c r="D5" s="4">
+        <v>1115</v>
+      </c>
+      <c r="E5" s="4" t="str">
+        <v/>
+      </c>
+      <c r="F5" s="4" t="str">
+        <v>2013-01-23</v>
+      </c>
+      <c r="G5" s="4" t="str">
+        <v>2012-11-30T15:59:00</v>
+      </c>
+      <c r="H5" s="4" t="str">
+        <v>2013-01-23T15:59:00</v>
+      </c>
+      <c r="I5" s="4" t="str">
+        <v>2012-11-23</v>
+      </c>
+      <c r="J5" s="4" t="str">
+        <v>2013-05-20</v>
+      </c>
+      <c r="K5" s="4" t="str">
+        <v/>
+      </c>
+      <c r="L5" s="4" t="str">
+        <v/>
+      </c>
+      <c r="M5" s="4">
+        <v>701</v>
+      </c>
+      <c r="N5" s="4">
+        <v>1928</v>
+      </c>
+      <c r="O5" s="4">
+        <v>84</v>
+      </c>
+      <c r="P5" s="4" t="str">
+        <v>YEARS</v>
+      </c>
+      <c r="Q5" s="4" t="str">
+        <v>M</v>
+      </c>
+      <c r="R5" s="4" t="str">
+        <v>WHITE</v>
+      </c>
+      <c r="S5" s="4" t="str">
+        <v>NOT HISPANIC OR LATINO</v>
+      </c>
+      <c r="T5" s="4" t="str">
+        <v>ZAN_LOW</v>
+      </c>
+      <c r="U5" s="4" t="str">
+        <v>Zanomaline Low Dose (54 mg)</v>
+      </c>
+      <c r="V5" s="4" t="str">
+        <v>ZAN_LOW</v>
+      </c>
+      <c r="W5" s="4" t="str">
+        <v>Zanomaline Low Dose (54 mg)</v>
+      </c>
+      <c r="X5" s="4" t="str">
+        <v/>
+      </c>
+      <c r="Y5" s="4" t="str">
+        <v/>
+      </c>
+      <c r="Z5" s="4" t="str">
+        <v>USA</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="str">
+        <v>CDISCPILOT01</v>
+      </c>
+      <c r="B6" s="4" t="str">
+        <v>DM</v>
+      </c>
+      <c r="C6" s="4" t="str">
+        <v>CDISC002</v>
+      </c>
+      <c r="D6" s="4">
+        <v>1211</v>
+      </c>
+      <c r="E6" s="4" t="str">
+        <v>2012-11-15</v>
+      </c>
+      <c r="F6" s="4" t="str">
+        <v>2013-01-14</v>
+      </c>
+      <c r="G6" s="4" t="str">
+        <v>2012-11-15T15:59:00</v>
+      </c>
+      <c r="H6" s="4" t="str">
+        <v>2013-01-12T15:59:00</v>
+      </c>
+      <c r="I6" s="4" t="str">
+        <v>2012-10-30</v>
+      </c>
+      <c r="J6" s="4" t="str">
+        <v>2013-01-14</v>
+      </c>
+      <c r="K6" s="4" t="str">
+        <v>2013-01-14</v>
+      </c>
+      <c r="L6" s="4" t="str">
+        <v>Y</v>
+      </c>
+      <c r="M6" s="4">
+        <v>701</v>
+      </c>
+      <c r="N6" s="4">
+        <v>1936</v>
+      </c>
+      <c r="O6" s="4">
+        <v>76</v>
+      </c>
+      <c r="P6" s="4" t="str">
+        <v>YEARS</v>
+      </c>
+      <c r="Q6" s="4" t="str">
+        <v>F</v>
+      </c>
+      <c r="R6" s="4" t="str">
+        <v>WHITE</v>
+      </c>
+      <c r="S6" s="4" t="str">
+        <v>NOT HISPANIC OR LATINO</v>
+      </c>
+      <c r="T6" s="4" t="str">
+        <v>ZAN_LOW</v>
+      </c>
+      <c r="U6" s="4" t="str">
+        <v>Zanomaline Low Dose (54 mg)</v>
+      </c>
+      <c r="V6" s="4" t="str">
+        <v>ZAN_LOW</v>
+      </c>
+      <c r="W6" s="4" t="str">
+        <v>Zanomaline Low Dose (54 mg)</v>
+      </c>
+      <c r="X6" s="4" t="str">
+        <v/>
+      </c>
+      <c r="Y6" s="4" t="str">
+        <v/>
+      </c>
+      <c r="Z6" s="4" t="str">
+        <v>USA</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="str">
+        <v>CDISCPILOT01</v>
+      </c>
+      <c r="B7" s="4" t="str">
+        <v>DM</v>
+      </c>
+      <c r="C7" s="4" t="str">
+        <v>CDISC003</v>
+      </c>
+      <c r="D7" s="4">
+        <v>1302</v>
+      </c>
+      <c r="E7" s="4" t="str">
+        <v/>
+      </c>
+      <c r="F7" s="4" t="str">
+        <v>2013-11-05</v>
+      </c>
+      <c r="G7" s="4" t="str">
+        <v>2013-08-29T15:59:00</v>
+      </c>
+      <c r="H7" s="4" t="str">
+        <v>2013-11-05T15:59:00</v>
+      </c>
+      <c r="I7" s="4" t="str">
+        <v>2013-08-20</v>
+      </c>
+      <c r="J7" s="4" t="str">
+        <v>2014-02-13</v>
+      </c>
+      <c r="K7" s="4" t="str">
+        <v/>
+      </c>
+      <c r="L7" s="4" t="str">
+        <v/>
+      </c>
+      <c r="M7" s="4">
+        <v>701</v>
+      </c>
+      <c r="N7" s="4">
+        <v>1951</v>
+      </c>
+      <c r="O7" s="4">
+        <v>61</v>
+      </c>
+      <c r="P7" s="4" t="str">
+        <v>YEARS</v>
+      </c>
+      <c r="Q7" s="4" t="str">
+        <v>M</v>
+      </c>
+      <c r="R7" s="4" t="str">
+        <v>WHITE</v>
+      </c>
+      <c r="S7" s="4" t="str">
+        <v>NOT HISPANIC OR LATINO</v>
+      </c>
+      <c r="T7" s="4" t="str">
+        <v>ZAN_HIGH</v>
+      </c>
+      <c r="U7" s="4" t="str">
+        <v>Zanomaline High Dose (81 mg)</v>
+      </c>
+      <c r="V7" s="4" t="str">
+        <v>ZAN_HIGH</v>
+      </c>
+      <c r="W7" s="4" t="str">
+        <v>Zanomaline High Dose (81 mg)</v>
+      </c>
+      <c r="X7" s="4" t="str">
+        <v/>
+      </c>
+      <c r="Y7" s="4" t="str">
+        <v/>
+      </c>
+      <c r="Z7" s="4" t="str">
+        <v>USA</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="str">
+        <v>CDISCPILOT01</v>
+      </c>
+      <c r="B8" s="4" t="str">
+        <v>DM</v>
+      </c>
+      <c r="C8" s="4" t="str">
+        <v>CDISC004</v>
+      </c>
+      <c r="D8" s="4">
+        <v>1345</v>
+      </c>
+      <c r="E8" s="4" t="str">
+        <v>2013-10-08</v>
+      </c>
+      <c r="F8" s="4" t="str">
+        <v>2014-03-18</v>
+      </c>
+      <c r="G8" s="4" t="str">
+        <v>2013-10-08T15:59:00</v>
+      </c>
+      <c r="H8" s="4" t="str">
+        <v>2014-03-18T15:59:00</v>
+      </c>
+      <c r="I8" s="4" t="str">
+        <v>2013-10-01</v>
+      </c>
+      <c r="J8" s="4" t="str">
+        <v>2014-03-18</v>
+      </c>
+      <c r="K8" s="4" t="str">
+        <v/>
+      </c>
+      <c r="L8" s="4" t="str">
+        <v/>
+      </c>
+      <c r="M8" s="4">
+        <v>701</v>
+      </c>
+      <c r="N8" s="4">
+        <v>1950</v>
+      </c>
+      <c r="O8" s="4">
+        <v>63</v>
+      </c>
+      <c r="P8" s="4" t="str">
+        <v>YEARS</v>
+      </c>
+      <c r="Q8" s="4" t="str">
+        <v>F</v>
+      </c>
+      <c r="R8" s="4" t="str">
+        <v>WHITE</v>
+      </c>
+      <c r="S8" s="4" t="str">
+        <v>NOT HISPANIC OR LATINO</v>
+      </c>
+      <c r="T8" s="4" t="str">
+        <v/>
+      </c>
+      <c r="U8" s="4" t="str">
+        <v/>
+      </c>
+      <c r="V8" s="4" t="str">
+        <v/>
+      </c>
+      <c r="W8" s="4" t="str">
+        <v/>
+      </c>
+      <c r="X8" s="4" t="str">
+        <v>SCREEN FAILURE</v>
+      </c>
+      <c r="Y8" s="4" t="str">
+        <v/>
+      </c>
+      <c r="Z8" s="4" t="str">
+        <v>USA</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="str">
+        <v>CDISCPILOT01</v>
+      </c>
+      <c r="B9" s="4" t="str">
+        <v>DM</v>
+      </c>
+      <c r="C9" s="4" t="str">
+        <v>CDISC005</v>
+      </c>
+      <c r="D9" s="4">
+        <v>1383</v>
+      </c>
+      <c r="E9" s="4" t="str">
+        <v/>
+      </c>
+      <c r="F9" s="4" t="str">
+        <v>2013-08-06</v>
+      </c>
+      <c r="G9" s="4" t="str">
+        <v>2013-02-04T15:59:00</v>
+      </c>
+      <c r="H9" s="4" t="str">
+        <v>2013-08-06T15:59:00</v>
+      </c>
+      <c r="I9" s="4" t="str">
+        <v>2013-01-22</v>
+      </c>
+      <c r="J9" s="4" t="str">
+        <v>2013-08-06</v>
+      </c>
+      <c r="K9" s="4" t="str">
+        <v/>
+      </c>
+      <c r="L9" s="4" t="str">
+        <v/>
+      </c>
+      <c r="M9" s="4">
+        <v>701</v>
+      </c>
+      <c r="N9" s="4">
+        <v>1941</v>
+      </c>
+      <c r="O9" s="4">
+        <v>72</v>
+      </c>
+      <c r="P9" s="4" t="str">
+        <v>YEARS</v>
+      </c>
+      <c r="Q9" s="4" t="str">
+        <v>F</v>
+      </c>
+      <c r="R9" s="4" t="str">
+        <v>WHITE</v>
+      </c>
+      <c r="S9" s="4" t="str">
+        <v>NOT HISPANIC OR LATINO</v>
+      </c>
+      <c r="T9" s="4" t="str">
+        <v>ZAN_HIGH</v>
+      </c>
+      <c r="U9" s="4" t="str">
+        <v>Zanomaline High Dose (81 mg)</v>
+      </c>
+      <c r="V9" s="4" t="str">
+        <v/>
+      </c>
+      <c r="W9" s="4" t="str">
+        <v/>
+      </c>
+      <c r="X9" s="4" t="str">
+        <v>NOT TREATED</v>
+      </c>
+      <c r="Y9" s="4" t="str">
+        <v/>
+      </c>
+      <c r="Z9" s="4" t="str">
+        <v>USA</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="str">
+        <v>CDISCPILOT01</v>
+      </c>
+      <c r="B10" s="4" t="str">
+        <v>DM</v>
+      </c>
+      <c r="C10" s="4" t="str">
+        <v>CDISC006</v>
+      </c>
+      <c r="D10" s="4">
+        <v>1429</v>
+      </c>
+      <c r="E10" s="4" t="str">
+        <v/>
+      </c>
+      <c r="F10" s="4" t="str">
+        <v>2013-04-30</v>
+      </c>
+      <c r="G10" s="4" t="str">
+        <v>2013-03-19T15:59:00</v>
+      </c>
+      <c r="H10" s="4" t="str">
+        <v>2013-04-30T15:59:00</v>
+      </c>
+      <c r="I10" s="4" t="str">
+        <v>2013-02-25</v>
+      </c>
+      <c r="J10" s="4" t="str">
+        <v>2013-04-30</v>
+      </c>
+      <c r="K10" s="4" t="str">
+        <v/>
+      </c>
+      <c r="L10" s="4" t="str">
+        <v/>
+      </c>
+      <c r="M10" s="4">
+        <v>701</v>
+      </c>
+      <c r="N10" s="4">
+        <v>1929</v>
+      </c>
+      <c r="O10" s="4">
+        <v>84</v>
+      </c>
+      <c r="P10" s="4" t="str">
+        <v>YEARS</v>
+      </c>
+      <c r="Q10" s="4" t="str">
+        <v>F</v>
+      </c>
+      <c r="R10" s="4" t="str">
+        <v>WHITE</v>
+      </c>
+      <c r="S10" s="4" t="str">
+        <v>NOT HISPANIC OR LATINO</v>
+      </c>
+      <c r="T10" s="4" t="str">
+        <v/>
+      </c>
+      <c r="U10" s="4" t="str">
+        <v/>
+      </c>
+      <c r="V10" s="4" t="str">
+        <v/>
+      </c>
+      <c r="W10" s="4" t="str">
+        <v/>
+      </c>
+      <c r="X10" s="4" t="str">
+        <v>NOT ASSIGNED</v>
+      </c>
+      <c r="Y10" s="4" t="str">
+        <v/>
+      </c>
+      <c r="Z10" s="4" t="str">
+        <v>USA</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="str">
+        <v>CDISCPILOT01</v>
+      </c>
+      <c r="B11" s="4" t="str">
+        <v>DM</v>
+      </c>
+      <c r="C11" s="4" t="str">
+        <v>CDISC007</v>
+      </c>
+      <c r="D11" s="4">
+        <v>1444</v>
+      </c>
+      <c r="E11" s="4" t="str">
+        <v>2013-01-05</v>
+      </c>
+      <c r="F11" s="4" t="str">
+        <v>2013-02-13</v>
+      </c>
+      <c r="G11" s="4" t="str">
+        <v>2013-01-05T15:59:00</v>
+      </c>
+      <c r="H11" s="4" t="str">
+        <v>2013-02-12T15:59:00</v>
+      </c>
+      <c r="I11" s="4" t="str">
+        <v>2012-12-31</v>
+      </c>
+      <c r="J11" s="4" t="str">
+        <v>2013-06-20</v>
+      </c>
+      <c r="K11" s="4" t="str">
+        <v/>
+      </c>
+      <c r="L11" s="4" t="str">
+        <v/>
+      </c>
+      <c r="M11" s="4">
+        <v>701</v>
+      </c>
+      <c r="N11" s="4">
+        <v>1949</v>
+      </c>
+      <c r="O11" s="4">
+        <v>63</v>
+      </c>
+      <c r="P11" s="4" t="str">
+        <v>YEARS</v>
+      </c>
+      <c r="Q11" s="4" t="str">
+        <v>M</v>
+      </c>
+      <c r="R11" s="4" t="str">
+        <v>WHITE</v>
+      </c>
+      <c r="S11" s="4" t="str">
+        <v>HISPANIC OR LATINO</v>
+      </c>
+      <c r="T11" s="4" t="str">
+        <v>ZAN_HIGH</v>
+      </c>
+      <c r="U11" s="4" t="str">
+        <v>Zanomaline High Dose (81 mg)</v>
+      </c>
+      <c r="V11" s="4" t="str">
+        <v>ZAN_HIGH</v>
+      </c>
+      <c r="W11" s="4" t="str">
+        <v/>
+      </c>
+      <c r="X11" s="4" t="str">
+        <v>UNPLANNED</v>
+      </c>
+      <c r="Y11" s="4" t="str">
+        <v/>
+      </c>
+      <c r="Z11" s="4" t="str">
+        <v>USA</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="str">
+        <v>CDISCPILOT01</v>
+      </c>
+      <c r="B12" s="4" t="str">
+        <v>DM</v>
+      </c>
+      <c r="C12" s="4" t="str">
+        <v>CDISC008</v>
+      </c>
+      <c r="D12" s="4">
+        <v>1445</v>
+      </c>
+      <c r="E12" s="4" t="str">
+        <v>2014-05-11</v>
+      </c>
+      <c r="F12" s="4" t="str">
+        <v>2014-11-01</v>
+      </c>
+      <c r="G12" s="4" t="str">
+        <v>2014-05-11T15:59:00</v>
+      </c>
+      <c r="H12" s="4" t="str">
+        <v>2014-11-01T15:59:00</v>
+      </c>
+      <c r="I12" s="4" t="str">
+        <v>2014-05-01</v>
+      </c>
+      <c r="J12" s="4" t="str">
+        <v>2014-11-01</v>
+      </c>
+      <c r="K12" s="4" t="str">
+        <v>2014-11-01</v>
+      </c>
+      <c r="L12" s="4" t="str">
+        <v>Y</v>
+      </c>
+      <c r="M12" s="4">
+        <v>704</v>
+      </c>
+      <c r="N12" s="4">
+        <v>1939</v>
+      </c>
+      <c r="O12" s="4">
+        <v>75</v>
+      </c>
+      <c r="P12" s="4" t="str">
+        <v>YEARS</v>
+      </c>
+      <c r="Q12" s="4" t="str">
+        <v>M</v>
+      </c>
+      <c r="R12" s="4" t="str">
+        <v>MULTIPLE</v>
+      </c>
+      <c r="S12" s="4" t="str">
+        <v>NOT HISPANIC OR LATINO</v>
+      </c>
+      <c r="T12" s="4" t="str">
+        <v>PLACEBO</v>
+      </c>
+      <c r="U12" s="4" t="str">
+        <v>Placebo</v>
+      </c>
+      <c r="V12" s="4" t="str">
+        <v>PLACEBO</v>
+      </c>
+      <c r="W12" s="4" t="str">
+        <v>Placebo</v>
+      </c>
+      <c r="X12" s="4" t="str">
+        <v/>
+      </c>
+      <c r="Y12" s="4" t="str">
+        <v/>
+      </c>
+      <c r="Z12" s="4" t="str">
+        <v>USA</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="str">
+        <v>CDISCPILOT01</v>
+      </c>
+      <c r="B13" s="4" t="str">
+        <v>DM</v>
+      </c>
+      <c r="C13" s="4" t="str">
+        <v>CDISC009</v>
+      </c>
+      <c r="D13" s="4">
+        <v>1087</v>
+      </c>
+      <c r="E13" s="4" t="str">
+        <v/>
+      </c>
+      <c r="F13" s="4" t="str">
+        <v>2013-04-28</v>
+      </c>
+      <c r="G13" s="4" t="str">
+        <v>2012-10-22T15:59:00</v>
+      </c>
+      <c r="H13" s="4" t="str">
+        <v>2013-04-28T15:59:00</v>
+      </c>
+      <c r="I13" s="4" t="str">
+        <v>2012-10-06</v>
+      </c>
+      <c r="J13" s="4" t="str">
+        <v>2013-04-28</v>
+      </c>
+      <c r="K13" s="4" t="str">
+        <v/>
+      </c>
+      <c r="L13" s="4" t="str">
+        <v/>
+      </c>
+      <c r="M13" s="4">
+        <v>708</v>
+      </c>
+      <c r="N13" s="4">
+        <v>1938</v>
+      </c>
+      <c r="O13" s="4">
+        <v>74</v>
+      </c>
+      <c r="P13" s="4" t="str">
+        <v>YEARS</v>
+      </c>
+      <c r="Q13" s="4" t="str">
+        <v>F</v>
+      </c>
+      <c r="R13" s="4" t="str">
+        <v>WHITE</v>
+      </c>
+      <c r="S13" s="4" t="str">
+        <v>NOT HISPANIC OR LATINO</v>
+      </c>
+      <c r="T13" s="4" t="str">
+        <v>PLACEBO</v>
+      </c>
+      <c r="U13" s="4" t="str">
+        <v>Placebo</v>
+      </c>
+      <c r="V13" s="4" t="str">
+        <v>PLACEBO</v>
+      </c>
+      <c r="W13" s="4" t="str">
+        <v>Placebo</v>
+      </c>
+      <c r="X13" s="4" t="str">
+        <v/>
+      </c>
+      <c r="Y13" s="4" t="str">
+        <v/>
+      </c>
+      <c r="Z13" s="4" t="str">
+        <v>USA</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="str">
+        <v>CDISCPILOT01</v>
+      </c>
+      <c r="B14" s="4" t="str">
+        <v>DM</v>
+      </c>
+      <c r="C14" s="4" t="str">
+        <v>CDISC010</v>
+      </c>
+      <c r="D14" s="4">
+        <v>1236</v>
+      </c>
+      <c r="E14" s="4" t="str">
+        <v>2013-09-21</v>
+      </c>
+      <c r="F14" s="4" t="str">
+        <v>2013-09-26</v>
+      </c>
+      <c r="G14" s="4" t="str">
+        <v>2013-09-21T15:59:00</v>
+      </c>
+      <c r="H14" s="4" t="str">
+        <v>2013-09-21T15:59:00</v>
+      </c>
+      <c r="I14" s="4" t="str">
+        <v>2013-09-08</v>
+      </c>
+      <c r="J14" s="4" t="str">
+        <v>2013-09-26</v>
+      </c>
+      <c r="K14" s="4" t="str">
+        <v/>
+      </c>
+      <c r="L14" s="4" t="str">
+        <v/>
+      </c>
+      <c r="M14" s="4">
+        <v>708</v>
+      </c>
+      <c r="N14" s="4">
+        <v>1927</v>
+      </c>
+      <c r="O14" s="4">
+        <v>86</v>
+      </c>
+      <c r="P14" s="4" t="str">
+        <v>YEARS</v>
+      </c>
+      <c r="Q14" s="4" t="str">
+        <v>F</v>
+      </c>
+      <c r="R14" s="4" t="str">
+        <v>WHITE</v>
+      </c>
+      <c r="S14" s="4" t="str">
+        <v>NOT HISPANIC OR LATINO</v>
+      </c>
+      <c r="T14" s="4" t="str">
+        <v>ZAN_HIGH</v>
+      </c>
+      <c r="U14" s="4" t="str">
+        <v>Zanomaline High Dose (81 mg)</v>
+      </c>
+      <c r="V14" s="4" t="str">
+        <v>ZAN_HIGH</v>
+      </c>
+      <c r="W14" s="4" t="str">
+        <v>Zanomaline High Dose (81 mg)</v>
+      </c>
+      <c r="X14" s="4" t="str">
+        <v/>
+      </c>
+      <c r="Y14" s="4" t="str">
+        <v/>
+      </c>
+      <c r="Z14" s="4" t="str">
+        <v>USA</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:Z14"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:T20"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="str">
+        <v>STUDYID</v>
+      </c>
+      <c r="B1" s="3" t="str">
+        <v>DOMAIN</v>
+      </c>
+      <c r="C1" s="3" t="str">
+        <v>USUBJID</v>
+      </c>
+      <c r="D1" s="3" t="str">
+        <v>ECSEQ</v>
+      </c>
+      <c r="E1" s="3" t="str">
+        <v>ECTRT</v>
+      </c>
+      <c r="F1" s="3" t="str">
+        <v>ECPRESP</v>
+      </c>
+      <c r="G1" s="3" t="str">
+        <v>ECOCCUR</v>
+      </c>
+      <c r="H1" s="3" t="str">
+        <v>ECDOSE</v>
+      </c>
+      <c r="I1" s="3" t="str">
+        <v>ECDOSU</v>
+      </c>
+      <c r="J1" s="3" t="str">
+        <v>ECDOSFRM</v>
+      </c>
+      <c r="K1" s="3" t="str">
+        <v>ECDOSFRQ</v>
+      </c>
+      <c r="L1" s="3" t="str">
+        <v>ECROUTE</v>
+      </c>
+      <c r="M1" s="3" t="str">
+        <v>ECLOT</v>
+      </c>
+      <c r="N1" s="3" t="str">
+        <v>ECPSTRG</v>
+      </c>
+      <c r="O1" s="3" t="str">
+        <v>ECPSTRGU</v>
+      </c>
+      <c r="P1" s="3" t="str">
+        <v>EPOCH</v>
+      </c>
+      <c r="Q1" s="3" t="str">
+        <v>ECSTDTC</v>
+      </c>
+      <c r="R1" s="3" t="str">
+        <v>ECENDTC</v>
+      </c>
+      <c r="S1" s="3" t="str">
+        <v>ECSTDY</v>
+      </c>
+      <c r="T1" s="3" t="str">
+        <v>ECENDY</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="str">
+        <v>Study Identifier</v>
+      </c>
+      <c r="B2" s="5" t="str">
+        <v>Domain Abbreviation</v>
+      </c>
+      <c r="C2" s="5" t="str">
+        <v>Unique Subject Identifier</v>
+      </c>
+      <c r="D2" s="5" t="str">
+        <v>Sequence Number</v>
+      </c>
+      <c r="E2" s="5" t="str">
+        <v>Name of Treatment</v>
+      </c>
+      <c r="F2" s="5" t="str">
+        <v>Pre-Specified</v>
+      </c>
+      <c r="G2" s="5" t="str">
+        <v>Occurrence</v>
+      </c>
+      <c r="H2" s="5" t="str">
+        <v>Dose</v>
+      </c>
+      <c r="I2" s="5" t="str">
+        <v>Dose Units</v>
+      </c>
+      <c r="J2" s="5" t="str">
+        <v>Dose Form</v>
+      </c>
+      <c r="K2" s="5" t="str">
+        <v>Dosing Frequency per Interval</v>
+      </c>
+      <c r="L2" s="5" t="str">
+        <v>Route of Administration</v>
+      </c>
+      <c r="M2" s="5" t="str">
+        <v>Lot Number</v>
+      </c>
+      <c r="N2" s="5" t="str">
+        <v>Pharmaceutical Strength</v>
+      </c>
+      <c r="O2" s="5" t="str">
+        <v>Pharmaceutical Strength Units</v>
+      </c>
+      <c r="P2" s="5" t="str">
+        <v>Epoch</v>
+      </c>
+      <c r="Q2" s="5" t="str">
+        <v>Start Date/Time of Treatment</v>
+      </c>
+      <c r="R2" s="5" t="str">
+        <v>End Date/Time of Treatment</v>
+      </c>
+      <c r="S2" s="5" t="str">
+        <v>Study Day of Start of Treatment</v>
+      </c>
+      <c r="T2" s="5" t="str">
+        <v>Study Day of End of Treatment</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="B3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="C3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="D3" s="5" t="str">
+        <v>Num</v>
+      </c>
+      <c r="E3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="F3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="G3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="H3" s="5" t="str">
+        <v>Num</v>
+      </c>
+      <c r="I3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="J3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="K3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="L3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="M3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="N3" s="5" t="str">
+        <v>Num</v>
+      </c>
+      <c r="O3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="P3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="Q3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="R3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="S3" s="5" t="str">
+        <v>Num</v>
+      </c>
+      <c r="T3" s="5" t="str">
+        <v>Num</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5">
+        <v>12</v>
+      </c>
+      <c r="B4" s="5">
+        <v>2</v>
+      </c>
+      <c r="C4" s="5">
+        <v>8</v>
+      </c>
+      <c r="D4" s="5">
+        <v>8</v>
+      </c>
+      <c r="E4" s="5">
+        <v>10</v>
+      </c>
+      <c r="F4" s="5">
+        <v>1</v>
+      </c>
+      <c r="G4" s="5">
+        <v>1</v>
+      </c>
+      <c r="H4" s="5">
+        <v>8</v>
+      </c>
+      <c r="I4" s="5">
+        <v>2</v>
+      </c>
+      <c r="J4" s="5">
+        <v>9</v>
+      </c>
+      <c r="K4" s="5">
+        <v>2</v>
+      </c>
+      <c r="L4" s="5">
+        <v>12</v>
+      </c>
+      <c r="M4" s="5">
+        <v>200</v>
+      </c>
+      <c r="N4" s="5">
+        <v>8</v>
+      </c>
+      <c r="O4" s="5">
+        <v>3</v>
+      </c>
+      <c r="P4" s="5">
+        <v>9</v>
+      </c>
+      <c r="Q4" s="5">
+        <v>19</v>
+      </c>
+      <c r="R4" s="5">
+        <v>10</v>
+      </c>
+      <c r="S4" s="5">
+        <v>8</v>
+      </c>
+      <c r="T4" s="5">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="str">
+        <v>CDISCPILOT01</v>
+      </c>
+      <c r="B5" s="4" t="str">
+        <v>EC</v>
+      </c>
+      <c r="C5" s="4" t="str">
+        <v>CDISC001</v>
+      </c>
+      <c r="D5" s="4">
+        <v>1</v>
+      </c>
+      <c r="E5" s="4" t="str">
+        <v>ZANOMALINE</v>
+      </c>
+      <c r="F5" s="4" t="str">
+        <v>Y</v>
+      </c>
+      <c r="G5" s="4" t="str">
+        <v>Y</v>
+      </c>
+      <c r="H5" s="4">
+        <v>5</v>
+      </c>
+      <c r="I5" s="4" t="str">
+        <v>mL</v>
+      </c>
+      <c r="J5" s="4" t="str">
+        <v>INJECTION</v>
+      </c>
+      <c r="K5" s="4" t="str">
+        <v>QD</v>
+      </c>
+      <c r="L5" s="4" t="str">
+        <v>SUBCUTANEOUS</v>
+      </c>
+      <c r="M5" s="4" t="str">
+        <v>SDS580-359</v>
+      </c>
+      <c r="N5" s="4">
+        <v>10.8</v>
+      </c>
+      <c r="O5" s="4" t="str">
+        <v>g/L</v>
+      </c>
+      <c r="P5" s="4" t="str">
+        <v>TREATMENT</v>
+      </c>
+      <c r="Q5" s="4" t="str">
+        <v>2012-12-01T15:59:00</v>
+      </c>
+      <c r="R5" s="4" t="str">
+        <v>2012-11-30</v>
+      </c>
+      <c r="S5" s="4">
+        <v>1</v>
+      </c>
+      <c r="T5" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="str">
+        <v>CDISCPILOT01</v>
+      </c>
+      <c r="B6" s="4" t="str">
+        <v>EC</v>
+      </c>
+      <c r="C6" s="4" t="str">
+        <v>CDISC001</v>
+      </c>
+      <c r="D6" s="4">
+        <v>2</v>
+      </c>
+      <c r="E6" s="4" t="str">
+        <v>ZANOMALINE</v>
+      </c>
+      <c r="F6" s="4" t="str">
+        <v>Y</v>
+      </c>
+      <c r="G6" s="4" t="str">
+        <v>Y</v>
+      </c>
+      <c r="H6" s="4">
+        <v>5</v>
+      </c>
+      <c r="I6" s="4" t="str">
+        <v>mL</v>
+      </c>
+      <c r="J6" s="4" t="str">
+        <v>INJECTION</v>
+      </c>
+      <c r="K6" s="4" t="str">
+        <v>QD</v>
+      </c>
+      <c r="L6" s="4" t="str">
+        <v>SUBCUTANEOUS</v>
+      </c>
+      <c r="M6" s="4" t="str">
+        <v>SDS580-359</v>
+      </c>
+      <c r="N6" s="4">
+        <v>10.8</v>
+      </c>
+      <c r="O6" s="4" t="str">
+        <v>g/L</v>
+      </c>
+      <c r="P6" s="4" t="str">
+        <v>TREATMENT</v>
+      </c>
+      <c r="Q6" s="4" t="str">
+        <v>2012-12-02T15:59:00</v>
+      </c>
+      <c r="R6" s="4" t="str">
+        <v>2012-12-01</v>
+      </c>
+      <c r="S6" s="4">
+        <v>2</v>
+      </c>
+      <c r="T6" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="str">
+        <v>CDISCPILOT01</v>
+      </c>
+      <c r="B7" s="4" t="str">
+        <v>EC</v>
+      </c>
+      <c r="C7" s="4" t="str">
+        <v>CDISC001</v>
+      </c>
+      <c r="D7" s="4">
+        <v>3</v>
+      </c>
+      <c r="E7" s="4" t="str">
+        <v>ZANOMALINE</v>
+      </c>
+      <c r="F7" s="4" t="str">
+        <v>Y</v>
+      </c>
+      <c r="G7" s="4" t="str">
+        <v>Y</v>
+      </c>
+      <c r="H7" s="4">
+        <v>5</v>
+      </c>
+      <c r="I7" s="4" t="str">
+        <v>mL</v>
+      </c>
+      <c r="J7" s="4" t="str">
+        <v>INJECTION</v>
+      </c>
+      <c r="K7" s="4" t="str">
+        <v>QD</v>
+      </c>
+      <c r="L7" s="4" t="str">
+        <v>SUBCUTANEOUS</v>
+      </c>
+      <c r="M7" s="4" t="str">
+        <v>SDS580-359</v>
+      </c>
+      <c r="N7" s="4">
+        <v>10.8</v>
+      </c>
+      <c r="O7" s="4" t="str">
+        <v>g/L</v>
+      </c>
+      <c r="P7" s="4" t="str">
+        <v>TREATMENT</v>
+      </c>
+      <c r="Q7" s="4" t="str">
+        <v>2012-12-03T15:59:00</v>
+      </c>
+      <c r="R7" s="4" t="str">
+        <v>2012-12-02</v>
+      </c>
+      <c r="S7" s="4">
+        <v>3</v>
+      </c>
+      <c r="T7" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="str">
+        <v>CDISCPILOT01</v>
+      </c>
+      <c r="B8" s="4" t="str">
+        <v>EC</v>
+      </c>
+      <c r="C8" s="4" t="str">
+        <v>CDISC001</v>
+      </c>
+      <c r="D8" s="4">
+        <v>4</v>
+      </c>
+      <c r="E8" s="4" t="str">
+        <v>ZANOMALINE</v>
+      </c>
+      <c r="F8" s="4" t="str">
+        <v>Y</v>
+      </c>
+      <c r="G8" s="4" t="str">
+        <v>Y</v>
+      </c>
+      <c r="H8" s="4">
+        <v>5</v>
+      </c>
+      <c r="I8" s="4" t="str">
+        <v>mL</v>
+      </c>
+      <c r="J8" s="4" t="str">
+        <v>INJECTION</v>
+      </c>
+      <c r="K8" s="4" t="str">
+        <v>QD</v>
+      </c>
+      <c r="L8" s="4" t="str">
+        <v>SUBCUTANEOUS</v>
+      </c>
+      <c r="M8" s="4" t="str">
+        <v>SDS580-359</v>
+      </c>
+      <c r="N8" s="4">
+        <v>10.8</v>
+      </c>
+      <c r="O8" s="4" t="str">
+        <v>g/L</v>
+      </c>
+      <c r="P8" s="4" t="str">
+        <v>TREATMENT</v>
+      </c>
+      <c r="Q8" s="4" t="str">
+        <v>2012-12-04T15:59:00</v>
+      </c>
+      <c r="R8" s="4" t="str">
+        <v>2012-12-03</v>
+      </c>
+      <c r="S8" s="4">
+        <v>4</v>
+      </c>
+      <c r="T8" s="4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="str">
+        <v>CDISCPILOT01</v>
+      </c>
+      <c r="B9" s="4" t="str">
+        <v>EC</v>
+      </c>
+      <c r="C9" s="4" t="str">
+        <v>CDISC001</v>
+      </c>
+      <c r="D9" s="4">
+        <v>5</v>
+      </c>
+      <c r="E9" s="4" t="str">
+        <v>ZANOMALINE</v>
+      </c>
+      <c r="F9" s="4" t="str">
+        <v>Y</v>
+      </c>
+      <c r="G9" s="4" t="str">
+        <v>Y</v>
+      </c>
+      <c r="H9" s="4">
+        <v>5</v>
+      </c>
+      <c r="I9" s="4" t="str">
+        <v>mL</v>
+      </c>
+      <c r="J9" s="4" t="str">
+        <v>INJECTION</v>
+      </c>
+      <c r="K9" s="4" t="str">
+        <v>QD</v>
+      </c>
+      <c r="L9" s="4" t="str">
+        <v>SUBCUTANEOUS</v>
+      </c>
+      <c r="M9" s="4" t="str">
+        <v>SDS580-359</v>
+      </c>
+      <c r="N9" s="4">
+        <v>10.8</v>
+      </c>
+      <c r="O9" s="4" t="str">
+        <v>g/L</v>
+      </c>
+      <c r="P9" s="4" t="str">
+        <v>TREATMENT</v>
+      </c>
+      <c r="Q9" s="4" t="str">
+        <v>2012-12-05T15:59:00</v>
+      </c>
+      <c r="R9" s="4" t="str">
+        <v>2012-12-04</v>
+      </c>
+      <c r="S9" s="4">
+        <v>5</v>
+      </c>
+      <c r="T9" s="4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="str">
+        <v>CDISCPILOT01</v>
+      </c>
+      <c r="B10" s="4" t="str">
+        <v>EC</v>
+      </c>
+      <c r="C10" s="4" t="str">
+        <v>CDISC001</v>
+      </c>
+      <c r="D10" s="4">
+        <v>6</v>
+      </c>
+      <c r="E10" s="4" t="str">
+        <v>ZANOMALINE</v>
+      </c>
+      <c r="F10" s="4" t="str">
+        <v>Y</v>
+      </c>
+      <c r="G10" s="4" t="str">
+        <v>Y</v>
+      </c>
+      <c r="H10" s="4">
+        <v>5</v>
+      </c>
+      <c r="I10" s="4" t="str">
+        <v>mL</v>
+      </c>
+      <c r="J10" s="4" t="str">
+        <v>INJECTION</v>
+      </c>
+      <c r="K10" s="4" t="str">
+        <v>QD</v>
+      </c>
+      <c r="L10" s="4" t="str">
+        <v>SUBCUTANEOUS</v>
+      </c>
+      <c r="M10" s="4" t="str">
+        <v>SDS580-359</v>
+      </c>
+      <c r="N10" s="4">
+        <v>10.8</v>
+      </c>
+      <c r="O10" s="4" t="str">
+        <v>g/L</v>
+      </c>
+      <c r="P10" s="4" t="str">
+        <v>TREATMENT</v>
+      </c>
+      <c r="Q10" s="4" t="str">
+        <v>2012-12-06T15:59:00</v>
+      </c>
+      <c r="R10" s="4" t="str">
+        <v>2012-12-05</v>
+      </c>
+      <c r="S10" s="4">
+        <v>6</v>
+      </c>
+      <c r="T10" s="4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="str">
+        <v>CDISCPILOT01</v>
+      </c>
+      <c r="B11" s="4" t="str">
+        <v>EC</v>
+      </c>
+      <c r="C11" s="4" t="str">
+        <v>CDISC001</v>
+      </c>
+      <c r="D11" s="4">
+        <v>7</v>
+      </c>
+      <c r="E11" s="4" t="str">
+        <v>ZANOMALINE</v>
+      </c>
+      <c r="F11" s="4" t="str">
+        <v>Y</v>
+      </c>
+      <c r="G11" s="4" t="str">
+        <v>Y</v>
+      </c>
+      <c r="H11" s="4">
+        <v>5</v>
+      </c>
+      <c r="I11" s="4" t="str">
+        <v>mL</v>
+      </c>
+      <c r="J11" s="4" t="str">
+        <v>INJECTION</v>
+      </c>
+      <c r="K11" s="4" t="str">
+        <v>QD</v>
+      </c>
+      <c r="L11" s="4" t="str">
+        <v>SUBCUTANEOUS</v>
+      </c>
+      <c r="M11" s="4" t="str">
+        <v>SDS580-359</v>
+      </c>
+      <c r="N11" s="4">
+        <v>10.8</v>
+      </c>
+      <c r="O11" s="4" t="str">
+        <v>g/L</v>
+      </c>
+      <c r="P11" s="4" t="str">
+        <v>TREATMENT</v>
+      </c>
+      <c r="Q11" s="4" t="str">
+        <v>2012-12-07T15:59:00</v>
+      </c>
+      <c r="R11" s="4" t="str">
+        <v>2012-12-06</v>
+      </c>
+      <c r="S11" s="4">
+        <v>7</v>
+      </c>
+      <c r="T11" s="4">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="str">
+        <v>CDISCPILOT01</v>
+      </c>
+      <c r="B12" s="4" t="str">
+        <v>EC</v>
+      </c>
+      <c r="C12" s="4" t="str">
+        <v>CDISC001</v>
+      </c>
+      <c r="D12" s="4">
+        <v>8</v>
+      </c>
+      <c r="E12" s="4" t="str">
+        <v>ZANOMALINE</v>
+      </c>
+      <c r="F12" s="4" t="str">
+        <v>Y</v>
+      </c>
+      <c r="G12" s="4" t="str">
+        <v>Y</v>
+      </c>
+      <c r="H12" s="4">
+        <v>5</v>
+      </c>
+      <c r="I12" s="4" t="str">
+        <v>mL</v>
+      </c>
+      <c r="J12" s="4" t="str">
+        <v>INJECTION</v>
+      </c>
+      <c r="K12" s="4" t="str">
+        <v>QD</v>
+      </c>
+      <c r="L12" s="4" t="str">
+        <v>SUBCUTANEOUS</v>
+      </c>
+      <c r="M12" s="4" t="str">
+        <v>SDS580-359</v>
+      </c>
+      <c r="N12" s="4">
+        <v>10.8</v>
+      </c>
+      <c r="O12" s="4" t="str">
+        <v>g/L</v>
+      </c>
+      <c r="P12" s="4" t="str">
+        <v>TREATMENT</v>
+      </c>
+      <c r="Q12" s="4" t="str">
+        <v>2012-12-08T15:59:00</v>
+      </c>
+      <c r="R12" s="4" t="str">
+        <v>2012-12-07</v>
+      </c>
+      <c r="S12" s="4">
+        <v>8</v>
+      </c>
+      <c r="T12" s="4">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="str">
+        <v>CDISCPILOT01</v>
+      </c>
+      <c r="B13" s="4" t="str">
+        <v>EC</v>
+      </c>
+      <c r="C13" s="4" t="str">
+        <v>CDISC001</v>
+      </c>
+      <c r="D13" s="4">
+        <v>9</v>
+      </c>
+      <c r="E13" s="4" t="str">
+        <v>ZANOMALINE</v>
+      </c>
+      <c r="F13" s="4" t="str">
+        <v>Y</v>
+      </c>
+      <c r="G13" s="4" t="str">
+        <v>Y</v>
+      </c>
+      <c r="H13" s="4">
+        <v>5</v>
+      </c>
+      <c r="I13" s="4" t="str">
+        <v>mL</v>
+      </c>
+      <c r="J13" s="4" t="str">
+        <v>INJECTION</v>
+      </c>
+      <c r="K13" s="4" t="str">
+        <v>QD</v>
+      </c>
+      <c r="L13" s="4" t="str">
+        <v>SUBCUTANEOUS</v>
+      </c>
+      <c r="M13" s="4" t="str">
+        <v>SDS580-359</v>
+      </c>
+      <c r="N13" s="4">
+        <v>10.8</v>
+      </c>
+      <c r="O13" s="4" t="str">
+        <v>g/L</v>
+      </c>
+      <c r="P13" s="4" t="str">
+        <v>TREATMENT</v>
+      </c>
+      <c r="Q13" s="4" t="str">
+        <v>2012-12-09T15:59:00</v>
+      </c>
+      <c r="R13" s="4" t="str">
+        <v>2012-12-08</v>
+      </c>
+      <c r="S13" s="4">
+        <v>9</v>
+      </c>
+      <c r="T13" s="4">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="str">
+        <v>CDISCPILOT01</v>
+      </c>
+      <c r="B14" s="4" t="str">
+        <v>EC</v>
+      </c>
+      <c r="C14" s="4" t="str">
+        <v>CDISC001</v>
+      </c>
+      <c r="D14" s="4">
+        <v>10</v>
+      </c>
+      <c r="E14" s="4" t="str">
+        <v>ZANOMALINE</v>
+      </c>
+      <c r="F14" s="4" t="str">
+        <v>Y</v>
+      </c>
+      <c r="G14" s="4" t="str">
+        <v>Y</v>
+      </c>
+      <c r="H14" s="4">
+        <v>5</v>
+      </c>
+      <c r="I14" s="4" t="str">
+        <v>mL</v>
+      </c>
+      <c r="J14" s="4" t="str">
+        <v>INJECTION</v>
+      </c>
+      <c r="K14" s="4" t="str">
+        <v>QD</v>
+      </c>
+      <c r="L14" s="4" t="str">
+        <v>SUBCUTANEOUS</v>
+      </c>
+      <c r="M14" s="4" t="str">
+        <v>SDS580-359</v>
+      </c>
+      <c r="N14" s="4">
+        <v>10.8</v>
+      </c>
+      <c r="O14" s="4" t="str">
+        <v>g/L</v>
+      </c>
+      <c r="P14" s="4" t="str">
+        <v>TREATMENT</v>
+      </c>
+      <c r="Q14" s="4" t="str">
+        <v>2012-12-10T15:59:00</v>
+      </c>
+      <c r="R14" s="4" t="str">
+        <v>2012-12-09</v>
+      </c>
+      <c r="S14" s="4">
+        <v>10</v>
+      </c>
+      <c r="T14" s="4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="str">
+        <v>CDISCPILOT01</v>
+      </c>
+      <c r="B15" s="4" t="str">
+        <v>EC</v>
+      </c>
+      <c r="C15" s="4" t="str">
+        <v>CDISC009</v>
+      </c>
+      <c r="D15" s="4">
+        <v>122</v>
+      </c>
+      <c r="E15" s="4" t="str">
+        <v>PLACEBO</v>
+      </c>
+      <c r="F15" s="4" t="str">
+        <v>Y</v>
+      </c>
+      <c r="G15" s="4" t="str">
+        <v>N</v>
+      </c>
+      <c r="H15" s="4">
+        <v>0</v>
+      </c>
+      <c r="I15" s="4" t="str">
+        <v>mL</v>
+      </c>
+      <c r="J15" s="4" t="str">
+        <v>INJECTION</v>
+      </c>
+      <c r="K15" s="4" t="str">
+        <v>QD</v>
+      </c>
+      <c r="L15" s="4" t="str">
+        <v>SUBCUTANEOUS</v>
+      </c>
+      <c r="M15" s="4" t="str">
+        <v>SDS580-485</v>
+      </c>
+      <c r="N15" s="4">
+        <v>0</v>
+      </c>
+      <c r="O15" s="4" t="str">
+        <v>g/L</v>
+      </c>
+      <c r="P15" s="4" t="str">
+        <v>TREATMENT</v>
+      </c>
+      <c r="Q15" s="4" t="str">
+        <v>2013-04-15T15:59:00</v>
+      </c>
+      <c r="R15" s="4" t="str">
+        <v>2013-02-20</v>
+      </c>
+      <c r="S15" s="4">
+        <v>122</v>
+      </c>
+      <c r="T15" s="4">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="str">
+        <v>CDISCPILOT01</v>
+      </c>
+      <c r="B16" s="4" t="str">
+        <v>EC</v>
+      </c>
+      <c r="C16" s="4" t="str">
+        <v>CDISC009</v>
+      </c>
+      <c r="D16" s="4">
+        <v>123</v>
+      </c>
+      <c r="E16" s="4" t="str">
+        <v>PLACEBO</v>
+      </c>
+      <c r="F16" s="4" t="str">
+        <v>Y</v>
+      </c>
+      <c r="G16" s="4" t="str">
+        <v>N</v>
+      </c>
+      <c r="H16" s="4">
+        <v>20</v>
+      </c>
+      <c r="I16" s="4" t="str">
+        <v>mL</v>
+      </c>
+      <c r="J16" s="4" t="str">
+        <v>INJECTION</v>
+      </c>
+      <c r="K16" s="4" t="str">
+        <v>QD</v>
+      </c>
+      <c r="L16" s="4" t="str">
+        <v>SUBCUTANEOUS</v>
+      </c>
+      <c r="M16" s="4" t="str">
+        <v>SDS580-485</v>
+      </c>
+      <c r="N16" s="4">
+        <v>0</v>
+      </c>
+      <c r="O16" s="4" t="str">
+        <v>g/L</v>
+      </c>
+      <c r="P16" s="4" t="str">
+        <v>TREATMENT</v>
+      </c>
+      <c r="Q16" s="4" t="str">
+        <v>2013-04-16T15:59:00</v>
+      </c>
+      <c r="R16" s="4" t="str">
+        <v>2013-02-21</v>
+      </c>
+      <c r="S16" s="4">
+        <v>123</v>
+      </c>
+      <c r="T16" s="4">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="str">
+        <v>CDISCPILOT01</v>
+      </c>
+      <c r="B17" s="4" t="str">
+        <v>EC</v>
+      </c>
+      <c r="C17" s="4" t="str">
+        <v>CDISC009</v>
+      </c>
+      <c r="D17" s="4">
+        <v>124</v>
+      </c>
+      <c r="E17" s="4" t="str">
+        <v>PLACEBO</v>
+      </c>
+      <c r="F17" s="4" t="str">
+        <v>Y</v>
+      </c>
+      <c r="G17" s="4" t="str">
+        <v>N</v>
+      </c>
+      <c r="H17" s="4">
+        <v>0</v>
+      </c>
+      <c r="I17" s="4" t="str">
+        <v>mL</v>
+      </c>
+      <c r="J17" s="4" t="str">
+        <v>INJECTION</v>
+      </c>
+      <c r="K17" s="4" t="str">
+        <v>QD</v>
+      </c>
+      <c r="L17" s="4" t="str">
+        <v>SUBCUTANEOUS</v>
+      </c>
+      <c r="M17" s="4" t="str">
+        <v>SDS580-485</v>
+      </c>
+      <c r="N17" s="4">
+        <v>0</v>
+      </c>
+      <c r="O17" s="4" t="str">
+        <v>g/L</v>
+      </c>
+      <c r="P17" s="4" t="str">
+        <v>TREATMENT</v>
+      </c>
+      <c r="Q17" s="4" t="str">
+        <v>2013-04-17T15:59:00</v>
+      </c>
+      <c r="R17" s="4" t="str">
+        <v>2013-02-22</v>
+      </c>
+      <c r="S17" s="4">
+        <v>124</v>
+      </c>
+      <c r="T17" s="4">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="str">
+        <v>CDISCPILOT01</v>
+      </c>
+      <c r="B18" s="4" t="str">
+        <v>EC</v>
+      </c>
+      <c r="C18" s="4" t="str">
+        <v>CDISC009</v>
+      </c>
+      <c r="D18" s="4">
+        <v>125</v>
+      </c>
+      <c r="E18" s="4" t="str">
+        <v>PLACEBO</v>
+      </c>
+      <c r="F18" s="4" t="str">
+        <v>Y</v>
+      </c>
+      <c r="G18" s="4" t="str">
+        <v>N</v>
+      </c>
+      <c r="H18" s="4">
+        <v>0</v>
+      </c>
+      <c r="I18" s="4" t="str">
+        <v>mL</v>
+      </c>
+      <c r="J18" s="4" t="str">
+        <v>INJECTION</v>
+      </c>
+      <c r="K18" s="4" t="str">
+        <v>QD</v>
+      </c>
+      <c r="L18" s="4" t="str">
+        <v>SUBCUTANEOUS</v>
+      </c>
+      <c r="M18" s="4" t="str">
+        <v>SDS580-485</v>
+      </c>
+      <c r="N18" s="4">
+        <v>0</v>
+      </c>
+      <c r="O18" s="4" t="str">
+        <v>g/L</v>
+      </c>
+      <c r="P18" s="4" t="str">
+        <v>TREATMENT</v>
+      </c>
+      <c r="Q18" s="4" t="str">
+        <v>2013-04-18T15:59:00</v>
+      </c>
+      <c r="R18" s="4" t="str">
+        <v>2013-02-23</v>
+      </c>
+      <c r="S18" s="4">
+        <v>125</v>
+      </c>
+      <c r="T18" s="4">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="str">
+        <v>CDISCPILOT01</v>
+      </c>
+      <c r="B19" s="4" t="str">
+        <v>EC</v>
+      </c>
+      <c r="C19" s="4" t="str">
+        <v>CDISC009</v>
+      </c>
+      <c r="D19" s="4">
+        <v>126</v>
+      </c>
+      <c r="E19" s="4" t="str">
+        <v>PLACEBO</v>
+      </c>
+      <c r="F19" s="4" t="str">
+        <v>Y</v>
+      </c>
+      <c r="G19" s="4" t="str">
+        <v>N</v>
+      </c>
+      <c r="H19" s="4">
+        <v>-10</v>
+      </c>
+      <c r="I19" s="4" t="str">
+        <v>mL</v>
+      </c>
+      <c r="J19" s="4" t="str">
+        <v>INJECTION</v>
+      </c>
+      <c r="K19" s="4" t="str">
+        <v>QD</v>
+      </c>
+      <c r="L19" s="4" t="str">
+        <v>SUBCUTANEOUS</v>
+      </c>
+      <c r="M19" s="4" t="str">
+        <v>SDS580-485</v>
+      </c>
+      <c r="N19" s="4">
+        <v>0</v>
+      </c>
+      <c r="O19" s="4" t="str">
+        <v>g/L</v>
+      </c>
+      <c r="P19" s="4" t="str">
+        <v>TREATMENT</v>
+      </c>
+      <c r="Q19" s="4" t="str">
+        <v>2013-04-19T15:59:00</v>
+      </c>
+      <c r="R19" s="4" t="str">
+        <v>2013-02-24</v>
+      </c>
+      <c r="S19" s="4">
+        <v>126</v>
+      </c>
+      <c r="T19" s="4">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="str">
+        <v>CDISCPILOT01</v>
+      </c>
+      <c r="B20" s="4" t="str">
+        <v>EC</v>
+      </c>
+      <c r="C20" s="4" t="str">
+        <v>CDISC009</v>
+      </c>
+      <c r="D20" s="4">
+        <v>127</v>
+      </c>
+      <c r="E20" s="4" t="str">
+        <v>PLACEBO</v>
+      </c>
+      <c r="F20" s="4" t="str">
+        <v>Y</v>
+      </c>
+      <c r="G20" s="4" t="str">
+        <v>N</v>
+      </c>
+      <c r="H20" s="4" t="str">
+        <v/>
+      </c>
+      <c r="I20" s="4" t="str">
+        <v/>
+      </c>
+      <c r="J20" s="4" t="str">
+        <v>INJECTION</v>
+      </c>
+      <c r="K20" s="4" t="str">
+        <v>QD</v>
+      </c>
+      <c r="L20" s="4" t="str">
+        <v>SUBCUTANEOUS</v>
+      </c>
+      <c r="M20" s="4" t="str">
+        <v>SDS580-485</v>
+      </c>
+      <c r="N20" s="4">
+        <v>0</v>
+      </c>
+      <c r="O20" s="4" t="str">
+        <v>g/L</v>
+      </c>
+      <c r="P20" s="4" t="str">
+        <v>TREATMENT</v>
+      </c>
+      <c r="Q20" s="4" t="str">
+        <v>2013-04-20T15:59:00</v>
+      </c>
+      <c r="R20" s="4" t="str">
+        <v>2013-02-25</v>
+      </c>
+      <c r="S20" s="4">
+        <v>127</v>
+      </c>
+      <c r="T20" s="4">
+        <v>127</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:T20"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:R7"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="str">
+        <v>STUDYID</v>
+      </c>
+      <c r="B1" s="3" t="str">
+        <v>DOMAIN</v>
+      </c>
+      <c r="C1" s="3" t="str">
+        <v>USUBJID</v>
+      </c>
+      <c r="D1" s="3" t="str">
+        <v>EXSEQ</v>
+      </c>
+      <c r="E1" s="3" t="str">
+        <v>EXLNKID</v>
+      </c>
+      <c r="F1" s="3" t="str">
+        <v>EXTRT</v>
+      </c>
+      <c r="G1" s="3" t="str">
+        <v>EXDOSE</v>
+      </c>
+      <c r="H1" s="3" t="str">
+        <v>EXDOSTXT</v>
+      </c>
+      <c r="I1" s="3" t="str">
+        <v>EXDOSU</v>
+      </c>
+      <c r="J1" s="3" t="str">
+        <v>EXDOSFRM</v>
+      </c>
+      <c r="K1" s="3" t="str">
+        <v>EXDOSFRQ</v>
+      </c>
+      <c r="L1" s="3" t="str">
+        <v>EXROUTE</v>
+      </c>
+      <c r="M1" s="3" t="str">
+        <v>EXVAMT</v>
+      </c>
+      <c r="N1" s="3" t="str">
+        <v>EXVAMTU</v>
+      </c>
+      <c r="O1" s="3" t="str">
+        <v>EXSTDTC</v>
+      </c>
+      <c r="P1" s="3" t="str">
+        <v>EXENDTC</v>
+      </c>
+      <c r="Q1" s="3" t="str">
+        <v>EXSTDY</v>
+      </c>
+      <c r="R1" s="3" t="str">
+        <v>EXENDY</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="str">
+        <v>Study Identifier</v>
+      </c>
+      <c r="B2" s="5" t="str">
+        <v>Domain Abbreviation</v>
+      </c>
+      <c r="C2" s="5" t="str">
+        <v>Unique Subject Identifier</v>
+      </c>
+      <c r="D2" s="5" t="str">
+        <v>Sequence Number</v>
+      </c>
+      <c r="E2" s="5" t="str">
+        <v>Link ID</v>
+      </c>
+      <c r="F2" s="5" t="str">
+        <v>Name of Treatment</v>
+      </c>
+      <c r="G2" s="5" t="str">
+        <v>Dose</v>
+      </c>
+      <c r="H2" s="5" t="str">
+        <v>Dose Description</v>
+      </c>
+      <c r="I2" s="5" t="str">
+        <v>Dose Units</v>
+      </c>
+      <c r="J2" s="5" t="str">
+        <v>Dose Form</v>
+      </c>
+      <c r="K2" s="5" t="str">
+        <v>Dosing Frequency per Interval</v>
+      </c>
+      <c r="L2" s="5" t="str">
+        <v>Route of Administration</v>
+      </c>
+      <c r="M2" s="5" t="str">
+        <v>Dose</v>
+      </c>
+      <c r="N2" s="5" t="str">
+        <v>Dose Units</v>
+      </c>
+      <c r="O2" s="5" t="str">
+        <v>Start Date/Time of Treatment</v>
+      </c>
+      <c r="P2" s="5" t="str">
+        <v>End Date/Time of Treatment</v>
+      </c>
+      <c r="Q2" s="5" t="str">
+        <v>Study Day of Start of Treatment</v>
+      </c>
+      <c r="R2" s="5" t="str">
+        <v>Study Day of End of Treatment</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="B3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="C3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="D3" s="5" t="str">
+        <v>Num</v>
+      </c>
+      <c r="E3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="F3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="G3" s="5" t="str">
+        <v>Num</v>
+      </c>
+      <c r="H3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="I3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="J3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="K3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="L3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="M3" s="5" t="str">
+        <v>Num</v>
+      </c>
+      <c r="N3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="O3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="P3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="Q3" s="5" t="str">
+        <v>Num</v>
+      </c>
+      <c r="R3" s="5" t="str">
+        <v>Num</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5">
+        <v>50</v>
+      </c>
+      <c r="B4" s="5">
+        <v>50</v>
+      </c>
+      <c r="C4" s="5">
+        <v>50</v>
+      </c>
+      <c r="D4" s="5">
+        <v>8</v>
+      </c>
+      <c r="E4" s="5">
+        <v>50</v>
+      </c>
+      <c r="F4" s="5">
+        <v>50</v>
+      </c>
+      <c r="G4" s="5">
+        <v>8</v>
+      </c>
+      <c r="H4" s="5">
+        <v>50</v>
+      </c>
+      <c r="I4" s="5">
+        <v>50</v>
+      </c>
+      <c r="J4" s="5">
+        <v>50</v>
+      </c>
+      <c r="K4" s="5">
+        <v>50</v>
+      </c>
+      <c r="L4" s="5">
+        <v>50</v>
+      </c>
+      <c r="M4" s="5">
+        <v>8</v>
+      </c>
+      <c r="N4" s="5">
+        <v>50</v>
+      </c>
+      <c r="O4" s="5">
+        <v>50</v>
+      </c>
+      <c r="P4" s="5">
+        <v>50</v>
+      </c>
+      <c r="Q4" s="5">
+        <v>8</v>
+      </c>
+      <c r="R4" s="5">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="str">
+        <v>ABC</v>
+      </c>
+      <c r="B5" s="2" t="str">
+        <v>EX</v>
+      </c>
+      <c r="C5" s="4" t="str">
+        <v>CDISC001</v>
+      </c>
+      <c r="D5" s="2">
+        <v>1</v>
+      </c>
+      <c r="E5" s="2" t="str">
+        <v>A2-10110114</v>
+      </c>
+      <c r="F5" s="2" t="str">
+        <v>DRUG X</v>
+      </c>
+      <c r="G5" s="2">
+        <v>3</v>
+      </c>
+      <c r="H5" s="2" t="str">
+        <v/>
+      </c>
+      <c r="I5" s="4" t="str">
+        <v>mg/kg</v>
+      </c>
+      <c r="J5" s="2" t="str">
+        <v>INJECTION</v>
+      </c>
+      <c r="K5" s="2" t="str">
+        <v>ONCE</v>
+      </c>
+      <c r="L5" s="2" t="str">
+        <v>SUBCUTANEOUS</v>
+      </c>
+      <c r="M5" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="N5" s="4" t="str">
+        <v>mL</v>
+      </c>
+      <c r="O5" s="4" t="str">
+        <v>2012-12-30T15:59:00</v>
+      </c>
+      <c r="P5" s="4" t="str">
+        <v>2011-01-28</v>
+      </c>
+      <c r="Q5" s="2">
+        <v>1</v>
+      </c>
+      <c r="R5" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="str">
+        <v>ABC</v>
+      </c>
+      <c r="B6" s="2" t="str">
+        <v>EX</v>
+      </c>
+      <c r="C6" s="4" t="str">
+        <v>CDISC002</v>
+      </c>
+      <c r="D6" s="2">
+        <v>1</v>
+      </c>
+      <c r="E6" s="2" t="str">
+        <v>A2-20110114</v>
+      </c>
+      <c r="F6" s="2" t="str">
+        <v>DRUG Z</v>
+      </c>
+      <c r="G6" s="2">
+        <v>500</v>
+      </c>
+      <c r="H6" s="2" t="str">
+        <v/>
+      </c>
+      <c r="I6" s="2" t="str">
+        <v>mg</v>
+      </c>
+      <c r="J6" s="2" t="str">
+        <v>TABLET</v>
+      </c>
+      <c r="K6" s="2" t="str">
+        <v>QD</v>
+      </c>
+      <c r="L6" s="2" t="str">
+        <v>ORAL</v>
+      </c>
+      <c r="M6" s="2" t="str">
+        <v/>
+      </c>
+      <c r="N6" s="2" t="str">
+        <v/>
+      </c>
+      <c r="O6" s="4" t="str">
+        <v>2012-12-14T15:59:00</v>
+      </c>
+      <c r="P6" s="4" t="str">
+        <v>2011-01-23</v>
+      </c>
+      <c r="Q6" s="2">
+        <v>1</v>
+      </c>
+      <c r="R6" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="str">
+        <v>ABC</v>
+      </c>
+      <c r="B7" s="2" t="str">
+        <v>EX</v>
+      </c>
+      <c r="C7" s="4" t="str">
+        <v>CDISC003</v>
+      </c>
+      <c r="D7" s="2">
+        <v>2</v>
+      </c>
+      <c r="E7" s="2" t="str">
+        <v>A2-20110125</v>
+      </c>
+      <c r="F7" s="2" t="str">
+        <v>DRUG Z</v>
+      </c>
+      <c r="G7" s="2">
+        <v>500</v>
+      </c>
+      <c r="H7" s="2" t="str">
+        <v/>
+      </c>
+      <c r="I7" s="2" t="str">
+        <v>mg</v>
+      </c>
+      <c r="J7" s="2" t="str">
+        <v>TABLET</v>
+      </c>
+      <c r="K7" s="2" t="str">
+        <v>QD</v>
+      </c>
+      <c r="L7" s="2" t="str">
+        <v>ORAL</v>
+      </c>
+      <c r="M7" s="2" t="str">
+        <v/>
+      </c>
+      <c r="N7" s="2" t="str">
+        <v/>
+      </c>
+      <c r="O7" s="4" t="str">
+        <v>2013-10-25T15:59:00</v>
+      </c>
+      <c r="P7" s="4" t="str">
+        <v>2014-01-28</v>
+      </c>
+      <c r="Q7" s="2">
+        <v>12</v>
+      </c>
+      <c r="R7" s="2">
+        <v>15</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:R7"/>
+  </ignoredErrors>
 </worksheet>
 </file>
--- a/rules/NEW-RULE/positive/01/data/new-rule-positive-01.xlsx
+++ b/rules/NEW-RULE/positive/01/data/new-rule-positive-01.xlsx
@@ -650,13 +650,13 @@
         <v/>
       </c>
       <c r="E5" s="6" t="str">
-        <v>CTAUG</v>
+        <v>FDATCHSP</v>
       </c>
       <c r="F5" s="6" t="str">
-        <v>CDISC Therapeutic Area User Guide</v>
+        <v>FDA Technical Specification Response</v>
       </c>
       <c r="G5" s="6" t="str">
-        <v>Tuberculosis Therapeutic Area User Guide v2.0</v>
+        <v>Study Data Technical Conformance Guide v4.2.1</v>
       </c>
       <c r="H5" s="6" t="str">
         <v>NA</v>

--- a/rules/NEW-RULE/positive/01/data/new-rule-positive-01.xlsx
+++ b/rules/NEW-RULE/positive/01/data/new-rule-positive-01.xlsx
@@ -668,7 +668,7 @@
         <v/>
       </c>
       <c r="K5" s="6" t="str">
-        <v/>
+        <v>2025-03-28</v>
       </c>
     </row>
   </sheetData>

--- a/rules/NEW-RULE/positive/01/data/new-rule-positive-01.xlsx
+++ b/rules/NEW-RULE/positive/01/data/new-rule-positive-01.xlsx
@@ -1,41 +1,614 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/enrico/Work/core-contributor/rules/NEW-RULE/positive/01/data/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A7E65A1-7F88-124E-A1AF-F4BF002E15A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="30240" yWindow="-4560" windowWidth="51200" windowHeight="28800" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Library" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Datasets" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Library" sheetId="1" r:id="rId1"/>
+    <sheet name="Datasets" sheetId="2" r:id="rId2"/>
+    <sheet name="dm.xpt" sheetId="10" r:id="rId3"/>
+    <sheet name="lb.xpt" sheetId="11" r:id="rId4"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="178">
+  <si>
+    <t>Product</t>
+  </si>
+  <si>
+    <t>Version</t>
+  </si>
+  <si>
+    <t>sdtmig</t>
+  </si>
+  <si>
+    <t>Filename</t>
+  </si>
+  <si>
+    <t>Label</t>
+  </si>
+  <si>
+    <t>dm.xpt</t>
+  </si>
+  <si>
+    <t>Demographics</t>
+  </si>
+  <si>
+    <t>STUDYID</t>
+  </si>
+  <si>
+    <t>DOMAIN</t>
+  </si>
+  <si>
+    <t>USUBJID</t>
+  </si>
+  <si>
+    <t>EPOCH</t>
+  </si>
+  <si>
+    <t>Study Identifier</t>
+  </si>
+  <si>
+    <t>Domain Abbreviation</t>
+  </si>
+  <si>
+    <t>Unique Subject Identifier</t>
+  </si>
+  <si>
+    <t>Sequence Number</t>
+  </si>
+  <si>
+    <t>Epoch</t>
+  </si>
+  <si>
+    <t>End Relative to Reference Time Point</t>
+  </si>
+  <si>
+    <t>End Reference Time Point</t>
+  </si>
+  <si>
+    <t>Char</t>
+  </si>
+  <si>
+    <t>Num</t>
+  </si>
+  <si>
+    <t>CDISCPILOT01</t>
+  </si>
+  <si>
+    <t>CDISC001</t>
+  </si>
+  <si>
+    <t>CDISC002</t>
+  </si>
+  <si>
+    <t>CDISC003</t>
+  </si>
+  <si>
+    <t>COINCIDENT</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>ARM</t>
+  </si>
+  <si>
+    <t>2012-11-23</t>
+  </si>
+  <si>
+    <t>2013-01-23</t>
+  </si>
+  <si>
+    <t>2013-05-20</t>
+  </si>
+  <si>
+    <t>SUBJID</t>
+  </si>
+  <si>
+    <t>RFSTDTC</t>
+  </si>
+  <si>
+    <t>RFENDTC</t>
+  </si>
+  <si>
+    <t>RFXSTDTC</t>
+  </si>
+  <si>
+    <t>RFXENDTC</t>
+  </si>
+  <si>
+    <t>RFICDTC</t>
+  </si>
+  <si>
+    <t>RFPENDTC</t>
+  </si>
+  <si>
+    <t>DTHDTC</t>
+  </si>
+  <si>
+    <t>DTHFL</t>
+  </si>
+  <si>
+    <t>SITEID</t>
+  </si>
+  <si>
+    <t>BRTHDTC</t>
+  </si>
+  <si>
+    <t>AGE</t>
+  </si>
+  <si>
+    <t>AGEU</t>
+  </si>
+  <si>
+    <t>SEX</t>
+  </si>
+  <si>
+    <t>RACE</t>
+  </si>
+  <si>
+    <t>ETHNIC</t>
+  </si>
+  <si>
+    <t>ARMCD</t>
+  </si>
+  <si>
+    <t>ACTARMCD</t>
+  </si>
+  <si>
+    <t>ACTARM</t>
+  </si>
+  <si>
+    <t>ARMNRS</t>
+  </si>
+  <si>
+    <t>ACTARMUD</t>
+  </si>
+  <si>
+    <t>COUNTRY</t>
+  </si>
+  <si>
+    <t>Subject Identifier for the Study</t>
+  </si>
+  <si>
+    <t>Subject Reference Start Date/Time</t>
+  </si>
+  <si>
+    <t>Subject Reference End Date/Time</t>
+  </si>
+  <si>
+    <t>Date/Time of First Study Treatment</t>
+  </si>
+  <si>
+    <t>Date/Time of Last Study Treatment</t>
+  </si>
+  <si>
+    <t>Date/Time of Informed Consent</t>
+  </si>
+  <si>
+    <t>Date/Time of End of Participation</t>
+  </si>
+  <si>
+    <t>Date/Time of Death</t>
+  </si>
+  <si>
+    <t>Subject Death Flag</t>
+  </si>
+  <si>
+    <t>Study Site Identifier</t>
+  </si>
+  <si>
+    <t>Date/Time of Birth</t>
+  </si>
+  <si>
+    <t>Age</t>
+  </si>
+  <si>
+    <t>Age Units</t>
+  </si>
+  <si>
+    <t>Sex</t>
+  </si>
+  <si>
+    <t>Race</t>
+  </si>
+  <si>
+    <t>Ethnicity</t>
+  </si>
+  <si>
+    <t>Planned Arm Code</t>
+  </si>
+  <si>
+    <t>Description of Planned Arm</t>
+  </si>
+  <si>
+    <t>Actual Arm Code</t>
+  </si>
+  <si>
+    <t>Description of Actual Arm</t>
+  </si>
+  <si>
+    <t>Reason Arm and/or Actual Arm is Null</t>
+  </si>
+  <si>
+    <t>Description of Unplanned Actual Arm</t>
+  </si>
+  <si>
+    <t>Country</t>
+  </si>
+  <si>
+    <t>DM</t>
+  </si>
+  <si>
+    <t>YEARS</t>
+  </si>
+  <si>
+    <t>M</t>
+  </si>
+  <si>
+    <t>WHITE</t>
+  </si>
+  <si>
+    <t>NOT HISPANIC OR LATINO</t>
+  </si>
+  <si>
+    <t>ZAN_LOW</t>
+  </si>
+  <si>
+    <t>Zanomaline Low Dose (54 mg)</t>
+  </si>
+  <si>
+    <t>USA</t>
+  </si>
+  <si>
+    <t>3-4</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>2012-11-30T15:59:00</t>
+  </si>
+  <si>
+    <t>2013-01-23T15:59:00</t>
+  </si>
+  <si>
+    <t>2012-11-15</t>
+  </si>
+  <si>
+    <t>2013-01-14</t>
+  </si>
+  <si>
+    <t>2012-11-15T15:59:00</t>
+  </si>
+  <si>
+    <t>2013-01-12T15:59:00</t>
+  </si>
+  <si>
+    <t>2012-10-30</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>2013-11-05</t>
+  </si>
+  <si>
+    <t>2013-08-29T15:59:00</t>
+  </si>
+  <si>
+    <t>2013-11-05T15:59:00</t>
+  </si>
+  <si>
+    <t>2013-08-20</t>
+  </si>
+  <si>
+    <t>2014-02-13</t>
+  </si>
+  <si>
+    <t>ZAN_HIGH</t>
+  </si>
+  <si>
+    <t>Zanomaline High Dose (81 mg)</t>
+  </si>
+  <si>
+    <t>LBSEQ</t>
+  </si>
+  <si>
+    <t>LBTESTCD</t>
+  </si>
+  <si>
+    <t>LBTEST</t>
+  </si>
+  <si>
+    <t>LBCAT</t>
+  </si>
+  <si>
+    <t>LBORRES</t>
+  </si>
+  <si>
+    <t>LBORRESU</t>
+  </si>
+  <si>
+    <t>LBORNRLO</t>
+  </si>
+  <si>
+    <t>LBORNRHI</t>
+  </si>
+  <si>
+    <t>LBSTRESC</t>
+  </si>
+  <si>
+    <t>LBSTRESN</t>
+  </si>
+  <si>
+    <t>LBSTRESU</t>
+  </si>
+  <si>
+    <t>LBSTNRLO</t>
+  </si>
+  <si>
+    <t>LBSTNRHI</t>
+  </si>
+  <si>
+    <t>LBNRIND</t>
+  </si>
+  <si>
+    <t>LBLOBXFL</t>
+  </si>
+  <si>
+    <t>VISITNUM</t>
+  </si>
+  <si>
+    <t>VISIT</t>
+  </si>
+  <si>
+    <t>LBDTC</t>
+  </si>
+  <si>
+    <t>LBENDTC</t>
+  </si>
+  <si>
+    <t>LBENRTPT</t>
+  </si>
+  <si>
+    <t>LBENTPT</t>
+  </si>
+  <si>
+    <t>LBDY</t>
+  </si>
+  <si>
+    <t>Lab Test or Examination Short Name</t>
+  </si>
+  <si>
+    <t>Lab Test or Examination Name</t>
+  </si>
+  <si>
+    <t>Category for Lab Test</t>
+  </si>
+  <si>
+    <t>Result or Finding in Original Units</t>
+  </si>
+  <si>
+    <t>Original Units</t>
+  </si>
+  <si>
+    <t>Reference Range Lower Limit in Orig Unit</t>
+  </si>
+  <si>
+    <t>Reference Range Upper Limit in Orig Unit</t>
+  </si>
+  <si>
+    <t>Character Result/Finding in Std Format</t>
+  </si>
+  <si>
+    <t>Numeric Result/Finding in Standard Units</t>
+  </si>
+  <si>
+    <t>Standard Units</t>
+  </si>
+  <si>
+    <t>Reference Range Lower Limit-Std Units</t>
+  </si>
+  <si>
+    <t>Reference Range Upper Limit-Std Units</t>
+  </si>
+  <si>
+    <t>Reference Range Indicator</t>
+  </si>
+  <si>
+    <t>Last Observation Before Exposure Flag</t>
+  </si>
+  <si>
+    <t>Visit Number</t>
+  </si>
+  <si>
+    <t>Visit Name</t>
+  </si>
+  <si>
+    <t>Date/Time of Specimen Collection</t>
+  </si>
+  <si>
+    <t>End Date/Time of Specimen Collection</t>
+  </si>
+  <si>
+    <t>Study Day of Specimen Collection</t>
+  </si>
+  <si>
+    <t>LB</t>
+  </si>
+  <si>
+    <t>ALB</t>
+  </si>
+  <si>
+    <t>Albumin</t>
+  </si>
+  <si>
+    <t>CHEMISTRY</t>
+  </si>
+  <si>
+    <t>3.9</t>
+  </si>
+  <si>
+    <t>g/dL</t>
+  </si>
+  <si>
+    <t>3.5</t>
+  </si>
+  <si>
+    <t>4.6</t>
+  </si>
+  <si>
+    <t>39</t>
+  </si>
+  <si>
+    <t>g/L</t>
+  </si>
+  <si>
+    <t>NORMAL</t>
+  </si>
+  <si>
+    <t>SCREENING 1</t>
+  </si>
+  <si>
+    <t>SCREENING</t>
+  </si>
+  <si>
+    <t>ALP</t>
+  </si>
+  <si>
+    <t>Alkaline Phosphatase</t>
+  </si>
+  <si>
+    <t>93</t>
+  </si>
+  <si>
+    <t>U/L</t>
+  </si>
+  <si>
+    <t>35</t>
+  </si>
+  <si>
+    <t>115</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>36</t>
+  </si>
+  <si>
+    <t>BASO</t>
+  </si>
+  <si>
+    <t>Basophils</t>
+  </si>
+  <si>
+    <t>HEMATOLOGY</t>
+  </si>
+  <si>
+    <t>0.03</t>
+  </si>
+  <si>
+    <t>10^9/L</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>0.2</t>
+  </si>
+  <si>
+    <t>0.1</t>
+  </si>
+  <si>
+    <t>LBSTDTC</t>
+  </si>
+  <si>
+    <t>Start Date/Time of Specimen Collection</t>
+  </si>
+  <si>
+    <t>lb.xpt</t>
+  </si>
+  <si>
+    <t>Laboratory Test Results</t>
+  </si>
+  <si>
+    <t>2012-11-24</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor rgb="FFFFFFCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -43,85 +616,74 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD9D9D9"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD9D9D9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+  <cellXfs count="9">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -409,36 +971,24 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Product</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Version</t>
-        </is>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>sdtmig</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>3-4</t>
-        </is>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" t="s">
+        <v>83</v>
       </c>
     </row>
   </sheetData>
@@ -447,31 +997,1341 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Filename</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Label</t>
-        </is>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
-      <c r="B2" t="inlineStr"/>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>175</v>
+      </c>
+      <c r="B3" t="s">
+        <v>176</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
+  <dimension ref="A1:Z7"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="2" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A2" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="J2" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="K2" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="L2" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="M2" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="N2" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="O2" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="P2" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q2" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="R2" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="S2" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="T2" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="U2" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="V2" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="W2" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="X2" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y2" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="Z2" s="5" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="3" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A3" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="J3" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="K3" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="L3" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="M3" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="N3" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="O3" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="P3" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q3" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="R3" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="S3" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="T3" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="U3" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="V3" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="W3" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="X3" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y3" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z3" s="5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A4" s="5">
+        <v>12</v>
+      </c>
+      <c r="B4" s="5">
+        <v>2</v>
+      </c>
+      <c r="C4" s="5">
+        <v>8</v>
+      </c>
+      <c r="D4" s="5">
+        <v>4</v>
+      </c>
+      <c r="E4" s="5">
+        <v>10</v>
+      </c>
+      <c r="F4" s="5">
+        <v>10</v>
+      </c>
+      <c r="G4" s="5">
+        <v>19</v>
+      </c>
+      <c r="H4" s="5">
+        <v>19</v>
+      </c>
+      <c r="I4" s="5">
+        <v>10</v>
+      </c>
+      <c r="J4" s="5">
+        <v>10</v>
+      </c>
+      <c r="K4" s="5">
+        <v>10</v>
+      </c>
+      <c r="L4" s="5">
+        <v>1</v>
+      </c>
+      <c r="M4" s="5">
+        <v>3</v>
+      </c>
+      <c r="N4" s="5">
+        <v>10</v>
+      </c>
+      <c r="O4" s="5">
+        <v>8</v>
+      </c>
+      <c r="P4" s="5">
+        <v>5</v>
+      </c>
+      <c r="Q4" s="5">
+        <v>1</v>
+      </c>
+      <c r="R4" s="5">
+        <v>41</v>
+      </c>
+      <c r="S4" s="5">
+        <v>22</v>
+      </c>
+      <c r="T4" s="5">
+        <v>8</v>
+      </c>
+      <c r="U4" s="5">
+        <v>28</v>
+      </c>
+      <c r="V4" s="5">
+        <v>8</v>
+      </c>
+      <c r="W4" s="5">
+        <v>28</v>
+      </c>
+      <c r="X4" s="5">
+        <v>14</v>
+      </c>
+      <c r="Y4" s="5">
+        <v>200</v>
+      </c>
+      <c r="Z4" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A5" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D5" s="6">
+        <v>1115</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="H5" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="I5" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="J5" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="K5" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="L5" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="M5" s="6">
+        <v>701</v>
+      </c>
+      <c r="N5" s="6">
+        <v>1928</v>
+      </c>
+      <c r="O5" s="6">
+        <v>84</v>
+      </c>
+      <c r="P5" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q5" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="R5" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="S5" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="T5" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="U5" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="V5" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="W5" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="X5" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="Y5" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="Z5" s="6" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A6" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" s="6">
+        <v>1211</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="H6" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="I6" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="J6" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="K6" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="L6" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="M6" s="6">
+        <v>701</v>
+      </c>
+      <c r="N6" s="6">
+        <v>1936</v>
+      </c>
+      <c r="O6" s="6">
+        <v>76</v>
+      </c>
+      <c r="P6" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q6" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="R6" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="S6" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="T6" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="U6" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="V6" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="W6" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="X6" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="Y6" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="Z6" s="6" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A7" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D7" s="6">
+        <v>1302</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="G7" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="H7" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="I7" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="J7" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="K7" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="L7" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="M7" s="6">
+        <v>701</v>
+      </c>
+      <c r="N7" s="6">
+        <v>1951</v>
+      </c>
+      <c r="O7" s="6">
+        <v>61</v>
+      </c>
+      <c r="P7" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q7" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="R7" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="S7" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="T7" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="U7" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="V7" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="W7" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="X7" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="Y7" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="Z7" s="6" t="s">
+        <v>82</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8C96987-FD28-5544-826B-B09F38914901}">
+  <dimension ref="A1:AA9"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:27" ht="16" x14ac:dyDescent="0.2">
+      <c r="A1" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="H1" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="I1" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="J1" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="K1" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="L1" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="M1" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="N1" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="O1" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="P1" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="Q1" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="R1" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="S1" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="T1" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="U1" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="V1" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="W1" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="X1" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="Y1" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="Z1" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="AA1" s="7" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="2" spans="1:27" ht="80" x14ac:dyDescent="0.2">
+      <c r="A2" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="G2" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="H2" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="I2" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="J2" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="K2" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="L2" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="M2" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="N2" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="O2" s="8" t="s">
+        <v>132</v>
+      </c>
+      <c r="P2" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="Q2" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="R2" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="S2" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="T2" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="U2" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="V2" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="W2" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="X2" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="Y2" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="Z2" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="AA2" s="8" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="3" spans="1:27" ht="16" x14ac:dyDescent="0.2">
+      <c r="A3" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G3" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="I3" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="J3" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="K3" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="L3" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="M3" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="N3" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="O3" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="P3" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q3" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="R3" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="S3" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="T3" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="U3" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="V3" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="W3" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="X3" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y3" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z3" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="AA3" s="8" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A4" s="8">
+        <v>12</v>
+      </c>
+      <c r="B4" s="8">
+        <v>2</v>
+      </c>
+      <c r="C4" s="8">
+        <v>8</v>
+      </c>
+      <c r="D4" s="8">
+        <v>8</v>
+      </c>
+      <c r="E4" s="8">
+        <v>7</v>
+      </c>
+      <c r="F4" s="8">
+        <v>39</v>
+      </c>
+      <c r="G4" s="8">
+        <v>10</v>
+      </c>
+      <c r="H4" s="8">
+        <v>6</v>
+      </c>
+      <c r="I4" s="8">
+        <v>7</v>
+      </c>
+      <c r="J4" s="8">
+        <v>200</v>
+      </c>
+      <c r="K4" s="8">
+        <v>200</v>
+      </c>
+      <c r="L4" s="8">
+        <v>8</v>
+      </c>
+      <c r="M4" s="8">
+        <v>8</v>
+      </c>
+      <c r="N4" s="8">
+        <v>7</v>
+      </c>
+      <c r="O4" s="8">
+        <v>8</v>
+      </c>
+      <c r="P4" s="8">
+        <v>8</v>
+      </c>
+      <c r="Q4" s="8">
+        <v>8</v>
+      </c>
+      <c r="R4" s="8">
+        <v>1</v>
+      </c>
+      <c r="S4" s="8">
+        <v>8</v>
+      </c>
+      <c r="T4" s="8">
+        <v>200</v>
+      </c>
+      <c r="U4" s="8">
+        <v>9</v>
+      </c>
+      <c r="V4" s="8">
+        <v>19</v>
+      </c>
+      <c r="W4" s="8">
+        <v>19</v>
+      </c>
+      <c r="X4" s="8">
+        <v>19</v>
+      </c>
+      <c r="Y4" s="3">
+        <v>50</v>
+      </c>
+      <c r="Z4" s="3">
+        <v>50</v>
+      </c>
+      <c r="AA4" s="8">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:27" ht="32" x14ac:dyDescent="0.2">
+      <c r="A5" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D5" s="4">
+        <v>1</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="K5" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="L5" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="M5" s="4">
+        <v>39</v>
+      </c>
+      <c r="N5" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="Q5" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="R5" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="S5" s="4">
+        <v>1</v>
+      </c>
+      <c r="T5" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="U5" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="V5" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="W5" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="X5" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y5" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z5" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="AA5" s="4">
+        <v>-7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:27" ht="32" x14ac:dyDescent="0.2">
+      <c r="A6" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" s="4">
+        <v>2</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="I6" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="J6" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="K6" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="L6" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="M6" s="4">
+        <v>93</v>
+      </c>
+      <c r="N6" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="O6" s="4">
+        <v>35</v>
+      </c>
+      <c r="P6" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="Q6" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="R6" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="S6" s="4">
+        <v>1</v>
+      </c>
+      <c r="T6" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="U6" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="V6" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="W6" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="X6" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="Y6" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z6" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="AA6" s="4">
+        <v>-7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:27" ht="32" x14ac:dyDescent="0.2">
+      <c r="A7" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D7" s="4">
+        <v>3</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="I7" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="J7" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="K7" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="L7" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="M7" s="4">
+        <v>18</v>
+      </c>
+      <c r="N7" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="O7" s="4">
+        <v>6</v>
+      </c>
+      <c r="Q7" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="R7" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="S7" s="4">
+        <v>1</v>
+      </c>
+      <c r="T7" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="U7" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="V7" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="W7" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="X7" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="Z7" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="AA7" s="4">
+        <v>-7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27" ht="32" x14ac:dyDescent="0.2">
+      <c r="A8" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D8" s="4">
+        <v>4</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="I8" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="J8" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="K8" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="L8" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="M8" s="4">
+        <v>26</v>
+      </c>
+      <c r="N8" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="P8" s="4">
+        <v>36</v>
+      </c>
+      <c r="Q8" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="R8" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="S8" s="4">
+        <v>1</v>
+      </c>
+      <c r="T8" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="U8" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="V8" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="W8" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="X8" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="Y8" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z8" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="AA8" s="4">
+        <v>-7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" ht="32" x14ac:dyDescent="0.2">
+      <c r="A9" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D9" s="4">
+        <v>5</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="I9" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="J9" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="K9" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="L9" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="M9" s="4">
+        <v>0.03</v>
+      </c>
+      <c r="N9" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="O9" s="4">
+        <v>0</v>
+      </c>
+      <c r="P9" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="Q9" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="R9" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="S9" s="4">
+        <v>1</v>
+      </c>
+      <c r="T9" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="U9" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="V9" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="W9" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="X9" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA9" s="4">
+        <v>-7</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/rules/NEW-RULE/positive/01/data/new-rule-positive-01.xlsx
+++ b/rules/NEW-RULE/positive/01/data/new-rule-positive-01.xlsx
@@ -1,38 +1,731 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
+  <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/enrico/Work/core-contributor/rules/NEW-RULE/positive/01/data/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C4317EF-2BBB-E042-964A-6F9A8B37181D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="30240" yWindow="-4560" windowWidth="51200" windowHeight="28800" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Library" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Datasets" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Library" sheetId="1" r:id="rId1"/>
+    <sheet name="Datasets" sheetId="2" r:id="rId2"/>
+    <sheet name="dm.xpt" sheetId="3" r:id="rId3"/>
+    <sheet name="ec.xpt" sheetId="4" r:id="rId4"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="609" uniqueCount="221">
+  <si>
+    <t>Product</t>
+  </si>
+  <si>
+    <t>Version</t>
+  </si>
+  <si>
+    <t>sdtmig</t>
+  </si>
+  <si>
+    <t>3-4</t>
+  </si>
+  <si>
+    <t>Filename</t>
+  </si>
+  <si>
+    <t>Label</t>
+  </si>
+  <si>
+    <t>dm.xpt</t>
+  </si>
+  <si>
+    <t>Demographics</t>
+  </si>
+  <si>
+    <t>ec.xpt</t>
+  </si>
+  <si>
+    <t>Exposure as Collected</t>
+  </si>
+  <si>
+    <t>STUDYID</t>
+  </si>
+  <si>
+    <t>DOMAIN</t>
+  </si>
+  <si>
+    <t>USUBJID</t>
+  </si>
+  <si>
+    <t>SUBJID</t>
+  </si>
+  <si>
+    <t>RFSTDTC</t>
+  </si>
+  <si>
+    <t>RFENDTC</t>
+  </si>
+  <si>
+    <t>RFXSTDTC</t>
+  </si>
+  <si>
+    <t>RFXENDTC</t>
+  </si>
+  <si>
+    <t>RFICDTC</t>
+  </si>
+  <si>
+    <t>RFPENDTC</t>
+  </si>
+  <si>
+    <t>DTHDTC</t>
+  </si>
+  <si>
+    <t>DTHFL</t>
+  </si>
+  <si>
+    <t>SITEID</t>
+  </si>
+  <si>
+    <t>BRTHDTC</t>
+  </si>
+  <si>
+    <t>AGE</t>
+  </si>
+  <si>
+    <t>AGEU</t>
+  </si>
+  <si>
+    <t>SEX</t>
+  </si>
+  <si>
+    <t>RACE</t>
+  </si>
+  <si>
+    <t>ETHNIC</t>
+  </si>
+  <si>
+    <t>ARMCD</t>
+  </si>
+  <si>
+    <t>ARM</t>
+  </si>
+  <si>
+    <t>ACTARMCD</t>
+  </si>
+  <si>
+    <t>ACTARM</t>
+  </si>
+  <si>
+    <t>ARMNRS</t>
+  </si>
+  <si>
+    <t>ACTARMUD</t>
+  </si>
+  <si>
+    <t>COUNTRY</t>
+  </si>
+  <si>
+    <t>Study Identifier</t>
+  </si>
+  <si>
+    <t>Domain Abbreviation</t>
+  </si>
+  <si>
+    <t>Unique Subject Identifier</t>
+  </si>
+  <si>
+    <t>Subject Identifier for the Study</t>
+  </si>
+  <si>
+    <t>Subject Reference Start Date/Time</t>
+  </si>
+  <si>
+    <t>Subject Reference End Date/Time</t>
+  </si>
+  <si>
+    <t>Date/Time of First Study Treatment</t>
+  </si>
+  <si>
+    <t>Date/Time of Last Study Treatment</t>
+  </si>
+  <si>
+    <t>Date/Time of Informed Consent</t>
+  </si>
+  <si>
+    <t>Date/Time of End of Participation</t>
+  </si>
+  <si>
+    <t>Date/Time of Death</t>
+  </si>
+  <si>
+    <t>Subject Death Flag</t>
+  </si>
+  <si>
+    <t>Study Site Identifier</t>
+  </si>
+  <si>
+    <t>Date/Time of Birth</t>
+  </si>
+  <si>
+    <t>Age</t>
+  </si>
+  <si>
+    <t>Age Units</t>
+  </si>
+  <si>
+    <t>Sex</t>
+  </si>
+  <si>
+    <t>Race</t>
+  </si>
+  <si>
+    <t>Ethnicity</t>
+  </si>
+  <si>
+    <t>Planned Arm Code</t>
+  </si>
+  <si>
+    <t>Description of Planned Arm</t>
+  </si>
+  <si>
+    <t>Actual Arm Code</t>
+  </si>
+  <si>
+    <t>Description of Actual Arm</t>
+  </si>
+  <si>
+    <t>Reason Arm and/or Actual Arm is Null</t>
+  </si>
+  <si>
+    <t>Description of Unplanned Actual Arm</t>
+  </si>
+  <si>
+    <t>Country</t>
+  </si>
+  <si>
+    <t>Char</t>
+  </si>
+  <si>
+    <t>Num</t>
+  </si>
+  <si>
+    <t>CDISCPILOT01</t>
+  </si>
+  <si>
+    <t>DM</t>
+  </si>
+  <si>
+    <t>CDISC001</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>2013-01-23</t>
+  </si>
+  <si>
+    <t>2012-11-30T15:59:00</t>
+  </si>
+  <si>
+    <t>2013-01-23T15:59:00</t>
+  </si>
+  <si>
+    <t>2012-11-23</t>
+  </si>
+  <si>
+    <t>2013-05-20</t>
+  </si>
+  <si>
+    <t>YEARS</t>
+  </si>
+  <si>
+    <t>M</t>
+  </si>
+  <si>
+    <t>WHITE</t>
+  </si>
+  <si>
+    <t>NOT HISPANIC OR LATINO</t>
+  </si>
+  <si>
+    <t>ZAN_LOW</t>
+  </si>
+  <si>
+    <t>Zanomaline Low Dose (54 mg)</t>
+  </si>
+  <si>
+    <t>USA</t>
+  </si>
+  <si>
+    <t>CDISC002</t>
+  </si>
+  <si>
+    <t>2012-11-15</t>
+  </si>
+  <si>
+    <t>2013-01-14</t>
+  </si>
+  <si>
+    <t>2012-11-15T15:59:00</t>
+  </si>
+  <si>
+    <t>2013-01-12T15:59:00</t>
+  </si>
+  <si>
+    <t>2012-10-30</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>CDISC003</t>
+  </si>
+  <si>
+    <t>2013-11-05</t>
+  </si>
+  <si>
+    <t>2013-08-29T15:59:00</t>
+  </si>
+  <si>
+    <t>2013-11-05T15:59:00</t>
+  </si>
+  <si>
+    <t>2013-08-20</t>
+  </si>
+  <si>
+    <t>2014-02-13</t>
+  </si>
+  <si>
+    <t>ZAN_HIGH</t>
+  </si>
+  <si>
+    <t>Zanomaline High Dose (81 mg)</t>
+  </si>
+  <si>
+    <t>CDISC004</t>
+  </si>
+  <si>
+    <t>2013-10-08</t>
+  </si>
+  <si>
+    <t>2014-03-18</t>
+  </si>
+  <si>
+    <t>2013-10-08T15:59:00</t>
+  </si>
+  <si>
+    <t>2014-03-18T15:59:00</t>
+  </si>
+  <si>
+    <t>2013-10-01</t>
+  </si>
+  <si>
+    <t>SCREEN FAILURE</t>
+  </si>
+  <si>
+    <t>CDISC005</t>
+  </si>
+  <si>
+    <t>2013-08-06</t>
+  </si>
+  <si>
+    <t>2013-02-04T15:59:00</t>
+  </si>
+  <si>
+    <t>2013-08-06T15:59:00</t>
+  </si>
+  <si>
+    <t>2013-01-22</t>
+  </si>
+  <si>
+    <t>NOT TREATED</t>
+  </si>
+  <si>
+    <t>CDISC006</t>
+  </si>
+  <si>
+    <t>2013-04-30</t>
+  </si>
+  <si>
+    <t>2013-03-19T15:59:00</t>
+  </si>
+  <si>
+    <t>2013-04-30T15:59:00</t>
+  </si>
+  <si>
+    <t>2013-02-25</t>
+  </si>
+  <si>
+    <t>NOT ASSIGNED</t>
+  </si>
+  <si>
+    <t>CDISC007</t>
+  </si>
+  <si>
+    <t>2013-01-05</t>
+  </si>
+  <si>
+    <t>2013-02-13</t>
+  </si>
+  <si>
+    <t>2013-01-05T15:59:00</t>
+  </si>
+  <si>
+    <t>2013-02-12T15:59:00</t>
+  </si>
+  <si>
+    <t>2012-12-31</t>
+  </si>
+  <si>
+    <t>2013-06-20</t>
+  </si>
+  <si>
+    <t>HISPANIC OR LATINO</t>
+  </si>
+  <si>
+    <t>UNPLANNED</t>
+  </si>
+  <si>
+    <t>CDISC008</t>
+  </si>
+  <si>
+    <t>2014-05-11</t>
+  </si>
+  <si>
+    <t>2014-11-01</t>
+  </si>
+  <si>
+    <t>2014-05-11T15:59:00</t>
+  </si>
+  <si>
+    <t>2014-11-01T15:59:00</t>
+  </si>
+  <si>
+    <t>2014-05-01</t>
+  </si>
+  <si>
+    <t>MULTIPLE</t>
+  </si>
+  <si>
+    <t>PLACEBO</t>
+  </si>
+  <si>
+    <t>Placebo</t>
+  </si>
+  <si>
+    <t>CDISC009</t>
+  </si>
+  <si>
+    <t>2013-04-28</t>
+  </si>
+  <si>
+    <t>2012-10-22T15:59:00</t>
+  </si>
+  <si>
+    <t>2013-04-28T15:59:00</t>
+  </si>
+  <si>
+    <t>2012-10-06</t>
+  </si>
+  <si>
+    <t>CDISC010</t>
+  </si>
+  <si>
+    <t>2013-09-21</t>
+  </si>
+  <si>
+    <t>2013-09-26</t>
+  </si>
+  <si>
+    <t>2013-09-21T15:59:00</t>
+  </si>
+  <si>
+    <t>2013-09-08</t>
+  </si>
+  <si>
+    <t>ECSEQ</t>
+  </si>
+  <si>
+    <t>ECTRT</t>
+  </si>
+  <si>
+    <t>ECPRESP</t>
+  </si>
+  <si>
+    <t>ECOCCUR</t>
+  </si>
+  <si>
+    <t>ECDOSE</t>
+  </si>
+  <si>
+    <t>ECDOSU</t>
+  </si>
+  <si>
+    <t>ECDOSFRM</t>
+  </si>
+  <si>
+    <t>ECDOSFRQ</t>
+  </si>
+  <si>
+    <t>ECROUTE</t>
+  </si>
+  <si>
+    <t>ECLOT</t>
+  </si>
+  <si>
+    <t>ECPSTRG</t>
+  </si>
+  <si>
+    <t>ECPSTRGU</t>
+  </si>
+  <si>
+    <t>EPOCH</t>
+  </si>
+  <si>
+    <t>ECSTDTC</t>
+  </si>
+  <si>
+    <t>ECENDTC</t>
+  </si>
+  <si>
+    <t>ECSTDY</t>
+  </si>
+  <si>
+    <t>ECENDY</t>
+  </si>
+  <si>
+    <t>Sequence Number</t>
+  </si>
+  <si>
+    <t>Name of Treatment</t>
+  </si>
+  <si>
+    <t>Pre-Specified</t>
+  </si>
+  <si>
+    <t>Occurrence</t>
+  </si>
+  <si>
+    <t>Dose</t>
+  </si>
+  <si>
+    <t>Dose Units</t>
+  </si>
+  <si>
+    <t>Dose Form</t>
+  </si>
+  <si>
+    <t>Dosing Frequency per Interval</t>
+  </si>
+  <si>
+    <t>Route of Administration</t>
+  </si>
+  <si>
+    <t>Lot Number</t>
+  </si>
+  <si>
+    <t>Pharmaceutical Strength</t>
+  </si>
+  <si>
+    <t>Pharmaceutical Strength Units</t>
+  </si>
+  <si>
+    <t>Epoch</t>
+  </si>
+  <si>
+    <t>Start Date/Time of Treatment</t>
+  </si>
+  <si>
+    <t>End Date/Time of Treatment</t>
+  </si>
+  <si>
+    <t>Study Day of Start of Treatment</t>
+  </si>
+  <si>
+    <t>Study Day of End of Treatment</t>
+  </si>
+  <si>
+    <t>EC</t>
+  </si>
+  <si>
+    <t>ZANOMALINE</t>
+  </si>
+  <si>
+    <t>mL</t>
+  </si>
+  <si>
+    <t>INJECTION</t>
+  </si>
+  <si>
+    <t>QD</t>
+  </si>
+  <si>
+    <t>SUBCUTANEOUS</t>
+  </si>
+  <si>
+    <t>SDS580-359</t>
+  </si>
+  <si>
+    <t>g/L</t>
+  </si>
+  <si>
+    <t>TREATMENT</t>
+  </si>
+  <si>
+    <t>2012-12-01T15:59:00</t>
+  </si>
+  <si>
+    <t>2012-11-30</t>
+  </si>
+  <si>
+    <t>2012-12-02T15:59:00</t>
+  </si>
+  <si>
+    <t>2012-12-01</t>
+  </si>
+  <si>
+    <t>2012-12-03T15:59:00</t>
+  </si>
+  <si>
+    <t>2012-12-02</t>
+  </si>
+  <si>
+    <t>2012-12-04T15:59:00</t>
+  </si>
+  <si>
+    <t>2012-12-03</t>
+  </si>
+  <si>
+    <t>2012-12-05T15:59:00</t>
+  </si>
+  <si>
+    <t>2012-12-04</t>
+  </si>
+  <si>
+    <t>2012-12-06T15:59:00</t>
+  </si>
+  <si>
+    <t>2012-12-05</t>
+  </si>
+  <si>
+    <t>2012-12-07T15:59:00</t>
+  </si>
+  <si>
+    <t>2012-12-06</t>
+  </si>
+  <si>
+    <t>2012-12-08T15:59:00</t>
+  </si>
+  <si>
+    <t>2012-12-07</t>
+  </si>
+  <si>
+    <t>2012-12-09T15:59:00</t>
+  </si>
+  <si>
+    <t>2012-12-08</t>
+  </si>
+  <si>
+    <t>2012-12-10T15:59:00</t>
+  </si>
+  <si>
+    <t>2012-12-09</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>SDS580-485</t>
+  </si>
+  <si>
+    <t>2013-04-15T15:59:00</t>
+  </si>
+  <si>
+    <t>2013-02-20</t>
+  </si>
+  <si>
+    <t>2013-04-16T15:59:00</t>
+  </si>
+  <si>
+    <t>2013-02-21</t>
+  </si>
+  <si>
+    <t>2013-04-17T15:59:00</t>
+  </si>
+  <si>
+    <t>2013-02-22</t>
+  </si>
+  <si>
+    <t>2013-04-18T15:59:00</t>
+  </si>
+  <si>
+    <t>2013-02-23</t>
+  </si>
+  <si>
+    <t>2013-04-19T15:59:00</t>
+  </si>
+  <si>
+    <t>2013-02-24</t>
+  </si>
+  <si>
+    <t>2013-04-20T15:59:00</t>
+  </si>
+  <si>
+    <t>2012-11-17</t>
+  </si>
+  <si>
+    <t>2012-11-13</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <scheme val="minor"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -47,81 +740,26 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+  <cellXfs count="5">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -200,6 +838,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -234,6 +873,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -268,20 +908,16 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="80000">
-              <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
+                <a:tint val="100000"/>
+                <a:shade val="100000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
+                <a:tint val="50000"/>
+                <a:shade val="100000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -403,75 +1039,2498 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
+  <a:objectDefaults>
+    <a:spDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="3">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </a:style>
+    </a:spDef>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
   <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Product</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Version</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>sdtmig</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>3-4</t>
-        </is>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" t="s">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <ignoredErrors>
+    <ignoredError sqref="A1:B2" numberStoredAsText="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Filename</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Label</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
-      <c r="B2" t="inlineStr"/>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>9</v>
+      </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <ignoredErrors>
+    <ignoredError sqref="A1:B3" numberStoredAsText="1"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:Z14"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="2" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A2" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="N2" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="O2" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="P2" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q2" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="R2" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="S2" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="T2" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="U2" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="V2" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="W2" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="X2" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="Y2" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="Z2" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="3" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A3" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="N3" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="O3" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="P3" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q3" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="R3" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="S3" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="T3" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="U3" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="V3" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="W3" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="X3" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="Y3" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="Z3" s="3" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="4" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A4" s="3">
+        <v>12</v>
+      </c>
+      <c r="B4" s="3">
+        <v>2</v>
+      </c>
+      <c r="C4" s="3">
+        <v>8</v>
+      </c>
+      <c r="D4" s="3">
+        <v>4</v>
+      </c>
+      <c r="E4" s="3">
+        <v>10</v>
+      </c>
+      <c r="F4" s="3">
+        <v>10</v>
+      </c>
+      <c r="G4" s="3">
+        <v>19</v>
+      </c>
+      <c r="H4" s="3">
+        <v>19</v>
+      </c>
+      <c r="I4" s="3">
+        <v>10</v>
+      </c>
+      <c r="J4" s="3">
+        <v>10</v>
+      </c>
+      <c r="K4" s="3">
+        <v>10</v>
+      </c>
+      <c r="L4" s="3">
+        <v>1</v>
+      </c>
+      <c r="M4" s="3">
+        <v>3</v>
+      </c>
+      <c r="N4" s="3">
+        <v>10</v>
+      </c>
+      <c r="O4" s="3">
+        <v>8</v>
+      </c>
+      <c r="P4" s="3">
+        <v>5</v>
+      </c>
+      <c r="Q4" s="3">
+        <v>1</v>
+      </c>
+      <c r="R4" s="3">
+        <v>41</v>
+      </c>
+      <c r="S4" s="3">
+        <v>22</v>
+      </c>
+      <c r="T4" s="3">
+        <v>8</v>
+      </c>
+      <c r="U4" s="3">
+        <v>28</v>
+      </c>
+      <c r="V4" s="3">
+        <v>8</v>
+      </c>
+      <c r="W4" s="3">
+        <v>28</v>
+      </c>
+      <c r="X4" s="3">
+        <v>14</v>
+      </c>
+      <c r="Y4" s="3">
+        <v>200</v>
+      </c>
+      <c r="Z4" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A5" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D5" s="2">
+        <v>1115</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="M5" s="2">
+        <v>701</v>
+      </c>
+      <c r="N5" s="2">
+        <v>1928</v>
+      </c>
+      <c r="O5" s="2">
+        <v>84</v>
+      </c>
+      <c r="P5" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q5" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="R5" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="S5" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="T5" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="U5" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="V5" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="W5" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="X5" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="Y5" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="Z5" s="2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A6" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="D6" s="2">
+        <v>1211</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="L6" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="M6" s="2">
+        <v>701</v>
+      </c>
+      <c r="N6" s="2">
+        <v>1936</v>
+      </c>
+      <c r="O6" s="2">
+        <v>76</v>
+      </c>
+      <c r="P6" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q6" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="R6" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="S6" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="T6" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="U6" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="V6" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="W6" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="X6" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="Y6" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="Z6" s="2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A7" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="D7" s="2">
+        <v>1302</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="K7" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="L7" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="M7" s="2">
+        <v>701</v>
+      </c>
+      <c r="N7" s="2">
+        <v>1951</v>
+      </c>
+      <c r="O7" s="2">
+        <v>61</v>
+      </c>
+      <c r="P7" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q7" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="R7" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="S7" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="T7" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="U7" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="V7" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="W7" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="X7" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="Y7" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="Z7" s="2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A8" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="D8" s="2">
+        <v>1345</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="L8" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="M8" s="2">
+        <v>701</v>
+      </c>
+      <c r="N8" s="2">
+        <v>1950</v>
+      </c>
+      <c r="O8" s="2">
+        <v>63</v>
+      </c>
+      <c r="P8" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q8" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="R8" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="S8" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="T8" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="U8" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="V8" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="W8" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="X8" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="Y8" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="Z8" s="2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A9" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="D9" s="2">
+        <v>1383</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="L9" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="M9" s="2">
+        <v>701</v>
+      </c>
+      <c r="N9" s="2">
+        <v>1941</v>
+      </c>
+      <c r="O9" s="2">
+        <v>72</v>
+      </c>
+      <c r="P9" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q9" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="R9" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="S9" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="T9" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="U9" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="V9" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="W9" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="X9" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="Y9" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="Z9" s="2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A10" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="D10" s="2">
+        <v>1429</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="L10" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="M10" s="2">
+        <v>701</v>
+      </c>
+      <c r="N10" s="2">
+        <v>1929</v>
+      </c>
+      <c r="O10" s="2">
+        <v>84</v>
+      </c>
+      <c r="P10" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q10" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="R10" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="S10" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="T10" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="U10" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="V10" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="W10" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="X10" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="Y10" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="Z10" s="2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A11" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="D11" s="2">
+        <v>1444</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="K11" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="L11" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="M11" s="2">
+        <v>701</v>
+      </c>
+      <c r="N11" s="2">
+        <v>1949</v>
+      </c>
+      <c r="O11" s="2">
+        <v>63</v>
+      </c>
+      <c r="P11" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q11" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="R11" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="S11" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="T11" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="U11" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="V11" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="W11" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="X11" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="Y11" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="Z11" s="2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A12" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="D12" s="2">
+        <v>1445</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="K12" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="L12" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="M12" s="2">
+        <v>704</v>
+      </c>
+      <c r="N12" s="2">
+        <v>1939</v>
+      </c>
+      <c r="O12" s="2">
+        <v>75</v>
+      </c>
+      <c r="P12" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q12" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="R12" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="S12" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="T12" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="U12" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="V12" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="W12" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="X12" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="Y12" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="Z12" s="2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A13" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="D13" s="2">
+        <v>1087</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="K13" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="L13" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="M13" s="2">
+        <v>708</v>
+      </c>
+      <c r="N13" s="2">
+        <v>1938</v>
+      </c>
+      <c r="O13" s="2">
+        <v>74</v>
+      </c>
+      <c r="P13" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q13" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="R13" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="S13" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="T13" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="U13" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="V13" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="W13" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="X13" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="Y13" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="Z13" s="2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A14" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="D14" s="2">
+        <v>1236</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="K14" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="L14" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="M14" s="2">
+        <v>708</v>
+      </c>
+      <c r="N14" s="2">
+        <v>1927</v>
+      </c>
+      <c r="O14" s="2">
+        <v>86</v>
+      </c>
+      <c r="P14" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q14" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="R14" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="S14" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="T14" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="U14" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="V14" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="W14" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="X14" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="Y14" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="Z14" s="2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <ignoredErrors>
+    <ignoredError sqref="A1:Z4 A6:Z6 A5:D5 F5:Z5 A8:Z8 A7:D7 F7:Z7 A11:Z12 A9:D9 F9:Z9 A10:D10 F10:Z10 A14:Z14 A13:D13 F13:Z13" numberStoredAsText="1"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:T20"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="2" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A2" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="N2" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="O2" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="P2" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="Q2" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="R2" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="S2" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="T2" s="3" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A3" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="N3" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="O3" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="P3" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q3" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="R3" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="S3" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="T3" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A4" s="3">
+        <v>12</v>
+      </c>
+      <c r="B4" s="3">
+        <v>2</v>
+      </c>
+      <c r="C4" s="3">
+        <v>8</v>
+      </c>
+      <c r="D4" s="3">
+        <v>8</v>
+      </c>
+      <c r="E4" s="3">
+        <v>10</v>
+      </c>
+      <c r="F4" s="3">
+        <v>1</v>
+      </c>
+      <c r="G4" s="3">
+        <v>1</v>
+      </c>
+      <c r="H4" s="3">
+        <v>8</v>
+      </c>
+      <c r="I4" s="3">
+        <v>2</v>
+      </c>
+      <c r="J4" s="3">
+        <v>9</v>
+      </c>
+      <c r="K4" s="3">
+        <v>2</v>
+      </c>
+      <c r="L4" s="3">
+        <v>12</v>
+      </c>
+      <c r="M4" s="3">
+        <v>200</v>
+      </c>
+      <c r="N4" s="3">
+        <v>8</v>
+      </c>
+      <c r="O4" s="3">
+        <v>3</v>
+      </c>
+      <c r="P4" s="3">
+        <v>9</v>
+      </c>
+      <c r="Q4" s="3">
+        <v>19</v>
+      </c>
+      <c r="R4" s="3">
+        <v>10</v>
+      </c>
+      <c r="S4" s="3">
+        <v>8</v>
+      </c>
+      <c r="T4" s="3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A5" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D5" s="2">
+        <v>1</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="H5" s="2">
+        <v>5</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="M5" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="N5" s="2">
+        <v>10.8</v>
+      </c>
+      <c r="O5" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="P5" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="Q5" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="R5" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="S5" s="2">
+        <v>1</v>
+      </c>
+      <c r="T5" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A6" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D6" s="2">
+        <v>2</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="H6" s="2">
+        <v>5</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="L6" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="M6" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="N6" s="2">
+        <v>10.8</v>
+      </c>
+      <c r="O6" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="P6" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="Q6" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="R6" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="S6" s="2">
+        <v>2</v>
+      </c>
+      <c r="T6" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A7" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D7" s="2">
+        <v>3</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="H7" s="2">
+        <v>5</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="K7" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="L7" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="M7" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="N7" s="2">
+        <v>10.8</v>
+      </c>
+      <c r="O7" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="P7" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="Q7" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="R7" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="S7" s="2">
+        <v>3</v>
+      </c>
+      <c r="T7" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A8" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D8" s="2">
+        <v>4</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="H8" s="2">
+        <v>5</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="L8" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="M8" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="N8" s="2">
+        <v>10.8</v>
+      </c>
+      <c r="O8" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="P8" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="Q8" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="R8" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="S8" s="2">
+        <v>4</v>
+      </c>
+      <c r="T8" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A9" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D9" s="2">
+        <v>5</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="H9" s="2">
+        <v>5</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="L9" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="M9" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="N9" s="2">
+        <v>10.8</v>
+      </c>
+      <c r="O9" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="P9" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="Q9" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="R9" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="S9" s="2">
+        <v>5</v>
+      </c>
+      <c r="T9" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A10" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D10" s="2">
+        <v>6</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="H10" s="2">
+        <v>5</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="L10" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="M10" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="N10" s="2">
+        <v>10.8</v>
+      </c>
+      <c r="O10" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="P10" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="Q10" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="R10" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="S10" s="2">
+        <v>6</v>
+      </c>
+      <c r="T10" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A11" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D11" s="2">
+        <v>7</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="H11" s="2">
+        <v>5</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="K11" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="L11" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="M11" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="N11" s="2">
+        <v>10.8</v>
+      </c>
+      <c r="O11" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="P11" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="Q11" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="R11" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="S11" s="2">
+        <v>7</v>
+      </c>
+      <c r="T11" s="2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A12" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D12" s="2">
+        <v>8</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="H12" s="2">
+        <v>5</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="K12" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="L12" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="M12" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="N12" s="2">
+        <v>10.8</v>
+      </c>
+      <c r="O12" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="P12" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="Q12" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="R12" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="S12" s="2">
+        <v>8</v>
+      </c>
+      <c r="T12" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A13" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D13" s="2">
+        <v>9</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="H13" s="2">
+        <v>5</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="K13" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="L13" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="M13" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="N13" s="2">
+        <v>10.8</v>
+      </c>
+      <c r="O13" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="P13" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="Q13" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="R13" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="S13" s="2">
+        <v>9</v>
+      </c>
+      <c r="T13" s="2">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A14" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D14" s="2">
+        <v>10</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="H14" s="2">
+        <v>5</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="K14" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="L14" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="M14" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="N14" s="2">
+        <v>10.8</v>
+      </c>
+      <c r="O14" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="P14" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="Q14" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="R14" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="S14" s="2">
+        <v>10</v>
+      </c>
+      <c r="T14" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A15" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="D15" s="2">
+        <v>122</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="H15" s="2">
+        <v>0</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="K15" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="L15" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="M15" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="N15" s="2">
+        <v>0</v>
+      </c>
+      <c r="O15" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="P15" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="Q15" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="R15" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="S15" s="2">
+        <v>122</v>
+      </c>
+      <c r="T15" s="2">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A16" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="D16" s="2">
+        <v>123</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="H16" s="2">
+        <v>20</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="K16" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="L16" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="M16" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="N16" s="2">
+        <v>0</v>
+      </c>
+      <c r="O16" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="P16" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="Q16" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="R16" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="S16" s="2">
+        <v>123</v>
+      </c>
+      <c r="T16" s="2">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="17" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A17" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="D17" s="2">
+        <v>124</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="H17" s="2">
+        <v>0</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="K17" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="L17" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="M17" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="N17" s="2">
+        <v>0</v>
+      </c>
+      <c r="O17" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="P17" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="Q17" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="R17" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="S17" s="2">
+        <v>124</v>
+      </c>
+      <c r="T17" s="2">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="18" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A18" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="D18" s="2">
+        <v>125</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="H18" s="2">
+        <v>0</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="K18" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="L18" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="M18" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="N18" s="2">
+        <v>0</v>
+      </c>
+      <c r="O18" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="P18" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="Q18" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="R18" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="S18" s="2">
+        <v>125</v>
+      </c>
+      <c r="T18" s="2">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="19" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A19" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="D19" s="2">
+        <v>126</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="H19" s="2">
+        <v>-10</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="K19" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="L19" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="M19" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="N19" s="2">
+        <v>0</v>
+      </c>
+      <c r="O19" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="P19" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="Q19" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="R19" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="S19" s="2">
+        <v>126</v>
+      </c>
+      <c r="T19" s="2">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="20" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A20" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="D20" s="2">
+        <v>127</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="K20" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="L20" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="M20" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="N20" s="2">
+        <v>0</v>
+      </c>
+      <c r="O20" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="P20" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="Q20" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="R20" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="S20" s="2">
+        <v>127</v>
+      </c>
+      <c r="T20" s="2">
+        <v>127</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <ignoredErrors>
+    <ignoredError sqref="A1:T20" numberStoredAsText="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
--- a/rules/NEW-RULE/positive/01/data/new-rule-positive-01.xlsx
+++ b/rules/NEW-RULE/positive/01/data/new-rule-positive-01.xlsx
@@ -488,7 +488,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:K6"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="4" t="str">
@@ -650,12 +650,50 @@
         <v>Planned Country of Investigational Sites</v>
       </c>
       <c r="G5" s="3" t="str">
-        <v>AFG</v>
+        <v>Afghanistan</v>
+      </c>
+      <c r="H5" s="2" t="str">
+        <v>NA</v>
+      </c>
+      <c r="I5" s="2" t="str">
+        <v>afghanistan-code</v>
+      </c>
+      <c r="J5" s="2" t="str">
+        <v>ISO 3166</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="str">
+        <v>CDISCPILOT01</v>
+      </c>
+      <c r="B6" s="2" t="str">
+        <v>TS</v>
+      </c>
+      <c r="C6" s="2">
+        <v>2</v>
+      </c>
+      <c r="E6" s="2" t="str">
+        <v>FCNTRY</v>
+      </c>
+      <c r="F6" s="2" t="str">
+        <v>Planned Country of Investigational Sites</v>
+      </c>
+      <c r="G6" s="2" t="str">
+        <v>Albania</v>
+      </c>
+      <c r="H6" s="2" t="str">
+        <v>NA</v>
+      </c>
+      <c r="I6" s="2" t="str">
+        <v>albania-code</v>
+      </c>
+      <c r="J6" s="2" t="str">
+        <v>GENC</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K6"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/rules/NEW-RULE/positive/01/data/new-rule-positive-01.xlsx
+++ b/rules/NEW-RULE/positive/01/data/new-rule-positive-01.xlsx
@@ -652,42 +652,45 @@
       <c r="G5" s="3" t="str">
         <v>Afghanistan</v>
       </c>
-      <c r="H5" s="2" t="str">
+      <c r="H5" s="3" t="str">
         <v>NA</v>
       </c>
-      <c r="I5" s="2" t="str">
-        <v>afghanistan-code</v>
-      </c>
-      <c r="J5" s="2" t="str">
+      <c r="I5" s="3" t="str">
+        <v>AFG</v>
+      </c>
+      <c r="J5" s="3" t="str">
         <v>ISO 3166</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="str">
+      <c r="A6" s="3" t="str">
         <v>CDISCPILOT01</v>
       </c>
-      <c r="B6" s="2" t="str">
+      <c r="B6" s="3" t="str">
         <v>TS</v>
       </c>
-      <c r="C6" s="2">
+      <c r="C6" s="3">
         <v>2</v>
       </c>
-      <c r="E6" s="2" t="str">
+      <c r="D6" s="2" t="str">
+        <v/>
+      </c>
+      <c r="E6" s="3" t="str">
         <v>FCNTRY</v>
       </c>
-      <c r="F6" s="2" t="str">
+      <c r="F6" s="3" t="str">
         <v>Planned Country of Investigational Sites</v>
       </c>
-      <c r="G6" s="2" t="str">
+      <c r="G6" s="3" t="str">
         <v>Albania</v>
       </c>
-      <c r="H6" s="2" t="str">
+      <c r="H6" s="3" t="str">
         <v>NA</v>
       </c>
-      <c r="I6" s="2" t="str">
-        <v>albania-code</v>
-      </c>
-      <c r="J6" s="2" t="str">
+      <c r="I6" s="3" t="str">
+        <v>ALB</v>
+      </c>
+      <c r="J6" s="3" t="str">
         <v>GENC</v>
       </c>
     </row>

--- a/rules/NEW-RULE/positive/01/data/new-rule-positive-01.xlsx
+++ b/rules/NEW-RULE/positive/01/data/new-rule-positive-01.xlsx
@@ -1,41 +1,106 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
-  <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
-  </bookViews>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Library" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Datasets" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Library" sheetId="1" r:id="rId1"/>
+    <sheet name="Datasets" sheetId="2" r:id="rId2"/>
+    <sheet name="ts.xpt" sheetId="3" r:id="rId3"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <color theme="1"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <scheme val="minor"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <i/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <i/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <color rgb="FF000000"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none">
+        <bgColor/>
+      </patternFill>
     </fill>
     <fill>
-      <patternFill patternType="gray125"/>
+      <patternFill patternType="gray125">
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor/>
+      </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left/>
       <right/>
@@ -44,84 +109,24 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+  <cellXfs count="8">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="1" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+  <cellStyles>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
 </styleSheet>
 </file>
 
@@ -200,6 +205,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -234,6 +240,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -268,20 +275,16 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
+                <a:tint val="100000"/>
+                <a:shade val="100000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="80000">
-              <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
+                <a:tint val="50000"/>
+                <a:shade val="100000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -403,75 +406,321 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
+  <a:objectDefaults>
+    <a:spDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="3">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </a:style>
+    </a:spDef>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
   <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Product</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Version</t>
-        </is>
+      <c r="A1" s="3" t="str">
+        <v>Product</v>
+      </c>
+      <c r="B1" s="3" t="str">
+        <v>Version</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>sdtmig</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>3-4</t>
-        </is>
+      <c r="A2" s="3" t="str">
+        <v>sdtmig</v>
+      </c>
+      <c r="B2" s="3" t="str">
+        <v>3-4</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:B2"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Filename</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Label</t>
-        </is>
+      <c r="A1" s="4" t="str">
+        <v>Filename</v>
+      </c>
+      <c r="B1" s="4" t="str">
+        <v>Label</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr"/>
-      <c r="B2" t="inlineStr"/>
+      <c r="A2" s="3" t="str">
+        <v>ts.xpt</v>
+      </c>
+      <c r="B2" s="3" t="str">
+        <v>Trial Summary Parameters</v>
+      </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:B2"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:K6"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="str">
+        <v>STUDYID</v>
+      </c>
+      <c r="B1" s="4" t="str">
+        <v>DOMAIN</v>
+      </c>
+      <c r="C1" s="4" t="str">
+        <v>TSSEQ</v>
+      </c>
+      <c r="D1" s="4" t="str">
+        <v>TSGRPID</v>
+      </c>
+      <c r="E1" s="4" t="str">
+        <v>TSPARMCD</v>
+      </c>
+      <c r="F1" s="4" t="str">
+        <v>TSPARM</v>
+      </c>
+      <c r="G1" s="4" t="str">
+        <v>TSVAL</v>
+      </c>
+      <c r="H1" s="4" t="str">
+        <v>TSVALNF</v>
+      </c>
+      <c r="I1" s="4" t="str">
+        <v>TSVALCD</v>
+      </c>
+      <c r="J1" s="4" t="str">
+        <v>TSVCDREF</v>
+      </c>
+      <c r="K1" s="4" t="str">
+        <v>TSVCDVER</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="str">
+        <v>Study Identifier</v>
+      </c>
+      <c r="B2" s="6" t="str">
+        <v>Domain Abbreviation</v>
+      </c>
+      <c r="C2" s="6" t="str">
+        <v>Sequence Number</v>
+      </c>
+      <c r="D2" s="6" t="str">
+        <v>Group ID</v>
+      </c>
+      <c r="E2" s="6" t="str">
+        <v>Trial Summary Parameter Short Name</v>
+      </c>
+      <c r="F2" s="6" t="str">
+        <v>Trial Summary Parameter</v>
+      </c>
+      <c r="G2" s="6" t="str">
+        <v>Parameter Value</v>
+      </c>
+      <c r="H2" s="6" t="str">
+        <v>Parameter Null Flavor</v>
+      </c>
+      <c r="I2" s="6" t="str">
+        <v>Parameter Value Code</v>
+      </c>
+      <c r="J2" s="6" t="str">
+        <v>Name of the Reference Terminology</v>
+      </c>
+      <c r="K2" s="6" t="str">
+        <v>Version of the Reference Terminology</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="str">
+        <v>Char</v>
+      </c>
+      <c r="B3" s="6" t="str">
+        <v>Char</v>
+      </c>
+      <c r="C3" s="6" t="str">
+        <v>Num</v>
+      </c>
+      <c r="D3" s="6" t="str">
+        <v>Char</v>
+      </c>
+      <c r="E3" s="6" t="str">
+        <v>Char</v>
+      </c>
+      <c r="F3" s="6" t="str">
+        <v>Char</v>
+      </c>
+      <c r="G3" s="6" t="str">
+        <v>Char</v>
+      </c>
+      <c r="H3" s="6" t="str">
+        <v>Char</v>
+      </c>
+      <c r="I3" s="6" t="str">
+        <v>Char</v>
+      </c>
+      <c r="J3" s="6" t="str">
+        <v>Char</v>
+      </c>
+      <c r="K3" s="6" t="str">
+        <v>Char</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="str">
+        <v>10</v>
+      </c>
+      <c r="B4" s="6" t="str">
+        <v>2</v>
+      </c>
+      <c r="C4" s="6" t="str">
+        <v>8</v>
+      </c>
+      <c r="D4" s="6" t="str">
+        <v>5</v>
+      </c>
+      <c r="E4" s="6" t="str">
+        <v>8</v>
+      </c>
+      <c r="F4" s="6" t="str">
+        <v>40</v>
+      </c>
+      <c r="G4" s="6" t="str">
+        <v>149</v>
+      </c>
+      <c r="H4" s="6" t="str">
+        <v>2</v>
+      </c>
+      <c r="I4" s="6" t="str">
+        <v>11</v>
+      </c>
+      <c r="J4" s="6" t="str">
+        <v>18</v>
+      </c>
+      <c r="K4" s="6" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="str">
+        <v>CDISCPILOT01</v>
+      </c>
+      <c r="B5" s="7" t="str">
+        <v>TS</v>
+      </c>
+      <c r="C5" s="7" t="str">
+        <v>1</v>
+      </c>
+      <c r="D5" s="7" t="str">
+        <v/>
+      </c>
+      <c r="E5" s="3" t="str">
+        <v>SDTIGVER</v>
+      </c>
+      <c r="F5" s="3" t="str">
+        <v>CDISC SDTM Implementation Guide Version</v>
+      </c>
+      <c r="G5" s="7" t="str">
+        <v>3.1.1</v>
+      </c>
+      <c r="H5" s="7" t="str">
+        <v/>
+      </c>
+      <c r="I5" s="7" t="str">
+        <v>C160924</v>
+      </c>
+      <c r="J5" s="7" t="str">
+        <v>CDISC</v>
+      </c>
+      <c r="K5" s="7" t="str">
+        <v>2025-03-28</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="str">
+        <v>CDISCPILOT01</v>
+      </c>
+      <c r="B6" s="7" t="str">
+        <v>TS</v>
+      </c>
+      <c r="C6" s="7" t="str">
+        <v>3</v>
+      </c>
+      <c r="D6" s="7" t="str">
+        <v/>
+      </c>
+      <c r="E6" s="3" t="str">
+        <v>SDTMVER</v>
+      </c>
+      <c r="F6" s="3" t="str">
+        <v>CDISC SDTM Version</v>
+      </c>
+      <c r="G6" s="7">
+        <v>1.1</v>
+      </c>
+      <c r="H6" s="7" t="str">
+        <v/>
+      </c>
+      <c r="I6" s="7" t="str">
+        <v>C160923</v>
+      </c>
+      <c r="J6" s="7" t="str">
+        <v>CDISC</v>
+      </c>
+      <c r="K6" s="7" t="str">
+        <v>2025-03-28</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:K6"/>
+  </ignoredErrors>
 </worksheet>
 </file>
--- a/rules/NEW-RULE/positive/01/data/new-rule-positive-01.xlsx
+++ b/rules/NEW-RULE/positive/01/data/new-rule-positive-01.xlsx
@@ -5,7 +5,7 @@
   <sheets>
     <sheet name="Library" sheetId="1" r:id="rId1"/>
     <sheet name="Datasets" sheetId="2" r:id="rId2"/>
-    <sheet name="ts.xpt" sheetId="3" r:id="rId3"/>
+    <sheet name="dm.xpt" sheetId="3" r:id="rId3"/>
   </sheets>
 </workbook>
 </file>
@@ -464,19 +464,19 @@
   <dimension ref="A1:B2"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="str">
+      <c r="A1" s="4" t="str">
         <v>Filename</v>
       </c>
-      <c r="B1" s="3" t="str">
+      <c r="B1" s="4" t="str">
         <v>Label</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="str">
-        <v>ts.xpt</v>
+        <v>dm.xpt</v>
       </c>
       <c r="B2" s="3" t="str">
-        <v>Trial Summary Parameters</v>
+        <v>Demographics</v>
       </c>
     </row>
   </sheetData>
@@ -488,7 +488,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:Z6"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="4" t="str">
@@ -498,31 +498,76 @@
         <v>DOMAIN</v>
       </c>
       <c r="C1" s="4" t="str">
-        <v>TSSEQ</v>
+        <v>USUBJID</v>
       </c>
       <c r="D1" s="4" t="str">
-        <v>TSGRPID</v>
+        <v>SUBJID</v>
       </c>
       <c r="E1" s="4" t="str">
-        <v>TSPARMCD</v>
+        <v>RFSTDTC</v>
       </c>
       <c r="F1" s="4" t="str">
-        <v>TSPARM</v>
+        <v>RFENDTC</v>
       </c>
       <c r="G1" s="4" t="str">
-        <v>TSVAL</v>
+        <v>RFXSTDTC</v>
       </c>
       <c r="H1" s="4" t="str">
-        <v>TSVALNF</v>
+        <v>RFXENDTC</v>
       </c>
       <c r="I1" s="4" t="str">
-        <v>TSVALCD</v>
+        <v>RFICDTC</v>
       </c>
       <c r="J1" s="4" t="str">
-        <v>TSVCDREF</v>
+        <v>RFPENDTC</v>
       </c>
       <c r="K1" s="4" t="str">
-        <v>TSVCDVER</v>
+        <v>DTHDTC</v>
+      </c>
+      <c r="L1" s="4" t="str">
+        <v>DTHFL</v>
+      </c>
+      <c r="M1" s="4" t="str">
+        <v>SITEID</v>
+      </c>
+      <c r="N1" s="4" t="str">
+        <v>BRTHDTC</v>
+      </c>
+      <c r="O1" s="4" t="str">
+        <v>AGE</v>
+      </c>
+      <c r="P1" s="4" t="str">
+        <v>AGEU</v>
+      </c>
+      <c r="Q1" s="4" t="str">
+        <v>SEX</v>
+      </c>
+      <c r="R1" s="4" t="str">
+        <v>RACE</v>
+      </c>
+      <c r="S1" s="4" t="str">
+        <v>ETHNIC</v>
+      </c>
+      <c r="T1" s="4" t="str">
+        <v>ARMCD</v>
+      </c>
+      <c r="U1" s="4" t="str">
+        <v>ARM</v>
+      </c>
+      <c r="V1" s="4" t="str">
+        <v>ACTARMCD</v>
+      </c>
+      <c r="W1" s="4" t="str">
+        <v>ACTARM</v>
+      </c>
+      <c r="X1" s="4" t="str">
+        <v>ARMNRS</v>
+      </c>
+      <c r="Y1" s="4" t="str">
+        <v>ACTARMUD</v>
+      </c>
+      <c r="Z1" s="4" t="str">
+        <v>COUNTRY</v>
       </c>
     </row>
     <row r="2">
@@ -533,31 +578,76 @@
         <v>Domain Abbreviation</v>
       </c>
       <c r="C2" s="5" t="str">
-        <v>Sequence Number</v>
+        <v>Unique Subject Identifier</v>
       </c>
       <c r="D2" s="5" t="str">
-        <v>Group ID</v>
+        <v>Subject Identifier for the Study</v>
       </c>
       <c r="E2" s="5" t="str">
-        <v>Trial Summary Parameter Short Name</v>
+        <v>Subject Reference Start Date/Time</v>
       </c>
       <c r="F2" s="5" t="str">
-        <v>Trial Summary Parameter</v>
+        <v>Subject Reference End Date/Time</v>
       </c>
       <c r="G2" s="5" t="str">
-        <v>Parameter Value</v>
+        <v>Date/Time of First Study Treatment</v>
       </c>
       <c r="H2" s="5" t="str">
-        <v>Parameter Null Flavor</v>
+        <v>Date/Time of Last Study Treatment</v>
       </c>
       <c r="I2" s="5" t="str">
-        <v>Parameter Value Code</v>
+        <v>Date/Time of Informed Consent</v>
       </c>
       <c r="J2" s="5" t="str">
-        <v>Name of the Reference Terminology</v>
+        <v>Date/Time of End of Participation</v>
       </c>
       <c r="K2" s="5" t="str">
-        <v>Version of the Reference Terminology</v>
+        <v>Date/Time of Death</v>
+      </c>
+      <c r="L2" s="5" t="str">
+        <v>Subject Death Flag</v>
+      </c>
+      <c r="M2" s="5" t="str">
+        <v>Study Site Identifier</v>
+      </c>
+      <c r="N2" s="5" t="str">
+        <v>Date/Time of Birth</v>
+      </c>
+      <c r="O2" s="5" t="str">
+        <v>Age</v>
+      </c>
+      <c r="P2" s="5" t="str">
+        <v>Age Units</v>
+      </c>
+      <c r="Q2" s="5" t="str">
+        <v>Sex</v>
+      </c>
+      <c r="R2" s="5" t="str">
+        <v>Race</v>
+      </c>
+      <c r="S2" s="5" t="str">
+        <v>Ethnicity</v>
+      </c>
+      <c r="T2" s="5" t="str">
+        <v>Planned Arm Code</v>
+      </c>
+      <c r="U2" s="5" t="str">
+        <v>Description of Planned Arm</v>
+      </c>
+      <c r="V2" s="5" t="str">
+        <v>Actual Arm Code</v>
+      </c>
+      <c r="W2" s="5" t="str">
+        <v>Description of Actual Arm</v>
+      </c>
+      <c r="X2" s="5" t="str">
+        <v>Reason Arm and/or Actual Arm is Null</v>
+      </c>
+      <c r="Y2" s="5" t="str">
+        <v>Description of Unplanned Actual Arm</v>
+      </c>
+      <c r="Z2" s="5" t="str">
+        <v>Country</v>
       </c>
     </row>
     <row r="3">
@@ -568,66 +658,156 @@
         <v>Char</v>
       </c>
       <c r="C3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="D3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="E3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="F3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="G3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="H3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="I3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="J3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="K3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="L3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="M3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="N3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="O3" s="5" t="str">
         <v>Num</v>
       </c>
-      <c r="D3" s="5" t="str">
-        <v>Char</v>
-      </c>
-      <c r="E3" s="5" t="str">
-        <v>Char</v>
-      </c>
-      <c r="F3" s="5" t="str">
-        <v>Char</v>
-      </c>
-      <c r="G3" s="5" t="str">
-        <v>Char</v>
-      </c>
-      <c r="H3" s="5" t="str">
-        <v>Char</v>
-      </c>
-      <c r="I3" s="5" t="str">
-        <v>Char</v>
-      </c>
-      <c r="J3" s="5" t="str">
-        <v>Char</v>
-      </c>
-      <c r="K3" s="5" t="str">
+      <c r="P3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="Q3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="R3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="S3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="T3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="U3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="V3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="W3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="X3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="Y3" s="5" t="str">
+        <v>Char</v>
+      </c>
+      <c r="Z3" s="5" t="str">
         <v>Char</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="B4" s="5">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="C4" s="5">
-        <v>8</v>
+        <v>50</v>
       </c>
       <c r="D4" s="5">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="E4" s="5">
-        <v>8</v>
+        <v>50</v>
       </c>
       <c r="F4" s="5">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="G4" s="5">
-        <v>149</v>
+        <v>50</v>
       </c>
       <c r="H4" s="5">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="I4" s="5">
-        <v>11</v>
+        <v>50</v>
       </c>
       <c r="J4" s="5">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="K4" s="5">
-        <v>10</v>
+        <v>50</v>
+      </c>
+      <c r="L4" s="5">
+        <v>50</v>
+      </c>
+      <c r="M4" s="5">
+        <v>50</v>
+      </c>
+      <c r="N4" s="5">
+        <v>50</v>
+      </c>
+      <c r="O4" s="5">
+        <v>50</v>
+      </c>
+      <c r="P4" s="5">
+        <v>50</v>
+      </c>
+      <c r="Q4" s="5">
+        <v>50</v>
+      </c>
+      <c r="R4" s="5">
+        <v>50</v>
+      </c>
+      <c r="S4" s="5">
+        <v>50</v>
+      </c>
+      <c r="T4" s="5">
+        <v>50</v>
+      </c>
+      <c r="U4" s="5">
+        <v>50</v>
+      </c>
+      <c r="V4" s="5">
+        <v>50</v>
+      </c>
+      <c r="W4" s="5">
+        <v>50</v>
+      </c>
+      <c r="X4" s="5">
+        <v>50</v>
+      </c>
+      <c r="Y4" s="5">
+        <v>50</v>
+      </c>
+      <c r="Z4" s="5">
+        <v>50</v>
       </c>
     </row>
     <row r="5">
@@ -635,31 +815,79 @@
         <v>CDISCPILOT01</v>
       </c>
       <c r="B5" s="3" t="str">
-        <v>TS</v>
-      </c>
-      <c r="C5" s="3">
+        <v>DM</v>
+      </c>
+      <c r="C5" s="3" t="str">
+        <v>CDISC001</v>
+      </c>
+      <c r="D5" s="3" t="str">
         <v>1</v>
       </c>
-      <c r="D5" s="3" t="str">
+      <c r="E5" s="3" t="str">
+        <v>2012-11-30</v>
+      </c>
+      <c r="F5" s="3" t="str">
+        <v>2013-01-23</v>
+      </c>
+      <c r="G5" s="3" t="str">
+        <v>2012-11-30</v>
+      </c>
+      <c r="H5" s="3" t="str">
+        <v>2013-01-23</v>
+      </c>
+      <c r="I5" s="3" t="str">
+        <v>2012-11-23</v>
+      </c>
+      <c r="J5" s="3" t="str">
+        <v>2013-05-20</v>
+      </c>
+      <c r="K5" s="3" t="str">
         <v/>
       </c>
-      <c r="E5" s="3" t="str">
-        <v>FCNTRY</v>
-      </c>
-      <c r="F5" s="3" t="str">
-        <v>Planned Country of Investigational Sites</v>
-      </c>
-      <c r="G5" s="3" t="str">
-        <v>Afghanistan</v>
-      </c>
-      <c r="H5" s="3" t="str">
-        <v>NA</v>
-      </c>
-      <c r="I5" s="3" t="str">
-        <v>AFG</v>
-      </c>
-      <c r="J5" s="3" t="str">
-        <v>ISO 3166</v>
+      <c r="L5" s="3" t="str">
+        <v/>
+      </c>
+      <c r="M5" s="3" t="str">
+        <v>701</v>
+      </c>
+      <c r="N5" s="3" t="str">
+        <v>1928</v>
+      </c>
+      <c r="O5" s="3">
+        <v>84</v>
+      </c>
+      <c r="P5" s="3" t="str">
+        <v>YEARS</v>
+      </c>
+      <c r="Q5" s="3" t="str">
+        <v>M</v>
+      </c>
+      <c r="R5" s="3" t="str">
+        <v>WHITE</v>
+      </c>
+      <c r="S5" s="3" t="str">
+        <v>NOT HISPANIC OR LATINO</v>
+      </c>
+      <c r="T5" s="3" t="str">
+        <v>ZAN_LOW</v>
+      </c>
+      <c r="U5" s="3" t="str">
+        <v>Zanomaline Low Dose (54 mg)</v>
+      </c>
+      <c r="V5" s="3" t="str">
+        <v>ZAN_LOW</v>
+      </c>
+      <c r="W5" s="3" t="str">
+        <v>Zanomaline Low Dose (54 mg)</v>
+      </c>
+      <c r="X5" s="3" t="str">
+        <v/>
+      </c>
+      <c r="Y5" s="3" t="str">
+        <v/>
+      </c>
+      <c r="Z5" s="3" t="str">
+        <v>USA</v>
       </c>
     </row>
     <row r="6">
@@ -667,36 +895,84 @@
         <v>CDISCPILOT01</v>
       </c>
       <c r="B6" s="3" t="str">
-        <v>TS</v>
-      </c>
-      <c r="C6" s="3">
+        <v>DM</v>
+      </c>
+      <c r="C6" s="3" t="str">
+        <v>CDISC002</v>
+      </c>
+      <c r="D6" s="3" t="str">
         <v>2</v>
       </c>
-      <c r="D6" s="2" t="str">
+      <c r="E6" s="3" t="str">
+        <v>2012-11-15</v>
+      </c>
+      <c r="F6" s="3" t="str">
+        <v>2013-01-14</v>
+      </c>
+      <c r="G6" s="3" t="str">
+        <v>2012-11-15</v>
+      </c>
+      <c r="H6" s="3" t="str">
+        <v>2013-01-12</v>
+      </c>
+      <c r="I6" s="3" t="str">
+        <v>2012-10-30</v>
+      </c>
+      <c r="J6" s="3" t="str">
+        <v>2013-01-14</v>
+      </c>
+      <c r="K6" s="3" t="str">
+        <v>2013-01-14</v>
+      </c>
+      <c r="L6" s="3" t="str">
+        <v>Y</v>
+      </c>
+      <c r="M6" s="3" t="str">
+        <v>701</v>
+      </c>
+      <c r="N6" s="3" t="str">
+        <v>1936</v>
+      </c>
+      <c r="O6" s="3">
+        <v>76</v>
+      </c>
+      <c r="P6" s="3" t="str">
+        <v>YEARS</v>
+      </c>
+      <c r="Q6" s="3" t="str">
+        <v>F</v>
+      </c>
+      <c r="R6" s="3" t="str">
+        <v>WHITE</v>
+      </c>
+      <c r="S6" s="3" t="str">
+        <v>NOT HISPANIC OR LATINO</v>
+      </c>
+      <c r="T6" s="3" t="str">
+        <v>ZAN_LOW</v>
+      </c>
+      <c r="U6" s="3" t="str">
+        <v>Zanomaline Low Dose (54 mg)</v>
+      </c>
+      <c r="V6" s="3" t="str">
+        <v>ZAN_LOW</v>
+      </c>
+      <c r="W6" s="3" t="str">
+        <v>Zanomaline Low Dose (54 mg)</v>
+      </c>
+      <c r="X6" s="3" t="str">
         <v/>
       </c>
-      <c r="E6" s="3" t="str">
-        <v>FCNTRY</v>
-      </c>
-      <c r="F6" s="3" t="str">
-        <v>Planned Country of Investigational Sites</v>
-      </c>
-      <c r="G6" s="3" t="str">
-        <v>Albania</v>
-      </c>
-      <c r="H6" s="3" t="str">
-        <v>NA</v>
-      </c>
-      <c r="I6" s="3" t="str">
-        <v>ALB</v>
-      </c>
-      <c r="J6" s="3" t="str">
-        <v>GENC</v>
+      <c r="Y6" s="3" t="str">
+        <v/>
+      </c>
+      <c r="Z6" s="3" t="str">
+        <v>BHS</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:Z6"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/rules/NEW-RULE/positive/01/data/new-rule-positive-01.xlsx
+++ b/rules/NEW-RULE/positive/01/data/new-rule-positive-01.xlsx
@@ -488,7 +488,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:K5"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="4" t="str">
@@ -650,53 +650,21 @@
         <v>Planned Country of Investigational Sites</v>
       </c>
       <c r="G5" s="3" t="str">
-        <v>Afghanistan</v>
+        <v>Albania</v>
       </c>
       <c r="H5" s="3" t="str">
         <v>NA</v>
       </c>
       <c r="I5" s="3" t="str">
-        <v>AFG</v>
+        <v>ALB</v>
       </c>
       <c r="J5" s="3" t="str">
-        <v>ISO 3166</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="str">
-        <v>CDISCPILOT01</v>
-      </c>
-      <c r="B6" s="3" t="str">
-        <v>TS</v>
-      </c>
-      <c r="C6" s="3">
-        <v>2</v>
-      </c>
-      <c r="D6" s="2" t="str">
-        <v/>
-      </c>
-      <c r="E6" s="3" t="str">
-        <v>FCNTRY</v>
-      </c>
-      <c r="F6" s="3" t="str">
-        <v>Planned Country of Investigational Sites</v>
-      </c>
-      <c r="G6" s="3" t="str">
-        <v>Albania</v>
-      </c>
-      <c r="H6" s="3" t="str">
-        <v>NA</v>
-      </c>
-      <c r="I6" s="3" t="str">
-        <v>ALB</v>
-      </c>
-      <c r="J6" s="3" t="str">
         <v>GENC</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K5"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/rules/NEW-RULE/positive/01/data/new-rule-positive-01.xlsx
+++ b/rules/NEW-RULE/positive/01/data/new-rule-positive-01.xlsx
@@ -8,22 +8,23 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/enrico/Work/core-contributor/rules/NEW-RULE/positive/01/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A7E65A1-7F88-124E-A1AF-F4BF002E15A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CE8799A-5F07-7041-BC50-0F2B7738E6D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30240" yWindow="-4560" windowWidth="51200" windowHeight="28800" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30240" yWindow="-4560" windowWidth="51200" windowHeight="28800" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Library" sheetId="1" r:id="rId1"/>
     <sheet name="Datasets" sheetId="2" r:id="rId2"/>
     <sheet name="dm.xpt" sheetId="10" r:id="rId3"/>
-    <sheet name="lb.xpt" sheetId="11" r:id="rId4"/>
+    <sheet name="lb1.xpt" sheetId="11" r:id="rId4"/>
+    <sheet name="lb2.xpt" sheetId="12" r:id="rId5"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="526" uniqueCount="181">
   <si>
     <t>Product</t>
   </si>
@@ -550,20 +551,29 @@
     <t>Start Date/Time of Specimen Collection</t>
   </si>
   <si>
-    <t>lb.xpt</t>
-  </si>
-  <si>
     <t>Laboratory Test Results</t>
   </si>
   <si>
     <t>2012-11-24</t>
+  </si>
+  <si>
+    <t>lb2.xpt</t>
+  </si>
+  <si>
+    <t>lb1.xpt</t>
+  </si>
+  <si>
+    <t>2012-11-23T15:39:00</t>
+  </si>
+  <si>
+    <t>2012-11-24T15:39:00</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -587,6 +597,13 @@
       <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -650,7 +667,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -668,6 +685,9 @@
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -998,7 +1018,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
@@ -1019,10 +1039,18 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
+        <v>178</v>
+      </c>
+      <c r="B3" t="s">
         <v>175</v>
       </c>
-      <c r="B3" t="s">
-        <v>176</v>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>177</v>
+      </c>
+      <c r="B4" t="s">
+        <v>175</v>
       </c>
     </row>
   </sheetData>
@@ -2085,7 +2113,7 @@
         <v>27</v>
       </c>
       <c r="X6" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Y6" s="4" t="s">
         <v>24</v>
@@ -2159,13 +2187,13 @@
         <v>153</v>
       </c>
       <c r="V7" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="W7" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="X7" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Z7" s="4" t="s">
         <v>152</v>
@@ -2236,13 +2264,13 @@
         <v>153</v>
       </c>
       <c r="V8" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="W8" s="4" t="s">
         <v>27</v>
       </c>
       <c r="X8" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Y8" s="4" t="s">
         <v>24</v>
@@ -2326,6 +2354,742 @@
       </c>
       <c r="X9" s="4" t="s">
         <v>27</v>
+      </c>
+      <c r="AA9" s="4">
+        <v>-7</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F127196-93C6-6E48-A5BC-C49EF39B5C8B}">
+  <dimension ref="A1:AA9"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:27" ht="16" x14ac:dyDescent="0.2">
+      <c r="A1" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="H1" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="I1" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="J1" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="K1" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="L1" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="M1" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="N1" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="O1" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="P1" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="Q1" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="R1" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="S1" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="T1" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="U1" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="V1" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="W1" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="X1" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="Y1" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="Z1" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="AA1" s="7" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="2" spans="1:27" ht="80" x14ac:dyDescent="0.2">
+      <c r="A2" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="G2" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="H2" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="I2" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="J2" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="K2" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="L2" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="M2" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="N2" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="O2" s="8" t="s">
+        <v>132</v>
+      </c>
+      <c r="P2" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="Q2" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="R2" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="S2" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="T2" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="U2" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="V2" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="W2" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="X2" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="Y2" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="Z2" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="AA2" s="8" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="3" spans="1:27" ht="16" x14ac:dyDescent="0.2">
+      <c r="A3" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G3" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="I3" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="J3" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="K3" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="L3" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="M3" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="N3" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="O3" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="P3" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q3" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="R3" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="S3" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="T3" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="U3" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="V3" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="W3" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="X3" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y3" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z3" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="AA3" s="8" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A4" s="8">
+        <v>12</v>
+      </c>
+      <c r="B4" s="8">
+        <v>2</v>
+      </c>
+      <c r="C4" s="8">
+        <v>8</v>
+      </c>
+      <c r="D4" s="8">
+        <v>8</v>
+      </c>
+      <c r="E4" s="8">
+        <v>7</v>
+      </c>
+      <c r="F4" s="8">
+        <v>39</v>
+      </c>
+      <c r="G4" s="8">
+        <v>10</v>
+      </c>
+      <c r="H4" s="8">
+        <v>6</v>
+      </c>
+      <c r="I4" s="8">
+        <v>7</v>
+      </c>
+      <c r="J4" s="8">
+        <v>200</v>
+      </c>
+      <c r="K4" s="8">
+        <v>200</v>
+      </c>
+      <c r="L4" s="8">
+        <v>8</v>
+      </c>
+      <c r="M4" s="8">
+        <v>8</v>
+      </c>
+      <c r="N4" s="8">
+        <v>7</v>
+      </c>
+      <c r="O4" s="8">
+        <v>8</v>
+      </c>
+      <c r="P4" s="8">
+        <v>8</v>
+      </c>
+      <c r="Q4" s="8">
+        <v>8</v>
+      </c>
+      <c r="R4" s="8">
+        <v>1</v>
+      </c>
+      <c r="S4" s="8">
+        <v>8</v>
+      </c>
+      <c r="T4" s="8">
+        <v>200</v>
+      </c>
+      <c r="U4" s="8">
+        <v>9</v>
+      </c>
+      <c r="V4" s="8">
+        <v>19</v>
+      </c>
+      <c r="W4" s="8">
+        <v>19</v>
+      </c>
+      <c r="X4" s="8">
+        <v>19</v>
+      </c>
+      <c r="Y4" s="3">
+        <v>50</v>
+      </c>
+      <c r="Z4" s="3">
+        <v>50</v>
+      </c>
+      <c r="AA4" s="8">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:27" ht="48" x14ac:dyDescent="0.2">
+      <c r="A5" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D5" s="4">
+        <v>1</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="K5" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="L5" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="M5" s="4">
+        <v>39</v>
+      </c>
+      <c r="N5" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="Q5" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="R5" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="S5" s="4">
+        <v>1</v>
+      </c>
+      <c r="T5" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="U5" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="V5" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="W5" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="X5" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="Y5" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z5" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="AA5" s="4">
+        <v>-7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:27" ht="48" x14ac:dyDescent="0.2">
+      <c r="A6" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" s="4">
+        <v>2</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="I6" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="J6" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="K6" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="L6" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="M6" s="4">
+        <v>93</v>
+      </c>
+      <c r="N6" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="O6" s="4">
+        <v>35</v>
+      </c>
+      <c r="P6" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="Q6" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="R6" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="S6" s="4">
+        <v>1</v>
+      </c>
+      <c r="T6" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="U6" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="V6" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="W6" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="X6" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="Y6" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z6" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="AA6" s="4">
+        <v>-7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:27" ht="48" x14ac:dyDescent="0.2">
+      <c r="A7" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D7" s="4">
+        <v>3</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="I7" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="J7" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="K7" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="L7" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="M7" s="4">
+        <v>18</v>
+      </c>
+      <c r="N7" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="O7" s="4">
+        <v>6</v>
+      </c>
+      <c r="Q7" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="R7" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="S7" s="4">
+        <v>1</v>
+      </c>
+      <c r="T7" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="U7" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="V7" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="W7" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="X7" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="Z7" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="AA7" s="4">
+        <v>-7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27" ht="48" x14ac:dyDescent="0.2">
+      <c r="A8" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D8" s="4">
+        <v>4</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="I8" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="J8" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="K8" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="L8" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="M8" s="4">
+        <v>26</v>
+      </c>
+      <c r="N8" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="P8" s="4">
+        <v>36</v>
+      </c>
+      <c r="Q8" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="R8" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="S8" s="4">
+        <v>1</v>
+      </c>
+      <c r="T8" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="U8" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="V8" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="W8" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="X8" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="Y8" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z8" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="AA8" s="4">
+        <v>-7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" ht="48" x14ac:dyDescent="0.2">
+      <c r="A9" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D9" s="4">
+        <v>5</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="I9" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="J9" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="K9" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="L9" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="M9" s="4">
+        <v>0.03</v>
+      </c>
+      <c r="N9" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="O9" s="4">
+        <v>0</v>
+      </c>
+      <c r="P9" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="Q9" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="R9" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="S9" s="4">
+        <v>1</v>
+      </c>
+      <c r="T9" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="U9" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="V9" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="W9" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="X9" s="4" t="s">
+        <v>179</v>
       </c>
       <c r="AA9" s="4">
         <v>-7</v>

--- a/rules/NEW-RULE/positive/01/data/new-rule-positive-01.xlsx
+++ b/rules/NEW-RULE/positive/01/data/new-rule-positive-01.xlsx
@@ -1,41 +1,120 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
-  <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
-  </bookViews>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Library" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Datasets" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Library" sheetId="1" r:id="rId1"/>
+    <sheet name="Datasets" sheetId="2" r:id="rId2"/>
+    <sheet name="dm.xpt" sheetId="3" r:id="rId3"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <color theme="1"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <scheme val="minor"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <i/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <color rgb="FF000000"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none">
+        <bgColor/>
+      </patternFill>
     </fill>
     <fill>
-      <patternFill patternType="gray125"/>
+      <patternFill patternType="gray125">
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left/>
       <right/>
@@ -44,84 +123,25 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+  <cellXfs count="9">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="1" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+  <cellStyles>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
 </styleSheet>
 </file>
 
@@ -200,6 +220,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -234,6 +255,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -268,20 +290,16 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
+                <a:tint val="100000"/>
+                <a:shade val="100000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="80000">
-              <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
+                <a:tint val="50000"/>
+                <a:shade val="100000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -403,75 +421,421 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
+  <a:objectDefaults>
+    <a:spDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="3">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </a:style>
+    </a:spDef>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
   <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Product</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Version</t>
-        </is>
+      <c r="A1" s="3" t="str">
+        <v>Product</v>
+      </c>
+      <c r="B1" s="3" t="str">
+        <v>Version</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>sdtmig</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>3-4</t>
-        </is>
+      <c r="A2" s="3" t="str">
+        <v>sdtmig</v>
+      </c>
+      <c r="B2" s="3" t="str">
+        <v>3-4</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:B2"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Filename</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Label</t>
-        </is>
+      <c r="A1" s="3" t="str">
+        <v>Filename</v>
+      </c>
+      <c r="B1" s="3" t="str">
+        <v>Label</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr"/>
-      <c r="B2" t="inlineStr"/>
+      <c r="A2" s="3" t="str">
+        <v>dm.xpt</v>
+      </c>
+      <c r="B2" s="3" t="str">
+        <v>Demographics</v>
+      </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:B2"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:T5"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="str">
+        <v>STUDYID</v>
+      </c>
+      <c r="B1" s="4" t="str">
+        <v>DOMAIN</v>
+      </c>
+      <c r="C1" s="4" t="str">
+        <v>USUBJID</v>
+      </c>
+      <c r="D1" s="4" t="str">
+        <v>SUBJID</v>
+      </c>
+      <c r="E1" s="4" t="str">
+        <v>RFSTDTC</v>
+      </c>
+      <c r="F1" s="4" t="str">
+        <v>RFENDTC</v>
+      </c>
+      <c r="G1" s="4" t="str">
+        <v>BRTHDTC</v>
+      </c>
+      <c r="H1" s="4" t="str">
+        <v>AGE</v>
+      </c>
+      <c r="I1" s="4" t="str">
+        <v>AGETXT</v>
+      </c>
+      <c r="J1" s="4" t="str">
+        <v>AGEU</v>
+      </c>
+      <c r="K1" s="4" t="str">
+        <v>SEX</v>
+      </c>
+      <c r="L1" s="4" t="str">
+        <v>RACE</v>
+      </c>
+      <c r="M1" s="4" t="str">
+        <v>ETHNIC</v>
+      </c>
+      <c r="N1" s="5" t="str">
+        <v>ARMCD</v>
+      </c>
+      <c r="O1" s="4" t="str">
+        <v>ARM</v>
+      </c>
+      <c r="P1" s="5" t="str">
+        <v>ACTARMCD</v>
+      </c>
+      <c r="Q1" s="5" t="str">
+        <v>ACTARM</v>
+      </c>
+      <c r="R1" s="5" t="str">
+        <v>ARMNRS</v>
+      </c>
+      <c r="S1" s="4" t="str">
+        <v>ACTARMUD</v>
+      </c>
+      <c r="T1" s="4" t="str">
+        <v>COUNTRY</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="6" t="str">
+        <v>Study Identifier</v>
+      </c>
+      <c r="B2" s="6" t="str">
+        <v>Domain Abbreviation</v>
+      </c>
+      <c r="C2" s="6" t="str">
+        <v>Unique Subject Identifier</v>
+      </c>
+      <c r="D2" s="6" t="str">
+        <v>Subject Identifier for the Study</v>
+      </c>
+      <c r="E2" s="6" t="str">
+        <v>Subject Reference Start Date/Time</v>
+      </c>
+      <c r="F2" s="6" t="str">
+        <v>Subject Reference End Date/Time</v>
+      </c>
+      <c r="G2" s="6" t="str">
+        <v>Date/Time of Birth</v>
+      </c>
+      <c r="H2" s="6" t="str">
+        <v>Age</v>
+      </c>
+      <c r="I2" s="6" t="str">
+        <v>Age Text</v>
+      </c>
+      <c r="J2" s="6" t="str">
+        <v>Age Units</v>
+      </c>
+      <c r="K2" s="6" t="str">
+        <v>Sex</v>
+      </c>
+      <c r="L2" s="6" t="str">
+        <v>Race</v>
+      </c>
+      <c r="M2" s="6" t="str">
+        <v>Ethnicity</v>
+      </c>
+      <c r="N2" s="6" t="str">
+        <v>Planned Arm Code</v>
+      </c>
+      <c r="O2" s="6" t="str">
+        <v>Description of Planned Arm</v>
+      </c>
+      <c r="P2" s="6" t="str">
+        <v>Actual Arm Code</v>
+      </c>
+      <c r="Q2" s="6" t="str">
+        <v>Description of Actual Arm</v>
+      </c>
+      <c r="R2" s="6" t="str">
+        <v>Reason Arm and/or Actual Arm is Null</v>
+      </c>
+      <c r="S2" s="6" t="str">
+        <v>Description of Unplanned Actual Arm</v>
+      </c>
+      <c r="T2" s="6" t="str">
+        <v>Country</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="str">
+        <v>Char</v>
+      </c>
+      <c r="B3" s="6" t="str">
+        <v>Char</v>
+      </c>
+      <c r="C3" s="6" t="str">
+        <v>Char</v>
+      </c>
+      <c r="D3" s="6" t="str">
+        <v>Char</v>
+      </c>
+      <c r="E3" s="6" t="str">
+        <v>Char</v>
+      </c>
+      <c r="F3" s="6" t="str">
+        <v>Char</v>
+      </c>
+      <c r="G3" s="6" t="str">
+        <v>Char</v>
+      </c>
+      <c r="H3" s="6" t="str">
+        <v>Num</v>
+      </c>
+      <c r="I3" s="6" t="str">
+        <v>Char</v>
+      </c>
+      <c r="J3" s="6" t="str">
+        <v>Char</v>
+      </c>
+      <c r="K3" s="6" t="str">
+        <v>Char</v>
+      </c>
+      <c r="L3" s="6" t="str">
+        <v>Char</v>
+      </c>
+      <c r="M3" s="6" t="str">
+        <v>Char</v>
+      </c>
+      <c r="N3" s="6" t="str">
+        <v>Char</v>
+      </c>
+      <c r="O3" s="6" t="str">
+        <v>Char</v>
+      </c>
+      <c r="P3" s="6" t="str">
+        <v>Char</v>
+      </c>
+      <c r="Q3" s="6" t="str">
+        <v>Char</v>
+      </c>
+      <c r="R3" s="6" t="str">
+        <v>Char</v>
+      </c>
+      <c r="S3" s="6" t="str">
+        <v>Char</v>
+      </c>
+      <c r="T3" s="6" t="str">
+        <v>Char</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6">
+        <v>12</v>
+      </c>
+      <c r="B4" s="6">
+        <v>2</v>
+      </c>
+      <c r="C4" s="6">
+        <v>20</v>
+      </c>
+      <c r="D4" s="6">
+        <v>12</v>
+      </c>
+      <c r="E4" s="6">
+        <v>10</v>
+      </c>
+      <c r="F4" s="6">
+        <v>10</v>
+      </c>
+      <c r="G4" s="6">
+        <v>10</v>
+      </c>
+      <c r="H4" s="6">
+        <v>8</v>
+      </c>
+      <c r="I4" s="6">
+        <v>5</v>
+      </c>
+      <c r="J4" s="6">
+        <v>5</v>
+      </c>
+      <c r="K4" s="6">
+        <v>1</v>
+      </c>
+      <c r="L4" s="6">
+        <v>41</v>
+      </c>
+      <c r="M4" s="6">
+        <v>22</v>
+      </c>
+      <c r="N4" s="6">
+        <v>8</v>
+      </c>
+      <c r="O4" s="6">
+        <v>28</v>
+      </c>
+      <c r="P4" s="6">
+        <v>8</v>
+      </c>
+      <c r="Q4" s="6">
+        <v>28</v>
+      </c>
+      <c r="R4" s="6">
+        <v>14</v>
+      </c>
+      <c r="S4" s="6">
+        <v>200</v>
+      </c>
+      <c r="T4" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="str">
+        <v>CDISCPILOT01</v>
+      </c>
+      <c r="B5" s="7" t="str">
+        <v>DM</v>
+      </c>
+      <c r="C5" s="7">
+        <v>1</v>
+      </c>
+      <c r="D5" s="7">
+        <v>1</v>
+      </c>
+      <c r="E5" s="7" t="str">
+        <v/>
+      </c>
+      <c r="F5" s="7" t="str">
+        <v/>
+      </c>
+      <c r="G5" s="7" t="str">
+        <v/>
+      </c>
+      <c r="H5" s="7" t="str">
+        <v/>
+      </c>
+      <c r="I5" s="7" t="str">
+        <v/>
+      </c>
+      <c r="J5" s="7" t="str">
+        <v/>
+      </c>
+      <c r="K5" s="7" t="str">
+        <v/>
+      </c>
+      <c r="L5" s="7" t="str">
+        <v/>
+      </c>
+      <c r="M5" s="7" t="str">
+        <v/>
+      </c>
+      <c r="N5" s="7" t="str">
+        <v/>
+      </c>
+      <c r="O5" s="8" t="str">
+        <v/>
+      </c>
+      <c r="P5" s="8" t="str">
+        <v/>
+      </c>
+      <c r="Q5" s="8" t="str">
+        <v/>
+      </c>
+      <c r="R5" s="7" t="str">
+        <v/>
+      </c>
+      <c r="S5" s="7" t="str">
+        <v/>
+      </c>
+      <c r="T5" s="7" t="str">
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:T5"/>
+  </ignoredErrors>
 </worksheet>
 </file>
--- a/rules/NEW-RULE/positive/01/data/new-rule-positive-01.xlsx
+++ b/rules/NEW-RULE/positive/01/data/new-rule-positive-01.xlsx
@@ -1,41 +1,619 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10621"/>
+  <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rich/Documents/github/core-contributor/rules/NEW-RULE/positive/01/data/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E10E07A-9942-694C-9BFB-F59AE453A0F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="38220" yWindow="-2260" windowWidth="30240" windowHeight="18980" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Library" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Datasets" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Library" sheetId="1" r:id="rId1"/>
+    <sheet name="Datasets" sheetId="2" r:id="rId2"/>
+    <sheet name="ae.xpt" sheetId="3" r:id="rId3"/>
+    <sheet name="dm.xpt" sheetId="4" r:id="rId4"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="175">
+  <si>
+    <t>Product</t>
+  </si>
+  <si>
+    <t>Version</t>
+  </si>
+  <si>
+    <t>sdtmig</t>
+  </si>
+  <si>
+    <t>3-4</t>
+  </si>
+  <si>
+    <t>Filename</t>
+  </si>
+  <si>
+    <t>Label</t>
+  </si>
+  <si>
+    <t>ae.xpt</t>
+  </si>
+  <si>
+    <t>Adverse Events</t>
+  </si>
+  <si>
+    <t>STUDYID</t>
+  </si>
+  <si>
+    <t>DOMAIN</t>
+  </si>
+  <si>
+    <t>USUBJID</t>
+  </si>
+  <si>
+    <t>AESEQ</t>
+  </si>
+  <si>
+    <t>AESPID</t>
+  </si>
+  <si>
+    <t>AETERM</t>
+  </si>
+  <si>
+    <t>AELLT</t>
+  </si>
+  <si>
+    <t>AELLTCD</t>
+  </si>
+  <si>
+    <t>AEDECOD</t>
+  </si>
+  <si>
+    <t>AEPTCD</t>
+  </si>
+  <si>
+    <t>AEHLT</t>
+  </si>
+  <si>
+    <t>AEHLTCD</t>
+  </si>
+  <si>
+    <t>AEHLGT</t>
+  </si>
+  <si>
+    <t>AEHLGTCD</t>
+  </si>
+  <si>
+    <t>AEBODSYS</t>
+  </si>
+  <si>
+    <t>AEBDSYCD</t>
+  </si>
+  <si>
+    <t>AESOC</t>
+  </si>
+  <si>
+    <t>AESOCCD</t>
+  </si>
+  <si>
+    <t>AESEV</t>
+  </si>
+  <si>
+    <t>AESER</t>
+  </si>
+  <si>
+    <t>AEACN</t>
+  </si>
+  <si>
+    <t>AEREL</t>
+  </si>
+  <si>
+    <t>AEOUT</t>
+  </si>
+  <si>
+    <t>AESHOSP</t>
+  </si>
+  <si>
+    <t>AESTDTC</t>
+  </si>
+  <si>
+    <t>AEENDTC</t>
+  </si>
+  <si>
+    <t>AESTDY</t>
+  </si>
+  <si>
+    <t>Study Identifier</t>
+  </si>
+  <si>
+    <t>Domain Abbreviation</t>
+  </si>
+  <si>
+    <t>Unique Subject Identifier</t>
+  </si>
+  <si>
+    <t>Sequence Number</t>
+  </si>
+  <si>
+    <t>Sponsor-Defined Identifier</t>
+  </si>
+  <si>
+    <t>Reported Term for the Adverse Event</t>
+  </si>
+  <si>
+    <t>Lowest Level Term</t>
+  </si>
+  <si>
+    <t>Lowest Level Term Code</t>
+  </si>
+  <si>
+    <t>Dictionary-Derived Term</t>
+  </si>
+  <si>
+    <t>Preferred Term Code</t>
+  </si>
+  <si>
+    <t>High Level Term</t>
+  </si>
+  <si>
+    <t>High Level Term Code</t>
+  </si>
+  <si>
+    <t>High Level Group Term</t>
+  </si>
+  <si>
+    <t>High Level Group Term Code</t>
+  </si>
+  <si>
+    <t>Body System or Organ Class</t>
+  </si>
+  <si>
+    <t>Body System or Organ Class Code</t>
+  </si>
+  <si>
+    <t>Primary System Organ Class</t>
+  </si>
+  <si>
+    <t>Primary System Organ Class Code</t>
+  </si>
+  <si>
+    <t>Severity/Intensity</t>
+  </si>
+  <si>
+    <t>Serious Event</t>
+  </si>
+  <si>
+    <t>Action Taken with Study Treatment</t>
+  </si>
+  <si>
+    <t>Causality</t>
+  </si>
+  <si>
+    <t>Outcome of Adverse Event</t>
+  </si>
+  <si>
+    <t>Requires or Prolongs Hospitalization</t>
+  </si>
+  <si>
+    <t>Start Date/Time of Adverse Event</t>
+  </si>
+  <si>
+    <t>End Date/Time of Adverse Event</t>
+  </si>
+  <si>
+    <t>Study Day of Start of Adverse Event</t>
+  </si>
+  <si>
+    <t>Char</t>
+  </si>
+  <si>
+    <t>Num</t>
+  </si>
+  <si>
+    <t>CDISC-TEST</t>
+  </si>
+  <si>
+    <t>AE</t>
+  </si>
+  <si>
+    <t>CDISC-TEST-001</t>
+  </si>
+  <si>
+    <t>UPSET STOMACH</t>
+  </si>
+  <si>
+    <t>Upset Stomach</t>
+  </si>
+  <si>
+    <t>Abdominal discomfort</t>
+  </si>
+  <si>
+    <t>Gastrointestinal signs and symptoms NEC</t>
+  </si>
+  <si>
+    <t>Gastrointestinal signs and symptoms</t>
+  </si>
+  <si>
+    <t>Gastrointestinal orders</t>
+  </si>
+  <si>
+    <t>Gastrointestinal disorders</t>
+  </si>
+  <si>
+    <t>MILD</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Extensible</t>
+  </si>
+  <si>
+    <t>RECOVERED/RESOLVED</t>
+  </si>
+  <si>
+    <t>BACK PAIN</t>
+  </si>
+  <si>
+    <t>Back pain</t>
+  </si>
+  <si>
+    <t>Musculoskeletal and connective tissue pain and discomfort</t>
+  </si>
+  <si>
+    <t>Musculoskeletal and connective tissue disorders NEC</t>
+  </si>
+  <si>
+    <t>Connective tissue disorders</t>
+  </si>
+  <si>
+    <t>Musculoskeletal and connective tissue disorders</t>
+  </si>
+  <si>
+    <t>Allergic conditions</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>DIARRHOEA</t>
+  </si>
+  <si>
+    <t>Diarrhoea</t>
+  </si>
+  <si>
+    <t>Diarrhoea (excl infective)</t>
+  </si>
+  <si>
+    <t>Gastrointestinal motility and defaecation conditions</t>
+  </si>
+  <si>
+    <t>HEADACHE</t>
+  </si>
+  <si>
+    <t>Headache</t>
+  </si>
+  <si>
+    <t>Headaches NEC</t>
+  </si>
+  <si>
+    <t>Headaches</t>
+  </si>
+  <si>
+    <t>NVD</t>
+  </si>
+  <si>
+    <t>Nervous system disorders</t>
+  </si>
+  <si>
+    <t>SUBJID</t>
+  </si>
+  <si>
+    <t>RFSTDTC</t>
+  </si>
+  <si>
+    <t>RFENDTC</t>
+  </si>
+  <si>
+    <t>RFXSTDTC</t>
+  </si>
+  <si>
+    <t>RFXENDTC</t>
+  </si>
+  <si>
+    <t>RFICDTC</t>
+  </si>
+  <si>
+    <t>RFPENDTC</t>
+  </si>
+  <si>
+    <t>DTHDTC</t>
+  </si>
+  <si>
+    <t>DTHFL</t>
+  </si>
+  <si>
+    <t>SITEID</t>
+  </si>
+  <si>
+    <t>BRTHDTC</t>
+  </si>
+  <si>
+    <t>AGE</t>
+  </si>
+  <si>
+    <t>AGEU</t>
+  </si>
+  <si>
+    <t>SEX</t>
+  </si>
+  <si>
+    <t>RACE</t>
+  </si>
+  <si>
+    <t>ETHNIC</t>
+  </si>
+  <si>
+    <t>ARMCD</t>
+  </si>
+  <si>
+    <t>ARM</t>
+  </si>
+  <si>
+    <t>ACTARMCD</t>
+  </si>
+  <si>
+    <t>ACTARM</t>
+  </si>
+  <si>
+    <t>ARMNRS</t>
+  </si>
+  <si>
+    <t>ACTARMUD</t>
+  </si>
+  <si>
+    <t>COUNTRY</t>
+  </si>
+  <si>
+    <t>Subject Identifier for the Study</t>
+  </si>
+  <si>
+    <t>Subject Reference Start Date/Time</t>
+  </si>
+  <si>
+    <t>Subject Reference End Date/Time</t>
+  </si>
+  <si>
+    <t>Date/Time of First Study Treatment</t>
+  </si>
+  <si>
+    <t>Date/Time of Last Study Treatment</t>
+  </si>
+  <si>
+    <t>Date/Time of Informed Consent</t>
+  </si>
+  <si>
+    <t>Date/Time of End of Participation</t>
+  </si>
+  <si>
+    <t>Date/Time of Death</t>
+  </si>
+  <si>
+    <t>Subject Death Flag</t>
+  </si>
+  <si>
+    <t>Study Site Identifier</t>
+  </si>
+  <si>
+    <t>Date/Time of Birth</t>
+  </si>
+  <si>
+    <t>Age</t>
+  </si>
+  <si>
+    <t>Age Units</t>
+  </si>
+  <si>
+    <t>Sex</t>
+  </si>
+  <si>
+    <t>Race</t>
+  </si>
+  <si>
+    <t>Ethnicity</t>
+  </si>
+  <si>
+    <t>Planned Arm Code</t>
+  </si>
+  <si>
+    <t>Description of Planned Arm</t>
+  </si>
+  <si>
+    <t>Actual Arm Code</t>
+  </si>
+  <si>
+    <t>Description of Actual Arm</t>
+  </si>
+  <si>
+    <t>Reason Arm and/or Actual Arm is Null</t>
+  </si>
+  <si>
+    <t>Description of Unplanned Actual Arm</t>
+  </si>
+  <si>
+    <t>Country</t>
+  </si>
+  <si>
+    <t>CDISCPILOT01</t>
+  </si>
+  <si>
+    <t>DM</t>
+  </si>
+  <si>
+    <t>CDISC001</t>
+  </si>
+  <si>
+    <t>2018-05-17T09:35</t>
+  </si>
+  <si>
+    <t>1947-07-24T00:00:00.000Z</t>
+  </si>
+  <si>
+    <t>YEARS</t>
+  </si>
+  <si>
+    <t>M</t>
+  </si>
+  <si>
+    <t>WHITE</t>
+  </si>
+  <si>
+    <t>NOT HISPANIC OR LATINO</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>Drug A</t>
+  </si>
+  <si>
+    <t>AUS</t>
+  </si>
+  <si>
+    <t>CDISC002</t>
+  </si>
+  <si>
+    <t>2018-05-24T12:00</t>
+  </si>
+  <si>
+    <t>1905-05-08T00:00:00.000Z</t>
+  </si>
+  <si>
+    <t>P</t>
+  </si>
+  <si>
+    <t>Placebo</t>
+  </si>
+  <si>
+    <t>CDISC003</t>
+  </si>
+  <si>
+    <t>1944-06-16T00:00:00.000Z</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>Drug B</t>
+  </si>
+  <si>
+    <t>CZE</t>
+  </si>
+  <si>
+    <t>CDISC004</t>
+  </si>
+  <si>
+    <t>2018-07-16T09:15</t>
+  </si>
+  <si>
+    <t>2018-11-06T14:00</t>
+  </si>
+  <si>
+    <t>1905-04-16T00:00:00.000Z</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>HISPANIC OR LATINO</t>
+  </si>
+  <si>
+    <t>CAN</t>
+  </si>
+  <si>
+    <t>H</t>
+  </si>
+  <si>
+    <t>dm.xpt</t>
+  </si>
+  <si>
+    <t>Demographics</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <scheme val="minor"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left/>
       <right/>
@@ -47,81 +625,30 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+  <cellXfs count="9">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -200,6 +727,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -234,6 +762,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -268,20 +797,16 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="80000">
-              <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
+                <a:tint val="100000"/>
+                <a:shade val="100000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
+                <a:tint val="50000"/>
+                <a:shade val="100000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -403,75 +928,1582 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
+  <a:objectDefaults>
+    <a:spDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="3">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </a:style>
+    </a:spDef>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
   <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Product</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Version</t>
-        </is>
+    <row r="1" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>sdtmig</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>3-4</t>
-        </is>
+    <row r="2" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <ignoredErrors>
+    <ignoredError sqref="A1:B2" numberStoredAsText="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Filename</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Label</t>
-        </is>
+    <row r="1" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
-      <c r="B2" t="inlineStr"/>
+    <row r="2" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A3" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>174</v>
+      </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <ignoredErrors>
+    <ignoredError sqref="A1:B2" numberStoredAsText="1"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:AA10"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:27" ht="15" x14ac:dyDescent="0.2">
+      <c r="A1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R1" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="S1" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="T1" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="V1" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="W1" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="X1" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="Y1" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="Z1" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="AA1" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="2" spans="1:27" ht="15" x14ac:dyDescent="0.2">
+      <c r="A2" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="L2" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="M2" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="N2" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="O2" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="P2" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q2" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="R2" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="S2" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="T2" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="U2" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="V2" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="W2" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="X2" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="Y2" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="Z2" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="AA2" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="3" spans="1:27" ht="15" x14ac:dyDescent="0.2">
+      <c r="A3" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="K3" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="L3" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="M3" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="N3" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="O3" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="P3" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q3" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="R3" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="S3" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="T3" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="U3" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="V3" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="W3" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="X3" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="Y3" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="Z3" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="AA3" s="4" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="4" spans="1:27" ht="15" x14ac:dyDescent="0.2">
+      <c r="A4" s="4">
+        <v>10</v>
+      </c>
+      <c r="B4" s="4">
+        <v>2</v>
+      </c>
+      <c r="C4" s="4">
+        <v>14</v>
+      </c>
+      <c r="D4" s="4">
+        <v>8</v>
+      </c>
+      <c r="E4" s="4">
+        <v>4</v>
+      </c>
+      <c r="F4" s="4">
+        <v>38</v>
+      </c>
+      <c r="G4" s="4">
+        <v>38</v>
+      </c>
+      <c r="H4" s="4">
+        <v>8</v>
+      </c>
+      <c r="I4" s="4">
+        <v>38</v>
+      </c>
+      <c r="J4" s="4">
+        <v>8</v>
+      </c>
+      <c r="K4" s="4">
+        <v>65</v>
+      </c>
+      <c r="L4" s="4">
+        <v>8</v>
+      </c>
+      <c r="M4" s="4">
+        <v>55</v>
+      </c>
+      <c r="N4" s="4">
+        <v>8</v>
+      </c>
+      <c r="O4" s="4">
+        <v>52</v>
+      </c>
+      <c r="P4" s="4">
+        <v>8</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>52</v>
+      </c>
+      <c r="R4" s="4">
+        <v>8</v>
+      </c>
+      <c r="S4" s="4">
+        <v>8</v>
+      </c>
+      <c r="T4" s="4">
+        <v>1</v>
+      </c>
+      <c r="U4" s="4">
+        <v>1</v>
+      </c>
+      <c r="V4" s="4">
+        <v>1</v>
+      </c>
+      <c r="W4" s="4">
+        <v>26</v>
+      </c>
+      <c r="X4" s="4">
+        <v>1</v>
+      </c>
+      <c r="Y4" s="4">
+        <v>10</v>
+      </c>
+      <c r="Z4" s="4">
+        <v>1</v>
+      </c>
+      <c r="AA4" s="4">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:27" ht="15" x14ac:dyDescent="0.2">
+      <c r="A5" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D5" s="1">
+        <v>1</v>
+      </c>
+      <c r="E5" s="1">
+        <v>1</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="H5" s="1">
+        <v>10046318</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="J5" s="1">
+        <v>10000059</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="L5" s="1">
+        <v>10027678</v>
+      </c>
+      <c r="M5" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="N5" s="1">
+        <v>10018012</v>
+      </c>
+      <c r="O5" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="P5" s="1">
+        <v>10017947</v>
+      </c>
+      <c r="Q5" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="R5" s="1">
+        <v>10017947</v>
+      </c>
+      <c r="S5" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="T5" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="U5" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="V5" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="W5" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="X5" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="Y5" s="1">
+        <v>43606</v>
+      </c>
+      <c r="Z5" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="AA5" s="1">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="6" spans="1:27" ht="15" x14ac:dyDescent="0.2">
+      <c r="A6" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D6" s="1">
+        <v>2</v>
+      </c>
+      <c r="E6" s="1">
+        <v>3</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="H6" s="1">
+        <v>10046318</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="J6" s="1">
+        <v>10000059</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="L6" s="1">
+        <v>10027678</v>
+      </c>
+      <c r="M6" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="N6" s="1">
+        <v>10018012</v>
+      </c>
+      <c r="O6" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="P6" s="1">
+        <v>10017947</v>
+      </c>
+      <c r="Q6" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="R6" s="1">
+        <v>10017947</v>
+      </c>
+      <c r="S6" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="T6" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="U6" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="V6" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="W6" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="X6" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="Y6" s="1">
+        <v>43631</v>
+      </c>
+      <c r="Z6" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="AA6" s="1">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="7" spans="1:27" ht="15" x14ac:dyDescent="0.2">
+      <c r="A7" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D7" s="1">
+        <v>3</v>
+      </c>
+      <c r="E7" s="1">
+        <v>12</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="H7" s="1">
+        <v>10003988</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="J7" s="1">
+        <v>10003988</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="L7" s="1">
+        <v>10068757</v>
+      </c>
+      <c r="M7" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="N7" s="1">
+        <v>10028393</v>
+      </c>
+      <c r="O7" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="P7" s="1">
+        <v>10028395</v>
+      </c>
+      <c r="Q7" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="R7" s="1">
+        <v>10028395</v>
+      </c>
+      <c r="S7" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="T7" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="U7" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="V7" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="W7" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="X7" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="Y7" s="1">
+        <v>43582</v>
+      </c>
+      <c r="Z7" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="AA7" s="1">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27" ht="15" x14ac:dyDescent="0.2">
+      <c r="A8" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D8" s="1">
+        <v>4</v>
+      </c>
+      <c r="E8" s="1">
+        <v>15</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="H8" s="1">
+        <v>10003988</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="J8" s="1">
+        <v>10003988</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="L8" s="1">
+        <v>10068757</v>
+      </c>
+      <c r="M8" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="N8" s="1">
+        <v>10028393</v>
+      </c>
+      <c r="O8" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="P8" s="1">
+        <v>10028395</v>
+      </c>
+      <c r="Q8" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="R8" s="1">
+        <v>10028395</v>
+      </c>
+      <c r="S8" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="T8" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="U8" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="V8" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="W8" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="X8" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="Y8" s="1">
+        <v>43584</v>
+      </c>
+      <c r="Z8" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="AA8" s="1">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" ht="15" x14ac:dyDescent="0.2">
+      <c r="A9" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D9" s="1">
+        <v>5</v>
+      </c>
+      <c r="E9" s="1">
+        <v>6</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="H9" s="1">
+        <v>10012735</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="J9" s="1">
+        <v>10012735</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="L9" s="1">
+        <v>10012736</v>
+      </c>
+      <c r="M9" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="N9" s="1">
+        <v>10017977</v>
+      </c>
+      <c r="O9" s="1">
+        <v>10017947</v>
+      </c>
+      <c r="P9" s="1">
+        <v>10017947</v>
+      </c>
+      <c r="Q9" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="R9" s="1">
+        <v>10017947</v>
+      </c>
+      <c r="S9" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="T9" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="U9" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="V9" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="W9" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="X9" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="Y9" s="1">
+        <v>43688</v>
+      </c>
+      <c r="Z9" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="AA9" s="1">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" ht="15" x14ac:dyDescent="0.2">
+      <c r="A10" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D10" s="1">
+        <v>6</v>
+      </c>
+      <c r="E10" s="1">
+        <v>14</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="H10" s="1">
+        <v>10019211</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="J10" s="1">
+        <v>10019211</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="L10" s="1">
+        <v>10019233</v>
+      </c>
+      <c r="M10" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="N10" s="1">
+        <v>10019231</v>
+      </c>
+      <c r="O10" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="P10" s="1">
+        <v>10029205</v>
+      </c>
+      <c r="Q10" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="R10" s="1">
+        <v>10029205</v>
+      </c>
+      <c r="S10" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="T10" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="U10" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="V10" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="W10" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="X10" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="Y10" s="1">
+        <v>43540</v>
+      </c>
+      <c r="Z10" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="AA10" s="1">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+  <ignoredErrors>
+    <ignoredError sqref="A1:AA6 A8:AA10 A7:S7 U7:AA7" numberStoredAsText="1"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{836014DE-782F-8A4E-836A-1683C63F2AAB}">
+  <dimension ref="A1:Z8"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A1" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="I1" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="J1" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="K1" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="L1" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="M1" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="N1" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="O1" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="P1" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q1" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="R1" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="S1" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="T1" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="U1" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="V1" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="W1" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="X1" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="Y1" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="Z1" s="6" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="2" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A2" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="L2" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="M2" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="N2" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="O2" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="P2" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q2" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="R2" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="S2" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="T2" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="U2" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="V2" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="W2" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="X2" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="Y2" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="Z2" s="4" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="3" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A3" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="K3" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="L3" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="M3" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="N3" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="O3" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="P3" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q3" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="R3" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="S3" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="T3" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="U3" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="V3" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="W3" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="X3" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="Y3" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="Z3" s="4" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="4" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A4" s="4">
+        <v>12</v>
+      </c>
+      <c r="B4" s="4">
+        <v>2</v>
+      </c>
+      <c r="C4" s="4">
+        <v>8</v>
+      </c>
+      <c r="D4" s="4">
+        <v>4</v>
+      </c>
+      <c r="E4" s="4">
+        <v>10</v>
+      </c>
+      <c r="F4" s="4">
+        <v>10</v>
+      </c>
+      <c r="G4" s="4">
+        <v>10</v>
+      </c>
+      <c r="H4" s="4">
+        <v>10</v>
+      </c>
+      <c r="I4" s="4">
+        <v>10</v>
+      </c>
+      <c r="J4" s="4">
+        <v>10</v>
+      </c>
+      <c r="K4" s="4">
+        <v>10</v>
+      </c>
+      <c r="L4" s="4">
+        <v>1</v>
+      </c>
+      <c r="M4" s="4">
+        <v>3</v>
+      </c>
+      <c r="N4" s="4">
+        <v>10</v>
+      </c>
+      <c r="O4" s="4">
+        <v>8</v>
+      </c>
+      <c r="P4" s="4">
+        <v>5</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>1</v>
+      </c>
+      <c r="R4" s="4">
+        <v>41</v>
+      </c>
+      <c r="S4" s="4">
+        <v>22</v>
+      </c>
+      <c r="T4" s="4">
+        <v>8</v>
+      </c>
+      <c r="U4" s="4">
+        <v>28</v>
+      </c>
+      <c r="V4" s="4">
+        <v>8</v>
+      </c>
+      <c r="W4" s="4">
+        <v>28</v>
+      </c>
+      <c r="X4" s="4">
+        <v>14</v>
+      </c>
+      <c r="Y4" s="4">
+        <v>200</v>
+      </c>
+      <c r="Z4" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A5" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="D5" s="7">
+        <v>1115</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="F5" s="8">
+        <v>43315</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="H5" s="8">
+        <v>43315</v>
+      </c>
+      <c r="I5" s="8">
+        <v>43216</v>
+      </c>
+      <c r="J5" s="8">
+        <v>43334</v>
+      </c>
+      <c r="K5" s="8">
+        <v>43334</v>
+      </c>
+      <c r="L5" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="M5" s="7">
+        <v>701</v>
+      </c>
+      <c r="N5" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="O5" s="7">
+        <v>70</v>
+      </c>
+      <c r="P5" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="Q5" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="R5" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="S5" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="T5" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="U5" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="V5" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="W5" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="X5" s="7"/>
+      <c r="Y5" s="7"/>
+      <c r="Z5" s="7" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A6" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="D6" s="7">
+        <v>1211</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="F6" s="8">
+        <v>43410</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="H6" s="8">
+        <v>43410</v>
+      </c>
+      <c r="I6" s="8">
+        <v>43227</v>
+      </c>
+      <c r="J6" s="8">
+        <v>43500</v>
+      </c>
+      <c r="K6" s="8">
+        <v>43500</v>
+      </c>
+      <c r="L6" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="M6" s="7">
+        <v>701</v>
+      </c>
+      <c r="N6" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="O6" s="7">
+        <v>78</v>
+      </c>
+      <c r="P6" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="Q6" s="7"/>
+      <c r="R6" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="S6" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="T6" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="U6" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="V6" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="W6" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="X6" s="7"/>
+      <c r="Y6" s="7"/>
+      <c r="Z6" s="7" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A7" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="D7" s="7">
+        <v>1302</v>
+      </c>
+      <c r="E7" s="8">
+        <v>38733</v>
+      </c>
+      <c r="F7" s="8">
+        <v>38795</v>
+      </c>
+      <c r="G7" s="8">
+        <v>38733</v>
+      </c>
+      <c r="H7" s="8">
+        <v>38795</v>
+      </c>
+      <c r="I7" s="8">
+        <v>38719</v>
+      </c>
+      <c r="J7" s="8">
+        <v>38795</v>
+      </c>
+      <c r="K7" s="7"/>
+      <c r="L7" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="M7" s="7">
+        <v>701</v>
+      </c>
+      <c r="N7" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="O7" s="7">
+        <v>74</v>
+      </c>
+      <c r="P7" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="Q7" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="R7" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="S7" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="T7" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="U7" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="V7" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="W7" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="X7" s="7"/>
+      <c r="Y7" s="7"/>
+      <c r="Z7" s="7" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A8" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="D8" s="7">
+        <v>1402</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="H8" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="I8" s="8">
+        <v>43278</v>
+      </c>
+      <c r="J8" s="8">
+        <v>43445</v>
+      </c>
+      <c r="K8" s="7"/>
+      <c r="L8" s="7"/>
+      <c r="M8" s="7">
+        <v>701</v>
+      </c>
+      <c r="N8" s="7" t="s">
+        <v>168</v>
+      </c>
+      <c r="O8" s="7">
+        <v>68</v>
+      </c>
+      <c r="P8" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="Q8" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="R8" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="S8" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="T8" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="U8" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="V8" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="W8" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="X8" s="7"/>
+      <c r="Y8" s="7"/>
+      <c r="Z8" s="7" t="s">
+        <v>171</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/rules/NEW-RULE/positive/01/data/new-rule-positive-01.xlsx
+++ b/rules/NEW-RULE/positive/01/data/new-rule-positive-01.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/enrico/Work/core-contributor/rules/NEW-RULE/positive/01/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{380B7BE0-9E34-904A-9921-03F3B6D9DF60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF2B8CE6-9B8F-2548-A45B-F38E74D80E6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30240" yWindow="-4560" windowWidth="51200" windowHeight="28800" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30240" yWindow="-7000" windowWidth="51200" windowHeight="28800" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Library" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="409" uniqueCount="204">
   <si>
     <t>Product</t>
   </si>
@@ -631,6 +631,9 @@
   </si>
   <si>
     <t>NA</t>
+  </si>
+  <si>
+    <t>AD</t>
   </si>
 </sst>
 </file>
@@ -722,7 +725,7 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1079,7 +1082,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:K56"/>
+  <dimension ref="A1:K58"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -1618,7 +1621,9 @@
       <c r="C21" s="4">
         <v>1</v>
       </c>
-      <c r="D21" s="4"/>
+      <c r="D21" s="4" t="s">
+        <v>120</v>
+      </c>
       <c r="E21" s="4" t="s">
         <v>88</v>
       </c>
@@ -1639,94 +1644,107 @@
         <v>41</v>
       </c>
     </row>
-    <row r="22" spans="1:11" ht="80" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:11" ht="48" x14ac:dyDescent="0.2">
       <c r="A22" s="4" t="s">
         <v>31</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="C22" s="4">
-        <v>1</v>
+      <c r="C22" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>122</v>
       </c>
       <c r="E22" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="G22" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="H22" s="4"/>
+      <c r="I22" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="J22" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="K22" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" ht="80" x14ac:dyDescent="0.2">
+      <c r="A23" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C23" s="4">
+        <v>1</v>
+      </c>
+      <c r="D23">
+        <v>1</v>
+      </c>
+      <c r="E23" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="F22" s="4" t="s">
+      <c r="F23" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="G22" s="4" t="s">
+      <c r="G23" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="H23" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="I23" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="J23" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="K23" s="4" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" ht="80" x14ac:dyDescent="0.2">
+      <c r="A24" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="D24">
+        <v>2</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="G24" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="H22" s="5" t="s">
-        <v>202</v>
-      </c>
-      <c r="I22" s="4" t="s">
+      <c r="H24" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="I24" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="J22" s="4" t="s">
+      <c r="J24" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="K22" s="4" t="s">
+      <c r="K24" s="4" t="s">
         <v>95</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" ht="32" x14ac:dyDescent="0.2">
-      <c r="A23" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B23" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C23" s="4">
-        <v>1</v>
-      </c>
-      <c r="E23" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="F23" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="G23" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="I23" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="J23" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="K23" s="4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" ht="32" x14ac:dyDescent="0.2">
-      <c r="A24" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B24" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C24" s="4">
-        <v>1</v>
-      </c>
-      <c r="E24" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="F24" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="G24" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="I24" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="J24" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="K24" s="4" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="25" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -1740,85 +1758,97 @@
         <v>1</v>
       </c>
       <c r="E25" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="G25" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="I25" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="J25" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="K25" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" ht="32" x14ac:dyDescent="0.2">
+      <c r="A26" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C26" s="4">
+        <v>1</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F26" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="G26" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="I26" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="J26" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="K26" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" ht="32" x14ac:dyDescent="0.2">
+      <c r="A27" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C27" s="4">
+        <v>1</v>
+      </c>
+      <c r="E27" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="F25" s="4" t="s">
+      <c r="F27" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="G25" s="4" t="s">
+      <c r="G27" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="J25" s="4" t="s">
+      <c r="J27" s="4" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="26" spans="1:11" ht="48" x14ac:dyDescent="0.2">
-      <c r="A26" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B26" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C26" s="4">
-        <v>1</v>
-      </c>
-      <c r="E26" s="4" t="s">
+    <row r="28" spans="1:11" ht="48" x14ac:dyDescent="0.2">
+      <c r="A28" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C28" s="4">
+        <v>1</v>
+      </c>
+      <c r="E28" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="F26" s="4" t="s">
+      <c r="F28" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="G26" s="4" t="s">
+      <c r="G28" s="4" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="27" spans="1:11" ht="112" x14ac:dyDescent="0.2">
-      <c r="A27" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B27" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C27" s="4">
-        <v>1</v>
-      </c>
-      <c r="D27" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="E27" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="F27" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="G27" s="4" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11" ht="112" x14ac:dyDescent="0.2">
-      <c r="A28" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B28" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C28" s="4">
-        <v>2</v>
-      </c>
-      <c r="D28" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="E28" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="F28" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="G28" s="4" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:11" ht="112" x14ac:dyDescent="0.2">
       <c r="A29" s="4" t="s">
         <v>31</v>
       </c>
@@ -1832,16 +1862,16 @@
         <v>109</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11" ht="365" x14ac:dyDescent="0.2">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" ht="112" x14ac:dyDescent="0.2">
       <c r="A30" s="4" t="s">
         <v>31</v>
       </c>
@@ -1852,27 +1882,27 @@
         <v>2</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11" ht="335" x14ac:dyDescent="0.2">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A31" s="4" t="s">
         <v>31</v>
       </c>
       <c r="B31" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="C31" s="4" t="s">
-        <v>70</v>
+      <c r="C31" s="4">
+        <v>1</v>
       </c>
       <c r="D31" s="4" t="s">
         <v>109</v>
@@ -1884,21 +1914,21 @@
         <v>116</v>
       </c>
       <c r="G31" s="4" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11" ht="128" x14ac:dyDescent="0.2">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" ht="365" x14ac:dyDescent="0.2">
       <c r="A32" s="4" t="s">
         <v>31</v>
       </c>
       <c r="B32" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="C32" s="4" t="s">
-        <v>120</v>
+      <c r="C32" s="4">
+        <v>2</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="E32" s="4" t="s">
         <v>115</v>
@@ -1907,10 +1937,10 @@
         <v>116</v>
       </c>
       <c r="G32" s="4" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11" ht="112" x14ac:dyDescent="0.2">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" ht="335" x14ac:dyDescent="0.2">
       <c r="A33" s="4" t="s">
         <v>31</v>
       </c>
@@ -1918,10 +1948,10 @@
         <v>32</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>122</v>
+        <v>70</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="E33" s="4" t="s">
         <v>115</v>
@@ -1930,128 +1960,128 @@
         <v>116</v>
       </c>
       <c r="G33" s="4" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" ht="128" x14ac:dyDescent="0.2">
+      <c r="A34" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="E34" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="F34" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="G34" s="4" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" ht="112" x14ac:dyDescent="0.2">
+      <c r="A35" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="E35" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="F35" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="G35" s="4" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="34" spans="1:11" ht="64" x14ac:dyDescent="0.2">
-      <c r="A34" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B34" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C34" s="4">
-        <v>1</v>
-      </c>
-      <c r="E34" s="4" t="s">
+    <row r="36" spans="1:11" ht="64" x14ac:dyDescent="0.2">
+      <c r="A36" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C36" s="4">
+        <v>1</v>
+      </c>
+      <c r="E36" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="F34" s="4" t="s">
+      <c r="F36" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="G34" s="4" t="s">
+      <c r="G36" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="I34" s="4" t="s">
+      <c r="I36" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="J34" s="4" t="s">
+      <c r="J36" s="4" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="35" spans="1:11" ht="64" x14ac:dyDescent="0.2">
-      <c r="A35" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B35" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C35" s="4">
-        <v>1</v>
-      </c>
-      <c r="E35" s="4" t="s">
+    <row r="37" spans="1:11" ht="64" x14ac:dyDescent="0.2">
+      <c r="A37" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C37" s="4">
+        <v>1</v>
+      </c>
+      <c r="E37" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="F35" s="4" t="s">
+      <c r="F37" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="G35" s="4" t="s">
+      <c r="G37" s="4" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="36" spans="1:11" ht="48" x14ac:dyDescent="0.2">
-      <c r="A36" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B36" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C36" s="4">
-        <v>1</v>
-      </c>
-      <c r="E36" s="4" t="s">
+    <row r="38" spans="1:11" ht="48" x14ac:dyDescent="0.2">
+      <c r="A38" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C38" s="4">
+        <v>1</v>
+      </c>
+      <c r="E38" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="F36" s="4" t="s">
+      <c r="F38" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="G36" s="4" t="s">
+      <c r="G38" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="I36" s="4" t="s">
+      <c r="I38" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="J36" s="4" t="s">
+      <c r="J38" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="K36" s="4" t="s">
+      <c r="K38" s="4" t="s">
         <v>41</v>
-      </c>
-    </row>
-    <row r="37" spans="1:11" ht="48" x14ac:dyDescent="0.2">
-      <c r="A37" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B37" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C37" s="4">
-        <v>1</v>
-      </c>
-      <c r="E37" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="F37" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="G37" s="4" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="38" spans="1:11" ht="32" x14ac:dyDescent="0.2">
-      <c r="A38" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B38" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C38" s="4">
-        <v>1</v>
-      </c>
-      <c r="E38" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="F38" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="G38" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="I38" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="J38" s="4" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="39" spans="1:11" ht="48" x14ac:dyDescent="0.2">
@@ -2065,22 +2095,13 @@
         <v>1</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="G39" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="I39" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="J39" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="K39" s="4" t="s">
-        <v>41</v>
+        <v>136</v>
       </c>
     </row>
     <row r="40" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -2094,16 +2115,22 @@
         <v>1</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="G40" s="4" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="41" spans="1:11" ht="32" x14ac:dyDescent="0.2">
+        <v>139</v>
+      </c>
+      <c r="I40" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="J40" s="4" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" ht="48" x14ac:dyDescent="0.2">
       <c r="A41" s="4" t="s">
         <v>31</v>
       </c>
@@ -2114,13 +2141,22 @@
         <v>1</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="G41" s="4" t="s">
-        <v>150</v>
+        <v>143</v>
+      </c>
+      <c r="I41" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="J41" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="K41" s="4" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="42" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -2134,108 +2170,105 @@
         <v>1</v>
       </c>
       <c r="E42" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="F42" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="G42" s="4" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" ht="32" x14ac:dyDescent="0.2">
+      <c r="A43" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C43" s="4">
+        <v>1</v>
+      </c>
+      <c r="E43" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="F43" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="G43" s="4" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" ht="32" x14ac:dyDescent="0.2">
+      <c r="A44" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C44" s="4">
+        <v>1</v>
+      </c>
+      <c r="E44" s="4" t="s">
         <v>151</v>
       </c>
-      <c r="F42" s="4" t="s">
+      <c r="F44" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="G42" s="4" t="s">
+      <c r="G44" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="J42" s="4" t="s">
+      <c r="J44" s="4" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="43" spans="1:11" ht="48" x14ac:dyDescent="0.2">
-      <c r="A43" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B43" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C43" s="4">
-        <v>1</v>
-      </c>
-      <c r="E43" s="4" t="s">
+    <row r="45" spans="1:11" ht="48" x14ac:dyDescent="0.2">
+      <c r="A45" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C45" s="4">
+        <v>1</v>
+      </c>
+      <c r="E45" s="4" t="s">
         <v>154</v>
       </c>
-      <c r="F43" s="4" t="s">
+      <c r="F45" s="4" t="s">
         <v>155</v>
       </c>
-      <c r="G43" s="4" t="s">
+      <c r="G45" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="I43" s="4" t="s">
+      <c r="I45" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="J43" s="4" t="s">
+      <c r="J45" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="K43" s="4" t="s">
+      <c r="K45" s="4" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="44" spans="1:11" ht="96" x14ac:dyDescent="0.2">
-      <c r="A44" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B44" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C44" s="4">
-        <v>1</v>
-      </c>
-      <c r="E44" s="4" t="s">
+    <row r="46" spans="1:11" ht="96" x14ac:dyDescent="0.2">
+      <c r="A46" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C46" s="4">
+        <v>1</v>
+      </c>
+      <c r="E46" s="4" t="s">
         <v>158</v>
       </c>
-      <c r="F44" s="4" t="s">
+      <c r="F46" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="G44" s="4" t="s">
+      <c r="G46" s="4" t="s">
         <v>160</v>
-      </c>
-    </row>
-    <row r="45" spans="1:11" ht="32" x14ac:dyDescent="0.2">
-      <c r="A45" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B45" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C45" s="4">
-        <v>1</v>
-      </c>
-      <c r="E45" s="4" t="s">
-        <v>161</v>
-      </c>
-      <c r="F45" s="4" t="s">
-        <v>162</v>
-      </c>
-      <c r="G45" s="4" t="s">
-        <v>163</v>
-      </c>
-      <c r="J45" s="4" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="46" spans="1:11" ht="48" x14ac:dyDescent="0.2">
-      <c r="A46" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B46" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C46" s="4">
-        <v>1</v>
-      </c>
-      <c r="E46" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="F46" s="4" t="s">
-        <v>165</v>
-      </c>
-      <c r="G46" s="4" t="s">
-        <v>166</v>
       </c>
     </row>
     <row r="47" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -2249,22 +2282,16 @@
         <v>1</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="G47" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="I47" s="4" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="J47" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="K47" s="4" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
     </row>
     <row r="48" spans="1:11" ht="48" x14ac:dyDescent="0.2">
@@ -2278,22 +2305,13 @@
         <v>1</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="G48" s="4" t="s">
-        <v>173</v>
-      </c>
-      <c r="I48" s="4" t="s">
-        <v>174</v>
-      </c>
-      <c r="J48" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="K48" s="4" t="s">
-        <v>41</v>
+        <v>166</v>
       </c>
     </row>
     <row r="49" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -2307,16 +2325,16 @@
         <v>1</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="G49" s="4" t="s">
-        <v>63</v>
+        <v>169</v>
       </c>
       <c r="I49" s="4" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="J49" s="4" t="s">
         <v>40</v>
@@ -2325,7 +2343,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="50" spans="1:11" ht="112" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:11" ht="48" x14ac:dyDescent="0.2">
       <c r="A50" s="4" t="s">
         <v>31</v>
       </c>
@@ -2336,20 +2354,25 @@
         <v>1</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="G50" s="4" t="s">
-        <v>180</v>
-      </c>
-      <c r="H50" s="4"/>
-      <c r="I50" s="4"/>
-      <c r="J50" s="4"/>
-      <c r="K50" s="4"/>
-    </row>
-    <row r="51" spans="1:11" ht="48" x14ac:dyDescent="0.2">
+        <v>173</v>
+      </c>
+      <c r="I50" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="J50" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="K50" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" ht="32" x14ac:dyDescent="0.2">
       <c r="A51" s="4" t="s">
         <v>31</v>
       </c>
@@ -2360,16 +2383,16 @@
         <v>1</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="G51" s="4" t="s">
-        <v>183</v>
+        <v>63</v>
       </c>
       <c r="I51" s="4" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="J51" s="4" t="s">
         <v>40</v>
@@ -2378,7 +2401,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="52" spans="1:11" ht="160" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:11" ht="112" x14ac:dyDescent="0.2">
       <c r="A52" s="4" t="s">
         <v>31</v>
       </c>
@@ -2389,16 +2412,20 @@
         <v>1</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="G52" s="4" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="53" spans="1:11" ht="64" x14ac:dyDescent="0.2">
+        <v>180</v>
+      </c>
+      <c r="H52" s="4"/>
+      <c r="I52" s="4"/>
+      <c r="J52" s="4"/>
+      <c r="K52" s="4"/>
+    </row>
+    <row r="53" spans="1:11" ht="48" x14ac:dyDescent="0.2">
       <c r="A53" s="4" t="s">
         <v>31</v>
       </c>
@@ -2409,16 +2436,16 @@
         <v>1</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="G53" s="4" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="I53" s="4" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="J53" s="4" t="s">
         <v>40</v>
@@ -2427,7 +2454,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="54" spans="1:11" ht="96" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:11" ht="160" x14ac:dyDescent="0.2">
       <c r="A54" s="4" t="s">
         <v>31</v>
       </c>
@@ -2438,22 +2465,16 @@
         <v>1</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="G54" s="4" t="s">
-        <v>194</v>
-      </c>
-      <c r="I54" s="4" t="s">
-        <v>195</v>
-      </c>
-      <c r="J54" s="4" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="55" spans="1:11" ht="32" x14ac:dyDescent="0.2">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11" ht="64" x14ac:dyDescent="0.2">
       <c r="A55" s="4" t="s">
         <v>31</v>
       </c>
@@ -2464,16 +2485,16 @@
         <v>1</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>197</v>
+        <v>188</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="G55" s="4" t="s">
-        <v>113</v>
+        <v>190</v>
       </c>
       <c r="I55" s="4" t="s">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="J55" s="4" t="s">
         <v>40</v>
@@ -2482,32 +2503,87 @@
         <v>41</v>
       </c>
     </row>
-    <row r="56" spans="1:11" ht="32" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:11" ht="96" x14ac:dyDescent="0.2">
       <c r="A56" s="4" t="s">
         <v>31</v>
       </c>
       <c r="B56" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="C56" s="4" t="s">
+      <c r="C56" s="4">
+        <v>1</v>
+      </c>
+      <c r="E56" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="F56" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="G56" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="I56" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="J56" s="4" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11" ht="32" x14ac:dyDescent="0.2">
+      <c r="A57" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B57" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C57" s="4">
+        <v>1</v>
+      </c>
+      <c r="E57" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="F57" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="G57" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="I57" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="J57" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="K57" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11" ht="32" x14ac:dyDescent="0.2">
+      <c r="A58" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B58" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C58" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="E56" s="4" t="s">
+      <c r="E58" s="4" t="s">
         <v>197</v>
       </c>
-      <c r="F56" s="4" t="s">
+      <c r="F58" s="4" t="s">
         <v>198</v>
       </c>
-      <c r="G56" s="4" t="s">
+      <c r="G58" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="I56" s="4" t="s">
+      <c r="I58" s="4" t="s">
         <v>200</v>
       </c>
-      <c r="J56" s="4" t="s">
+      <c r="J58" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="K56" s="4" t="s">
+      <c r="K58" s="4" t="s">
         <v>41</v>
       </c>
     </row>

--- a/rules/NEW-RULE/positive/01/data/new-rule-positive-01.xlsx
+++ b/rules/NEW-RULE/positive/01/data/new-rule-positive-01.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/enrico/Work/core-contributor/rules/NEW-RULE/positive/01/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1425DCBB-1E88-044E-8F1D-52497450C9B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FA28602-A2A3-624D-912A-14B91E9200A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30240" yWindow="-4560" windowWidth="51200" windowHeight="28800" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30240" yWindow="-7000" windowWidth="51200" windowHeight="28800" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Library" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="402" uniqueCount="206">
   <si>
     <t>Product</t>
   </si>
@@ -631,6 +631,15 @@
   </si>
   <si>
     <t>NA</t>
+  </si>
+  <si>
+    <t>STYPE1</t>
+  </si>
+  <si>
+    <t>STYPE2</t>
+  </si>
+  <si>
+    <t>OTHERTYPE</t>
   </si>
 </sst>
 </file>
@@ -1079,7 +1088,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:K56"/>
+  <dimension ref="A1:K57"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -1684,6 +1693,9 @@
       <c r="C23" s="4">
         <v>1</v>
       </c>
+      <c r="D23" t="s">
+        <v>203</v>
+      </c>
       <c r="E23" s="4" t="s">
         <v>96</v>
       </c>
@@ -1713,6 +1725,9 @@
       <c r="C24" s="4">
         <v>1</v>
       </c>
+      <c r="D24" t="s">
+        <v>203</v>
+      </c>
       <c r="E24" s="4" t="s">
         <v>100</v>
       </c>
@@ -2251,6 +2266,9 @@
       <c r="C47" s="4">
         <v>1</v>
       </c>
+      <c r="D47" t="s">
+        <v>203</v>
+      </c>
       <c r="E47" s="4" t="s">
         <v>167</v>
       </c>
@@ -2270,27 +2288,30 @@
         <v>41</v>
       </c>
     </row>
-    <row r="48" spans="1:11" ht="48" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:11" ht="32" x14ac:dyDescent="0.2">
       <c r="A48" s="4" t="s">
         <v>31</v>
       </c>
       <c r="B48" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="C48" s="4">
-        <v>1</v>
+      <c r="C48" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="D48" t="s">
+        <v>204</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="G48" s="4" t="s">
-        <v>173</v>
+        <v>205</v>
       </c>
       <c r="I48" s="4" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="J48" s="4" t="s">
         <v>40</v>
@@ -2299,7 +2320,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="49" spans="1:11" ht="32" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:11" ht="48" x14ac:dyDescent="0.2">
       <c r="A49" s="4" t="s">
         <v>31</v>
       </c>
@@ -2310,16 +2331,16 @@
         <v>1</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="G49" s="4" t="s">
-        <v>63</v>
+        <v>173</v>
       </c>
       <c r="I49" s="4" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="J49" s="4" t="s">
         <v>40</v>
@@ -2328,7 +2349,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="50" spans="1:11" ht="112" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:11" ht="32" x14ac:dyDescent="0.2">
       <c r="A50" s="4" t="s">
         <v>31</v>
       </c>
@@ -2339,150 +2360,150 @@
         <v>1</v>
       </c>
       <c r="E50" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="F50" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="G50" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="I50" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="J50" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="K50" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" ht="112" x14ac:dyDescent="0.2">
+      <c r="A51" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B51" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C51" s="4">
+        <v>1</v>
+      </c>
+      <c r="E51" s="4" t="s">
         <v>178</v>
       </c>
-      <c r="F50" s="4" t="s">
+      <c r="F51" s="4" t="s">
         <v>179</v>
       </c>
-      <c r="G50" s="4" t="s">
+      <c r="G51" s="4" t="s">
         <v>180</v>
       </c>
-      <c r="H50" s="4"/>
-      <c r="I50" s="4"/>
-      <c r="J50" s="4"/>
-      <c r="K50" s="4"/>
-    </row>
-    <row r="51" spans="1:11" ht="48" x14ac:dyDescent="0.2">
-      <c r="A51" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B51" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C51" s="4">
-        <v>1</v>
-      </c>
-      <c r="E51" s="4" t="s">
+      <c r="H51" s="4"/>
+      <c r="I51" s="4"/>
+      <c r="J51" s="4"/>
+      <c r="K51" s="4"/>
+    </row>
+    <row r="52" spans="1:11" ht="48" x14ac:dyDescent="0.2">
+      <c r="A52" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C52" s="4">
+        <v>1</v>
+      </c>
+      <c r="E52" s="4" t="s">
         <v>181</v>
       </c>
-      <c r="F51" s="4" t="s">
+      <c r="F52" s="4" t="s">
         <v>182</v>
       </c>
-      <c r="G51" s="4" t="s">
+      <c r="G52" s="4" t="s">
         <v>183</v>
       </c>
-      <c r="I51" s="4" t="s">
+      <c r="I52" s="4" t="s">
         <v>184</v>
       </c>
-      <c r="J51" s="4" t="s">
+      <c r="J52" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="K51" s="4" t="s">
+      <c r="K52" s="4" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="52" spans="1:11" ht="160" x14ac:dyDescent="0.2">
-      <c r="A52" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B52" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C52" s="4">
-        <v>1</v>
-      </c>
-      <c r="E52" s="4" t="s">
+    <row r="53" spans="1:11" ht="160" x14ac:dyDescent="0.2">
+      <c r="A53" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B53" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C53" s="4">
+        <v>1</v>
+      </c>
+      <c r="E53" s="4" t="s">
         <v>185</v>
       </c>
-      <c r="F52" s="4" t="s">
+      <c r="F53" s="4" t="s">
         <v>186</v>
       </c>
-      <c r="G52" s="4" t="s">
+      <c r="G53" s="4" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="53" spans="1:11" ht="64" x14ac:dyDescent="0.2">
-      <c r="A53" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B53" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C53" s="4">
-        <v>1</v>
-      </c>
-      <c r="E53" s="4" t="s">
+    <row r="54" spans="1:11" ht="64" x14ac:dyDescent="0.2">
+      <c r="A54" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B54" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C54" s="4">
+        <v>1</v>
+      </c>
+      <c r="E54" s="4" t="s">
         <v>188</v>
       </c>
-      <c r="F53" s="4" t="s">
+      <c r="F54" s="4" t="s">
         <v>189</v>
       </c>
-      <c r="G53" s="4" t="s">
+      <c r="G54" s="4" t="s">
         <v>190</v>
       </c>
-      <c r="I53" s="4" t="s">
+      <c r="I54" s="4" t="s">
         <v>191</v>
       </c>
-      <c r="J53" s="4" t="s">
+      <c r="J54" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="K53" s="4" t="s">
+      <c r="K54" s="4" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="54" spans="1:11" ht="96" x14ac:dyDescent="0.2">
-      <c r="A54" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B54" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C54" s="4">
-        <v>1</v>
-      </c>
-      <c r="E54" s="4" t="s">
+    <row r="55" spans="1:11" ht="96" x14ac:dyDescent="0.2">
+      <c r="A55" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B55" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C55" s="4">
+        <v>1</v>
+      </c>
+      <c r="E55" s="4" t="s">
         <v>192</v>
       </c>
-      <c r="F54" s="4" t="s">
+      <c r="F55" s="4" t="s">
         <v>193</v>
       </c>
-      <c r="G54" s="4" t="s">
+      <c r="G55" s="4" t="s">
         <v>194</v>
       </c>
-      <c r="I54" s="4" t="s">
+      <c r="I55" s="4" t="s">
         <v>195</v>
       </c>
-      <c r="J54" s="4" t="s">
+      <c r="J55" s="4" t="s">
         <v>196</v>
-      </c>
-    </row>
-    <row r="55" spans="1:11" ht="32" x14ac:dyDescent="0.2">
-      <c r="A55" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B55" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C55" s="4">
-        <v>1</v>
-      </c>
-      <c r="E55" s="4" t="s">
-        <v>197</v>
-      </c>
-      <c r="F55" s="4" t="s">
-        <v>198</v>
-      </c>
-      <c r="G55" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="I55" s="4" t="s">
-        <v>199</v>
-      </c>
-      <c r="J55" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="K55" s="4" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="56" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -2492,8 +2513,8 @@
       <c r="B56" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="C56" s="4" t="s">
-        <v>120</v>
+      <c r="C56" s="4">
+        <v>1</v>
       </c>
       <c r="E56" s="4" t="s">
         <v>197</v>
@@ -2502,15 +2523,44 @@
         <v>198</v>
       </c>
       <c r="G56" s="4" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="I56" s="4" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="J56" s="4" t="s">
         <v>40</v>
       </c>
       <c r="K56" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11" ht="32" x14ac:dyDescent="0.2">
+      <c r="A57" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B57" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C57" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="E57" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="F57" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="G57" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="I57" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="J57" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="K57" s="4" t="s">
         <v>41</v>
       </c>
     </row>

--- a/rules/NEW-RULE/positive/01/data/new-rule-positive-01.xlsx
+++ b/rules/NEW-RULE/positive/01/data/new-rule-positive-01.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/enrico/Work/core-contributor/rules/NEW-RULE/positive/01/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1425DCBB-1E88-044E-8F1D-52497450C9B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93DB8275-93A4-0C46-8DAB-BB1EF6883CC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30240" yWindow="-4560" windowWidth="51200" windowHeight="28800" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30240" yWindow="-7000" windowWidth="51200" windowHeight="28800" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Library" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="207">
   <si>
     <t>Product</t>
   </si>
@@ -631,6 +631,18 @@
   </si>
   <si>
     <t>NA</t>
+  </si>
+  <si>
+    <t>STYPE1</t>
+  </si>
+  <si>
+    <t>STYPE2</t>
+  </si>
+  <si>
+    <t>NON-INT</t>
+  </si>
+  <si>
+    <t>C98389</t>
   </si>
 </sst>
 </file>
@@ -1079,7 +1091,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:K56"/>
+  <dimension ref="A1:K57"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -2251,6 +2263,9 @@
       <c r="C47" s="4">
         <v>1</v>
       </c>
+      <c r="D47" t="s">
+        <v>203</v>
+      </c>
       <c r="E47" s="4" t="s">
         <v>167</v>
       </c>
@@ -2270,7 +2285,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="48" spans="1:11" ht="48" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:11" ht="32" x14ac:dyDescent="0.2">
       <c r="A48" s="4" t="s">
         <v>31</v>
       </c>
@@ -2280,17 +2295,20 @@
       <c r="C48" s="4">
         <v>1</v>
       </c>
+      <c r="D48" t="s">
+        <v>204</v>
+      </c>
       <c r="E48" s="4" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="G48" s="4" t="s">
-        <v>173</v>
+        <v>205</v>
       </c>
       <c r="I48" s="4" t="s">
-        <v>174</v>
+        <v>206</v>
       </c>
       <c r="J48" s="4" t="s">
         <v>40</v>
@@ -2299,7 +2317,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="49" spans="1:11" ht="32" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:11" ht="48" x14ac:dyDescent="0.2">
       <c r="A49" s="4" t="s">
         <v>31</v>
       </c>
@@ -2310,16 +2328,16 @@
         <v>1</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="G49" s="4" t="s">
-        <v>63</v>
+        <v>173</v>
       </c>
       <c r="I49" s="4" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="J49" s="4" t="s">
         <v>40</v>
@@ -2328,7 +2346,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="50" spans="1:11" ht="112" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:11" ht="32" x14ac:dyDescent="0.2">
       <c r="A50" s="4" t="s">
         <v>31</v>
       </c>
@@ -2339,150 +2357,153 @@
         <v>1</v>
       </c>
       <c r="E50" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="F50" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="G50" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="I50" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="J50" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="K50" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" ht="112" x14ac:dyDescent="0.2">
+      <c r="A51" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B51" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C51" s="4">
+        <v>1</v>
+      </c>
+      <c r="E51" s="4" t="s">
         <v>178</v>
       </c>
-      <c r="F50" s="4" t="s">
+      <c r="F51" s="4" t="s">
         <v>179</v>
       </c>
-      <c r="G50" s="4" t="s">
+      <c r="G51" s="4" t="s">
         <v>180</v>
       </c>
-      <c r="H50" s="4"/>
-      <c r="I50" s="4"/>
-      <c r="J50" s="4"/>
-      <c r="K50" s="4"/>
-    </row>
-    <row r="51" spans="1:11" ht="48" x14ac:dyDescent="0.2">
-      <c r="A51" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B51" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C51" s="4">
-        <v>1</v>
-      </c>
-      <c r="E51" s="4" t="s">
+      <c r="H51" s="4"/>
+      <c r="I51" s="4"/>
+      <c r="J51" s="4"/>
+      <c r="K51" s="4"/>
+    </row>
+    <row r="52" spans="1:11" ht="48" x14ac:dyDescent="0.2">
+      <c r="A52" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C52" s="4">
+        <v>1</v>
+      </c>
+      <c r="E52" s="4" t="s">
         <v>181</v>
       </c>
-      <c r="F51" s="4" t="s">
+      <c r="F52" s="4" t="s">
         <v>182</v>
       </c>
-      <c r="G51" s="4" t="s">
+      <c r="G52" s="4" t="s">
         <v>183</v>
       </c>
-      <c r="I51" s="4" t="s">
+      <c r="I52" s="4" t="s">
         <v>184</v>
       </c>
-      <c r="J51" s="4" t="s">
+      <c r="J52" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="K51" s="4" t="s">
+      <c r="K52" s="4" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="52" spans="1:11" ht="160" x14ac:dyDescent="0.2">
-      <c r="A52" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B52" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C52" s="4">
-        <v>1</v>
-      </c>
-      <c r="E52" s="4" t="s">
+    <row r="53" spans="1:11" ht="160" x14ac:dyDescent="0.2">
+      <c r="A53" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B53" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C53" s="4">
+        <v>1</v>
+      </c>
+      <c r="E53" s="4" t="s">
         <v>185</v>
       </c>
-      <c r="F52" s="4" t="s">
+      <c r="F53" s="4" t="s">
         <v>186</v>
       </c>
-      <c r="G52" s="4" t="s">
+      <c r="G53" s="4" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="53" spans="1:11" ht="64" x14ac:dyDescent="0.2">
-      <c r="A53" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B53" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C53" s="4">
-        <v>1</v>
-      </c>
-      <c r="E53" s="4" t="s">
+    <row r="54" spans="1:11" ht="64" x14ac:dyDescent="0.2">
+      <c r="A54" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B54" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C54" s="4">
+        <v>1</v>
+      </c>
+      <c r="E54" s="4" t="s">
         <v>188</v>
       </c>
-      <c r="F53" s="4" t="s">
+      <c r="F54" s="4" t="s">
         <v>189</v>
       </c>
-      <c r="G53" s="4" t="s">
+      <c r="G54" s="4" t="s">
         <v>190</v>
       </c>
-      <c r="I53" s="4" t="s">
+      <c r="I54" s="4" t="s">
         <v>191</v>
       </c>
-      <c r="J53" s="4" t="s">
+      <c r="J54" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="K53" s="4" t="s">
+      <c r="K54" s="4" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="54" spans="1:11" ht="96" x14ac:dyDescent="0.2">
-      <c r="A54" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B54" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C54" s="4">
-        <v>1</v>
-      </c>
-      <c r="E54" s="4" t="s">
+    <row r="55" spans="1:11" ht="96" x14ac:dyDescent="0.2">
+      <c r="A55" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B55" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C55" s="4">
+        <v>1</v>
+      </c>
+      <c r="D55" t="s">
+        <v>203</v>
+      </c>
+      <c r="E55" s="4" t="s">
         <v>192</v>
       </c>
-      <c r="F54" s="4" t="s">
+      <c r="F55" s="4" t="s">
         <v>193</v>
       </c>
-      <c r="G54" s="4" t="s">
+      <c r="G55" s="4" t="s">
         <v>194</v>
       </c>
-      <c r="I54" s="4" t="s">
+      <c r="I55" s="4" t="s">
         <v>195</v>
       </c>
-      <c r="J54" s="4" t="s">
+      <c r="J55" s="4" t="s">
         <v>196</v>
-      </c>
-    </row>
-    <row r="55" spans="1:11" ht="32" x14ac:dyDescent="0.2">
-      <c r="A55" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B55" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C55" s="4">
-        <v>1</v>
-      </c>
-      <c r="E55" s="4" t="s">
-        <v>197</v>
-      </c>
-      <c r="F55" s="4" t="s">
-        <v>198</v>
-      </c>
-      <c r="G55" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="I55" s="4" t="s">
-        <v>199</v>
-      </c>
-      <c r="J55" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="K55" s="4" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="56" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -2492,8 +2513,8 @@
       <c r="B56" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="C56" s="4" t="s">
-        <v>120</v>
+      <c r="C56" s="4">
+        <v>1</v>
       </c>
       <c r="E56" s="4" t="s">
         <v>197</v>
@@ -2502,15 +2523,44 @@
         <v>198</v>
       </c>
       <c r="G56" s="4" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="I56" s="4" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="J56" s="4" t="s">
         <v>40</v>
       </c>
       <c r="K56" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11" ht="32" x14ac:dyDescent="0.2">
+      <c r="A57" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B57" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C57" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="E57" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="F57" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="G57" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="I57" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="J57" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="K57" s="4" t="s">
         <v>41</v>
       </c>
     </row>

--- a/rules/NEW-RULE/positive/01/data/new-rule-positive-01.xlsx
+++ b/rules/NEW-RULE/positive/01/data/new-rule-positive-01.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/enrico/Work/core-contributor/rules/NEW-RULE/positive/01/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97B4F468-9027-9B47-A4B0-6E7BA057D3C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2ECF9CB7-0753-6E4B-A17E-4968EB857661}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30240" yWindow="-4560" windowWidth="51200" windowHeight="28800" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30240" yWindow="-7000" windowWidth="51200" windowHeight="28800" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Library" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="401" uniqueCount="206">
   <si>
     <t>Product</t>
   </si>
@@ -631,6 +631,15 @@
   </si>
   <si>
     <t>NA</t>
+  </si>
+  <si>
+    <t>HLTSUBJ1</t>
+  </si>
+  <si>
+    <t>HLTSUBJ2</t>
+  </si>
+  <si>
+    <t>C49489</t>
   </si>
 </sst>
 </file>
@@ -1079,7 +1088,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:K56"/>
+  <dimension ref="A1:K57"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -1621,7 +1630,9 @@
       <c r="C21" s="4">
         <v>1</v>
       </c>
-      <c r="D21" s="4"/>
+      <c r="D21" s="4" t="s">
+        <v>203</v>
+      </c>
       <c r="E21" s="4" t="s">
         <v>88</v>
       </c>
@@ -1642,65 +1653,69 @@
         <v>41</v>
       </c>
     </row>
-    <row r="22" spans="1:11" ht="80" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:11" ht="48" x14ac:dyDescent="0.2">
       <c r="A22" s="4" t="s">
         <v>31</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="C22" s="4">
-        <v>1</v>
+      <c r="C22" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>204</v>
       </c>
       <c r="E22" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="G22" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="H22" s="4"/>
+      <c r="I22" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="J22" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="K22" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" ht="80" x14ac:dyDescent="0.2">
+      <c r="A23" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C23" s="4">
+        <v>1</v>
+      </c>
+      <c r="E23" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="F22" s="4" t="s">
+      <c r="F23" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="G22" s="4" t="s">
+      <c r="G23" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="H22" s="5" t="s">
+      <c r="H23" s="5" t="s">
         <v>202</v>
       </c>
-      <c r="I22" s="4" t="s">
+      <c r="I23" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="J22" s="4" t="s">
+      <c r="J23" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="K22" s="4" t="s">
+      <c r="K23" s="4" t="s">
         <v>95</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" ht="32" x14ac:dyDescent="0.2">
-      <c r="A23" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B23" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C23" s="4">
-        <v>1</v>
-      </c>
-      <c r="E23" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="F23" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="G23" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="I23" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="J23" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="K23" s="4" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="24" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -1714,16 +1729,16 @@
         <v>1</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="I24" s="4" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="J24" s="4" t="s">
         <v>40</v>
@@ -1743,59 +1758,65 @@
         <v>1</v>
       </c>
       <c r="E25" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="G25" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="I25" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="J25" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="K25" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" ht="32" x14ac:dyDescent="0.2">
+      <c r="A26" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C26" s="4">
+        <v>1</v>
+      </c>
+      <c r="E26" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="F25" s="4" t="s">
+      <c r="F26" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="G25" s="4" t="s">
+      <c r="G26" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="J25" s="4" t="s">
+      <c r="J26" s="4" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="26" spans="1:11" ht="48" x14ac:dyDescent="0.2">
-      <c r="A26" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B26" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C26" s="4">
-        <v>1</v>
-      </c>
-      <c r="E26" s="4" t="s">
+    <row r="27" spans="1:11" ht="48" x14ac:dyDescent="0.2">
+      <c r="A27" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C27" s="4">
+        <v>1</v>
+      </c>
+      <c r="E27" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="F26" s="4" t="s">
+      <c r="F27" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="G26" s="4" t="s">
+      <c r="G27" s="4" t="s">
         <v>70</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" ht="112" x14ac:dyDescent="0.2">
-      <c r="A27" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B27" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C27" s="4">
-        <v>1</v>
-      </c>
-      <c r="D27" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="E27" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="F27" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="G27" s="4" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="28" spans="1:11" ht="112" x14ac:dyDescent="0.2">
@@ -1806,10 +1827,10 @@
         <v>32</v>
       </c>
       <c r="C28" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="E28" s="4" t="s">
         <v>110</v>
@@ -1818,33 +1839,33 @@
         <v>111</v>
       </c>
       <c r="G28" s="4" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" ht="112" x14ac:dyDescent="0.2">
+      <c r="A29" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C29" s="4">
+        <v>2</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="F29" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="G29" s="4" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="29" spans="1:11" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A29" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B29" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C29" s="4">
-        <v>1</v>
-      </c>
-      <c r="D29" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="E29" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="F29" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="G29" s="4" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11" ht="365" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:11" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A30" s="4" t="s">
         <v>31</v>
       </c>
@@ -1852,7 +1873,7 @@
         <v>32</v>
       </c>
       <c r="C30" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D30" s="4" t="s">
         <v>109</v>
@@ -1864,18 +1885,18 @@
         <v>116</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11" ht="335" x14ac:dyDescent="0.2">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" ht="365" x14ac:dyDescent="0.2">
       <c r="A31" s="4" t="s">
         <v>31</v>
       </c>
       <c r="B31" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="C31" s="4" t="s">
-        <v>70</v>
+      <c r="C31" s="4">
+        <v>2</v>
       </c>
       <c r="D31" s="4" t="s">
         <v>109</v>
@@ -1887,10 +1908,10 @@
         <v>116</v>
       </c>
       <c r="G31" s="4" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11" ht="128" x14ac:dyDescent="0.2">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" ht="335" x14ac:dyDescent="0.2">
       <c r="A32" s="4" t="s">
         <v>31</v>
       </c>
@@ -1898,10 +1919,10 @@
         <v>32</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>120</v>
+        <v>70</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="E32" s="4" t="s">
         <v>115</v>
@@ -1910,10 +1931,10 @@
         <v>116</v>
       </c>
       <c r="G32" s="4" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11" ht="112" x14ac:dyDescent="0.2">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" ht="128" x14ac:dyDescent="0.2">
       <c r="A33" s="4" t="s">
         <v>31</v>
       </c>
@@ -1921,7 +1942,7 @@
         <v>32</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D33" s="4" t="s">
         <v>113</v>
@@ -1933,33 +1954,30 @@
         <v>116</v>
       </c>
       <c r="G33" s="4" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" ht="112" x14ac:dyDescent="0.2">
+      <c r="A34" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="E34" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="F34" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="G34" s="4" t="s">
         <v>123</v>
-      </c>
-    </row>
-    <row r="34" spans="1:11" ht="64" x14ac:dyDescent="0.2">
-      <c r="A34" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B34" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C34" s="4">
-        <v>1</v>
-      </c>
-      <c r="E34" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="F34" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="G34" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="I34" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="J34" s="4" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="35" spans="1:11" ht="64" x14ac:dyDescent="0.2">
@@ -1973,42 +1991,39 @@
         <v>1</v>
       </c>
       <c r="E35" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="F35" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="G35" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="I35" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="J35" s="4" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" ht="64" x14ac:dyDescent="0.2">
+      <c r="A36" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C36" s="4">
+        <v>1</v>
+      </c>
+      <c r="E36" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="F35" s="4" t="s">
+      <c r="F36" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="G35" s="4" t="s">
+      <c r="G36" s="4" t="s">
         <v>131</v>
-      </c>
-    </row>
-    <row r="36" spans="1:11" ht="48" x14ac:dyDescent="0.2">
-      <c r="A36" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B36" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C36" s="4">
-        <v>1</v>
-      </c>
-      <c r="E36" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="F36" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="G36" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="I36" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="J36" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="K36" s="4" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="37" spans="1:11" ht="48" x14ac:dyDescent="0.2">
@@ -2022,88 +2037,97 @@
         <v>1</v>
       </c>
       <c r="E37" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="F37" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="G37" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="I37" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="J37" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="K37" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" ht="48" x14ac:dyDescent="0.2">
+      <c r="A38" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C38" s="4">
+        <v>1</v>
+      </c>
+      <c r="E38" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="F37" s="4" t="s">
+      <c r="F38" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="G37" s="4" t="s">
+      <c r="G38" s="4" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="38" spans="1:11" ht="32" x14ac:dyDescent="0.2">
-      <c r="A38" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B38" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C38" s="4">
-        <v>1</v>
-      </c>
-      <c r="E38" s="4" t="s">
+    <row r="39" spans="1:11" ht="32" x14ac:dyDescent="0.2">
+      <c r="A39" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C39" s="4">
+        <v>1</v>
+      </c>
+      <c r="E39" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="F38" s="4" t="s">
+      <c r="F39" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="G38" s="4" t="s">
+      <c r="G39" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="I38" s="4" t="s">
+      <c r="I39" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="J38" s="4" t="s">
+      <c r="J39" s="4" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="39" spans="1:11" ht="48" x14ac:dyDescent="0.2">
-      <c r="A39" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B39" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C39" s="4">
-        <v>1</v>
-      </c>
-      <c r="E39" s="4" t="s">
+    <row r="40" spans="1:11" ht="48" x14ac:dyDescent="0.2">
+      <c r="A40" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C40" s="4">
+        <v>1</v>
+      </c>
+      <c r="E40" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="F39" s="4" t="s">
+      <c r="F40" s="4" t="s">
         <v>142</v>
       </c>
-      <c r="G39" s="4" t="s">
+      <c r="G40" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="I39" s="4" t="s">
+      <c r="I40" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="J39" s="4" t="s">
+      <c r="J40" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="K39" s="4" t="s">
+      <c r="K40" s="4" t="s">
         <v>41</v>
-      </c>
-    </row>
-    <row r="40" spans="1:11" ht="32" x14ac:dyDescent="0.2">
-      <c r="A40" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B40" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C40" s="4">
-        <v>1</v>
-      </c>
-      <c r="E40" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="F40" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="G40" s="4" t="s">
-        <v>147</v>
       </c>
     </row>
     <row r="41" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -2117,13 +2141,13 @@
         <v>1</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="G41" s="4" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="42" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -2137,160 +2161,151 @@
         <v>1</v>
       </c>
       <c r="E42" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="F42" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="G42" s="4" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" ht="32" x14ac:dyDescent="0.2">
+      <c r="A43" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C43" s="4">
+        <v>1</v>
+      </c>
+      <c r="E43" s="4" t="s">
         <v>151</v>
       </c>
-      <c r="F42" s="4" t="s">
+      <c r="F43" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="G42" s="4" t="s">
+      <c r="G43" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="J42" s="4" t="s">
+      <c r="J43" s="4" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="43" spans="1:11" ht="48" x14ac:dyDescent="0.2">
-      <c r="A43" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B43" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C43" s="4">
-        <v>1</v>
-      </c>
-      <c r="E43" s="4" t="s">
+    <row r="44" spans="1:11" ht="48" x14ac:dyDescent="0.2">
+      <c r="A44" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C44" s="4">
+        <v>1</v>
+      </c>
+      <c r="E44" s="4" t="s">
         <v>154</v>
       </c>
-      <c r="F43" s="4" t="s">
+      <c r="F44" s="4" t="s">
         <v>155</v>
       </c>
-      <c r="G43" s="4" t="s">
+      <c r="G44" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="I43" s="4" t="s">
+      <c r="I44" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="J43" s="4" t="s">
+      <c r="J44" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="K43" s="4" t="s">
+      <c r="K44" s="4" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="44" spans="1:11" ht="96" x14ac:dyDescent="0.2">
-      <c r="A44" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B44" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C44" s="4">
-        <v>1</v>
-      </c>
-      <c r="E44" s="4" t="s">
+    <row r="45" spans="1:11" ht="96" x14ac:dyDescent="0.2">
+      <c r="A45" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C45" s="4">
+        <v>1</v>
+      </c>
+      <c r="E45" s="4" t="s">
         <v>158</v>
       </c>
-      <c r="F44" s="4" t="s">
+      <c r="F45" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="G44" s="4" t="s">
+      <c r="G45" s="4" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="45" spans="1:11" ht="32" x14ac:dyDescent="0.2">
-      <c r="A45" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B45" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C45" s="4">
-        <v>1</v>
-      </c>
-      <c r="E45" s="4" t="s">
+    <row r="46" spans="1:11" ht="32" x14ac:dyDescent="0.2">
+      <c r="A46" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C46" s="4">
+        <v>1</v>
+      </c>
+      <c r="E46" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="F45" s="4" t="s">
+      <c r="F46" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="G45" s="4" t="s">
+      <c r="G46" s="4" t="s">
         <v>163</v>
       </c>
-      <c r="J45" s="4" t="s">
+      <c r="J46" s="4" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="46" spans="1:11" ht="48" x14ac:dyDescent="0.2">
-      <c r="A46" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B46" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C46" s="4">
-        <v>1</v>
-      </c>
-      <c r="E46" s="4" t="s">
+    <row r="47" spans="1:11" ht="48" x14ac:dyDescent="0.2">
+      <c r="A47" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C47" s="4">
+        <v>1</v>
+      </c>
+      <c r="E47" s="4" t="s">
         <v>164</v>
       </c>
-      <c r="F46" s="4" t="s">
+      <c r="F47" s="4" t="s">
         <v>165</v>
       </c>
-      <c r="G46" s="4" t="s">
+      <c r="G47" s="4" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="47" spans="1:11" ht="32" x14ac:dyDescent="0.2">
-      <c r="A47" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B47" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C47" s="4">
-        <v>1</v>
-      </c>
-      <c r="E47" s="4" t="s">
+    <row r="48" spans="1:11" ht="32" x14ac:dyDescent="0.2">
+      <c r="A48" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C48" s="4">
+        <v>1</v>
+      </c>
+      <c r="E48" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="F47" s="4" t="s">
+      <c r="F48" s="4" t="s">
         <v>168</v>
       </c>
-      <c r="G47" s="4" t="s">
+      <c r="G48" s="4" t="s">
         <v>169</v>
       </c>
-      <c r="I47" s="4" t="s">
+      <c r="I48" s="4" t="s">
         <v>170</v>
-      </c>
-      <c r="J47" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="K47" s="4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="48" spans="1:11" ht="48" x14ac:dyDescent="0.2">
-      <c r="A48" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B48" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C48" s="4">
-        <v>1</v>
-      </c>
-      <c r="E48" s="4" t="s">
-        <v>171</v>
-      </c>
-      <c r="F48" s="4" t="s">
-        <v>172</v>
-      </c>
-      <c r="G48" s="4" t="s">
-        <v>173</v>
-      </c>
-      <c r="I48" s="4" t="s">
-        <v>174</v>
       </c>
       <c r="J48" s="4" t="s">
         <v>40</v>
@@ -2299,7 +2314,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="49" spans="1:11" ht="32" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:11" ht="48" x14ac:dyDescent="0.2">
       <c r="A49" s="4" t="s">
         <v>31</v>
       </c>
@@ -2310,16 +2325,16 @@
         <v>1</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="G49" s="4" t="s">
-        <v>63</v>
+        <v>173</v>
       </c>
       <c r="I49" s="4" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="J49" s="4" t="s">
         <v>40</v>
@@ -2328,7 +2343,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="50" spans="1:11" ht="112" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:11" ht="32" x14ac:dyDescent="0.2">
       <c r="A50" s="4" t="s">
         <v>31</v>
       </c>
@@ -2339,150 +2354,153 @@
         <v>1</v>
       </c>
       <c r="E50" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="F50" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="G50" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="I50" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="J50" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="K50" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" ht="112" x14ac:dyDescent="0.2">
+      <c r="A51" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B51" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C51" s="4">
+        <v>1</v>
+      </c>
+      <c r="D51" t="s">
+        <v>203</v>
+      </c>
+      <c r="E51" s="4" t="s">
         <v>178</v>
       </c>
-      <c r="F50" s="4" t="s">
+      <c r="F51" s="4" t="s">
         <v>179</v>
       </c>
-      <c r="G50" s="4" t="s">
+      <c r="G51" s="4" t="s">
         <v>180</v>
       </c>
-      <c r="H50" s="4"/>
-      <c r="I50" s="4"/>
-      <c r="J50" s="4"/>
-      <c r="K50" s="4"/>
-    </row>
-    <row r="51" spans="1:11" ht="48" x14ac:dyDescent="0.2">
-      <c r="A51" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B51" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C51" s="4">
-        <v>1</v>
-      </c>
-      <c r="E51" s="4" t="s">
+      <c r="H51" s="4"/>
+      <c r="I51" s="4"/>
+      <c r="J51" s="4"/>
+      <c r="K51" s="4"/>
+    </row>
+    <row r="52" spans="1:11" ht="48" x14ac:dyDescent="0.2">
+      <c r="A52" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C52" s="4">
+        <v>1</v>
+      </c>
+      <c r="E52" s="4" t="s">
         <v>181</v>
       </c>
-      <c r="F51" s="4" t="s">
+      <c r="F52" s="4" t="s">
         <v>182</v>
       </c>
-      <c r="G51" s="4" t="s">
+      <c r="G52" s="4" t="s">
         <v>183</v>
       </c>
-      <c r="I51" s="4" t="s">
+      <c r="I52" s="4" t="s">
         <v>184</v>
       </c>
-      <c r="J51" s="4" t="s">
+      <c r="J52" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="K51" s="4" t="s">
+      <c r="K52" s="4" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="52" spans="1:11" ht="160" x14ac:dyDescent="0.2">
-      <c r="A52" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B52" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C52" s="4">
-        <v>1</v>
-      </c>
-      <c r="E52" s="4" t="s">
+    <row r="53" spans="1:11" ht="160" x14ac:dyDescent="0.2">
+      <c r="A53" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B53" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C53" s="4">
+        <v>1</v>
+      </c>
+      <c r="E53" s="4" t="s">
         <v>185</v>
       </c>
-      <c r="F52" s="4" t="s">
+      <c r="F53" s="4" t="s">
         <v>186</v>
       </c>
-      <c r="G52" s="4" t="s">
+      <c r="G53" s="4" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="53" spans="1:11" ht="64" x14ac:dyDescent="0.2">
-      <c r="A53" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B53" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C53" s="4">
-        <v>1</v>
-      </c>
-      <c r="E53" s="4" t="s">
+    <row r="54" spans="1:11" ht="64" x14ac:dyDescent="0.2">
+      <c r="A54" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B54" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C54" s="4">
+        <v>1</v>
+      </c>
+      <c r="E54" s="4" t="s">
         <v>188</v>
       </c>
-      <c r="F53" s="4" t="s">
+      <c r="F54" s="4" t="s">
         <v>189</v>
       </c>
-      <c r="G53" s="4" t="s">
+      <c r="G54" s="4" t="s">
         <v>190</v>
       </c>
-      <c r="I53" s="4" t="s">
+      <c r="I54" s="4" t="s">
         <v>191</v>
       </c>
-      <c r="J53" s="4" t="s">
+      <c r="J54" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="K53" s="4" t="s">
+      <c r="K54" s="4" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="54" spans="1:11" ht="96" x14ac:dyDescent="0.2">
-      <c r="A54" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B54" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C54" s="4">
-        <v>1</v>
-      </c>
-      <c r="E54" s="4" t="s">
+    <row r="55" spans="1:11" ht="96" x14ac:dyDescent="0.2">
+      <c r="A55" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B55" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C55" s="4">
+        <v>1</v>
+      </c>
+      <c r="E55" s="4" t="s">
         <v>192</v>
       </c>
-      <c r="F54" s="4" t="s">
+      <c r="F55" s="4" t="s">
         <v>193</v>
       </c>
-      <c r="G54" s="4" t="s">
+      <c r="G55" s="4" t="s">
         <v>194</v>
       </c>
-      <c r="I54" s="4" t="s">
+      <c r="I55" s="4" t="s">
         <v>195</v>
       </c>
-      <c r="J54" s="4" t="s">
+      <c r="J55" s="4" t="s">
         <v>196</v>
-      </c>
-    </row>
-    <row r="55" spans="1:11" ht="32" x14ac:dyDescent="0.2">
-      <c r="A55" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B55" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C55" s="4">
-        <v>1</v>
-      </c>
-      <c r="E55" s="4" t="s">
-        <v>197</v>
-      </c>
-      <c r="F55" s="4" t="s">
-        <v>198</v>
-      </c>
-      <c r="G55" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="I55" s="4" t="s">
-        <v>199</v>
-      </c>
-      <c r="J55" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="K55" s="4" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="56" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -2492,8 +2510,8 @@
       <c r="B56" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="C56" s="4" t="s">
-        <v>120</v>
+      <c r="C56" s="4">
+        <v>1</v>
       </c>
       <c r="E56" s="4" t="s">
         <v>197</v>
@@ -2502,15 +2520,44 @@
         <v>198</v>
       </c>
       <c r="G56" s="4" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="I56" s="4" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="J56" s="4" t="s">
         <v>40</v>
       </c>
       <c r="K56" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11" ht="32" x14ac:dyDescent="0.2">
+      <c r="A57" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B57" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C57" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="E57" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="F57" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="G57" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="I57" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="J57" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="K57" s="4" t="s">
         <v>41</v>
       </c>
     </row>

--- a/rules/NEW-RULE/positive/01/data/new-rule-positive-01.xlsx
+++ b/rules/NEW-RULE/positive/01/data/new-rule-positive-01.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/enrico/Work/core-contributor/rules/NEW-RULE/positive/01/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rich/Documents/github/core-contributor/rules/NEW-RULE/positive/01/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9638809-9B87-7F49-B4AA-B31B69F44160}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90FF7017-A805-F34A-9455-5B50374F4CB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1420" yWindow="680" windowWidth="28800" windowHeight="18980" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="40020" yWindow="-2880" windowWidth="28800" windowHeight="18980" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Library" sheetId="1" r:id="rId1"/>
@@ -20,13 +20,15 @@
     <sheet name="ti.xpt" sheetId="8" r:id="rId5"/>
     <sheet name="ts.xpt" sheetId="9" r:id="rId6"/>
     <sheet name="tv.xpt" sheetId="6" r:id="rId7"/>
+    <sheet name="td.xpt" sheetId="11" r:id="rId8"/>
+    <sheet name="tm.xpt" sheetId="10" r:id="rId9"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="698" uniqueCount="334">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="762" uniqueCount="368">
   <si>
     <t>Product</t>
   </si>
@@ -1028,13 +1030,115 @@
   </si>
   <si>
     <t>Trial Summary Parameters</t>
+  </si>
+  <si>
+    <t>td.xpt</t>
+  </si>
+  <si>
+    <t>tm.xpt</t>
+  </si>
+  <si>
+    <t>Trial Disease Assessments</t>
+  </si>
+  <si>
+    <t>Trial Disease Milestones</t>
+  </si>
+  <si>
+    <t>TDORDER</t>
+  </si>
+  <si>
+    <t>TDANCVAR</t>
+  </si>
+  <si>
+    <t>TDSTOFF</t>
+  </si>
+  <si>
+    <t>TDTGTPAI</t>
+  </si>
+  <si>
+    <t>TDMINPAI</t>
+  </si>
+  <si>
+    <t>TDMAXPAI</t>
+  </si>
+  <si>
+    <t>TDNUMRPT</t>
+  </si>
+  <si>
+    <t>Sequence of Planned Assessment Schedule</t>
+  </si>
+  <si>
+    <t>Anchor Variable Name</t>
+  </si>
+  <si>
+    <t>Offset from the Anchor</t>
+  </si>
+  <si>
+    <t>Planned Assessment Interval</t>
+  </si>
+  <si>
+    <t>Planned Assessment Interval Minimum</t>
+  </si>
+  <si>
+    <t>Planned Assessment Interval Maximum</t>
+  </si>
+  <si>
+    <t>Maximum Number of Actual Assessments</t>
+  </si>
+  <si>
+    <t>CDISC-PILOT</t>
+  </si>
+  <si>
+    <t>TD</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>P0D</t>
+  </si>
+  <si>
+    <t>P12W</t>
+  </si>
+  <si>
+    <t>MIDSTYPE</t>
+  </si>
+  <si>
+    <t>TMDEF</t>
+  </si>
+  <si>
+    <t>TMRPT</t>
+  </si>
+  <si>
+    <t>Disease Milestone Type</t>
+  </si>
+  <si>
+    <t>Disease Milestone Definition</t>
+  </si>
+  <si>
+    <t>Disease Milestone Repetition Indicator</t>
+  </si>
+  <si>
+    <t>TM</t>
+  </si>
+  <si>
+    <t>DKA Event</t>
+  </si>
+  <si>
+    <t>Occurrence of Diabetic Ketoacidosis</t>
+  </si>
+  <si>
+    <t>DIAGNOSIS</t>
+  </si>
+  <si>
+    <t>Diagnosis</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1075,8 +1179,31 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1101,8 +1228,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="7">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -1184,11 +1317,26 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -1220,6 +1368,24 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1549,7 +1715,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
@@ -1598,6 +1764,22 @@
       </c>
       <c r="B6" t="s">
         <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>334</v>
+      </c>
+      <c r="B7" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>335</v>
+      </c>
+      <c r="B8" t="s">
+        <v>337</v>
       </c>
     </row>
   </sheetData>
@@ -4305,4 +4487,270 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B0D6DC6-F962-8649-8669-5A1A8DBAA0FD}">
+  <dimension ref="A1:I6"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+      <c r="A1" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" s="14" t="s">
+        <v>338</v>
+      </c>
+      <c r="D1" s="14" t="s">
+        <v>339</v>
+      </c>
+      <c r="E1" s="14" t="s">
+        <v>340</v>
+      </c>
+      <c r="F1" s="14" t="s">
+        <v>341</v>
+      </c>
+      <c r="G1" s="14" t="s">
+        <v>342</v>
+      </c>
+      <c r="H1" s="14" t="s">
+        <v>343</v>
+      </c>
+      <c r="I1" s="14" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="64" x14ac:dyDescent="0.2">
+      <c r="A2" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" s="15" t="s">
+        <v>345</v>
+      </c>
+      <c r="D2" s="15" t="s">
+        <v>346</v>
+      </c>
+      <c r="E2" s="15" t="s">
+        <v>347</v>
+      </c>
+      <c r="F2" s="15" t="s">
+        <v>348</v>
+      </c>
+      <c r="G2" s="15" t="s">
+        <v>349</v>
+      </c>
+      <c r="H2" s="15" t="s">
+        <v>350</v>
+      </c>
+      <c r="I2" s="15" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+      <c r="A3" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="G3" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="H3" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="I3" s="15" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A4" s="15">
+        <v>50</v>
+      </c>
+      <c r="B4" s="15">
+        <v>50</v>
+      </c>
+      <c r="C4" s="15">
+        <v>8</v>
+      </c>
+      <c r="D4" s="15">
+        <v>50</v>
+      </c>
+      <c r="E4" s="15">
+        <v>50</v>
+      </c>
+      <c r="F4" s="15">
+        <v>50</v>
+      </c>
+      <c r="G4" s="15">
+        <v>50</v>
+      </c>
+      <c r="H4" s="15">
+        <v>50</v>
+      </c>
+      <c r="I4" s="15">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+      <c r="A5" s="16" t="s">
+        <v>352</v>
+      </c>
+      <c r="B5" s="16" t="s">
+        <v>353</v>
+      </c>
+      <c r="C5" s="16" t="s">
+        <v>354</v>
+      </c>
+      <c r="E5" s="16" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+      <c r="A6" s="16" t="s">
+        <v>352</v>
+      </c>
+      <c r="B6" s="16" t="s">
+        <v>353</v>
+      </c>
+      <c r="C6" s="16" t="s">
+        <v>354</v>
+      </c>
+      <c r="E6" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94BF575F-FBF1-D54A-8EC9-373561903205}">
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A1" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" s="17" t="s">
+        <v>357</v>
+      </c>
+      <c r="D1" s="17" t="s">
+        <v>358</v>
+      </c>
+      <c r="E1" s="17" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="64" x14ac:dyDescent="0.2">
+      <c r="A2" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" s="18" t="s">
+        <v>360</v>
+      </c>
+      <c r="D2" s="18" t="s">
+        <v>361</v>
+      </c>
+      <c r="E2" s="18" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A3" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" s="18" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A4" s="18">
+        <v>50</v>
+      </c>
+      <c r="B4" s="18">
+        <v>50</v>
+      </c>
+      <c r="C4" s="18">
+        <v>50</v>
+      </c>
+      <c r="D4" s="18">
+        <v>50</v>
+      </c>
+      <c r="E4" s="18">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="48" x14ac:dyDescent="0.2">
+      <c r="A5" s="19" t="s">
+        <v>124</v>
+      </c>
+      <c r="B5" s="19" t="s">
+        <v>363</v>
+      </c>
+      <c r="C5" s="19" t="s">
+        <v>364</v>
+      </c>
+      <c r="D5" s="19" t="s">
+        <v>365</v>
+      </c>
+      <c r="E5" s="19" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A6" s="19" t="s">
+        <v>124</v>
+      </c>
+      <c r="B6" s="19" t="s">
+        <v>363</v>
+      </c>
+      <c r="C6" s="19" t="s">
+        <v>366</v>
+      </c>
+      <c r="D6" s="19" t="s">
+        <v>367</v>
+      </c>
+      <c r="E6" s="19" t="s">
+        <v>161</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/rules/NEW-RULE/positive/01/data/new-rule-positive-01.xlsx
+++ b/rules/NEW-RULE/positive/01/data/new-rule-positive-01.xlsx
@@ -1,41 +1,193 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10628"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rich/Documents/github/core-contributor/rules/NEW-RULE/positive/01/data/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10A05B83-5250-804A-966B-C9C603802B2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="38860" yWindow="-4900" windowWidth="30240" windowHeight="18980" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
     <sheet name="Library" sheetId="1" r:id="rId1"/>
     <sheet name="Datasets" sheetId="2" r:id="rId2"/>
     <sheet name="sv.xpt" sheetId="3" r:id="rId3"/>
     <sheet name="tv.xpt" sheetId="4" r:id="rId4"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="53">
+  <si>
+    <t>Product</t>
+  </si>
+  <si>
+    <t>Version</t>
+  </si>
+  <si>
+    <t>sdtmig</t>
+  </si>
+  <si>
+    <t>3-4</t>
+  </si>
+  <si>
+    <t>Filename</t>
+  </si>
+  <si>
+    <t>Label</t>
+  </si>
+  <si>
+    <t>sv.xpt</t>
+  </si>
+  <si>
+    <t>Subject Visits</t>
+  </si>
+  <si>
+    <t>tv.xpt</t>
+  </si>
+  <si>
+    <t>Trial Visits</t>
+  </si>
+  <si>
+    <t>STUDYID</t>
+  </si>
+  <si>
+    <t>DOMAIN</t>
+  </si>
+  <si>
+    <t>USUBJID</t>
+  </si>
+  <si>
+    <t>SUBJID</t>
+  </si>
+  <si>
+    <t>VISITNUM</t>
+  </si>
+  <si>
+    <t>VISIT</t>
+  </si>
+  <si>
+    <t>EPOCH</t>
+  </si>
+  <si>
+    <t>SVSTDTC</t>
+  </si>
+  <si>
+    <t>SVENDTC</t>
+  </si>
+  <si>
+    <t>SVSTDY</t>
+  </si>
+  <si>
+    <t>SVENDY</t>
+  </si>
+  <si>
+    <t>SVUPDES</t>
+  </si>
+  <si>
+    <t>Study Identifier</t>
+  </si>
+  <si>
+    <t>Domain Abbreviation</t>
+  </si>
+  <si>
+    <t>Unique Subject Identifier</t>
+  </si>
+  <si>
+    <t>Subject Identifier for the Study</t>
+  </si>
+  <si>
+    <t>Visit Number</t>
+  </si>
+  <si>
+    <t>Visit Name</t>
+  </si>
+  <si>
+    <t>Epoch</t>
+  </si>
+  <si>
+    <t>Start Date/Time of Visit</t>
+  </si>
+  <si>
+    <t>End Date/Time of Visit</t>
+  </si>
+  <si>
+    <t>Study Day of Start of Visit</t>
+  </si>
+  <si>
+    <t>Study Day of End of Visit</t>
+  </si>
+  <si>
+    <t>Description of Unplanned Visit</t>
+  </si>
+  <si>
+    <t>Char</t>
+  </si>
+  <si>
+    <t>Num</t>
+  </si>
+  <si>
+    <t>CDISCPILOT01</t>
+  </si>
+  <si>
+    <t>SV</t>
+  </si>
+  <si>
+    <t>CDISC001</t>
+  </si>
+  <si>
+    <t>SCREENING</t>
+  </si>
+  <si>
+    <t>2018-08-03</t>
+  </si>
+  <si>
+    <t>2018-08-04</t>
+  </si>
+  <si>
+    <t>INFECTION</t>
+  </si>
+  <si>
+    <t>ARMCD</t>
+  </si>
+  <si>
+    <t>TVSTRL</t>
+  </si>
+  <si>
+    <t>TVENRL</t>
+  </si>
+  <si>
+    <t>Planned Arm Code</t>
+  </si>
+  <si>
+    <t>Visit Start Rule</t>
+  </si>
+  <si>
+    <t>Visit End Rule</t>
+  </si>
+  <si>
+    <t>TV</t>
+  </si>
+  <si>
+    <t>Screening</t>
+  </si>
+  <si>
+    <t>SCREEN</t>
+  </si>
+  <si>
+    <t>Screen</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <numFmts count="0"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -44,48 +196,40 @@
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
       <name val="Calibri"/>
-      <b/>
+      <family val="2"/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
       <name val="Calibri"/>
-      <i/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
     <fill>
-      <patternFill patternType="none">
-        <bgColor/>
-      </patternFill>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="gray125">
-        <bgColor/>
-      </patternFill>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
-        <bgColor/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -94,22 +238,29 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs>
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="1" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -434,390 +585,461 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="3" t="str">
-        <v>Product</v>
-      </c>
-      <c r="B1" s="3" t="str">
-        <v>Version</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="3" t="str">
-        <v>sdtmig</v>
-      </c>
-      <c r="B2" s="3" t="str">
-        <v>3-4</v>
+    <row r="1" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B2"/>
+    <ignoredError sqref="A1:B2" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="3" t="str">
-        <v>Filename</v>
-      </c>
-      <c r="B1" s="3" t="str">
-        <v>Label</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="3" t="str">
-        <v>sv.xpt</v>
-      </c>
-      <c r="B2" s="3" t="str">
-        <v>Subject Visits</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="str">
-        <v>tv.xpt</v>
-      </c>
-      <c r="B3" s="3" t="str">
-        <v>Trial Visits</v>
+    <row r="1" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B3"/>
+    <ignoredError sqref="A1:B3" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:L6"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="4" t="str">
-        <v>STUDYID</v>
-      </c>
-      <c r="B1" s="4" t="str">
-        <v>DOMAIN</v>
-      </c>
-      <c r="C1" s="4" t="str">
-        <v>USUBJID</v>
-      </c>
-      <c r="D1" s="4" t="str">
-        <v>SUBJID</v>
-      </c>
-      <c r="E1" s="4" t="str">
-        <v>VISITNUM</v>
-      </c>
-      <c r="F1" s="4" t="str">
-        <v>VISIT</v>
-      </c>
-      <c r="G1" s="4" t="str">
-        <v>EPOCH</v>
-      </c>
-      <c r="H1" s="4" t="str">
-        <v>SVSTDTC</v>
-      </c>
-      <c r="I1" s="4" t="str">
-        <v>SVENDTC</v>
-      </c>
-      <c r="J1" s="4" t="str">
-        <v>SVSTDY</v>
-      </c>
-      <c r="K1" s="4" t="str">
-        <v>SVENDY</v>
-      </c>
-      <c r="L1" s="4" t="str">
-        <v>SVUPDES</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="5" t="str">
-        <v>Study Identifier</v>
-      </c>
-      <c r="B2" s="5" t="str">
-        <v>Domain Abbreviation</v>
-      </c>
-      <c r="C2" s="5" t="str">
-        <v>Unique Subject Identifier</v>
-      </c>
-      <c r="D2" s="5" t="str">
-        <v>Subject Identifier for the Study</v>
-      </c>
-      <c r="E2" s="5" t="str">
-        <v>Visit Number</v>
-      </c>
-      <c r="F2" s="5" t="str">
-        <v>Visit Name</v>
-      </c>
-      <c r="G2" s="5" t="str">
-        <v>Epoch</v>
-      </c>
-      <c r="H2" s="5" t="str">
-        <v>Start Date/Time of Visit</v>
-      </c>
-      <c r="I2" s="5" t="str">
-        <v>End Date/Time of Visit</v>
-      </c>
-      <c r="J2" s="5" t="str">
-        <v>Study Day of Start of Visit</v>
-      </c>
-      <c r="K2" s="5" t="str">
-        <v>Study Day of End of Visit</v>
-      </c>
-      <c r="L2" s="5" t="str">
-        <v>Description of Unplanned Visit</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="5" t="str">
-        <v>Char</v>
-      </c>
-      <c r="B3" s="5" t="str">
-        <v>Char</v>
-      </c>
-      <c r="C3" s="5" t="str">
-        <v>Char</v>
-      </c>
-      <c r="D3" s="5" t="str">
-        <v>Char</v>
-      </c>
-      <c r="E3" s="5" t="str">
-        <v>Num</v>
-      </c>
-      <c r="F3" s="5" t="str">
-        <v>Char</v>
-      </c>
-      <c r="G3" s="5" t="str">
-        <v>Char</v>
-      </c>
-      <c r="H3" s="5" t="str">
-        <v>Char</v>
-      </c>
-      <c r="I3" s="5" t="str">
-        <v>Char</v>
-      </c>
-      <c r="J3" s="5" t="str">
-        <v>Num</v>
-      </c>
-      <c r="K3" s="5" t="str">
-        <v>Num</v>
-      </c>
-      <c r="L3" s="5" t="str">
-        <v>Char</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="5">
+    <row r="1" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+      <c r="A1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="5">
+      <c r="D1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+      <c r="A2" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+      <c r="A3" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+      <c r="A4" s="3">
+        <v>12</v>
+      </c>
+      <c r="B4" s="3">
         <v>2</v>
       </c>
-      <c r="C4" s="5">
+      <c r="C4" s="3">
         <v>8</v>
       </c>
-      <c r="D4" s="5">
-        <v>1</v>
-      </c>
-      <c r="E4" s="5">
-        <v>1</v>
-      </c>
-      <c r="F4" s="5">
+      <c r="D4" s="3">
+        <v>1</v>
+      </c>
+      <c r="E4" s="3">
+        <v>1</v>
+      </c>
+      <c r="F4" s="3">
         <v>9</v>
       </c>
-      <c r="G4" s="5">
+      <c r="G4" s="3">
         <v>9</v>
       </c>
-      <c r="H4" s="5">
+      <c r="H4" s="3">
         <v>10</v>
       </c>
-      <c r="I4" s="5">
+      <c r="I4" s="3">
         <v>10</v>
       </c>
-      <c r="J4" s="5">
+      <c r="J4" s="3">
         <v>3</v>
       </c>
-      <c r="K4" s="5">
-        <v>1</v>
-      </c>
-      <c r="L4" s="5">
+      <c r="K4" s="3">
+        <v>1</v>
+      </c>
+      <c r="L4" s="3">
         <v>9</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="3" t="str">
-        <v>CDISCPILOT01</v>
-      </c>
-      <c r="B5" s="3" t="str">
-        <v>SV</v>
-      </c>
-      <c r="C5" s="3" t="str">
-        <v>CDISC001</v>
-      </c>
-      <c r="D5" s="3">
-        <v>1</v>
-      </c>
-      <c r="E5" s="3">
-        <v>1</v>
-      </c>
-      <c r="F5" s="3" t="str">
-        <v>SCREENING</v>
-      </c>
-      <c r="G5" s="3" t="str">
-        <v>SCREENING</v>
-      </c>
-      <c r="H5" s="3" t="str">
-        <v>2018-08-03</v>
-      </c>
-      <c r="I5" s="3" t="str">
-        <v>2018-08-04</v>
-      </c>
-      <c r="J5" s="3">
+    <row r="5" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+      <c r="A5" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D5" s="1">
+        <v>1</v>
+      </c>
+      <c r="E5" s="1">
+        <v>1</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="J5" s="1">
         <v>-28</v>
       </c>
-      <c r="K5" s="3">
+      <c r="K5" s="1">
         <v>4</v>
       </c>
-      <c r="L5" s="3" t="str">
-        <v>INFECTION</v>
+      <c r="L5" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+      <c r="A6" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D6" s="1">
+        <v>1</v>
+      </c>
+      <c r="E6" s="1">
+        <v>1</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="J6" s="1">
+        <v>-28</v>
+      </c>
+      <c r="K6" s="1">
+        <v>4</v>
+      </c>
+      <c r="L6" s="1" t="s">
+        <v>42</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L5"/>
+    <ignoredError sqref="A1:L5" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:G6"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="4" t="str">
-        <v>STUDYID</v>
-      </c>
-      <c r="B1" s="4" t="str">
-        <v>DOMAIN</v>
-      </c>
-      <c r="C1" s="4" t="str">
-        <v>VISITNUM</v>
-      </c>
-      <c r="D1" s="4" t="str">
-        <v>VISIT</v>
-      </c>
-      <c r="E1" s="4" t="str">
-        <v>ARMCD</v>
-      </c>
-      <c r="F1" s="4" t="str">
-        <v>TVSTRL</v>
-      </c>
-      <c r="G1" s="4" t="str">
-        <v>TVENRL</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="5" t="str">
-        <v>Study Identifier</v>
-      </c>
-      <c r="B2" s="5" t="str">
-        <v>Domain Abbreviation</v>
-      </c>
-      <c r="C2" s="5" t="str">
-        <v>Visit Number</v>
-      </c>
-      <c r="D2" s="5" t="str">
-        <v>Visit Name</v>
-      </c>
-      <c r="E2" s="5" t="str">
-        <v>Planned Arm Code</v>
-      </c>
-      <c r="F2" s="5" t="str">
-        <v>Visit Start Rule</v>
-      </c>
-      <c r="G2" s="5" t="str">
-        <v>Visit End Rule</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="5" t="str">
-        <v>Char</v>
-      </c>
-      <c r="B3" s="5" t="str">
-        <v>Char</v>
-      </c>
-      <c r="C3" s="5" t="str">
-        <v>Num</v>
-      </c>
-      <c r="D3" s="5" t="str">
-        <v>Char</v>
-      </c>
-      <c r="E3" s="5" t="str">
-        <v>Char</v>
-      </c>
-      <c r="F3" s="5" t="str">
-        <v>Char</v>
-      </c>
-      <c r="G3" s="5" t="str">
-        <v>Char</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="5">
+    <row r="1" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A2" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A3" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A4" s="3">
         <v>12</v>
       </c>
-      <c r="B4" s="5">
+      <c r="B4" s="3">
         <v>2</v>
       </c>
-      <c r="C4" s="5">
-        <v>1</v>
-      </c>
-      <c r="D4" s="5">
+      <c r="C4" s="3">
+        <v>1</v>
+      </c>
+      <c r="D4" s="3">
         <v>9</v>
       </c>
-      <c r="E4" s="5">
+      <c r="E4" s="3">
         <v>8</v>
       </c>
-      <c r="F4" s="5">
+      <c r="F4" s="3">
         <v>9</v>
       </c>
-      <c r="G4" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="str">
-        <v>CDISCPILOT01</v>
-      </c>
-      <c r="B5" s="3" t="str">
-        <v>TV</v>
-      </c>
-      <c r="C5" s="3">
-        <v>1</v>
-      </c>
-      <c r="D5" s="3" t="str">
-        <v>SCREENING</v>
-      </c>
-      <c r="E5" s="3">
+      <c r="G4" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A5" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C5" s="1">
+        <v>1</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E5" s="1">
         <v>13094209</v>
       </c>
-      <c r="F5" s="3" t="str">
-        <v>Screening</v>
-      </c>
-      <c r="G5" s="3">
+      <c r="F5" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G5" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A6" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C6" s="1">
+        <v>1</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="E6" s="1">
+        <v>13094209</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="G6" s="1">
         <v>1</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G5"/>
+    <ignoredError sqref="A1:G5" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/rules/NEW-RULE/positive/01/data/new-rule-positive-01.xlsx
+++ b/rules/NEW-RULE/positive/01/data/new-rule-positive-01.xlsx
@@ -1,41 +1,148 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10628"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rich/Documents/github/core-contributor/rules/NEW-RULE/positive/01/data/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{258E2C6D-9D3D-F941-87FA-15EFF5505325}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
     <sheet name="Library" sheetId="1" r:id="rId1"/>
     <sheet name="Datasets" sheetId="2" r:id="rId2"/>
     <sheet name="ts.xpt" sheetId="3" r:id="rId3"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="38">
+  <si>
+    <t>Product</t>
+  </si>
+  <si>
+    <t>Version</t>
+  </si>
+  <si>
+    <t>sdtmig</t>
+  </si>
+  <si>
+    <t>3-4</t>
+  </si>
+  <si>
+    <t>Filename</t>
+  </si>
+  <si>
+    <t>Label</t>
+  </si>
+  <si>
+    <t>ts.xpt</t>
+  </si>
+  <si>
+    <t>Trial Summary Parameters</t>
+  </si>
+  <si>
+    <t>STUDYID</t>
+  </si>
+  <si>
+    <t>DOMAIN</t>
+  </si>
+  <si>
+    <t>TSSEQ</t>
+  </si>
+  <si>
+    <t>TSGRPID</t>
+  </si>
+  <si>
+    <t>TSPARMCD</t>
+  </si>
+  <si>
+    <t>TSPARM</t>
+  </si>
+  <si>
+    <t>TSVAL</t>
+  </si>
+  <si>
+    <t>TSVALNF</t>
+  </si>
+  <si>
+    <t>TSVCDREF</t>
+  </si>
+  <si>
+    <t>TSVCDVER</t>
+  </si>
+  <si>
+    <t>Study Identifier</t>
+  </si>
+  <si>
+    <t>Domain Abbreviation</t>
+  </si>
+  <si>
+    <t>Sequence Number</t>
+  </si>
+  <si>
+    <t>Group ID</t>
+  </si>
+  <si>
+    <t>Trial Summary Parameter Short Name</t>
+  </si>
+  <si>
+    <t>Trial Summary Parameter</t>
+  </si>
+  <si>
+    <t>Parameter Value</t>
+  </si>
+  <si>
+    <t>Parameter Null Flavor</t>
+  </si>
+  <si>
+    <t>Name of the Reference Terminology</t>
+  </si>
+  <si>
+    <t>Version of the Reference Terminology</t>
+  </si>
+  <si>
+    <t>Char</t>
+  </si>
+  <si>
+    <t>Num</t>
+  </si>
+  <si>
+    <t>CDISCPILOT01</t>
+  </si>
+  <si>
+    <t>TS</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>FCNTRY</t>
+  </si>
+  <si>
+    <t>Planned Country of Investigational Sites</t>
+  </si>
+  <si>
+    <t>NA</t>
+  </si>
+  <si>
+    <t>ALB</t>
+  </si>
+  <si>
+    <t>GENC</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <numFmts count="0"/>
-  <fonts count="5" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -43,48 +150,35 @@
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
       <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <i/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
     <fill>
-      <patternFill patternType="none">
-        <bgColor/>
-      </patternFill>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="gray125">
-        <bgColor/>
-      </patternFill>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
-        <bgColor/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -93,22 +187,28 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs>
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="1" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
-  <cellStyles>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -433,238 +533,229 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="3" t="str">
-        <v>Product</v>
-      </c>
-      <c r="B1" s="3" t="str">
-        <v>Version</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="3" t="str">
-        <v>sdtmig</v>
-      </c>
-      <c r="B2" s="3" t="str">
-        <v>3-4</v>
+    <row r="1" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B2"/>
+    <ignoredError sqref="A1:B2" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="3" t="str">
-        <v>Filename</v>
-      </c>
-      <c r="B1" s="3" t="str">
-        <v>Label</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="3" t="str">
-        <v>ts.xpt</v>
-      </c>
-      <c r="B2" s="3" t="str">
-        <v>Trial Summary Parameters</v>
+    <row r="1" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B2"/>
+    <ignoredError sqref="A1:B2" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:J5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="4" t="str">
-        <v>STUDYID</v>
-      </c>
-      <c r="B1" s="4" t="str">
-        <v>DOMAIN</v>
-      </c>
-      <c r="C1" s="4" t="str">
-        <v>TSSEQ</v>
-      </c>
-      <c r="D1" s="4" t="str">
-        <v>TSGRPID</v>
-      </c>
-      <c r="E1" s="4" t="str">
-        <v>TSPARMCD</v>
-      </c>
-      <c r="F1" s="4" t="str">
-        <v>TSPARM</v>
-      </c>
-      <c r="G1" s="4" t="str">
-        <v>TSVAL</v>
-      </c>
-      <c r="H1" s="4" t="str">
-        <v>TSVALNF</v>
-      </c>
-      <c r="I1" s="4" t="str">
-        <v>TSVALCD</v>
-      </c>
-      <c r="J1" s="4" t="str">
-        <v>TSVCDREF</v>
-      </c>
-      <c r="K1" s="4" t="str">
-        <v>TSVCDVER</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="5" t="str">
-        <v>Study Identifier</v>
-      </c>
-      <c r="B2" s="5" t="str">
-        <v>Domain Abbreviation</v>
-      </c>
-      <c r="C2" s="5" t="str">
-        <v>Sequence Number</v>
-      </c>
-      <c r="D2" s="5" t="str">
-        <v>Group ID</v>
-      </c>
-      <c r="E2" s="5" t="str">
-        <v>Trial Summary Parameter Short Name</v>
-      </c>
-      <c r="F2" s="5" t="str">
-        <v>Trial Summary Parameter</v>
-      </c>
-      <c r="G2" s="5" t="str">
-        <v>Parameter Value</v>
-      </c>
-      <c r="H2" s="5" t="str">
-        <v>Parameter Null Flavor</v>
-      </c>
-      <c r="I2" s="5" t="str">
-        <v>Parameter Value Code</v>
-      </c>
-      <c r="J2" s="5" t="str">
-        <v>Name of the Reference Terminology</v>
-      </c>
-      <c r="K2" s="5" t="str">
-        <v>Version of the Reference Terminology</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="5" t="str">
-        <v>Char</v>
-      </c>
-      <c r="B3" s="5" t="str">
-        <v>Char</v>
-      </c>
-      <c r="C3" s="5" t="str">
-        <v>Num</v>
-      </c>
-      <c r="D3" s="5" t="str">
-        <v>Char</v>
-      </c>
-      <c r="E3" s="5" t="str">
-        <v>Char</v>
-      </c>
-      <c r="F3" s="5" t="str">
-        <v>Char</v>
-      </c>
-      <c r="G3" s="5" t="str">
-        <v>Char</v>
-      </c>
-      <c r="H3" s="5" t="str">
-        <v>Char</v>
-      </c>
-      <c r="I3" s="5" t="str">
-        <v>Char</v>
-      </c>
-      <c r="J3" s="5" t="str">
-        <v>Char</v>
-      </c>
-      <c r="K3" s="5" t="str">
-        <v>Char</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="5">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="5">
+      <c r="D1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A3" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A4" s="3">
+        <v>10</v>
+      </c>
+      <c r="B4" s="3">
         <v>2</v>
       </c>
-      <c r="C4" s="5">
+      <c r="C4" s="3">
         <v>8</v>
       </c>
-      <c r="D4" s="5">
+      <c r="D4" s="3">
         <v>5</v>
       </c>
-      <c r="E4" s="5">
+      <c r="E4" s="3">
         <v>8</v>
       </c>
-      <c r="F4" s="5">
+      <c r="F4" s="3">
         <v>40</v>
       </c>
-      <c r="G4" s="5">
+      <c r="G4" s="3">
         <v>149</v>
       </c>
-      <c r="H4" s="5">
+      <c r="H4" s="3">
         <v>2</v>
       </c>
-      <c r="I4" s="5">
-        <v>11</v>
-      </c>
-      <c r="J4" s="5">
+      <c r="I4" s="3">
         <v>18</v>
       </c>
-      <c r="K4" s="5">
+      <c r="J4" s="3">
         <v>10</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="3" t="str">
-        <v>CDISCPILOT01</v>
-      </c>
-      <c r="B5" s="3" t="str">
-        <v>TS</v>
-      </c>
-      <c r="C5" s="3">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A5" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C5" s="1">
         <v>1</v>
       </c>
-      <c r="D5" s="3" t="str">
-        <v/>
-      </c>
-      <c r="E5" s="3" t="str">
-        <v>FCNTRY</v>
-      </c>
-      <c r="F5" s="3" t="str">
-        <v>Planned Country of Investigational Sites</v>
-      </c>
-      <c r="G5" s="3" t="str">
-        <v>Albania</v>
-      </c>
-      <c r="H5" s="3" t="str">
-        <v>NA</v>
-      </c>
-      <c r="I5" s="3" t="str">
-        <v>ALB</v>
-      </c>
-      <c r="J5" s="3" t="str">
-        <v>GENC</v>
+      <c r="D5" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>37</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K5"/>
+    <ignoredError sqref="A1:H4 A5:F5 I5:J5 H5 I1:J4" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/rules/NEW-RULE/positive/01/data/new-rule-positive-01.xlsx
+++ b/rules/NEW-RULE/positive/01/data/new-rule-positive-01.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/enrico/Work/core-contributor/rules/NEW-RULE/positive/01/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FA28602-A2A3-624D-912A-14B91E9200A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1DCFD52-FC18-3C45-8093-711255DD8A36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="30240" yWindow="-7000" windowWidth="51200" windowHeight="28800" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="402" uniqueCount="206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="203">
   <si>
     <t>Product</t>
   </si>
@@ -631,15 +631,6 @@
   </si>
   <si>
     <t>NA</t>
-  </si>
-  <si>
-    <t>STYPE1</t>
-  </si>
-  <si>
-    <t>STYPE2</t>
-  </si>
-  <si>
-    <t>OTHERTYPE</t>
   </si>
 </sst>
 </file>
@@ -1088,7 +1079,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:K57"/>
+  <dimension ref="A1:K56"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -1693,9 +1684,6 @@
       <c r="C23" s="4">
         <v>1</v>
       </c>
-      <c r="D23" t="s">
-        <v>203</v>
-      </c>
       <c r="E23" s="4" t="s">
         <v>96</v>
       </c>
@@ -1725,9 +1713,6 @@
       <c r="C24" s="4">
         <v>1</v>
       </c>
-      <c r="D24" t="s">
-        <v>203</v>
-      </c>
       <c r="E24" s="4" t="s">
         <v>100</v>
       </c>
@@ -2266,9 +2251,6 @@
       <c r="C47" s="4">
         <v>1</v>
       </c>
-      <c r="D47" t="s">
-        <v>203</v>
-      </c>
       <c r="E47" s="4" t="s">
         <v>167</v>
       </c>
@@ -2288,30 +2270,27 @@
         <v>41</v>
       </c>
     </row>
-    <row r="48" spans="1:11" ht="32" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:11" ht="48" x14ac:dyDescent="0.2">
       <c r="A48" s="4" t="s">
         <v>31</v>
       </c>
       <c r="B48" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="C48" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="D48" t="s">
-        <v>204</v>
+      <c r="C48" s="4">
+        <v>1</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="G48" s="4" t="s">
-        <v>205</v>
+        <v>173</v>
       </c>
       <c r="I48" s="4" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="J48" s="4" t="s">
         <v>40</v>
@@ -2320,7 +2299,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="49" spans="1:11" ht="48" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:11" ht="32" x14ac:dyDescent="0.2">
       <c r="A49" s="4" t="s">
         <v>31</v>
       </c>
@@ -2331,16 +2310,16 @@
         <v>1</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="G49" s="4" t="s">
-        <v>173</v>
+        <v>63</v>
       </c>
       <c r="I49" s="4" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="J49" s="4" t="s">
         <v>40</v>
@@ -2349,7 +2328,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="50" spans="1:11" ht="32" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:11" ht="112" x14ac:dyDescent="0.2">
       <c r="A50" s="4" t="s">
         <v>31</v>
       </c>
@@ -2360,49 +2339,49 @@
         <v>1</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="G50" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="I50" s="4" t="s">
-        <v>177</v>
-      </c>
-      <c r="J50" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="H50" s="4"/>
+      <c r="I50" s="4"/>
+      <c r="J50" s="4"/>
+      <c r="K50" s="4"/>
+    </row>
+    <row r="51" spans="1:11" ht="48" x14ac:dyDescent="0.2">
+      <c r="A51" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B51" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C51" s="4">
+        <v>1</v>
+      </c>
+      <c r="E51" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="F51" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="G51" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="I51" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="J51" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="K50" s="4" t="s">
+      <c r="K51" s="4" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="51" spans="1:11" ht="112" x14ac:dyDescent="0.2">
-      <c r="A51" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B51" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C51" s="4">
-        <v>1</v>
-      </c>
-      <c r="E51" s="4" t="s">
-        <v>178</v>
-      </c>
-      <c r="F51" s="4" t="s">
-        <v>179</v>
-      </c>
-      <c r="G51" s="4" t="s">
-        <v>180</v>
-      </c>
-      <c r="H51" s="4"/>
-      <c r="I51" s="4"/>
-      <c r="J51" s="4"/>
-      <c r="K51" s="4"/>
-    </row>
-    <row r="52" spans="1:11" ht="48" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:11" ht="160" x14ac:dyDescent="0.2">
       <c r="A52" s="4" t="s">
         <v>31</v>
       </c>
@@ -2413,45 +2392,45 @@
         <v>1</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="G52" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="I52" s="4" t="s">
-        <v>184</v>
-      </c>
-      <c r="J52" s="4" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11" ht="64" x14ac:dyDescent="0.2">
+      <c r="A53" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B53" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C53" s="4">
+        <v>1</v>
+      </c>
+      <c r="E53" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="F53" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="G53" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="I53" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="J53" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="K52" s="4" t="s">
+      <c r="K53" s="4" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="53" spans="1:11" ht="160" x14ac:dyDescent="0.2">
-      <c r="A53" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B53" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C53" s="4">
-        <v>1</v>
-      </c>
-      <c r="E53" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="F53" s="4" t="s">
-        <v>186</v>
-      </c>
-      <c r="G53" s="4" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="54" spans="1:11" ht="64" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:11" ht="96" x14ac:dyDescent="0.2">
       <c r="A54" s="4" t="s">
         <v>31</v>
       </c>
@@ -2462,48 +2441,48 @@
         <v>1</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="G54" s="4" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="I54" s="4" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="J54" s="4" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11" ht="32" x14ac:dyDescent="0.2">
+      <c r="A55" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B55" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C55" s="4">
+        <v>1</v>
+      </c>
+      <c r="E55" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="F55" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="G55" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="I55" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="J55" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="K54" s="4" t="s">
+      <c r="K55" s="4" t="s">
         <v>41</v>
-      </c>
-    </row>
-    <row r="55" spans="1:11" ht="96" x14ac:dyDescent="0.2">
-      <c r="A55" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B55" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C55" s="4">
-        <v>1</v>
-      </c>
-      <c r="E55" s="4" t="s">
-        <v>192</v>
-      </c>
-      <c r="F55" s="4" t="s">
-        <v>193</v>
-      </c>
-      <c r="G55" s="4" t="s">
-        <v>194</v>
-      </c>
-      <c r="I55" s="4" t="s">
-        <v>195</v>
-      </c>
-      <c r="J55" s="4" t="s">
-        <v>196</v>
       </c>
     </row>
     <row r="56" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -2513,8 +2492,8 @@
       <c r="B56" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="C56" s="4">
-        <v>1</v>
+      <c r="C56" s="4" t="s">
+        <v>120</v>
       </c>
       <c r="E56" s="4" t="s">
         <v>197</v>
@@ -2523,44 +2502,15 @@
         <v>198</v>
       </c>
       <c r="G56" s="4" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="I56" s="4" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="J56" s="4" t="s">
         <v>40</v>
       </c>
       <c r="K56" s="4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="57" spans="1:11" ht="32" x14ac:dyDescent="0.2">
-      <c r="A57" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B57" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C57" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="E57" s="4" t="s">
-        <v>197</v>
-      </c>
-      <c r="F57" s="4" t="s">
-        <v>198</v>
-      </c>
-      <c r="G57" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="I57" s="4" t="s">
-        <v>200</v>
-      </c>
-      <c r="J57" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="K57" s="4" t="s">
         <v>41</v>
       </c>
     </row>

--- a/rules/NEW-RULE/positive/01/data/new-rule-positive-01.xlsx
+++ b/rules/NEW-RULE/positive/01/data/new-rule-positive-01.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/enrico/Work/core-contributor/rules/NEW-RULE/positive/01/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93DB8275-93A4-0C46-8DAB-BB1EF6883CC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2753BBE0-B96B-2448-B796-0607E3661DE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="30240" yWindow="-7000" windowWidth="51200" windowHeight="28800" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="203">
   <si>
     <t>Product</t>
   </si>
@@ -631,18 +631,6 @@
   </si>
   <si>
     <t>NA</t>
-  </si>
-  <si>
-    <t>STYPE1</t>
-  </si>
-  <si>
-    <t>STYPE2</t>
-  </si>
-  <si>
-    <t>NON-INT</t>
-  </si>
-  <si>
-    <t>C98389</t>
   </si>
 </sst>
 </file>
@@ -1091,7 +1079,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:K57"/>
+  <dimension ref="A1:K56"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -2263,9 +2251,6 @@
       <c r="C47" s="4">
         <v>1</v>
       </c>
-      <c r="D47" t="s">
-        <v>203</v>
-      </c>
       <c r="E47" s="4" t="s">
         <v>167</v>
       </c>
@@ -2285,7 +2270,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="48" spans="1:11" ht="32" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:11" ht="48" x14ac:dyDescent="0.2">
       <c r="A48" s="4" t="s">
         <v>31</v>
       </c>
@@ -2295,20 +2280,17 @@
       <c r="C48" s="4">
         <v>1</v>
       </c>
-      <c r="D48" t="s">
-        <v>204</v>
-      </c>
       <c r="E48" s="4" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="G48" s="4" t="s">
-        <v>205</v>
+        <v>173</v>
       </c>
       <c r="I48" s="4" t="s">
-        <v>206</v>
+        <v>174</v>
       </c>
       <c r="J48" s="4" t="s">
         <v>40</v>
@@ -2317,7 +2299,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="49" spans="1:11" ht="48" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:11" ht="32" x14ac:dyDescent="0.2">
       <c r="A49" s="4" t="s">
         <v>31</v>
       </c>
@@ -2328,16 +2310,16 @@
         <v>1</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="G49" s="4" t="s">
-        <v>173</v>
+        <v>63</v>
       </c>
       <c r="I49" s="4" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="J49" s="4" t="s">
         <v>40</v>
@@ -2346,7 +2328,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="50" spans="1:11" ht="32" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:11" ht="112" x14ac:dyDescent="0.2">
       <c r="A50" s="4" t="s">
         <v>31</v>
       </c>
@@ -2357,49 +2339,49 @@
         <v>1</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="G50" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="I50" s="4" t="s">
-        <v>177</v>
-      </c>
-      <c r="J50" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="H50" s="4"/>
+      <c r="I50" s="4"/>
+      <c r="J50" s="4"/>
+      <c r="K50" s="4"/>
+    </row>
+    <row r="51" spans="1:11" ht="48" x14ac:dyDescent="0.2">
+      <c r="A51" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B51" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C51" s="4">
+        <v>1</v>
+      </c>
+      <c r="E51" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="F51" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="G51" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="I51" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="J51" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="K50" s="4" t="s">
+      <c r="K51" s="4" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="51" spans="1:11" ht="112" x14ac:dyDescent="0.2">
-      <c r="A51" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B51" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C51" s="4">
-        <v>1</v>
-      </c>
-      <c r="E51" s="4" t="s">
-        <v>178</v>
-      </c>
-      <c r="F51" s="4" t="s">
-        <v>179</v>
-      </c>
-      <c r="G51" s="4" t="s">
-        <v>180</v>
-      </c>
-      <c r="H51" s="4"/>
-      <c r="I51" s="4"/>
-      <c r="J51" s="4"/>
-      <c r="K51" s="4"/>
-    </row>
-    <row r="52" spans="1:11" ht="48" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:11" ht="160" x14ac:dyDescent="0.2">
       <c r="A52" s="4" t="s">
         <v>31</v>
       </c>
@@ -2410,45 +2392,45 @@
         <v>1</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="G52" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="I52" s="4" t="s">
-        <v>184</v>
-      </c>
-      <c r="J52" s="4" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11" ht="64" x14ac:dyDescent="0.2">
+      <c r="A53" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B53" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C53" s="4">
+        <v>1</v>
+      </c>
+      <c r="E53" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="F53" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="G53" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="I53" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="J53" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="K52" s="4" t="s">
+      <c r="K53" s="4" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="53" spans="1:11" ht="160" x14ac:dyDescent="0.2">
-      <c r="A53" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B53" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C53" s="4">
-        <v>1</v>
-      </c>
-      <c r="E53" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="F53" s="4" t="s">
-        <v>186</v>
-      </c>
-      <c r="G53" s="4" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="54" spans="1:11" ht="64" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:11" ht="96" x14ac:dyDescent="0.2">
       <c r="A54" s="4" t="s">
         <v>31</v>
       </c>
@@ -2459,51 +2441,48 @@
         <v>1</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="G54" s="4" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="I54" s="4" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="J54" s="4" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11" ht="32" x14ac:dyDescent="0.2">
+      <c r="A55" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B55" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C55" s="4">
+        <v>1</v>
+      </c>
+      <c r="E55" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="F55" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="G55" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="I55" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="J55" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="K54" s="4" t="s">
+      <c r="K55" s="4" t="s">
         <v>41</v>
-      </c>
-    </row>
-    <row r="55" spans="1:11" ht="96" x14ac:dyDescent="0.2">
-      <c r="A55" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B55" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C55" s="4">
-        <v>1</v>
-      </c>
-      <c r="D55" t="s">
-        <v>203</v>
-      </c>
-      <c r="E55" s="4" t="s">
-        <v>192</v>
-      </c>
-      <c r="F55" s="4" t="s">
-        <v>193</v>
-      </c>
-      <c r="G55" s="4" t="s">
-        <v>194</v>
-      </c>
-      <c r="I55" s="4" t="s">
-        <v>195</v>
-      </c>
-      <c r="J55" s="4" t="s">
-        <v>196</v>
       </c>
     </row>
     <row r="56" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -2513,8 +2492,8 @@
       <c r="B56" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="C56" s="4">
-        <v>1</v>
+      <c r="C56" s="4" t="s">
+        <v>120</v>
       </c>
       <c r="E56" s="4" t="s">
         <v>197</v>
@@ -2523,44 +2502,15 @@
         <v>198</v>
       </c>
       <c r="G56" s="4" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="I56" s="4" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="J56" s="4" t="s">
         <v>40</v>
       </c>
       <c r="K56" s="4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="57" spans="1:11" ht="32" x14ac:dyDescent="0.2">
-      <c r="A57" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B57" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C57" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="E57" s="4" t="s">
-        <v>197</v>
-      </c>
-      <c r="F57" s="4" t="s">
-        <v>198</v>
-      </c>
-      <c r="G57" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="I57" s="4" t="s">
-        <v>200</v>
-      </c>
-      <c r="J57" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="K57" s="4" t="s">
         <v>41</v>
       </c>
     </row>

--- a/rules/NEW-RULE/positive/01/data/new-rule-positive-01.xlsx
+++ b/rules/NEW-RULE/positive/01/data/new-rule-positive-01.xlsx
@@ -1,40 +1,147 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10628"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/enrico/Work/core-contributor/rules/NEW-RULE/positive/01/data/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF18A0C3-9C06-1447-B6CF-343523769A20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="20" yWindow="660" windowWidth="30240" windowHeight="18980" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
     <sheet name="Library" sheetId="1" r:id="rId1"/>
     <sheet name="Datasets" sheetId="2" r:id="rId2"/>
     <sheet name="ts.xpt" sheetId="3" r:id="rId3"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="38">
+  <si>
+    <t>Product</t>
+  </si>
+  <si>
+    <t>Version</t>
+  </si>
+  <si>
+    <t>sdtmig</t>
+  </si>
+  <si>
+    <t>3-4</t>
+  </si>
+  <si>
+    <t>Filename</t>
+  </si>
+  <si>
+    <t>Label</t>
+  </si>
+  <si>
+    <t>ts.xpt</t>
+  </si>
+  <si>
+    <t>Trial Summary Parameters</t>
+  </si>
+  <si>
+    <t>STUDYID</t>
+  </si>
+  <si>
+    <t>DOMAIN</t>
+  </si>
+  <si>
+    <t>TSSEQ</t>
+  </si>
+  <si>
+    <t>TSGRPID</t>
+  </si>
+  <si>
+    <t>TSPARMCD</t>
+  </si>
+  <si>
+    <t>TSPARM</t>
+  </si>
+  <si>
+    <t>TSVAL</t>
+  </si>
+  <si>
+    <t>TSVALNF</t>
+  </si>
+  <si>
+    <t>TSVALCD</t>
+  </si>
+  <si>
+    <t>TSVCDREF</t>
+  </si>
+  <si>
+    <t>TSVCDVER</t>
+  </si>
+  <si>
+    <t>Study Identifier</t>
+  </si>
+  <si>
+    <t>Domain Abbreviation</t>
+  </si>
+  <si>
+    <t>Sequence Number</t>
+  </si>
+  <si>
+    <t>Group ID</t>
+  </si>
+  <si>
+    <t>Trial Summary Parameter Short Name</t>
+  </si>
+  <si>
+    <t>Trial Summary Parameter</t>
+  </si>
+  <si>
+    <t>Parameter Value</t>
+  </si>
+  <si>
+    <t>Parameter Null Flavor</t>
+  </si>
+  <si>
+    <t>Parameter Value Code</t>
+  </si>
+  <si>
+    <t>Name of the Reference Terminology</t>
+  </si>
+  <si>
+    <t>Version of the Reference Terminology</t>
+  </si>
+  <si>
+    <t>Char</t>
+  </si>
+  <si>
+    <t>Num</t>
+  </si>
+  <si>
+    <t>CDISCPILOT01</t>
+  </si>
+  <si>
+    <t>TS</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>INDIC</t>
+  </si>
+  <si>
+    <t>Extension Trial Indicator</t>
+  </si>
+  <si>
+    <t>Description term 2.</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <numFmts count="0"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -43,48 +150,40 @@
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
-      <b/>
+      <family val="2"/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
       <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <i/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
     <fill>
-      <patternFill patternType="none">
-        <bgColor/>
-      </patternFill>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="gray125">
-        <bgColor/>
-      </patternFill>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFFCC"/>
-        <bgColor/>
+        <fgColor rgb="FFFFFFCC"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -93,22 +192,29 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs>
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="1" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -433,235 +539,241 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="21" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="3" t="str">
-        <v>Product</v>
-      </c>
-      <c r="B1" s="3" t="str">
-        <v>Version</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="str">
-        <v>sdtmig</v>
-      </c>
-      <c r="B2" s="4" t="str">
-        <v>3-4</v>
+    <row r="1" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B2"/>
+    <ignoredError sqref="A1:B2" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="21" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="3" t="str">
-        <v>Filename</v>
-      </c>
-      <c r="B1" s="3" t="str">
-        <v>Label</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="str">
-        <v>ts.xpt</v>
-      </c>
-      <c r="B2" s="4" t="str">
-        <v>Trial Summary Parameters</v>
+    <row r="1" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B2"/>
+    <ignoredError sqref="A1:B2" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:K5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="21" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="3" t="str">
-        <v>STUDYID</v>
-      </c>
-      <c r="B1" s="3" t="str">
-        <v>DOMAIN</v>
-      </c>
-      <c r="C1" s="3" t="str">
-        <v>TSSEQ</v>
-      </c>
-      <c r="D1" s="3" t="str">
-        <v>TSGRPID</v>
-      </c>
-      <c r="E1" s="3" t="str">
-        <v>TSPARMCD</v>
-      </c>
-      <c r="F1" s="3" t="str">
-        <v>TSPARM</v>
-      </c>
-      <c r="G1" s="3" t="str">
-        <v>TSVAL</v>
-      </c>
-      <c r="H1" s="3" t="str">
-        <v>TSVALNF</v>
-      </c>
-      <c r="I1" s="3" t="str">
-        <v>TSVALCD</v>
-      </c>
-      <c r="J1" s="3" t="str">
-        <v>TSVCDREF</v>
-      </c>
-      <c r="K1" s="3" t="str">
-        <v>TSVCDVER</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="5" t="str">
-        <v>Study Identifier</v>
-      </c>
-      <c r="B2" s="5" t="str">
-        <v>Domain Abbreviation</v>
-      </c>
-      <c r="C2" s="5" t="str">
-        <v>Sequence Number</v>
-      </c>
-      <c r="D2" s="5" t="str">
-        <v>Group ID</v>
-      </c>
-      <c r="E2" s="5" t="str">
-        <v>Trial Summary Parameter Short Name</v>
-      </c>
-      <c r="F2" s="5" t="str">
-        <v>Trial Summary Parameter</v>
-      </c>
-      <c r="G2" s="5" t="str">
-        <v>Parameter Value</v>
-      </c>
-      <c r="H2" s="5" t="str">
-        <v>Parameter Null Flavor</v>
-      </c>
-      <c r="I2" s="5" t="str">
-        <v>Parameter Value Code</v>
-      </c>
-      <c r="J2" s="5" t="str">
-        <v>Name of the Reference Terminology</v>
-      </c>
-      <c r="K2" s="5" t="str">
-        <v>Version of the Reference Terminology</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="5" t="str">
-        <v>Char</v>
-      </c>
-      <c r="B3" s="5" t="str">
-        <v>Char</v>
-      </c>
-      <c r="C3" s="5" t="str">
-        <v>Num</v>
-      </c>
-      <c r="D3" s="5" t="str">
-        <v>Char</v>
-      </c>
-      <c r="E3" s="5" t="str">
-        <v>Char</v>
-      </c>
-      <c r="F3" s="5" t="str">
-        <v>Char</v>
-      </c>
-      <c r="G3" s="5" t="str">
-        <v>Char</v>
-      </c>
-      <c r="H3" s="5" t="str">
-        <v>Char</v>
-      </c>
-      <c r="I3" s="5" t="str">
-        <v>Char</v>
-      </c>
-      <c r="J3" s="5" t="str">
-        <v>Char</v>
-      </c>
-      <c r="K3" s="5" t="str">
-        <v>Char</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="5">
+    <row r="1" spans="1:11" ht="15" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="5">
+      <c r="D1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="15" x14ac:dyDescent="0.2">
+      <c r="A2" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="15" x14ac:dyDescent="0.2">
+      <c r="A3" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="15" x14ac:dyDescent="0.2">
+      <c r="A4" s="3">
+        <v>10</v>
+      </c>
+      <c r="B4" s="3">
         <v>2</v>
       </c>
-      <c r="C4" s="5">
+      <c r="C4" s="3">
         <v>8</v>
       </c>
-      <c r="D4" s="5">
+      <c r="D4" s="3">
         <v>5</v>
       </c>
-      <c r="E4" s="5">
+      <c r="E4" s="3">
         <v>8</v>
       </c>
-      <c r="F4" s="5">
+      <c r="F4" s="3">
         <v>40</v>
       </c>
-      <c r="G4" s="5">
+      <c r="G4" s="3">
         <v>149</v>
       </c>
-      <c r="H4" s="5">
+      <c r="H4" s="3">
         <v>2</v>
       </c>
-      <c r="I4" s="5">
+      <c r="I4" s="3">
         <v>11</v>
       </c>
-      <c r="J4" s="5">
+      <c r="J4" s="3">
         <v>18</v>
       </c>
-      <c r="K4" s="5">
+      <c r="K4" s="3">
         <v>10</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="4" t="str">
-        <v>CDISCPILOT01</v>
-      </c>
-      <c r="B5" s="4" t="str">
-        <v>TS</v>
-      </c>
-      <c r="C5" s="4">
+    <row r="5" spans="1:11" ht="15" x14ac:dyDescent="0.2">
+      <c r="A5" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C5" s="2">
         <v>1</v>
       </c>
-      <c r="D5" s="4" t="str">
-        <v/>
-      </c>
-      <c r="E5" s="4" t="str">
-        <v>INDIC</v>
-      </c>
-      <c r="F5" s="4" t="str">
-        <v>Extension Trial Indicator</v>
-      </c>
-      <c r="G5" s="4" t="str">
-        <v>TextDefinition term 1.</v>
-      </c>
-      <c r="H5" s="4" t="str">
-        <v/>
-      </c>
-      <c r="I5" s="4">
+      <c r="D5" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="I5" s="2">
         <v>1</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K5"/>
+    <ignoredError sqref="A1:K4 A5:F5 H5:K5" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/rules/NEW-RULE/positive/01/data/new-rule-positive-01.xlsx
+++ b/rules/NEW-RULE/positive/01/data/new-rule-positive-01.xlsx
@@ -1,40 +1,150 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10628"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/enrico/Work/core-contributor/rules/NEW-RULE/positive/01/data/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF68D225-271B-E144-ACBF-6928236211A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="30240" yWindow="-7000" windowWidth="51200" windowHeight="28800" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
     <sheet name="Library" sheetId="1" r:id="rId1"/>
     <sheet name="Datasets" sheetId="2" r:id="rId2"/>
     <sheet name="ts.xpt" sheetId="3" r:id="rId3"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="39">
+  <si>
+    <t>Product</t>
+  </si>
+  <si>
+    <t>Version</t>
+  </si>
+  <si>
+    <t>sdtmig</t>
+  </si>
+  <si>
+    <t>3-4</t>
+  </si>
+  <si>
+    <t>Filename</t>
+  </si>
+  <si>
+    <t>Label</t>
+  </si>
+  <si>
+    <t>ts.xpt</t>
+  </si>
+  <si>
+    <t>Trial Summary Parameters</t>
+  </si>
+  <si>
+    <t>STUDYID</t>
+  </si>
+  <si>
+    <t>DOMAIN</t>
+  </si>
+  <si>
+    <t>TSSEQ</t>
+  </si>
+  <si>
+    <t>TSGRPID</t>
+  </si>
+  <si>
+    <t>TSPARMCD</t>
+  </si>
+  <si>
+    <t>TSPARM</t>
+  </si>
+  <si>
+    <t>TSVAL</t>
+  </si>
+  <si>
+    <t>TSVALNF</t>
+  </si>
+  <si>
+    <t>TSVALCD</t>
+  </si>
+  <si>
+    <t>TSVCDREF</t>
+  </si>
+  <si>
+    <t>TSVCDVER</t>
+  </si>
+  <si>
+    <t>Study Identifier</t>
+  </si>
+  <si>
+    <t>Domain Abbreviation</t>
+  </si>
+  <si>
+    <t>Sequence Number</t>
+  </si>
+  <si>
+    <t>Group ID</t>
+  </si>
+  <si>
+    <t>Trial Summary Parameter Short Name</t>
+  </si>
+  <si>
+    <t>Trial Summary Parameter</t>
+  </si>
+  <si>
+    <t>Parameter Value</t>
+  </si>
+  <si>
+    <t>Parameter Null Flavor</t>
+  </si>
+  <si>
+    <t>Parameter Value Code</t>
+  </si>
+  <si>
+    <t>Name of the Reference Terminology</t>
+  </si>
+  <si>
+    <t>Version of the Reference Terminology</t>
+  </si>
+  <si>
+    <t>Char</t>
+  </si>
+  <si>
+    <t>Num</t>
+  </si>
+  <si>
+    <t>CDISCPILOT01</t>
+  </si>
+  <si>
+    <t>TS</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>INDIC</t>
+  </si>
+  <si>
+    <t>Extension Trial Indicator</t>
+  </si>
+  <si>
+    <t>Acetylcholine Activity Alteration</t>
+  </si>
+  <si>
+    <t>0000000003</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <numFmts count="0"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -43,48 +153,40 @@
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
-      <b/>
+      <family val="2"/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
       <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <i/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
     <fill>
-      <patternFill patternType="none">
-        <bgColor/>
-      </patternFill>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="gray125">
-        <bgColor/>
-      </patternFill>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFFCC"/>
-        <bgColor/>
+        <fgColor rgb="FFFFFFCC"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -93,22 +195,29 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs>
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="1" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -433,235 +542,241 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="3" t="str">
-        <v>Product</v>
-      </c>
-      <c r="B1" s="3" t="str">
-        <v>Version</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="str">
-        <v>sdtmig</v>
-      </c>
-      <c r="B2" s="4" t="str">
-        <v>3-4</v>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B2"/>
+    <ignoredError sqref="A1:B2" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="3" t="str">
-        <v>Filename</v>
-      </c>
-      <c r="B1" s="3" t="str">
-        <v>Label</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="str">
-        <v>ts.xpt</v>
-      </c>
-      <c r="B2" s="4" t="str">
-        <v>Trial Summary Parameters</v>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B2"/>
+    <ignoredError sqref="A1:B2" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:K5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="3" t="str">
-        <v>STUDYID</v>
-      </c>
-      <c r="B1" s="3" t="str">
-        <v>DOMAIN</v>
-      </c>
-      <c r="C1" s="3" t="str">
-        <v>TSSEQ</v>
-      </c>
-      <c r="D1" s="3" t="str">
-        <v>TSGRPID</v>
-      </c>
-      <c r="E1" s="3" t="str">
-        <v>TSPARMCD</v>
-      </c>
-      <c r="F1" s="3" t="str">
-        <v>TSPARM</v>
-      </c>
-      <c r="G1" s="3" t="str">
-        <v>TSVAL</v>
-      </c>
-      <c r="H1" s="3" t="str">
-        <v>TSVALNF</v>
-      </c>
-      <c r="I1" s="3" t="str">
-        <v>TSVALCD</v>
-      </c>
-      <c r="J1" s="3" t="str">
-        <v>TSVCDREF</v>
-      </c>
-      <c r="K1" s="3" t="str">
-        <v>TSVCDVER</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="5" t="str">
-        <v>Study Identifier</v>
-      </c>
-      <c r="B2" s="5" t="str">
-        <v>Domain Abbreviation</v>
-      </c>
-      <c r="C2" s="5" t="str">
-        <v>Sequence Number</v>
-      </c>
-      <c r="D2" s="5" t="str">
-        <v>Group ID</v>
-      </c>
-      <c r="E2" s="5" t="str">
-        <v>Trial Summary Parameter Short Name</v>
-      </c>
-      <c r="F2" s="5" t="str">
-        <v>Trial Summary Parameter</v>
-      </c>
-      <c r="G2" s="5" t="str">
-        <v>Parameter Value</v>
-      </c>
-      <c r="H2" s="5" t="str">
-        <v>Parameter Null Flavor</v>
-      </c>
-      <c r="I2" s="5" t="str">
-        <v>Parameter Value Code</v>
-      </c>
-      <c r="J2" s="5" t="str">
-        <v>Name of the Reference Terminology</v>
-      </c>
-      <c r="K2" s="5" t="str">
-        <v>Version of the Reference Terminology</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="5" t="str">
-        <v>Char</v>
-      </c>
-      <c r="B3" s="5" t="str">
-        <v>Char</v>
-      </c>
-      <c r="C3" s="5" t="str">
-        <v>Num</v>
-      </c>
-      <c r="D3" s="5" t="str">
-        <v>Char</v>
-      </c>
-      <c r="E3" s="5" t="str">
-        <v>Char</v>
-      </c>
-      <c r="F3" s="5" t="str">
-        <v>Char</v>
-      </c>
-      <c r="G3" s="5" t="str">
-        <v>Char</v>
-      </c>
-      <c r="H3" s="5" t="str">
-        <v>Char</v>
-      </c>
-      <c r="I3" s="5" t="str">
-        <v>Char</v>
-      </c>
-      <c r="J3" s="5" t="str">
-        <v>Char</v>
-      </c>
-      <c r="K3" s="5" t="str">
-        <v>Char</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="5">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="5">
+      <c r="D1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A2" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A3" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A4" s="3">
+        <v>10</v>
+      </c>
+      <c r="B4" s="3">
         <v>2</v>
       </c>
-      <c r="C4" s="5">
+      <c r="C4" s="3">
         <v>8</v>
       </c>
-      <c r="D4" s="5">
+      <c r="D4" s="3">
         <v>5</v>
       </c>
-      <c r="E4" s="5">
+      <c r="E4" s="3">
         <v>8</v>
       </c>
-      <c r="F4" s="5">
+      <c r="F4" s="3">
         <v>40</v>
       </c>
-      <c r="G4" s="5">
+      <c r="G4" s="3">
         <v>149</v>
       </c>
-      <c r="H4" s="5">
+      <c r="H4" s="3">
         <v>2</v>
       </c>
-      <c r="I4" s="5">
+      <c r="I4" s="3">
         <v>11</v>
       </c>
-      <c r="J4" s="5">
+      <c r="J4" s="3">
         <v>18</v>
       </c>
-      <c r="K4" s="5">
+      <c r="K4" s="3">
         <v>10</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="4" t="str">
-        <v>CDISCPILOT01</v>
-      </c>
-      <c r="B5" s="4" t="str">
-        <v>TS</v>
-      </c>
-      <c r="C5" s="4">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A5" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C5" s="2">
         <v>1</v>
       </c>
-      <c r="D5" s="4" t="str">
-        <v/>
-      </c>
-      <c r="E5" s="4" t="str">
-        <v>INDIC</v>
-      </c>
-      <c r="F5" s="4" t="str">
-        <v>Extension Trial Indicator</v>
-      </c>
-      <c r="G5" s="4" t="str">
-        <v>Acetylcholine Activity Alteration</v>
-      </c>
-      <c r="H5" s="4" t="str">
-        <v/>
-      </c>
-      <c r="I5" s="4" t="str">
-        <v>N0000008290</v>
+      <c r="D5" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>38</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K5"/>
+    <ignoredError sqref="A1:K4 A5:H5 J5:K5" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/rules/NEW-RULE/positive/01/data/new-rule-positive-01.xlsx
+++ b/rules/NEW-RULE/positive/01/data/new-rule-positive-01.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10621"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10628"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rich/Documents/github/core-contributor/rules/NEW-RULE/positive/01/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E10E07A-9942-694C-9BFB-F59AE453A0F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19A29F0B-9A0C-E54D-986F-CFC886110722}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38220" yWindow="-2260" windowWidth="30240" windowHeight="18980" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="175">
   <si>
     <t>Product</t>
   </si>
@@ -625,7 +625,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -634,7 +634,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -975,9 +974,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -985,7 +984,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -1004,9 +1003,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
@@ -1014,7 +1013,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
@@ -1022,7 +1021,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
         <v>173</v>
       </c>
@@ -1041,9 +1040,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:AA10"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:27" ht="15" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>8</v>
       </c>
@@ -1126,7 +1125,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="2" spans="1:27" ht="15" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
         <v>35</v>
       </c>
@@ -1209,7 +1208,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="3" spans="1:27" ht="15" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
         <v>62</v>
       </c>
@@ -1292,7 +1291,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="4" spans="1:27" ht="15" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A4" s="4">
         <v>10</v>
       </c>
@@ -1375,7 +1374,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:27" ht="15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>64</v>
       </c>
@@ -1458,7 +1457,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="6" spans="1:27" ht="15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>64</v>
       </c>
@@ -1541,7 +1540,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>64</v>
       </c>
@@ -1624,7 +1623,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="15" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>64</v>
       </c>
@@ -1707,7 +1706,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="15" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>64</v>
       </c>
@@ -1790,7 +1789,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="10" spans="1:27" ht="15" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>64</v>
       </c>
@@ -2223,22 +2222,22 @@
       <c r="E5" s="7" t="s">
         <v>146</v>
       </c>
-      <c r="F5" s="8">
+      <c r="F5" s="7">
         <v>43315</v>
       </c>
       <c r="G5" s="7" t="s">
         <v>146</v>
       </c>
-      <c r="H5" s="8">
+      <c r="H5" s="7">
         <v>43315</v>
       </c>
-      <c r="I5" s="8">
+      <c r="I5" s="7">
         <v>43216</v>
       </c>
-      <c r="J5" s="8">
+      <c r="J5" s="7">
         <v>43334</v>
       </c>
-      <c r="K5" s="8">
+      <c r="K5" s="7">
         <v>43334</v>
       </c>
       <c r="L5" s="7" t="s">
@@ -2277,7 +2276,6 @@
       <c r="W5" s="7" t="s">
         <v>153</v>
       </c>
-      <c r="X5" s="7"/>
       <c r="Y5" s="7"/>
       <c r="Z5" s="7" t="s">
         <v>154</v>
@@ -2299,22 +2297,22 @@
       <c r="E6" s="7" t="s">
         <v>156</v>
       </c>
-      <c r="F6" s="8">
+      <c r="F6" s="7">
         <v>43410</v>
       </c>
       <c r="G6" s="7" t="s">
         <v>156</v>
       </c>
-      <c r="H6" s="8">
+      <c r="H6" s="7">
         <v>43410</v>
       </c>
-      <c r="I6" s="8">
+      <c r="I6" s="7">
         <v>43227</v>
       </c>
-      <c r="J6" s="8">
+      <c r="J6" s="7">
         <v>43500</v>
       </c>
-      <c r="K6" s="8">
+      <c r="K6" s="7">
         <v>43500</v>
       </c>
       <c r="L6" s="7" t="s">
@@ -2351,7 +2349,9 @@
       <c r="W6" s="7" t="s">
         <v>159</v>
       </c>
-      <c r="X6" s="7"/>
+      <c r="X6" s="7" t="s">
+        <v>77</v>
+      </c>
       <c r="Y6" s="7"/>
       <c r="Z6" s="7" t="s">
         <v>154</v>
@@ -2370,22 +2370,22 @@
       <c r="D7" s="7">
         <v>1302</v>
       </c>
-      <c r="E7" s="8">
+      <c r="E7" s="7">
         <v>38733</v>
       </c>
-      <c r="F7" s="8">
+      <c r="F7" s="7">
         <v>38795</v>
       </c>
-      <c r="G7" s="8">
+      <c r="G7" s="7">
         <v>38733</v>
       </c>
-      <c r="H7" s="8">
+      <c r="H7" s="7">
         <v>38795</v>
       </c>
-      <c r="I7" s="8">
+      <c r="I7" s="7">
         <v>38719</v>
       </c>
-      <c r="J7" s="8">
+      <c r="J7" s="7">
         <v>38795</v>
       </c>
       <c r="K7" s="7"/>
@@ -2456,10 +2456,10 @@
       <c r="H8" s="7" t="s">
         <v>167</v>
       </c>
-      <c r="I8" s="8">
+      <c r="I8" s="7">
         <v>43278</v>
       </c>
-      <c r="J8" s="8">
+      <c r="J8" s="7">
         <v>43445</v>
       </c>
       <c r="K8" s="7"/>

--- a/rules/NEW-RULE/positive/01/data/new-rule-positive-01.xlsx
+++ b/rules/NEW-RULE/positive/01/data/new-rule-positive-01.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10621"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/enrico/Work/core-contributor/rules/NEW-RULE/positive/01/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A7537C1-7054-D540-A256-1C65524BF887}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E2423F8-D0A2-614F-91EA-C00FF827F37F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="30240" yWindow="-7000" windowWidth="51200" windowHeight="28800" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,14 +17,13 @@
     <sheet name="Datasets" sheetId="2" r:id="rId2"/>
     <sheet name="pc.xpt" sheetId="4" r:id="rId3"/>
     <sheet name="pp.xpt" sheetId="3" r:id="rId4"/>
-    <sheet name="relrec.xpt" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="405" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="99">
   <si>
     <t>Product</t>
   </si>
@@ -92,9 +91,6 @@
     <t>PCORRESU</t>
   </si>
   <si>
-    <t>8</t>
-  </si>
-  <si>
     <t>PC</t>
   </si>
   <si>
@@ -315,44 +311,6 @@
   </si>
   <si>
     <t>123-0002-13</t>
-  </si>
-  <si>
-    <t>RDOMAIN</t>
-  </si>
-  <si>
-    <t>IDVAR</t>
-  </si>
-  <si>
-    <t>IDVARVAL</t>
-  </si>
-  <si>
-    <t>RELTYPE</t>
-  </si>
-  <si>
-    <t>RELID</t>
-  </si>
-  <si>
-    <t>Identifying
-Variable</t>
-  </si>
-  <si>
-    <t>Identifying
-VariableValue</t>
-  </si>
-  <si>
-    <t>RelationshipType</t>
-  </si>
-  <si>
-    <t>RelationshipIdentifier</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>ONE</t>
   </si>
   <si>
     <t>relrec.xpt</t>
@@ -368,7 +326,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -399,16 +357,8 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="8">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -439,20 +389,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor rgb="FFD9D9D9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="4">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -460,54 +398,11 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFD9D9D9"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFD9D9D9"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFD9D9D9"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFD9D9D9"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFA5A5A5"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFA5A5A5"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFA5A5A5"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FFA5A5A5"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FFA5A5A5"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFA5A5A5"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FFA5A5A5"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
@@ -547,21 +442,6 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -963,26 +843,26 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B2" t="s">
         <v>25</v>
-      </c>
-      <c r="B2" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B3" t="s">
         <v>27</v>
-      </c>
-      <c r="B3" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>109</v>
+        <v>96</v>
       </c>
       <c r="B4" t="s">
-        <v>110</v>
+        <v>97</v>
       </c>
     </row>
   </sheetData>
@@ -1014,10 +894,10 @@
         <v>17</v>
       </c>
       <c r="E1" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="F1" s="9" t="s">
         <v>84</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>85</v>
       </c>
       <c r="G1" s="9" t="s">
         <v>18</v>
@@ -1026,10 +906,10 @@
         <v>19</v>
       </c>
       <c r="I1" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="J1" s="9" t="s">
         <v>86</v>
-      </c>
-      <c r="J1" s="9" t="s">
-        <v>87</v>
       </c>
       <c r="K1" s="9" t="s">
         <v>20</v>
@@ -1038,72 +918,72 @@
         <v>21</v>
       </c>
       <c r="M1" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="N1" s="9" t="s">
         <v>88</v>
       </c>
-      <c r="N1" s="9" t="s">
+      <c r="O1" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="P1" s="10" t="s">
         <v>89</v>
       </c>
-      <c r="O1" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="P1" s="10" t="s">
+      <c r="Q1" s="4" t="s">
         <v>90</v>
-      </c>
-      <c r="Q1" s="4" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="2" spans="1:17" ht="64" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="P2" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="J2" s="2" t="s">
+      <c r="Q2" s="2" t="s">
         <v>54</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="M2" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="N2" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="O2" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="P2" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q2" s="2" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="3" spans="1:17" ht="16" x14ac:dyDescent="0.2">
@@ -1173,81 +1053,81 @@
         <v>8</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F4" s="2">
         <v>20</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="N4" s="2">
         <v>8</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="Q4" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="5" spans="1:17" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" s="14" t="s">
         <v>57</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C5" s="14" t="s">
-        <v>58</v>
       </c>
       <c r="D5" s="6">
         <v>1</v>
       </c>
-      <c r="E5" s="19" t="s">
-        <v>60</v>
+      <c r="E5" s="14" t="s">
+        <v>59</v>
       </c>
       <c r="F5" s="14" t="s">
+        <v>92</v>
+      </c>
+      <c r="G5" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="G5" s="13" t="s">
+      <c r="H5" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="I5" s="14" t="s">
         <v>94</v>
       </c>
-      <c r="H5" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="I5" s="14" t="s">
-        <v>95</v>
-      </c>
       <c r="J5" s="14" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="K5" s="6">
         <v>9</v>
       </c>
       <c r="L5" s="6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M5" s="6">
         <v>9</v>
@@ -1256,51 +1136,51 @@
         <v>9</v>
       </c>
       <c r="O5" s="6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="P5" s="13" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="Q5" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="6" spans="1:17" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" s="14" t="s">
         <v>57</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C6" s="14" t="s">
-        <v>58</v>
       </c>
       <c r="D6" s="6">
         <v>3</v>
       </c>
       <c r="E6" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="F6" s="14" t="s">
+        <v>95</v>
+      </c>
+      <c r="G6" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="H6" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="F6" s="14" t="s">
-        <v>96</v>
-      </c>
-      <c r="G6" s="13" t="s">
+      <c r="I6" s="14" t="s">
         <v>94</v>
       </c>
-      <c r="H6" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="I6" s="14" t="s">
-        <v>95</v>
-      </c>
       <c r="J6" s="14" t="s">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="K6" s="6">
         <v>10</v>
       </c>
       <c r="L6" s="6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M6" s="6">
         <v>10</v>
@@ -1309,13 +1189,13 @@
         <v>10</v>
       </c>
       <c r="O6" s="6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="P6" s="13" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="Q6" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
   </sheetData>
@@ -1352,10 +1232,10 @@
         <v>9</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G1" s="4" t="s">
         <v>10</v>
@@ -1364,7 +1244,7 @@
         <v>11</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J1" s="4" t="s">
         <v>12</v>
@@ -1373,75 +1253,75 @@
         <v>13</v>
       </c>
       <c r="L1" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="M1" s="4" t="s">
+      <c r="N1" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="N1" s="4" t="s">
+      <c r="O1" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="O1" s="4" t="s">
+      <c r="P1" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q1" s="4" t="s">
         <v>34</v>
-      </c>
-      <c r="P1" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="Q1" s="4" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:17" ht="48" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="F2" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="G2" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="H2" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="I2" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="J2" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="K2" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="L2" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="M2" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="M2" s="2" t="s">
+      <c r="N2" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="N2" s="2" t="s">
+      <c r="O2" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="O2" s="2" t="s">
+      <c r="P2" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q2" s="2" t="s">
         <v>54</v>
-      </c>
-      <c r="P2" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q2" s="2" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="3" spans="1:17" ht="16" x14ac:dyDescent="0.2">
@@ -1511,78 +1391,78 @@
         <v>8</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M4" s="2">
         <v>8</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="Q4" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="5" spans="1:17" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B5" s="7" t="s">
         <v>16</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D5" s="6">
         <v>1</v>
       </c>
       <c r="E5" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="F5" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="F5" s="19" t="s">
+      <c r="G5" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="G5" s="6" t="s">
+      <c r="H5" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="H5" s="6" t="s">
+      <c r="I5" s="8" t="s">
         <v>62</v>
-      </c>
-      <c r="I5" s="8" t="s">
-        <v>63</v>
       </c>
       <c r="J5" s="6">
         <v>1.87</v>
       </c>
       <c r="K5" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="L5" s="6">
         <v>1.87</v>
@@ -1591,51 +1471,51 @@
         <v>1.87</v>
       </c>
       <c r="N5" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="O5" s="6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="P5" s="6">
         <v>1</v>
       </c>
       <c r="Q5" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="6" spans="1:17" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B6" s="7" t="s">
         <v>16</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D6" s="6">
         <v>2</v>
       </c>
       <c r="E6" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="F6" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="F6" s="19" t="s">
-        <v>60</v>
-      </c>
       <c r="G6" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="H6" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="H6" s="6" t="s">
-        <v>66</v>
-      </c>
       <c r="I6" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J6" s="6">
         <v>44.5</v>
       </c>
       <c r="K6" s="6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="L6" s="6">
         <v>44.5</v>
@@ -1644,51 +1524,51 @@
         <v>44.5</v>
       </c>
       <c r="N6" s="6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="O6" s="6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="P6" s="6">
         <v>1</v>
       </c>
       <c r="Q6" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="7" spans="1:17" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B7" s="7" t="s">
         <v>16</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D7" s="6">
         <v>3</v>
       </c>
       <c r="E7" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="F7" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="F7" s="19" t="s">
-        <v>60</v>
-      </c>
       <c r="G7" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="H7" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="H7" s="6" t="s">
-        <v>69</v>
-      </c>
       <c r="I7" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J7" s="6">
         <v>294.7</v>
       </c>
       <c r="K7" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="L7" s="6">
         <v>294.7</v>
@@ -1697,51 +1577,51 @@
         <v>294.7</v>
       </c>
       <c r="N7" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="O7" s="6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="P7" s="6">
         <v>1</v>
       </c>
       <c r="Q7" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="8" spans="1:17" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B8" s="7" t="s">
         <v>16</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D8" s="6">
         <v>4</v>
       </c>
       <c r="E8" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="F8" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="F8" s="19" t="s">
-        <v>60</v>
-      </c>
       <c r="G8" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="H8" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="H8" s="6" t="s">
-        <v>72</v>
-      </c>
       <c r="I8" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J8" s="6">
         <v>0.75</v>
       </c>
       <c r="K8" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="L8" s="6">
         <v>0.75</v>
@@ -1750,51 +1630,51 @@
         <v>0.75</v>
       </c>
       <c r="N8" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="O8" s="6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="P8" s="6">
         <v>1</v>
       </c>
       <c r="Q8" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="9" spans="1:17" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B9" s="7" t="s">
         <v>16</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D9" s="6">
         <v>5</v>
       </c>
       <c r="E9" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="F9" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="F9" s="19" t="s">
-        <v>60</v>
-      </c>
       <c r="G9" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="H9" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="H9" s="6" t="s">
-        <v>74</v>
-      </c>
       <c r="I9" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J9" s="6">
         <v>4.6900000000000004</v>
       </c>
       <c r="K9" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="L9" s="6">
         <v>4.6900000000000004</v>
@@ -1803,51 +1683,51 @@
         <v>4.6900000000000004</v>
       </c>
       <c r="N9" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="O9" s="6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="P9" s="6">
         <v>1</v>
       </c>
       <c r="Q9" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="10" spans="1:17" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B10" s="7" t="s">
         <v>16</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D10" s="6">
         <v>6</v>
       </c>
       <c r="E10" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="F10" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="F10" s="19" t="s">
-        <v>60</v>
-      </c>
       <c r="G10" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="H10" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="H10" s="6" t="s">
-        <v>76</v>
-      </c>
       <c r="I10" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J10" s="6">
         <v>10.9</v>
       </c>
       <c r="K10" s="6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="L10" s="6">
         <v>10.9</v>
@@ -1856,51 +1736,51 @@
         <v>10.9</v>
       </c>
       <c r="N10" s="6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="O10" s="6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="P10" s="6">
         <v>1</v>
       </c>
       <c r="Q10" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="11" spans="1:17" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B11" s="7" t="s">
         <v>16</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D11" s="6">
         <v>7</v>
       </c>
       <c r="E11" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="F11" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="F11" s="19" t="s">
-        <v>60</v>
-      </c>
       <c r="G11" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="H11" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="H11" s="6" t="s">
-        <v>79</v>
-      </c>
       <c r="I11" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J11" s="6">
         <v>1.68</v>
       </c>
       <c r="K11" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L11" s="6">
         <v>1.68</v>
@@ -1909,51 +1789,51 @@
         <v>1.68</v>
       </c>
       <c r="N11" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="O11" s="6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="P11" s="6">
         <v>8</v>
       </c>
       <c r="Q11" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="12" spans="1:17" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B12" s="7" t="s">
         <v>16</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D12" s="6">
         <v>8</v>
       </c>
       <c r="E12" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="F12" s="14" t="s">
         <v>81</v>
       </c>
-      <c r="F12" s="19" t="s">
+      <c r="G12" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="H12" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="I12" s="8" t="s">
         <v>82</v>
-      </c>
-      <c r="G12" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="H12" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="I12" s="8" t="s">
-        <v>83</v>
       </c>
       <c r="J12" s="6">
         <v>1.91</v>
       </c>
       <c r="K12" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="L12" s="6">
         <v>1.91</v>
@@ -1962,51 +1842,51 @@
         <v>1.91</v>
       </c>
       <c r="N12" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="O12" s="6" t="s">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="P12" s="6">
         <v>8</v>
       </c>
       <c r="Q12" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="13" spans="1:17" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>16</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D13" s="6">
         <v>9</v>
       </c>
       <c r="E13" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="F13" s="14" t="s">
         <v>81</v>
       </c>
-      <c r="F13" s="19" t="s">
+      <c r="G13" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="H13" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="I13" s="8" t="s">
         <v>82</v>
-      </c>
-      <c r="G13" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="H13" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="I13" s="8" t="s">
-        <v>83</v>
       </c>
       <c r="J13" s="6">
         <v>46</v>
       </c>
       <c r="K13" s="6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="L13" s="6">
         <v>46</v>
@@ -2015,51 +1895,51 @@
         <v>46</v>
       </c>
       <c r="N13" s="6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="O13" s="6" t="s">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="P13" s="6">
         <v>8</v>
       </c>
       <c r="Q13" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="14" spans="1:17" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B14" s="7" t="s">
         <v>16</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D14" s="6">
         <v>10</v>
       </c>
       <c r="E14" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="F14" s="14" t="s">
         <v>81</v>
       </c>
-      <c r="F14" s="19" t="s">
+      <c r="G14" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="H14" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="I14" s="8" t="s">
         <v>82</v>
-      </c>
-      <c r="G14" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="H14" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="I14" s="8" t="s">
-        <v>83</v>
       </c>
       <c r="J14" s="6">
         <v>289</v>
       </c>
       <c r="K14" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="L14" s="6">
         <v>289</v>
@@ -2068,51 +1948,51 @@
         <v>289</v>
       </c>
       <c r="N14" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="O14" s="6" t="s">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="P14" s="6">
         <v>8</v>
       </c>
       <c r="Q14" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="15" spans="1:17" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B15" s="7" t="s">
         <v>16</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D15" s="6">
         <v>11</v>
       </c>
       <c r="E15" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="F15" s="14" t="s">
         <v>81</v>
       </c>
-      <c r="F15" s="19" t="s">
+      <c r="G15" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="H15" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="I15" s="8" t="s">
         <v>82</v>
-      </c>
-      <c r="G15" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="H15" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="I15" s="8" t="s">
-        <v>83</v>
       </c>
       <c r="J15" s="6">
         <v>0.77</v>
       </c>
       <c r="K15" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="L15" s="6">
         <v>0.77</v>
@@ -2121,51 +2001,51 @@
         <v>0.77</v>
       </c>
       <c r="N15" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="O15" s="6" t="s">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="P15" s="6">
         <v>8</v>
       </c>
       <c r="Q15" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="16" spans="1:17" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B16" s="7" t="s">
         <v>16</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D16" s="6">
         <v>12</v>
       </c>
       <c r="E16" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="F16" s="14" t="s">
         <v>81</v>
       </c>
-      <c r="F16" s="19" t="s">
+      <c r="G16" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="H16" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="I16" s="8" t="s">
         <v>82</v>
-      </c>
-      <c r="G16" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="H16" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="I16" s="8" t="s">
-        <v>83</v>
       </c>
       <c r="J16" s="6">
         <v>4.5</v>
       </c>
       <c r="K16" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="L16" s="6">
         <v>4.5</v>
@@ -2174,16 +2054,16 @@
         <v>4.5</v>
       </c>
       <c r="N16" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="O16" s="6" t="s">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="P16" s="6">
         <v>8</v>
       </c>
       <c r="Q16" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
   </sheetData>
@@ -2194,431 +2074,4 @@
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C2DFA22-7454-AA4B-BC49-0F3BD2B98BB8}">
-  <dimension ref="A1:G18"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="3" max="3" width="14.5" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="B1" s="16" t="s">
-        <v>97</v>
-      </c>
-      <c r="C1" s="16" t="s">
-        <v>8</v>
-      </c>
-      <c r="D1" s="16" t="s">
-        <v>98</v>
-      </c>
-      <c r="E1" s="16" t="s">
-        <v>99</v>
-      </c>
-      <c r="F1" s="16" t="s">
-        <v>100</v>
-      </c>
-      <c r="G1" s="16" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="48" x14ac:dyDescent="0.2">
-      <c r="A2" s="17" t="s">
-        <v>40</v>
-      </c>
-      <c r="B2" s="17" t="s">
-        <v>41</v>
-      </c>
-      <c r="C2" s="17" t="s">
-        <v>42</v>
-      </c>
-      <c r="D2" s="17" t="s">
-        <v>102</v>
-      </c>
-      <c r="E2" s="17" t="s">
-        <v>103</v>
-      </c>
-      <c r="F2" s="17" t="s">
-        <v>104</v>
-      </c>
-      <c r="G2" s="17" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="16" x14ac:dyDescent="0.2">
-      <c r="A3" s="18" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3" s="18" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" s="18" t="s">
-        <v>14</v>
-      </c>
-      <c r="D3" s="18" t="s">
-        <v>14</v>
-      </c>
-      <c r="E3" s="18" t="s">
-        <v>14</v>
-      </c>
-      <c r="F3" s="18" t="s">
-        <v>14</v>
-      </c>
-      <c r="G3" s="18" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="16" x14ac:dyDescent="0.2">
-      <c r="A4" s="17" t="s">
-        <v>106</v>
-      </c>
-      <c r="B4" s="17" t="s">
-        <v>107</v>
-      </c>
-      <c r="C4" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="D4" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="E4" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="F4" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="G4" s="17" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="C5" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="D5" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="E5" s="13">
-        <v>1</v>
-      </c>
-      <c r="F5" s="13" t="s">
-        <v>108</v>
-      </c>
-      <c r="G5" s="13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="D6" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="E6" s="13">
-        <v>1</v>
-      </c>
-      <c r="F6" s="13" t="s">
-        <v>108</v>
-      </c>
-      <c r="G6" s="13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="D7" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="E7" s="13">
-        <v>2</v>
-      </c>
-      <c r="F7" s="13" t="s">
-        <v>108</v>
-      </c>
-      <c r="G7" s="13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="C8" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="D8" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="E8" s="13">
-        <v>3</v>
-      </c>
-      <c r="F8" s="13" t="s">
-        <v>108</v>
-      </c>
-      <c r="G8" s="13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="C9" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="D9" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="E9" s="13">
-        <v>4</v>
-      </c>
-      <c r="F9" s="13" t="s">
-        <v>108</v>
-      </c>
-      <c r="G9" s="13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="C10" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="D10" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="E10" s="13">
-        <v>5</v>
-      </c>
-      <c r="F10" s="13" t="s">
-        <v>108</v>
-      </c>
-      <c r="G10" s="13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="C11" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="D11" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="E11" s="13">
-        <v>6</v>
-      </c>
-      <c r="F11" s="13" t="s">
-        <v>108</v>
-      </c>
-      <c r="G11" s="13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="C12" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="D12" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="E12" s="13">
-        <v>7</v>
-      </c>
-      <c r="F12" s="13" t="s">
-        <v>108</v>
-      </c>
-      <c r="G12" s="13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="C13" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="D13" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="E13" s="13">
-        <v>3</v>
-      </c>
-      <c r="F13" s="13" t="s">
-        <v>108</v>
-      </c>
-      <c r="G13" s="13">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="C14" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="D14" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="E14" s="13">
-        <v>8</v>
-      </c>
-      <c r="F14" s="13" t="s">
-        <v>108</v>
-      </c>
-      <c r="G14" s="13">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="B15" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="C15" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="D15" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="E15" s="13">
-        <v>9</v>
-      </c>
-      <c r="F15" s="13" t="s">
-        <v>108</v>
-      </c>
-      <c r="G15" s="13">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="C16" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="D16" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="E16" s="13">
-        <v>10</v>
-      </c>
-      <c r="F16" s="13" t="s">
-        <v>108</v>
-      </c>
-      <c r="G16" s="13">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="C17" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="D17" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="E17" s="13">
-        <v>11</v>
-      </c>
-      <c r="F17" s="13" t="s">
-        <v>108</v>
-      </c>
-      <c r="G17" s="13">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="C18" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="D18" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="E18" s="13">
-        <v>12</v>
-      </c>
-      <c r="F18" s="13" t="s">
-        <v>108</v>
-      </c>
-      <c r="G18" s="13">
-        <v>2</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/rules/NEW-RULE/positive/01/data/new-rule-positive-01.xlsx
+++ b/rules/NEW-RULE/positive/01/data/new-rule-positive-01.xlsx
@@ -1,40 +1,126 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10821"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rich/Documents/github/core-contributor/rules/NEW-RULE/positive/01/data/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DD228D5-C828-C448-80AF-38B85F84445D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
     <sheet name="Library" sheetId="1" r:id="rId1"/>
     <sheet name="Datasets" sheetId="2" r:id="rId2"/>
     <sheet name="cm.xpt" sheetId="3" r:id="rId3"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="31">
+  <si>
+    <t>Product</t>
+  </si>
+  <si>
+    <t>Version</t>
+  </si>
+  <si>
+    <t>sdtmig</t>
+  </si>
+  <si>
+    <t>3-4</t>
+  </si>
+  <si>
+    <t>Filename</t>
+  </si>
+  <si>
+    <t>Label</t>
+  </si>
+  <si>
+    <t>cm.xpt</t>
+  </si>
+  <si>
+    <t>Concomitant Medications</t>
+  </si>
+  <si>
+    <t>STUDYID</t>
+  </si>
+  <si>
+    <t>DOMAIN</t>
+  </si>
+  <si>
+    <t>USUBJID</t>
+  </si>
+  <si>
+    <t>CMSEQ</t>
+  </si>
+  <si>
+    <t>CMDECOD</t>
+  </si>
+  <si>
+    <t>Study Identifier</t>
+  </si>
+  <si>
+    <t>Domain Abbreviation</t>
+  </si>
+  <si>
+    <t>Unique Subject Identifier</t>
+  </si>
+  <si>
+    <t>Sequence Number</t>
+  </si>
+  <si>
+    <t>Standardized Medication Name</t>
+  </si>
+  <si>
+    <t>Char</t>
+  </si>
+  <si>
+    <t>Num</t>
+  </si>
+  <si>
+    <t>STUDY001</t>
+  </si>
+  <si>
+    <t>CM</t>
+  </si>
+  <si>
+    <t>STUDY001-SUBJ0001</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>STUDY001-SUBJ0003</t>
+  </si>
+  <si>
+    <t>Metronidazole</t>
+  </si>
+  <si>
+    <t>STUDY001-SUBJ0005</t>
+  </si>
+  <si>
+    <t>NAPROXEN</t>
+  </si>
+  <si>
+    <t>STUDY001-SUBJ0007</t>
+  </si>
+  <si>
+    <t>STUDY001-SUBJ0009</t>
+  </si>
+  <si>
+    <t>Cetirizine</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <numFmts count="0"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -43,48 +129,40 @@
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
       <name val="Calibri"/>
-      <b/>
+      <family val="2"/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
       <name val="Calibri"/>
-      <i/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
     <fill>
-      <patternFill patternType="none">
-        <bgColor/>
-      </patternFill>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="gray125">
-        <bgColor/>
-      </patternFill>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
-        <bgColor/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -93,22 +171,29 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs>
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="1" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -433,246 +518,225 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="3" t="str">
-        <v>Product</v>
-      </c>
-      <c r="B1" s="3" t="str">
-        <v>Version</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="3" t="str">
-        <v>sdtmig</v>
-      </c>
-      <c r="B2" s="3" t="str">
-        <v>3-4</v>
+    <row r="1" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B2"/>
+    <ignoredError sqref="A1:B2" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="3" t="str">
-        <v>Filename</v>
-      </c>
-      <c r="B1" s="3" t="str">
-        <v>Label</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="3" t="str">
-        <v>cm.xpt</v>
-      </c>
-      <c r="B2" s="3" t="str">
-        <v>Concomitant Medications</v>
+    <row r="1" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B2"/>
+    <ignoredError sqref="A1:B2" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F9"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:E9"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="4" t="str">
-        <v>STUDYID</v>
-      </c>
-      <c r="B1" s="4" t="str">
-        <v>DOMAIN</v>
-      </c>
-      <c r="C1" s="4" t="str">
-        <v>USUBJID</v>
-      </c>
-      <c r="D1" s="4" t="str">
-        <v>CMSEQ</v>
-      </c>
-      <c r="E1" s="4" t="str">
-        <v>CMTRT</v>
-      </c>
-      <c r="F1" s="4" t="str">
-        <v>CMDECOD</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="5" t="str">
-        <v>Study Identifier</v>
-      </c>
-      <c r="B2" s="5" t="str">
-        <v>Domain Abbreviation</v>
-      </c>
-      <c r="C2" s="5" t="str">
-        <v>Unique Subject Identifier</v>
-      </c>
-      <c r="D2" s="5" t="str">
-        <v>Sequence Number</v>
-      </c>
-      <c r="E2" s="5" t="str">
-        <v>Reported Name of Drug, Med, or Therapy</v>
-      </c>
-      <c r="F2" s="5" t="str">
-        <v>Standardized Medication Name</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="5" t="str">
-        <v>Char</v>
-      </c>
-      <c r="B3" s="5" t="str">
-        <v>Char</v>
-      </c>
-      <c r="C3" s="5" t="str">
-        <v>Char</v>
-      </c>
-      <c r="D3" s="5" t="str">
-        <v>Num</v>
-      </c>
-      <c r="E3" s="5" t="str">
-        <v>Char</v>
-      </c>
-      <c r="F3" s="5" t="str">
-        <v>Char</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A3" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A4" s="3">
         <v>50</v>
       </c>
-      <c r="B4" s="5">
+      <c r="B4" s="3">
         <v>50</v>
       </c>
-      <c r="C4" s="5">
+      <c r="C4" s="3">
         <v>50</v>
       </c>
-      <c r="D4" s="5">
+      <c r="D4" s="3">
         <v>8</v>
       </c>
-      <c r="E4" s="5">
+      <c r="E4" s="3">
         <v>50</v>
       </c>
-      <c r="F4" s="5">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="str">
-        <v>STUDY001</v>
-      </c>
-      <c r="B5" s="3" t="str">
-        <v>CM</v>
-      </c>
-      <c r="C5" s="3" t="str">
-        <v>STUDY001-SUBJ0001</v>
-      </c>
-      <c r="D5" s="3">
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A5" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" s="1">
         <v>1</v>
       </c>
-      <c r="E5" s="3" t="str">
-        <v>PLACEBO CETIRIZINE</v>
-      </c>
-      <c r="F5" s="3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="str">
-        <v>STUDY001</v>
-      </c>
-      <c r="B6" s="3" t="str">
-        <v>CM</v>
-      </c>
-      <c r="C6" s="3" t="str">
-        <v>STUDY001-SUBJ0003</v>
-      </c>
-      <c r="D6" s="3">
+      <c r="E5" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A6" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D6" s="1">
         <v>1</v>
       </c>
-      <c r="E6" s="3" t="str">
-        <v>Metronidazole</v>
-      </c>
-      <c r="F6" s="3" t="str">
-        <v>Metronidazole</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="str">
-        <v>STUDY001</v>
-      </c>
-      <c r="B7" s="3" t="str">
-        <v>CM</v>
-      </c>
-      <c r="C7" s="3" t="str">
-        <v>STUDY001-SUBJ0005</v>
-      </c>
-      <c r="D7" s="3">
+      <c r="E6" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A7" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" s="1">
         <v>1</v>
       </c>
-      <c r="E7" s="3" t="str">
-        <v>NAPROXEN</v>
-      </c>
-      <c r="F7" s="3" t="str">
-        <v>N</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="str">
-        <v>STUDY001</v>
-      </c>
-      <c r="B8" s="3" t="str">
-        <v>CM</v>
-      </c>
-      <c r="C8" s="3" t="str">
-        <v>STUDY001-SUBJ0007</v>
-      </c>
-      <c r="D8" s="3">
+      <c r="E7" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A8" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D8" s="1">
         <v>1</v>
       </c>
-      <c r="E8" s="3" t="str">
-        <v/>
-      </c>
-      <c r="F8" s="3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="str">
-        <v>STUDY001</v>
-      </c>
-      <c r="B9" s="3" t="str">
-        <v>CM</v>
-      </c>
-      <c r="C9" s="3" t="str">
-        <v>STUDY001-SUBJ0009</v>
-      </c>
-      <c r="D9" s="3">
+      <c r="E8" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A9" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D9" s="1">
         <v>1</v>
       </c>
-      <c r="E9" s="3" t="str">
-        <v/>
-      </c>
-      <c r="F9" s="3" t="str">
-        <v>Cetirizine</v>
+      <c r="E9" s="1" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F9"/>
+    <ignoredError sqref="A1:D9 E1:E6 E8:E9" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>